--- a/calendrier.xlsx
+++ b/calendrier.xlsx
@@ -358,14 +358,17 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -380,22 +383,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -430,13 +424,19 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="7" t="n"/>
-      <c r="X4" s="16" t="inlineStr">
+      <c r="X4" s="18" t="inlineStr">
         <is>
           <t>WE Engagés ccn</t>
         </is>
@@ -1065,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="12" t="n"/>
-      <c r="AB4" s="18" t="n"/>
+      <c r="AB4" s="19" t="n"/>
       <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="7" t="n"/>
-      <c r="AF4" s="18" t="n"/>
+      <c r="AF4" s="19" t="n"/>
       <c r="AG4" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1085,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="AI4" s="12" t="n"/>
-      <c r="AJ4" s="17" t="inlineStr">
+      <c r="AJ4" s="20" t="inlineStr">
         <is>
           <t>Fête du travail</t>
         </is>
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="AM4" s="7" t="n"/>
-      <c r="AN4" s="19" t="inlineStr">
+      <c r="AN4" s="16" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="18" t="n"/>
+      <c r="AR4" s="19" t="n"/>
       <c r="AS4" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1123,103 +1123,115 @@
         <v>1</v>
       </c>
       <c r="AU4" s="12" t="n"/>
-      <c r="AV4" s="20" t="n"/>
+      <c r="AV4" s="21" t="n"/>
     </row>
     <row r="5" ht="20.1" customHeight="1">
-      <c r="A5" s="21" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="23" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="K5" s="24" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="O5" s="22" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="21" t="n"/>
-      <c r="S5" s="24" t="n"/>
-      <c r="T5" s="23" t="n"/>
-      <c r="U5" s="21" t="n"/>
-      <c r="W5" s="22" t="n"/>
-      <c r="X5" s="23" t="n"/>
-      <c r="Y5" s="21" t="n"/>
-      <c r="AA5" s="24" t="n"/>
-      <c r="AB5" s="26" t="n"/>
-      <c r="AC5" s="21" t="n"/>
-      <c r="AE5" s="22" t="n"/>
-      <c r="AF5" s="26" t="n"/>
-      <c r="AG5" s="21" t="n"/>
-      <c r="AI5" s="24" t="n"/>
-      <c r="AJ5" s="23" t="n"/>
-      <c r="AK5" s="21" t="n"/>
-      <c r="AM5" s="22" t="n"/>
-      <c r="AN5" s="25" t="n"/>
-      <c r="AO5" s="21" t="n"/>
-      <c r="AQ5" s="22" t="n"/>
-      <c r="AR5" s="26" t="n"/>
-      <c r="AS5" s="21" t="n"/>
-      <c r="AU5" s="24" t="n"/>
-      <c r="AV5" s="27" t="n"/>
+      <c r="A5" s="22" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="24" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="26" t="n"/>
+      <c r="M5" s="22" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Q5" s="22" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
+      <c r="U5" s="22" t="n"/>
+      <c r="W5" s="23" t="n"/>
+      <c r="X5" s="24" t="n"/>
+      <c r="Y5" s="22" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="27" t="n"/>
+      <c r="AC5" s="22" t="n"/>
+      <c r="AE5" s="23" t="n"/>
+      <c r="AF5" s="27" t="n"/>
+      <c r="AG5" s="22" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="24" t="n"/>
+      <c r="AK5" s="22" t="n"/>
+      <c r="AM5" s="23" t="n"/>
+      <c r="AN5" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="AO5" s="22" t="n"/>
+      <c r="AQ5" s="23" t="n"/>
+      <c r="AR5" s="27" t="n"/>
+      <c r="AS5" s="22" t="n"/>
+      <c r="AU5" s="25" t="n"/>
+      <c r="AV5" s="28" t="n"/>
     </row>
     <row r="6" ht="20.1" customHeight="1">
-      <c r="A6" s="28" t="n"/>
-      <c r="B6" s="29" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="29" t="n"/>
-      <c r="K6" s="31" t="n"/>
-      <c r="L6" s="32" t="inlineStr">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="31" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="30" t="n"/>
+      <c r="K6" s="32" t="n"/>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>Toussaint</t>
         </is>
       </c>
-      <c r="M6" s="28" t="n"/>
-      <c r="N6" s="29" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="25" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="29" t="n"/>
-      <c r="S6" s="31" t="n"/>
-      <c r="T6" s="25" t="n"/>
-      <c r="U6" s="28" t="n"/>
-      <c r="V6" s="29" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="25" t="n"/>
-      <c r="Y6" s="28" t="n"/>
-      <c r="Z6" s="29" t="n"/>
-      <c r="AA6" s="31" t="n"/>
+      <c r="M6" s="29" t="n"/>
+      <c r="N6" s="30" t="n"/>
+      <c r="O6" s="31" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="29" t="n"/>
+      <c r="R6" s="30" t="n"/>
+      <c r="S6" s="32" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="29" t="n"/>
+      <c r="V6" s="30" t="n"/>
+      <c r="W6" s="31" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="29" t="n"/>
+      <c r="Z6" s="30" t="n"/>
+      <c r="AA6" s="32" t="n"/>
       <c r="AB6" s="33" t="n"/>
-      <c r="AC6" s="28" t="n"/>
-      <c r="AD6" s="29" t="n"/>
-      <c r="AE6" s="30" t="n"/>
+      <c r="AC6" s="29" t="n"/>
+      <c r="AD6" s="30" t="n"/>
+      <c r="AE6" s="31" t="n"/>
       <c r="AF6" s="33" t="n"/>
-      <c r="AG6" s="28" t="n"/>
-      <c r="AH6" s="29" t="n"/>
-      <c r="AI6" s="31" t="n"/>
-      <c r="AJ6" s="25" t="n"/>
-      <c r="AK6" s="28" t="n"/>
-      <c r="AL6" s="29" t="n"/>
-      <c r="AM6" s="30" t="n"/>
-      <c r="AN6" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="AO6" s="28" t="n"/>
-      <c r="AP6" s="29" t="n"/>
-      <c r="AQ6" s="30" t="n"/>
+      <c r="AG6" s="29" t="n"/>
+      <c r="AH6" s="30" t="n"/>
+      <c r="AI6" s="32" t="n"/>
+      <c r="AJ6" s="26" t="n"/>
+      <c r="AK6" s="29" t="n"/>
+      <c r="AL6" s="30" t="n"/>
+      <c r="AM6" s="31" t="n"/>
+      <c r="AN6" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AO6" s="29" t="n"/>
+      <c r="AP6" s="30" t="n"/>
+      <c r="AQ6" s="31" t="n"/>
       <c r="AR6" s="33" t="n"/>
-      <c r="AS6" s="28" t="n"/>
-      <c r="AT6" s="29" t="n"/>
-      <c r="AU6" s="31" t="n"/>
-      <c r="AV6" s="35" t="n"/>
+      <c r="AS6" s="29" t="n"/>
+      <c r="AT6" s="30" t="n"/>
+      <c r="AU6" s="32" t="n"/>
+      <c r="AV6" s="34" t="n"/>
     </row>
     <row r="7" ht="20.1" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1231,7 +1243,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="D7" s="19" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1241,7 +1253,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="36" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -1255,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="7" t="n"/>
-      <c r="L7" s="37" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>Défunts</t>
         </is>
@@ -1269,7 +1281,7 @@
         <v>2</v>
       </c>
       <c r="O7" s="7" t="n"/>
-      <c r="P7" s="18" t="n"/>
+      <c r="P7" s="19" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1279,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="S7" s="12" t="n"/>
-      <c r="T7" s="18" t="n"/>
+      <c r="T7" s="19" t="n"/>
       <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -1303,7 +1315,11 @@
         <v>2</v>
       </c>
       <c r="AA7" s="12" t="n"/>
-      <c r="AB7" s="18" t="n"/>
+      <c r="AB7" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1313,7 +1329,11 @@
         <v>2</v>
       </c>
       <c r="AE7" s="7" t="n"/>
-      <c r="AF7" s="18" t="n"/>
+      <c r="AF7" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="AG7" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1323,7 +1343,7 @@
         <v>2</v>
       </c>
       <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="20" t="n"/>
+      <c r="AJ7" s="21" t="n"/>
       <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1333,7 +1353,7 @@
         <v>2</v>
       </c>
       <c r="AM7" s="7" t="n"/>
-      <c r="AN7" s="18" t="n"/>
+      <c r="AN7" s="19" t="n"/>
       <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1343,7 +1363,11 @@
         <v>2</v>
       </c>
       <c r="AQ7" s="7" t="n"/>
-      <c r="AR7" s="18" t="n"/>
+      <c r="AR7" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="AS7" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -1353,98 +1377,102 @@
         <v>2</v>
       </c>
       <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="18" t="n"/>
+      <c r="AV7" s="19" t="n"/>
     </row>
     <row r="8" ht="20.1" customHeight="1">
-      <c r="A8" s="21" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="34" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t>Messe des défunts</t>
         </is>
       </c>
-      <c r="M8" s="21" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="26" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="26" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="23" t="n"/>
-      <c r="Y8" s="21" t="n"/>
-      <c r="AA8" s="24" t="n"/>
-      <c r="AB8" s="26" t="n"/>
-      <c r="AC8" s="21" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="26" t="n"/>
-      <c r="AG8" s="21" t="n"/>
-      <c r="AI8" s="24" t="n"/>
-      <c r="AJ8" s="27" t="n"/>
-      <c r="AK8" s="21" t="n"/>
-      <c r="AM8" s="22" t="n"/>
-      <c r="AN8" s="26" t="n"/>
-      <c r="AO8" s="21" t="n"/>
-      <c r="AQ8" s="22" t="n"/>
-      <c r="AR8" s="26" t="n"/>
-      <c r="AS8" s="21" t="n"/>
-      <c r="AU8" s="24" t="n"/>
-      <c r="AV8" s="26" t="n"/>
+      <c r="M8" s="22" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="27" t="n"/>
+      <c r="Q8" s="22" t="n"/>
+      <c r="S8" s="25" t="n"/>
+      <c r="T8" s="27" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="W8" s="23" t="n"/>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Y8" s="22" t="n"/>
+      <c r="AA8" s="25" t="n"/>
+      <c r="AB8" s="24" t="n"/>
+      <c r="AC8" s="22" t="n"/>
+      <c r="AE8" s="23" t="n"/>
+      <c r="AF8" s="24" t="n"/>
+      <c r="AG8" s="22" t="n"/>
+      <c r="AI8" s="25" t="n"/>
+      <c r="AJ8" s="28" t="n"/>
+      <c r="AK8" s="22" t="n"/>
+      <c r="AM8" s="23" t="n"/>
+      <c r="AN8" s="27" t="n"/>
+      <c r="AO8" s="22" t="n"/>
+      <c r="AQ8" s="23" t="n"/>
+      <c r="AR8" s="24" t="n"/>
+      <c r="AS8" s="22" t="n"/>
+      <c r="AU8" s="25" t="n"/>
+      <c r="AV8" s="27" t="n"/>
     </row>
     <row r="9" ht="20.1" customHeight="1">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="30" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="31" t="n"/>
       <c r="D9" s="33" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="38" t="n"/>
-      <c r="M9" s="28" t="n"/>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="30" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="31" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="30" t="n"/>
+      <c r="O9" s="31" t="n"/>
       <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="31" t="n"/>
+      <c r="Q9" s="29" t="n"/>
+      <c r="R9" s="30" t="n"/>
+      <c r="S9" s="32" t="n"/>
       <c r="T9" s="33" t="n"/>
-      <c r="U9" s="28" t="n"/>
-      <c r="V9" s="29" t="n"/>
-      <c r="W9" s="30" t="n"/>
-      <c r="X9" s="25" t="n"/>
-      <c r="Y9" s="28" t="n"/>
-      <c r="Z9" s="29" t="n"/>
-      <c r="AA9" s="31" t="n"/>
-      <c r="AB9" s="33" t="n"/>
-      <c r="AC9" s="28" t="n"/>
-      <c r="AD9" s="29" t="n"/>
-      <c r="AE9" s="30" t="n"/>
-      <c r="AF9" s="33" t="n"/>
-      <c r="AG9" s="28" t="n"/>
-      <c r="AH9" s="29" t="n"/>
-      <c r="AI9" s="31" t="n"/>
-      <c r="AJ9" s="35" t="n"/>
-      <c r="AK9" s="28" t="n"/>
-      <c r="AL9" s="29" t="n"/>
-      <c r="AM9" s="30" t="n"/>
+      <c r="U9" s="29" t="n"/>
+      <c r="V9" s="30" t="n"/>
+      <c r="W9" s="31" t="n"/>
+      <c r="X9" s="33" t="n"/>
+      <c r="Y9" s="29" t="n"/>
+      <c r="Z9" s="30" t="n"/>
+      <c r="AA9" s="32" t="n"/>
+      <c r="AB9" s="26" t="n"/>
+      <c r="AC9" s="29" t="n"/>
+      <c r="AD9" s="30" t="n"/>
+      <c r="AE9" s="31" t="n"/>
+      <c r="AF9" s="26" t="n"/>
+      <c r="AG9" s="29" t="n"/>
+      <c r="AH9" s="30" t="n"/>
+      <c r="AI9" s="32" t="n"/>
+      <c r="AJ9" s="34" t="n"/>
+      <c r="AK9" s="29" t="n"/>
+      <c r="AL9" s="30" t="n"/>
+      <c r="AM9" s="31" t="n"/>
       <c r="AN9" s="33" t="n"/>
-      <c r="AO9" s="28" t="n"/>
-      <c r="AP9" s="29" t="n"/>
-      <c r="AQ9" s="30" t="n"/>
-      <c r="AR9" s="33" t="n"/>
-      <c r="AS9" s="28" t="n"/>
-      <c r="AT9" s="29" t="n"/>
-      <c r="AU9" s="31" t="n"/>
+      <c r="AO9" s="29" t="n"/>
+      <c r="AP9" s="30" t="n"/>
+      <c r="AQ9" s="31" t="n"/>
+      <c r="AR9" s="26" t="n"/>
+      <c r="AS9" s="29" t="n"/>
+      <c r="AT9" s="30" t="n"/>
+      <c r="AU9" s="32" t="n"/>
       <c r="AV9" s="33" t="n"/>
     </row>
     <row r="10" ht="20.1" customHeight="1">
@@ -1457,7 +1485,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="18" t="n"/>
+      <c r="D10" s="19" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1467,7 +1495,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="37" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -1481,7 +1509,7 @@
         <v>3</v>
       </c>
       <c r="K10" s="7" t="n"/>
-      <c r="L10" s="23" t="n"/>
+      <c r="L10" s="26" t="n"/>
       <c r="M10" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -1491,7 +1519,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="7" t="n"/>
-      <c r="P10" s="18" t="n"/>
+      <c r="P10" s="19" t="n"/>
       <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1501,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="S10" s="12" t="n"/>
-      <c r="T10" s="39" t="n"/>
+      <c r="T10" s="37" t="n"/>
       <c r="U10" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1511,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="W10" s="7" t="n"/>
-      <c r="X10" s="18" t="n"/>
+      <c r="X10" s="19" t="n"/>
       <c r="Y10" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1521,7 +1549,7 @@
         <v>3</v>
       </c>
       <c r="AA10" s="12" t="n"/>
-      <c r="AB10" s="18" t="n"/>
+      <c r="AB10" s="19" t="n"/>
       <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1531,7 +1559,7 @@
         <v>3</v>
       </c>
       <c r="AE10" s="7" t="n"/>
-      <c r="AF10" s="36" t="inlineStr">
+      <c r="AF10" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -1545,7 +1573,7 @@
         <v>3</v>
       </c>
       <c r="AI10" s="7" t="n"/>
-      <c r="AJ10" s="18" t="n"/>
+      <c r="AJ10" s="19" t="n"/>
       <c r="AK10" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1555,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="AM10" s="7" t="n"/>
-      <c r="AN10" s="18" t="n"/>
+      <c r="AN10" s="19" t="n"/>
       <c r="AO10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1565,7 +1593,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" s="12" t="n"/>
-      <c r="AR10" s="40" t="inlineStr">
+      <c r="AR10" s="38" t="inlineStr">
         <is>
           <t>Repas catéchuménat</t>
         </is>
@@ -1579,106 +1607,110 @@
         <v>3</v>
       </c>
       <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="18" t="n"/>
+      <c r="AV10" s="19" t="n"/>
     </row>
     <row r="11" ht="20.1" customHeight="1">
-      <c r="A11" s="21" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="41" t="inlineStr">
+      <c r="A11" s="22" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="39" t="inlineStr">
         <is>
           <t>Rencontre CMP &amp; CPAE</t>
         </is>
       </c>
-      <c r="I11" s="21" t="n"/>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="25" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="O11" s="22" t="n"/>
-      <c r="P11" s="26" t="n"/>
-      <c r="Q11" s="21" t="n"/>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="23" t="n"/>
-      <c r="U11" s="21" t="n"/>
-      <c r="W11" s="22" t="n"/>
-      <c r="X11" s="26" t="n"/>
-      <c r="Y11" s="21" t="n"/>
-      <c r="AA11" s="24" t="n"/>
-      <c r="AB11" s="26" t="n"/>
-      <c r="AC11" s="21" t="n"/>
-      <c r="AE11" s="22" t="n"/>
-      <c r="AF11" s="23" t="n"/>
-      <c r="AG11" s="21" t="n"/>
-      <c r="AI11" s="22" t="n"/>
-      <c r="AJ11" s="26" t="n"/>
-      <c r="AK11" s="21" t="n"/>
-      <c r="AM11" s="22" t="n"/>
-      <c r="AN11" s="26" t="n"/>
-      <c r="AO11" s="21" t="n"/>
-      <c r="AQ11" s="24" t="n"/>
-      <c r="AR11" s="23" t="n"/>
-      <c r="AS11" s="21" t="n"/>
-      <c r="AU11" s="24" t="n"/>
-      <c r="AV11" s="26" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="M11" s="22" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="27" t="n"/>
+      <c r="Q11" s="22" t="n"/>
+      <c r="S11" s="25" t="n"/>
+      <c r="T11" s="24" t="n"/>
+      <c r="U11" s="22" t="n"/>
+      <c r="W11" s="23" t="n"/>
+      <c r="X11" s="27" t="n"/>
+      <c r="Y11" s="22" t="n"/>
+      <c r="AA11" s="25" t="n"/>
+      <c r="AB11" s="27" t="n"/>
+      <c r="AC11" s="22" t="n"/>
+      <c r="AE11" s="23" t="n"/>
+      <c r="AF11" s="24" t="n"/>
+      <c r="AG11" s="22" t="n"/>
+      <c r="AI11" s="23" t="n"/>
+      <c r="AJ11" s="27" t="n"/>
+      <c r="AK11" s="22" t="n"/>
+      <c r="AM11" s="23" t="n"/>
+      <c r="AN11" s="27" t="n"/>
+      <c r="AO11" s="22" t="n"/>
+      <c r="AQ11" s="25" t="n"/>
+      <c r="AR11" s="24" t="n"/>
+      <c r="AS11" s="22" t="n"/>
+      <c r="AU11" s="25" t="n"/>
+      <c r="AV11" s="27" t="n"/>
     </row>
     <row r="12" ht="20.1" customHeight="1">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="29" t="n"/>
-      <c r="C12" s="30" t="n"/>
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="31" t="n"/>
       <c r="D12" s="33" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="42" t="inlineStr">
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="30" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="31" t="n"/>
       <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="31" t="n"/>
-      <c r="T12" s="23" t="n"/>
-      <c r="U12" s="28" t="n"/>
-      <c r="V12" s="29" t="n"/>
-      <c r="W12" s="30" t="n"/>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="30" t="n"/>
+      <c r="S12" s="32" t="n"/>
+      <c r="T12" s="24" t="n"/>
+      <c r="U12" s="29" t="n"/>
+      <c r="V12" s="30" t="n"/>
+      <c r="W12" s="31" t="n"/>
       <c r="X12" s="33" t="n"/>
-      <c r="Y12" s="28" t="n"/>
-      <c r="Z12" s="29" t="n"/>
-      <c r="AA12" s="31" t="n"/>
+      <c r="Y12" s="29" t="n"/>
+      <c r="Z12" s="30" t="n"/>
+      <c r="AA12" s="32" t="n"/>
       <c r="AB12" s="33" t="n"/>
-      <c r="AC12" s="28" t="n"/>
-      <c r="AD12" s="29" t="n"/>
-      <c r="AE12" s="30" t="n"/>
-      <c r="AF12" s="25" t="n"/>
-      <c r="AG12" s="28" t="n"/>
-      <c r="AH12" s="29" t="n"/>
-      <c r="AI12" s="30" t="n"/>
+      <c r="AC12" s="29" t="n"/>
+      <c r="AD12" s="30" t="n"/>
+      <c r="AE12" s="31" t="n"/>
+      <c r="AF12" s="26" t="n"/>
+      <c r="AG12" s="29" t="n"/>
+      <c r="AH12" s="30" t="n"/>
+      <c r="AI12" s="31" t="n"/>
       <c r="AJ12" s="33" t="n"/>
-      <c r="AK12" s="28" t="n"/>
-      <c r="AL12" s="29" t="n"/>
-      <c r="AM12" s="30" t="n"/>
+      <c r="AK12" s="29" t="n"/>
+      <c r="AL12" s="30" t="n"/>
+      <c r="AM12" s="31" t="n"/>
       <c r="AN12" s="33" t="n"/>
-      <c r="AO12" s="28" t="n"/>
-      <c r="AP12" s="29" t="n"/>
-      <c r="AQ12" s="31" t="n"/>
-      <c r="AR12" s="25" t="n"/>
-      <c r="AS12" s="28" t="n"/>
-      <c r="AT12" s="29" t="n"/>
-      <c r="AU12" s="31" t="n"/>
+      <c r="AO12" s="29" t="n"/>
+      <c r="AP12" s="30" t="n"/>
+      <c r="AQ12" s="32" t="n"/>
+      <c r="AR12" s="26" t="n"/>
+      <c r="AS12" s="29" t="n"/>
+      <c r="AT12" s="30" t="n"/>
+      <c r="AU12" s="32" t="n"/>
       <c r="AV12" s="33" t="n"/>
     </row>
     <row r="13" ht="20.1" customHeight="1">
@@ -1691,7 +1723,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="D13" s="19" t="n"/>
       <c r="E13" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1700,8 +1732,8 @@
       <c r="F13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="20" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="21" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1711,11 +1743,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="7" t="n"/>
-      <c r="L13" s="44" t="inlineStr">
-        <is>
-          <t>Père Pascal en Côte d'Ivoire</t>
-        </is>
-      </c>
+      <c r="L13" s="42" t="n"/>
       <c r="M13" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -1725,7 +1753,11 @@
         <v>4</v>
       </c>
       <c r="O13" s="7" t="n"/>
-      <c r="P13" s="18" t="n"/>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -1735,7 +1767,7 @@
         <v>4</v>
       </c>
       <c r="S13" s="7" t="n"/>
-      <c r="T13" s="23" t="n"/>
+      <c r="T13" s="24" t="n"/>
       <c r="U13" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1745,7 +1777,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="7" t="n"/>
-      <c r="X13" s="18" t="n"/>
+      <c r="X13" s="19" t="n"/>
       <c r="Y13" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -1755,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="AA13" s="12" t="n"/>
-      <c r="AB13" s="36" t="inlineStr">
+      <c r="AB13" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -1768,8 +1800,8 @@
       <c r="AD13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AE13" s="43" t="n"/>
-      <c r="AF13" s="45" t="inlineStr">
+      <c r="AE13" s="41" t="n"/>
+      <c r="AF13" s="43" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
@@ -1785,7 +1817,7 @@
       <c r="AI13" s="7" t="n"/>
       <c r="AJ13" s="16" t="inlineStr">
         <is>
-          <t>Groupe de prière</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -1797,7 +1829,11 @@
         <v>4</v>
       </c>
       <c r="AM13" s="7" t="n"/>
-      <c r="AN13" s="18" t="n"/>
+      <c r="AN13" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="AO13" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1807,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="AQ13" s="12" t="n"/>
-      <c r="AR13" s="36" t="inlineStr">
+      <c r="AR13" s="35" t="inlineStr">
         <is>
           <t>Profession de foi</t>
         </is>
@@ -1821,102 +1857,110 @@
         <v>4</v>
       </c>
       <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="18" t="n"/>
+      <c r="AV13" s="19" t="n"/>
     </row>
     <row r="14" ht="20.1" customHeight="1">
-      <c r="A14" s="21" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="K14" s="22" t="n"/>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="21" t="n"/>
-      <c r="S14" s="22" t="n"/>
-      <c r="T14" s="23" t="n"/>
-      <c r="U14" s="21" t="n"/>
-      <c r="W14" s="22" t="n"/>
-      <c r="X14" s="26" t="n"/>
-      <c r="Y14" s="21" t="n"/>
-      <c r="AA14" s="24" t="n"/>
-      <c r="AB14" s="23" t="n"/>
-      <c r="AC14" s="21" t="n"/>
-      <c r="AE14" s="46" t="n"/>
-      <c r="AF14" s="32" t="inlineStr">
+      <c r="A14" s="22" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="G14" s="44" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="22" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="24" t="n"/>
+      <c r="Q14" s="22" t="n"/>
+      <c r="S14" s="23" t="n"/>
+      <c r="T14" s="24" t="n"/>
+      <c r="U14" s="22" t="n"/>
+      <c r="W14" s="23" t="n"/>
+      <c r="X14" s="27" t="n"/>
+      <c r="Y14" s="22" t="n"/>
+      <c r="AA14" s="25" t="n"/>
+      <c r="AB14" s="24" t="n"/>
+      <c r="AC14" s="22" t="n"/>
+      <c r="AE14" s="44" t="n"/>
+      <c r="AF14" s="17" t="inlineStr">
         <is>
           <t>Divine Miséricorde</t>
         </is>
       </c>
-      <c r="AG14" s="21" t="n"/>
-      <c r="AI14" s="22" t="n"/>
-      <c r="AJ14" s="23" t="n"/>
-      <c r="AK14" s="21" t="n"/>
-      <c r="AM14" s="22" t="n"/>
-      <c r="AN14" s="26" t="n"/>
-      <c r="AO14" s="21" t="n"/>
-      <c r="AQ14" s="24" t="n"/>
-      <c r="AR14" s="23" t="n"/>
-      <c r="AS14" s="21" t="n"/>
-      <c r="AU14" s="24" t="n"/>
-      <c r="AV14" s="26" t="n"/>
+      <c r="AG14" s="22" t="n"/>
+      <c r="AI14" s="23" t="n"/>
+      <c r="AJ14" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="AK14" s="22" t="n"/>
+      <c r="AM14" s="23" t="n"/>
+      <c r="AN14" s="24" t="n"/>
+      <c r="AO14" s="22" t="n"/>
+      <c r="AQ14" s="25" t="n"/>
+      <c r="AR14" s="24" t="n"/>
+      <c r="AS14" s="22" t="n"/>
+      <c r="AU14" s="25" t="n"/>
+      <c r="AV14" s="27" t="n"/>
     </row>
     <row r="15" ht="20.1" customHeight="1">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="30" t="n"/>
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="31" t="n"/>
       <c r="D15" s="33" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="47" t="n"/>
-      <c r="H15" s="35" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="30" t="n"/>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="28" t="n"/>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="33" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="29" t="n"/>
-      <c r="S15" s="30" t="n"/>
-      <c r="T15" s="23" t="n"/>
-      <c r="U15" s="28" t="n"/>
-      <c r="V15" s="29" t="n"/>
-      <c r="W15" s="30" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="45" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="30" t="n"/>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="24" t="n"/>
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="30" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="26" t="n"/>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="30" t="n"/>
+      <c r="S15" s="31" t="n"/>
+      <c r="T15" s="24" t="n"/>
+      <c r="U15" s="29" t="n"/>
+      <c r="V15" s="30" t="n"/>
+      <c r="W15" s="31" t="n"/>
       <c r="X15" s="33" t="n"/>
-      <c r="Y15" s="28" t="n"/>
-      <c r="Z15" s="29" t="n"/>
-      <c r="AA15" s="31" t="n"/>
-      <c r="AB15" s="25" t="n"/>
-      <c r="AC15" s="28" t="n"/>
-      <c r="AD15" s="29" t="n"/>
-      <c r="AE15" s="47" t="n"/>
-      <c r="AF15" s="48" t="inlineStr">
+      <c r="Y15" s="29" t="n"/>
+      <c r="Z15" s="30" t="n"/>
+      <c r="AA15" s="32" t="n"/>
+      <c r="AB15" s="26" t="n"/>
+      <c r="AC15" s="29" t="n"/>
+      <c r="AD15" s="30" t="n"/>
+      <c r="AE15" s="45" t="n"/>
+      <c r="AF15" s="46" t="inlineStr">
         <is>
           <t>J. Sexualité</t>
         </is>
       </c>
-      <c r="AG15" s="28" t="n"/>
-      <c r="AH15" s="29" t="n"/>
-      <c r="AI15" s="30" t="n"/>
-      <c r="AJ15" s="25" t="n"/>
-      <c r="AK15" s="28" t="n"/>
-      <c r="AL15" s="29" t="n"/>
-      <c r="AM15" s="30" t="n"/>
-      <c r="AN15" s="33" t="n"/>
-      <c r="AO15" s="28" t="n"/>
-      <c r="AP15" s="29" t="n"/>
-      <c r="AQ15" s="31" t="n"/>
-      <c r="AR15" s="25" t="n"/>
-      <c r="AS15" s="28" t="n"/>
-      <c r="AT15" s="29" t="n"/>
-      <c r="AU15" s="31" t="n"/>
+      <c r="AG15" s="29" t="n"/>
+      <c r="AH15" s="30" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AK15" s="29" t="n"/>
+      <c r="AL15" s="30" t="n"/>
+      <c r="AM15" s="31" t="n"/>
+      <c r="AN15" s="26" t="n"/>
+      <c r="AO15" s="29" t="n"/>
+      <c r="AP15" s="30" t="n"/>
+      <c r="AQ15" s="32" t="n"/>
+      <c r="AR15" s="26" t="n"/>
+      <c r="AS15" s="29" t="n"/>
+      <c r="AT15" s="30" t="n"/>
+      <c r="AU15" s="32" t="n"/>
       <c r="AV15" s="33" t="n"/>
     </row>
     <row r="16" ht="20.1" customHeight="1">
@@ -1929,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="D16" s="19" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -1939,7 +1983,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1949,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="K16" s="7" t="n"/>
-      <c r="L16" s="23" t="n"/>
+      <c r="L16" s="24" t="n"/>
       <c r="M16" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -1959,7 +2003,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="7" t="n"/>
-      <c r="P16" s="40" t="inlineStr">
+      <c r="P16" s="38" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -1973,7 +2017,7 @@
         <v>5</v>
       </c>
       <c r="S16" s="7" t="n"/>
-      <c r="T16" s="23" t="n"/>
+      <c r="T16" s="26" t="n"/>
       <c r="U16" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1983,7 +2027,11 @@
         <v>5</v>
       </c>
       <c r="W16" s="7" t="n"/>
-      <c r="X16" s="18" t="n"/>
+      <c r="X16" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="Y16" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -1993,7 +2041,11 @@
         <v>5</v>
       </c>
       <c r="AA16" s="12" t="n"/>
-      <c r="AB16" s="18" t="n"/>
+      <c r="AB16" s="18" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
       <c r="AC16" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2003,7 +2055,7 @@
         <v>5</v>
       </c>
       <c r="AE16" s="7" t="n"/>
-      <c r="AF16" s="17" t="inlineStr">
+      <c r="AF16" s="20" t="inlineStr">
         <is>
           <t>Annonciation</t>
         </is>
@@ -2017,7 +2069,7 @@
         <v>5</v>
       </c>
       <c r="AI16" s="7" t="n"/>
-      <c r="AJ16" s="18" t="n"/>
+      <c r="AJ16" s="19" t="n"/>
       <c r="AK16" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2027,7 +2079,7 @@
         <v>5</v>
       </c>
       <c r="AM16" s="7" t="n"/>
-      <c r="AN16" s="41" t="inlineStr">
+      <c r="AN16" s="39" t="inlineStr">
         <is>
           <t>Chartres 2040</t>
         </is>
@@ -2041,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="AQ16" s="12" t="n"/>
-      <c r="AR16" s="18" t="n"/>
+      <c r="AR16" s="19" t="n"/>
       <c r="AS16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2051,102 +2103,106 @@
         <v>5</v>
       </c>
       <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="18" t="n"/>
+      <c r="AV16" s="19" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1">
-      <c r="A17" s="21" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="K17" s="22" t="n"/>
-      <c r="L17" s="23" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="O17" s="22" t="n"/>
-      <c r="P17" s="23" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="S17" s="22" t="n"/>
-      <c r="T17" s="25" t="n"/>
-      <c r="U17" s="21" t="n"/>
-      <c r="W17" s="22" t="n"/>
-      <c r="X17" s="26" t="n"/>
-      <c r="Y17" s="21" t="n"/>
-      <c r="AA17" s="24" t="n"/>
-      <c r="AB17" s="26" t="n"/>
-      <c r="AC17" s="21" t="n"/>
-      <c r="AE17" s="22" t="n"/>
-      <c r="AF17" s="23" t="n"/>
-      <c r="AG17" s="21" t="n"/>
-      <c r="AI17" s="22" t="n"/>
-      <c r="AJ17" s="26" t="n"/>
-      <c r="AK17" s="21" t="n"/>
-      <c r="AM17" s="22" t="n"/>
-      <c r="AN17" s="42" t="inlineStr">
+      <c r="A17" s="22" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="24" t="n"/>
+      <c r="Q17" s="22" t="n"/>
+      <c r="S17" s="23" t="n"/>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="U17" s="22" t="n"/>
+      <c r="W17" s="23" t="n"/>
+      <c r="X17" s="24" t="n"/>
+      <c r="Y17" s="22" t="n"/>
+      <c r="AA17" s="25" t="n"/>
+      <c r="AB17" s="24" t="n"/>
+      <c r="AC17" s="22" t="n"/>
+      <c r="AE17" s="23" t="n"/>
+      <c r="AF17" s="24" t="n"/>
+      <c r="AG17" s="22" t="n"/>
+      <c r="AI17" s="23" t="n"/>
+      <c r="AJ17" s="27" t="n"/>
+      <c r="AK17" s="22" t="n"/>
+      <c r="AM17" s="23" t="n"/>
+      <c r="AN17" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="AO17" s="21" t="n"/>
-      <c r="AQ17" s="24" t="n"/>
-      <c r="AR17" s="26" t="n"/>
-      <c r="AS17" s="21" t="n"/>
-      <c r="AU17" s="24" t="n"/>
-      <c r="AV17" s="26" t="n"/>
+      <c r="AO17" s="22" t="n"/>
+      <c r="AQ17" s="25" t="n"/>
+      <c r="AR17" s="27" t="n"/>
+      <c r="AS17" s="22" t="n"/>
+      <c r="AU17" s="25" t="n"/>
+      <c r="AV17" s="27" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="29" t="n"/>
-      <c r="C18" s="30" t="n"/>
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="31" t="n"/>
       <c r="D18" s="33" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="30" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="31" t="n"/>
       <c r="H18" s="33" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="29" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="29" t="n"/>
-      <c r="O18" s="30" t="n"/>
-      <c r="P18" s="25" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="29" t="n"/>
-      <c r="S18" s="30" t="n"/>
-      <c r="T18" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="U18" s="28" t="n"/>
-      <c r="V18" s="29" t="n"/>
-      <c r="W18" s="30" t="n"/>
-      <c r="X18" s="33" t="n"/>
-      <c r="Y18" s="28" t="n"/>
-      <c r="Z18" s="29" t="n"/>
-      <c r="AA18" s="31" t="n"/>
-      <c r="AB18" s="33" t="n"/>
-      <c r="AC18" s="28" t="n"/>
-      <c r="AD18" s="29" t="n"/>
-      <c r="AE18" s="30" t="n"/>
-      <c r="AF18" s="25" t="n"/>
-      <c r="AG18" s="28" t="n"/>
-      <c r="AH18" s="29" t="n"/>
-      <c r="AI18" s="30" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="30" t="n"/>
+      <c r="K18" s="31" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="30" t="n"/>
+      <c r="O18" s="31" t="n"/>
+      <c r="P18" s="26" t="n"/>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="30" t="n"/>
+      <c r="S18" s="31" t="n"/>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="U18" s="29" t="n"/>
+      <c r="V18" s="30" t="n"/>
+      <c r="W18" s="31" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="29" t="n"/>
+      <c r="Z18" s="30" t="n"/>
+      <c r="AA18" s="32" t="n"/>
+      <c r="AB18" s="26" t="n"/>
+      <c r="AC18" s="29" t="n"/>
+      <c r="AD18" s="30" t="n"/>
+      <c r="AE18" s="31" t="n"/>
+      <c r="AF18" s="26" t="n"/>
+      <c r="AG18" s="29" t="n"/>
+      <c r="AH18" s="30" t="n"/>
+      <c r="AI18" s="31" t="n"/>
       <c r="AJ18" s="33" t="n"/>
-      <c r="AK18" s="28" t="n"/>
-      <c r="AL18" s="29" t="n"/>
-      <c r="AM18" s="30" t="n"/>
+      <c r="AK18" s="29" t="n"/>
+      <c r="AL18" s="30" t="n"/>
+      <c r="AM18" s="31" t="n"/>
       <c r="AN18" s="33" t="n"/>
-      <c r="AO18" s="28" t="n"/>
-      <c r="AP18" s="29" t="n"/>
-      <c r="AQ18" s="31" t="n"/>
+      <c r="AO18" s="29" t="n"/>
+      <c r="AP18" s="30" t="n"/>
+      <c r="AQ18" s="32" t="n"/>
       <c r="AR18" s="33" t="n"/>
-      <c r="AS18" s="28" t="n"/>
-      <c r="AT18" s="29" t="n"/>
-      <c r="AU18" s="31" t="n"/>
+      <c r="AS18" s="29" t="n"/>
+      <c r="AT18" s="30" t="n"/>
+      <c r="AU18" s="32" t="n"/>
       <c r="AV18" s="33" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1">
@@ -2158,8 +2214,8 @@
       <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="43" t="n"/>
-      <c r="D19" s="20" t="n"/>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="21" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -2169,7 +2225,7 @@
         <v>6</v>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="34" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Equipe pilote</t>
         </is>
@@ -2183,7 +2239,7 @@
         <v>6</v>
       </c>
       <c r="K19" s="7" t="n"/>
-      <c r="L19" s="23" t="n"/>
+      <c r="L19" s="26" t="n"/>
       <c r="M19" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -2192,8 +2248,8 @@
       <c r="N19" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="O19" s="43" t="n"/>
-      <c r="P19" s="49" t="inlineStr">
+      <c r="O19" s="41" t="n"/>
+      <c r="P19" s="47" t="inlineStr">
         <is>
           <t>2e dim. de l'Avent</t>
         </is>
@@ -2207,7 +2263,7 @@
         <v>6</v>
       </c>
       <c r="S19" s="7" t="n"/>
-      <c r="T19" s="39" t="inlineStr">
+      <c r="T19" s="37" t="inlineStr">
         <is>
           <t>Semaine Épiphanie</t>
         </is>
@@ -2221,9 +2277,9 @@
         <v>6</v>
       </c>
       <c r="W19" s="7" t="n"/>
-      <c r="X19" s="40" t="inlineStr">
-        <is>
-          <t>Catéchuménat</t>
+      <c r="X19" s="16" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="Y19" s="14" t="inlineStr">
@@ -2235,7 +2291,7 @@
         <v>6</v>
       </c>
       <c r="AA19" s="12" t="n"/>
-      <c r="AB19" s="37" t="inlineStr">
+      <c r="AB19" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -2263,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="AI19" s="7" t="n"/>
-      <c r="AJ19" s="32" t="inlineStr">
+      <c r="AJ19" s="17" t="inlineStr">
         <is>
           <t>Ascension</t>
         </is>
@@ -2276,8 +2332,8 @@
       <c r="AL19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="AM19" s="43" t="n"/>
-      <c r="AN19" s="36" t="inlineStr">
+      <c r="AM19" s="41" t="n"/>
+      <c r="AN19" s="35" t="inlineStr">
         <is>
           <t>1ère Communion</t>
         </is>
@@ -2291,7 +2347,11 @@
         <v>6</v>
       </c>
       <c r="AQ19" s="12" t="n"/>
-      <c r="AR19" s="18" t="n"/>
+      <c r="AR19" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="AS19" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2301,115 +2361,127 @@
         <v>6</v>
       </c>
       <c r="AU19" s="12" t="n"/>
-      <c r="AV19" s="17" t="inlineStr">
+      <c r="AV19" s="20" t="inlineStr">
         <is>
           <t>Transfiguration</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1">
-      <c r="A20" s="21" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="34" t="inlineStr">
+      <c r="A20" s="22" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="28" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="I20" s="21" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="25" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="O20" s="46" t="n"/>
-      <c r="P20" s="23" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="23" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="23" t="n"/>
-      <c r="Y20" s="21" t="n"/>
-      <c r="AA20" s="24" t="n"/>
-      <c r="AB20" s="50" t="inlineStr">
+      <c r="I20" s="22" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="40" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="n"/>
+      <c r="O20" s="44" t="n"/>
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="24" t="n"/>
+      <c r="U20" s="22" t="n"/>
+      <c r="W20" s="23" t="n"/>
+      <c r="X20" s="36" t="inlineStr">
+        <is>
+          <t>Catéchuménat</t>
+        </is>
+      </c>
+      <c r="Y20" s="22" t="n"/>
+      <c r="AA20" s="25" t="n"/>
+      <c r="AB20" s="48" t="inlineStr">
         <is>
           <t>WE Prépa Mariage</t>
         </is>
       </c>
-      <c r="AC20" s="21" t="n"/>
-      <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="23" t="n"/>
-      <c r="AG20" s="21" t="n"/>
-      <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="16" t="inlineStr">
-        <is>
-          <t>WE Ascension</t>
-        </is>
-      </c>
-      <c r="AK20" s="21" t="n"/>
-      <c r="AM20" s="46" t="n"/>
-      <c r="AN20" s="23" t="n"/>
-      <c r="AO20" s="21" t="n"/>
-      <c r="AQ20" s="24" t="n"/>
-      <c r="AR20" s="26" t="n"/>
-      <c r="AS20" s="21" t="n"/>
-      <c r="AU20" s="24" t="n"/>
-      <c r="AV20" s="23" t="n"/>
+      <c r="AC20" s="22" t="n"/>
+      <c r="AE20" s="23" t="n"/>
+      <c r="AF20" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AG20" s="22" t="n"/>
+      <c r="AI20" s="23" t="n"/>
+      <c r="AJ20" s="18" t="n"/>
+      <c r="AK20" s="22" t="n"/>
+      <c r="AM20" s="44" t="n"/>
+      <c r="AN20" s="24" t="n"/>
+      <c r="AO20" s="22" t="n"/>
+      <c r="AQ20" s="25" t="n"/>
+      <c r="AR20" s="24" t="n"/>
+      <c r="AS20" s="22" t="n"/>
+      <c r="AU20" s="25" t="n"/>
+      <c r="AV20" s="24" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="35" t="n"/>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="28" t="n"/>
-      <c r="J21" s="29" t="n"/>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="42" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="M21" s="28" t="n"/>
-      <c r="N21" s="29" t="n"/>
-      <c r="O21" s="47" t="n"/>
-      <c r="P21" s="25" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="29" t="n"/>
-      <c r="S21" s="30" t="n"/>
-      <c r="T21" s="23" t="n"/>
-      <c r="U21" s="28" t="n"/>
-      <c r="V21" s="29" t="n"/>
-      <c r="W21" s="30" t="n"/>
-      <c r="X21" s="25" t="n"/>
-      <c r="Y21" s="28" t="n"/>
-      <c r="Z21" s="29" t="n"/>
-      <c r="AA21" s="31" t="n"/>
-      <c r="AB21" s="23" t="n"/>
-      <c r="AC21" s="28" t="n"/>
-      <c r="AD21" s="29" t="n"/>
-      <c r="AE21" s="30" t="n"/>
-      <c r="AF21" s="25" t="n"/>
-      <c r="AG21" s="28" t="n"/>
-      <c r="AH21" s="29" t="n"/>
-      <c r="AI21" s="30" t="n"/>
-      <c r="AJ21" s="23" t="n"/>
-      <c r="AK21" s="28" t="n"/>
-      <c r="AL21" s="29" t="n"/>
-      <c r="AM21" s="47" t="n"/>
-      <c r="AN21" s="25" t="n"/>
-      <c r="AO21" s="28" t="n"/>
-      <c r="AP21" s="29" t="n"/>
-      <c r="AQ21" s="31" t="n"/>
-      <c r="AR21" s="33" t="n"/>
-      <c r="AS21" s="28" t="n"/>
-      <c r="AT21" s="29" t="n"/>
-      <c r="AU21" s="31" t="n"/>
-      <c r="AV21" s="25" t="n"/>
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="45" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="30" t="n"/>
+      <c r="K21" s="31" t="n"/>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
+      <c r="M21" s="29" t="n"/>
+      <c r="N21" s="30" t="n"/>
+      <c r="O21" s="45" t="n"/>
+      <c r="P21" s="26" t="n"/>
+      <c r="Q21" s="29" t="n"/>
+      <c r="R21" s="30" t="n"/>
+      <c r="S21" s="31" t="n"/>
+      <c r="T21" s="24" t="n"/>
+      <c r="U21" s="29" t="n"/>
+      <c r="V21" s="30" t="n"/>
+      <c r="W21" s="31" t="n"/>
+      <c r="X21" s="33" t="n"/>
+      <c r="Y21" s="29" t="n"/>
+      <c r="Z21" s="30" t="n"/>
+      <c r="AA21" s="32" t="n"/>
+      <c r="AB21" s="24" t="n"/>
+      <c r="AC21" s="29" t="n"/>
+      <c r="AD21" s="30" t="n"/>
+      <c r="AE21" s="31" t="n"/>
+      <c r="AF21" s="33" t="n"/>
+      <c r="AG21" s="29" t="n"/>
+      <c r="AH21" s="30" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="24" t="n"/>
+      <c r="AK21" s="29" t="n"/>
+      <c r="AL21" s="30" t="n"/>
+      <c r="AM21" s="45" t="n"/>
+      <c r="AN21" s="26" t="n"/>
+      <c r="AO21" s="29" t="n"/>
+      <c r="AP21" s="30" t="n"/>
+      <c r="AQ21" s="32" t="n"/>
+      <c r="AR21" s="26" t="n"/>
+      <c r="AS21" s="29" t="n"/>
+      <c r="AT21" s="30" t="n"/>
+      <c r="AU21" s="32" t="n"/>
+      <c r="AV21" s="26" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2421,7 +2493,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="18" t="n"/>
+      <c r="D22" s="19" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2431,7 +2503,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="18" t="n"/>
+      <c r="H22" s="19" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2441,9 +2513,9 @@
         <v>7</v>
       </c>
       <c r="K22" s="7" t="n"/>
-      <c r="L22" s="37" t="inlineStr">
-        <is>
-          <t>Catéchuménat</t>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>CMP avec Florence Metayer</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
@@ -2455,7 +2527,7 @@
         <v>7</v>
       </c>
       <c r="O22" s="7" t="n"/>
-      <c r="P22" s="18" t="n"/>
+      <c r="P22" s="19" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2465,7 +2537,7 @@
         <v>7</v>
       </c>
       <c r="S22" s="7" t="n"/>
-      <c r="T22" s="23" t="n"/>
+      <c r="T22" s="24" t="n"/>
       <c r="U22" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2474,8 +2546,8 @@
       <c r="V22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="W22" s="43" t="n"/>
-      <c r="X22" s="20" t="n"/>
+      <c r="W22" s="41" t="n"/>
+      <c r="X22" s="21" t="n"/>
       <c r="Y22" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -2485,7 +2557,7 @@
         <v>7</v>
       </c>
       <c r="AA22" s="12" t="n"/>
-      <c r="AB22" s="25" t="n"/>
+      <c r="AB22" s="26" t="n"/>
       <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2495,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="AE22" s="7" t="n"/>
-      <c r="AF22" s="18" t="n"/>
+      <c r="AF22" s="19" t="n"/>
       <c r="AG22" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2505,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="AI22" s="7" t="n"/>
-      <c r="AJ22" s="23" t="n"/>
+      <c r="AJ22" s="26" t="n"/>
       <c r="AK22" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2515,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="AM22" s="7" t="n"/>
-      <c r="AN22" s="18" t="n"/>
+      <c r="AN22" s="19" t="n"/>
       <c r="AO22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2525,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" s="12" t="n"/>
-      <c r="AR22" s="18" t="n"/>
+      <c r="AR22" s="19" t="n"/>
       <c r="AS22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2535,110 +2607,118 @@
         <v>7</v>
       </c>
       <c r="AU22" s="12" t="n"/>
-      <c r="AV22" s="18" t="n"/>
+      <c r="AV22" s="19" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1">
-      <c r="A23" s="21" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="26" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="42" t="inlineStr">
+      <c r="A23" s="22" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="27" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="36" t="inlineStr">
+        <is>
+          <t>Catéchuménat</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="n"/>
+      <c r="O23" s="23" t="n"/>
+      <c r="P23" s="27" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="S23" s="23" t="n"/>
+      <c r="T23" s="24" t="n"/>
+      <c r="U23" s="22" t="n"/>
+      <c r="W23" s="44" t="n"/>
+      <c r="X23" s="28" t="n"/>
+      <c r="Y23" s="22" t="n"/>
+      <c r="AA23" s="25" t="n"/>
+      <c r="AB23" s="49" t="inlineStr">
+        <is>
+          <t>4e dim. de Carême</t>
+        </is>
+      </c>
+      <c r="AC23" s="22" t="n"/>
+      <c r="AE23" s="23" t="n"/>
+      <c r="AF23" s="27" t="n"/>
+      <c r="AG23" s="22" t="n"/>
+      <c r="AI23" s="23" t="n"/>
+      <c r="AJ23" s="43" t="inlineStr">
+        <is>
+          <t>Pont de l'Ascension</t>
+        </is>
+      </c>
+      <c r="AK23" s="22" t="n"/>
+      <c r="AM23" s="23" t="n"/>
+      <c r="AN23" s="27" t="n"/>
+      <c r="AO23" s="22" t="n"/>
+      <c r="AQ23" s="25" t="n"/>
+      <c r="AR23" s="27" t="n"/>
+      <c r="AS23" s="22" t="n"/>
+      <c r="AU23" s="25" t="n"/>
+      <c r="AV23" s="27" t="n"/>
+    </row>
+    <row r="24" ht="20.1" customHeight="1">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="M23" s="21" t="n"/>
-      <c r="O23" s="22" t="n"/>
-      <c r="P23" s="26" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="S23" s="22" t="n"/>
-      <c r="T23" s="23" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="W23" s="46" t="n"/>
-      <c r="X23" s="27" t="n"/>
-      <c r="Y23" s="21" t="n"/>
-      <c r="AA23" s="24" t="n"/>
-      <c r="AB23" s="51" t="inlineStr">
-        <is>
-          <t>4e dim. de Carême</t>
-        </is>
-      </c>
-      <c r="AC23" s="21" t="n"/>
-      <c r="AE23" s="22" t="n"/>
-      <c r="AF23" s="26" t="n"/>
-      <c r="AG23" s="21" t="n"/>
-      <c r="AI23" s="22" t="n"/>
-      <c r="AJ23" s="25" t="n"/>
-      <c r="AK23" s="21" t="n"/>
-      <c r="AM23" s="22" t="n"/>
-      <c r="AN23" s="26" t="n"/>
-      <c r="AO23" s="21" t="n"/>
-      <c r="AQ23" s="24" t="n"/>
-      <c r="AR23" s="26" t="n"/>
-      <c r="AS23" s="21" t="n"/>
-      <c r="AU23" s="24" t="n"/>
-      <c r="AV23" s="26" t="n"/>
-    </row>
-    <row r="24" ht="20.1" customHeight="1">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="28" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="44" t="n"/>
-      <c r="M24" s="28" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="30" t="n"/>
+      <c r="M24" s="29" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="31" t="n"/>
       <c r="P24" s="33" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="29" t="n"/>
-      <c r="S24" s="30" t="n"/>
-      <c r="T24" s="23" t="n"/>
-      <c r="U24" s="28" t="n"/>
-      <c r="V24" s="29" t="n"/>
-      <c r="W24" s="47" t="n"/>
-      <c r="X24" s="35" t="n"/>
-      <c r="Y24" s="28" t="n"/>
-      <c r="Z24" s="29" t="n"/>
-      <c r="AA24" s="31" t="n"/>
-      <c r="AB24" s="37" t="inlineStr">
+      <c r="Q24" s="29" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="31" t="n"/>
+      <c r="T24" s="24" t="n"/>
+      <c r="U24" s="29" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="45" t="n"/>
+      <c r="X24" s="34" t="n"/>
+      <c r="Y24" s="29" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="32" t="n"/>
+      <c r="AB24" s="36" t="inlineStr">
         <is>
           <t>2ème scrutin</t>
         </is>
       </c>
-      <c r="AC24" s="28" t="n"/>
-      <c r="AD24" s="29" t="n"/>
-      <c r="AE24" s="30" t="n"/>
+      <c r="AC24" s="29" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="31" t="n"/>
       <c r="AF24" s="33" t="n"/>
-      <c r="AG24" s="28" t="n"/>
-      <c r="AH24" s="29" t="n"/>
-      <c r="AI24" s="30" t="n"/>
-      <c r="AJ24" s="45" t="inlineStr">
-        <is>
-          <t>Pont de l'Ascension</t>
-        </is>
-      </c>
-      <c r="AK24" s="28" t="n"/>
-      <c r="AL24" s="29" t="n"/>
-      <c r="AM24" s="30" t="n"/>
+      <c r="AG24" s="29" t="n"/>
+      <c r="AH24" s="30" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="16" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
+      <c r="AK24" s="29" t="n"/>
+      <c r="AL24" s="30" t="n"/>
+      <c r="AM24" s="31" t="n"/>
       <c r="AN24" s="33" t="n"/>
-      <c r="AO24" s="28" t="n"/>
-      <c r="AP24" s="29" t="n"/>
-      <c r="AQ24" s="31" t="n"/>
+      <c r="AO24" s="29" t="n"/>
+      <c r="AP24" s="30" t="n"/>
+      <c r="AQ24" s="32" t="n"/>
       <c r="AR24" s="33" t="n"/>
-      <c r="AS24" s="28" t="n"/>
-      <c r="AT24" s="29" t="n"/>
-      <c r="AU24" s="31" t="n"/>
+      <c r="AS24" s="29" t="n"/>
+      <c r="AT24" s="30" t="n"/>
+      <c r="AU24" s="32" t="n"/>
       <c r="AV24" s="33" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1">
@@ -2651,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>Equipe pilote</t>
         </is>
@@ -2665,7 +2745,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="18" t="n"/>
+      <c r="H25" s="19" t="n"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2674,8 +2754,8 @@
       <c r="J25" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K25" s="43" t="n"/>
-      <c r="L25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="50" t="n"/>
       <c r="M25" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -2687,7 +2767,7 @@
       <c r="O25" s="7" t="n"/>
       <c r="P25" s="16" t="inlineStr">
         <is>
-          <t>Soirée réconciliation</t>
+          <t>Journée d'adoration</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
@@ -2699,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="S25" s="7" t="n"/>
-      <c r="T25" s="23" t="n"/>
+      <c r="T25" s="24" t="n"/>
       <c r="U25" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2709,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="W25" s="7" t="n"/>
-      <c r="X25" s="18" t="n"/>
+      <c r="X25" s="19" t="n"/>
       <c r="Y25" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -2719,7 +2799,7 @@
         <v>8</v>
       </c>
       <c r="AA25" s="7" t="n"/>
-      <c r="AB25" s="16" t="inlineStr">
+      <c r="AB25" s="18" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -2733,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="AE25" s="7" t="n"/>
-      <c r="AF25" s="18" t="n"/>
+      <c r="AF25" s="19" t="n"/>
       <c r="AG25" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2743,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="AI25" s="7" t="n"/>
-      <c r="AJ25" s="32" t="inlineStr">
+      <c r="AJ25" s="17" t="inlineStr">
         <is>
           <t>Victoire 1945</t>
         </is>
@@ -2771,7 +2851,7 @@
         <v>8</v>
       </c>
       <c r="AQ25" s="12" t="n"/>
-      <c r="AR25" s="18" t="n"/>
+      <c r="AR25" s="19" t="n"/>
       <c r="AS25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2781,99 +2861,111 @@
         <v>8</v>
       </c>
       <c r="AU25" s="12" t="n"/>
-      <c r="AV25" s="20" t="n"/>
+      <c r="AV25" s="21" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1">
-      <c r="A26" s="21" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="G26" s="22" t="n"/>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="K26" s="46" t="n"/>
-      <c r="L26" s="23" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="O26" s="22" t="n"/>
-      <c r="P26" s="23" t="n"/>
-      <c r="Q26" s="21" t="n"/>
-      <c r="S26" s="22" t="n"/>
-      <c r="T26" s="23" t="n"/>
-      <c r="U26" s="21" t="n"/>
-      <c r="W26" s="22" t="n"/>
-      <c r="X26" s="26" t="n"/>
-      <c r="Y26" s="21" t="n"/>
-      <c r="AA26" s="22" t="n"/>
-      <c r="AB26" s="23" t="n"/>
-      <c r="AC26" s="21" t="n"/>
-      <c r="AE26" s="22" t="n"/>
-      <c r="AF26" s="26" t="n"/>
-      <c r="AG26" s="21" t="n"/>
-      <c r="AI26" s="22" t="n"/>
-      <c r="AJ26" s="34" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="AK26" s="21" t="n"/>
-      <c r="AM26" s="22" t="n"/>
-      <c r="AN26" s="23" t="n"/>
-      <c r="AO26" s="21" t="n"/>
-      <c r="AQ26" s="24" t="n"/>
-      <c r="AR26" s="26" t="n"/>
-      <c r="AS26" s="21" t="n"/>
-      <c r="AU26" s="24" t="n"/>
-      <c r="AV26" s="27" t="n"/>
+      <c r="A26" s="22" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="K26" s="44" t="n"/>
+      <c r="L26" s="24" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>Soirée réconciliation</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="n"/>
+      <c r="S26" s="23" t="n"/>
+      <c r="T26" s="24" t="n"/>
+      <c r="U26" s="22" t="n"/>
+      <c r="W26" s="23" t="n"/>
+      <c r="X26" s="27" t="n"/>
+      <c r="Y26" s="22" t="n"/>
+      <c r="AA26" s="23" t="n"/>
+      <c r="AB26" s="24" t="n"/>
+      <c r="AC26" s="22" t="n"/>
+      <c r="AE26" s="23" t="n"/>
+      <c r="AF26" s="27" t="n"/>
+      <c r="AG26" s="22" t="n"/>
+      <c r="AI26" s="23" t="n"/>
+      <c r="AJ26" s="16" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
+      <c r="AK26" s="22" t="n"/>
+      <c r="AM26" s="23" t="n"/>
+      <c r="AN26" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AO26" s="22" t="n"/>
+      <c r="AQ26" s="25" t="n"/>
+      <c r="AR26" s="27" t="n"/>
+      <c r="AS26" s="22" t="n"/>
+      <c r="AU26" s="25" t="n"/>
+      <c r="AV26" s="28" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="28" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="30" t="n"/>
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="26" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="31" t="n"/>
       <c r="H27" s="33" t="n"/>
-      <c r="I27" s="28" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="47" t="n"/>
-      <c r="L27" s="23" t="n"/>
-      <c r="M27" s="28" t="n"/>
-      <c r="N27" s="29" t="n"/>
-      <c r="O27" s="30" t="n"/>
-      <c r="P27" s="25" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="29" t="n"/>
-      <c r="S27" s="30" t="n"/>
-      <c r="T27" s="25" t="n"/>
-      <c r="U27" s="28" t="n"/>
-      <c r="V27" s="29" t="n"/>
-      <c r="W27" s="30" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="45" t="n"/>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="30" t="n"/>
+      <c r="O27" s="31" t="n"/>
+      <c r="P27" s="33" t="n"/>
+      <c r="Q27" s="29" t="n"/>
+      <c r="R27" s="30" t="n"/>
+      <c r="S27" s="31" t="n"/>
+      <c r="T27" s="26" t="n"/>
+      <c r="U27" s="29" t="n"/>
+      <c r="V27" s="30" t="n"/>
+      <c r="W27" s="31" t="n"/>
       <c r="X27" s="33" t="n"/>
-      <c r="Y27" s="28" t="n"/>
-      <c r="Z27" s="29" t="n"/>
-      <c r="AA27" s="30" t="n"/>
-      <c r="AB27" s="23" t="n"/>
-      <c r="AC27" s="28" t="n"/>
-      <c r="AD27" s="29" t="n"/>
-      <c r="AE27" s="30" t="n"/>
+      <c r="Y27" s="29" t="n"/>
+      <c r="Z27" s="30" t="n"/>
+      <c r="AA27" s="31" t="n"/>
+      <c r="AB27" s="24" t="n"/>
+      <c r="AC27" s="29" t="n"/>
+      <c r="AD27" s="30" t="n"/>
+      <c r="AE27" s="31" t="n"/>
       <c r="AF27" s="33" t="n"/>
-      <c r="AG27" s="28" t="n"/>
-      <c r="AH27" s="29" t="n"/>
-      <c r="AI27" s="30" t="n"/>
-      <c r="AJ27" s="16" t="n"/>
-      <c r="AK27" s="28" t="n"/>
-      <c r="AL27" s="29" t="n"/>
-      <c r="AM27" s="30" t="n"/>
-      <c r="AN27" s="25" t="n"/>
-      <c r="AO27" s="28" t="n"/>
-      <c r="AP27" s="29" t="n"/>
-      <c r="AQ27" s="31" t="n"/>
+      <c r="AG27" s="29" t="n"/>
+      <c r="AH27" s="30" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="18" t="inlineStr">
+        <is>
+          <t>WE Ascension</t>
+        </is>
+      </c>
+      <c r="AK27" s="29" t="n"/>
+      <c r="AL27" s="30" t="n"/>
+      <c r="AM27" s="31" t="n"/>
+      <c r="AN27" s="33" t="n"/>
+      <c r="AO27" s="29" t="n"/>
+      <c r="AP27" s="30" t="n"/>
+      <c r="AQ27" s="32" t="n"/>
       <c r="AR27" s="33" t="n"/>
-      <c r="AS27" s="28" t="n"/>
-      <c r="AT27" s="29" t="n"/>
-      <c r="AU27" s="31" t="n"/>
-      <c r="AV27" s="35" t="n"/>
+      <c r="AS27" s="29" t="n"/>
+      <c r="AT27" s="30" t="n"/>
+      <c r="AU27" s="32" t="n"/>
+      <c r="AV27" s="34" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2885,7 +2977,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2895,7 +2987,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="18" t="n"/>
+      <c r="H28" s="19" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2905,7 +2997,7 @@
         <v>9</v>
       </c>
       <c r="K28" s="7" t="n"/>
-      <c r="L28" s="23" t="n"/>
+      <c r="L28" s="24" t="n"/>
       <c r="M28" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2915,7 +3007,7 @@
         <v>9</v>
       </c>
       <c r="O28" s="7" t="n"/>
-      <c r="P28" s="18" t="n"/>
+      <c r="P28" s="19" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2925,7 +3017,7 @@
         <v>9</v>
       </c>
       <c r="S28" s="7" t="n"/>
-      <c r="T28" s="34" t="inlineStr">
+      <c r="T28" s="16" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -2953,7 +3045,7 @@
         <v>9</v>
       </c>
       <c r="AA28" s="7" t="n"/>
-      <c r="AB28" s="23" t="n"/>
+      <c r="AB28" s="26" t="n"/>
       <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2963,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="AE28" s="7" t="n"/>
-      <c r="AF28" s="18" t="n"/>
+      <c r="AF28" s="19" t="n"/>
       <c r="AG28" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2972,8 +3064,8 @@
       <c r="AH28" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="AI28" s="43" t="n"/>
-      <c r="AJ28" s="23" t="n"/>
+      <c r="AI28" s="41" t="n"/>
+      <c r="AJ28" s="24" t="n"/>
       <c r="AK28" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2983,7 +3075,7 @@
         <v>9</v>
       </c>
       <c r="AM28" s="7" t="n"/>
-      <c r="AN28" s="18" t="n"/>
+      <c r="AN28" s="19" t="n"/>
       <c r="AO28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2993,7 +3085,7 @@
         <v>9</v>
       </c>
       <c r="AQ28" s="12" t="n"/>
-      <c r="AR28" s="18" t="n"/>
+      <c r="AR28" s="19" t="n"/>
       <c r="AS28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3003,106 +3095,114 @@
         <v>9</v>
       </c>
       <c r="AU28" s="12" t="n"/>
-      <c r="AV28" s="18" t="n"/>
+      <c r="AV28" s="19" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1">
-      <c r="A29" s="21" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="25" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="O29" s="22" t="n"/>
-      <c r="P29" s="26" t="n"/>
-      <c r="Q29" s="21" t="n"/>
-      <c r="S29" s="22" t="n"/>
-      <c r="T29" s="37" t="inlineStr">
+      <c r="A29" s="22" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="27" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="26" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="S29" s="23" t="n"/>
+      <c r="T29" s="36" t="inlineStr">
         <is>
           <t>Prépa Appel décisif</t>
         </is>
       </c>
-      <c r="U29" s="21" t="n"/>
-      <c r="W29" s="22" t="n"/>
-      <c r="X29" s="23" t="n"/>
-      <c r="Y29" s="21" t="n"/>
-      <c r="AA29" s="22" t="n"/>
-      <c r="AB29" s="25" t="n"/>
-      <c r="AC29" s="21" t="n"/>
-      <c r="AE29" s="22" t="n"/>
-      <c r="AF29" s="26" t="n"/>
-      <c r="AG29" s="21" t="n"/>
-      <c r="AI29" s="46" t="n"/>
-      <c r="AJ29" s="23" t="n"/>
-      <c r="AK29" s="21" t="n"/>
-      <c r="AM29" s="22" t="n"/>
-      <c r="AN29" s="26" t="n"/>
-      <c r="AO29" s="21" t="n"/>
-      <c r="AQ29" s="24" t="n"/>
-      <c r="AR29" s="26" t="n"/>
-      <c r="AS29" s="21" t="n"/>
-      <c r="AU29" s="24" t="n"/>
-      <c r="AV29" s="26" t="n"/>
+      <c r="U29" s="22" t="n"/>
+      <c r="W29" s="23" t="n"/>
+      <c r="X29" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Y29" s="22" t="n"/>
+      <c r="AA29" s="23" t="n"/>
+      <c r="AB29" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="AC29" s="22" t="n"/>
+      <c r="AE29" s="23" t="n"/>
+      <c r="AF29" s="27" t="n"/>
+      <c r="AG29" s="22" t="n"/>
+      <c r="AI29" s="44" t="n"/>
+      <c r="AJ29" s="24" t="n"/>
+      <c r="AK29" s="22" t="n"/>
+      <c r="AM29" s="23" t="n"/>
+      <c r="AN29" s="27" t="n"/>
+      <c r="AO29" s="22" t="n"/>
+      <c r="AQ29" s="25" t="n"/>
+      <c r="AR29" s="27" t="n"/>
+      <c r="AS29" s="22" t="n"/>
+      <c r="AU29" s="25" t="n"/>
+      <c r="AV29" s="27" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1">
-      <c r="A30" s="28" t="n"/>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="30" t="n"/>
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="31" t="n"/>
       <c r="D30" s="33" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="29" t="n"/>
-      <c r="G30" s="30" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="31" t="n"/>
       <c r="H30" s="33" t="n"/>
-      <c r="I30" s="28" t="n"/>
-      <c r="J30" s="29" t="n"/>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="19" t="inlineStr">
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="51" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
       </c>
-      <c r="M30" s="28" t="n"/>
-      <c r="N30" s="29" t="n"/>
-      <c r="O30" s="30" t="n"/>
+      <c r="M30" s="29" t="n"/>
+      <c r="N30" s="30" t="n"/>
+      <c r="O30" s="31" t="n"/>
       <c r="P30" s="33" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="29" t="n"/>
-      <c r="S30" s="30" t="n"/>
+      <c r="Q30" s="29" t="n"/>
+      <c r="R30" s="30" t="n"/>
+      <c r="S30" s="31" t="n"/>
       <c r="T30" s="33" t="n"/>
-      <c r="U30" s="28" t="n"/>
-      <c r="V30" s="29" t="n"/>
-      <c r="W30" s="30" t="n"/>
-      <c r="X30" s="25" t="n"/>
-      <c r="Y30" s="28" t="n"/>
-      <c r="Z30" s="29" t="n"/>
-      <c r="AA30" s="30" t="n"/>
-      <c r="AB30" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="AC30" s="28" t="n"/>
-      <c r="AD30" s="29" t="n"/>
-      <c r="AE30" s="30" t="n"/>
+      <c r="U30" s="29" t="n"/>
+      <c r="V30" s="30" t="n"/>
+      <c r="W30" s="31" t="n"/>
+      <c r="X30" s="33" t="n"/>
+      <c r="Y30" s="29" t="n"/>
+      <c r="Z30" s="30" t="n"/>
+      <c r="AA30" s="31" t="n"/>
+      <c r="AB30" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AC30" s="29" t="n"/>
+      <c r="AD30" s="30" t="n"/>
+      <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="33" t="n"/>
-      <c r="AG30" s="28" t="n"/>
-      <c r="AH30" s="29" t="n"/>
-      <c r="AI30" s="47" t="n"/>
-      <c r="AJ30" s="25" t="n"/>
-      <c r="AK30" s="28" t="n"/>
-      <c r="AL30" s="29" t="n"/>
-      <c r="AM30" s="30" t="n"/>
+      <c r="AG30" s="29" t="n"/>
+      <c r="AH30" s="30" t="n"/>
+      <c r="AI30" s="45" t="n"/>
+      <c r="AJ30" s="26" t="n"/>
+      <c r="AK30" s="29" t="n"/>
+      <c r="AL30" s="30" t="n"/>
+      <c r="AM30" s="31" t="n"/>
       <c r="AN30" s="33" t="n"/>
-      <c r="AO30" s="28" t="n"/>
-      <c r="AP30" s="29" t="n"/>
-      <c r="AQ30" s="31" t="n"/>
+      <c r="AO30" s="29" t="n"/>
+      <c r="AP30" s="30" t="n"/>
+      <c r="AQ30" s="32" t="n"/>
       <c r="AR30" s="33" t="n"/>
-      <c r="AS30" s="28" t="n"/>
-      <c r="AT30" s="29" t="n"/>
-      <c r="AU30" s="31" t="n"/>
+      <c r="AS30" s="29" t="n"/>
+      <c r="AT30" s="30" t="n"/>
+      <c r="AU30" s="32" t="n"/>
       <c r="AV30" s="33" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1">
@@ -3115,7 +3215,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3125,9 +3225,9 @@
         <v>10</v>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="34" t="inlineStr">
-        <is>
-          <t>CMP</t>
+      <c r="H31" s="40" t="inlineStr">
+        <is>
+          <t>Baptême</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3139,7 +3239,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="25" t="n"/>
+      <c r="L31" s="26" t="n"/>
       <c r="M31" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3149,7 +3249,7 @@
         <v>10</v>
       </c>
       <c r="O31" s="7" t="n"/>
-      <c r="P31" s="18" t="n"/>
+      <c r="P31" s="19" t="n"/>
       <c r="Q31" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3158,8 +3258,8 @@
       <c r="R31" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S31" s="43" t="n"/>
-      <c r="T31" s="16" t="inlineStr">
+      <c r="S31" s="41" t="n"/>
+      <c r="T31" s="18" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3173,7 +3273,7 @@
         <v>10</v>
       </c>
       <c r="W31" s="7" t="n"/>
-      <c r="X31" s="49" t="inlineStr">
+      <c r="X31" s="47" t="inlineStr">
         <is>
           <t>Cendres</t>
         </is>
@@ -3187,7 +3287,7 @@
         <v>10</v>
       </c>
       <c r="AA31" s="7" t="n"/>
-      <c r="AB31" s="18" t="n"/>
+      <c r="AB31" s="19" t="n"/>
       <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3197,7 +3297,7 @@
         <v>10</v>
       </c>
       <c r="AE31" s="7" t="n"/>
-      <c r="AF31" s="34" t="inlineStr">
+      <c r="AF31" s="16" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3211,7 +3311,7 @@
         <v>10</v>
       </c>
       <c r="AI31" s="7" t="n"/>
-      <c r="AJ31" s="18" t="n"/>
+      <c r="AJ31" s="19" t="n"/>
       <c r="AK31" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3221,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="AM31" s="7" t="n"/>
-      <c r="AN31" s="18" t="n"/>
+      <c r="AN31" s="19" t="n"/>
       <c r="AO31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3231,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" s="12" t="n"/>
-      <c r="AR31" s="16" t="inlineStr">
+      <c r="AR31" s="18" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3245,106 +3345,114 @@
         <v>10</v>
       </c>
       <c r="AU31" s="12" t="n"/>
-      <c r="AV31" s="18" t="n"/>
+      <c r="AV31" s="19" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1">
-      <c r="A32" s="21" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="42" t="inlineStr">
+      <c r="A32" s="22" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="n"/>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="n"/>
+      <c r="O32" s="23" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="S32" s="44" t="n"/>
+      <c r="T32" s="24" t="n"/>
+      <c r="U32" s="22" t="n"/>
+      <c r="W32" s="23" t="n"/>
+      <c r="X32" s="24" t="n"/>
+      <c r="Y32" s="22" t="n"/>
+      <c r="AA32" s="23" t="n"/>
+      <c r="AB32" s="27" t="n"/>
+      <c r="AC32" s="22" t="n"/>
+      <c r="AE32" s="23" t="n"/>
+      <c r="AF32" s="36" t="inlineStr">
+        <is>
+          <t>Formation Eucharistie</t>
+        </is>
+      </c>
+      <c r="AG32" s="22" t="n"/>
+      <c r="AI32" s="23" t="n"/>
+      <c r="AJ32" s="27" t="n"/>
+      <c r="AK32" s="22" t="n"/>
+      <c r="AM32" s="23" t="n"/>
+      <c r="AN32" s="27" t="n"/>
+      <c r="AO32" s="22" t="n"/>
+      <c r="AQ32" s="25" t="n"/>
+      <c r="AR32" s="24" t="n"/>
+      <c r="AS32" s="22" t="n"/>
+      <c r="AU32" s="25" t="n"/>
+      <c r="AV32" s="27" t="n"/>
+    </row>
+    <row r="33" ht="20.1" customHeight="1">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="I32" s="21" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="n"/>
-      <c r="O32" s="22" t="n"/>
-      <c r="P32" s="26" t="n"/>
-      <c r="Q32" s="21" t="n"/>
-      <c r="S32" s="46" t="n"/>
-      <c r="T32" s="23" t="n"/>
-      <c r="U32" s="21" t="n"/>
-      <c r="W32" s="22" t="n"/>
-      <c r="X32" s="23" t="n"/>
-      <c r="Y32" s="21" t="n"/>
-      <c r="AA32" s="22" t="n"/>
-      <c r="AB32" s="26" t="n"/>
-      <c r="AC32" s="21" t="n"/>
-      <c r="AE32" s="22" t="n"/>
-      <c r="AF32" s="37" t="inlineStr">
-        <is>
-          <t>Formation Eucharistie</t>
-        </is>
-      </c>
-      <c r="AG32" s="21" t="n"/>
-      <c r="AI32" s="22" t="n"/>
-      <c r="AJ32" s="26" t="n"/>
-      <c r="AK32" s="21" t="n"/>
-      <c r="AM32" s="22" t="n"/>
-      <c r="AN32" s="26" t="n"/>
-      <c r="AO32" s="21" t="n"/>
-      <c r="AQ32" s="24" t="n"/>
-      <c r="AR32" s="23" t="n"/>
-      <c r="AS32" s="21" t="n"/>
-      <c r="AU32" s="24" t="n"/>
-      <c r="AV32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="20.1" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="28" t="n"/>
-      <c r="J33" s="29" t="n"/>
-      <c r="K33" s="30" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="28" t="n"/>
-      <c r="N33" s="29" t="n"/>
-      <c r="O33" s="30" t="n"/>
+      <c r="I33" s="29" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="31" t="n"/>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="M33" s="29" t="n"/>
+      <c r="N33" s="30" t="n"/>
+      <c r="O33" s="31" t="n"/>
       <c r="P33" s="33" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="29" t="n"/>
-      <c r="S33" s="47" t="n"/>
-      <c r="T33" s="25" t="n"/>
-      <c r="U33" s="28" t="n"/>
-      <c r="V33" s="29" t="n"/>
-      <c r="W33" s="30" t="n"/>
-      <c r="X33" s="25" t="n"/>
-      <c r="Y33" s="28" t="n"/>
-      <c r="Z33" s="29" t="n"/>
-      <c r="AA33" s="30" t="n"/>
+      <c r="Q33" s="29" t="n"/>
+      <c r="R33" s="30" t="n"/>
+      <c r="S33" s="45" t="n"/>
+      <c r="T33" s="26" t="n"/>
+      <c r="U33" s="29" t="n"/>
+      <c r="V33" s="30" t="n"/>
+      <c r="W33" s="31" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="29" t="n"/>
+      <c r="Z33" s="30" t="n"/>
+      <c r="AA33" s="31" t="n"/>
       <c r="AB33" s="33" t="n"/>
-      <c r="AC33" s="28" t="n"/>
-      <c r="AD33" s="29" t="n"/>
-      <c r="AE33" s="30" t="n"/>
+      <c r="AC33" s="29" t="n"/>
+      <c r="AD33" s="30" t="n"/>
+      <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="33" t="n"/>
-      <c r="AG33" s="28" t="n"/>
-      <c r="AH33" s="29" t="n"/>
-      <c r="AI33" s="30" t="n"/>
+      <c r="AG33" s="29" t="n"/>
+      <c r="AH33" s="30" t="n"/>
+      <c r="AI33" s="31" t="n"/>
       <c r="AJ33" s="33" t="n"/>
-      <c r="AK33" s="28" t="n"/>
-      <c r="AL33" s="29" t="n"/>
-      <c r="AM33" s="30" t="n"/>
+      <c r="AK33" s="29" t="n"/>
+      <c r="AL33" s="30" t="n"/>
+      <c r="AM33" s="31" t="n"/>
       <c r="AN33" s="33" t="n"/>
-      <c r="AO33" s="28" t="n"/>
-      <c r="AP33" s="29" t="n"/>
-      <c r="AQ33" s="31" t="n"/>
-      <c r="AR33" s="25" t="n"/>
-      <c r="AS33" s="28" t="n"/>
-      <c r="AT33" s="29" t="n"/>
-      <c r="AU33" s="31" t="n"/>
+      <c r="AO33" s="29" t="n"/>
+      <c r="AP33" s="30" t="n"/>
+      <c r="AQ33" s="32" t="n"/>
+      <c r="AR33" s="26" t="n"/>
+      <c r="AS33" s="29" t="n"/>
+      <c r="AT33" s="30" t="n"/>
+      <c r="AU33" s="32" t="n"/>
       <c r="AV33" s="33" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1">
@@ -3357,7 +3465,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3366,10 +3474,10 @@
       <c r="F34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>Éveil à la Foi</t>
+      <c r="G34" s="41" t="n"/>
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>Baptême</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3381,7 +3489,11 @@
         <v>11</v>
       </c>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="25" t="n"/>
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>Armistice 1918</t>
+        </is>
+      </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3391,7 +3503,7 @@
         <v>11</v>
       </c>
       <c r="O34" s="7" t="n"/>
-      <c r="P34" s="36" t="inlineStr">
+      <c r="P34" s="35" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -3405,7 +3517,7 @@
         <v>11</v>
       </c>
       <c r="S34" s="7" t="n"/>
-      <c r="T34" s="18" t="n"/>
+      <c r="T34" s="19" t="n"/>
       <c r="U34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3415,7 +3527,7 @@
         <v>11</v>
       </c>
       <c r="W34" s="7" t="n"/>
-      <c r="X34" s="18" t="n"/>
+      <c r="X34" s="19" t="n"/>
       <c r="Y34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3425,7 +3537,7 @@
         <v>11</v>
       </c>
       <c r="AA34" s="7" t="n"/>
-      <c r="AB34" s="36" t="inlineStr">
+      <c r="AB34" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -3438,8 +3550,8 @@
       <c r="AD34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="AE34" s="43" t="n"/>
-      <c r="AF34" s="16" t="inlineStr">
+      <c r="AE34" s="41" t="n"/>
+      <c r="AF34" s="18" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3467,7 +3579,7 @@
         <v>11</v>
       </c>
       <c r="AM34" s="7" t="n"/>
-      <c r="AN34" s="18" t="n"/>
+      <c r="AN34" s="19" t="n"/>
       <c r="AO34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3477,7 +3589,7 @@
         <v>11</v>
       </c>
       <c r="AQ34" s="12" t="n"/>
-      <c r="AR34" s="20" t="n"/>
+      <c r="AR34" s="21" t="n"/>
       <c r="AS34" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3487,102 +3599,110 @@
         <v>11</v>
       </c>
       <c r="AU34" s="12" t="n"/>
-      <c r="AV34" s="18" t="n"/>
+      <c r="AV34" s="19" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1">
-      <c r="A35" s="21" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="G35" s="46" t="n"/>
-      <c r="H35" s="52" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="K35" s="22" t="n"/>
-      <c r="L35" s="32" t="inlineStr">
-        <is>
-          <t>Armistice 1918</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="n"/>
-      <c r="O35" s="22" t="n"/>
-      <c r="P35" s="23" t="n"/>
-      <c r="Q35" s="21" t="n"/>
-      <c r="S35" s="22" t="n"/>
-      <c r="T35" s="26" t="n"/>
-      <c r="U35" s="21" t="n"/>
-      <c r="W35" s="22" t="n"/>
-      <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="21" t="n"/>
-      <c r="AA35" s="22" t="n"/>
-      <c r="AB35" s="23" t="n"/>
-      <c r="AC35" s="21" t="n"/>
-      <c r="AE35" s="46" t="n"/>
-      <c r="AF35" s="23" t="n"/>
-      <c r="AG35" s="21" t="n"/>
-      <c r="AI35" s="22" t="n"/>
-      <c r="AJ35" s="23" t="n"/>
-      <c r="AK35" s="21" t="n"/>
-      <c r="AM35" s="22" t="n"/>
-      <c r="AN35" s="26" t="n"/>
-      <c r="AO35" s="21" t="n"/>
-      <c r="AQ35" s="24" t="n"/>
-      <c r="AR35" s="27" t="n"/>
-      <c r="AS35" s="21" t="n"/>
-      <c r="AU35" s="24" t="n"/>
-      <c r="AV35" s="26" t="n"/>
+      <c r="A35" s="22" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="G35" s="44" t="n"/>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Éveil à la Foi</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="n"/>
+      <c r="K35" s="23" t="n"/>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>Éveil à la Foi</t>
+        </is>
+      </c>
+      <c r="M35" s="22" t="n"/>
+      <c r="O35" s="23" t="n"/>
+      <c r="P35" s="24" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="S35" s="23" t="n"/>
+      <c r="T35" s="27" t="n"/>
+      <c r="U35" s="22" t="n"/>
+      <c r="W35" s="23" t="n"/>
+      <c r="X35" s="27" t="n"/>
+      <c r="Y35" s="22" t="n"/>
+      <c r="AA35" s="23" t="n"/>
+      <c r="AB35" s="24" t="n"/>
+      <c r="AC35" s="22" t="n"/>
+      <c r="AE35" s="44" t="n"/>
+      <c r="AF35" s="24" t="n"/>
+      <c r="AG35" s="22" t="n"/>
+      <c r="AI35" s="23" t="n"/>
+      <c r="AJ35" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AK35" s="22" t="n"/>
+      <c r="AM35" s="23" t="n"/>
+      <c r="AN35" s="27" t="n"/>
+      <c r="AO35" s="22" t="n"/>
+      <c r="AQ35" s="25" t="n"/>
+      <c r="AR35" s="28" t="n"/>
+      <c r="AS35" s="22" t="n"/>
+      <c r="AU35" s="25" t="n"/>
+      <c r="AV35" s="27" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1">
-      <c r="A36" s="28" t="n"/>
-      <c r="B36" s="29" t="n"/>
-      <c r="C36" s="30" t="n"/>
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="31" t="n"/>
       <c r="D36" s="33" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="47" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="28" t="n"/>
-      <c r="J36" s="29" t="n"/>
-      <c r="K36" s="30" t="n"/>
-      <c r="L36" s="34" t="inlineStr">
-        <is>
-          <t>Éveil à la Foi</t>
-        </is>
-      </c>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="30" t="n"/>
-      <c r="P36" s="25" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="30" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="45" t="n"/>
+      <c r="H36" s="52" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="42" t="inlineStr">
+        <is>
+          <t>Père Pascal en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="30" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="26" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="30" t="n"/>
+      <c r="S36" s="31" t="n"/>
       <c r="T36" s="33" t="n"/>
-      <c r="U36" s="28" t="n"/>
-      <c r="V36" s="29" t="n"/>
-      <c r="W36" s="30" t="n"/>
+      <c r="U36" s="29" t="n"/>
+      <c r="V36" s="30" t="n"/>
+      <c r="W36" s="31" t="n"/>
       <c r="X36" s="33" t="n"/>
-      <c r="Y36" s="28" t="n"/>
-      <c r="Z36" s="29" t="n"/>
-      <c r="AA36" s="30" t="n"/>
-      <c r="AB36" s="25" t="n"/>
-      <c r="AC36" s="28" t="n"/>
-      <c r="AD36" s="29" t="n"/>
-      <c r="AE36" s="47" t="n"/>
-      <c r="AF36" s="25" t="n"/>
-      <c r="AG36" s="28" t="n"/>
-      <c r="AH36" s="29" t="n"/>
-      <c r="AI36" s="30" t="n"/>
-      <c r="AJ36" s="25" t="n"/>
-      <c r="AK36" s="28" t="n"/>
-      <c r="AL36" s="29" t="n"/>
-      <c r="AM36" s="30" t="n"/>
+      <c r="Y36" s="29" t="n"/>
+      <c r="Z36" s="30" t="n"/>
+      <c r="AA36" s="31" t="n"/>
+      <c r="AB36" s="26" t="n"/>
+      <c r="AC36" s="29" t="n"/>
+      <c r="AD36" s="30" t="n"/>
+      <c r="AE36" s="45" t="n"/>
+      <c r="AF36" s="26" t="n"/>
+      <c r="AG36" s="29" t="n"/>
+      <c r="AH36" s="30" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="33" t="n"/>
+      <c r="AK36" s="29" t="n"/>
+      <c r="AL36" s="30" t="n"/>
+      <c r="AM36" s="31" t="n"/>
       <c r="AN36" s="33" t="n"/>
-      <c r="AO36" s="28" t="n"/>
-      <c r="AP36" s="29" t="n"/>
-      <c r="AQ36" s="31" t="n"/>
-      <c r="AR36" s="35" t="n"/>
-      <c r="AS36" s="28" t="n"/>
-      <c r="AT36" s="29" t="n"/>
-      <c r="AU36" s="31" t="n"/>
+      <c r="AO36" s="29" t="n"/>
+      <c r="AP36" s="30" t="n"/>
+      <c r="AQ36" s="32" t="n"/>
+      <c r="AR36" s="34" t="n"/>
+      <c r="AS36" s="29" t="n"/>
+      <c r="AT36" s="30" t="n"/>
+      <c r="AU36" s="32" t="n"/>
       <c r="AV36" s="33" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1">
@@ -3595,7 +3715,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Rentrée Cté</t>
         </is>
@@ -3609,7 +3729,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="23" t="n"/>
+      <c r="H37" s="24" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3619,7 +3739,7 @@
         <v>12</v>
       </c>
       <c r="K37" s="7" t="n"/>
-      <c r="L37" s="44" t="n"/>
+      <c r="L37" s="24" t="n"/>
       <c r="M37" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -3629,9 +3749,9 @@
         <v>12</v>
       </c>
       <c r="O37" s="7" t="n"/>
-      <c r="P37" s="34" t="inlineStr">
-        <is>
-          <t>CMP</t>
+      <c r="P37" s="16" t="inlineStr">
+        <is>
+          <t>CMP avec Ecole des témoins</t>
         </is>
       </c>
       <c r="Q37" s="5" t="inlineStr">
@@ -3657,7 +3777,7 @@
         <v>12</v>
       </c>
       <c r="W37" s="7" t="n"/>
-      <c r="X37" s="18" t="n"/>
+      <c r="X37" s="19" t="n"/>
       <c r="Y37" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3667,7 +3787,7 @@
         <v>12</v>
       </c>
       <c r="AA37" s="7" t="n"/>
-      <c r="AB37" s="18" t="n"/>
+      <c r="AB37" s="19" t="n"/>
       <c r="AC37" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3677,7 +3797,7 @@
         <v>12</v>
       </c>
       <c r="AE37" s="7" t="n"/>
-      <c r="AF37" s="18" t="n"/>
+      <c r="AF37" s="19" t="n"/>
       <c r="AG37" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3687,7 +3807,7 @@
         <v>12</v>
       </c>
       <c r="AI37" s="7" t="n"/>
-      <c r="AJ37" s="18" t="n"/>
+      <c r="AJ37" s="19" t="n"/>
       <c r="AK37" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3697,7 +3817,7 @@
         <v>12</v>
       </c>
       <c r="AM37" s="7" t="n"/>
-      <c r="AN37" s="34" t="inlineStr">
+      <c r="AN37" s="16" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3711,7 +3831,7 @@
         <v>12</v>
       </c>
       <c r="AQ37" s="12" t="n"/>
-      <c r="AR37" s="18" t="n"/>
+      <c r="AR37" s="19" t="n"/>
       <c r="AS37" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3721,102 +3841,106 @@
         <v>12</v>
       </c>
       <c r="AU37" s="12" t="n"/>
-      <c r="AV37" s="18" t="n"/>
+      <c r="AV37" s="19" t="n"/>
     </row>
     <row r="38" ht="20.1" customHeight="1">
-      <c r="A38" s="21" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="23" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="23" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="O38" s="22" t="n"/>
-      <c r="P38" s="16" t="inlineStr">
+      <c r="A38" s="22" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="K38" s="23" t="n"/>
+      <c r="L38" s="24" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="O38" s="23" t="n"/>
+      <c r="P38" s="18" t="inlineStr">
         <is>
           <t>WE Frat ccn</t>
         </is>
       </c>
-      <c r="Q38" s="21" t="n"/>
-      <c r="S38" s="22" t="n"/>
-      <c r="T38" s="23" t="n"/>
-      <c r="U38" s="21" t="n"/>
-      <c r="W38" s="22" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="21" t="n"/>
-      <c r="AA38" s="22" t="n"/>
-      <c r="AB38" s="26" t="n"/>
-      <c r="AC38" s="21" t="n"/>
-      <c r="AE38" s="22" t="n"/>
-      <c r="AF38" s="26" t="n"/>
-      <c r="AG38" s="21" t="n"/>
-      <c r="AI38" s="22" t="n"/>
-      <c r="AJ38" s="26" t="n"/>
-      <c r="AK38" s="21" t="n"/>
-      <c r="AM38" s="22" t="n"/>
-      <c r="AN38" s="37" t="inlineStr">
+      <c r="Q38" s="22" t="n"/>
+      <c r="S38" s="23" t="n"/>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="U38" s="22" t="n"/>
+      <c r="W38" s="23" t="n"/>
+      <c r="X38" s="27" t="n"/>
+      <c r="Y38" s="22" t="n"/>
+      <c r="AA38" s="23" t="n"/>
+      <c r="AB38" s="27" t="n"/>
+      <c r="AC38" s="22" t="n"/>
+      <c r="AE38" s="23" t="n"/>
+      <c r="AF38" s="27" t="n"/>
+      <c r="AG38" s="22" t="n"/>
+      <c r="AI38" s="23" t="n"/>
+      <c r="AJ38" s="27" t="n"/>
+      <c r="AK38" s="22" t="n"/>
+      <c r="AM38" s="23" t="n"/>
+      <c r="AN38" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
-      <c r="AO38" s="21" t="n"/>
-      <c r="AQ38" s="24" t="n"/>
-      <c r="AR38" s="26" t="n"/>
-      <c r="AS38" s="21" t="n"/>
-      <c r="AU38" s="24" t="n"/>
-      <c r="AV38" s="26" t="n"/>
+      <c r="AO38" s="22" t="n"/>
+      <c r="AQ38" s="25" t="n"/>
+      <c r="AR38" s="27" t="n"/>
+      <c r="AS38" s="22" t="n"/>
+      <c r="AU38" s="25" t="n"/>
+      <c r="AV38" s="27" t="n"/>
     </row>
     <row r="39" ht="20.1" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="28" t="n"/>
-      <c r="F39" s="29" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="23" t="n"/>
-      <c r="I39" s="28" t="n"/>
-      <c r="J39" s="29" t="n"/>
-      <c r="K39" s="30" t="n"/>
-      <c r="L39" s="23" t="n"/>
-      <c r="M39" s="28" t="n"/>
-      <c r="N39" s="29" t="n"/>
-      <c r="O39" s="30" t="n"/>
-      <c r="P39" s="23" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="29" t="n"/>
-      <c r="S39" s="30" t="n"/>
-      <c r="T39" s="25" t="n"/>
-      <c r="U39" s="28" t="n"/>
-      <c r="V39" s="29" t="n"/>
-      <c r="W39" s="30" t="n"/>
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="29" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="31" t="n"/>
+      <c r="L39" s="24" t="n"/>
+      <c r="M39" s="29" t="n"/>
+      <c r="N39" s="30" t="n"/>
+      <c r="O39" s="31" t="n"/>
+      <c r="P39" s="24" t="n"/>
+      <c r="Q39" s="29" t="n"/>
+      <c r="R39" s="30" t="n"/>
+      <c r="S39" s="31" t="n"/>
+      <c r="T39" s="33" t="n"/>
+      <c r="U39" s="29" t="n"/>
+      <c r="V39" s="30" t="n"/>
+      <c r="W39" s="31" t="n"/>
       <c r="X39" s="33" t="n"/>
-      <c r="Y39" s="28" t="n"/>
-      <c r="Z39" s="29" t="n"/>
-      <c r="AA39" s="30" t="n"/>
+      <c r="Y39" s="29" t="n"/>
+      <c r="Z39" s="30" t="n"/>
+      <c r="AA39" s="31" t="n"/>
       <c r="AB39" s="33" t="n"/>
-      <c r="AC39" s="28" t="n"/>
-      <c r="AD39" s="29" t="n"/>
-      <c r="AE39" s="30" t="n"/>
+      <c r="AC39" s="29" t="n"/>
+      <c r="AD39" s="30" t="n"/>
+      <c r="AE39" s="31" t="n"/>
       <c r="AF39" s="33" t="n"/>
-      <c r="AG39" s="28" t="n"/>
-      <c r="AH39" s="29" t="n"/>
-      <c r="AI39" s="30" t="n"/>
+      <c r="AG39" s="29" t="n"/>
+      <c r="AH39" s="30" t="n"/>
+      <c r="AI39" s="31" t="n"/>
       <c r="AJ39" s="33" t="n"/>
-      <c r="AK39" s="28" t="n"/>
-      <c r="AL39" s="29" t="n"/>
-      <c r="AM39" s="30" t="n"/>
+      <c r="AK39" s="29" t="n"/>
+      <c r="AL39" s="30" t="n"/>
+      <c r="AM39" s="31" t="n"/>
       <c r="AN39" s="33" t="n"/>
-      <c r="AO39" s="28" t="n"/>
-      <c r="AP39" s="29" t="n"/>
-      <c r="AQ39" s="31" t="n"/>
+      <c r="AO39" s="29" t="n"/>
+      <c r="AP39" s="30" t="n"/>
+      <c r="AQ39" s="32" t="n"/>
       <c r="AR39" s="33" t="n"/>
-      <c r="AS39" s="28" t="n"/>
-      <c r="AT39" s="29" t="n"/>
-      <c r="AU39" s="31" t="n"/>
+      <c r="AS39" s="29" t="n"/>
+      <c r="AT39" s="30" t="n"/>
+      <c r="AU39" s="32" t="n"/>
       <c r="AV39" s="33" t="n"/>
     </row>
     <row r="40" ht="20.1" customHeight="1">
@@ -3828,8 +3952,8 @@
       <c r="B40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C40" s="43" t="n"/>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="C40" s="41" t="n"/>
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>Rentrée Kion</t>
         </is>
@@ -3843,7 +3967,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="23" t="n"/>
+      <c r="H40" s="24" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3853,7 +3977,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="7" t="n"/>
-      <c r="L40" s="23" t="n"/>
+      <c r="L40" s="24" t="n"/>
       <c r="M40" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -3862,8 +3986,8 @@
       <c r="N40" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="O40" s="43" t="n"/>
-      <c r="P40" s="25" t="n"/>
+      <c r="O40" s="41" t="n"/>
+      <c r="P40" s="26" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3873,7 +3997,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="7" t="n"/>
-      <c r="T40" s="18" t="n"/>
+      <c r="T40" s="19" t="n"/>
       <c r="U40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -3883,11 +4007,7 @@
         <v>13</v>
       </c>
       <c r="W40" s="7" t="n"/>
-      <c r="X40" s="16" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
+      <c r="X40" s="19" t="n"/>
       <c r="Y40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -3897,7 +4017,7 @@
         <v>13</v>
       </c>
       <c r="AA40" s="7" t="n"/>
-      <c r="AB40" s="16" t="inlineStr">
+      <c r="AB40" s="18" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3925,7 +4045,7 @@
         <v>13</v>
       </c>
       <c r="AI40" s="7" t="n"/>
-      <c r="AJ40" s="36" t="inlineStr">
+      <c r="AJ40" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -3938,8 +4058,8 @@
       <c r="AL40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="AM40" s="43" t="n"/>
-      <c r="AN40" s="20" t="n"/>
+      <c r="AM40" s="41" t="n"/>
+      <c r="AN40" s="21" t="n"/>
       <c r="AO40" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -3949,7 +4069,7 @@
         <v>13</v>
       </c>
       <c r="AQ40" s="12" t="n"/>
-      <c r="AR40" s="18" t="n"/>
+      <c r="AR40" s="19" t="n"/>
       <c r="AS40" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3959,106 +4079,110 @@
         <v>13</v>
       </c>
       <c r="AU40" s="12" t="n"/>
-      <c r="AV40" s="18" t="n"/>
+      <c r="AV40" s="19" t="n"/>
     </row>
     <row r="41" ht="20.1" customHeight="1">
-      <c r="A41" s="21" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="G41" s="22" t="n"/>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="K41" s="22" t="n"/>
-      <c r="L41" s="23" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="O41" s="46" t="n"/>
-      <c r="P41" s="51" t="inlineStr">
+      <c r="A41" s="22" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="K41" s="23" t="n"/>
+      <c r="L41" s="24" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="O41" s="44" t="n"/>
+      <c r="P41" s="49" t="inlineStr">
         <is>
           <t>3e dim. de l'Avent</t>
         </is>
       </c>
-      <c r="Q41" s="21" t="n"/>
-      <c r="S41" s="22" t="n"/>
-      <c r="T41" s="26" t="n"/>
-      <c r="U41" s="21" t="n"/>
-      <c r="W41" s="22" t="n"/>
-      <c r="X41" s="23" t="n"/>
-      <c r="Y41" s="21" t="n"/>
-      <c r="AA41" s="22" t="n"/>
-      <c r="AB41" s="23" t="n"/>
-      <c r="AC41" s="21" t="n"/>
-      <c r="AE41" s="22" t="n"/>
-      <c r="AF41" s="23" t="n"/>
-      <c r="AG41" s="21" t="n"/>
-      <c r="AI41" s="22" t="n"/>
-      <c r="AJ41" s="23" t="n"/>
-      <c r="AK41" s="21" t="n"/>
-      <c r="AM41" s="46" t="n"/>
-      <c r="AN41" s="27" t="n"/>
-      <c r="AO41" s="21" t="n"/>
-      <c r="AQ41" s="24" t="n"/>
-      <c r="AR41" s="26" t="n"/>
-      <c r="AS41" s="21" t="n"/>
-      <c r="AU41" s="24" t="n"/>
-      <c r="AV41" s="26" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="S41" s="23" t="n"/>
+      <c r="T41" s="27" t="n"/>
+      <c r="U41" s="22" t="n"/>
+      <c r="W41" s="23" t="n"/>
+      <c r="X41" s="27" t="n"/>
+      <c r="Y41" s="22" t="n"/>
+      <c r="AA41" s="23" t="n"/>
+      <c r="AB41" s="24" t="n"/>
+      <c r="AC41" s="22" t="n"/>
+      <c r="AE41" s="23" t="n"/>
+      <c r="AF41" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AG41" s="22" t="n"/>
+      <c r="AI41" s="23" t="n"/>
+      <c r="AJ41" s="24" t="n"/>
+      <c r="AK41" s="22" t="n"/>
+      <c r="AM41" s="44" t="n"/>
+      <c r="AN41" s="28" t="n"/>
+      <c r="AO41" s="22" t="n"/>
+      <c r="AQ41" s="25" t="n"/>
+      <c r="AR41" s="27" t="n"/>
+      <c r="AS41" s="22" t="n"/>
+      <c r="AU41" s="25" t="n"/>
+      <c r="AV41" s="27" t="n"/>
     </row>
     <row r="42" ht="20.1" customHeight="1">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="47" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="34" t="inlineStr">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="45" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="29" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="29" t="n"/>
-      <c r="K42" s="30" t="n"/>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="28" t="n"/>
-      <c r="N42" s="29" t="n"/>
-      <c r="O42" s="47" t="n"/>
-      <c r="P42" s="34" t="inlineStr">
+      <c r="I42" s="29" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="31" t="n"/>
+      <c r="L42" s="24" t="n"/>
+      <c r="M42" s="29" t="n"/>
+      <c r="N42" s="30" t="n"/>
+      <c r="O42" s="45" t="n"/>
+      <c r="P42" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="29" t="n"/>
-      <c r="S42" s="30" t="n"/>
+      <c r="Q42" s="29" t="n"/>
+      <c r="R42" s="30" t="n"/>
+      <c r="S42" s="31" t="n"/>
       <c r="T42" s="33" t="n"/>
-      <c r="U42" s="28" t="n"/>
-      <c r="V42" s="29" t="n"/>
-      <c r="W42" s="30" t="n"/>
-      <c r="X42" s="25" t="n"/>
-      <c r="Y42" s="28" t="n"/>
-      <c r="Z42" s="29" t="n"/>
-      <c r="AA42" s="30" t="n"/>
-      <c r="AB42" s="25" t="n"/>
-      <c r="AC42" s="28" t="n"/>
-      <c r="AD42" s="29" t="n"/>
-      <c r="AE42" s="30" t="n"/>
-      <c r="AF42" s="25" t="n"/>
-      <c r="AG42" s="28" t="n"/>
-      <c r="AH42" s="29" t="n"/>
-      <c r="AI42" s="30" t="n"/>
-      <c r="AJ42" s="25" t="n"/>
-      <c r="AK42" s="28" t="n"/>
-      <c r="AL42" s="29" t="n"/>
-      <c r="AM42" s="47" t="n"/>
-      <c r="AN42" s="35" t="n"/>
-      <c r="AO42" s="28" t="n"/>
-      <c r="AP42" s="29" t="n"/>
-      <c r="AQ42" s="31" t="n"/>
+      <c r="U42" s="29" t="n"/>
+      <c r="V42" s="30" t="n"/>
+      <c r="W42" s="31" t="n"/>
+      <c r="X42" s="33" t="n"/>
+      <c r="Y42" s="29" t="n"/>
+      <c r="Z42" s="30" t="n"/>
+      <c r="AA42" s="31" t="n"/>
+      <c r="AB42" s="26" t="n"/>
+      <c r="AC42" s="29" t="n"/>
+      <c r="AD42" s="30" t="n"/>
+      <c r="AE42" s="31" t="n"/>
+      <c r="AF42" s="33" t="n"/>
+      <c r="AG42" s="29" t="n"/>
+      <c r="AH42" s="30" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="26" t="n"/>
+      <c r="AK42" s="29" t="n"/>
+      <c r="AL42" s="30" t="n"/>
+      <c r="AM42" s="45" t="n"/>
+      <c r="AN42" s="34" t="n"/>
+      <c r="AO42" s="29" t="n"/>
+      <c r="AP42" s="30" t="n"/>
+      <c r="AQ42" s="32" t="n"/>
       <c r="AR42" s="33" t="n"/>
-      <c r="AS42" s="28" t="n"/>
-      <c r="AT42" s="29" t="n"/>
-      <c r="AU42" s="31" t="n"/>
+      <c r="AS42" s="29" t="n"/>
+      <c r="AT42" s="30" t="n"/>
+      <c r="AU42" s="32" t="n"/>
       <c r="AV42" s="33" t="n"/>
     </row>
     <row r="43" ht="20.1" customHeight="1">
@@ -4071,7 +4195,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="D43" s="19" t="n"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4081,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="42" t="inlineStr">
+      <c r="H43" s="40" t="inlineStr">
         <is>
           <t>Catéchisme</t>
         </is>
@@ -4095,11 +4219,7 @@
         <v>14</v>
       </c>
       <c r="K43" s="7" t="n"/>
-      <c r="L43" s="34" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
+      <c r="L43" s="26" t="n"/>
       <c r="M43" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4109,7 +4229,7 @@
         <v>14</v>
       </c>
       <c r="O43" s="7" t="n"/>
-      <c r="P43" s="18" t="n"/>
+      <c r="P43" s="19" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4119,7 +4239,7 @@
         <v>14</v>
       </c>
       <c r="S43" s="7" t="n"/>
-      <c r="T43" s="18" t="n"/>
+      <c r="T43" s="19" t="n"/>
       <c r="U43" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -4128,8 +4248,8 @@
       <c r="V43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="W43" s="43" t="n"/>
-      <c r="X43" s="51" t="inlineStr">
+      <c r="W43" s="41" t="n"/>
+      <c r="X43" s="49" t="inlineStr">
         <is>
           <t>1er dim. de Carême</t>
         </is>
@@ -4142,8 +4262,8 @@
       <c r="Z43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="AA43" s="43" t="n"/>
-      <c r="AB43" s="51" t="inlineStr">
+      <c r="AA43" s="41" t="n"/>
+      <c r="AB43" s="49" t="inlineStr">
         <is>
           <t>5e dim. de Carême</t>
         </is>
@@ -4157,7 +4277,7 @@
         <v>14</v>
       </c>
       <c r="AE43" s="7" t="n"/>
-      <c r="AF43" s="18" t="n"/>
+      <c r="AF43" s="19" t="n"/>
       <c r="AG43" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4167,7 +4287,7 @@
         <v>14</v>
       </c>
       <c r="AI43" s="7" t="n"/>
-      <c r="AJ43" s="18" t="n"/>
+      <c r="AJ43" s="19" t="n"/>
       <c r="AK43" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4177,7 +4297,7 @@
         <v>14</v>
       </c>
       <c r="AM43" s="7" t="n"/>
-      <c r="AN43" s="18" t="n"/>
+      <c r="AN43" s="19" t="n"/>
       <c r="AO43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4187,7 +4307,7 @@
         <v>14</v>
       </c>
       <c r="AQ43" s="12" t="n"/>
-      <c r="AR43" s="17" t="inlineStr">
+      <c r="AR43" s="20" t="inlineStr">
         <is>
           <t>Fête nationale</t>
         </is>
@@ -4201,122 +4321,122 @@
         <v>14</v>
       </c>
       <c r="AU43" s="12" t="n"/>
-      <c r="AV43" s="18" t="n"/>
+      <c r="AV43" s="19" t="n"/>
     </row>
     <row r="44" ht="20.1" customHeight="1">
-      <c r="A44" s="21" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="G44" s="22" t="n"/>
+      <c r="A44" s="22" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="G44" s="23" t="n"/>
       <c r="H44" s="53" t="inlineStr">
         <is>
           <t>Semaine missionnaire</t>
         </is>
       </c>
-      <c r="I44" s="21" t="n"/>
-      <c r="K44" s="22" t="n"/>
-      <c r="L44" s="37" t="inlineStr">
+      <c r="I44" s="22" t="n"/>
+      <c r="K44" s="23" t="n"/>
+      <c r="L44" s="16" t="inlineStr">
+        <is>
+          <t>WE Couples Miss.</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="n"/>
+      <c r="O44" s="23" t="n"/>
+      <c r="P44" s="27" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="S44" s="23" t="n"/>
+      <c r="T44" s="27" t="n"/>
+      <c r="U44" s="22" t="n"/>
+      <c r="W44" s="44" t="n"/>
+      <c r="X44" s="36" t="inlineStr">
+        <is>
+          <t>Appel décisif</t>
+        </is>
+      </c>
+      <c r="Y44" s="22" t="n"/>
+      <c r="AA44" s="44" t="n"/>
+      <c r="AB44" s="36" t="inlineStr">
+        <is>
+          <t>3ème scrutin</t>
+        </is>
+      </c>
+      <c r="AC44" s="22" t="n"/>
+      <c r="AE44" s="23" t="n"/>
+      <c r="AF44" s="27" t="n"/>
+      <c r="AG44" s="22" t="n"/>
+      <c r="AI44" s="23" t="n"/>
+      <c r="AJ44" s="27" t="n"/>
+      <c r="AK44" s="22" t="n"/>
+      <c r="AM44" s="23" t="n"/>
+      <c r="AN44" s="27" t="n"/>
+      <c r="AO44" s="22" t="n"/>
+      <c r="AQ44" s="25" t="n"/>
+      <c r="AR44" s="24" t="n"/>
+      <c r="AS44" s="22" t="n"/>
+      <c r="AU44" s="25" t="n"/>
+      <c r="AV44" s="27" t="n"/>
+    </row>
+    <row r="45" ht="20.1" customHeight="1">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="30" t="n"/>
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="33" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="30" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="29" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="31" t="n"/>
+      <c r="L45" s="36" t="inlineStr">
         <is>
           <t>Formation accompagnateurs</t>
         </is>
       </c>
-      <c r="M44" s="21" t="n"/>
-      <c r="O44" s="22" t="n"/>
-      <c r="P44" s="26" t="n"/>
-      <c r="Q44" s="21" t="n"/>
-      <c r="S44" s="22" t="n"/>
-      <c r="T44" s="26" t="n"/>
-      <c r="U44" s="21" t="n"/>
-      <c r="W44" s="46" t="n"/>
-      <c r="X44" s="37" t="inlineStr">
-        <is>
-          <t>Appel décisif</t>
-        </is>
-      </c>
-      <c r="Y44" s="21" t="n"/>
-      <c r="AA44" s="46" t="n"/>
-      <c r="AB44" s="37" t="inlineStr">
-        <is>
-          <t>3ème scrutin</t>
-        </is>
-      </c>
-      <c r="AC44" s="21" t="n"/>
-      <c r="AE44" s="22" t="n"/>
-      <c r="AF44" s="26" t="n"/>
-      <c r="AG44" s="21" t="n"/>
-      <c r="AI44" s="22" t="n"/>
-      <c r="AJ44" s="26" t="n"/>
-      <c r="AK44" s="21" t="n"/>
-      <c r="AM44" s="22" t="n"/>
-      <c r="AN44" s="26" t="n"/>
-      <c r="AO44" s="21" t="n"/>
-      <c r="AQ44" s="24" t="n"/>
-      <c r="AR44" s="23" t="n"/>
-      <c r="AS44" s="21" t="n"/>
-      <c r="AU44" s="24" t="n"/>
-      <c r="AV44" s="26" t="n"/>
-    </row>
-    <row r="45" ht="20.1" customHeight="1">
-      <c r="A45" s="28" t="n"/>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="28" t="n"/>
-      <c r="F45" s="29" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="23" t="n"/>
-      <c r="I45" s="28" t="n"/>
-      <c r="J45" s="29" t="n"/>
-      <c r="K45" s="30" t="n"/>
-      <c r="L45" s="19" t="inlineStr">
-        <is>
-          <t>WE Couples Miss.</t>
-        </is>
-      </c>
-      <c r="M45" s="28" t="n"/>
-      <c r="N45" s="29" t="n"/>
-      <c r="O45" s="30" t="n"/>
+      <c r="M45" s="29" t="n"/>
+      <c r="N45" s="30" t="n"/>
+      <c r="O45" s="31" t="n"/>
       <c r="P45" s="33" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="29" t="n"/>
-      <c r="S45" s="30" t="n"/>
+      <c r="Q45" s="29" t="n"/>
+      <c r="R45" s="30" t="n"/>
+      <c r="S45" s="31" t="n"/>
       <c r="T45" s="33" t="n"/>
-      <c r="U45" s="28" t="n"/>
-      <c r="V45" s="29" t="n"/>
-      <c r="W45" s="47" t="n"/>
-      <c r="X45" s="34" t="inlineStr">
+      <c r="U45" s="29" t="n"/>
+      <c r="V45" s="30" t="n"/>
+      <c r="W45" s="45" t="n"/>
+      <c r="X45" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Y45" s="28" t="n"/>
-      <c r="Z45" s="29" t="n"/>
-      <c r="AA45" s="47" t="n"/>
-      <c r="AB45" s="34" t="inlineStr">
+      <c r="Y45" s="29" t="n"/>
+      <c r="Z45" s="30" t="n"/>
+      <c r="AA45" s="45" t="n"/>
+      <c r="AB45" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="AC45" s="28" t="n"/>
-      <c r="AD45" s="29" t="n"/>
-      <c r="AE45" s="30" t="n"/>
+      <c r="AC45" s="29" t="n"/>
+      <c r="AD45" s="30" t="n"/>
+      <c r="AE45" s="31" t="n"/>
       <c r="AF45" s="33" t="n"/>
-      <c r="AG45" s="28" t="n"/>
-      <c r="AH45" s="29" t="n"/>
-      <c r="AI45" s="30" t="n"/>
+      <c r="AG45" s="29" t="n"/>
+      <c r="AH45" s="30" t="n"/>
+      <c r="AI45" s="31" t="n"/>
       <c r="AJ45" s="33" t="n"/>
-      <c r="AK45" s="28" t="n"/>
-      <c r="AL45" s="29" t="n"/>
-      <c r="AM45" s="30" t="n"/>
+      <c r="AK45" s="29" t="n"/>
+      <c r="AL45" s="30" t="n"/>
+      <c r="AM45" s="31" t="n"/>
       <c r="AN45" s="33" t="n"/>
-      <c r="AO45" s="28" t="n"/>
-      <c r="AP45" s="29" t="n"/>
-      <c r="AQ45" s="31" t="n"/>
-      <c r="AR45" s="25" t="n"/>
-      <c r="AS45" s="28" t="n"/>
-      <c r="AT45" s="29" t="n"/>
-      <c r="AU45" s="31" t="n"/>
+      <c r="AO45" s="29" t="n"/>
+      <c r="AP45" s="30" t="n"/>
+      <c r="AQ45" s="32" t="n"/>
+      <c r="AR45" s="26" t="n"/>
+      <c r="AS45" s="29" t="n"/>
+      <c r="AT45" s="30" t="n"/>
+      <c r="AU45" s="32" t="n"/>
       <c r="AV45" s="33" t="n"/>
     </row>
     <row r="46" ht="20.1" customHeight="1">
@@ -4329,7 +4449,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="18" t="n"/>
+      <c r="D46" s="19" t="n"/>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4339,7 +4459,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="23" t="n"/>
+      <c r="H46" s="24" t="n"/>
       <c r="I46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4348,8 +4468,8 @@
       <c r="J46" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="K46" s="43" t="n"/>
-      <c r="L46" s="25" t="n"/>
+      <c r="K46" s="41" t="n"/>
+      <c r="L46" s="16" t="n"/>
       <c r="M46" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4373,7 +4493,7 @@
         <v>15</v>
       </c>
       <c r="S46" s="7" t="n"/>
-      <c r="T46" s="18" t="n"/>
+      <c r="T46" s="19" t="n"/>
       <c r="U46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4383,7 +4503,7 @@
         <v>15</v>
       </c>
       <c r="W46" s="7" t="n"/>
-      <c r="X46" s="18" t="n"/>
+      <c r="X46" s="19" t="n"/>
       <c r="Y46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4393,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="AA46" s="7" t="n"/>
-      <c r="AB46" s="18" t="n"/>
+      <c r="AB46" s="19" t="n"/>
       <c r="AC46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4403,7 +4523,7 @@
         <v>15</v>
       </c>
       <c r="AE46" s="7" t="n"/>
-      <c r="AF46" s="50" t="inlineStr">
+      <c r="AF46" s="48" t="inlineStr">
         <is>
           <t>Prépa Mariage 3</t>
         </is>
@@ -4417,7 +4537,7 @@
         <v>15</v>
       </c>
       <c r="AI46" s="7" t="n"/>
-      <c r="AJ46" s="37" t="inlineStr">
+      <c r="AJ46" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -4445,7 +4565,7 @@
         <v>15</v>
       </c>
       <c r="AQ46" s="12" t="n"/>
-      <c r="AR46" s="18" t="n"/>
+      <c r="AR46" s="19" t="n"/>
       <c r="AS46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4455,103 +4575,111 @@
         <v>15</v>
       </c>
       <c r="AU46" s="12" t="n"/>
-      <c r="AV46" s="17" t="inlineStr">
+      <c r="AV46" s="20" t="inlineStr">
         <is>
           <t>Assomption</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1">
-      <c r="A47" s="21" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="G47" s="22" t="n"/>
-      <c r="H47" s="23" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="K47" s="46" t="n"/>
-      <c r="L47" s="44" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="O47" s="22" t="n"/>
-      <c r="P47" s="23" t="n"/>
-      <c r="Q47" s="21" t="n"/>
-      <c r="S47" s="22" t="n"/>
-      <c r="T47" s="26" t="n"/>
-      <c r="U47" s="21" t="n"/>
-      <c r="W47" s="22" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="21" t="n"/>
-      <c r="AA47" s="22" t="n"/>
-      <c r="AB47" s="26" t="n"/>
-      <c r="AC47" s="21" t="n"/>
-      <c r="AE47" s="22" t="n"/>
-      <c r="AF47" s="23" t="n"/>
-      <c r="AG47" s="21" t="n"/>
-      <c r="AI47" s="22" t="n"/>
-      <c r="AJ47" s="16" t="inlineStr">
+      <c r="A47" s="22" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="K47" s="44" t="n"/>
+      <c r="L47" s="50" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="O47" s="23" t="n"/>
+      <c r="P47" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Q47" s="22" t="n"/>
+      <c r="S47" s="23" t="n"/>
+      <c r="T47" s="27" t="n"/>
+      <c r="U47" s="22" t="n"/>
+      <c r="W47" s="23" t="n"/>
+      <c r="X47" s="27" t="n"/>
+      <c r="Y47" s="22" t="n"/>
+      <c r="AA47" s="23" t="n"/>
+      <c r="AB47" s="27" t="n"/>
+      <c r="AC47" s="22" t="n"/>
+      <c r="AE47" s="23" t="n"/>
+      <c r="AF47" s="24" t="n"/>
+      <c r="AG47" s="22" t="n"/>
+      <c r="AI47" s="23" t="n"/>
+      <c r="AJ47" s="18" t="inlineStr">
         <is>
           <t>Pentecôte Miss. ccn</t>
         </is>
       </c>
-      <c r="AK47" s="21" t="n"/>
-      <c r="AM47" s="22" t="n"/>
-      <c r="AN47" s="23" t="n"/>
-      <c r="AO47" s="21" t="n"/>
-      <c r="AQ47" s="24" t="n"/>
-      <c r="AR47" s="26" t="n"/>
-      <c r="AS47" s="21" t="n"/>
-      <c r="AU47" s="24" t="n"/>
-      <c r="AV47" s="23" t="n"/>
+      <c r="AK47" s="22" t="n"/>
+      <c r="AM47" s="23" t="n"/>
+      <c r="AN47" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AO47" s="22" t="n"/>
+      <c r="AQ47" s="25" t="n"/>
+      <c r="AR47" s="27" t="n"/>
+      <c r="AS47" s="22" t="n"/>
+      <c r="AU47" s="25" t="n"/>
+      <c r="AV47" s="24" t="n"/>
     </row>
     <row r="48" ht="20.1" customHeight="1">
-      <c r="A48" s="28" t="n"/>
-      <c r="B48" s="29" t="n"/>
-      <c r="C48" s="30" t="n"/>
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="31" t="n"/>
       <c r="D48" s="33" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="23" t="n"/>
-      <c r="I48" s="28" t="n"/>
-      <c r="J48" s="29" t="n"/>
-      <c r="K48" s="47" t="n"/>
-      <c r="L48" s="23" t="n"/>
-      <c r="M48" s="28" t="n"/>
-      <c r="N48" s="29" t="n"/>
-      <c r="O48" s="30" t="n"/>
-      <c r="P48" s="25" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="29" t="n"/>
-      <c r="S48" s="30" t="n"/>
+      <c r="E48" s="29" t="n"/>
+      <c r="F48" s="30" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="29" t="n"/>
+      <c r="J48" s="30" t="n"/>
+      <c r="K48" s="45" t="n"/>
+      <c r="L48" s="24" t="n"/>
+      <c r="M48" s="29" t="n"/>
+      <c r="N48" s="30" t="n"/>
+      <c r="O48" s="31" t="n"/>
+      <c r="P48" s="33" t="n"/>
+      <c r="Q48" s="29" t="n"/>
+      <c r="R48" s="30" t="n"/>
+      <c r="S48" s="31" t="n"/>
       <c r="T48" s="33" t="n"/>
-      <c r="U48" s="28" t="n"/>
-      <c r="V48" s="29" t="n"/>
-      <c r="W48" s="30" t="n"/>
+      <c r="U48" s="29" t="n"/>
+      <c r="V48" s="30" t="n"/>
+      <c r="W48" s="31" t="n"/>
       <c r="X48" s="33" t="n"/>
-      <c r="Y48" s="28" t="n"/>
-      <c r="Z48" s="29" t="n"/>
-      <c r="AA48" s="30" t="n"/>
+      <c r="Y48" s="29" t="n"/>
+      <c r="Z48" s="30" t="n"/>
+      <c r="AA48" s="31" t="n"/>
       <c r="AB48" s="33" t="n"/>
-      <c r="AC48" s="28" t="n"/>
-      <c r="AD48" s="29" t="n"/>
-      <c r="AE48" s="30" t="n"/>
-      <c r="AF48" s="25" t="n"/>
-      <c r="AG48" s="28" t="n"/>
-      <c r="AH48" s="29" t="n"/>
-      <c r="AI48" s="30" t="n"/>
-      <c r="AJ48" s="23" t="n"/>
-      <c r="AK48" s="28" t="n"/>
-      <c r="AL48" s="29" t="n"/>
-      <c r="AM48" s="30" t="n"/>
-      <c r="AN48" s="25" t="n"/>
-      <c r="AO48" s="28" t="n"/>
-      <c r="AP48" s="29" t="n"/>
-      <c r="AQ48" s="31" t="n"/>
+      <c r="AC48" s="29" t="n"/>
+      <c r="AD48" s="30" t="n"/>
+      <c r="AE48" s="31" t="n"/>
+      <c r="AF48" s="26" t="n"/>
+      <c r="AG48" s="29" t="n"/>
+      <c r="AH48" s="30" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="24" t="n"/>
+      <c r="AK48" s="29" t="n"/>
+      <c r="AL48" s="30" t="n"/>
+      <c r="AM48" s="31" t="n"/>
+      <c r="AN48" s="33" t="n"/>
+      <c r="AO48" s="29" t="n"/>
+      <c r="AP48" s="30" t="n"/>
+      <c r="AQ48" s="32" t="n"/>
       <c r="AR48" s="33" t="n"/>
-      <c r="AS48" s="28" t="n"/>
-      <c r="AT48" s="29" t="n"/>
-      <c r="AU48" s="31" t="n"/>
-      <c r="AV48" s="25" t="n"/>
+      <c r="AS48" s="29" t="n"/>
+      <c r="AT48" s="30" t="n"/>
+      <c r="AU48" s="32" t="n"/>
+      <c r="AV48" s="26" t="n"/>
     </row>
     <row r="49" ht="20.1" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -4563,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="18" t="n"/>
+      <c r="D49" s="19" t="n"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4573,7 +4701,7 @@
         <v>16</v>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="23" t="n"/>
+      <c r="H49" s="24" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4583,7 +4711,7 @@
         <v>16</v>
       </c>
       <c r="K49" s="7" t="n"/>
-      <c r="L49" s="23" t="n"/>
+      <c r="L49" s="24" t="n"/>
       <c r="M49" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4593,7 +4721,7 @@
         <v>16</v>
       </c>
       <c r="O49" s="7" t="n"/>
-      <c r="P49" s="18" t="n"/>
+      <c r="P49" s="19" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4603,7 +4731,7 @@
         <v>16</v>
       </c>
       <c r="S49" s="7" t="n"/>
-      <c r="T49" s="18" t="n"/>
+      <c r="T49" s="19" t="n"/>
       <c r="U49" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4629,7 +4757,7 @@
       <c r="AA49" s="7" t="n"/>
       <c r="AB49" s="16" t="inlineStr">
         <is>
-          <t>Soirée réconciliation</t>
+          <t>Journée d'adoration</t>
         </is>
       </c>
       <c r="AC49" s="5" t="inlineStr">
@@ -4641,7 +4769,7 @@
         <v>16</v>
       </c>
       <c r="AE49" s="7" t="n"/>
-      <c r="AF49" s="18" t="n"/>
+      <c r="AF49" s="19" t="n"/>
       <c r="AG49" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4650,8 +4778,8 @@
       <c r="AH49" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AI49" s="43" t="n"/>
-      <c r="AJ49" s="23" t="n"/>
+      <c r="AI49" s="41" t="n"/>
+      <c r="AJ49" s="24" t="n"/>
       <c r="AK49" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4661,7 +4789,7 @@
         <v>16</v>
       </c>
       <c r="AM49" s="7" t="n"/>
-      <c r="AN49" s="18" t="n"/>
+      <c r="AN49" s="19" t="n"/>
       <c r="AO49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4671,7 +4799,7 @@
         <v>16</v>
       </c>
       <c r="AQ49" s="12" t="n"/>
-      <c r="AR49" s="18" t="n"/>
+      <c r="AR49" s="19" t="n"/>
       <c r="AS49" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4681,98 +4809,106 @@
         <v>16</v>
       </c>
       <c r="AU49" s="12" t="n"/>
-      <c r="AV49" s="18" t="n"/>
+      <c r="AV49" s="19" t="n"/>
     </row>
     <row r="50" ht="20.1" customHeight="1">
-      <c r="A50" s="21" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="26" t="n"/>
-      <c r="E50" s="21" t="n"/>
-      <c r="G50" s="22" t="n"/>
-      <c r="H50" s="23" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="K50" s="22" t="n"/>
-      <c r="L50" s="23" t="n"/>
-      <c r="M50" s="21" t="n"/>
-      <c r="O50" s="22" t="n"/>
-      <c r="P50" s="26" t="n"/>
-      <c r="Q50" s="21" t="n"/>
-      <c r="S50" s="22" t="n"/>
-      <c r="T50" s="26" t="n"/>
-      <c r="U50" s="21" t="n"/>
-      <c r="W50" s="22" t="n"/>
-      <c r="X50" s="23" t="n"/>
-      <c r="Y50" s="21" t="n"/>
-      <c r="AA50" s="22" t="n"/>
-      <c r="AB50" s="23" t="n"/>
-      <c r="AC50" s="21" t="n"/>
-      <c r="AE50" s="22" t="n"/>
-      <c r="AF50" s="26" t="n"/>
-      <c r="AG50" s="21" t="n"/>
-      <c r="AI50" s="46" t="n"/>
-      <c r="AJ50" s="25" t="n"/>
-      <c r="AK50" s="21" t="n"/>
-      <c r="AM50" s="22" t="n"/>
-      <c r="AN50" s="26" t="n"/>
-      <c r="AO50" s="21" t="n"/>
-      <c r="AQ50" s="24" t="n"/>
-      <c r="AR50" s="26" t="n"/>
-      <c r="AS50" s="21" t="n"/>
-      <c r="AU50" s="24" t="n"/>
-      <c r="AV50" s="26" t="n"/>
+      <c r="A50" s="22" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="27" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="K50" s="23" t="n"/>
+      <c r="L50" s="24" t="n"/>
+      <c r="M50" s="22" t="n"/>
+      <c r="O50" s="23" t="n"/>
+      <c r="P50" s="27" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="S50" s="23" t="n"/>
+      <c r="T50" s="27" t="n"/>
+      <c r="U50" s="22" t="n"/>
+      <c r="W50" s="23" t="n"/>
+      <c r="X50" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Y50" s="22" t="n"/>
+      <c r="AA50" s="23" t="n"/>
+      <c r="AB50" s="16" t="inlineStr">
+        <is>
+          <t>Soirée réconciliation</t>
+        </is>
+      </c>
+      <c r="AC50" s="22" t="n"/>
+      <c r="AE50" s="23" t="n"/>
+      <c r="AF50" s="27" t="n"/>
+      <c r="AG50" s="22" t="n"/>
+      <c r="AI50" s="44" t="n"/>
+      <c r="AJ50" s="26" t="n"/>
+      <c r="AK50" s="22" t="n"/>
+      <c r="AM50" s="23" t="n"/>
+      <c r="AN50" s="27" t="n"/>
+      <c r="AO50" s="22" t="n"/>
+      <c r="AQ50" s="25" t="n"/>
+      <c r="AR50" s="27" t="n"/>
+      <c r="AS50" s="22" t="n"/>
+      <c r="AU50" s="25" t="n"/>
+      <c r="AV50" s="27" t="n"/>
     </row>
     <row r="51" ht="20.1" customHeight="1">
-      <c r="A51" s="28" t="n"/>
-      <c r="B51" s="29" t="n"/>
-      <c r="C51" s="30" t="n"/>
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="31" t="n"/>
       <c r="D51" s="33" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="29" t="n"/>
-      <c r="G51" s="30" t="n"/>
-      <c r="H51" s="23" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="29" t="n"/>
-      <c r="K51" s="30" t="n"/>
-      <c r="L51" s="23" t="n"/>
-      <c r="M51" s="28" t="n"/>
-      <c r="N51" s="29" t="n"/>
-      <c r="O51" s="30" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="30" t="n"/>
+      <c r="G51" s="31" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="29" t="n"/>
+      <c r="J51" s="30" t="n"/>
+      <c r="K51" s="31" t="n"/>
+      <c r="L51" s="26" t="n"/>
+      <c r="M51" s="29" t="n"/>
+      <c r="N51" s="30" t="n"/>
+      <c r="O51" s="31" t="n"/>
       <c r="P51" s="33" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="29" t="n"/>
-      <c r="S51" s="30" t="n"/>
+      <c r="Q51" s="29" t="n"/>
+      <c r="R51" s="30" t="n"/>
+      <c r="S51" s="31" t="n"/>
       <c r="T51" s="33" t="n"/>
-      <c r="U51" s="28" t="n"/>
-      <c r="V51" s="29" t="n"/>
-      <c r="W51" s="30" t="n"/>
-      <c r="X51" s="25" t="n"/>
-      <c r="Y51" s="28" t="n"/>
-      <c r="Z51" s="29" t="n"/>
-      <c r="AA51" s="30" t="n"/>
-      <c r="AB51" s="25" t="n"/>
-      <c r="AC51" s="28" t="n"/>
-      <c r="AD51" s="29" t="n"/>
-      <c r="AE51" s="30" t="n"/>
+      <c r="U51" s="29" t="n"/>
+      <c r="V51" s="30" t="n"/>
+      <c r="W51" s="31" t="n"/>
+      <c r="X51" s="33" t="n"/>
+      <c r="Y51" s="29" t="n"/>
+      <c r="Z51" s="30" t="n"/>
+      <c r="AA51" s="31" t="n"/>
+      <c r="AB51" s="33" t="n"/>
+      <c r="AC51" s="29" t="n"/>
+      <c r="AD51" s="30" t="n"/>
+      <c r="AE51" s="31" t="n"/>
       <c r="AF51" s="33" t="n"/>
-      <c r="AG51" s="28" t="n"/>
-      <c r="AH51" s="29" t="n"/>
-      <c r="AI51" s="47" t="n"/>
-      <c r="AJ51" s="32" t="inlineStr">
+      <c r="AG51" s="29" t="n"/>
+      <c r="AH51" s="30" t="n"/>
+      <c r="AI51" s="45" t="n"/>
+      <c r="AJ51" s="17" t="inlineStr">
         <is>
           <t>Pentecôte</t>
         </is>
       </c>
-      <c r="AK51" s="28" t="n"/>
-      <c r="AL51" s="29" t="n"/>
-      <c r="AM51" s="30" t="n"/>
+      <c r="AK51" s="29" t="n"/>
+      <c r="AL51" s="30" t="n"/>
+      <c r="AM51" s="31" t="n"/>
       <c r="AN51" s="33" t="n"/>
-      <c r="AO51" s="28" t="n"/>
-      <c r="AP51" s="29" t="n"/>
-      <c r="AQ51" s="31" t="n"/>
+      <c r="AO51" s="29" t="n"/>
+      <c r="AP51" s="30" t="n"/>
+      <c r="AQ51" s="32" t="n"/>
       <c r="AR51" s="33" t="n"/>
-      <c r="AS51" s="28" t="n"/>
-      <c r="AT51" s="29" t="n"/>
-      <c r="AU51" s="31" t="n"/>
+      <c r="AS51" s="29" t="n"/>
+      <c r="AT51" s="30" t="n"/>
+      <c r="AU51" s="32" t="n"/>
       <c r="AV51" s="33" t="n"/>
     </row>
     <row r="52" ht="20.1" customHeight="1">
@@ -4785,7 +4921,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="18" t="n"/>
+      <c r="D52" s="19" t="n"/>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4795,7 +4931,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="12" t="n"/>
-      <c r="H52" s="23" t="n"/>
+      <c r="H52" s="24" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4805,7 +4941,11 @@
         <v>17</v>
       </c>
       <c r="K52" s="7" t="n"/>
-      <c r="L52" s="25" t="n"/>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>Equipe Pilote</t>
+        </is>
+      </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -4815,7 +4955,7 @@
         <v>17</v>
       </c>
       <c r="O52" s="7" t="n"/>
-      <c r="P52" s="18" t="n"/>
+      <c r="P52" s="19" t="n"/>
       <c r="Q52" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4824,8 +4964,8 @@
       <c r="R52" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="S52" s="43" t="n"/>
-      <c r="T52" s="20" t="n"/>
+      <c r="S52" s="41" t="n"/>
+      <c r="T52" s="21" t="n"/>
       <c r="U52" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4835,7 +4975,7 @@
         <v>17</v>
       </c>
       <c r="W52" s="7" t="n"/>
-      <c r="X52" s="18" t="n"/>
+      <c r="X52" s="19" t="n"/>
       <c r="Y52" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4845,7 +4985,7 @@
         <v>17</v>
       </c>
       <c r="AA52" s="7" t="n"/>
-      <c r="AB52" s="18" t="n"/>
+      <c r="AB52" s="19" t="n"/>
       <c r="AC52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4855,7 +4995,7 @@
         <v>17</v>
       </c>
       <c r="AE52" s="12" t="n"/>
-      <c r="AF52" s="18" t="n"/>
+      <c r="AF52" s="19" t="n"/>
       <c r="AG52" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4865,7 +5005,7 @@
         <v>17</v>
       </c>
       <c r="AI52" s="7" t="n"/>
-      <c r="AJ52" s="19" t="n"/>
+      <c r="AJ52" s="51" t="n"/>
       <c r="AK52" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4875,7 +5015,7 @@
         <v>17</v>
       </c>
       <c r="AM52" s="7" t="n"/>
-      <c r="AN52" s="18" t="n"/>
+      <c r="AN52" s="19" t="n"/>
       <c r="AO52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4885,7 +5025,7 @@
         <v>17</v>
       </c>
       <c r="AQ52" s="12" t="n"/>
-      <c r="AR52" s="18" t="n"/>
+      <c r="AR52" s="19" t="n"/>
       <c r="AS52" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4895,106 +5035,106 @@
         <v>17</v>
       </c>
       <c r="AU52" s="12" t="n"/>
-      <c r="AV52" s="18" t="n"/>
+      <c r="AV52" s="19" t="n"/>
     </row>
     <row r="53" ht="20.1" customHeight="1">
-      <c r="A53" s="21" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="26" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="G53" s="24" t="n"/>
-      <c r="H53" s="23" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="K53" s="22" t="n"/>
-      <c r="L53" s="34" t="inlineStr">
-        <is>
-          <t>Equipe Pilote</t>
-        </is>
-      </c>
-      <c r="M53" s="21" t="n"/>
-      <c r="O53" s="22" t="n"/>
-      <c r="P53" s="26" t="n"/>
-      <c r="Q53" s="21" t="n"/>
-      <c r="S53" s="46" t="n"/>
-      <c r="T53" s="27" t="n"/>
-      <c r="U53" s="21" t="n"/>
-      <c r="W53" s="22" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="21" t="n"/>
-      <c r="AA53" s="22" t="n"/>
-      <c r="AB53" s="26" t="n"/>
-      <c r="AC53" s="21" t="n"/>
-      <c r="AE53" s="24" t="n"/>
-      <c r="AF53" s="26" t="n"/>
-      <c r="AG53" s="21" t="n"/>
-      <c r="AI53" s="22" t="n"/>
-      <c r="AJ53" s="25" t="n"/>
-      <c r="AK53" s="21" t="n"/>
-      <c r="AM53" s="22" t="n"/>
-      <c r="AN53" s="26" t="n"/>
-      <c r="AO53" s="21" t="n"/>
-      <c r="AQ53" s="24" t="n"/>
-      <c r="AR53" s="26" t="n"/>
-      <c r="AS53" s="21" t="n"/>
-      <c r="AU53" s="24" t="n"/>
-      <c r="AV53" s="26" t="n"/>
+      <c r="A53" s="22" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="G53" s="25" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="K53" s="23" t="n"/>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
+      <c r="M53" s="22" t="n"/>
+      <c r="O53" s="23" t="n"/>
+      <c r="P53" s="27" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="S53" s="44" t="n"/>
+      <c r="T53" s="28" t="n"/>
+      <c r="U53" s="22" t="n"/>
+      <c r="W53" s="23" t="n"/>
+      <c r="X53" s="27" t="n"/>
+      <c r="Y53" s="22" t="n"/>
+      <c r="AA53" s="23" t="n"/>
+      <c r="AB53" s="27" t="n"/>
+      <c r="AC53" s="22" t="n"/>
+      <c r="AE53" s="25" t="n"/>
+      <c r="AF53" s="27" t="n"/>
+      <c r="AG53" s="22" t="n"/>
+      <c r="AI53" s="23" t="n"/>
+      <c r="AJ53" s="26" t="n"/>
+      <c r="AK53" s="22" t="n"/>
+      <c r="AM53" s="23" t="n"/>
+      <c r="AN53" s="27" t="n"/>
+      <c r="AO53" s="22" t="n"/>
+      <c r="AQ53" s="25" t="n"/>
+      <c r="AR53" s="27" t="n"/>
+      <c r="AS53" s="22" t="n"/>
+      <c r="AU53" s="25" t="n"/>
+      <c r="AV53" s="27" t="n"/>
     </row>
     <row r="54" ht="20.1" customHeight="1">
-      <c r="A54" s="28" t="n"/>
-      <c r="B54" s="29" t="n"/>
-      <c r="C54" s="30" t="n"/>
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="30" t="n"/>
+      <c r="C54" s="31" t="n"/>
       <c r="D54" s="33" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="31" t="n"/>
-      <c r="H54" s="23" t="n"/>
-      <c r="I54" s="28" t="n"/>
-      <c r="J54" s="29" t="n"/>
-      <c r="K54" s="30" t="n"/>
-      <c r="L54" s="34" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="M54" s="28" t="n"/>
-      <c r="N54" s="29" t="n"/>
-      <c r="O54" s="30" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="30" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="29" t="n"/>
+      <c r="J54" s="30" t="n"/>
+      <c r="K54" s="31" t="n"/>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="M54" s="29" t="n"/>
+      <c r="N54" s="30" t="n"/>
+      <c r="O54" s="31" t="n"/>
       <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="29" t="n"/>
-      <c r="S54" s="47" t="n"/>
-      <c r="T54" s="35" t="n"/>
-      <c r="U54" s="28" t="n"/>
-      <c r="V54" s="29" t="n"/>
-      <c r="W54" s="30" t="n"/>
+      <c r="Q54" s="29" t="n"/>
+      <c r="R54" s="30" t="n"/>
+      <c r="S54" s="45" t="n"/>
+      <c r="T54" s="34" t="n"/>
+      <c r="U54" s="29" t="n"/>
+      <c r="V54" s="30" t="n"/>
+      <c r="W54" s="31" t="n"/>
       <c r="X54" s="33" t="n"/>
-      <c r="Y54" s="28" t="n"/>
-      <c r="Z54" s="29" t="n"/>
-      <c r="AA54" s="30" t="n"/>
+      <c r="Y54" s="29" t="n"/>
+      <c r="Z54" s="30" t="n"/>
+      <c r="AA54" s="31" t="n"/>
       <c r="AB54" s="33" t="n"/>
-      <c r="AC54" s="28" t="n"/>
-      <c r="AD54" s="29" t="n"/>
-      <c r="AE54" s="31" t="n"/>
+      <c r="AC54" s="29" t="n"/>
+      <c r="AD54" s="30" t="n"/>
+      <c r="AE54" s="32" t="n"/>
       <c r="AF54" s="33" t="n"/>
-      <c r="AG54" s="28" t="n"/>
-      <c r="AH54" s="29" t="n"/>
-      <c r="AI54" s="30" t="n"/>
-      <c r="AJ54" s="32" t="inlineStr">
+      <c r="AG54" s="29" t="n"/>
+      <c r="AH54" s="30" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="17" t="inlineStr">
         <is>
           <t>Lundi de Pentecôte</t>
         </is>
       </c>
-      <c r="AK54" s="28" t="n"/>
-      <c r="AL54" s="29" t="n"/>
-      <c r="AM54" s="30" t="n"/>
+      <c r="AK54" s="29" t="n"/>
+      <c r="AL54" s="30" t="n"/>
+      <c r="AM54" s="31" t="n"/>
       <c r="AN54" s="33" t="n"/>
-      <c r="AO54" s="28" t="n"/>
-      <c r="AP54" s="29" t="n"/>
-      <c r="AQ54" s="31" t="n"/>
+      <c r="AO54" s="29" t="n"/>
+      <c r="AP54" s="30" t="n"/>
+      <c r="AQ54" s="32" t="n"/>
       <c r="AR54" s="33" t="n"/>
-      <c r="AS54" s="28" t="n"/>
-      <c r="AT54" s="29" t="n"/>
-      <c r="AU54" s="31" t="n"/>
+      <c r="AS54" s="29" t="n"/>
+      <c r="AT54" s="30" t="n"/>
+      <c r="AU54" s="32" t="n"/>
       <c r="AV54" s="33" t="n"/>
     </row>
     <row r="55" ht="20.1" customHeight="1">
@@ -5007,7 +5147,7 @@
         <v>18</v>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="36" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -5021,7 +5161,7 @@
         <v>18</v>
       </c>
       <c r="G55" s="12" t="n"/>
-      <c r="H55" s="23" t="n"/>
+      <c r="H55" s="24" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5031,7 +5171,7 @@
         <v>18</v>
       </c>
       <c r="K55" s="7" t="n"/>
-      <c r="L55" s="38" t="n"/>
+      <c r="L55" s="50" t="n"/>
       <c r="M55" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5041,7 +5181,7 @@
         <v>18</v>
       </c>
       <c r="O55" s="7" t="n"/>
-      <c r="P55" s="18" t="n"/>
+      <c r="P55" s="19" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5051,7 +5191,7 @@
         <v>18</v>
       </c>
       <c r="S55" s="7" t="n"/>
-      <c r="T55" s="18" t="n"/>
+      <c r="T55" s="19" t="n"/>
       <c r="U55" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -5061,7 +5201,7 @@
         <v>18</v>
       </c>
       <c r="W55" s="7" t="n"/>
-      <c r="X55" s="50" t="inlineStr">
+      <c r="X55" s="48" t="inlineStr">
         <is>
           <t>Prépa Mariage 2</t>
         </is>
@@ -5075,7 +5215,7 @@
         <v>18</v>
       </c>
       <c r="AA55" s="7" t="n"/>
-      <c r="AB55" s="36" t="inlineStr">
+      <c r="AB55" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -5089,7 +5229,7 @@
         <v>18</v>
       </c>
       <c r="AE55" s="12" t="n"/>
-      <c r="AF55" s="20" t="n"/>
+      <c r="AF55" s="21" t="n"/>
       <c r="AG55" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5113,7 +5253,7 @@
         <v>18</v>
       </c>
       <c r="AM55" s="7" t="n"/>
-      <c r="AN55" s="18" t="n"/>
+      <c r="AN55" s="19" t="n"/>
       <c r="AO55" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -5123,7 +5263,7 @@
         <v>18</v>
       </c>
       <c r="AQ55" s="12" t="n"/>
-      <c r="AR55" s="20" t="n"/>
+      <c r="AR55" s="21" t="n"/>
       <c r="AS55" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5133,98 +5273,102 @@
         <v>18</v>
       </c>
       <c r="AU55" s="12" t="n"/>
-      <c r="AV55" s="18" t="n"/>
+      <c r="AV55" s="19" t="n"/>
     </row>
     <row r="56" ht="20.1" customHeight="1">
-      <c r="A56" s="21" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="21" t="n"/>
-      <c r="G56" s="24" t="n"/>
-      <c r="H56" s="25" t="n"/>
-      <c r="I56" s="21" t="n"/>
-      <c r="K56" s="22" t="n"/>
-      <c r="L56" s="23" t="n"/>
-      <c r="M56" s="21" t="n"/>
-      <c r="O56" s="22" t="n"/>
-      <c r="P56" s="26" t="n"/>
-      <c r="Q56" s="21" t="n"/>
-      <c r="S56" s="22" t="n"/>
-      <c r="T56" s="26" t="n"/>
-      <c r="U56" s="21" t="n"/>
-      <c r="W56" s="22" t="n"/>
-      <c r="X56" s="23" t="n"/>
-      <c r="Y56" s="21" t="n"/>
-      <c r="AA56" s="22" t="n"/>
-      <c r="AB56" s="23" t="n"/>
-      <c r="AC56" s="21" t="n"/>
-      <c r="AE56" s="24" t="n"/>
-      <c r="AF56" s="27" t="n"/>
-      <c r="AG56" s="21" t="n"/>
-      <c r="AI56" s="22" t="n"/>
-      <c r="AJ56" s="23" t="n"/>
-      <c r="AK56" s="21" t="n"/>
-      <c r="AM56" s="22" t="n"/>
-      <c r="AN56" s="26" t="n"/>
-      <c r="AO56" s="21" t="n"/>
-      <c r="AQ56" s="24" t="n"/>
-      <c r="AR56" s="27" t="n"/>
-      <c r="AS56" s="21" t="n"/>
-      <c r="AU56" s="24" t="n"/>
-      <c r="AV56" s="26" t="n"/>
+      <c r="A56" s="22" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="24" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="26" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="K56" s="23" t="n"/>
+      <c r="L56" s="24" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="O56" s="23" t="n"/>
+      <c r="P56" s="27" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="S56" s="23" t="n"/>
+      <c r="T56" s="27" t="n"/>
+      <c r="U56" s="22" t="n"/>
+      <c r="W56" s="23" t="n"/>
+      <c r="X56" s="24" t="n"/>
+      <c r="Y56" s="22" t="n"/>
+      <c r="AA56" s="23" t="n"/>
+      <c r="AB56" s="24" t="n"/>
+      <c r="AC56" s="22" t="n"/>
+      <c r="AE56" s="25" t="n"/>
+      <c r="AF56" s="28" t="n"/>
+      <c r="AG56" s="22" t="n"/>
+      <c r="AI56" s="23" t="n"/>
+      <c r="AJ56" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AK56" s="22" t="n"/>
+      <c r="AM56" s="23" t="n"/>
+      <c r="AN56" s="27" t="n"/>
+      <c r="AO56" s="22" t="n"/>
+      <c r="AQ56" s="25" t="n"/>
+      <c r="AR56" s="28" t="n"/>
+      <c r="AS56" s="22" t="n"/>
+      <c r="AU56" s="25" t="n"/>
+      <c r="AV56" s="27" t="n"/>
     </row>
     <row r="57" ht="20.1" customHeight="1">
-      <c r="A57" s="28" t="n"/>
-      <c r="B57" s="29" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="25" t="n"/>
-      <c r="E57" s="28" t="n"/>
-      <c r="F57" s="29" t="n"/>
-      <c r="G57" s="31" t="n"/>
-      <c r="H57" s="45" t="inlineStr">
+      <c r="A57" s="29" t="n"/>
+      <c r="B57" s="30" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="26" t="n"/>
+      <c r="E57" s="29" t="n"/>
+      <c r="F57" s="30" t="n"/>
+      <c r="G57" s="32" t="n"/>
+      <c r="H57" s="43" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
       </c>
-      <c r="I57" s="28" t="n"/>
-      <c r="J57" s="29" t="n"/>
-      <c r="K57" s="30" t="n"/>
-      <c r="L57" s="23" t="n"/>
-      <c r="M57" s="28" t="n"/>
-      <c r="N57" s="29" t="n"/>
-      <c r="O57" s="30" t="n"/>
+      <c r="I57" s="29" t="n"/>
+      <c r="J57" s="30" t="n"/>
+      <c r="K57" s="31" t="n"/>
+      <c r="L57" s="24" t="n"/>
+      <c r="M57" s="29" t="n"/>
+      <c r="N57" s="30" t="n"/>
+      <c r="O57" s="31" t="n"/>
       <c r="P57" s="33" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="29" t="n"/>
-      <c r="S57" s="30" t="n"/>
+      <c r="Q57" s="29" t="n"/>
+      <c r="R57" s="30" t="n"/>
+      <c r="S57" s="31" t="n"/>
       <c r="T57" s="33" t="n"/>
-      <c r="U57" s="28" t="n"/>
-      <c r="V57" s="29" t="n"/>
-      <c r="W57" s="30" t="n"/>
-      <c r="X57" s="25" t="n"/>
-      <c r="Y57" s="28" t="n"/>
-      <c r="Z57" s="29" t="n"/>
-      <c r="AA57" s="30" t="n"/>
-      <c r="AB57" s="25" t="n"/>
-      <c r="AC57" s="28" t="n"/>
-      <c r="AD57" s="29" t="n"/>
-      <c r="AE57" s="31" t="n"/>
-      <c r="AF57" s="35" t="n"/>
-      <c r="AG57" s="28" t="n"/>
-      <c r="AH57" s="29" t="n"/>
-      <c r="AI57" s="30" t="n"/>
-      <c r="AJ57" s="25" t="n"/>
-      <c r="AK57" s="28" t="n"/>
-      <c r="AL57" s="29" t="n"/>
-      <c r="AM57" s="30" t="n"/>
+      <c r="U57" s="29" t="n"/>
+      <c r="V57" s="30" t="n"/>
+      <c r="W57" s="31" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="29" t="n"/>
+      <c r="Z57" s="30" t="n"/>
+      <c r="AA57" s="31" t="n"/>
+      <c r="AB57" s="26" t="n"/>
+      <c r="AC57" s="29" t="n"/>
+      <c r="AD57" s="30" t="n"/>
+      <c r="AE57" s="32" t="n"/>
+      <c r="AF57" s="34" t="n"/>
+      <c r="AG57" s="29" t="n"/>
+      <c r="AH57" s="30" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="33" t="n"/>
+      <c r="AK57" s="29" t="n"/>
+      <c r="AL57" s="30" t="n"/>
+      <c r="AM57" s="31" t="n"/>
       <c r="AN57" s="33" t="n"/>
-      <c r="AO57" s="28" t="n"/>
-      <c r="AP57" s="29" t="n"/>
-      <c r="AQ57" s="31" t="n"/>
-      <c r="AR57" s="35" t="n"/>
-      <c r="AS57" s="28" t="n"/>
-      <c r="AT57" s="29" t="n"/>
-      <c r="AU57" s="31" t="n"/>
+      <c r="AO57" s="29" t="n"/>
+      <c r="AP57" s="30" t="n"/>
+      <c r="AQ57" s="32" t="n"/>
+      <c r="AR57" s="34" t="n"/>
+      <c r="AS57" s="29" t="n"/>
+      <c r="AT57" s="30" t="n"/>
+      <c r="AU57" s="32" t="n"/>
       <c r="AV57" s="33" t="n"/>
     </row>
     <row r="58" ht="20.1" customHeight="1">
@@ -5237,7 +5381,7 @@
         <v>19</v>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="42" t="inlineStr">
+      <c r="D58" s="40" t="inlineStr">
         <is>
           <t>Baptême</t>
         </is>
@@ -5251,7 +5395,7 @@
         <v>19</v>
       </c>
       <c r="G58" s="12" t="n"/>
-      <c r="H58" s="18" t="n"/>
+      <c r="H58" s="19" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5261,7 +5405,7 @@
         <v>19</v>
       </c>
       <c r="K58" s="7" t="n"/>
-      <c r="L58" s="23" t="n"/>
+      <c r="L58" s="24" t="n"/>
       <c r="M58" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5271,7 +5415,7 @@
         <v>19</v>
       </c>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="18" t="n"/>
+      <c r="P58" s="19" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5295,7 +5439,7 @@
         <v>19</v>
       </c>
       <c r="W58" s="7" t="n"/>
-      <c r="X58" s="18" t="n"/>
+      <c r="X58" s="19" t="n"/>
       <c r="Y58" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5305,7 +5449,7 @@
         <v>19</v>
       </c>
       <c r="AA58" s="7" t="n"/>
-      <c r="AB58" s="18" t="n"/>
+      <c r="AB58" s="19" t="n"/>
       <c r="AC58" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5315,7 +5459,7 @@
         <v>19</v>
       </c>
       <c r="AE58" s="12" t="n"/>
-      <c r="AF58" s="18" t="n"/>
+      <c r="AF58" s="19" t="n"/>
       <c r="AG58" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5325,7 +5469,7 @@
         <v>19</v>
       </c>
       <c r="AI58" s="7" t="n"/>
-      <c r="AJ58" s="18" t="n"/>
+      <c r="AJ58" s="19" t="n"/>
       <c r="AK58" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5335,7 +5479,7 @@
         <v>19</v>
       </c>
       <c r="AM58" s="7" t="n"/>
-      <c r="AN58" s="17" t="inlineStr">
+      <c r="AN58" s="20" t="inlineStr">
         <is>
           <t>St Antoine (Tamoul)</t>
         </is>
@@ -5349,7 +5493,7 @@
         <v>19</v>
       </c>
       <c r="AQ58" s="12" t="n"/>
-      <c r="AR58" s="18" t="n"/>
+      <c r="AR58" s="19" t="n"/>
       <c r="AS58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5359,102 +5503,106 @@
         <v>19</v>
       </c>
       <c r="AU58" s="12" t="n"/>
-      <c r="AV58" s="18" t="n"/>
+      <c r="AV58" s="19" t="n"/>
     </row>
     <row r="59" ht="20.1" customHeight="1">
-      <c r="A59" s="21" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="A59" s="22" t="n"/>
+      <c r="C59" s="23" t="n"/>
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>ND Velankanni (Tamoul)</t>
         </is>
       </c>
-      <c r="E59" s="21" t="n"/>
-      <c r="G59" s="24" t="n"/>
-      <c r="H59" s="26" t="n"/>
-      <c r="I59" s="21" t="n"/>
-      <c r="K59" s="22" t="n"/>
-      <c r="L59" s="25" t="n"/>
-      <c r="M59" s="21" t="n"/>
-      <c r="O59" s="24" t="n"/>
-      <c r="P59" s="26" t="n"/>
-      <c r="Q59" s="21" t="n"/>
-      <c r="S59" s="22" t="n"/>
-      <c r="T59" s="23" t="n"/>
-      <c r="U59" s="21" t="n"/>
-      <c r="W59" s="22" t="n"/>
-      <c r="X59" s="26" t="n"/>
-      <c r="Y59" s="21" t="n"/>
-      <c r="AA59" s="22" t="n"/>
-      <c r="AB59" s="26" t="n"/>
-      <c r="AC59" s="21" t="n"/>
-      <c r="AE59" s="24" t="n"/>
-      <c r="AF59" s="26" t="n"/>
-      <c r="AG59" s="21" t="n"/>
-      <c r="AI59" s="22" t="n"/>
-      <c r="AJ59" s="26" t="n"/>
-      <c r="AK59" s="21" t="n"/>
-      <c r="AM59" s="22" t="n"/>
-      <c r="AN59" s="23" t="n"/>
-      <c r="AO59" s="21" t="n"/>
-      <c r="AQ59" s="24" t="n"/>
-      <c r="AR59" s="26" t="n"/>
-      <c r="AS59" s="21" t="n"/>
-      <c r="AU59" s="24" t="n"/>
-      <c r="AV59" s="26" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="G59" s="25" t="n"/>
+      <c r="H59" s="27" t="n"/>
+      <c r="I59" s="22" t="n"/>
+      <c r="K59" s="23" t="n"/>
+      <c r="L59" s="26" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="O59" s="25" t="n"/>
+      <c r="P59" s="27" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="S59" s="23" t="n"/>
+      <c r="T59" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="U59" s="22" t="n"/>
+      <c r="W59" s="23" t="n"/>
+      <c r="X59" s="27" t="n"/>
+      <c r="Y59" s="22" t="n"/>
+      <c r="AA59" s="23" t="n"/>
+      <c r="AB59" s="27" t="n"/>
+      <c r="AC59" s="22" t="n"/>
+      <c r="AE59" s="25" t="n"/>
+      <c r="AF59" s="27" t="n"/>
+      <c r="AG59" s="22" t="n"/>
+      <c r="AI59" s="23" t="n"/>
+      <c r="AJ59" s="27" t="n"/>
+      <c r="AK59" s="22" t="n"/>
+      <c r="AM59" s="23" t="n"/>
+      <c r="AN59" s="24" t="n"/>
+      <c r="AO59" s="22" t="n"/>
+      <c r="AQ59" s="25" t="n"/>
+      <c r="AR59" s="27" t="n"/>
+      <c r="AS59" s="22" t="n"/>
+      <c r="AU59" s="25" t="n"/>
+      <c r="AV59" s="27" t="n"/>
     </row>
     <row r="60" ht="20.1" customHeight="1">
-      <c r="A60" s="28" t="n"/>
-      <c r="B60" s="29" t="n"/>
-      <c r="C60" s="30" t="n"/>
+      <c r="A60" s="29" t="n"/>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="31" t="n"/>
       <c r="D60" s="33" t="n"/>
-      <c r="E60" s="28" t="n"/>
-      <c r="F60" s="29" t="n"/>
-      <c r="G60" s="31" t="n"/>
+      <c r="E60" s="29" t="n"/>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="32" t="n"/>
       <c r="H60" s="33" t="n"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="29" t="n"/>
-      <c r="K60" s="30" t="n"/>
-      <c r="L60" s="41" t="inlineStr">
+      <c r="I60" s="29" t="n"/>
+      <c r="J60" s="30" t="n"/>
+      <c r="K60" s="31" t="n"/>
+      <c r="L60" s="39" t="inlineStr">
         <is>
           <t>Conseil presbytéral</t>
         </is>
       </c>
-      <c r="M60" s="28" t="n"/>
-      <c r="N60" s="29" t="n"/>
-      <c r="O60" s="31" t="n"/>
+      <c r="M60" s="29" t="n"/>
+      <c r="N60" s="30" t="n"/>
+      <c r="O60" s="32" t="n"/>
       <c r="P60" s="33" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="29" t="n"/>
-      <c r="S60" s="30" t="n"/>
-      <c r="T60" s="25" t="n"/>
-      <c r="U60" s="28" t="n"/>
-      <c r="V60" s="29" t="n"/>
-      <c r="W60" s="30" t="n"/>
+      <c r="Q60" s="29" t="n"/>
+      <c r="R60" s="30" t="n"/>
+      <c r="S60" s="31" t="n"/>
+      <c r="T60" s="33" t="n"/>
+      <c r="U60" s="29" t="n"/>
+      <c r="V60" s="30" t="n"/>
+      <c r="W60" s="31" t="n"/>
       <c r="X60" s="33" t="n"/>
-      <c r="Y60" s="28" t="n"/>
-      <c r="Z60" s="29" t="n"/>
-      <c r="AA60" s="30" t="n"/>
+      <c r="Y60" s="29" t="n"/>
+      <c r="Z60" s="30" t="n"/>
+      <c r="AA60" s="31" t="n"/>
       <c r="AB60" s="33" t="n"/>
-      <c r="AC60" s="28" t="n"/>
-      <c r="AD60" s="29" t="n"/>
-      <c r="AE60" s="31" t="n"/>
+      <c r="AC60" s="29" t="n"/>
+      <c r="AD60" s="30" t="n"/>
+      <c r="AE60" s="32" t="n"/>
       <c r="AF60" s="33" t="n"/>
-      <c r="AG60" s="28" t="n"/>
-      <c r="AH60" s="29" t="n"/>
-      <c r="AI60" s="30" t="n"/>
+      <c r="AG60" s="29" t="n"/>
+      <c r="AH60" s="30" t="n"/>
+      <c r="AI60" s="31" t="n"/>
       <c r="AJ60" s="33" t="n"/>
-      <c r="AK60" s="28" t="n"/>
-      <c r="AL60" s="29" t="n"/>
-      <c r="AM60" s="30" t="n"/>
-      <c r="AN60" s="25" t="n"/>
-      <c r="AO60" s="28" t="n"/>
-      <c r="AP60" s="29" t="n"/>
-      <c r="AQ60" s="31" t="n"/>
+      <c r="AK60" s="29" t="n"/>
+      <c r="AL60" s="30" t="n"/>
+      <c r="AM60" s="31" t="n"/>
+      <c r="AN60" s="26" t="n"/>
+      <c r="AO60" s="29" t="n"/>
+      <c r="AP60" s="30" t="n"/>
+      <c r="AQ60" s="32" t="n"/>
       <c r="AR60" s="33" t="n"/>
-      <c r="AS60" s="28" t="n"/>
-      <c r="AT60" s="29" t="n"/>
-      <c r="AU60" s="31" t="n"/>
+      <c r="AS60" s="29" t="n"/>
+      <c r="AT60" s="30" t="n"/>
+      <c r="AU60" s="32" t="n"/>
       <c r="AV60" s="33" t="n"/>
     </row>
     <row r="61" ht="20.1" customHeight="1">
@@ -5466,8 +5614,8 @@
       <c r="B61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C61" s="43" t="n"/>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="C61" s="41" t="n"/>
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Journée Communautaire</t>
         </is>
@@ -5481,7 +5629,11 @@
         <v>20</v>
       </c>
       <c r="G61" s="12" t="n"/>
-      <c r="H61" s="44" t="n"/>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5491,7 +5643,7 @@
         <v>20</v>
       </c>
       <c r="K61" s="7" t="n"/>
-      <c r="L61" s="38" t="n"/>
+      <c r="L61" s="50" t="n"/>
       <c r="M61" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -5501,7 +5653,7 @@
         <v>20</v>
       </c>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="49" t="inlineStr">
+      <c r="P61" s="47" t="inlineStr">
         <is>
           <t>4e dim. de l'Avent</t>
         </is>
@@ -5515,7 +5667,7 @@
         <v>20</v>
       </c>
       <c r="S61" s="7" t="n"/>
-      <c r="T61" s="18" t="n"/>
+      <c r="T61" s="19" t="n"/>
       <c r="U61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5525,7 +5677,7 @@
         <v>20</v>
       </c>
       <c r="W61" s="12" t="n"/>
-      <c r="X61" s="18" t="n"/>
+      <c r="X61" s="19" t="n"/>
       <c r="Y61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5535,7 +5687,11 @@
         <v>20</v>
       </c>
       <c r="AA61" s="7" t="n"/>
-      <c r="AB61" s="18" t="n"/>
+      <c r="AB61" s="18" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
       <c r="AC61" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5545,7 +5701,11 @@
         <v>20</v>
       </c>
       <c r="AE61" s="12" t="n"/>
-      <c r="AF61" s="18" t="n"/>
+      <c r="AF61" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="AG61" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5555,7 +5715,7 @@
         <v>20</v>
       </c>
       <c r="AI61" s="7" t="n"/>
-      <c r="AJ61" s="36" t="inlineStr">
+      <c r="AJ61" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -5568,8 +5728,8 @@
       <c r="AL61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AM61" s="43" t="n"/>
-      <c r="AN61" s="20" t="n"/>
+      <c r="AM61" s="41" t="n"/>
+      <c r="AN61" s="21" t="n"/>
       <c r="AO61" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5579,7 +5739,7 @@
         <v>20</v>
       </c>
       <c r="AQ61" s="12" t="n"/>
-      <c r="AR61" s="18" t="n"/>
+      <c r="AR61" s="19" t="n"/>
       <c r="AS61" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5589,94 +5749,94 @@
         <v>20</v>
       </c>
       <c r="AU61" s="12" t="n"/>
-      <c r="AV61" s="18" t="n"/>
+      <c r="AV61" s="19" t="n"/>
     </row>
     <row r="62" ht="20.1" customHeight="1">
-      <c r="A62" s="21" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="21" t="n"/>
-      <c r="G62" s="24" t="n"/>
-      <c r="H62" s="23" t="n"/>
-      <c r="I62" s="21" t="n"/>
-      <c r="K62" s="22" t="n"/>
-      <c r="L62" s="23" t="n"/>
-      <c r="M62" s="21" t="n"/>
-      <c r="O62" s="24" t="n"/>
-      <c r="P62" s="23" t="n"/>
-      <c r="Q62" s="21" t="n"/>
-      <c r="S62" s="22" t="n"/>
-      <c r="T62" s="26" t="n"/>
-      <c r="U62" s="21" t="n"/>
-      <c r="W62" s="24" t="n"/>
-      <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="21" t="n"/>
-      <c r="AA62" s="22" t="n"/>
-      <c r="AB62" s="26" t="n"/>
-      <c r="AC62" s="21" t="n"/>
-      <c r="AE62" s="24" t="n"/>
-      <c r="AF62" s="26" t="n"/>
-      <c r="AG62" s="21" t="n"/>
-      <c r="AI62" s="22" t="n"/>
-      <c r="AJ62" s="23" t="n"/>
-      <c r="AK62" s="21" t="n"/>
-      <c r="AM62" s="46" t="n"/>
-      <c r="AN62" s="27" t="n"/>
-      <c r="AO62" s="21" t="n"/>
-      <c r="AQ62" s="24" t="n"/>
-      <c r="AR62" s="26" t="n"/>
-      <c r="AS62" s="21" t="n"/>
-      <c r="AU62" s="24" t="n"/>
-      <c r="AV62" s="26" t="n"/>
+      <c r="A62" s="22" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="42" t="n"/>
+      <c r="I62" s="22" t="n"/>
+      <c r="K62" s="23" t="n"/>
+      <c r="L62" s="24" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="O62" s="25" t="n"/>
+      <c r="P62" s="24" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="S62" s="23" t="n"/>
+      <c r="T62" s="27" t="n"/>
+      <c r="U62" s="22" t="n"/>
+      <c r="W62" s="25" t="n"/>
+      <c r="X62" s="27" t="n"/>
+      <c r="Y62" s="22" t="n"/>
+      <c r="AA62" s="23" t="n"/>
+      <c r="AB62" s="24" t="n"/>
+      <c r="AC62" s="22" t="n"/>
+      <c r="AE62" s="25" t="n"/>
+      <c r="AF62" s="24" t="n"/>
+      <c r="AG62" s="22" t="n"/>
+      <c r="AI62" s="23" t="n"/>
+      <c r="AJ62" s="24" t="n"/>
+      <c r="AK62" s="22" t="n"/>
+      <c r="AM62" s="44" t="n"/>
+      <c r="AN62" s="28" t="n"/>
+      <c r="AO62" s="22" t="n"/>
+      <c r="AQ62" s="25" t="n"/>
+      <c r="AR62" s="27" t="n"/>
+      <c r="AS62" s="22" t="n"/>
+      <c r="AU62" s="25" t="n"/>
+      <c r="AV62" s="27" t="n"/>
     </row>
     <row r="63" ht="20.1" customHeight="1">
-      <c r="A63" s="28" t="n"/>
-      <c r="B63" s="29" t="n"/>
-      <c r="C63" s="47" t="n"/>
-      <c r="D63" s="25" t="n"/>
-      <c r="E63" s="28" t="n"/>
-      <c r="F63" s="29" t="n"/>
-      <c r="G63" s="31" t="n"/>
-      <c r="H63" s="23" t="n"/>
-      <c r="I63" s="28" t="n"/>
-      <c r="J63" s="29" t="n"/>
-      <c r="K63" s="30" t="n"/>
-      <c r="L63" s="25" t="n"/>
-      <c r="M63" s="28" t="n"/>
-      <c r="N63" s="29" t="n"/>
-      <c r="O63" s="31" t="n"/>
-      <c r="P63" s="25" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="29" t="n"/>
-      <c r="S63" s="30" t="n"/>
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="45" t="n"/>
+      <c r="D63" s="26" t="n"/>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="30" t="n"/>
+      <c r="G63" s="32" t="n"/>
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="29" t="n"/>
+      <c r="J63" s="30" t="n"/>
+      <c r="K63" s="31" t="n"/>
+      <c r="L63" s="26" t="n"/>
+      <c r="M63" s="29" t="n"/>
+      <c r="N63" s="30" t="n"/>
+      <c r="O63" s="32" t="n"/>
+      <c r="P63" s="26" t="n"/>
+      <c r="Q63" s="29" t="n"/>
+      <c r="R63" s="30" t="n"/>
+      <c r="S63" s="31" t="n"/>
       <c r="T63" s="33" t="n"/>
-      <c r="U63" s="28" t="n"/>
-      <c r="V63" s="29" t="n"/>
-      <c r="W63" s="31" t="n"/>
+      <c r="U63" s="29" t="n"/>
+      <c r="V63" s="30" t="n"/>
+      <c r="W63" s="32" t="n"/>
       <c r="X63" s="33" t="n"/>
-      <c r="Y63" s="28" t="n"/>
-      <c r="Z63" s="29" t="n"/>
-      <c r="AA63" s="30" t="n"/>
-      <c r="AB63" s="33" t="n"/>
-      <c r="AC63" s="28" t="n"/>
-      <c r="AD63" s="29" t="n"/>
-      <c r="AE63" s="31" t="n"/>
-      <c r="AF63" s="33" t="n"/>
-      <c r="AG63" s="28" t="n"/>
-      <c r="AH63" s="29" t="n"/>
-      <c r="AI63" s="30" t="n"/>
-      <c r="AJ63" s="25" t="n"/>
-      <c r="AK63" s="28" t="n"/>
-      <c r="AL63" s="29" t="n"/>
-      <c r="AM63" s="47" t="n"/>
-      <c r="AN63" s="35" t="n"/>
-      <c r="AO63" s="28" t="n"/>
-      <c r="AP63" s="29" t="n"/>
-      <c r="AQ63" s="31" t="n"/>
+      <c r="Y63" s="29" t="n"/>
+      <c r="Z63" s="30" t="n"/>
+      <c r="AA63" s="31" t="n"/>
+      <c r="AB63" s="26" t="n"/>
+      <c r="AC63" s="29" t="n"/>
+      <c r="AD63" s="30" t="n"/>
+      <c r="AE63" s="32" t="n"/>
+      <c r="AF63" s="26" t="n"/>
+      <c r="AG63" s="29" t="n"/>
+      <c r="AH63" s="30" t="n"/>
+      <c r="AI63" s="31" t="n"/>
+      <c r="AJ63" s="26" t="n"/>
+      <c r="AK63" s="29" t="n"/>
+      <c r="AL63" s="30" t="n"/>
+      <c r="AM63" s="45" t="n"/>
+      <c r="AN63" s="34" t="n"/>
+      <c r="AO63" s="29" t="n"/>
+      <c r="AP63" s="30" t="n"/>
+      <c r="AQ63" s="32" t="n"/>
       <c r="AR63" s="33" t="n"/>
-      <c r="AS63" s="28" t="n"/>
-      <c r="AT63" s="29" t="n"/>
-      <c r="AU63" s="31" t="n"/>
+      <c r="AS63" s="29" t="n"/>
+      <c r="AT63" s="30" t="n"/>
+      <c r="AU63" s="32" t="n"/>
       <c r="AV63" s="33" t="n"/>
     </row>
     <row r="64" ht="20.1" customHeight="1">
@@ -5689,7 +5849,7 @@
         <v>21</v>
       </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="18" t="n"/>
+      <c r="D64" s="19" t="n"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5699,7 +5859,7 @@
         <v>21</v>
       </c>
       <c r="G64" s="12" t="n"/>
-      <c r="H64" s="23" t="n"/>
+      <c r="H64" s="24" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5709,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="K64" s="7" t="n"/>
-      <c r="L64" s="18" t="n"/>
+      <c r="L64" s="19" t="n"/>
       <c r="M64" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -5719,7 +5879,7 @@
         <v>21</v>
       </c>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="18" t="n"/>
+      <c r="P64" s="19" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5729,7 +5889,7 @@
         <v>21</v>
       </c>
       <c r="S64" s="7" t="n"/>
-      <c r="T64" s="18" t="n"/>
+      <c r="T64" s="19" t="n"/>
       <c r="U64" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -5739,7 +5899,7 @@
         <v>21</v>
       </c>
       <c r="W64" s="12" t="n"/>
-      <c r="X64" s="51" t="inlineStr">
+      <c r="X64" s="49" t="inlineStr">
         <is>
           <t>2e dim. de Carême</t>
         </is>
@@ -5752,8 +5912,8 @@
       <c r="Z64" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="AA64" s="43" t="n"/>
-      <c r="AB64" s="51" t="inlineStr">
+      <c r="AA64" s="41" t="n"/>
+      <c r="AB64" s="49" t="inlineStr">
         <is>
           <t>Rameaux</t>
         </is>
@@ -5767,7 +5927,7 @@
         <v>21</v>
       </c>
       <c r="AE64" s="12" t="n"/>
-      <c r="AF64" s="18" t="n"/>
+      <c r="AF64" s="19" t="n"/>
       <c r="AG64" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5777,7 +5937,7 @@
         <v>21</v>
       </c>
       <c r="AI64" s="7" t="n"/>
-      <c r="AJ64" s="18" t="n"/>
+      <c r="AJ64" s="19" t="n"/>
       <c r="AK64" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5787,7 +5947,7 @@
         <v>21</v>
       </c>
       <c r="AM64" s="7" t="n"/>
-      <c r="AN64" s="18" t="n"/>
+      <c r="AN64" s="19" t="n"/>
       <c r="AO64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5797,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="AQ64" s="12" t="n"/>
-      <c r="AR64" s="18" t="n"/>
+      <c r="AR64" s="19" t="n"/>
       <c r="AS64" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5807,102 +5967,98 @@
         <v>21</v>
       </c>
       <c r="AU64" s="12" t="n"/>
-      <c r="AV64" s="18" t="n"/>
+      <c r="AV64" s="19" t="n"/>
     </row>
     <row r="65" ht="20.1" customHeight="1">
-      <c r="A65" s="21" t="n"/>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="26" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="G65" s="24" t="n"/>
-      <c r="H65" s="23" t="n"/>
-      <c r="I65" s="21" t="n"/>
-      <c r="K65" s="22" t="n"/>
-      <c r="L65" s="26" t="n"/>
-      <c r="M65" s="21" t="n"/>
-      <c r="O65" s="24" t="n"/>
-      <c r="P65" s="26" t="n"/>
-      <c r="Q65" s="21" t="n"/>
-      <c r="S65" s="22" t="n"/>
-      <c r="T65" s="26" t="n"/>
-      <c r="U65" s="21" t="n"/>
-      <c r="W65" s="24" t="n"/>
-      <c r="X65" s="54" t="inlineStr">
-        <is>
-          <t>Retraite des prêtres</t>
-        </is>
-      </c>
-      <c r="Y65" s="21" t="n"/>
-      <c r="AA65" s="46" t="n"/>
+      <c r="A65" s="22" t="n"/>
+      <c r="C65" s="23" t="n"/>
+      <c r="D65" s="27" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="G65" s="25" t="n"/>
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="K65" s="23" t="n"/>
+      <c r="L65" s="27" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="O65" s="25" t="n"/>
+      <c r="P65" s="27" t="n"/>
+      <c r="Q65" s="22" t="n"/>
+      <c r="S65" s="23" t="n"/>
+      <c r="T65" s="27" t="n"/>
+      <c r="U65" s="22" t="n"/>
+      <c r="W65" s="25" t="n"/>
+      <c r="X65" s="54" t="n"/>
+      <c r="Y65" s="22" t="n"/>
+      <c r="AA65" s="44" t="n"/>
       <c r="AB65" s="55" t="inlineStr">
         <is>
           <t>Semaine Sainte</t>
         </is>
       </c>
-      <c r="AC65" s="21" t="n"/>
-      <c r="AE65" s="24" t="n"/>
-      <c r="AF65" s="26" t="n"/>
-      <c r="AG65" s="21" t="n"/>
-      <c r="AI65" s="22" t="n"/>
-      <c r="AJ65" s="26" t="n"/>
-      <c r="AK65" s="21" t="n"/>
-      <c r="AM65" s="22" t="n"/>
-      <c r="AN65" s="26" t="n"/>
-      <c r="AO65" s="21" t="n"/>
-      <c r="AQ65" s="24" t="n"/>
-      <c r="AR65" s="26" t="n"/>
-      <c r="AS65" s="21" t="n"/>
-      <c r="AU65" s="24" t="n"/>
-      <c r="AV65" s="26" t="n"/>
+      <c r="AC65" s="22" t="n"/>
+      <c r="AE65" s="25" t="n"/>
+      <c r="AF65" s="27" t="n"/>
+      <c r="AG65" s="22" t="n"/>
+      <c r="AI65" s="23" t="n"/>
+      <c r="AJ65" s="27" t="n"/>
+      <c r="AK65" s="22" t="n"/>
+      <c r="AM65" s="23" t="n"/>
+      <c r="AN65" s="27" t="n"/>
+      <c r="AO65" s="22" t="n"/>
+      <c r="AQ65" s="25" t="n"/>
+      <c r="AR65" s="27" t="n"/>
+      <c r="AS65" s="22" t="n"/>
+      <c r="AU65" s="25" t="n"/>
+      <c r="AV65" s="27" t="n"/>
     </row>
     <row r="66" ht="20.1" customHeight="1">
-      <c r="A66" s="28" t="n"/>
-      <c r="B66" s="29" t="n"/>
-      <c r="C66" s="30" t="n"/>
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="30" t="n"/>
+      <c r="C66" s="31" t="n"/>
       <c r="D66" s="33" t="n"/>
-      <c r="E66" s="28" t="n"/>
-      <c r="F66" s="29" t="n"/>
-      <c r="G66" s="31" t="n"/>
-      <c r="H66" s="23" t="n"/>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="30" t="n"/>
+      <c r="E66" s="29" t="n"/>
+      <c r="F66" s="30" t="n"/>
+      <c r="G66" s="32" t="n"/>
+      <c r="H66" s="24" t="n"/>
+      <c r="I66" s="29" t="n"/>
+      <c r="J66" s="30" t="n"/>
+      <c r="K66" s="31" t="n"/>
       <c r="L66" s="33" t="n"/>
-      <c r="M66" s="28" t="n"/>
-      <c r="N66" s="29" t="n"/>
-      <c r="O66" s="31" t="n"/>
+      <c r="M66" s="29" t="n"/>
+      <c r="N66" s="30" t="n"/>
+      <c r="O66" s="32" t="n"/>
       <c r="P66" s="33" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="29" t="n"/>
-      <c r="S66" s="30" t="n"/>
+      <c r="Q66" s="29" t="n"/>
+      <c r="R66" s="30" t="n"/>
+      <c r="S66" s="31" t="n"/>
       <c r="T66" s="33" t="n"/>
-      <c r="U66" s="28" t="n"/>
-      <c r="V66" s="29" t="n"/>
-      <c r="W66" s="31" t="n"/>
-      <c r="X66" s="23" t="n"/>
-      <c r="Y66" s="28" t="n"/>
-      <c r="Z66" s="29" t="n"/>
-      <c r="AA66" s="47" t="n"/>
-      <c r="AB66" s="23" t="n"/>
-      <c r="AC66" s="28" t="n"/>
-      <c r="AD66" s="29" t="n"/>
-      <c r="AE66" s="31" t="n"/>
+      <c r="U66" s="29" t="n"/>
+      <c r="V66" s="30" t="n"/>
+      <c r="W66" s="32" t="n"/>
+      <c r="X66" s="24" t="n"/>
+      <c r="Y66" s="29" t="n"/>
+      <c r="Z66" s="30" t="n"/>
+      <c r="AA66" s="45" t="n"/>
+      <c r="AB66" s="24" t="n"/>
+      <c r="AC66" s="29" t="n"/>
+      <c r="AD66" s="30" t="n"/>
+      <c r="AE66" s="32" t="n"/>
       <c r="AF66" s="33" t="n"/>
-      <c r="AG66" s="28" t="n"/>
-      <c r="AH66" s="29" t="n"/>
-      <c r="AI66" s="30" t="n"/>
+      <c r="AG66" s="29" t="n"/>
+      <c r="AH66" s="30" t="n"/>
+      <c r="AI66" s="31" t="n"/>
       <c r="AJ66" s="33" t="n"/>
-      <c r="AK66" s="28" t="n"/>
-      <c r="AL66" s="29" t="n"/>
-      <c r="AM66" s="30" t="n"/>
+      <c r="AK66" s="29" t="n"/>
+      <c r="AL66" s="30" t="n"/>
+      <c r="AM66" s="31" t="n"/>
       <c r="AN66" s="33" t="n"/>
-      <c r="AO66" s="28" t="n"/>
-      <c r="AP66" s="29" t="n"/>
-      <c r="AQ66" s="31" t="n"/>
+      <c r="AO66" s="29" t="n"/>
+      <c r="AP66" s="30" t="n"/>
+      <c r="AQ66" s="32" t="n"/>
       <c r="AR66" s="33" t="n"/>
-      <c r="AS66" s="28" t="n"/>
-      <c r="AT66" s="29" t="n"/>
-      <c r="AU66" s="31" t="n"/>
+      <c r="AS66" s="29" t="n"/>
+      <c r="AT66" s="30" t="n"/>
+      <c r="AU66" s="32" t="n"/>
       <c r="AV66" s="33" t="n"/>
     </row>
     <row r="67" ht="20.1" customHeight="1">
@@ -5915,7 +6071,7 @@
         <v>22</v>
       </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="18" t="n"/>
+      <c r="D67" s="19" t="n"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5925,7 +6081,7 @@
         <v>22</v>
       </c>
       <c r="G67" s="12" t="n"/>
-      <c r="H67" s="23" t="n"/>
+      <c r="H67" s="24" t="n"/>
       <c r="I67" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -5934,8 +6090,8 @@
       <c r="J67" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="K67" s="43" t="n"/>
-      <c r="L67" s="17" t="inlineStr">
+      <c r="K67" s="41" t="n"/>
+      <c r="L67" s="20" t="inlineStr">
         <is>
           <t>Christ Roi</t>
         </is>
@@ -5949,7 +6105,11 @@
         <v>22</v>
       </c>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="18" t="n"/>
+      <c r="P67" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5959,7 +6119,7 @@
         <v>22</v>
       </c>
       <c r="S67" s="7" t="n"/>
-      <c r="T67" s="18" t="n"/>
+      <c r="T67" s="19" t="n"/>
       <c r="U67" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -5969,7 +6129,7 @@
         <v>22</v>
       </c>
       <c r="W67" s="12" t="n"/>
-      <c r="X67" s="23" t="n"/>
+      <c r="X67" s="24" t="n"/>
       <c r="Y67" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -5979,7 +6139,7 @@
         <v>22</v>
       </c>
       <c r="AA67" s="7" t="n"/>
-      <c r="AB67" s="23" t="n"/>
+      <c r="AB67" s="24" t="n"/>
       <c r="AC67" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5989,7 +6149,7 @@
         <v>22</v>
       </c>
       <c r="AE67" s="12" t="n"/>
-      <c r="AF67" s="18" t="n"/>
+      <c r="AF67" s="19" t="n"/>
       <c r="AG67" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5999,7 +6159,11 @@
         <v>22</v>
       </c>
       <c r="AI67" s="7" t="n"/>
-      <c r="AJ67" s="18" t="n"/>
+      <c r="AJ67" s="18" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
       <c r="AK67" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6023,7 +6187,7 @@
         <v>22</v>
       </c>
       <c r="AQ67" s="12" t="n"/>
-      <c r="AR67" s="18" t="n"/>
+      <c r="AR67" s="19" t="n"/>
       <c r="AS67" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6033,95 +6197,99 @@
         <v>22</v>
       </c>
       <c r="AU67" s="12" t="n"/>
-      <c r="AV67" s="20" t="n"/>
+      <c r="AV67" s="21" t="n"/>
     </row>
     <row r="68" ht="20.1" customHeight="1">
-      <c r="A68" s="21" t="n"/>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="26" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="G68" s="24" t="n"/>
-      <c r="H68" s="23" t="n"/>
-      <c r="I68" s="21" t="n"/>
-      <c r="K68" s="46" t="n"/>
-      <c r="L68" s="23" t="n"/>
-      <c r="M68" s="21" t="n"/>
-      <c r="O68" s="24" t="n"/>
-      <c r="P68" s="26" t="n"/>
-      <c r="Q68" s="21" t="n"/>
-      <c r="S68" s="22" t="n"/>
-      <c r="T68" s="26" t="n"/>
-      <c r="U68" s="21" t="n"/>
-      <c r="W68" s="24" t="n"/>
-      <c r="X68" s="23" t="n"/>
-      <c r="Y68" s="21" t="n"/>
-      <c r="AA68" s="22" t="n"/>
-      <c r="AB68" s="23" t="n"/>
-      <c r="AC68" s="21" t="n"/>
-      <c r="AE68" s="24" t="n"/>
-      <c r="AF68" s="26" t="n"/>
-      <c r="AG68" s="21" t="n"/>
-      <c r="AI68" s="22" t="n"/>
-      <c r="AJ68" s="26" t="n"/>
-      <c r="AK68" s="21" t="n"/>
-      <c r="AM68" s="22" t="n"/>
-      <c r="AN68" s="23" t="n"/>
-      <c r="AO68" s="21" t="n"/>
-      <c r="AQ68" s="24" t="n"/>
-      <c r="AR68" s="26" t="n"/>
-      <c r="AS68" s="21" t="n"/>
-      <c r="AU68" s="24" t="n"/>
-      <c r="AV68" s="27" t="n"/>
+      <c r="A68" s="22" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="27" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="G68" s="25" t="n"/>
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="22" t="n"/>
+      <c r="K68" s="44" t="n"/>
+      <c r="L68" s="24" t="n"/>
+      <c r="M68" s="22" t="n"/>
+      <c r="O68" s="25" t="n"/>
+      <c r="P68" s="24" t="n"/>
+      <c r="Q68" s="22" t="n"/>
+      <c r="S68" s="23" t="n"/>
+      <c r="T68" s="27" t="n"/>
+      <c r="U68" s="22" t="n"/>
+      <c r="W68" s="25" t="n"/>
+      <c r="X68" s="24" t="n"/>
+      <c r="Y68" s="22" t="n"/>
+      <c r="AA68" s="23" t="n"/>
+      <c r="AB68" s="24" t="n"/>
+      <c r="AC68" s="22" t="n"/>
+      <c r="AE68" s="25" t="n"/>
+      <c r="AF68" s="27" t="n"/>
+      <c r="AG68" s="22" t="n"/>
+      <c r="AI68" s="23" t="n"/>
+      <c r="AJ68" s="24" t="n"/>
+      <c r="AK68" s="22" t="n"/>
+      <c r="AM68" s="23" t="n"/>
+      <c r="AN68" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AO68" s="22" t="n"/>
+      <c r="AQ68" s="25" t="n"/>
+      <c r="AR68" s="27" t="n"/>
+      <c r="AS68" s="22" t="n"/>
+      <c r="AU68" s="25" t="n"/>
+      <c r="AV68" s="28" t="n"/>
     </row>
     <row r="69" ht="20.1" customHeight="1">
-      <c r="A69" s="28" t="n"/>
-      <c r="B69" s="29" t="n"/>
-      <c r="C69" s="30" t="n"/>
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="31" t="n"/>
       <c r="D69" s="33" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="29" t="n"/>
-      <c r="G69" s="31" t="n"/>
-      <c r="H69" s="23" t="n"/>
-      <c r="I69" s="28" t="n"/>
-      <c r="J69" s="29" t="n"/>
-      <c r="K69" s="47" t="n"/>
-      <c r="L69" s="25" t="n"/>
-      <c r="M69" s="28" t="n"/>
-      <c r="N69" s="29" t="n"/>
-      <c r="O69" s="31" t="n"/>
-      <c r="P69" s="33" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="29" t="n"/>
-      <c r="S69" s="30" t="n"/>
+      <c r="E69" s="29" t="n"/>
+      <c r="F69" s="30" t="n"/>
+      <c r="G69" s="32" t="n"/>
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="29" t="n"/>
+      <c r="J69" s="30" t="n"/>
+      <c r="K69" s="45" t="n"/>
+      <c r="L69" s="26" t="n"/>
+      <c r="M69" s="29" t="n"/>
+      <c r="N69" s="30" t="n"/>
+      <c r="O69" s="32" t="n"/>
+      <c r="P69" s="26" t="n"/>
+      <c r="Q69" s="29" t="n"/>
+      <c r="R69" s="30" t="n"/>
+      <c r="S69" s="31" t="n"/>
       <c r="T69" s="33" t="n"/>
-      <c r="U69" s="28" t="n"/>
-      <c r="V69" s="29" t="n"/>
-      <c r="W69" s="31" t="n"/>
-      <c r="X69" s="23" t="n"/>
-      <c r="Y69" s="28" t="n"/>
-      <c r="Z69" s="29" t="n"/>
-      <c r="AA69" s="30" t="n"/>
-      <c r="AB69" s="23" t="n"/>
-      <c r="AC69" s="28" t="n"/>
-      <c r="AD69" s="29" t="n"/>
-      <c r="AE69" s="31" t="n"/>
+      <c r="U69" s="29" t="n"/>
+      <c r="V69" s="30" t="n"/>
+      <c r="W69" s="32" t="n"/>
+      <c r="X69" s="24" t="n"/>
+      <c r="Y69" s="29" t="n"/>
+      <c r="Z69" s="30" t="n"/>
+      <c r="AA69" s="31" t="n"/>
+      <c r="AB69" s="24" t="n"/>
+      <c r="AC69" s="29" t="n"/>
+      <c r="AD69" s="30" t="n"/>
+      <c r="AE69" s="32" t="n"/>
       <c r="AF69" s="33" t="n"/>
-      <c r="AG69" s="28" t="n"/>
-      <c r="AH69" s="29" t="n"/>
-      <c r="AI69" s="30" t="n"/>
-      <c r="AJ69" s="33" t="n"/>
-      <c r="AK69" s="28" t="n"/>
-      <c r="AL69" s="29" t="n"/>
-      <c r="AM69" s="30" t="n"/>
-      <c r="AN69" s="25" t="n"/>
-      <c r="AO69" s="28" t="n"/>
-      <c r="AP69" s="29" t="n"/>
-      <c r="AQ69" s="31" t="n"/>
+      <c r="AG69" s="29" t="n"/>
+      <c r="AH69" s="30" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="26" t="n"/>
+      <c r="AK69" s="29" t="n"/>
+      <c r="AL69" s="30" t="n"/>
+      <c r="AM69" s="31" t="n"/>
+      <c r="AN69" s="33" t="n"/>
+      <c r="AO69" s="29" t="n"/>
+      <c r="AP69" s="30" t="n"/>
+      <c r="AQ69" s="32" t="n"/>
       <c r="AR69" s="33" t="n"/>
-      <c r="AS69" s="28" t="n"/>
-      <c r="AT69" s="29" t="n"/>
-      <c r="AU69" s="31" t="n"/>
-      <c r="AV69" s="35" t="n"/>
+      <c r="AS69" s="29" t="n"/>
+      <c r="AT69" s="30" t="n"/>
+      <c r="AU69" s="32" t="n"/>
+      <c r="AV69" s="34" t="n"/>
     </row>
     <row r="70" ht="20.1" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -6133,7 +6301,7 @@
         <v>23</v>
       </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="18" t="n"/>
+      <c r="D70" s="19" t="n"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6143,7 +6311,7 @@
         <v>23</v>
       </c>
       <c r="G70" s="12" t="n"/>
-      <c r="H70" s="23" t="n"/>
+      <c r="H70" s="24" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6153,7 +6321,7 @@
         <v>23</v>
       </c>
       <c r="K70" s="7" t="n"/>
-      <c r="L70" s="18" t="n"/>
+      <c r="L70" s="19" t="n"/>
       <c r="M70" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6163,7 +6331,7 @@
         <v>23</v>
       </c>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="18" t="n"/>
+      <c r="P70" s="19" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6173,7 +6341,11 @@
         <v>23</v>
       </c>
       <c r="S70" s="7" t="n"/>
-      <c r="T70" s="18" t="n"/>
+      <c r="T70" s="18" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
       <c r="U70" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6183,7 +6355,7 @@
         <v>23</v>
       </c>
       <c r="W70" s="12" t="n"/>
-      <c r="X70" s="23" t="n"/>
+      <c r="X70" s="24" t="n"/>
       <c r="Y70" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6193,7 +6365,7 @@
         <v>23</v>
       </c>
       <c r="AA70" s="7" t="n"/>
-      <c r="AB70" s="25" t="n"/>
+      <c r="AB70" s="26" t="n"/>
       <c r="AC70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6203,7 +6375,7 @@
         <v>23</v>
       </c>
       <c r="AE70" s="12" t="n"/>
-      <c r="AF70" s="18" t="n"/>
+      <c r="AF70" s="19" t="n"/>
       <c r="AG70" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6212,8 +6384,8 @@
       <c r="AH70" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="AI70" s="43" t="n"/>
-      <c r="AJ70" s="20" t="n"/>
+      <c r="AI70" s="41" t="n"/>
+      <c r="AJ70" s="21" t="n"/>
       <c r="AK70" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6223,7 +6395,7 @@
         <v>23</v>
       </c>
       <c r="AM70" s="7" t="n"/>
-      <c r="AN70" s="18" t="n"/>
+      <c r="AN70" s="19" t="n"/>
       <c r="AO70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6233,7 +6405,7 @@
         <v>23</v>
       </c>
       <c r="AQ70" s="12" t="n"/>
-      <c r="AR70" s="18" t="n"/>
+      <c r="AR70" s="19" t="n"/>
       <c r="AS70" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6243,106 +6415,110 @@
         <v>23</v>
       </c>
       <c r="AU70" s="12" t="n"/>
-      <c r="AV70" s="18" t="n"/>
+      <c r="AV70" s="19" t="n"/>
     </row>
     <row r="71" ht="20.1" customHeight="1">
-      <c r="A71" s="21" t="n"/>
-      <c r="C71" s="22" t="n"/>
-      <c r="D71" s="26" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="G71" s="24" t="n"/>
-      <c r="H71" s="25" t="n"/>
-      <c r="I71" s="21" t="n"/>
-      <c r="K71" s="22" t="n"/>
-      <c r="L71" s="26" t="n"/>
-      <c r="M71" s="21" t="n"/>
-      <c r="O71" s="24" t="n"/>
-      <c r="P71" s="26" t="n"/>
-      <c r="Q71" s="21" t="n"/>
-      <c r="S71" s="22" t="n"/>
-      <c r="T71" s="26" t="n"/>
-      <c r="U71" s="21" t="n"/>
-      <c r="W71" s="24" t="n"/>
-      <c r="X71" s="23" t="n"/>
-      <c r="Y71" s="21" t="n"/>
-      <c r="AA71" s="22" t="n"/>
-      <c r="AB71" s="51" t="inlineStr">
+      <c r="A71" s="22" t="n"/>
+      <c r="C71" s="23" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="G71" s="25" t="n"/>
+      <c r="H71" s="26" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="K71" s="23" t="n"/>
+      <c r="L71" s="27" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="O71" s="25" t="n"/>
+      <c r="P71" s="27" t="n"/>
+      <c r="Q71" s="22" t="n"/>
+      <c r="S71" s="23" t="n"/>
+      <c r="T71" s="24" t="n"/>
+      <c r="U71" s="22" t="n"/>
+      <c r="W71" s="25" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="22" t="n"/>
+      <c r="AA71" s="23" t="n"/>
+      <c r="AB71" s="49" t="inlineStr">
         <is>
           <t>Messe Chrismale</t>
         </is>
       </c>
-      <c r="AC71" s="21" t="n"/>
-      <c r="AE71" s="24" t="n"/>
-      <c r="AF71" s="26" t="n"/>
-      <c r="AG71" s="21" t="n"/>
-      <c r="AI71" s="46" t="n"/>
-      <c r="AJ71" s="27" t="n"/>
-      <c r="AK71" s="21" t="n"/>
-      <c r="AM71" s="22" t="n"/>
-      <c r="AN71" s="26" t="n"/>
-      <c r="AO71" s="21" t="n"/>
-      <c r="AQ71" s="24" t="n"/>
-      <c r="AR71" s="26" t="n"/>
-      <c r="AS71" s="21" t="n"/>
-      <c r="AU71" s="24" t="n"/>
-      <c r="AV71" s="26" t="n"/>
+      <c r="AC71" s="22" t="n"/>
+      <c r="AE71" s="25" t="n"/>
+      <c r="AF71" s="27" t="n"/>
+      <c r="AG71" s="22" t="n"/>
+      <c r="AI71" s="44" t="n"/>
+      <c r="AJ71" s="28" t="n"/>
+      <c r="AK71" s="22" t="n"/>
+      <c r="AM71" s="23" t="n"/>
+      <c r="AN71" s="27" t="n"/>
+      <c r="AO71" s="22" t="n"/>
+      <c r="AQ71" s="25" t="n"/>
+      <c r="AR71" s="27" t="n"/>
+      <c r="AS71" s="22" t="n"/>
+      <c r="AU71" s="25" t="n"/>
+      <c r="AV71" s="27" t="n"/>
     </row>
     <row r="72" ht="20.1" customHeight="1">
-      <c r="A72" s="28" t="n"/>
-      <c r="B72" s="29" t="n"/>
-      <c r="C72" s="30" t="n"/>
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="30" t="n"/>
+      <c r="C72" s="31" t="n"/>
       <c r="D72" s="33" t="n"/>
-      <c r="E72" s="28" t="n"/>
-      <c r="F72" s="29" t="n"/>
-      <c r="G72" s="31" t="n"/>
-      <c r="H72" s="42" t="inlineStr">
+      <c r="E72" s="29" t="n"/>
+      <c r="F72" s="30" t="n"/>
+      <c r="G72" s="32" t="n"/>
+      <c r="H72" s="40" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
       </c>
-      <c r="I72" s="28" t="n"/>
-      <c r="J72" s="29" t="n"/>
-      <c r="K72" s="30" t="n"/>
+      <c r="I72" s="29" t="n"/>
+      <c r="J72" s="30" t="n"/>
+      <c r="K72" s="31" t="n"/>
       <c r="L72" s="33" t="n"/>
-      <c r="M72" s="28" t="n"/>
-      <c r="N72" s="29" t="n"/>
-      <c r="O72" s="31" t="n"/>
+      <c r="M72" s="29" t="n"/>
+      <c r="N72" s="30" t="n"/>
+      <c r="O72" s="32" t="n"/>
       <c r="P72" s="33" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="29" t="n"/>
-      <c r="S72" s="30" t="n"/>
-      <c r="T72" s="33" t="n"/>
-      <c r="U72" s="28" t="n"/>
-      <c r="V72" s="29" t="n"/>
-      <c r="W72" s="31" t="n"/>
-      <c r="X72" s="23" t="n"/>
-      <c r="Y72" s="28" t="n"/>
-      <c r="Z72" s="29" t="n"/>
-      <c r="AA72" s="30" t="n"/>
-      <c r="AB72" s="41" t="inlineStr">
+      <c r="Q72" s="29" t="n"/>
+      <c r="R72" s="30" t="n"/>
+      <c r="S72" s="31" t="n"/>
+      <c r="T72" s="26" t="n"/>
+      <c r="U72" s="29" t="n"/>
+      <c r="V72" s="30" t="n"/>
+      <c r="W72" s="32" t="n"/>
+      <c r="X72" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Y72" s="29" t="n"/>
+      <c r="Z72" s="30" t="n"/>
+      <c r="AA72" s="31" t="n"/>
+      <c r="AB72" s="39" t="inlineStr">
         <is>
           <t>Rencontre des prêtres</t>
         </is>
       </c>
-      <c r="AC72" s="28" t="n"/>
-      <c r="AD72" s="29" t="n"/>
-      <c r="AE72" s="31" t="n"/>
+      <c r="AC72" s="29" t="n"/>
+      <c r="AD72" s="30" t="n"/>
+      <c r="AE72" s="32" t="n"/>
       <c r="AF72" s="33" t="n"/>
-      <c r="AG72" s="28" t="n"/>
-      <c r="AH72" s="29" t="n"/>
-      <c r="AI72" s="47" t="n"/>
-      <c r="AJ72" s="35" t="n"/>
-      <c r="AK72" s="28" t="n"/>
-      <c r="AL72" s="29" t="n"/>
-      <c r="AM72" s="30" t="n"/>
+      <c r="AG72" s="29" t="n"/>
+      <c r="AH72" s="30" t="n"/>
+      <c r="AI72" s="45" t="n"/>
+      <c r="AJ72" s="34" t="n"/>
+      <c r="AK72" s="29" t="n"/>
+      <c r="AL72" s="30" t="n"/>
+      <c r="AM72" s="31" t="n"/>
       <c r="AN72" s="33" t="n"/>
-      <c r="AO72" s="28" t="n"/>
-      <c r="AP72" s="29" t="n"/>
-      <c r="AQ72" s="31" t="n"/>
+      <c r="AO72" s="29" t="n"/>
+      <c r="AP72" s="30" t="n"/>
+      <c r="AQ72" s="32" t="n"/>
       <c r="AR72" s="33" t="n"/>
-      <c r="AS72" s="28" t="n"/>
-      <c r="AT72" s="29" t="n"/>
-      <c r="AU72" s="31" t="n"/>
+      <c r="AS72" s="29" t="n"/>
+      <c r="AT72" s="30" t="n"/>
+      <c r="AU72" s="32" t="n"/>
       <c r="AV72" s="33" t="n"/>
     </row>
     <row r="73" ht="20.1" customHeight="1">
@@ -6355,7 +6531,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="18" t="n"/>
+      <c r="D73" s="19" t="n"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6365,11 +6541,7 @@
         <v>24</v>
       </c>
       <c r="G73" s="12" t="n"/>
-      <c r="H73" s="56" t="inlineStr">
-        <is>
-          <t>Père Pascal en Côte d'Ivoire</t>
-        </is>
-      </c>
+      <c r="H73" s="42" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6393,7 +6565,7 @@
         <v>24</v>
       </c>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="18" t="n"/>
+      <c r="P73" s="19" t="n"/>
       <c r="Q73" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6402,8 +6574,8 @@
       <c r="R73" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S73" s="43" t="n"/>
-      <c r="T73" s="20" t="n"/>
+      <c r="S73" s="41" t="n"/>
+      <c r="T73" s="21" t="n"/>
       <c r="U73" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6413,7 +6585,11 @@
         <v>24</v>
       </c>
       <c r="W73" s="12" t="n"/>
-      <c r="X73" s="23" t="n"/>
+      <c r="X73" s="54" t="inlineStr">
+        <is>
+          <t>Retraite des prêtres</t>
+        </is>
+      </c>
       <c r="Y73" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6423,7 +6599,7 @@
         <v>24</v>
       </c>
       <c r="AA73" s="7" t="n"/>
-      <c r="AB73" s="49" t="n"/>
+      <c r="AB73" s="47" t="n"/>
       <c r="AC73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6433,7 +6609,7 @@
         <v>24</v>
       </c>
       <c r="AE73" s="12" t="n"/>
-      <c r="AF73" s="18" t="n"/>
+      <c r="AF73" s="19" t="n"/>
       <c r="AG73" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6443,7 +6619,7 @@
         <v>24</v>
       </c>
       <c r="AI73" s="7" t="n"/>
-      <c r="AJ73" s="18" t="n"/>
+      <c r="AJ73" s="19" t="n"/>
       <c r="AK73" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6453,7 +6629,7 @@
         <v>24</v>
       </c>
       <c r="AM73" s="7" t="n"/>
-      <c r="AN73" s="18" t="n"/>
+      <c r="AN73" s="19" t="n"/>
       <c r="AO73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6463,7 +6639,7 @@
         <v>24</v>
       </c>
       <c r="AQ73" s="12" t="n"/>
-      <c r="AR73" s="18" t="n"/>
+      <c r="AR73" s="19" t="n"/>
       <c r="AS73" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6473,94 +6649,98 @@
         <v>24</v>
       </c>
       <c r="AU73" s="12" t="n"/>
-      <c r="AV73" s="18" t="n"/>
+      <c r="AV73" s="19" t="n"/>
     </row>
     <row r="74" ht="20.1" customHeight="1">
-      <c r="A74" s="21" t="n"/>
-      <c r="C74" s="22" t="n"/>
-      <c r="D74" s="26" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="G74" s="24" t="n"/>
-      <c r="H74" s="23" t="n"/>
-      <c r="I74" s="21" t="n"/>
-      <c r="K74" s="22" t="n"/>
-      <c r="L74" s="23" t="n"/>
-      <c r="M74" s="21" t="n"/>
-      <c r="O74" s="24" t="n"/>
-      <c r="P74" s="26" t="n"/>
-      <c r="Q74" s="21" t="n"/>
-      <c r="S74" s="46" t="n"/>
-      <c r="T74" s="27" t="n"/>
-      <c r="U74" s="21" t="n"/>
-      <c r="W74" s="24" t="n"/>
-      <c r="X74" s="23" t="n"/>
-      <c r="Y74" s="21" t="n"/>
-      <c r="AA74" s="22" t="n"/>
-      <c r="AB74" s="23" t="n"/>
-      <c r="AC74" s="21" t="n"/>
-      <c r="AE74" s="24" t="n"/>
-      <c r="AF74" s="26" t="n"/>
-      <c r="AG74" s="21" t="n"/>
-      <c r="AI74" s="22" t="n"/>
-      <c r="AJ74" s="26" t="n"/>
-      <c r="AK74" s="21" t="n"/>
-      <c r="AM74" s="22" t="n"/>
-      <c r="AN74" s="26" t="n"/>
-      <c r="AO74" s="21" t="n"/>
-      <c r="AQ74" s="24" t="n"/>
-      <c r="AR74" s="26" t="n"/>
-      <c r="AS74" s="21" t="n"/>
-      <c r="AU74" s="24" t="n"/>
-      <c r="AV74" s="26" t="n"/>
+      <c r="A74" s="22" t="n"/>
+      <c r="C74" s="23" t="n"/>
+      <c r="D74" s="27" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="G74" s="25" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="22" t="n"/>
+      <c r="K74" s="23" t="n"/>
+      <c r="L74" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="M74" s="22" t="n"/>
+      <c r="O74" s="25" t="n"/>
+      <c r="P74" s="27" t="n"/>
+      <c r="Q74" s="22" t="n"/>
+      <c r="S74" s="44" t="n"/>
+      <c r="T74" s="28" t="n"/>
+      <c r="U74" s="22" t="n"/>
+      <c r="W74" s="25" t="n"/>
+      <c r="X74" s="24" t="n"/>
+      <c r="Y74" s="22" t="n"/>
+      <c r="AA74" s="23" t="n"/>
+      <c r="AB74" s="24" t="n"/>
+      <c r="AC74" s="22" t="n"/>
+      <c r="AE74" s="25" t="n"/>
+      <c r="AF74" s="27" t="n"/>
+      <c r="AG74" s="22" t="n"/>
+      <c r="AI74" s="23" t="n"/>
+      <c r="AJ74" s="27" t="n"/>
+      <c r="AK74" s="22" t="n"/>
+      <c r="AM74" s="23" t="n"/>
+      <c r="AN74" s="27" t="n"/>
+      <c r="AO74" s="22" t="n"/>
+      <c r="AQ74" s="25" t="n"/>
+      <c r="AR74" s="27" t="n"/>
+      <c r="AS74" s="22" t="n"/>
+      <c r="AU74" s="25" t="n"/>
+      <c r="AV74" s="27" t="n"/>
     </row>
     <row r="75" ht="20.1" customHeight="1">
-      <c r="A75" s="28" t="n"/>
-      <c r="B75" s="29" t="n"/>
-      <c r="C75" s="30" t="n"/>
+      <c r="A75" s="29" t="n"/>
+      <c r="B75" s="30" t="n"/>
+      <c r="C75" s="31" t="n"/>
       <c r="D75" s="33" t="n"/>
-      <c r="E75" s="28" t="n"/>
-      <c r="F75" s="29" t="n"/>
-      <c r="G75" s="31" t="n"/>
-      <c r="H75" s="23" t="n"/>
-      <c r="I75" s="28" t="n"/>
-      <c r="J75" s="29" t="n"/>
-      <c r="K75" s="30" t="n"/>
-      <c r="L75" s="25" t="n"/>
-      <c r="M75" s="28" t="n"/>
-      <c r="N75" s="29" t="n"/>
-      <c r="O75" s="31" t="n"/>
+      <c r="E75" s="29" t="n"/>
+      <c r="F75" s="30" t="n"/>
+      <c r="G75" s="32" t="n"/>
+      <c r="H75" s="24" t="n"/>
+      <c r="I75" s="29" t="n"/>
+      <c r="J75" s="30" t="n"/>
+      <c r="K75" s="31" t="n"/>
+      <c r="L75" s="33" t="n"/>
+      <c r="M75" s="29" t="n"/>
+      <c r="N75" s="30" t="n"/>
+      <c r="O75" s="32" t="n"/>
       <c r="P75" s="33" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="29" t="n"/>
-      <c r="S75" s="47" t="n"/>
-      <c r="T75" s="35" t="n"/>
-      <c r="U75" s="28" t="n"/>
-      <c r="V75" s="29" t="n"/>
-      <c r="W75" s="31" t="n"/>
-      <c r="X75" s="23" t="n"/>
-      <c r="Y75" s="28" t="n"/>
-      <c r="Z75" s="29" t="n"/>
-      <c r="AA75" s="30" t="n"/>
-      <c r="AB75" s="23" t="n"/>
-      <c r="AC75" s="28" t="n"/>
-      <c r="AD75" s="29" t="n"/>
-      <c r="AE75" s="31" t="n"/>
+      <c r="Q75" s="29" t="n"/>
+      <c r="R75" s="30" t="n"/>
+      <c r="S75" s="45" t="n"/>
+      <c r="T75" s="34" t="n"/>
+      <c r="U75" s="29" t="n"/>
+      <c r="V75" s="30" t="n"/>
+      <c r="W75" s="32" t="n"/>
+      <c r="X75" s="24" t="n"/>
+      <c r="Y75" s="29" t="n"/>
+      <c r="Z75" s="30" t="n"/>
+      <c r="AA75" s="31" t="n"/>
+      <c r="AB75" s="24" t="n"/>
+      <c r="AC75" s="29" t="n"/>
+      <c r="AD75" s="30" t="n"/>
+      <c r="AE75" s="32" t="n"/>
       <c r="AF75" s="33" t="n"/>
-      <c r="AG75" s="28" t="n"/>
-      <c r="AH75" s="29" t="n"/>
-      <c r="AI75" s="30" t="n"/>
+      <c r="AG75" s="29" t="n"/>
+      <c r="AH75" s="30" t="n"/>
+      <c r="AI75" s="31" t="n"/>
       <c r="AJ75" s="33" t="n"/>
-      <c r="AK75" s="28" t="n"/>
-      <c r="AL75" s="29" t="n"/>
-      <c r="AM75" s="30" t="n"/>
+      <c r="AK75" s="29" t="n"/>
+      <c r="AL75" s="30" t="n"/>
+      <c r="AM75" s="31" t="n"/>
       <c r="AN75" s="33" t="n"/>
-      <c r="AO75" s="28" t="n"/>
-      <c r="AP75" s="29" t="n"/>
-      <c r="AQ75" s="31" t="n"/>
+      <c r="AO75" s="29" t="n"/>
+      <c r="AP75" s="30" t="n"/>
+      <c r="AQ75" s="32" t="n"/>
       <c r="AR75" s="33" t="n"/>
-      <c r="AS75" s="28" t="n"/>
-      <c r="AT75" s="29" t="n"/>
-      <c r="AU75" s="31" t="n"/>
+      <c r="AS75" s="29" t="n"/>
+      <c r="AT75" s="30" t="n"/>
+      <c r="AU75" s="32" t="n"/>
       <c r="AV75" s="33" t="n"/>
     </row>
     <row r="76" ht="20.1" customHeight="1">
@@ -6573,7 +6753,7 @@
         <v>25</v>
       </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="38" t="inlineStr">
+      <c r="D76" s="50" t="inlineStr">
         <is>
           <t>Visite du Pape</t>
         </is>
@@ -6587,7 +6767,7 @@
         <v>25</v>
       </c>
       <c r="G76" s="12" t="n"/>
-      <c r="H76" s="23" t="n"/>
+      <c r="H76" s="24" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6597,7 +6777,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="7" t="n"/>
-      <c r="L76" s="18" t="n"/>
+      <c r="L76" s="19" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6607,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="17" t="inlineStr">
+      <c r="P76" s="20" t="inlineStr">
         <is>
           <t>Noël</t>
         </is>
@@ -6621,7 +6801,7 @@
         <v>25</v>
       </c>
       <c r="S76" s="7" t="n"/>
-      <c r="T76" s="18" t="n"/>
+      <c r="T76" s="19" t="n"/>
       <c r="U76" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6631,7 +6811,7 @@
         <v>25</v>
       </c>
       <c r="W76" s="12" t="n"/>
-      <c r="X76" s="23" t="n"/>
+      <c r="X76" s="24" t="n"/>
       <c r="Y76" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6641,7 +6821,7 @@
         <v>25</v>
       </c>
       <c r="AA76" s="7" t="n"/>
-      <c r="AB76" s="23" t="n"/>
+      <c r="AB76" s="24" t="n"/>
       <c r="AC76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6651,7 +6831,7 @@
         <v>25</v>
       </c>
       <c r="AE76" s="12" t="n"/>
-      <c r="AF76" s="20" t="n"/>
+      <c r="AF76" s="21" t="n"/>
       <c r="AG76" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6675,7 +6855,7 @@
         <v>25</v>
       </c>
       <c r="AM76" s="7" t="n"/>
-      <c r="AN76" s="18" t="n"/>
+      <c r="AN76" s="19" t="n"/>
       <c r="AO76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6685,7 +6865,7 @@
         <v>25</v>
       </c>
       <c r="AQ76" s="12" t="n"/>
-      <c r="AR76" s="20" t="n"/>
+      <c r="AR76" s="21" t="n"/>
       <c r="AS76" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6695,98 +6875,102 @@
         <v>25</v>
       </c>
       <c r="AU76" s="12" t="n"/>
-      <c r="AV76" s="18" t="n"/>
+      <c r="AV76" s="19" t="n"/>
     </row>
     <row r="77" ht="20.1" customHeight="1">
-      <c r="A77" s="21" t="n"/>
-      <c r="C77" s="22" t="n"/>
-      <c r="D77" s="23" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="G77" s="24" t="n"/>
-      <c r="H77" s="23" t="n"/>
-      <c r="I77" s="21" t="n"/>
-      <c r="K77" s="22" t="n"/>
-      <c r="L77" s="26" t="n"/>
-      <c r="M77" s="21" t="n"/>
-      <c r="O77" s="24" t="n"/>
-      <c r="P77" s="23" t="n"/>
-      <c r="Q77" s="21" t="n"/>
-      <c r="S77" s="22" t="n"/>
-      <c r="T77" s="26" t="n"/>
-      <c r="U77" s="21" t="n"/>
-      <c r="W77" s="24" t="n"/>
-      <c r="X77" s="23" t="n"/>
-      <c r="Y77" s="21" t="n"/>
-      <c r="AA77" s="22" t="n"/>
-      <c r="AB77" s="25" t="n"/>
-      <c r="AC77" s="21" t="n"/>
-      <c r="AE77" s="24" t="n"/>
-      <c r="AF77" s="27" t="n"/>
-      <c r="AG77" s="21" t="n"/>
-      <c r="AI77" s="22" t="n"/>
-      <c r="AJ77" s="23" t="n"/>
-      <c r="AK77" s="21" t="n"/>
-      <c r="AM77" s="22" t="n"/>
-      <c r="AN77" s="26" t="n"/>
-      <c r="AO77" s="21" t="n"/>
-      <c r="AQ77" s="24" t="n"/>
-      <c r="AR77" s="27" t="n"/>
-      <c r="AS77" s="21" t="n"/>
-      <c r="AU77" s="24" t="n"/>
-      <c r="AV77" s="26" t="n"/>
+      <c r="A77" s="22" t="n"/>
+      <c r="C77" s="23" t="n"/>
+      <c r="D77" s="24" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="G77" s="25" t="n"/>
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="22" t="n"/>
+      <c r="K77" s="23" t="n"/>
+      <c r="L77" s="27" t="n"/>
+      <c r="M77" s="22" t="n"/>
+      <c r="O77" s="25" t="n"/>
+      <c r="P77" s="24" t="n"/>
+      <c r="Q77" s="22" t="n"/>
+      <c r="S77" s="23" t="n"/>
+      <c r="T77" s="27" t="n"/>
+      <c r="U77" s="22" t="n"/>
+      <c r="W77" s="25" t="n"/>
+      <c r="X77" s="24" t="n"/>
+      <c r="Y77" s="22" t="n"/>
+      <c r="AA77" s="23" t="n"/>
+      <c r="AB77" s="26" t="n"/>
+      <c r="AC77" s="22" t="n"/>
+      <c r="AE77" s="25" t="n"/>
+      <c r="AF77" s="28" t="n"/>
+      <c r="AG77" s="22" t="n"/>
+      <c r="AI77" s="23" t="n"/>
+      <c r="AJ77" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AK77" s="22" t="n"/>
+      <c r="AM77" s="23" t="n"/>
+      <c r="AN77" s="27" t="n"/>
+      <c r="AO77" s="22" t="n"/>
+      <c r="AQ77" s="25" t="n"/>
+      <c r="AR77" s="28" t="n"/>
+      <c r="AS77" s="22" t="n"/>
+      <c r="AU77" s="25" t="n"/>
+      <c r="AV77" s="27" t="n"/>
     </row>
     <row r="78" ht="20.1" customHeight="1">
-      <c r="A78" s="28" t="n"/>
-      <c r="B78" s="29" t="n"/>
-      <c r="C78" s="30" t="n"/>
-      <c r="D78" s="23" t="n"/>
-      <c r="E78" s="28" t="n"/>
-      <c r="F78" s="29" t="n"/>
-      <c r="G78" s="31" t="n"/>
-      <c r="H78" s="23" t="n"/>
-      <c r="I78" s="28" t="n"/>
-      <c r="J78" s="29" t="n"/>
-      <c r="K78" s="30" t="n"/>
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="30" t="n"/>
+      <c r="C78" s="31" t="n"/>
+      <c r="D78" s="24" t="n"/>
+      <c r="E78" s="29" t="n"/>
+      <c r="F78" s="30" t="n"/>
+      <c r="G78" s="32" t="n"/>
+      <c r="H78" s="24" t="n"/>
+      <c r="I78" s="29" t="n"/>
+      <c r="J78" s="30" t="n"/>
+      <c r="K78" s="31" t="n"/>
       <c r="L78" s="33" t="n"/>
-      <c r="M78" s="28" t="n"/>
-      <c r="N78" s="29" t="n"/>
-      <c r="O78" s="31" t="n"/>
-      <c r="P78" s="25" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="29" t="n"/>
-      <c r="S78" s="30" t="n"/>
+      <c r="M78" s="29" t="n"/>
+      <c r="N78" s="30" t="n"/>
+      <c r="O78" s="32" t="n"/>
+      <c r="P78" s="26" t="n"/>
+      <c r="Q78" s="29" t="n"/>
+      <c r="R78" s="30" t="n"/>
+      <c r="S78" s="31" t="n"/>
       <c r="T78" s="33" t="n"/>
-      <c r="U78" s="28" t="n"/>
-      <c r="V78" s="29" t="n"/>
-      <c r="W78" s="31" t="n"/>
-      <c r="X78" s="23" t="n"/>
-      <c r="Y78" s="28" t="n"/>
-      <c r="Z78" s="29" t="n"/>
-      <c r="AA78" s="30" t="n"/>
-      <c r="AB78" s="51" t="inlineStr">
+      <c r="U78" s="29" t="n"/>
+      <c r="V78" s="30" t="n"/>
+      <c r="W78" s="32" t="n"/>
+      <c r="X78" s="24" t="n"/>
+      <c r="Y78" s="29" t="n"/>
+      <c r="Z78" s="30" t="n"/>
+      <c r="AA78" s="31" t="n"/>
+      <c r="AB78" s="49" t="inlineStr">
         <is>
           <t>Jeudi saint</t>
         </is>
       </c>
-      <c r="AC78" s="28" t="n"/>
-      <c r="AD78" s="29" t="n"/>
-      <c r="AE78" s="31" t="n"/>
-      <c r="AF78" s="35" t="n"/>
-      <c r="AG78" s="28" t="n"/>
-      <c r="AH78" s="29" t="n"/>
-      <c r="AI78" s="30" t="n"/>
-      <c r="AJ78" s="25" t="n"/>
-      <c r="AK78" s="28" t="n"/>
-      <c r="AL78" s="29" t="n"/>
-      <c r="AM78" s="30" t="n"/>
+      <c r="AC78" s="29" t="n"/>
+      <c r="AD78" s="30" t="n"/>
+      <c r="AE78" s="32" t="n"/>
+      <c r="AF78" s="34" t="n"/>
+      <c r="AG78" s="29" t="n"/>
+      <c r="AH78" s="30" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="33" t="n"/>
+      <c r="AK78" s="29" t="n"/>
+      <c r="AL78" s="30" t="n"/>
+      <c r="AM78" s="31" t="n"/>
       <c r="AN78" s="33" t="n"/>
-      <c r="AO78" s="28" t="n"/>
-      <c r="AP78" s="29" t="n"/>
-      <c r="AQ78" s="31" t="n"/>
-      <c r="AR78" s="35" t="n"/>
-      <c r="AS78" s="28" t="n"/>
-      <c r="AT78" s="29" t="n"/>
-      <c r="AU78" s="31" t="n"/>
+      <c r="AO78" s="29" t="n"/>
+      <c r="AP78" s="30" t="n"/>
+      <c r="AQ78" s="32" t="n"/>
+      <c r="AR78" s="34" t="n"/>
+      <c r="AS78" s="29" t="n"/>
+      <c r="AT78" s="30" t="n"/>
+      <c r="AU78" s="32" t="n"/>
       <c r="AV78" s="33" t="n"/>
     </row>
     <row r="79" ht="20.1" customHeight="1">
@@ -6799,7 +6983,7 @@
         <v>26</v>
       </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="23" t="n"/>
+      <c r="D79" s="24" t="n"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6809,7 +6993,7 @@
         <v>26</v>
       </c>
       <c r="G79" s="12" t="n"/>
-      <c r="H79" s="23" t="n"/>
+      <c r="H79" s="24" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6819,7 +7003,7 @@
         <v>26</v>
       </c>
       <c r="K79" s="7" t="n"/>
-      <c r="L79" s="18" t="n"/>
+      <c r="L79" s="19" t="n"/>
       <c r="M79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6829,7 +7013,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="18" t="n"/>
+      <c r="P79" s="19" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6853,7 +7037,7 @@
         <v>26</v>
       </c>
       <c r="W79" s="12" t="n"/>
-      <c r="X79" s="23" t="n"/>
+      <c r="X79" s="24" t="n"/>
       <c r="Y79" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -6863,7 +7047,7 @@
         <v>26</v>
       </c>
       <c r="AA79" s="7" t="n"/>
-      <c r="AB79" s="51" t="inlineStr">
+      <c r="AB79" s="49" t="inlineStr">
         <is>
           <t>Vendredi saint</t>
         </is>
@@ -6877,7 +7061,7 @@
         <v>26</v>
       </c>
       <c r="AE79" s="12" t="n"/>
-      <c r="AF79" s="18" t="n"/>
+      <c r="AF79" s="19" t="n"/>
       <c r="AG79" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6887,7 +7071,7 @@
         <v>26</v>
       </c>
       <c r="AI79" s="7" t="n"/>
-      <c r="AJ79" s="18" t="n"/>
+      <c r="AJ79" s="19" t="n"/>
       <c r="AK79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6897,7 +7081,7 @@
         <v>26</v>
       </c>
       <c r="AM79" s="7" t="n"/>
-      <c r="AN79" s="18" t="n"/>
+      <c r="AN79" s="19" t="n"/>
       <c r="AO79" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6907,7 +7091,7 @@
         <v>26</v>
       </c>
       <c r="AQ79" s="12" t="n"/>
-      <c r="AR79" s="18" t="n"/>
+      <c r="AR79" s="19" t="n"/>
       <c r="AS79" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6917,98 +7101,102 @@
         <v>26</v>
       </c>
       <c r="AU79" s="12" t="n"/>
-      <c r="AV79" s="18" t="n"/>
+      <c r="AV79" s="19" t="n"/>
     </row>
     <row r="80" ht="20.1" customHeight="1">
-      <c r="A80" s="21" t="n"/>
-      <c r="C80" s="22" t="n"/>
-      <c r="D80" s="25" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="G80" s="24" t="n"/>
-      <c r="H80" s="23" t="n"/>
-      <c r="I80" s="21" t="n"/>
-      <c r="K80" s="22" t="n"/>
-      <c r="L80" s="26" t="n"/>
-      <c r="M80" s="21" t="n"/>
-      <c r="O80" s="24" t="n"/>
-      <c r="P80" s="26" t="n"/>
-      <c r="Q80" s="21" t="n"/>
-      <c r="S80" s="22" t="n"/>
-      <c r="T80" s="23" t="n"/>
-      <c r="U80" s="21" t="n"/>
-      <c r="W80" s="24" t="n"/>
-      <c r="X80" s="23" t="n"/>
-      <c r="Y80" s="21" t="n"/>
-      <c r="AA80" s="22" t="n"/>
-      <c r="AB80" s="49" t="n"/>
-      <c r="AC80" s="21" t="n"/>
-      <c r="AE80" s="24" t="n"/>
-      <c r="AF80" s="26" t="n"/>
-      <c r="AG80" s="21" t="n"/>
-      <c r="AI80" s="22" t="n"/>
-      <c r="AJ80" s="26" t="n"/>
-      <c r="AK80" s="21" t="n"/>
-      <c r="AM80" s="22" t="n"/>
-      <c r="AN80" s="26" t="n"/>
-      <c r="AO80" s="21" t="n"/>
-      <c r="AQ80" s="24" t="n"/>
-      <c r="AR80" s="26" t="n"/>
-      <c r="AS80" s="21" t="n"/>
-      <c r="AU80" s="24" t="n"/>
-      <c r="AV80" s="26" t="n"/>
+      <c r="A80" s="22" t="n"/>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="26" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="G80" s="25" t="n"/>
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="22" t="n"/>
+      <c r="K80" s="23" t="n"/>
+      <c r="L80" s="27" t="n"/>
+      <c r="M80" s="22" t="n"/>
+      <c r="O80" s="25" t="n"/>
+      <c r="P80" s="27" t="n"/>
+      <c r="Q80" s="22" t="n"/>
+      <c r="S80" s="23" t="n"/>
+      <c r="T80" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="U80" s="22" t="n"/>
+      <c r="W80" s="25" t="n"/>
+      <c r="X80" s="24" t="n"/>
+      <c r="Y80" s="22" t="n"/>
+      <c r="AA80" s="23" t="n"/>
+      <c r="AB80" s="47" t="n"/>
+      <c r="AC80" s="22" t="n"/>
+      <c r="AE80" s="25" t="n"/>
+      <c r="AF80" s="27" t="n"/>
+      <c r="AG80" s="22" t="n"/>
+      <c r="AI80" s="23" t="n"/>
+      <c r="AJ80" s="27" t="n"/>
+      <c r="AK80" s="22" t="n"/>
+      <c r="AM80" s="23" t="n"/>
+      <c r="AN80" s="27" t="n"/>
+      <c r="AO80" s="22" t="n"/>
+      <c r="AQ80" s="25" t="n"/>
+      <c r="AR80" s="27" t="n"/>
+      <c r="AS80" s="22" t="n"/>
+      <c r="AU80" s="25" t="n"/>
+      <c r="AV80" s="27" t="n"/>
     </row>
     <row r="81" ht="20.1" customHeight="1">
-      <c r="A81" s="28" t="n"/>
-      <c r="B81" s="29" t="n"/>
-      <c r="C81" s="30" t="n"/>
-      <c r="D81" s="42" t="inlineStr">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="30" t="n"/>
+      <c r="C81" s="31" t="n"/>
+      <c r="D81" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="E81" s="28" t="n"/>
-      <c r="F81" s="29" t="n"/>
-      <c r="G81" s="31" t="n"/>
-      <c r="H81" s="23" t="n"/>
-      <c r="I81" s="28" t="n"/>
-      <c r="J81" s="29" t="n"/>
-      <c r="K81" s="30" t="n"/>
+      <c r="E81" s="29" t="n"/>
+      <c r="F81" s="30" t="n"/>
+      <c r="G81" s="32" t="n"/>
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="29" t="n"/>
+      <c r="J81" s="30" t="n"/>
+      <c r="K81" s="31" t="n"/>
       <c r="L81" s="33" t="n"/>
-      <c r="M81" s="28" t="n"/>
-      <c r="N81" s="29" t="n"/>
-      <c r="O81" s="31" t="n"/>
+      <c r="M81" s="29" t="n"/>
+      <c r="N81" s="30" t="n"/>
+      <c r="O81" s="32" t="n"/>
       <c r="P81" s="33" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="29" t="n"/>
-      <c r="S81" s="30" t="n"/>
-      <c r="T81" s="25" t="n"/>
-      <c r="U81" s="28" t="n"/>
-      <c r="V81" s="29" t="n"/>
-      <c r="W81" s="31" t="n"/>
-      <c r="X81" s="25" t="n"/>
-      <c r="Y81" s="28" t="n"/>
-      <c r="Z81" s="29" t="n"/>
-      <c r="AA81" s="30" t="n"/>
-      <c r="AB81" s="23" t="n"/>
-      <c r="AC81" s="28" t="n"/>
-      <c r="AD81" s="29" t="n"/>
-      <c r="AE81" s="31" t="n"/>
+      <c r="Q81" s="29" t="n"/>
+      <c r="R81" s="30" t="n"/>
+      <c r="S81" s="31" t="n"/>
+      <c r="T81" s="33" t="n"/>
+      <c r="U81" s="29" t="n"/>
+      <c r="V81" s="30" t="n"/>
+      <c r="W81" s="32" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="29" t="n"/>
+      <c r="Z81" s="30" t="n"/>
+      <c r="AA81" s="31" t="n"/>
+      <c r="AB81" s="24" t="n"/>
+      <c r="AC81" s="29" t="n"/>
+      <c r="AD81" s="30" t="n"/>
+      <c r="AE81" s="32" t="n"/>
       <c r="AF81" s="33" t="n"/>
-      <c r="AG81" s="28" t="n"/>
-      <c r="AH81" s="29" t="n"/>
-      <c r="AI81" s="30" t="n"/>
+      <c r="AG81" s="29" t="n"/>
+      <c r="AH81" s="30" t="n"/>
+      <c r="AI81" s="31" t="n"/>
       <c r="AJ81" s="33" t="n"/>
-      <c r="AK81" s="28" t="n"/>
-      <c r="AL81" s="29" t="n"/>
-      <c r="AM81" s="30" t="n"/>
+      <c r="AK81" s="29" t="n"/>
+      <c r="AL81" s="30" t="n"/>
+      <c r="AM81" s="31" t="n"/>
       <c r="AN81" s="33" t="n"/>
-      <c r="AO81" s="28" t="n"/>
-      <c r="AP81" s="29" t="n"/>
-      <c r="AQ81" s="31" t="n"/>
+      <c r="AO81" s="29" t="n"/>
+      <c r="AP81" s="30" t="n"/>
+      <c r="AQ81" s="32" t="n"/>
       <c r="AR81" s="33" t="n"/>
-      <c r="AS81" s="28" t="n"/>
-      <c r="AT81" s="29" t="n"/>
-      <c r="AU81" s="31" t="n"/>
+      <c r="AS81" s="29" t="n"/>
+      <c r="AT81" s="30" t="n"/>
+      <c r="AU81" s="32" t="n"/>
       <c r="AV81" s="33" t="n"/>
     </row>
     <row r="82" ht="20.1" customHeight="1">
@@ -7020,8 +7208,8 @@
       <c r="B82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C82" s="43" t="n"/>
-      <c r="D82" s="42" t="inlineStr">
+      <c r="C82" s="41" t="n"/>
+      <c r="D82" s="40" t="inlineStr">
         <is>
           <t>Baptême</t>
         </is>
@@ -7035,7 +7223,7 @@
         <v>27</v>
       </c>
       <c r="G82" s="12" t="n"/>
-      <c r="H82" s="23" t="n"/>
+      <c r="H82" s="24" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7045,7 +7233,7 @@
         <v>27</v>
       </c>
       <c r="K82" s="7" t="n"/>
-      <c r="L82" s="36" t="inlineStr">
+      <c r="L82" s="35" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -7059,7 +7247,7 @@
         <v>27</v>
       </c>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="20" t="n"/>
+      <c r="P82" s="21" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7069,7 +7257,7 @@
         <v>27</v>
       </c>
       <c r="S82" s="7" t="n"/>
-      <c r="T82" s="18" t="n"/>
+      <c r="T82" s="19" t="n"/>
       <c r="U82" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -7079,7 +7267,7 @@
         <v>27</v>
       </c>
       <c r="W82" s="12" t="n"/>
-      <c r="X82" s="18" t="n"/>
+      <c r="X82" s="19" t="n"/>
       <c r="Y82" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -7089,7 +7277,7 @@
         <v>27</v>
       </c>
       <c r="AA82" s="7" t="n"/>
-      <c r="AB82" s="23" t="n"/>
+      <c r="AB82" s="24" t="n"/>
       <c r="AC82" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7099,7 +7287,11 @@
         <v>27</v>
       </c>
       <c r="AE82" s="12" t="n"/>
-      <c r="AF82" s="18" t="n"/>
+      <c r="AF82" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="AG82" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7109,7 +7301,7 @@
         <v>27</v>
       </c>
       <c r="AI82" s="7" t="n"/>
-      <c r="AJ82" s="36" t="inlineStr">
+      <c r="AJ82" s="35" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -7122,8 +7314,12 @@
       <c r="AL82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="AM82" s="43" t="n"/>
-      <c r="AN82" s="20" t="n"/>
+      <c r="AM82" s="41" t="n"/>
+      <c r="AN82" s="18" t="inlineStr">
+        <is>
+          <t>Fête de départ de la paroisse</t>
+        </is>
+      </c>
       <c r="AO82" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7133,7 +7329,7 @@
         <v>27</v>
       </c>
       <c r="AQ82" s="12" t="n"/>
-      <c r="AR82" s="18" t="n"/>
+      <c r="AR82" s="19" t="n"/>
       <c r="AS82" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7143,98 +7339,102 @@
         <v>27</v>
       </c>
       <c r="AU82" s="12" t="n"/>
-      <c r="AV82" s="18" t="n"/>
+      <c r="AV82" s="19" t="n"/>
     </row>
     <row r="83" ht="20.1" customHeight="1">
-      <c r="A83" s="21" t="n"/>
-      <c r="C83" s="46" t="n"/>
-      <c r="D83" s="38" t="n"/>
-      <c r="E83" s="21" t="n"/>
-      <c r="G83" s="24" t="n"/>
-      <c r="H83" s="23" t="n"/>
-      <c r="I83" s="21" t="n"/>
-      <c r="K83" s="22" t="n"/>
-      <c r="L83" s="23" t="n"/>
-      <c r="M83" s="21" t="n"/>
-      <c r="O83" s="24" t="n"/>
-      <c r="P83" s="27" t="n"/>
-      <c r="Q83" s="21" t="n"/>
-      <c r="S83" s="22" t="n"/>
-      <c r="T83" s="26" t="n"/>
-      <c r="U83" s="21" t="n"/>
-      <c r="W83" s="24" t="n"/>
-      <c r="X83" s="26" t="n"/>
-      <c r="Y83" s="21" t="n"/>
-      <c r="AA83" s="22" t="n"/>
-      <c r="AB83" s="25" t="n"/>
-      <c r="AC83" s="21" t="n"/>
-      <c r="AE83" s="24" t="n"/>
-      <c r="AF83" s="26" t="n"/>
-      <c r="AG83" s="21" t="n"/>
-      <c r="AI83" s="22" t="n"/>
-      <c r="AJ83" s="23" t="n"/>
-      <c r="AK83" s="21" t="n"/>
-      <c r="AM83" s="46" t="n"/>
-      <c r="AN83" s="27" t="n"/>
-      <c r="AO83" s="21" t="n"/>
-      <c r="AQ83" s="24" t="n"/>
-      <c r="AR83" s="26" t="n"/>
-      <c r="AS83" s="21" t="n"/>
-      <c r="AU83" s="24" t="n"/>
-      <c r="AV83" s="26" t="n"/>
+      <c r="A83" s="22" t="n"/>
+      <c r="C83" s="44" t="n"/>
+      <c r="D83" s="50" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="G83" s="25" t="n"/>
+      <c r="H83" s="26" t="n"/>
+      <c r="I83" s="22" t="n"/>
+      <c r="K83" s="23" t="n"/>
+      <c r="L83" s="24" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="O83" s="25" t="n"/>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="22" t="n"/>
+      <c r="S83" s="23" t="n"/>
+      <c r="T83" s="27" t="n"/>
+      <c r="U83" s="22" t="n"/>
+      <c r="W83" s="25" t="n"/>
+      <c r="X83" s="27" t="n"/>
+      <c r="Y83" s="22" t="n"/>
+      <c r="AA83" s="23" t="n"/>
+      <c r="AB83" s="26" t="n"/>
+      <c r="AC83" s="22" t="n"/>
+      <c r="AE83" s="25" t="n"/>
+      <c r="AF83" s="24" t="n"/>
+      <c r="AG83" s="22" t="n"/>
+      <c r="AI83" s="23" t="n"/>
+      <c r="AJ83" s="24" t="n"/>
+      <c r="AK83" s="22" t="n"/>
+      <c r="AM83" s="44" t="n"/>
+      <c r="AN83" s="24" t="n"/>
+      <c r="AO83" s="22" t="n"/>
+      <c r="AQ83" s="25" t="n"/>
+      <c r="AR83" s="27" t="n"/>
+      <c r="AS83" s="22" t="n"/>
+      <c r="AU83" s="25" t="n"/>
+      <c r="AV83" s="27" t="n"/>
     </row>
     <row r="84" ht="20.1" customHeight="1">
-      <c r="A84" s="28" t="n"/>
-      <c r="B84" s="29" t="n"/>
-      <c r="C84" s="47" t="n"/>
-      <c r="D84" s="23" t="n"/>
-      <c r="E84" s="28" t="n"/>
-      <c r="F84" s="29" t="n"/>
-      <c r="G84" s="31" t="n"/>
-      <c r="H84" s="23" t="n"/>
-      <c r="I84" s="28" t="n"/>
-      <c r="J84" s="29" t="n"/>
-      <c r="K84" s="30" t="n"/>
-      <c r="L84" s="25" t="n"/>
-      <c r="M84" s="28" t="n"/>
-      <c r="N84" s="29" t="n"/>
-      <c r="O84" s="31" t="n"/>
-      <c r="P84" s="35" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="29" t="n"/>
-      <c r="S84" s="30" t="n"/>
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="30" t="n"/>
+      <c r="C84" s="45" t="n"/>
+      <c r="D84" s="24" t="n"/>
+      <c r="E84" s="29" t="n"/>
+      <c r="F84" s="30" t="n"/>
+      <c r="G84" s="32" t="n"/>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="I84" s="29" t="n"/>
+      <c r="J84" s="30" t="n"/>
+      <c r="K84" s="31" t="n"/>
+      <c r="L84" s="26" t="n"/>
+      <c r="M84" s="29" t="n"/>
+      <c r="N84" s="30" t="n"/>
+      <c r="O84" s="32" t="n"/>
+      <c r="P84" s="34" t="n"/>
+      <c r="Q84" s="29" t="n"/>
+      <c r="R84" s="30" t="n"/>
+      <c r="S84" s="31" t="n"/>
       <c r="T84" s="33" t="n"/>
-      <c r="U84" s="28" t="n"/>
-      <c r="V84" s="29" t="n"/>
-      <c r="W84" s="31" t="n"/>
+      <c r="U84" s="29" t="n"/>
+      <c r="V84" s="30" t="n"/>
+      <c r="W84" s="32" t="n"/>
       <c r="X84" s="33" t="n"/>
-      <c r="Y84" s="28" t="n"/>
-      <c r="Z84" s="29" t="n"/>
-      <c r="AA84" s="30" t="n"/>
-      <c r="AB84" s="37" t="inlineStr">
+      <c r="Y84" s="29" t="n"/>
+      <c r="Z84" s="30" t="n"/>
+      <c r="AA84" s="31" t="n"/>
+      <c r="AB84" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
-      <c r="AC84" s="28" t="n"/>
-      <c r="AD84" s="29" t="n"/>
-      <c r="AE84" s="31" t="n"/>
-      <c r="AF84" s="33" t="n"/>
-      <c r="AG84" s="28" t="n"/>
-      <c r="AH84" s="29" t="n"/>
-      <c r="AI84" s="30" t="n"/>
-      <c r="AJ84" s="25" t="n"/>
-      <c r="AK84" s="28" t="n"/>
-      <c r="AL84" s="29" t="n"/>
-      <c r="AM84" s="47" t="n"/>
-      <c r="AN84" s="35" t="n"/>
-      <c r="AO84" s="28" t="n"/>
-      <c r="AP84" s="29" t="n"/>
-      <c r="AQ84" s="31" t="n"/>
+      <c r="AC84" s="29" t="n"/>
+      <c r="AD84" s="30" t="n"/>
+      <c r="AE84" s="32" t="n"/>
+      <c r="AF84" s="26" t="n"/>
+      <c r="AG84" s="29" t="n"/>
+      <c r="AH84" s="30" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="26" t="n"/>
+      <c r="AK84" s="29" t="n"/>
+      <c r="AL84" s="30" t="n"/>
+      <c r="AM84" s="45" t="n"/>
+      <c r="AN84" s="26" t="n"/>
+      <c r="AO84" s="29" t="n"/>
+      <c r="AP84" s="30" t="n"/>
+      <c r="AQ84" s="32" t="n"/>
       <c r="AR84" s="33" t="n"/>
-      <c r="AS84" s="28" t="n"/>
-      <c r="AT84" s="29" t="n"/>
-      <c r="AU84" s="31" t="n"/>
+      <c r="AS84" s="29" t="n"/>
+      <c r="AT84" s="30" t="n"/>
+      <c r="AU84" s="32" t="n"/>
       <c r="AV84" s="33" t="n"/>
     </row>
     <row r="85" ht="20.1" customHeight="1">
@@ -7247,7 +7447,7 @@
         <v>28</v>
       </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="23" t="n"/>
+      <c r="D85" s="24" t="n"/>
       <c r="E85" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7257,7 +7457,11 @@
         <v>28</v>
       </c>
       <c r="G85" s="12" t="n"/>
-      <c r="H85" s="23" t="n"/>
+      <c r="H85" s="56" t="inlineStr">
+        <is>
+          <t>Père Pascal en Côte d'Ivoire</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7267,7 +7471,11 @@
         <v>28</v>
       </c>
       <c r="K85" s="7" t="n"/>
-      <c r="L85" s="18" t="n"/>
+      <c r="L85" s="18" t="inlineStr">
+        <is>
+          <t>CMP avec Chartres 2040</t>
+        </is>
+      </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7277,7 +7485,7 @@
         <v>28</v>
       </c>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="18" t="n"/>
+      <c r="P85" s="19" t="n"/>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7287,7 +7495,7 @@
         <v>28</v>
       </c>
       <c r="S85" s="7" t="n"/>
-      <c r="T85" s="50" t="inlineStr">
+      <c r="T85" s="48" t="inlineStr">
         <is>
           <t>Prépa Mariage 1</t>
         </is>
@@ -7301,7 +7509,7 @@
         <v>28</v>
       </c>
       <c r="W85" s="12" t="n"/>
-      <c r="X85" s="51" t="inlineStr">
+      <c r="X85" s="49" t="inlineStr">
         <is>
           <t>3e dim. de Carême</t>
         </is>
@@ -7314,8 +7522,8 @@
       <c r="Z85" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AA85" s="43" t="n"/>
-      <c r="AB85" s="17" t="inlineStr">
+      <c r="AA85" s="41" t="n"/>
+      <c r="AB85" s="20" t="inlineStr">
         <is>
           <t>Pâques</t>
         </is>
@@ -7329,7 +7537,7 @@
         <v>28</v>
       </c>
       <c r="AE85" s="12" t="n"/>
-      <c r="AF85" s="18" t="n"/>
+      <c r="AF85" s="19" t="n"/>
       <c r="AG85" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7339,7 +7547,7 @@
         <v>28</v>
       </c>
       <c r="AI85" s="7" t="n"/>
-      <c r="AJ85" s="18" t="n"/>
+      <c r="AJ85" s="19" t="n"/>
       <c r="AK85" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7349,7 +7557,7 @@
         <v>28</v>
       </c>
       <c r="AM85" s="7" t="n"/>
-      <c r="AN85" s="18" t="n"/>
+      <c r="AN85" s="19" t="n"/>
       <c r="AO85" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7359,7 +7567,7 @@
         <v>28</v>
       </c>
       <c r="AQ85" s="12" t="n"/>
-      <c r="AR85" s="18" t="n"/>
+      <c r="AR85" s="19" t="n"/>
       <c r="AS85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7369,98 +7577,98 @@
         <v>28</v>
       </c>
       <c r="AU85" s="12" t="n"/>
-      <c r="AV85" s="18" t="n"/>
+      <c r="AV85" s="19" t="n"/>
     </row>
     <row r="86" ht="20.1" customHeight="1">
-      <c r="A86" s="21" t="n"/>
-      <c r="C86" s="22" t="n"/>
-      <c r="D86" s="23" t="n"/>
-      <c r="E86" s="21" t="n"/>
-      <c r="G86" s="24" t="n"/>
-      <c r="H86" s="23" t="n"/>
-      <c r="I86" s="21" t="n"/>
-      <c r="K86" s="22" t="n"/>
-      <c r="L86" s="26" t="n"/>
-      <c r="M86" s="21" t="n"/>
-      <c r="O86" s="24" t="n"/>
-      <c r="P86" s="26" t="n"/>
-      <c r="Q86" s="21" t="n"/>
-      <c r="S86" s="22" t="n"/>
-      <c r="T86" s="23" t="n"/>
-      <c r="U86" s="21" t="n"/>
-      <c r="W86" s="24" t="n"/>
-      <c r="X86" s="37" t="inlineStr">
+      <c r="A86" s="22" t="n"/>
+      <c r="C86" s="23" t="n"/>
+      <c r="D86" s="24" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="G86" s="25" t="n"/>
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="K86" s="23" t="n"/>
+      <c r="L86" s="24" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="O86" s="25" t="n"/>
+      <c r="P86" s="27" t="n"/>
+      <c r="Q86" s="22" t="n"/>
+      <c r="S86" s="23" t="n"/>
+      <c r="T86" s="24" t="n"/>
+      <c r="U86" s="22" t="n"/>
+      <c r="W86" s="25" t="n"/>
+      <c r="X86" s="36" t="inlineStr">
         <is>
           <t>1er scrutin</t>
         </is>
       </c>
-      <c r="Y86" s="21" t="n"/>
-      <c r="AA86" s="46" t="n"/>
-      <c r="AB86" s="23" t="n"/>
-      <c r="AC86" s="21" t="n"/>
-      <c r="AE86" s="24" t="n"/>
-      <c r="AF86" s="26" t="n"/>
-      <c r="AG86" s="21" t="n"/>
-      <c r="AI86" s="22" t="n"/>
-      <c r="AJ86" s="26" t="n"/>
-      <c r="AK86" s="21" t="n"/>
-      <c r="AM86" s="22" t="n"/>
-      <c r="AN86" s="26" t="n"/>
-      <c r="AO86" s="21" t="n"/>
-      <c r="AQ86" s="24" t="n"/>
-      <c r="AR86" s="26" t="n"/>
-      <c r="AS86" s="21" t="n"/>
-      <c r="AU86" s="24" t="n"/>
-      <c r="AV86" s="26" t="n"/>
+      <c r="Y86" s="22" t="n"/>
+      <c r="AA86" s="44" t="n"/>
+      <c r="AB86" s="24" t="n"/>
+      <c r="AC86" s="22" t="n"/>
+      <c r="AE86" s="25" t="n"/>
+      <c r="AF86" s="27" t="n"/>
+      <c r="AG86" s="22" t="n"/>
+      <c r="AI86" s="23" t="n"/>
+      <c r="AJ86" s="27" t="n"/>
+      <c r="AK86" s="22" t="n"/>
+      <c r="AM86" s="23" t="n"/>
+      <c r="AN86" s="27" t="n"/>
+      <c r="AO86" s="22" t="n"/>
+      <c r="AQ86" s="25" t="n"/>
+      <c r="AR86" s="27" t="n"/>
+      <c r="AS86" s="22" t="n"/>
+      <c r="AU86" s="25" t="n"/>
+      <c r="AV86" s="27" t="n"/>
     </row>
     <row r="87" ht="20.1" customHeight="1">
-      <c r="A87" s="28" t="n"/>
-      <c r="B87" s="29" t="n"/>
-      <c r="C87" s="30" t="n"/>
-      <c r="D87" s="25" t="n"/>
-      <c r="E87" s="28" t="n"/>
-      <c r="F87" s="29" t="n"/>
-      <c r="G87" s="31" t="n"/>
-      <c r="H87" s="23" t="n"/>
-      <c r="I87" s="28" t="n"/>
-      <c r="J87" s="29" t="n"/>
-      <c r="K87" s="30" t="n"/>
-      <c r="L87" s="33" t="n"/>
-      <c r="M87" s="28" t="n"/>
-      <c r="N87" s="29" t="n"/>
-      <c r="O87" s="31" t="n"/>
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="n"/>
+      <c r="C87" s="31" t="n"/>
+      <c r="D87" s="26" t="n"/>
+      <c r="E87" s="29" t="n"/>
+      <c r="F87" s="30" t="n"/>
+      <c r="G87" s="32" t="n"/>
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="29" t="n"/>
+      <c r="J87" s="30" t="n"/>
+      <c r="K87" s="31" t="n"/>
+      <c r="L87" s="26" t="n"/>
+      <c r="M87" s="29" t="n"/>
+      <c r="N87" s="30" t="n"/>
+      <c r="O87" s="32" t="n"/>
       <c r="P87" s="33" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="29" t="n"/>
-      <c r="S87" s="30" t="n"/>
-      <c r="T87" s="25" t="n"/>
-      <c r="U87" s="28" t="n"/>
-      <c r="V87" s="29" t="n"/>
-      <c r="W87" s="31" t="n"/>
-      <c r="X87" s="35" t="n"/>
-      <c r="Y87" s="28" t="n"/>
-      <c r="Z87" s="29" t="n"/>
-      <c r="AA87" s="47" t="n"/>
-      <c r="AB87" s="25" t="n"/>
-      <c r="AC87" s="28" t="n"/>
-      <c r="AD87" s="29" t="n"/>
-      <c r="AE87" s="31" t="n"/>
+      <c r="Q87" s="29" t="n"/>
+      <c r="R87" s="30" t="n"/>
+      <c r="S87" s="31" t="n"/>
+      <c r="T87" s="26" t="n"/>
+      <c r="U87" s="29" t="n"/>
+      <c r="V87" s="30" t="n"/>
+      <c r="W87" s="32" t="n"/>
+      <c r="X87" s="34" t="n"/>
+      <c r="Y87" s="29" t="n"/>
+      <c r="Z87" s="30" t="n"/>
+      <c r="AA87" s="45" t="n"/>
+      <c r="AB87" s="26" t="n"/>
+      <c r="AC87" s="29" t="n"/>
+      <c r="AD87" s="30" t="n"/>
+      <c r="AE87" s="32" t="n"/>
       <c r="AF87" s="33" t="n"/>
-      <c r="AG87" s="28" t="n"/>
-      <c r="AH87" s="29" t="n"/>
-      <c r="AI87" s="30" t="n"/>
+      <c r="AG87" s="29" t="n"/>
+      <c r="AH87" s="30" t="n"/>
+      <c r="AI87" s="31" t="n"/>
       <c r="AJ87" s="33" t="n"/>
-      <c r="AK87" s="28" t="n"/>
-      <c r="AL87" s="29" t="n"/>
-      <c r="AM87" s="30" t="n"/>
+      <c r="AK87" s="29" t="n"/>
+      <c r="AL87" s="30" t="n"/>
+      <c r="AM87" s="31" t="n"/>
       <c r="AN87" s="33" t="n"/>
-      <c r="AO87" s="28" t="n"/>
-      <c r="AP87" s="29" t="n"/>
-      <c r="AQ87" s="31" t="n"/>
+      <c r="AO87" s="29" t="n"/>
+      <c r="AP87" s="30" t="n"/>
+      <c r="AQ87" s="32" t="n"/>
       <c r="AR87" s="33" t="n"/>
-      <c r="AS87" s="28" t="n"/>
-      <c r="AT87" s="29" t="n"/>
-      <c r="AU87" s="31" t="n"/>
+      <c r="AS87" s="29" t="n"/>
+      <c r="AT87" s="30" t="n"/>
+      <c r="AU87" s="32" t="n"/>
       <c r="AV87" s="33" t="n"/>
     </row>
     <row r="88" ht="20.1" customHeight="1">
@@ -7473,7 +7681,7 @@
         <v>29</v>
       </c>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
@@ -7487,7 +7695,7 @@
         <v>29</v>
       </c>
       <c r="G88" s="12" t="n"/>
-      <c r="H88" s="23" t="n"/>
+      <c r="H88" s="24" t="n"/>
       <c r="I88" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -7496,8 +7704,8 @@
       <c r="J88" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="K88" s="43" t="n"/>
-      <c r="L88" s="49" t="inlineStr">
+      <c r="K88" s="41" t="n"/>
+      <c r="L88" s="47" t="inlineStr">
         <is>
           <t>1er dim. de l'Avent</t>
         </is>
@@ -7511,7 +7719,11 @@
         <v>29</v>
       </c>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="18" t="n"/>
+      <c r="P88" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7521,7 +7733,7 @@
         <v>29</v>
       </c>
       <c r="S88" s="7" t="n"/>
-      <c r="T88" s="18" t="n"/>
+      <c r="T88" s="19" t="n"/>
       <c r="Y88" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7531,7 +7743,7 @@
         <v>29</v>
       </c>
       <c r="AA88" s="7" t="n"/>
-      <c r="AB88" s="17" t="inlineStr">
+      <c r="AB88" s="20" t="inlineStr">
         <is>
           <t>Lundi de Pâques</t>
         </is>
@@ -7545,7 +7757,7 @@
         <v>29</v>
       </c>
       <c r="AE88" s="12" t="n"/>
-      <c r="AF88" s="18" t="n"/>
+      <c r="AF88" s="19" t="n"/>
       <c r="AG88" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7569,7 +7781,11 @@
         <v>29</v>
       </c>
       <c r="AM88" s="7" t="n"/>
-      <c r="AN88" s="18" t="n"/>
+      <c r="AN88" s="18" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
       <c r="AO88" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7579,7 +7795,7 @@
         <v>29</v>
       </c>
       <c r="AQ88" s="12" t="n"/>
-      <c r="AR88" s="18" t="n"/>
+      <c r="AR88" s="19" t="n"/>
       <c r="AS88" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7589,88 +7805,88 @@
         <v>29</v>
       </c>
       <c r="AU88" s="12" t="n"/>
-      <c r="AV88" s="20" t="n"/>
+      <c r="AV88" s="21" t="n"/>
     </row>
     <row r="89" ht="20.1" customHeight="1">
-      <c r="A89" s="21" t="n"/>
-      <c r="C89" s="22" t="n"/>
-      <c r="D89" s="23" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="G89" s="24" t="n"/>
-      <c r="H89" s="23" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="K89" s="46" t="n"/>
-      <c r="L89" s="23" t="n"/>
-      <c r="M89" s="21" t="n"/>
-      <c r="O89" s="24" t="n"/>
-      <c r="P89" s="26" t="n"/>
-      <c r="Q89" s="21" t="n"/>
-      <c r="S89" s="22" t="n"/>
-      <c r="T89" s="26" t="n"/>
-      <c r="Y89" s="21" t="n"/>
-      <c r="AA89" s="22" t="n"/>
-      <c r="AB89" s="23" t="n"/>
-      <c r="AC89" s="21" t="n"/>
-      <c r="AE89" s="24" t="n"/>
-      <c r="AF89" s="26" t="n"/>
-      <c r="AG89" s="21" t="n"/>
-      <c r="AI89" s="22" t="n"/>
-      <c r="AJ89" s="23" t="n"/>
-      <c r="AK89" s="21" t="n"/>
-      <c r="AM89" s="22" t="n"/>
-      <c r="AN89" s="26" t="n"/>
-      <c r="AO89" s="21" t="n"/>
-      <c r="AQ89" s="24" t="n"/>
-      <c r="AR89" s="26" t="n"/>
-      <c r="AS89" s="21" t="n"/>
-      <c r="AU89" s="24" t="n"/>
-      <c r="AV89" s="27" t="n"/>
+      <c r="A89" s="22" t="n"/>
+      <c r="C89" s="23" t="n"/>
+      <c r="D89" s="24" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="G89" s="25" t="n"/>
+      <c r="H89" s="24" t="n"/>
+      <c r="I89" s="22" t="n"/>
+      <c r="K89" s="44" t="n"/>
+      <c r="L89" s="24" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="O89" s="25" t="n"/>
+      <c r="P89" s="24" t="n"/>
+      <c r="Q89" s="22" t="n"/>
+      <c r="S89" s="23" t="n"/>
+      <c r="T89" s="27" t="n"/>
+      <c r="Y89" s="22" t="n"/>
+      <c r="AA89" s="23" t="n"/>
+      <c r="AB89" s="24" t="n"/>
+      <c r="AC89" s="22" t="n"/>
+      <c r="AE89" s="25" t="n"/>
+      <c r="AF89" s="27" t="n"/>
+      <c r="AG89" s="22" t="n"/>
+      <c r="AI89" s="23" t="n"/>
+      <c r="AJ89" s="24" t="n"/>
+      <c r="AK89" s="22" t="n"/>
+      <c r="AM89" s="23" t="n"/>
+      <c r="AN89" s="24" t="n"/>
+      <c r="AO89" s="22" t="n"/>
+      <c r="AQ89" s="25" t="n"/>
+      <c r="AR89" s="27" t="n"/>
+      <c r="AS89" s="22" t="n"/>
+      <c r="AU89" s="25" t="n"/>
+      <c r="AV89" s="28" t="n"/>
     </row>
     <row r="90" ht="20.1" customHeight="1">
-      <c r="A90" s="28" t="n"/>
-      <c r="B90" s="29" t="n"/>
-      <c r="C90" s="30" t="n"/>
-      <c r="D90" s="25" t="n"/>
-      <c r="E90" s="28" t="n"/>
-      <c r="F90" s="29" t="n"/>
-      <c r="G90" s="31" t="n"/>
-      <c r="H90" s="23" t="n"/>
-      <c r="I90" s="28" t="n"/>
-      <c r="J90" s="29" t="n"/>
-      <c r="K90" s="47" t="n"/>
-      <c r="L90" s="25" t="n"/>
-      <c r="M90" s="28" t="n"/>
-      <c r="N90" s="29" t="n"/>
-      <c r="O90" s="31" t="n"/>
-      <c r="P90" s="33" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="29" t="n"/>
-      <c r="S90" s="30" t="n"/>
+      <c r="A90" s="29" t="n"/>
+      <c r="B90" s="30" t="n"/>
+      <c r="C90" s="31" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="29" t="n"/>
+      <c r="F90" s="30" t="n"/>
+      <c r="G90" s="32" t="n"/>
+      <c r="H90" s="24" t="n"/>
+      <c r="I90" s="29" t="n"/>
+      <c r="J90" s="30" t="n"/>
+      <c r="K90" s="45" t="n"/>
+      <c r="L90" s="26" t="n"/>
+      <c r="M90" s="29" t="n"/>
+      <c r="N90" s="30" t="n"/>
+      <c r="O90" s="32" t="n"/>
+      <c r="P90" s="26" t="n"/>
+      <c r="Q90" s="29" t="n"/>
+      <c r="R90" s="30" t="n"/>
+      <c r="S90" s="31" t="n"/>
       <c r="T90" s="33" t="n"/>
-      <c r="Y90" s="28" t="n"/>
-      <c r="Z90" s="29" t="n"/>
-      <c r="AA90" s="30" t="n"/>
-      <c r="AB90" s="25" t="n"/>
-      <c r="AC90" s="28" t="n"/>
-      <c r="AD90" s="29" t="n"/>
-      <c r="AE90" s="31" t="n"/>
+      <c r="Y90" s="29" t="n"/>
+      <c r="Z90" s="30" t="n"/>
+      <c r="AA90" s="31" t="n"/>
+      <c r="AB90" s="26" t="n"/>
+      <c r="AC90" s="29" t="n"/>
+      <c r="AD90" s="30" t="n"/>
+      <c r="AE90" s="32" t="n"/>
       <c r="AF90" s="33" t="n"/>
-      <c r="AG90" s="28" t="n"/>
-      <c r="AH90" s="29" t="n"/>
-      <c r="AI90" s="30" t="n"/>
-      <c r="AJ90" s="25" t="n"/>
-      <c r="AK90" s="28" t="n"/>
-      <c r="AL90" s="29" t="n"/>
-      <c r="AM90" s="30" t="n"/>
-      <c r="AN90" s="33" t="n"/>
-      <c r="AO90" s="28" t="n"/>
-      <c r="AP90" s="29" t="n"/>
-      <c r="AQ90" s="31" t="n"/>
+      <c r="AG90" s="29" t="n"/>
+      <c r="AH90" s="30" t="n"/>
+      <c r="AI90" s="31" t="n"/>
+      <c r="AJ90" s="26" t="n"/>
+      <c r="AK90" s="29" t="n"/>
+      <c r="AL90" s="30" t="n"/>
+      <c r="AM90" s="31" t="n"/>
+      <c r="AN90" s="26" t="n"/>
+      <c r="AO90" s="29" t="n"/>
+      <c r="AP90" s="30" t="n"/>
+      <c r="AQ90" s="32" t="n"/>
       <c r="AR90" s="33" t="n"/>
-      <c r="AS90" s="28" t="n"/>
-      <c r="AT90" s="29" t="n"/>
-      <c r="AU90" s="31" t="n"/>
-      <c r="AV90" s="35" t="n"/>
+      <c r="AS90" s="29" t="n"/>
+      <c r="AT90" s="30" t="n"/>
+      <c r="AU90" s="32" t="n"/>
+      <c r="AV90" s="34" t="n"/>
     </row>
     <row r="91" ht="20.1" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -7682,7 +7898,7 @@
         <v>30</v>
       </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="18" t="n"/>
+      <c r="D91" s="19" t="n"/>
       <c r="E91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7692,7 +7908,7 @@
         <v>30</v>
       </c>
       <c r="G91" s="12" t="n"/>
-      <c r="H91" s="23" t="n"/>
+      <c r="H91" s="24" t="n"/>
       <c r="I91" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -7702,7 +7918,7 @@
         <v>30</v>
       </c>
       <c r="K91" s="7" t="n"/>
-      <c r="L91" s="18" t="n"/>
+      <c r="L91" s="19" t="n"/>
       <c r="M91" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7712,7 +7928,7 @@
         <v>30</v>
       </c>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="18" t="n"/>
+      <c r="P91" s="19" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7722,7 +7938,7 @@
         <v>30</v>
       </c>
       <c r="S91" s="7" t="n"/>
-      <c r="T91" s="37" t="inlineStr">
+      <c r="T91" s="36" t="inlineStr">
         <is>
           <t>WE catéchumènes</t>
         </is>
@@ -7750,7 +7966,7 @@
         <v>30</v>
       </c>
       <c r="AE91" s="12" t="n"/>
-      <c r="AF91" s="18" t="n"/>
+      <c r="AF91" s="19" t="n"/>
       <c r="AG91" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7759,8 +7975,8 @@
       <c r="AH91" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AI91" s="43" t="n"/>
-      <c r="AJ91" s="20" t="n"/>
+      <c r="AI91" s="41" t="n"/>
+      <c r="AJ91" s="21" t="n"/>
       <c r="AK91" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7770,7 +7986,7 @@
         <v>30</v>
       </c>
       <c r="AM91" s="7" t="n"/>
-      <c r="AN91" s="18" t="n"/>
+      <c r="AN91" s="19" t="n"/>
       <c r="AO91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7780,7 +7996,7 @@
         <v>30</v>
       </c>
       <c r="AQ91" s="12" t="n"/>
-      <c r="AR91" s="18" t="n"/>
+      <c r="AR91" s="19" t="n"/>
       <c r="AS91" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7790,91 +8006,95 @@
         <v>30</v>
       </c>
       <c r="AU91" s="12" t="n"/>
-      <c r="AV91" s="18" t="n"/>
+      <c r="AV91" s="19" t="n"/>
     </row>
     <row r="92" ht="20.1" customHeight="1">
-      <c r="A92" s="21" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="26" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="G92" s="24" t="n"/>
-      <c r="H92" s="23" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="K92" s="22" t="n"/>
-      <c r="L92" s="26" t="n"/>
-      <c r="M92" s="21" t="n"/>
-      <c r="O92" s="24" t="n"/>
-      <c r="P92" s="26" t="n"/>
-      <c r="Q92" s="21" t="n"/>
-      <c r="S92" s="22" t="n"/>
-      <c r="T92" s="16" t="inlineStr">
+      <c r="A92" s="22" t="n"/>
+      <c r="C92" s="23" t="n"/>
+      <c r="D92" s="27" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="24" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="K92" s="23" t="n"/>
+      <c r="L92" s="27" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="O92" s="25" t="n"/>
+      <c r="P92" s="27" t="n"/>
+      <c r="Q92" s="22" t="n"/>
+      <c r="S92" s="23" t="n"/>
+      <c r="T92" s="18" t="inlineStr">
         <is>
           <t>WE Engagés ccn</t>
         </is>
       </c>
-      <c r="Y92" s="21" t="n"/>
-      <c r="AA92" s="22" t="n"/>
-      <c r="AB92" s="23" t="n"/>
-      <c r="AC92" s="21" t="n"/>
-      <c r="AE92" s="24" t="n"/>
-      <c r="AF92" s="26" t="n"/>
-      <c r="AG92" s="21" t="n"/>
-      <c r="AI92" s="46" t="n"/>
-      <c r="AJ92" s="27" t="n"/>
-      <c r="AK92" s="21" t="n"/>
-      <c r="AM92" s="22" t="n"/>
-      <c r="AN92" s="26" t="n"/>
-      <c r="AO92" s="21" t="n"/>
-      <c r="AQ92" s="24" t="n"/>
-      <c r="AR92" s="26" t="n"/>
-      <c r="AS92" s="21" t="n"/>
-      <c r="AU92" s="24" t="n"/>
-      <c r="AV92" s="26" t="n"/>
+      <c r="Y92" s="22" t="n"/>
+      <c r="AA92" s="23" t="n"/>
+      <c r="AB92" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="AC92" s="22" t="n"/>
+      <c r="AE92" s="25" t="n"/>
+      <c r="AF92" s="27" t="n"/>
+      <c r="AG92" s="22" t="n"/>
+      <c r="AI92" s="44" t="n"/>
+      <c r="AJ92" s="28" t="n"/>
+      <c r="AK92" s="22" t="n"/>
+      <c r="AM92" s="23" t="n"/>
+      <c r="AN92" s="27" t="n"/>
+      <c r="AO92" s="22" t="n"/>
+      <c r="AQ92" s="25" t="n"/>
+      <c r="AR92" s="27" t="n"/>
+      <c r="AS92" s="22" t="n"/>
+      <c r="AU92" s="25" t="n"/>
+      <c r="AV92" s="27" t="n"/>
     </row>
     <row r="93" ht="20.1" customHeight="1">
-      <c r="A93" s="28" t="n"/>
-      <c r="B93" s="29" t="n"/>
-      <c r="C93" s="30" t="n"/>
+      <c r="A93" s="29" t="n"/>
+      <c r="B93" s="30" t="n"/>
+      <c r="C93" s="31" t="n"/>
       <c r="D93" s="33" t="n"/>
-      <c r="E93" s="28" t="n"/>
-      <c r="F93" s="29" t="n"/>
-      <c r="G93" s="31" t="n"/>
-      <c r="H93" s="23" t="n"/>
-      <c r="I93" s="28" t="n"/>
-      <c r="J93" s="29" t="n"/>
-      <c r="K93" s="30" t="n"/>
+      <c r="E93" s="29" t="n"/>
+      <c r="F93" s="30" t="n"/>
+      <c r="G93" s="32" t="n"/>
+      <c r="H93" s="24" t="n"/>
+      <c r="I93" s="29" t="n"/>
+      <c r="J93" s="30" t="n"/>
+      <c r="K93" s="31" t="n"/>
       <c r="L93" s="33" t="n"/>
-      <c r="M93" s="28" t="n"/>
-      <c r="N93" s="29" t="n"/>
-      <c r="O93" s="31" t="n"/>
+      <c r="M93" s="29" t="n"/>
+      <c r="N93" s="30" t="n"/>
+      <c r="O93" s="32" t="n"/>
       <c r="P93" s="33" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="29" t="n"/>
-      <c r="S93" s="30" t="n"/>
-      <c r="T93" s="23" t="n"/>
-      <c r="Y93" s="28" t="n"/>
-      <c r="Z93" s="29" t="n"/>
-      <c r="AA93" s="30" t="n"/>
-      <c r="AB93" s="25" t="n"/>
-      <c r="AC93" s="28" t="n"/>
-      <c r="AD93" s="29" t="n"/>
-      <c r="AE93" s="31" t="n"/>
+      <c r="Q93" s="29" t="n"/>
+      <c r="R93" s="30" t="n"/>
+      <c r="S93" s="31" t="n"/>
+      <c r="T93" s="24" t="n"/>
+      <c r="Y93" s="29" t="n"/>
+      <c r="Z93" s="30" t="n"/>
+      <c r="AA93" s="31" t="n"/>
+      <c r="AB93" s="33" t="n"/>
+      <c r="AC93" s="29" t="n"/>
+      <c r="AD93" s="30" t="n"/>
+      <c r="AE93" s="32" t="n"/>
       <c r="AF93" s="33" t="n"/>
-      <c r="AG93" s="28" t="n"/>
-      <c r="AH93" s="29" t="n"/>
-      <c r="AI93" s="47" t="n"/>
-      <c r="AJ93" s="35" t="n"/>
-      <c r="AK93" s="28" t="n"/>
-      <c r="AL93" s="29" t="n"/>
-      <c r="AM93" s="30" t="n"/>
+      <c r="AG93" s="29" t="n"/>
+      <c r="AH93" s="30" t="n"/>
+      <c r="AI93" s="45" t="n"/>
+      <c r="AJ93" s="34" t="n"/>
+      <c r="AK93" s="29" t="n"/>
+      <c r="AL93" s="30" t="n"/>
+      <c r="AM93" s="31" t="n"/>
       <c r="AN93" s="33" t="n"/>
-      <c r="AO93" s="28" t="n"/>
-      <c r="AP93" s="29" t="n"/>
-      <c r="AQ93" s="31" t="n"/>
+      <c r="AO93" s="29" t="n"/>
+      <c r="AP93" s="30" t="n"/>
+      <c r="AQ93" s="32" t="n"/>
       <c r="AR93" s="33" t="n"/>
-      <c r="AS93" s="28" t="n"/>
-      <c r="AT93" s="29" t="n"/>
-      <c r="AU93" s="31" t="n"/>
+      <c r="AS93" s="29" t="n"/>
+      <c r="AT93" s="30" t="n"/>
+      <c r="AU93" s="32" t="n"/>
       <c r="AV93" s="33" t="n"/>
     </row>
     <row r="94" ht="20.1" customHeight="1">
@@ -7887,7 +8107,7 @@
         <v>31</v>
       </c>
       <c r="G94" s="12" t="n"/>
-      <c r="H94" s="23" t="n"/>
+      <c r="H94" s="24" t="n"/>
       <c r="M94" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7897,7 +8117,7 @@
         <v>31</v>
       </c>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="18" t="n"/>
+      <c r="P94" s="19" t="n"/>
       <c r="Q94" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7906,8 +8126,8 @@
       <c r="R94" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="S94" s="43" t="n"/>
-      <c r="T94" s="23" t="n"/>
+      <c r="S94" s="41" t="n"/>
+      <c r="T94" s="24" t="n"/>
       <c r="Y94" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7917,7 +8137,7 @@
         <v>31</v>
       </c>
       <c r="AA94" s="7" t="n"/>
-      <c r="AB94" s="18" t="n"/>
+      <c r="AB94" s="19" t="n"/>
       <c r="AG94" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7927,7 +8147,7 @@
         <v>31</v>
       </c>
       <c r="AI94" s="7" t="n"/>
-      <c r="AJ94" s="16" t="inlineStr">
+      <c r="AJ94" s="18" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -7941,7 +8161,7 @@
         <v>31</v>
       </c>
       <c r="AQ94" s="12" t="n"/>
-      <c r="AR94" s="18" t="n"/>
+      <c r="AR94" s="19" t="n"/>
       <c r="AS94" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7951,63 +8171,63 @@
         <v>31</v>
       </c>
       <c r="AU94" s="12" t="n"/>
-      <c r="AV94" s="18" t="n"/>
+      <c r="AV94" s="19" t="n"/>
     </row>
     <row r="95" ht="20.1" customHeight="1">
-      <c r="E95" s="21" t="n"/>
-      <c r="G95" s="24" t="n"/>
-      <c r="H95" s="23" t="n"/>
-      <c r="M95" s="21" t="n"/>
-      <c r="O95" s="24" t="n"/>
-      <c r="P95" s="26" t="n"/>
-      <c r="Q95" s="21" t="n"/>
-      <c r="S95" s="46" t="n"/>
-      <c r="T95" s="25" t="n"/>
-      <c r="Y95" s="21" t="n"/>
-      <c r="AA95" s="22" t="n"/>
-      <c r="AB95" s="26" t="n"/>
-      <c r="AG95" s="21" t="n"/>
-      <c r="AI95" s="22" t="n"/>
-      <c r="AJ95" s="23" t="n"/>
-      <c r="AO95" s="21" t="n"/>
-      <c r="AQ95" s="24" t="n"/>
-      <c r="AR95" s="26" t="n"/>
-      <c r="AS95" s="21" t="n"/>
-      <c r="AU95" s="24" t="n"/>
-      <c r="AV95" s="26" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="G95" s="25" t="n"/>
+      <c r="H95" s="24" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="O95" s="25" t="n"/>
+      <c r="P95" s="27" t="n"/>
+      <c r="Q95" s="22" t="n"/>
+      <c r="S95" s="44" t="n"/>
+      <c r="T95" s="26" t="n"/>
+      <c r="Y95" s="22" t="n"/>
+      <c r="AA95" s="23" t="n"/>
+      <c r="AB95" s="27" t="n"/>
+      <c r="AG95" s="22" t="n"/>
+      <c r="AI95" s="23" t="n"/>
+      <c r="AJ95" s="24" t="n"/>
+      <c r="AO95" s="22" t="n"/>
+      <c r="AQ95" s="25" t="n"/>
+      <c r="AR95" s="27" t="n"/>
+      <c r="AS95" s="22" t="n"/>
+      <c r="AU95" s="25" t="n"/>
+      <c r="AV95" s="27" t="n"/>
     </row>
     <row r="96" ht="20.1" customHeight="1">
-      <c r="E96" s="28" t="n"/>
-      <c r="F96" s="29" t="n"/>
-      <c r="G96" s="31" t="n"/>
-      <c r="H96" s="25" t="n"/>
-      <c r="M96" s="28" t="n"/>
-      <c r="N96" s="29" t="n"/>
-      <c r="O96" s="31" t="n"/>
+      <c r="E96" s="29" t="n"/>
+      <c r="F96" s="30" t="n"/>
+      <c r="G96" s="32" t="n"/>
+      <c r="H96" s="26" t="n"/>
+      <c r="M96" s="29" t="n"/>
+      <c r="N96" s="30" t="n"/>
+      <c r="O96" s="32" t="n"/>
       <c r="P96" s="33" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="29" t="n"/>
-      <c r="S96" s="47" t="n"/>
-      <c r="T96" s="37" t="n"/>
-      <c r="Y96" s="28" t="n"/>
-      <c r="Z96" s="29" t="n"/>
-      <c r="AA96" s="30" t="n"/>
+      <c r="Q96" s="29" t="n"/>
+      <c r="R96" s="30" t="n"/>
+      <c r="S96" s="45" t="n"/>
+      <c r="T96" s="36" t="n"/>
+      <c r="Y96" s="29" t="n"/>
+      <c r="Z96" s="30" t="n"/>
+      <c r="AA96" s="31" t="n"/>
       <c r="AB96" s="33" t="n"/>
-      <c r="AG96" s="28" t="n"/>
-      <c r="AH96" s="29" t="n"/>
-      <c r="AI96" s="30" t="n"/>
-      <c r="AJ96" s="25" t="n"/>
-      <c r="AO96" s="28" t="n"/>
-      <c r="AP96" s="29" t="n"/>
-      <c r="AQ96" s="31" t="n"/>
+      <c r="AG96" s="29" t="n"/>
+      <c r="AH96" s="30" t="n"/>
+      <c r="AI96" s="31" t="n"/>
+      <c r="AJ96" s="26" t="n"/>
+      <c r="AO96" s="29" t="n"/>
+      <c r="AP96" s="30" t="n"/>
+      <c r="AQ96" s="32" t="n"/>
       <c r="AR96" s="33" t="n"/>
-      <c r="AS96" s="28" t="n"/>
-      <c r="AT96" s="29" t="n"/>
-      <c r="AU96" s="31" t="n"/>
+      <c r="AS96" s="29" t="n"/>
+      <c r="AT96" s="30" t="n"/>
+      <c r="AU96" s="32" t="n"/>
       <c r="AV96" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="846">
+  <mergeCells count="839">
     <mergeCell ref="AC22:AC24"/>
     <mergeCell ref="R91:R93"/>
     <mergeCell ref="B34:B36"/>
@@ -8023,6 +8243,7 @@
     <mergeCell ref="V55:V57"/>
     <mergeCell ref="Z19:Z21"/>
     <mergeCell ref="AT67:AT69"/>
+    <mergeCell ref="X73:X81"/>
     <mergeCell ref="AO31:AO33"/>
     <mergeCell ref="I88:I90"/>
     <mergeCell ref="AG58:AG60"/>
@@ -8030,7 +8251,6 @@
     <mergeCell ref="AG73:AG75"/>
     <mergeCell ref="M52:M54"/>
     <mergeCell ref="AF34:AF36"/>
-    <mergeCell ref="T10:T17"/>
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="AH28:AH30"/>
     <mergeCell ref="N7:N9"/>
@@ -8040,9 +8260,10 @@
     <mergeCell ref="Q43:Q45"/>
     <mergeCell ref="AS88:AS90"/>
     <mergeCell ref="AG25:AG27"/>
+    <mergeCell ref="L47:L51"/>
     <mergeCell ref="AH67:AH69"/>
     <mergeCell ref="N46:N48"/>
-    <mergeCell ref="P46:P48"/>
+    <mergeCell ref="AJ67:AJ69"/>
     <mergeCell ref="AL61:AL63"/>
     <mergeCell ref="R40:R42"/>
     <mergeCell ref="V4:V6"/>
@@ -8056,6 +8277,7 @@
     <mergeCell ref="AC10:AC12"/>
     <mergeCell ref="J79:J81"/>
     <mergeCell ref="AO58:AO60"/>
+    <mergeCell ref="T70:T72"/>
     <mergeCell ref="N73:N75"/>
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="A1:AV1"/>
@@ -8074,7 +8296,6 @@
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="I13:I15"/>
     <mergeCell ref="I64:I66"/>
-    <mergeCell ref="H61:H71"/>
     <mergeCell ref="AK61:AK63"/>
     <mergeCell ref="U4:U6"/>
     <mergeCell ref="AD52:AD54"/>
@@ -8098,7 +8319,6 @@
     <mergeCell ref="AO7:AO9"/>
     <mergeCell ref="AB20:AB22"/>
     <mergeCell ref="AB85:AB87"/>
-    <mergeCell ref="AB91:AB93"/>
     <mergeCell ref="AJ82:AJ84"/>
     <mergeCell ref="M10:M12"/>
     <mergeCell ref="Z22:Z24"/>
@@ -8126,7 +8346,6 @@
     <mergeCell ref="AO25:AO27"/>
     <mergeCell ref="U52:U54"/>
     <mergeCell ref="AC49:AC51"/>
-    <mergeCell ref="X40:X42"/>
     <mergeCell ref="AT61:AT63"/>
     <mergeCell ref="R43:R45"/>
     <mergeCell ref="Z40:Z42"/>
@@ -8139,6 +8358,7 @@
     <mergeCell ref="V58:V60"/>
     <mergeCell ref="Q37:Q39"/>
     <mergeCell ref="AG94:AG96"/>
+    <mergeCell ref="L9:L10"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="V73:V75"/>
     <mergeCell ref="B52:B54"/>
@@ -8153,12 +8373,12 @@
     <mergeCell ref="AO13:AO15"/>
     <mergeCell ref="AS40:AS42"/>
     <mergeCell ref="AS46:AS48"/>
+    <mergeCell ref="P67:P69"/>
     <mergeCell ref="F91:F93"/>
     <mergeCell ref="N82:N84"/>
     <mergeCell ref="U7:U9"/>
     <mergeCell ref="AK64:AK66"/>
     <mergeCell ref="AH19:AH21"/>
-    <mergeCell ref="AB25:AB29"/>
     <mergeCell ref="AH55:AH57"/>
     <mergeCell ref="F22:F24"/>
     <mergeCell ref="H44:H56"/>
@@ -8170,6 +8390,7 @@
     <mergeCell ref="Y16:Y18"/>
     <mergeCell ref="Y52:Y54"/>
     <mergeCell ref="M76:M78"/>
+    <mergeCell ref="AJ20:AJ22"/>
     <mergeCell ref="J31:J33"/>
     <mergeCell ref="AL85:AL87"/>
     <mergeCell ref="N31:N33"/>
@@ -8191,11 +8412,11 @@
     <mergeCell ref="F40:F42"/>
     <mergeCell ref="AK19:AK21"/>
     <mergeCell ref="J64:J66"/>
+    <mergeCell ref="P88:P90"/>
     <mergeCell ref="R88:R90"/>
     <mergeCell ref="AF10:AF12"/>
     <mergeCell ref="M79:M81"/>
     <mergeCell ref="E67:E69"/>
-    <mergeCell ref="AJ94:AJ96"/>
     <mergeCell ref="V79:V81"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="M94:M96"/>
@@ -8210,7 +8431,6 @@
     <mergeCell ref="AT91:AT93"/>
     <mergeCell ref="AD34:AD36"/>
     <mergeCell ref="AL25:AL27"/>
-    <mergeCell ref="AN25:AN27"/>
     <mergeCell ref="Q22:Q24"/>
     <mergeCell ref="Y46:Y48"/>
     <mergeCell ref="AL58:AL60"/>
@@ -8220,6 +8440,7 @@
     <mergeCell ref="AS61:AS63"/>
     <mergeCell ref="AJ27:AJ30"/>
     <mergeCell ref="AN58:AN60"/>
+    <mergeCell ref="X65:X71"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="R52:R54"/>
     <mergeCell ref="V16:V18"/>
@@ -8236,7 +8457,6 @@
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="I49:I51"/>
     <mergeCell ref="AC70:AC72"/>
-    <mergeCell ref="H73:H96"/>
     <mergeCell ref="R64:R66"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="Z61:Z63"/>
@@ -8244,7 +8464,7 @@
     <mergeCell ref="N85:N87"/>
     <mergeCell ref="U10:U12"/>
     <mergeCell ref="AH22:AH24"/>
-    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="H36:H41"/>
     <mergeCell ref="AG88:AG90"/>
     <mergeCell ref="M67:M69"/>
     <mergeCell ref="AL22:AL24"/>
@@ -8257,7 +8477,6 @@
     <mergeCell ref="AS76:AS78"/>
     <mergeCell ref="AC76:AC78"/>
     <mergeCell ref="AD31:AD33"/>
-    <mergeCell ref="T58:T60"/>
     <mergeCell ref="V31:V33"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AP79:AP81"/>
@@ -8284,7 +8503,7 @@
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="Q61:Q63"/>
     <mergeCell ref="J52:J54"/>
-    <mergeCell ref="L33:L34"/>
+    <mergeCell ref="AR7:AR9"/>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="AL10:AL12"/>
@@ -8308,7 +8527,6 @@
     <mergeCell ref="R55:R57"/>
     <mergeCell ref="V19:V21"/>
     <mergeCell ref="AP67:AP69"/>
-    <mergeCell ref="X19:X21"/>
     <mergeCell ref="E88:E90"/>
     <mergeCell ref="AK58:AK60"/>
     <mergeCell ref="AC58:AC60"/>
@@ -8320,7 +8538,6 @@
     <mergeCell ref="M16:M18"/>
     <mergeCell ref="AC73:AC75"/>
     <mergeCell ref="AK10:AK12"/>
-    <mergeCell ref="T79:T81"/>
     <mergeCell ref="AG91:AG93"/>
     <mergeCell ref="Q34:Q36"/>
     <mergeCell ref="AO88:AO90"/>
@@ -8332,17 +8549,16 @@
     <mergeCell ref="AC25:AC27"/>
     <mergeCell ref="J46:J48"/>
     <mergeCell ref="M85:M87"/>
+    <mergeCell ref="AB7:AB9"/>
     <mergeCell ref="E85:E87"/>
     <mergeCell ref="AD7:AD9"/>
     <mergeCell ref="AT64:AT66"/>
-    <mergeCell ref="T37:T39"/>
     <mergeCell ref="N40:N42"/>
     <mergeCell ref="V37:V39"/>
     <mergeCell ref="AO55:AO57"/>
     <mergeCell ref="AS19:AS21"/>
     <mergeCell ref="Z88:Z90"/>
     <mergeCell ref="F67:F69"/>
-    <mergeCell ref="L47:L52"/>
     <mergeCell ref="F82:F84"/>
     <mergeCell ref="AP16:AP18"/>
     <mergeCell ref="A79:A81"/>
@@ -8386,7 +8602,6 @@
     <mergeCell ref="AS7:AS9"/>
     <mergeCell ref="F28:F30"/>
     <mergeCell ref="AG43:AG45"/>
-    <mergeCell ref="AN4:AN5"/>
     <mergeCell ref="F64:F66"/>
     <mergeCell ref="V22:V24"/>
     <mergeCell ref="Z13:Z15"/>
@@ -8394,7 +8609,6 @@
     <mergeCell ref="A67:A69"/>
     <mergeCell ref="E91:E93"/>
     <mergeCell ref="E25:E27"/>
-    <mergeCell ref="AF40:AF42"/>
     <mergeCell ref="AJ4:AJ6"/>
     <mergeCell ref="AL4:AL6"/>
     <mergeCell ref="AO52:AO54"/>
@@ -8411,6 +8625,7 @@
     <mergeCell ref="AK25:AK27"/>
     <mergeCell ref="Q52:Q54"/>
     <mergeCell ref="E28:E30"/>
+    <mergeCell ref="AN88:AN90"/>
     <mergeCell ref="N43:N45"/>
     <mergeCell ref="V40:V42"/>
     <mergeCell ref="AP88:AP90"/>
@@ -8422,15 +8637,16 @@
     <mergeCell ref="AP19:AP21"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="U37:U39"/>
+    <mergeCell ref="AR19:AR21"/>
     <mergeCell ref="M37:M39"/>
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="AK31:AK33"/>
     <mergeCell ref="AB65:AB70"/>
     <mergeCell ref="AJ52:AJ53"/>
     <mergeCell ref="AT34:AT36"/>
+    <mergeCell ref="H73:H83"/>
     <mergeCell ref="AB13:AB15"/>
     <mergeCell ref="Z10:Z12"/>
-    <mergeCell ref="L9:L11"/>
     <mergeCell ref="I79:I81"/>
     <mergeCell ref="Z28:Z30"/>
     <mergeCell ref="AT49:AT51"/>
@@ -8447,7 +8663,6 @@
     <mergeCell ref="Q7:Q9"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="AB55:AB57"/>
-    <mergeCell ref="AF19:AF21"/>
     <mergeCell ref="AF46:AF48"/>
     <mergeCell ref="AD55:AD57"/>
     <mergeCell ref="AP37:AP39"/>
@@ -8456,19 +8671,18 @@
     <mergeCell ref="N4:N6"/>
     <mergeCell ref="V61:V63"/>
     <mergeCell ref="Y58:Y60"/>
-    <mergeCell ref="P4:P6"/>
+    <mergeCell ref="AF61:AF63"/>
     <mergeCell ref="Q58:Q60"/>
     <mergeCell ref="AC16:AC18"/>
     <mergeCell ref="I76:I78"/>
     <mergeCell ref="AS10:AS12"/>
-    <mergeCell ref="H35:H41"/>
     <mergeCell ref="AD79:AD81"/>
     <mergeCell ref="AL70:AL72"/>
     <mergeCell ref="R49:R51"/>
+    <mergeCell ref="L13:L19"/>
     <mergeCell ref="F79:F81"/>
     <mergeCell ref="AR13:AR15"/>
     <mergeCell ref="E34:E36"/>
-    <mergeCell ref="AJ13:AJ15"/>
     <mergeCell ref="AC82:AC84"/>
     <mergeCell ref="M25:M27"/>
     <mergeCell ref="AH43:AH45"/>
@@ -8487,7 +8701,6 @@
     <mergeCell ref="AT31:AT33"/>
     <mergeCell ref="N88:N90"/>
     <mergeCell ref="AT58:AT60"/>
-    <mergeCell ref="AJ55:AJ57"/>
     <mergeCell ref="AO34:AO36"/>
     <mergeCell ref="AT73:AT75"/>
     <mergeCell ref="AD16:AD18"/>
@@ -8517,7 +8730,6 @@
     <mergeCell ref="V67:V69"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="J37:J39"/>
-    <mergeCell ref="AJ20:AJ23"/>
     <mergeCell ref="N37:N39"/>
     <mergeCell ref="B61:B63"/>
     <mergeCell ref="Q79:Q81"/>
@@ -8527,15 +8739,17 @@
     <mergeCell ref="N64:N66"/>
     <mergeCell ref="AS43:AS45"/>
     <mergeCell ref="Y10:Y12"/>
+    <mergeCell ref="T10:T16"/>
     <mergeCell ref="J85:J87"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="AO91:AO93"/>
     <mergeCell ref="Y34:Y36"/>
+    <mergeCell ref="L85:L87"/>
     <mergeCell ref="I67:I69"/>
     <mergeCell ref="AL55:AL57"/>
-    <mergeCell ref="AN46:AN48"/>
     <mergeCell ref="R70:R72"/>
     <mergeCell ref="AP46:AP48"/>
+    <mergeCell ref="L36:L43"/>
     <mergeCell ref="AP40:AP42"/>
     <mergeCell ref="N13:N15"/>
     <mergeCell ref="AJ47:AJ50"/>
@@ -8554,13 +8768,11 @@
     <mergeCell ref="AT70:AT72"/>
     <mergeCell ref="Z49:Z51"/>
     <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="AB49:AB51"/>
     <mergeCell ref="Y3:AB3"/>
     <mergeCell ref="J76:J78"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="R73:R75"/>
     <mergeCell ref="AP43:AP45"/>
-    <mergeCell ref="L24:L29"/>
     <mergeCell ref="AG85:AG87"/>
     <mergeCell ref="M64:M66"/>
     <mergeCell ref="Q28:Q30"/>
@@ -8579,7 +8791,7 @@
     <mergeCell ref="AG22:AG24"/>
     <mergeCell ref="AL43:AL45"/>
     <mergeCell ref="AS4:AS6"/>
-    <mergeCell ref="P25:P27"/>
+    <mergeCell ref="AF82:AF84"/>
     <mergeCell ref="AT76:AT78"/>
     <mergeCell ref="AD19:AD21"/>
     <mergeCell ref="AS31:AS33"/>
@@ -8589,7 +8801,7 @@
     <mergeCell ref="AH34:AH36"/>
     <mergeCell ref="AK73:AK75"/>
     <mergeCell ref="D76:D80"/>
-    <mergeCell ref="AJ34:AJ36"/>
+    <mergeCell ref="P13:P15"/>
     <mergeCell ref="AH64:AH66"/>
     <mergeCell ref="AL28:AL30"/>
     <mergeCell ref="Z52:Z54"/>
@@ -8599,16 +8811,16 @@
     <mergeCell ref="U43:U45"/>
     <mergeCell ref="Y7:Y9"/>
     <mergeCell ref="AC40:AC42"/>
+    <mergeCell ref="L25:L29"/>
     <mergeCell ref="J22:J24"/>
     <mergeCell ref="AL67:AL69"/>
     <mergeCell ref="R46:R48"/>
-    <mergeCell ref="AJ76:AJ78"/>
     <mergeCell ref="AP61:AP63"/>
     <mergeCell ref="Z4:Z6"/>
     <mergeCell ref="AD37:AD39"/>
     <mergeCell ref="AH61:AH63"/>
     <mergeCell ref="AT94:AT96"/>
-    <mergeCell ref="L37:L42"/>
+    <mergeCell ref="AJ94:AJ96"/>
     <mergeCell ref="R61:R63"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="L30:L31"/>
@@ -8627,7 +8839,6 @@
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="I85:I87"/>
     <mergeCell ref="M49:M51"/>
-    <mergeCell ref="X7:X9"/>
     <mergeCell ref="AP64:AP66"/>
     <mergeCell ref="R10:R12"/>
     <mergeCell ref="Z7:Z9"/>
@@ -8649,9 +8860,9 @@
     <mergeCell ref="AK79:AK81"/>
     <mergeCell ref="AS70:AS72"/>
     <mergeCell ref="Y49:Y51"/>
-    <mergeCell ref="AN67:AN69"/>
     <mergeCell ref="AD91:AD93"/>
     <mergeCell ref="N34:N36"/>
+    <mergeCell ref="H62:H71"/>
     <mergeCell ref="AD85:AD87"/>
     <mergeCell ref="N28:N30"/>
     <mergeCell ref="V25:V27"/>
@@ -8659,6 +8870,7 @@
     <mergeCell ref="AH49:AH51"/>
     <mergeCell ref="AL82:AL84"/>
     <mergeCell ref="AK37:AK39"/>
+    <mergeCell ref="AN82:AN84"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="AD22:AD24"/>
     <mergeCell ref="U64:U66"/>
@@ -8695,6 +8907,7 @@
     <mergeCell ref="AS52:AS54"/>
     <mergeCell ref="AG76:AG78"/>
     <mergeCell ref="Q19:Q21"/>
+    <mergeCell ref="H85:H96"/>
     <mergeCell ref="AK76:AK78"/>
     <mergeCell ref="I55:I57"/>
     <mergeCell ref="B88:B90"/>
@@ -8705,6 +8918,7 @@
     <mergeCell ref="F52:F54"/>
     <mergeCell ref="J16:J18"/>
     <mergeCell ref="Y28:Y30"/>
+    <mergeCell ref="AB25:AB28"/>
     <mergeCell ref="AJ88:AJ90"/>
     <mergeCell ref="J43:J45"/>
     <mergeCell ref="AL88:AL90"/>
@@ -8712,7 +8926,6 @@
     <mergeCell ref="Y70:Y72"/>
     <mergeCell ref="AO22:AO24"/>
     <mergeCell ref="AS13:AS15"/>
-    <mergeCell ref="L13:L20"/>
     <mergeCell ref="T92:T95"/>
     <mergeCell ref="R82:R84"/>
     <mergeCell ref="B25:B27"/>
@@ -8733,7 +8946,6 @@
     <mergeCell ref="E79:E81"/>
     <mergeCell ref="V28:V30"/>
     <mergeCell ref="M70:M72"/>
-    <mergeCell ref="X28:X30"/>
     <mergeCell ref="AP85:AP87"/>
     <mergeCell ref="R31:R33"/>
     <mergeCell ref="AC64:AC66"/>
@@ -8747,13 +8959,16 @@
     <mergeCell ref="AL37:AL39"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="AB80:AB83"/>
+    <mergeCell ref="AB61:AB63"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="E76:E78"/>
     <mergeCell ref="AO10:AO12"/>
+    <mergeCell ref="AF7:AF9"/>
     <mergeCell ref="Z79:Z81"/>
     <mergeCell ref="F58:F60"/>
     <mergeCell ref="AH70:AH72"/>
     <mergeCell ref="N49:N51"/>
+    <mergeCell ref="AN13:AN15"/>
     <mergeCell ref="Q91:Q93"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="A28:A30"/>
@@ -8766,7 +8981,6 @@
     <mergeCell ref="I61:I63"/>
     <mergeCell ref="AP4:AP6"/>
     <mergeCell ref="AP25:AP27"/>
-    <mergeCell ref="X65:X81"/>
     <mergeCell ref="U22:U24"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="J88:J90"/>
@@ -8774,6 +8988,7 @@
     <mergeCell ref="J82:J84"/>
     <mergeCell ref="AP58:AP60"/>
     <mergeCell ref="L82:L84"/>
+    <mergeCell ref="X16:X18"/>
     <mergeCell ref="AH76:AH78"/>
     <mergeCell ref="R19:R21"/>
     <mergeCell ref="Z16:Z18"/>
@@ -8786,6 +9001,7 @@
     <mergeCell ref="AH73:AH75"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="AP73:AP75"/>
+    <mergeCell ref="AB16:AB18"/>
     <mergeCell ref="Y79:Y81"/>
     <mergeCell ref="AL91:AL93"/>
     <mergeCell ref="V34:V36"/>
@@ -8834,7 +9050,6 @@
     <mergeCell ref="J13:J15"/>
     <mergeCell ref="R4:R6"/>
     <mergeCell ref="AJ61:AJ63"/>
-    <mergeCell ref="T4:T6"/>
     <mergeCell ref="AD64:AD66"/>
     <mergeCell ref="Y55:Y57"/>
     <mergeCell ref="AG52:AG54"/>
@@ -8845,8 +9060,6 @@
     <mergeCell ref="U61:U63"/>
     <mergeCell ref="N52:N54"/>
     <mergeCell ref="V49:V51"/>
-    <mergeCell ref="X49:X51"/>
-    <mergeCell ref="L73:L75"/>
     <mergeCell ref="U3:X3"/>
     <mergeCell ref="F76:F78"/>
     <mergeCell ref="AP10:AP12"/>

--- a/calendrier.xlsx
+++ b/calendrier.xlsx
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Q26" s="22" t="n"/>
       <c r="S26" s="23" t="n"/>
-      <c r="T26" s="24" t="n"/>
+      <c r="T26" s="26" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="W26" s="23" t="n"/>
       <c r="X26" s="27" t="n"/>
@@ -2933,7 +2933,11 @@
       <c r="Q27" s="29" t="n"/>
       <c r="R27" s="30" t="n"/>
       <c r="S27" s="31" t="n"/>
-      <c r="T27" s="26" t="n"/>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <t>Rencontre CCN + Kion</t>
+        </is>
+      </c>
       <c r="U27" s="29" t="n"/>
       <c r="V27" s="30" t="n"/>
       <c r="W27" s="31" t="n"/>
@@ -6071,7 +6075,11 @@
         <v>22</v>
       </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="19" t="n"/>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>Rentrée District CCN + Kion</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6202,7 +6210,7 @@
     <row r="68" ht="20.1" customHeight="1">
       <c r="A68" s="22" t="n"/>
       <c r="C68" s="23" t="n"/>
-      <c r="D68" s="27" t="n"/>
+      <c r="D68" s="24" t="n"/>
       <c r="E68" s="22" t="n"/>
       <c r="G68" s="25" t="n"/>
       <c r="H68" s="24" t="n"/>
@@ -6245,7 +6253,7 @@
       <c r="A69" s="29" t="n"/>
       <c r="B69" s="30" t="n"/>
       <c r="C69" s="31" t="n"/>
-      <c r="D69" s="33" t="n"/>
+      <c r="D69" s="26" t="n"/>
       <c r="E69" s="29" t="n"/>
       <c r="F69" s="30" t="n"/>
       <c r="G69" s="32" t="n"/>
@@ -7743,7 +7751,7 @@
         <v>29</v>
       </c>
       <c r="AA88" s="7" t="n"/>
-      <c r="AB88" s="20" t="inlineStr">
+      <c r="AB88" s="17" t="inlineStr">
         <is>
           <t>Lundi de Pâques</t>
         </is>
@@ -7825,7 +7833,11 @@
       <c r="T89" s="27" t="n"/>
       <c r="Y89" s="22" t="n"/>
       <c r="AA89" s="23" t="n"/>
-      <c r="AB89" s="24" t="n"/>
+      <c r="AB89" s="16" t="inlineStr">
+        <is>
+          <t>Lundi de Pâques CCN + Kion + Cana</t>
+        </is>
+      </c>
       <c r="AC89" s="22" t="n"/>
       <c r="AE89" s="25" t="n"/>
       <c r="AF89" s="27" t="n"/>
@@ -7866,7 +7878,7 @@
       <c r="Y90" s="29" t="n"/>
       <c r="Z90" s="30" t="n"/>
       <c r="AA90" s="31" t="n"/>
-      <c r="AB90" s="26" t="n"/>
+      <c r="AB90" s="33" t="n"/>
       <c r="AC90" s="29" t="n"/>
       <c r="AD90" s="30" t="n"/>
       <c r="AE90" s="32" t="n"/>
@@ -8559,6 +8571,7 @@
     <mergeCell ref="AS19:AS21"/>
     <mergeCell ref="Z88:Z90"/>
     <mergeCell ref="F67:F69"/>
+    <mergeCell ref="D67:D69"/>
     <mergeCell ref="F82:F84"/>
     <mergeCell ref="AP16:AP18"/>
     <mergeCell ref="A79:A81"/>
@@ -8693,6 +8706,7 @@
     <mergeCell ref="Q85:Q87"/>
     <mergeCell ref="E61:E63"/>
     <mergeCell ref="AT4:AT6"/>
+    <mergeCell ref="T19:T26"/>
     <mergeCell ref="AO43:AO45"/>
     <mergeCell ref="AC19:AC21"/>
     <mergeCell ref="D4:D6"/>
@@ -8777,7 +8791,6 @@
     <mergeCell ref="M64:M66"/>
     <mergeCell ref="Q28:Q30"/>
     <mergeCell ref="AR43:AR45"/>
-    <mergeCell ref="AB88:AB90"/>
     <mergeCell ref="V64:V66"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="F7:F9"/>
@@ -9040,7 +9053,6 @@
     <mergeCell ref="AK91:AK93"/>
     <mergeCell ref="AO49:AO51"/>
     <mergeCell ref="P38:P40"/>
-    <mergeCell ref="T19:T27"/>
     <mergeCell ref="N70:N72"/>
     <mergeCell ref="AH13:AH15"/>
     <mergeCell ref="AL46:AL48"/>

--- a/calendrier.xlsx
+++ b/calendrier.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,12 +82,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -317,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -349,8 +343,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -359,9 +353,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -376,12 +367,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -403,10 +397,10 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -421,11 +415,11 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -440,9 +434,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1013,7 +1004,11 @@
         <v>1</v>
       </c>
       <c r="K4" s="12" t="n"/>
-      <c r="L4" s="13" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Toussaint</t>
+        </is>
+      </c>
       <c r="M4" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -1037,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="12" t="n"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="T4" s="13" t="inlineStr">
         <is>
           <t>Jour de l'an</t>
         </is>
@@ -1051,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="7" t="n"/>
-      <c r="X4" s="18" t="inlineStr">
+      <c r="X4" s="17" t="inlineStr">
         <is>
           <t>WE Engagés ccn</t>
         </is>
@@ -1065,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="12" t="n"/>
-      <c r="AB4" s="19" t="n"/>
+      <c r="AB4" s="18" t="n"/>
       <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1075,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="7" t="n"/>
-      <c r="AF4" s="19" t="n"/>
+      <c r="AF4" s="18" t="n"/>
       <c r="AG4" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1085,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="AI4" s="12" t="n"/>
-      <c r="AJ4" s="20" t="inlineStr">
+      <c r="AJ4" s="19" t="inlineStr">
         <is>
           <t>Fête du travail</t>
         </is>
@@ -1113,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="19" t="n"/>
+      <c r="AR4" s="18" t="n"/>
       <c r="AS4" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1123,113 +1118,109 @@
         <v>1</v>
       </c>
       <c r="AU4" s="12" t="n"/>
-      <c r="AV4" s="21" t="n"/>
+      <c r="AV4" s="20" t="n"/>
     </row>
     <row r="5" ht="20.1" customHeight="1">
-      <c r="A5" s="22" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="G5" s="23" t="n"/>
-      <c r="H5" s="24" t="n"/>
-      <c r="I5" s="22" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="26" t="n"/>
-      <c r="M5" s="22" t="n"/>
-      <c r="O5" s="23" t="n"/>
+      <c r="A5" s="21" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="21" t="n"/>
+      <c r="K5" s="24" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="21" t="n"/>
+      <c r="O5" s="22" t="n"/>
       <c r="P5" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="n"/>
-      <c r="S5" s="25" t="n"/>
+      <c r="Q5" s="21" t="n"/>
+      <c r="S5" s="24" t="n"/>
       <c r="T5" s="16" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
-      <c r="U5" s="22" t="n"/>
-      <c r="W5" s="23" t="n"/>
-      <c r="X5" s="24" t="n"/>
-      <c r="Y5" s="22" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="27" t="n"/>
-      <c r="AC5" s="22" t="n"/>
-      <c r="AE5" s="23" t="n"/>
-      <c r="AF5" s="27" t="n"/>
-      <c r="AG5" s="22" t="n"/>
-      <c r="AI5" s="25" t="n"/>
-      <c r="AJ5" s="24" t="n"/>
-      <c r="AK5" s="22" t="n"/>
-      <c r="AM5" s="23" t="n"/>
+      <c r="U5" s="21" t="n"/>
+      <c r="W5" s="22" t="n"/>
+      <c r="X5" s="23" t="n"/>
+      <c r="Y5" s="21" t="n"/>
+      <c r="AA5" s="24" t="n"/>
+      <c r="AB5" s="26" t="n"/>
+      <c r="AC5" s="21" t="n"/>
+      <c r="AE5" s="22" t="n"/>
+      <c r="AF5" s="26" t="n"/>
+      <c r="AG5" s="21" t="n"/>
+      <c r="AI5" s="24" t="n"/>
+      <c r="AJ5" s="23" t="n"/>
+      <c r="AK5" s="21" t="n"/>
+      <c r="AM5" s="22" t="n"/>
       <c r="AN5" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="AO5" s="22" t="n"/>
-      <c r="AQ5" s="23" t="n"/>
-      <c r="AR5" s="27" t="n"/>
-      <c r="AS5" s="22" t="n"/>
-      <c r="AU5" s="25" t="n"/>
-      <c r="AV5" s="28" t="n"/>
+      <c r="AO5" s="21" t="n"/>
+      <c r="AQ5" s="22" t="n"/>
+      <c r="AR5" s="26" t="n"/>
+      <c r="AS5" s="21" t="n"/>
+      <c r="AU5" s="24" t="n"/>
+      <c r="AV5" s="27" t="n"/>
     </row>
     <row r="6" ht="20.1" customHeight="1">
-      <c r="A6" s="29" t="n"/>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="31" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="29" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="31" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="29" t="n"/>
-      <c r="J6" s="30" t="n"/>
+      <c r="A6" s="28" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="29" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="31" t="n"/>
+      <c r="I6" s="28" t="n"/>
+      <c r="J6" s="29" t="n"/>
       <c r="K6" s="32" t="n"/>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>Toussaint</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="31" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="28" t="n"/>
+      <c r="N6" s="29" t="n"/>
+      <c r="O6" s="30" t="n"/>
       <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="29" t="n"/>
-      <c r="R6" s="30" t="n"/>
+      <c r="Q6" s="28" t="n"/>
+      <c r="R6" s="29" t="n"/>
       <c r="S6" s="32" t="n"/>
       <c r="T6" s="33" t="n"/>
-      <c r="U6" s="29" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="31" t="n"/>
-      <c r="X6" s="26" t="n"/>
-      <c r="Y6" s="29" t="n"/>
-      <c r="Z6" s="30" t="n"/>
+      <c r="U6" s="28" t="n"/>
+      <c r="V6" s="29" t="n"/>
+      <c r="W6" s="30" t="n"/>
+      <c r="X6" s="31" t="n"/>
+      <c r="Y6" s="28" t="n"/>
+      <c r="Z6" s="29" t="n"/>
       <c r="AA6" s="32" t="n"/>
       <c r="AB6" s="33" t="n"/>
-      <c r="AC6" s="29" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="31" t="n"/>
+      <c r="AC6" s="28" t="n"/>
+      <c r="AD6" s="29" t="n"/>
+      <c r="AE6" s="30" t="n"/>
       <c r="AF6" s="33" t="n"/>
-      <c r="AG6" s="29" t="n"/>
-      <c r="AH6" s="30" t="n"/>
+      <c r="AG6" s="28" t="n"/>
+      <c r="AH6" s="29" t="n"/>
       <c r="AI6" s="32" t="n"/>
-      <c r="AJ6" s="26" t="n"/>
-      <c r="AK6" s="29" t="n"/>
-      <c r="AL6" s="30" t="n"/>
-      <c r="AM6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="28" t="n"/>
+      <c r="AL6" s="29" t="n"/>
+      <c r="AM6" s="30" t="n"/>
       <c r="AN6" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AO6" s="29" t="n"/>
-      <c r="AP6" s="30" t="n"/>
-      <c r="AQ6" s="31" t="n"/>
+      <c r="AO6" s="28" t="n"/>
+      <c r="AP6" s="29" t="n"/>
+      <c r="AQ6" s="30" t="n"/>
       <c r="AR6" s="33" t="n"/>
-      <c r="AS6" s="29" t="n"/>
-      <c r="AT6" s="30" t="n"/>
+      <c r="AS6" s="28" t="n"/>
+      <c r="AT6" s="29" t="n"/>
       <c r="AU6" s="32" t="n"/>
       <c r="AV6" s="34" t="n"/>
     </row>
@@ -1243,7 +1234,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="19" t="n"/>
+      <c r="D7" s="18" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1267,11 +1258,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="7" t="n"/>
-      <c r="L7" s="36" t="inlineStr">
-        <is>
-          <t>Défunts</t>
-        </is>
-      </c>
+      <c r="L7" s="31" t="n"/>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1281,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="O7" s="7" t="n"/>
-      <c r="P7" s="19" t="n"/>
+      <c r="P7" s="18" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1291,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="S7" s="12" t="n"/>
-      <c r="T7" s="19" t="n"/>
+      <c r="T7" s="18" t="n"/>
       <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -1315,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="AA7" s="12" t="n"/>
-      <c r="AB7" s="18" t="inlineStr">
+      <c r="AB7" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -1329,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="AE7" s="7" t="n"/>
-      <c r="AF7" s="18" t="inlineStr">
+      <c r="AF7" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1343,7 +1330,7 @@
         <v>2</v>
       </c>
       <c r="AI7" s="12" t="n"/>
-      <c r="AJ7" s="21" t="n"/>
+      <c r="AJ7" s="20" t="n"/>
       <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1353,7 +1340,7 @@
         <v>2</v>
       </c>
       <c r="AM7" s="7" t="n"/>
-      <c r="AN7" s="19" t="n"/>
+      <c r="AN7" s="18" t="n"/>
       <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1363,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" s="7" t="n"/>
-      <c r="AR7" s="18" t="inlineStr">
+      <c r="AR7" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1377,101 +1364,105 @@
         <v>2</v>
       </c>
       <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="19" t="n"/>
+      <c r="AV7" s="18" t="n"/>
     </row>
     <row r="8" ht="20.1" customHeight="1">
-      <c r="A8" s="22" t="n"/>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="K8" s="23" t="n"/>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="A8" s="21" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="K8" s="22" t="n"/>
+      <c r="L8" s="36" t="inlineStr">
+        <is>
+          <t>Défunts</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="n"/>
+      <c r="O8" s="22" t="n"/>
+      <c r="P8" s="26" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="S8" s="24" t="n"/>
+      <c r="T8" s="26" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="W8" s="22" t="n"/>
+      <c r="X8" s="16" t="inlineStr">
+        <is>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="Y8" s="21" t="n"/>
+      <c r="AA8" s="24" t="n"/>
+      <c r="AB8" s="23" t="n"/>
+      <c r="AC8" s="21" t="n"/>
+      <c r="AE8" s="22" t="n"/>
+      <c r="AF8" s="23" t="n"/>
+      <c r="AG8" s="21" t="n"/>
+      <c r="AI8" s="24" t="n"/>
+      <c r="AJ8" s="27" t="n"/>
+      <c r="AK8" s="21" t="n"/>
+      <c r="AM8" s="22" t="n"/>
+      <c r="AN8" s="26" t="n"/>
+      <c r="AO8" s="21" t="n"/>
+      <c r="AQ8" s="22" t="n"/>
+      <c r="AR8" s="23" t="n"/>
+      <c r="AS8" s="21" t="n"/>
+      <c r="AU8" s="24" t="n"/>
+      <c r="AV8" s="26" t="n"/>
+    </row>
+    <row r="9" ht="20.1" customHeight="1">
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="30" t="n"/>
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>Messe des défunts</t>
         </is>
       </c>
-      <c r="M8" s="22" t="n"/>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="27" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="S8" s="25" t="n"/>
-      <c r="T8" s="27" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="W8" s="23" t="n"/>
-      <c r="X8" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="Y8" s="22" t="n"/>
-      <c r="AA8" s="25" t="n"/>
-      <c r="AB8" s="24" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AE8" s="23" t="n"/>
-      <c r="AF8" s="24" t="n"/>
-      <c r="AG8" s="22" t="n"/>
-      <c r="AI8" s="25" t="n"/>
-      <c r="AJ8" s="28" t="n"/>
-      <c r="AK8" s="22" t="n"/>
-      <c r="AM8" s="23" t="n"/>
-      <c r="AN8" s="27" t="n"/>
-      <c r="AO8" s="22" t="n"/>
-      <c r="AQ8" s="23" t="n"/>
-      <c r="AR8" s="24" t="n"/>
-      <c r="AS8" s="22" t="n"/>
-      <c r="AU8" s="25" t="n"/>
-      <c r="AV8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="20.1" customHeight="1">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="31" t="n"/>
-      <c r="L9" s="13" t="n"/>
-      <c r="M9" s="29" t="n"/>
-      <c r="N9" s="30" t="n"/>
-      <c r="O9" s="31" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="30" t="n"/>
       <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="29" t="n"/>
-      <c r="R9" s="30" t="n"/>
+      <c r="Q9" s="28" t="n"/>
+      <c r="R9" s="29" t="n"/>
       <c r="S9" s="32" t="n"/>
       <c r="T9" s="33" t="n"/>
-      <c r="U9" s="29" t="n"/>
-      <c r="V9" s="30" t="n"/>
-      <c r="W9" s="31" t="n"/>
+      <c r="U9" s="28" t="n"/>
+      <c r="V9" s="29" t="n"/>
+      <c r="W9" s="30" t="n"/>
       <c r="X9" s="33" t="n"/>
-      <c r="Y9" s="29" t="n"/>
-      <c r="Z9" s="30" t="n"/>
+      <c r="Y9" s="28" t="n"/>
+      <c r="Z9" s="29" t="n"/>
       <c r="AA9" s="32" t="n"/>
-      <c r="AB9" s="26" t="n"/>
-      <c r="AC9" s="29" t="n"/>
-      <c r="AD9" s="30" t="n"/>
-      <c r="AE9" s="31" t="n"/>
-      <c r="AF9" s="26" t="n"/>
-      <c r="AG9" s="29" t="n"/>
-      <c r="AH9" s="30" t="n"/>
+      <c r="AB9" s="31" t="n"/>
+      <c r="AC9" s="28" t="n"/>
+      <c r="AD9" s="29" t="n"/>
+      <c r="AE9" s="30" t="n"/>
+      <c r="AF9" s="31" t="n"/>
+      <c r="AG9" s="28" t="n"/>
+      <c r="AH9" s="29" t="n"/>
       <c r="AI9" s="32" t="n"/>
       <c r="AJ9" s="34" t="n"/>
-      <c r="AK9" s="29" t="n"/>
-      <c r="AL9" s="30" t="n"/>
-      <c r="AM9" s="31" t="n"/>
+      <c r="AK9" s="28" t="n"/>
+      <c r="AL9" s="29" t="n"/>
+      <c r="AM9" s="30" t="n"/>
       <c r="AN9" s="33" t="n"/>
-      <c r="AO9" s="29" t="n"/>
-      <c r="AP9" s="30" t="n"/>
-      <c r="AQ9" s="31" t="n"/>
-      <c r="AR9" s="26" t="n"/>
-      <c r="AS9" s="29" t="n"/>
-      <c r="AT9" s="30" t="n"/>
+      <c r="AO9" s="28" t="n"/>
+      <c r="AP9" s="29" t="n"/>
+      <c r="AQ9" s="30" t="n"/>
+      <c r="AR9" s="31" t="n"/>
+      <c r="AS9" s="28" t="n"/>
+      <c r="AT9" s="29" t="n"/>
       <c r="AU9" s="32" t="n"/>
       <c r="AV9" s="33" t="n"/>
     </row>
@@ -1485,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="19" t="n"/>
+      <c r="D10" s="18" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1509,7 +1500,11 @@
         <v>3</v>
       </c>
       <c r="K10" s="7" t="n"/>
-      <c r="L10" s="26" t="n"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Groupe de prière</t>
+        </is>
+      </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -1519,7 +1514,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="7" t="n"/>
-      <c r="P10" s="19" t="n"/>
+      <c r="P10" s="18" t="n"/>
       <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1539,7 +1534,7 @@
         <v>3</v>
       </c>
       <c r="W10" s="7" t="n"/>
-      <c r="X10" s="19" t="n"/>
+      <c r="X10" s="18" t="n"/>
       <c r="Y10" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1549,7 +1544,7 @@
         <v>3</v>
       </c>
       <c r="AA10" s="12" t="n"/>
-      <c r="AB10" s="19" t="n"/>
+      <c r="AB10" s="18" t="n"/>
       <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1573,7 +1568,7 @@
         <v>3</v>
       </c>
       <c r="AI10" s="7" t="n"/>
-      <c r="AJ10" s="19" t="n"/>
+      <c r="AJ10" s="18" t="n"/>
       <c r="AK10" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1583,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="AM10" s="7" t="n"/>
-      <c r="AN10" s="19" t="n"/>
+      <c r="AN10" s="18" t="n"/>
       <c r="AO10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1607,109 +1602,105 @@
         <v>3</v>
       </c>
       <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="19" t="n"/>
+      <c r="AV10" s="18" t="n"/>
     </row>
     <row r="11" ht="20.1" customHeight="1">
-      <c r="A11" s="22" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="G11" s="23" t="n"/>
+      <c r="A11" s="21" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="G11" s="22" t="n"/>
       <c r="H11" s="39" t="inlineStr">
         <is>
           <t>Rencontre CMP &amp; CPAE</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n"/>
-      <c r="K11" s="23" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="K11" s="22" t="n"/>
       <c r="L11" s="16" t="inlineStr">
         <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="M11" s="22" t="n"/>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="27" t="n"/>
-      <c r="Q11" s="22" t="n"/>
-      <c r="S11" s="25" t="n"/>
-      <c r="T11" s="24" t="n"/>
-      <c r="U11" s="22" t="n"/>
-      <c r="W11" s="23" t="n"/>
-      <c r="X11" s="27" t="n"/>
-      <c r="Y11" s="22" t="n"/>
-      <c r="AA11" s="25" t="n"/>
-      <c r="AB11" s="27" t="n"/>
-      <c r="AC11" s="22" t="n"/>
-      <c r="AE11" s="23" t="n"/>
-      <c r="AF11" s="24" t="n"/>
-      <c r="AG11" s="22" t="n"/>
-      <c r="AI11" s="23" t="n"/>
-      <c r="AJ11" s="27" t="n"/>
-      <c r="AK11" s="22" t="n"/>
-      <c r="AM11" s="23" t="n"/>
-      <c r="AN11" s="27" t="n"/>
-      <c r="AO11" s="22" t="n"/>
-      <c r="AQ11" s="25" t="n"/>
-      <c r="AR11" s="24" t="n"/>
-      <c r="AS11" s="22" t="n"/>
-      <c r="AU11" s="25" t="n"/>
-      <c r="AV11" s="27" t="n"/>
+          <t>Journée d'adoration</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="26" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="S11" s="24" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="AA11" s="24" t="n"/>
+      <c r="AB11" s="26" t="n"/>
+      <c r="AC11" s="21" t="n"/>
+      <c r="AE11" s="22" t="n"/>
+      <c r="AF11" s="23" t="n"/>
+      <c r="AG11" s="21" t="n"/>
+      <c r="AI11" s="22" t="n"/>
+      <c r="AJ11" s="26" t="n"/>
+      <c r="AK11" s="21" t="n"/>
+      <c r="AM11" s="22" t="n"/>
+      <c r="AN11" s="26" t="n"/>
+      <c r="AO11" s="21" t="n"/>
+      <c r="AQ11" s="24" t="n"/>
+      <c r="AR11" s="23" t="n"/>
+      <c r="AS11" s="21" t="n"/>
+      <c r="AU11" s="24" t="n"/>
+      <c r="AV11" s="26" t="n"/>
     </row>
     <row r="12" ht="20.1" customHeight="1">
-      <c r="A12" s="29" t="n"/>
-      <c r="B12" s="30" t="n"/>
-      <c r="C12" s="31" t="n"/>
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="30" t="n"/>
       <c r="D12" s="33" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="30" t="n"/>
       <c r="H12" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="31" t="n"/>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="31" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="30" t="n"/>
+      <c r="L12" s="41" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="29" t="n"/>
+      <c r="O12" s="30" t="n"/>
       <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="29" t="n"/>
-      <c r="R12" s="30" t="n"/>
+      <c r="Q12" s="28" t="n"/>
+      <c r="R12" s="29" t="n"/>
       <c r="S12" s="32" t="n"/>
-      <c r="T12" s="24" t="n"/>
-      <c r="U12" s="29" t="n"/>
-      <c r="V12" s="30" t="n"/>
-      <c r="W12" s="31" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="U12" s="28" t="n"/>
+      <c r="V12" s="29" t="n"/>
+      <c r="W12" s="30" t="n"/>
       <c r="X12" s="33" t="n"/>
-      <c r="Y12" s="29" t="n"/>
-      <c r="Z12" s="30" t="n"/>
+      <c r="Y12" s="28" t="n"/>
+      <c r="Z12" s="29" t="n"/>
       <c r="AA12" s="32" t="n"/>
       <c r="AB12" s="33" t="n"/>
-      <c r="AC12" s="29" t="n"/>
-      <c r="AD12" s="30" t="n"/>
-      <c r="AE12" s="31" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="29" t="n"/>
-      <c r="AH12" s="30" t="n"/>
-      <c r="AI12" s="31" t="n"/>
+      <c r="AC12" s="28" t="n"/>
+      <c r="AD12" s="29" t="n"/>
+      <c r="AE12" s="30" t="n"/>
+      <c r="AF12" s="31" t="n"/>
+      <c r="AG12" s="28" t="n"/>
+      <c r="AH12" s="29" t="n"/>
+      <c r="AI12" s="30" t="n"/>
       <c r="AJ12" s="33" t="n"/>
-      <c r="AK12" s="29" t="n"/>
-      <c r="AL12" s="30" t="n"/>
-      <c r="AM12" s="31" t="n"/>
+      <c r="AK12" s="28" t="n"/>
+      <c r="AL12" s="29" t="n"/>
+      <c r="AM12" s="30" t="n"/>
       <c r="AN12" s="33" t="n"/>
-      <c r="AO12" s="29" t="n"/>
-      <c r="AP12" s="30" t="n"/>
+      <c r="AO12" s="28" t="n"/>
+      <c r="AP12" s="29" t="n"/>
       <c r="AQ12" s="32" t="n"/>
-      <c r="AR12" s="26" t="n"/>
-      <c r="AS12" s="29" t="n"/>
-      <c r="AT12" s="30" t="n"/>
+      <c r="AR12" s="31" t="n"/>
+      <c r="AS12" s="28" t="n"/>
+      <c r="AT12" s="29" t="n"/>
       <c r="AU12" s="32" t="n"/>
       <c r="AV12" s="33" t="n"/>
     </row>
@@ -1723,7 +1714,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="19" t="n"/>
+      <c r="D13" s="18" t="n"/>
       <c r="E13" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1732,8 +1723,8 @@
       <c r="F13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="41" t="n"/>
-      <c r="H13" s="21" t="n"/>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="20" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1743,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="7" t="n"/>
-      <c r="L13" s="42" t="n"/>
+      <c r="L13" s="23" t="n"/>
       <c r="M13" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -1753,7 +1744,7 @@
         <v>4</v>
       </c>
       <c r="O13" s="7" t="n"/>
-      <c r="P13" s="18" t="inlineStr">
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1767,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="S13" s="7" t="n"/>
-      <c r="T13" s="24" t="n"/>
+      <c r="T13" s="23" t="n"/>
       <c r="U13" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1777,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="7" t="n"/>
-      <c r="X13" s="19" t="n"/>
+      <c r="X13" s="18" t="n"/>
       <c r="Y13" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -1800,7 +1791,7 @@
       <c r="AD13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AE13" s="41" t="n"/>
+      <c r="AE13" s="42" t="n"/>
       <c r="AF13" s="43" t="inlineStr">
         <is>
           <t>Concert</t>
@@ -1829,7 +1820,7 @@
         <v>4</v>
       </c>
       <c r="AM13" s="7" t="n"/>
-      <c r="AN13" s="18" t="inlineStr">
+      <c r="AN13" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1857,109 +1848,109 @@
         <v>4</v>
       </c>
       <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="19" t="n"/>
+      <c r="AV13" s="18" t="n"/>
     </row>
     <row r="14" ht="20.1" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="22" t="n"/>
+      <c r="A14" s="21" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="21" t="n"/>
       <c r="G14" s="44" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="K14" s="23" t="n"/>
-      <c r="L14" s="24" t="n"/>
-      <c r="M14" s="22" t="n"/>
-      <c r="O14" s="23" t="n"/>
-      <c r="P14" s="24" t="n"/>
-      <c r="Q14" s="22" t="n"/>
-      <c r="S14" s="23" t="n"/>
-      <c r="T14" s="24" t="n"/>
-      <c r="U14" s="22" t="n"/>
-      <c r="W14" s="23" t="n"/>
-      <c r="X14" s="27" t="n"/>
-      <c r="Y14" s="22" t="n"/>
-      <c r="AA14" s="25" t="n"/>
-      <c r="AB14" s="24" t="n"/>
-      <c r="AC14" s="22" t="n"/>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="21" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="23" t="n"/>
+      <c r="U14" s="21" t="n"/>
+      <c r="W14" s="22" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="21" t="n"/>
+      <c r="AA14" s="24" t="n"/>
+      <c r="AB14" s="23" t="n"/>
+      <c r="AC14" s="21" t="n"/>
       <c r="AE14" s="44" t="n"/>
-      <c r="AF14" s="17" t="inlineStr">
+      <c r="AF14" s="13" t="inlineStr">
         <is>
           <t>Divine Miséricorde</t>
         </is>
       </c>
-      <c r="AG14" s="22" t="n"/>
-      <c r="AI14" s="23" t="n"/>
+      <c r="AG14" s="21" t="n"/>
+      <c r="AI14" s="22" t="n"/>
       <c r="AJ14" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="AK14" s="22" t="n"/>
-      <c r="AM14" s="23" t="n"/>
-      <c r="AN14" s="24" t="n"/>
-      <c r="AO14" s="22" t="n"/>
-      <c r="AQ14" s="25" t="n"/>
-      <c r="AR14" s="24" t="n"/>
-      <c r="AS14" s="22" t="n"/>
-      <c r="AU14" s="25" t="n"/>
-      <c r="AV14" s="27" t="n"/>
+      <c r="AK14" s="21" t="n"/>
+      <c r="AM14" s="22" t="n"/>
+      <c r="AN14" s="23" t="n"/>
+      <c r="AO14" s="21" t="n"/>
+      <c r="AQ14" s="24" t="n"/>
+      <c r="AR14" s="23" t="n"/>
+      <c r="AS14" s="21" t="n"/>
+      <c r="AU14" s="24" t="n"/>
+      <c r="AV14" s="26" t="n"/>
     </row>
     <row r="15" ht="20.1" customHeight="1">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="30" t="n"/>
-      <c r="C15" s="31" t="n"/>
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
       <c r="D15" s="33" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="30" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="29" t="n"/>
       <c r="G15" s="45" t="n"/>
       <c r="H15" s="34" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="30" t="n"/>
-      <c r="K15" s="31" t="n"/>
-      <c r="L15" s="24" t="n"/>
-      <c r="M15" s="29" t="n"/>
-      <c r="N15" s="30" t="n"/>
-      <c r="O15" s="31" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="29" t="n"/>
-      <c r="R15" s="30" t="n"/>
-      <c r="S15" s="31" t="n"/>
-      <c r="T15" s="24" t="n"/>
-      <c r="U15" s="29" t="n"/>
-      <c r="V15" s="30" t="n"/>
-      <c r="W15" s="31" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="29" t="n"/>
+      <c r="K15" s="30" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="28" t="n"/>
+      <c r="N15" s="29" t="n"/>
+      <c r="O15" s="30" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="28" t="n"/>
+      <c r="R15" s="29" t="n"/>
+      <c r="S15" s="30" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="28" t="n"/>
+      <c r="V15" s="29" t="n"/>
+      <c r="W15" s="30" t="n"/>
       <c r="X15" s="33" t="n"/>
-      <c r="Y15" s="29" t="n"/>
-      <c r="Z15" s="30" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="29" t="n"/>
       <c r="AA15" s="32" t="n"/>
-      <c r="AB15" s="26" t="n"/>
-      <c r="AC15" s="29" t="n"/>
-      <c r="AD15" s="30" t="n"/>
+      <c r="AB15" s="31" t="n"/>
+      <c r="AC15" s="28" t="n"/>
+      <c r="AD15" s="29" t="n"/>
       <c r="AE15" s="45" t="n"/>
       <c r="AF15" s="46" t="inlineStr">
         <is>
           <t>J. Sexualité</t>
         </is>
       </c>
-      <c r="AG15" s="29" t="n"/>
-      <c r="AH15" s="30" t="n"/>
-      <c r="AI15" s="31" t="n"/>
+      <c r="AG15" s="28" t="n"/>
+      <c r="AH15" s="29" t="n"/>
+      <c r="AI15" s="30" t="n"/>
       <c r="AJ15" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AK15" s="29" t="n"/>
-      <c r="AL15" s="30" t="n"/>
-      <c r="AM15" s="31" t="n"/>
-      <c r="AN15" s="26" t="n"/>
-      <c r="AO15" s="29" t="n"/>
-      <c r="AP15" s="30" t="n"/>
+      <c r="AK15" s="28" t="n"/>
+      <c r="AL15" s="29" t="n"/>
+      <c r="AM15" s="30" t="n"/>
+      <c r="AN15" s="31" t="n"/>
+      <c r="AO15" s="28" t="n"/>
+      <c r="AP15" s="29" t="n"/>
       <c r="AQ15" s="32" t="n"/>
-      <c r="AR15" s="26" t="n"/>
-      <c r="AS15" s="29" t="n"/>
-      <c r="AT15" s="30" t="n"/>
+      <c r="AR15" s="31" t="n"/>
+      <c r="AS15" s="28" t="n"/>
+      <c r="AT15" s="29" t="n"/>
       <c r="AU15" s="32" t="n"/>
       <c r="AV15" s="33" t="n"/>
     </row>
@@ -1973,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="19" t="n"/>
+      <c r="D16" s="18" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -1983,7 +1974,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="19" t="n"/>
+      <c r="H16" s="18" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1993,7 +1984,7 @@
         <v>5</v>
       </c>
       <c r="K16" s="7" t="n"/>
-      <c r="L16" s="24" t="n"/>
+      <c r="L16" s="23" t="n"/>
       <c r="M16" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -2017,7 +2008,7 @@
         <v>5</v>
       </c>
       <c r="S16" s="7" t="n"/>
-      <c r="T16" s="26" t="n"/>
+      <c r="T16" s="31" t="n"/>
       <c r="U16" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2027,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="W16" s="7" t="n"/>
-      <c r="X16" s="18" t="inlineStr">
+      <c r="X16" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -2041,7 +2032,7 @@
         <v>5</v>
       </c>
       <c r="AA16" s="12" t="n"/>
-      <c r="AB16" s="18" t="inlineStr">
+      <c r="AB16" s="17" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -2055,7 +2046,7 @@
         <v>5</v>
       </c>
       <c r="AE16" s="7" t="n"/>
-      <c r="AF16" s="20" t="inlineStr">
+      <c r="AF16" s="19" t="inlineStr">
         <is>
           <t>Annonciation</t>
         </is>
@@ -2069,7 +2060,7 @@
         <v>5</v>
       </c>
       <c r="AI16" s="7" t="n"/>
-      <c r="AJ16" s="19" t="n"/>
+      <c r="AJ16" s="18" t="n"/>
       <c r="AK16" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2093,7 +2084,7 @@
         <v>5</v>
       </c>
       <c r="AQ16" s="12" t="n"/>
-      <c r="AR16" s="19" t="n"/>
+      <c r="AR16" s="18" t="n"/>
       <c r="AS16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2103,105 +2094,109 @@
         <v>5</v>
       </c>
       <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="19" t="n"/>
+      <c r="AV16" s="18" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1">
-      <c r="A17" s="22" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="22" t="n"/>
-      <c r="G17" s="23" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="22" t="n"/>
-      <c r="K17" s="23" t="n"/>
-      <c r="L17" s="24" t="n"/>
-      <c r="M17" s="22" t="n"/>
-      <c r="O17" s="23" t="n"/>
-      <c r="P17" s="24" t="n"/>
-      <c r="Q17" s="22" t="n"/>
-      <c r="S17" s="23" t="n"/>
+      <c r="A17" s="21" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="26" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="31" t="n"/>
+      <c r="M17" s="21" t="n"/>
+      <c r="O17" s="22" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="21" t="n"/>
+      <c r="S17" s="22" t="n"/>
       <c r="T17" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="U17" s="22" t="n"/>
-      <c r="W17" s="23" t="n"/>
-      <c r="X17" s="24" t="n"/>
-      <c r="Y17" s="22" t="n"/>
-      <c r="AA17" s="25" t="n"/>
-      <c r="AB17" s="24" t="n"/>
-      <c r="AC17" s="22" t="n"/>
-      <c r="AE17" s="23" t="n"/>
-      <c r="AF17" s="24" t="n"/>
-      <c r="AG17" s="22" t="n"/>
-      <c r="AI17" s="23" t="n"/>
-      <c r="AJ17" s="27" t="n"/>
-      <c r="AK17" s="22" t="n"/>
-      <c r="AM17" s="23" t="n"/>
+      <c r="U17" s="21" t="n"/>
+      <c r="W17" s="22" t="n"/>
+      <c r="X17" s="23" t="n"/>
+      <c r="Y17" s="21" t="n"/>
+      <c r="AA17" s="24" t="n"/>
+      <c r="AB17" s="23" t="n"/>
+      <c r="AC17" s="21" t="n"/>
+      <c r="AE17" s="22" t="n"/>
+      <c r="AF17" s="23" t="n"/>
+      <c r="AG17" s="21" t="n"/>
+      <c r="AI17" s="22" t="n"/>
+      <c r="AJ17" s="26" t="n"/>
+      <c r="AK17" s="21" t="n"/>
+      <c r="AM17" s="22" t="n"/>
       <c r="AN17" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="AO17" s="22" t="n"/>
-      <c r="AQ17" s="25" t="n"/>
-      <c r="AR17" s="27" t="n"/>
-      <c r="AS17" s="22" t="n"/>
-      <c r="AU17" s="25" t="n"/>
-      <c r="AV17" s="27" t="n"/>
+      <c r="AO17" s="21" t="n"/>
+      <c r="AQ17" s="24" t="n"/>
+      <c r="AR17" s="26" t="n"/>
+      <c r="AS17" s="21" t="n"/>
+      <c r="AU17" s="24" t="n"/>
+      <c r="AV17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1">
-      <c r="A18" s="29" t="n"/>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="31" t="n"/>
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="30" t="n"/>
       <c r="D18" s="33" t="n"/>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="31" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="30" t="n"/>
       <c r="H18" s="33" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="30" t="n"/>
-      <c r="K18" s="31" t="n"/>
-      <c r="L18" s="24" t="n"/>
-      <c r="M18" s="29" t="n"/>
-      <c r="N18" s="30" t="n"/>
-      <c r="O18" s="31" t="n"/>
-      <c r="P18" s="26" t="n"/>
-      <c r="Q18" s="29" t="n"/>
-      <c r="R18" s="30" t="n"/>
-      <c r="S18" s="31" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>Reunion Paroissiale Chartres 2040</t>
+        </is>
+      </c>
+      <c r="M18" s="28" t="n"/>
+      <c r="N18" s="29" t="n"/>
+      <c r="O18" s="30" t="n"/>
+      <c r="P18" s="31" t="n"/>
+      <c r="Q18" s="28" t="n"/>
+      <c r="R18" s="29" t="n"/>
+      <c r="S18" s="30" t="n"/>
       <c r="T18" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="U18" s="29" t="n"/>
-      <c r="V18" s="30" t="n"/>
-      <c r="W18" s="31" t="n"/>
-      <c r="X18" s="26" t="n"/>
-      <c r="Y18" s="29" t="n"/>
-      <c r="Z18" s="30" t="n"/>
+      <c r="U18" s="28" t="n"/>
+      <c r="V18" s="29" t="n"/>
+      <c r="W18" s="30" t="n"/>
+      <c r="X18" s="31" t="n"/>
+      <c r="Y18" s="28" t="n"/>
+      <c r="Z18" s="29" t="n"/>
       <c r="AA18" s="32" t="n"/>
-      <c r="AB18" s="26" t="n"/>
-      <c r="AC18" s="29" t="n"/>
-      <c r="AD18" s="30" t="n"/>
-      <c r="AE18" s="31" t="n"/>
-      <c r="AF18" s="26" t="n"/>
-      <c r="AG18" s="29" t="n"/>
-      <c r="AH18" s="30" t="n"/>
-      <c r="AI18" s="31" t="n"/>
+      <c r="AB18" s="31" t="n"/>
+      <c r="AC18" s="28" t="n"/>
+      <c r="AD18" s="29" t="n"/>
+      <c r="AE18" s="30" t="n"/>
+      <c r="AF18" s="31" t="n"/>
+      <c r="AG18" s="28" t="n"/>
+      <c r="AH18" s="29" t="n"/>
+      <c r="AI18" s="30" t="n"/>
       <c r="AJ18" s="33" t="n"/>
-      <c r="AK18" s="29" t="n"/>
-      <c r="AL18" s="30" t="n"/>
-      <c r="AM18" s="31" t="n"/>
+      <c r="AK18" s="28" t="n"/>
+      <c r="AL18" s="29" t="n"/>
+      <c r="AM18" s="30" t="n"/>
       <c r="AN18" s="33" t="n"/>
-      <c r="AO18" s="29" t="n"/>
-      <c r="AP18" s="30" t="n"/>
+      <c r="AO18" s="28" t="n"/>
+      <c r="AP18" s="29" t="n"/>
       <c r="AQ18" s="32" t="n"/>
       <c r="AR18" s="33" t="n"/>
-      <c r="AS18" s="29" t="n"/>
-      <c r="AT18" s="30" t="n"/>
+      <c r="AS18" s="28" t="n"/>
+      <c r="AT18" s="29" t="n"/>
       <c r="AU18" s="32" t="n"/>
       <c r="AV18" s="33" t="n"/>
     </row>
@@ -2214,8 +2209,8 @@
       <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="41" t="n"/>
-      <c r="D19" s="21" t="n"/>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="20" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -2239,7 +2234,11 @@
         <v>6</v>
       </c>
       <c r="K19" s="7" t="n"/>
-      <c r="L19" s="26" t="n"/>
+      <c r="L19" s="40" t="inlineStr">
+        <is>
+          <t>Casa</t>
+        </is>
+      </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -2248,7 +2247,7 @@
       <c r="N19" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="O19" s="41" t="n"/>
+      <c r="O19" s="42" t="n"/>
       <c r="P19" s="47" t="inlineStr">
         <is>
           <t>2e dim. de l'Avent</t>
@@ -2319,7 +2318,7 @@
         <v>6</v>
       </c>
       <c r="AI19" s="7" t="n"/>
-      <c r="AJ19" s="17" t="inlineStr">
+      <c r="AJ19" s="13" t="inlineStr">
         <is>
           <t>Ascension</t>
         </is>
@@ -2332,7 +2331,7 @@
       <c r="AL19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="AM19" s="41" t="n"/>
+      <c r="AM19" s="42" t="n"/>
       <c r="AN19" s="35" t="inlineStr">
         <is>
           <t>1ère Communion</t>
@@ -2347,7 +2346,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" s="12" t="n"/>
-      <c r="AR19" s="18" t="inlineStr">
+      <c r="AR19" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -2361,127 +2360,123 @@
         <v>6</v>
       </c>
       <c r="AU19" s="12" t="n"/>
-      <c r="AV19" s="20" t="inlineStr">
+      <c r="AV19" s="19" t="inlineStr">
         <is>
           <t>Transfiguration</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20.1" customHeight="1">
-      <c r="A20" s="22" t="n"/>
+      <c r="A20" s="21" t="n"/>
       <c r="C20" s="44" t="n"/>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="G20" s="23" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="G20" s="22" t="n"/>
       <c r="H20" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="I20" s="22" t="n"/>
-      <c r="K20" s="23" t="n"/>
-      <c r="L20" s="40" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="M20" s="22" t="n"/>
+      <c r="I20" s="21" t="n"/>
+      <c r="K20" s="22" t="n"/>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>Nuit d'adoration</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="n"/>
       <c r="O20" s="44" t="n"/>
-      <c r="P20" s="24" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="S20" s="23" t="n"/>
-      <c r="T20" s="24" t="n"/>
-      <c r="U20" s="22" t="n"/>
-      <c r="W20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="21" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="21" t="n"/>
+      <c r="W20" s="22" t="n"/>
       <c r="X20" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
-      <c r="Y20" s="22" t="n"/>
-      <c r="AA20" s="25" t="n"/>
+      <c r="Y20" s="21" t="n"/>
+      <c r="AA20" s="24" t="n"/>
       <c r="AB20" s="48" t="inlineStr">
         <is>
           <t>WE Prépa Mariage</t>
         </is>
       </c>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AE20" s="23" t="n"/>
+      <c r="AC20" s="21" t="n"/>
+      <c r="AE20" s="22" t="n"/>
       <c r="AF20" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AG20" s="22" t="n"/>
-      <c r="AI20" s="23" t="n"/>
-      <c r="AJ20" s="18" t="n"/>
-      <c r="AK20" s="22" t="n"/>
+      <c r="AG20" s="21" t="n"/>
+      <c r="AI20" s="22" t="n"/>
+      <c r="AJ20" s="17" t="n"/>
+      <c r="AK20" s="21" t="n"/>
       <c r="AM20" s="44" t="n"/>
-      <c r="AN20" s="24" t="n"/>
-      <c r="AO20" s="22" t="n"/>
-      <c r="AQ20" s="25" t="n"/>
-      <c r="AR20" s="24" t="n"/>
-      <c r="AS20" s="22" t="n"/>
-      <c r="AU20" s="25" t="n"/>
-      <c r="AV20" s="24" t="n"/>
+      <c r="AN20" s="23" t="n"/>
+      <c r="AO20" s="21" t="n"/>
+      <c r="AQ20" s="24" t="n"/>
+      <c r="AR20" s="23" t="n"/>
+      <c r="AS20" s="21" t="n"/>
+      <c r="AU20" s="24" t="n"/>
+      <c r="AV20" s="23" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="30" t="n"/>
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="29" t="n"/>
       <c r="C21" s="45" t="n"/>
       <c r="D21" s="34" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="31" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="30" t="n"/>
       <c r="H21" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="30" t="n"/>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>Nuit d'adoration</t>
-        </is>
-      </c>
-      <c r="M21" s="29" t="n"/>
-      <c r="N21" s="30" t="n"/>
+      <c r="I21" s="28" t="n"/>
+      <c r="J21" s="29" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="49" t="n"/>
+      <c r="M21" s="28" t="n"/>
+      <c r="N21" s="29" t="n"/>
       <c r="O21" s="45" t="n"/>
-      <c r="P21" s="26" t="n"/>
-      <c r="Q21" s="29" t="n"/>
-      <c r="R21" s="30" t="n"/>
-      <c r="S21" s="31" t="n"/>
-      <c r="T21" s="24" t="n"/>
-      <c r="U21" s="29" t="n"/>
-      <c r="V21" s="30" t="n"/>
-      <c r="W21" s="31" t="n"/>
+      <c r="P21" s="31" t="n"/>
+      <c r="Q21" s="28" t="n"/>
+      <c r="R21" s="29" t="n"/>
+      <c r="S21" s="30" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="28" t="n"/>
+      <c r="V21" s="29" t="n"/>
+      <c r="W21" s="30" t="n"/>
       <c r="X21" s="33" t="n"/>
-      <c r="Y21" s="29" t="n"/>
-      <c r="Z21" s="30" t="n"/>
+      <c r="Y21" s="28" t="n"/>
+      <c r="Z21" s="29" t="n"/>
       <c r="AA21" s="32" t="n"/>
-      <c r="AB21" s="24" t="n"/>
-      <c r="AC21" s="29" t="n"/>
-      <c r="AD21" s="30" t="n"/>
-      <c r="AE21" s="31" t="n"/>
+      <c r="AB21" s="23" t="n"/>
+      <c r="AC21" s="28" t="n"/>
+      <c r="AD21" s="29" t="n"/>
+      <c r="AE21" s="30" t="n"/>
       <c r="AF21" s="33" t="n"/>
-      <c r="AG21" s="29" t="n"/>
-      <c r="AH21" s="30" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="24" t="n"/>
-      <c r="AK21" s="29" t="n"/>
-      <c r="AL21" s="30" t="n"/>
+      <c r="AG21" s="28" t="n"/>
+      <c r="AH21" s="29" t="n"/>
+      <c r="AI21" s="30" t="n"/>
+      <c r="AJ21" s="23" t="n"/>
+      <c r="AK21" s="28" t="n"/>
+      <c r="AL21" s="29" t="n"/>
       <c r="AM21" s="45" t="n"/>
-      <c r="AN21" s="26" t="n"/>
-      <c r="AO21" s="29" t="n"/>
-      <c r="AP21" s="30" t="n"/>
+      <c r="AN21" s="31" t="n"/>
+      <c r="AO21" s="28" t="n"/>
+      <c r="AP21" s="29" t="n"/>
       <c r="AQ21" s="32" t="n"/>
-      <c r="AR21" s="26" t="n"/>
-      <c r="AS21" s="29" t="n"/>
-      <c r="AT21" s="30" t="n"/>
+      <c r="AR21" s="31" t="n"/>
+      <c r="AS21" s="28" t="n"/>
+      <c r="AT21" s="29" t="n"/>
       <c r="AU21" s="32" t="n"/>
-      <c r="AV21" s="26" t="n"/>
+      <c r="AV21" s="31" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2493,7 +2488,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="19" t="n"/>
+      <c r="D22" s="18" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2503,7 +2498,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="19" t="n"/>
+      <c r="H22" s="18" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2527,7 +2522,7 @@
         <v>7</v>
       </c>
       <c r="O22" s="7" t="n"/>
-      <c r="P22" s="19" t="n"/>
+      <c r="P22" s="18" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2537,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="S22" s="7" t="n"/>
-      <c r="T22" s="24" t="n"/>
+      <c r="T22" s="23" t="n"/>
       <c r="U22" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2546,8 +2541,8 @@
       <c r="V22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="W22" s="41" t="n"/>
-      <c r="X22" s="21" t="n"/>
+      <c r="W22" s="42" t="n"/>
+      <c r="X22" s="20" t="n"/>
       <c r="Y22" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -2557,7 +2552,7 @@
         <v>7</v>
       </c>
       <c r="AA22" s="12" t="n"/>
-      <c r="AB22" s="26" t="n"/>
+      <c r="AB22" s="31" t="n"/>
       <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2567,7 +2562,7 @@
         <v>7</v>
       </c>
       <c r="AE22" s="7" t="n"/>
-      <c r="AF22" s="19" t="n"/>
+      <c r="AF22" s="18" t="n"/>
       <c r="AG22" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2577,7 +2572,7 @@
         <v>7</v>
       </c>
       <c r="AI22" s="7" t="n"/>
-      <c r="AJ22" s="26" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
       <c r="AK22" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2587,7 +2582,7 @@
         <v>7</v>
       </c>
       <c r="AM22" s="7" t="n"/>
-      <c r="AN22" s="19" t="n"/>
+      <c r="AN22" s="18" t="n"/>
       <c r="AO22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2597,7 +2592,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" s="12" t="n"/>
-      <c r="AR22" s="19" t="n"/>
+      <c r="AR22" s="18" t="n"/>
       <c r="AS22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2607,117 +2602,117 @@
         <v>7</v>
       </c>
       <c r="AU22" s="12" t="n"/>
-      <c r="AV22" s="19" t="n"/>
+      <c r="AV22" s="18" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1">
-      <c r="A23" s="22" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="K23" s="23" t="n"/>
+      <c r="A23" s="21" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="26" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="26" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="K23" s="22" t="n"/>
       <c r="L23" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
-      <c r="M23" s="22" t="n"/>
-      <c r="O23" s="23" t="n"/>
-      <c r="P23" s="27" t="n"/>
-      <c r="Q23" s="22" t="n"/>
-      <c r="S23" s="23" t="n"/>
-      <c r="T23" s="24" t="n"/>
-      <c r="U23" s="22" t="n"/>
+      <c r="M23" s="21" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="26" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="23" t="n"/>
+      <c r="U23" s="21" t="n"/>
       <c r="W23" s="44" t="n"/>
-      <c r="X23" s="28" t="n"/>
-      <c r="Y23" s="22" t="n"/>
-      <c r="AA23" s="25" t="n"/>
-      <c r="AB23" s="49" t="inlineStr">
+      <c r="X23" s="27" t="n"/>
+      <c r="Y23" s="21" t="n"/>
+      <c r="AA23" s="24" t="n"/>
+      <c r="AB23" s="50" t="inlineStr">
         <is>
           <t>4e dim. de Carême</t>
         </is>
       </c>
-      <c r="AC23" s="22" t="n"/>
-      <c r="AE23" s="23" t="n"/>
-      <c r="AF23" s="27" t="n"/>
-      <c r="AG23" s="22" t="n"/>
-      <c r="AI23" s="23" t="n"/>
+      <c r="AC23" s="21" t="n"/>
+      <c r="AE23" s="22" t="n"/>
+      <c r="AF23" s="26" t="n"/>
+      <c r="AG23" s="21" t="n"/>
+      <c r="AI23" s="22" t="n"/>
       <c r="AJ23" s="43" t="inlineStr">
         <is>
           <t>Pont de l'Ascension</t>
         </is>
       </c>
-      <c r="AK23" s="22" t="n"/>
-      <c r="AM23" s="23" t="n"/>
-      <c r="AN23" s="27" t="n"/>
-      <c r="AO23" s="22" t="n"/>
-      <c r="AQ23" s="25" t="n"/>
-      <c r="AR23" s="27" t="n"/>
-      <c r="AS23" s="22" t="n"/>
-      <c r="AU23" s="25" t="n"/>
-      <c r="AV23" s="27" t="n"/>
+      <c r="AK23" s="21" t="n"/>
+      <c r="AM23" s="22" t="n"/>
+      <c r="AN23" s="26" t="n"/>
+      <c r="AO23" s="21" t="n"/>
+      <c r="AQ23" s="24" t="n"/>
+      <c r="AR23" s="26" t="n"/>
+      <c r="AS23" s="21" t="n"/>
+      <c r="AU23" s="24" t="n"/>
+      <c r="AV23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1">
-      <c r="A24" s="29" t="n"/>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="31" t="n"/>
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="30" t="n"/>
       <c r="D24" s="33" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="31" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="30" t="n"/>
       <c r="H24" s="33" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="30" t="n"/>
-      <c r="K24" s="31" t="n"/>
+      <c r="I24" s="28" t="n"/>
+      <c r="J24" s="29" t="n"/>
+      <c r="K24" s="30" t="n"/>
       <c r="L24" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="M24" s="29" t="n"/>
-      <c r="N24" s="30" t="n"/>
-      <c r="O24" s="31" t="n"/>
+      <c r="M24" s="28" t="n"/>
+      <c r="N24" s="29" t="n"/>
+      <c r="O24" s="30" t="n"/>
       <c r="P24" s="33" t="n"/>
-      <c r="Q24" s="29" t="n"/>
-      <c r="R24" s="30" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="24" t="n"/>
-      <c r="U24" s="29" t="n"/>
-      <c r="V24" s="30" t="n"/>
+      <c r="Q24" s="28" t="n"/>
+      <c r="R24" s="29" t="n"/>
+      <c r="S24" s="30" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="28" t="n"/>
+      <c r="V24" s="29" t="n"/>
       <c r="W24" s="45" t="n"/>
       <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="29" t="n"/>
-      <c r="Z24" s="30" t="n"/>
+      <c r="Y24" s="28" t="n"/>
+      <c r="Z24" s="29" t="n"/>
       <c r="AA24" s="32" t="n"/>
       <c r="AB24" s="36" t="inlineStr">
         <is>
           <t>2ème scrutin</t>
         </is>
       </c>
-      <c r="AC24" s="29" t="n"/>
-      <c r="AD24" s="30" t="n"/>
-      <c r="AE24" s="31" t="n"/>
+      <c r="AC24" s="28" t="n"/>
+      <c r="AD24" s="29" t="n"/>
+      <c r="AE24" s="30" t="n"/>
       <c r="AF24" s="33" t="n"/>
-      <c r="AG24" s="29" t="n"/>
-      <c r="AH24" s="30" t="n"/>
-      <c r="AI24" s="31" t="n"/>
+      <c r="AG24" s="28" t="n"/>
+      <c r="AH24" s="29" t="n"/>
+      <c r="AI24" s="30" t="n"/>
       <c r="AJ24" s="16" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
-      <c r="AK24" s="29" t="n"/>
-      <c r="AL24" s="30" t="n"/>
-      <c r="AM24" s="31" t="n"/>
+      <c r="AK24" s="28" t="n"/>
+      <c r="AL24" s="29" t="n"/>
+      <c r="AM24" s="30" t="n"/>
       <c r="AN24" s="33" t="n"/>
-      <c r="AO24" s="29" t="n"/>
-      <c r="AP24" s="30" t="n"/>
+      <c r="AO24" s="28" t="n"/>
+      <c r="AP24" s="29" t="n"/>
       <c r="AQ24" s="32" t="n"/>
       <c r="AR24" s="33" t="n"/>
-      <c r="AS24" s="29" t="n"/>
-      <c r="AT24" s="30" t="n"/>
+      <c r="AS24" s="28" t="n"/>
+      <c r="AT24" s="29" t="n"/>
       <c r="AU24" s="32" t="n"/>
       <c r="AV24" s="33" t="n"/>
     </row>
@@ -2731,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Equipe pilote</t>
         </is>
@@ -2745,7 +2740,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="19" t="n"/>
+      <c r="H25" s="18" t="n"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2754,8 +2749,8 @@
       <c r="J25" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K25" s="41" t="n"/>
-      <c r="L25" s="50" t="n"/>
+      <c r="K25" s="42" t="n"/>
+      <c r="L25" s="25" t="n"/>
       <c r="M25" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -2779,7 +2774,7 @@
         <v>8</v>
       </c>
       <c r="S25" s="7" t="n"/>
-      <c r="T25" s="24" t="n"/>
+      <c r="T25" s="23" t="n"/>
       <c r="U25" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2789,7 +2784,7 @@
         <v>8</v>
       </c>
       <c r="W25" s="7" t="n"/>
-      <c r="X25" s="19" t="n"/>
+      <c r="X25" s="18" t="n"/>
       <c r="Y25" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -2799,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="AA25" s="7" t="n"/>
-      <c r="AB25" s="18" t="inlineStr">
+      <c r="AB25" s="17" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -2813,7 +2808,7 @@
         <v>8</v>
       </c>
       <c r="AE25" s="7" t="n"/>
-      <c r="AF25" s="19" t="n"/>
+      <c r="AF25" s="18" t="n"/>
       <c r="AG25" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2823,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="AI25" s="7" t="n"/>
-      <c r="AJ25" s="17" t="inlineStr">
+      <c r="AJ25" s="13" t="inlineStr">
         <is>
           <t>Victoire 1945</t>
         </is>
@@ -2851,7 +2846,7 @@
         <v>8</v>
       </c>
       <c r="AQ25" s="12" t="n"/>
-      <c r="AR25" s="19" t="n"/>
+      <c r="AR25" s="18" t="n"/>
       <c r="AS25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2861,113 +2856,113 @@
         <v>8</v>
       </c>
       <c r="AU25" s="12" t="n"/>
-      <c r="AV25" s="21" t="n"/>
+      <c r="AV25" s="20" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1">
-      <c r="A26" s="22" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="G26" s="23" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="22" t="n"/>
+      <c r="A26" s="21" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="21" t="n"/>
       <c r="K26" s="44" t="n"/>
-      <c r="L26" s="24" t="n"/>
-      <c r="M26" s="22" t="n"/>
-      <c r="O26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="21" t="n"/>
+      <c r="O26" s="22" t="n"/>
       <c r="P26" s="16" t="inlineStr">
         <is>
           <t>Soirée réconciliation</t>
         </is>
       </c>
-      <c r="Q26" s="22" t="n"/>
-      <c r="S26" s="23" t="n"/>
-      <c r="T26" s="26" t="n"/>
-      <c r="U26" s="22" t="n"/>
-      <c r="W26" s="23" t="n"/>
-      <c r="X26" s="27" t="n"/>
-      <c r="Y26" s="22" t="n"/>
-      <c r="AA26" s="23" t="n"/>
-      <c r="AB26" s="24" t="n"/>
-      <c r="AC26" s="22" t="n"/>
-      <c r="AE26" s="23" t="n"/>
-      <c r="AF26" s="27" t="n"/>
-      <c r="AG26" s="22" t="n"/>
-      <c r="AI26" s="23" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="31" t="n"/>
+      <c r="U26" s="21" t="n"/>
+      <c r="W26" s="22" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="21" t="n"/>
+      <c r="AA26" s="22" t="n"/>
+      <c r="AB26" s="23" t="n"/>
+      <c r="AC26" s="21" t="n"/>
+      <c r="AE26" s="22" t="n"/>
+      <c r="AF26" s="26" t="n"/>
+      <c r="AG26" s="21" t="n"/>
+      <c r="AI26" s="22" t="n"/>
       <c r="AJ26" s="16" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
-      <c r="AK26" s="22" t="n"/>
-      <c r="AM26" s="23" t="n"/>
+      <c r="AK26" s="21" t="n"/>
+      <c r="AM26" s="22" t="n"/>
       <c r="AN26" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AO26" s="22" t="n"/>
-      <c r="AQ26" s="25" t="n"/>
-      <c r="AR26" s="27" t="n"/>
-      <c r="AS26" s="22" t="n"/>
-      <c r="AU26" s="25" t="n"/>
-      <c r="AV26" s="28" t="n"/>
+      <c r="AO26" s="21" t="n"/>
+      <c r="AQ26" s="24" t="n"/>
+      <c r="AR26" s="26" t="n"/>
+      <c r="AS26" s="21" t="n"/>
+      <c r="AU26" s="24" t="n"/>
+      <c r="AV26" s="27" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="31" t="n"/>
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="30" t="n"/>
       <c r="H27" s="33" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="30" t="n"/>
+      <c r="I27" s="28" t="n"/>
+      <c r="J27" s="29" t="n"/>
       <c r="K27" s="45" t="n"/>
-      <c r="L27" s="24" t="n"/>
-      <c r="M27" s="29" t="n"/>
-      <c r="N27" s="30" t="n"/>
-      <c r="O27" s="31" t="n"/>
+      <c r="L27" s="23" t="n"/>
+      <c r="M27" s="28" t="n"/>
+      <c r="N27" s="29" t="n"/>
+      <c r="O27" s="30" t="n"/>
       <c r="P27" s="33" t="n"/>
-      <c r="Q27" s="29" t="n"/>
-      <c r="R27" s="30" t="n"/>
-      <c r="S27" s="31" t="n"/>
+      <c r="Q27" s="28" t="n"/>
+      <c r="R27" s="29" t="n"/>
+      <c r="S27" s="30" t="n"/>
       <c r="T27" s="16" t="inlineStr">
         <is>
           <t>Rencontre CCN + Kion</t>
         </is>
       </c>
-      <c r="U27" s="29" t="n"/>
-      <c r="V27" s="30" t="n"/>
-      <c r="W27" s="31" t="n"/>
+      <c r="U27" s="28" t="n"/>
+      <c r="V27" s="29" t="n"/>
+      <c r="W27" s="30" t="n"/>
       <c r="X27" s="33" t="n"/>
-      <c r="Y27" s="29" t="n"/>
-      <c r="Z27" s="30" t="n"/>
-      <c r="AA27" s="31" t="n"/>
-      <c r="AB27" s="24" t="n"/>
-      <c r="AC27" s="29" t="n"/>
-      <c r="AD27" s="30" t="n"/>
-      <c r="AE27" s="31" t="n"/>
+      <c r="Y27" s="28" t="n"/>
+      <c r="Z27" s="29" t="n"/>
+      <c r="AA27" s="30" t="n"/>
+      <c r="AB27" s="23" t="n"/>
+      <c r="AC27" s="28" t="n"/>
+      <c r="AD27" s="29" t="n"/>
+      <c r="AE27" s="30" t="n"/>
       <c r="AF27" s="33" t="n"/>
-      <c r="AG27" s="29" t="n"/>
-      <c r="AH27" s="30" t="n"/>
-      <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="18" t="inlineStr">
+      <c r="AG27" s="28" t="n"/>
+      <c r="AH27" s="29" t="n"/>
+      <c r="AI27" s="30" t="n"/>
+      <c r="AJ27" s="17" t="inlineStr">
         <is>
           <t>WE Ascension</t>
         </is>
       </c>
-      <c r="AK27" s="29" t="n"/>
-      <c r="AL27" s="30" t="n"/>
-      <c r="AM27" s="31" t="n"/>
+      <c r="AK27" s="28" t="n"/>
+      <c r="AL27" s="29" t="n"/>
+      <c r="AM27" s="30" t="n"/>
       <c r="AN27" s="33" t="n"/>
-      <c r="AO27" s="29" t="n"/>
-      <c r="AP27" s="30" t="n"/>
+      <c r="AO27" s="28" t="n"/>
+      <c r="AP27" s="29" t="n"/>
       <c r="AQ27" s="32" t="n"/>
       <c r="AR27" s="33" t="n"/>
-      <c r="AS27" s="29" t="n"/>
-      <c r="AT27" s="30" t="n"/>
+      <c r="AS27" s="28" t="n"/>
+      <c r="AT27" s="29" t="n"/>
       <c r="AU27" s="32" t="n"/>
       <c r="AV27" s="34" t="n"/>
     </row>
@@ -2981,7 +2976,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="19" t="n"/>
+      <c r="D28" s="18" t="n"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2991,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="19" t="n"/>
+      <c r="H28" s="18" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3001,7 +2996,7 @@
         <v>9</v>
       </c>
       <c r="K28" s="7" t="n"/>
-      <c r="L28" s="24" t="n"/>
+      <c r="L28" s="23" t="n"/>
       <c r="M28" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3011,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="O28" s="7" t="n"/>
-      <c r="P28" s="19" t="n"/>
+      <c r="P28" s="18" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3049,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="AA28" s="7" t="n"/>
-      <c r="AB28" s="26" t="n"/>
+      <c r="AB28" s="31" t="n"/>
       <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3059,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="AE28" s="7" t="n"/>
-      <c r="AF28" s="19" t="n"/>
+      <c r="AF28" s="18" t="n"/>
       <c r="AG28" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3068,8 +3063,8 @@
       <c r="AH28" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="AI28" s="41" t="n"/>
-      <c r="AJ28" s="24" t="n"/>
+      <c r="AI28" s="42" t="n"/>
+      <c r="AJ28" s="23" t="n"/>
       <c r="AK28" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3079,7 +3074,7 @@
         <v>9</v>
       </c>
       <c r="AM28" s="7" t="n"/>
-      <c r="AN28" s="19" t="n"/>
+      <c r="AN28" s="18" t="n"/>
       <c r="AO28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3089,7 +3084,7 @@
         <v>9</v>
       </c>
       <c r="AQ28" s="12" t="n"/>
-      <c r="AR28" s="19" t="n"/>
+      <c r="AR28" s="18" t="n"/>
       <c r="AS28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3099,113 +3094,113 @@
         <v>9</v>
       </c>
       <c r="AU28" s="12" t="n"/>
-      <c r="AV28" s="19" t="n"/>
+      <c r="AV28" s="18" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1">
-      <c r="A29" s="22" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="22" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="K29" s="23" t="n"/>
-      <c r="L29" s="26" t="n"/>
-      <c r="M29" s="22" t="n"/>
-      <c r="O29" s="23" t="n"/>
-      <c r="P29" s="27" t="n"/>
-      <c r="Q29" s="22" t="n"/>
-      <c r="S29" s="23" t="n"/>
+      <c r="A29" s="21" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="26" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="26" t="n"/>
+      <c r="I29" s="21" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="31" t="n"/>
+      <c r="M29" s="21" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="26" t="n"/>
+      <c r="Q29" s="21" t="n"/>
+      <c r="S29" s="22" t="n"/>
       <c r="T29" s="36" t="inlineStr">
         <is>
           <t>Prépa Appel décisif</t>
         </is>
       </c>
-      <c r="U29" s="22" t="n"/>
-      <c r="W29" s="23" t="n"/>
+      <c r="U29" s="21" t="n"/>
+      <c r="W29" s="22" t="n"/>
       <c r="X29" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="Y29" s="22" t="n"/>
-      <c r="AA29" s="23" t="n"/>
+      <c r="Y29" s="21" t="n"/>
+      <c r="AA29" s="22" t="n"/>
       <c r="AB29" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="AC29" s="22" t="n"/>
-      <c r="AE29" s="23" t="n"/>
-      <c r="AF29" s="27" t="n"/>
-      <c r="AG29" s="22" t="n"/>
+      <c r="AC29" s="21" t="n"/>
+      <c r="AE29" s="22" t="n"/>
+      <c r="AF29" s="26" t="n"/>
+      <c r="AG29" s="21" t="n"/>
       <c r="AI29" s="44" t="n"/>
-      <c r="AJ29" s="24" t="n"/>
-      <c r="AK29" s="22" t="n"/>
-      <c r="AM29" s="23" t="n"/>
-      <c r="AN29" s="27" t="n"/>
-      <c r="AO29" s="22" t="n"/>
-      <c r="AQ29" s="25" t="n"/>
-      <c r="AR29" s="27" t="n"/>
-      <c r="AS29" s="22" t="n"/>
-      <c r="AU29" s="25" t="n"/>
-      <c r="AV29" s="27" t="n"/>
+      <c r="AJ29" s="23" t="n"/>
+      <c r="AK29" s="21" t="n"/>
+      <c r="AM29" s="22" t="n"/>
+      <c r="AN29" s="26" t="n"/>
+      <c r="AO29" s="21" t="n"/>
+      <c r="AQ29" s="24" t="n"/>
+      <c r="AR29" s="26" t="n"/>
+      <c r="AS29" s="21" t="n"/>
+      <c r="AU29" s="24" t="n"/>
+      <c r="AV29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1">
-      <c r="A30" s="29" t="n"/>
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="31" t="n"/>
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="30" t="n"/>
       <c r="D30" s="33" t="n"/>
-      <c r="E30" s="29" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="31" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="30" t="n"/>
       <c r="H30" s="33" t="n"/>
-      <c r="I30" s="29" t="n"/>
-      <c r="J30" s="30" t="n"/>
-      <c r="K30" s="31" t="n"/>
+      <c r="I30" s="28" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="30" t="n"/>
       <c r="L30" s="51" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
       </c>
-      <c r="M30" s="29" t="n"/>
-      <c r="N30" s="30" t="n"/>
-      <c r="O30" s="31" t="n"/>
+      <c r="M30" s="28" t="n"/>
+      <c r="N30" s="29" t="n"/>
+      <c r="O30" s="30" t="n"/>
       <c r="P30" s="33" t="n"/>
-      <c r="Q30" s="29" t="n"/>
-      <c r="R30" s="30" t="n"/>
-      <c r="S30" s="31" t="n"/>
+      <c r="Q30" s="28" t="n"/>
+      <c r="R30" s="29" t="n"/>
+      <c r="S30" s="30" t="n"/>
       <c r="T30" s="33" t="n"/>
-      <c r="U30" s="29" t="n"/>
-      <c r="V30" s="30" t="n"/>
-      <c r="W30" s="31" t="n"/>
+      <c r="U30" s="28" t="n"/>
+      <c r="V30" s="29" t="n"/>
+      <c r="W30" s="30" t="n"/>
       <c r="X30" s="33" t="n"/>
-      <c r="Y30" s="29" t="n"/>
-      <c r="Z30" s="30" t="n"/>
-      <c r="AA30" s="31" t="n"/>
+      <c r="Y30" s="28" t="n"/>
+      <c r="Z30" s="29" t="n"/>
+      <c r="AA30" s="30" t="n"/>
       <c r="AB30" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AC30" s="29" t="n"/>
-      <c r="AD30" s="30" t="n"/>
-      <c r="AE30" s="31" t="n"/>
+      <c r="AC30" s="28" t="n"/>
+      <c r="AD30" s="29" t="n"/>
+      <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="33" t="n"/>
-      <c r="AG30" s="29" t="n"/>
-      <c r="AH30" s="30" t="n"/>
+      <c r="AG30" s="28" t="n"/>
+      <c r="AH30" s="29" t="n"/>
       <c r="AI30" s="45" t="n"/>
-      <c r="AJ30" s="26" t="n"/>
-      <c r="AK30" s="29" t="n"/>
-      <c r="AL30" s="30" t="n"/>
-      <c r="AM30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="28" t="n"/>
+      <c r="AL30" s="29" t="n"/>
+      <c r="AM30" s="30" t="n"/>
       <c r="AN30" s="33" t="n"/>
-      <c r="AO30" s="29" t="n"/>
-      <c r="AP30" s="30" t="n"/>
+      <c r="AO30" s="28" t="n"/>
+      <c r="AP30" s="29" t="n"/>
       <c r="AQ30" s="32" t="n"/>
       <c r="AR30" s="33" t="n"/>
-      <c r="AS30" s="29" t="n"/>
-      <c r="AT30" s="30" t="n"/>
+      <c r="AS30" s="28" t="n"/>
+      <c r="AT30" s="29" t="n"/>
       <c r="AU30" s="32" t="n"/>
       <c r="AV30" s="33" t="n"/>
     </row>
@@ -3219,7 +3214,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="19" t="n"/>
+      <c r="D31" s="18" t="n"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3243,7 +3238,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="26" t="n"/>
+      <c r="L31" s="31" t="n"/>
       <c r="M31" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3253,7 +3248,7 @@
         <v>10</v>
       </c>
       <c r="O31" s="7" t="n"/>
-      <c r="P31" s="19" t="n"/>
+      <c r="P31" s="18" t="n"/>
       <c r="Q31" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3262,8 +3257,8 @@
       <c r="R31" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S31" s="41" t="n"/>
-      <c r="T31" s="18" t="inlineStr">
+      <c r="S31" s="42" t="n"/>
+      <c r="T31" s="17" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3291,7 +3286,7 @@
         <v>10</v>
       </c>
       <c r="AA31" s="7" t="n"/>
-      <c r="AB31" s="19" t="n"/>
+      <c r="AB31" s="18" t="n"/>
       <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3315,7 +3310,7 @@
         <v>10</v>
       </c>
       <c r="AI31" s="7" t="n"/>
-      <c r="AJ31" s="19" t="n"/>
+      <c r="AJ31" s="18" t="n"/>
       <c r="AK31" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3325,7 +3320,7 @@
         <v>10</v>
       </c>
       <c r="AM31" s="7" t="n"/>
-      <c r="AN31" s="19" t="n"/>
+      <c r="AN31" s="18" t="n"/>
       <c r="AO31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3335,7 +3330,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" s="12" t="n"/>
-      <c r="AR31" s="18" t="inlineStr">
+      <c r="AR31" s="17" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3349,113 +3344,113 @@
         <v>10</v>
       </c>
       <c r="AU31" s="12" t="n"/>
-      <c r="AV31" s="19" t="n"/>
+      <c r="AV31" s="18" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1">
-      <c r="A32" s="22" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="A32" s="21" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="21" t="n"/>
+      <c r="G32" s="22" t="n"/>
       <c r="H32" s="16" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
       </c>
-      <c r="I32" s="22" t="n"/>
-      <c r="K32" s="23" t="n"/>
+      <c r="I32" s="21" t="n"/>
+      <c r="K32" s="22" t="n"/>
       <c r="L32" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="M32" s="22" t="n"/>
-      <c r="O32" s="23" t="n"/>
-      <c r="P32" s="27" t="n"/>
-      <c r="Q32" s="22" t="n"/>
+      <c r="M32" s="21" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="26" t="n"/>
+      <c r="Q32" s="21" t="n"/>
       <c r="S32" s="44" t="n"/>
-      <c r="T32" s="24" t="n"/>
-      <c r="U32" s="22" t="n"/>
-      <c r="W32" s="23" t="n"/>
-      <c r="X32" s="24" t="n"/>
-      <c r="Y32" s="22" t="n"/>
-      <c r="AA32" s="23" t="n"/>
-      <c r="AB32" s="27" t="n"/>
-      <c r="AC32" s="22" t="n"/>
-      <c r="AE32" s="23" t="n"/>
+      <c r="T32" s="23" t="n"/>
+      <c r="U32" s="21" t="n"/>
+      <c r="W32" s="22" t="n"/>
+      <c r="X32" s="23" t="n"/>
+      <c r="Y32" s="21" t="n"/>
+      <c r="AA32" s="22" t="n"/>
+      <c r="AB32" s="26" t="n"/>
+      <c r="AC32" s="21" t="n"/>
+      <c r="AE32" s="22" t="n"/>
       <c r="AF32" s="36" t="inlineStr">
         <is>
           <t>Formation Eucharistie</t>
         </is>
       </c>
-      <c r="AG32" s="22" t="n"/>
-      <c r="AI32" s="23" t="n"/>
-      <c r="AJ32" s="27" t="n"/>
-      <c r="AK32" s="22" t="n"/>
-      <c r="AM32" s="23" t="n"/>
-      <c r="AN32" s="27" t="n"/>
-      <c r="AO32" s="22" t="n"/>
-      <c r="AQ32" s="25" t="n"/>
-      <c r="AR32" s="24" t="n"/>
-      <c r="AS32" s="22" t="n"/>
-      <c r="AU32" s="25" t="n"/>
-      <c r="AV32" s="27" t="n"/>
+      <c r="AG32" s="21" t="n"/>
+      <c r="AI32" s="22" t="n"/>
+      <c r="AJ32" s="26" t="n"/>
+      <c r="AK32" s="21" t="n"/>
+      <c r="AM32" s="22" t="n"/>
+      <c r="AN32" s="26" t="n"/>
+      <c r="AO32" s="21" t="n"/>
+      <c r="AQ32" s="24" t="n"/>
+      <c r="AR32" s="23" t="n"/>
+      <c r="AS32" s="21" t="n"/>
+      <c r="AU32" s="24" t="n"/>
+      <c r="AV32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="31" t="n"/>
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="30" t="n"/>
       <c r="D33" s="33" t="n"/>
-      <c r="E33" s="29" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="31" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="30" t="n"/>
       <c r="H33" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="I33" s="29" t="n"/>
-      <c r="J33" s="30" t="n"/>
-      <c r="K33" s="31" t="n"/>
+      <c r="I33" s="28" t="n"/>
+      <c r="J33" s="29" t="n"/>
+      <c r="K33" s="30" t="n"/>
       <c r="L33" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="M33" s="29" t="n"/>
-      <c r="N33" s="30" t="n"/>
-      <c r="O33" s="31" t="n"/>
+      <c r="M33" s="28" t="n"/>
+      <c r="N33" s="29" t="n"/>
+      <c r="O33" s="30" t="n"/>
       <c r="P33" s="33" t="n"/>
-      <c r="Q33" s="29" t="n"/>
-      <c r="R33" s="30" t="n"/>
+      <c r="Q33" s="28" t="n"/>
+      <c r="R33" s="29" t="n"/>
       <c r="S33" s="45" t="n"/>
-      <c r="T33" s="26" t="n"/>
-      <c r="U33" s="29" t="n"/>
-      <c r="V33" s="30" t="n"/>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="29" t="n"/>
-      <c r="Z33" s="30" t="n"/>
-      <c r="AA33" s="31" t="n"/>
+      <c r="T33" s="31" t="n"/>
+      <c r="U33" s="28" t="n"/>
+      <c r="V33" s="29" t="n"/>
+      <c r="W33" s="30" t="n"/>
+      <c r="X33" s="31" t="n"/>
+      <c r="Y33" s="28" t="n"/>
+      <c r="Z33" s="29" t="n"/>
+      <c r="AA33" s="30" t="n"/>
       <c r="AB33" s="33" t="n"/>
-      <c r="AC33" s="29" t="n"/>
-      <c r="AD33" s="30" t="n"/>
-      <c r="AE33" s="31" t="n"/>
+      <c r="AC33" s="28" t="n"/>
+      <c r="AD33" s="29" t="n"/>
+      <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="33" t="n"/>
-      <c r="AG33" s="29" t="n"/>
-      <c r="AH33" s="30" t="n"/>
-      <c r="AI33" s="31" t="n"/>
+      <c r="AG33" s="28" t="n"/>
+      <c r="AH33" s="29" t="n"/>
+      <c r="AI33" s="30" t="n"/>
       <c r="AJ33" s="33" t="n"/>
-      <c r="AK33" s="29" t="n"/>
-      <c r="AL33" s="30" t="n"/>
-      <c r="AM33" s="31" t="n"/>
+      <c r="AK33" s="28" t="n"/>
+      <c r="AL33" s="29" t="n"/>
+      <c r="AM33" s="30" t="n"/>
       <c r="AN33" s="33" t="n"/>
-      <c r="AO33" s="29" t="n"/>
-      <c r="AP33" s="30" t="n"/>
+      <c r="AO33" s="28" t="n"/>
+      <c r="AP33" s="29" t="n"/>
       <c r="AQ33" s="32" t="n"/>
-      <c r="AR33" s="26" t="n"/>
-      <c r="AS33" s="29" t="n"/>
-      <c r="AT33" s="30" t="n"/>
+      <c r="AR33" s="31" t="n"/>
+      <c r="AS33" s="28" t="n"/>
+      <c r="AT33" s="29" t="n"/>
       <c r="AU33" s="32" t="n"/>
       <c r="AV33" s="33" t="n"/>
     </row>
@@ -3469,7 +3464,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="19" t="n"/>
+      <c r="D34" s="18" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3478,7 +3473,7 @@
       <c r="F34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="41" t="n"/>
+      <c r="G34" s="42" t="n"/>
       <c r="H34" s="40" t="inlineStr">
         <is>
           <t>Baptême</t>
@@ -3493,7 +3488,7 @@
         <v>11</v>
       </c>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="17" t="inlineStr">
+      <c r="L34" s="13" t="inlineStr">
         <is>
           <t>Armistice 1918</t>
         </is>
@@ -3521,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="S34" s="7" t="n"/>
-      <c r="T34" s="19" t="n"/>
+      <c r="T34" s="18" t="n"/>
       <c r="U34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3531,7 +3526,7 @@
         <v>11</v>
       </c>
       <c r="W34" s="7" t="n"/>
-      <c r="X34" s="19" t="n"/>
+      <c r="X34" s="18" t="n"/>
       <c r="Y34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3554,8 +3549,8 @@
       <c r="AD34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="AE34" s="41" t="n"/>
-      <c r="AF34" s="18" t="inlineStr">
+      <c r="AE34" s="42" t="n"/>
+      <c r="AF34" s="17" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3583,7 +3578,7 @@
         <v>11</v>
       </c>
       <c r="AM34" s="7" t="n"/>
-      <c r="AN34" s="19" t="n"/>
+      <c r="AN34" s="18" t="n"/>
       <c r="AO34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3593,7 +3588,7 @@
         <v>11</v>
       </c>
       <c r="AQ34" s="12" t="n"/>
-      <c r="AR34" s="21" t="n"/>
+      <c r="AR34" s="20" t="n"/>
       <c r="AS34" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3603,109 +3598,109 @@
         <v>11</v>
       </c>
       <c r="AU34" s="12" t="n"/>
-      <c r="AV34" s="19" t="n"/>
+      <c r="AV34" s="18" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1">
-      <c r="A35" s="22" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="22" t="n"/>
+      <c r="A35" s="21" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="26" t="n"/>
+      <c r="E35" s="21" t="n"/>
       <c r="G35" s="44" t="n"/>
       <c r="H35" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="I35" s="22" t="n"/>
-      <c r="K35" s="23" t="n"/>
+      <c r="I35" s="21" t="n"/>
+      <c r="K35" s="22" t="n"/>
       <c r="L35" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="M35" s="22" t="n"/>
-      <c r="O35" s="23" t="n"/>
-      <c r="P35" s="24" t="n"/>
-      <c r="Q35" s="22" t="n"/>
-      <c r="S35" s="23" t="n"/>
-      <c r="T35" s="27" t="n"/>
-      <c r="U35" s="22" t="n"/>
-      <c r="W35" s="23" t="n"/>
-      <c r="X35" s="27" t="n"/>
-      <c r="Y35" s="22" t="n"/>
-      <c r="AA35" s="23" t="n"/>
-      <c r="AB35" s="24" t="n"/>
-      <c r="AC35" s="22" t="n"/>
+      <c r="M35" s="21" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="23" t="n"/>
+      <c r="Q35" s="21" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="26" t="n"/>
+      <c r="U35" s="21" t="n"/>
+      <c r="W35" s="22" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="21" t="n"/>
+      <c r="AA35" s="22" t="n"/>
+      <c r="AB35" s="23" t="n"/>
+      <c r="AC35" s="21" t="n"/>
       <c r="AE35" s="44" t="n"/>
-      <c r="AF35" s="24" t="n"/>
-      <c r="AG35" s="22" t="n"/>
-      <c r="AI35" s="23" t="n"/>
+      <c r="AF35" s="23" t="n"/>
+      <c r="AG35" s="21" t="n"/>
+      <c r="AI35" s="22" t="n"/>
       <c r="AJ35" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AK35" s="22" t="n"/>
-      <c r="AM35" s="23" t="n"/>
-      <c r="AN35" s="27" t="n"/>
-      <c r="AO35" s="22" t="n"/>
-      <c r="AQ35" s="25" t="n"/>
-      <c r="AR35" s="28" t="n"/>
-      <c r="AS35" s="22" t="n"/>
-      <c r="AU35" s="25" t="n"/>
-      <c r="AV35" s="27" t="n"/>
+      <c r="AK35" s="21" t="n"/>
+      <c r="AM35" s="22" t="n"/>
+      <c r="AN35" s="26" t="n"/>
+      <c r="AO35" s="21" t="n"/>
+      <c r="AQ35" s="24" t="n"/>
+      <c r="AR35" s="27" t="n"/>
+      <c r="AS35" s="21" t="n"/>
+      <c r="AU35" s="24" t="n"/>
+      <c r="AV35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1">
-      <c r="A36" s="29" t="n"/>
-      <c r="B36" s="30" t="n"/>
-      <c r="C36" s="31" t="n"/>
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="30" t="n"/>
       <c r="D36" s="33" t="n"/>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="30" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="29" t="n"/>
       <c r="G36" s="45" t="n"/>
       <c r="H36" s="52" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="30" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="42" t="inlineStr">
+      <c r="I36" s="28" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="41" t="inlineStr">
         <is>
           <t>Père Pascal en Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="M36" s="29" t="n"/>
-      <c r="N36" s="30" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="26" t="n"/>
-      <c r="Q36" s="29" t="n"/>
-      <c r="R36" s="30" t="n"/>
-      <c r="S36" s="31" t="n"/>
+      <c r="M36" s="28" t="n"/>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="30" t="n"/>
+      <c r="P36" s="31" t="n"/>
+      <c r="Q36" s="28" t="n"/>
+      <c r="R36" s="29" t="n"/>
+      <c r="S36" s="30" t="n"/>
       <c r="T36" s="33" t="n"/>
-      <c r="U36" s="29" t="n"/>
-      <c r="V36" s="30" t="n"/>
-      <c r="W36" s="31" t="n"/>
+      <c r="U36" s="28" t="n"/>
+      <c r="V36" s="29" t="n"/>
+      <c r="W36" s="30" t="n"/>
       <c r="X36" s="33" t="n"/>
-      <c r="Y36" s="29" t="n"/>
-      <c r="Z36" s="30" t="n"/>
-      <c r="AA36" s="31" t="n"/>
-      <c r="AB36" s="26" t="n"/>
-      <c r="AC36" s="29" t="n"/>
-      <c r="AD36" s="30" t="n"/>
+      <c r="Y36" s="28" t="n"/>
+      <c r="Z36" s="29" t="n"/>
+      <c r="AA36" s="30" t="n"/>
+      <c r="AB36" s="31" t="n"/>
+      <c r="AC36" s="28" t="n"/>
+      <c r="AD36" s="29" t="n"/>
       <c r="AE36" s="45" t="n"/>
-      <c r="AF36" s="26" t="n"/>
-      <c r="AG36" s="29" t="n"/>
-      <c r="AH36" s="30" t="n"/>
-      <c r="AI36" s="31" t="n"/>
+      <c r="AF36" s="31" t="n"/>
+      <c r="AG36" s="28" t="n"/>
+      <c r="AH36" s="29" t="n"/>
+      <c r="AI36" s="30" t="n"/>
       <c r="AJ36" s="33" t="n"/>
-      <c r="AK36" s="29" t="n"/>
-      <c r="AL36" s="30" t="n"/>
-      <c r="AM36" s="31" t="n"/>
+      <c r="AK36" s="28" t="n"/>
+      <c r="AL36" s="29" t="n"/>
+      <c r="AM36" s="30" t="n"/>
       <c r="AN36" s="33" t="n"/>
-      <c r="AO36" s="29" t="n"/>
-      <c r="AP36" s="30" t="n"/>
+      <c r="AO36" s="28" t="n"/>
+      <c r="AP36" s="29" t="n"/>
       <c r="AQ36" s="32" t="n"/>
       <c r="AR36" s="34" t="n"/>
-      <c r="AS36" s="29" t="n"/>
-      <c r="AT36" s="30" t="n"/>
+      <c r="AS36" s="28" t="n"/>
+      <c r="AT36" s="29" t="n"/>
       <c r="AU36" s="32" t="n"/>
       <c r="AV36" s="33" t="n"/>
     </row>
@@ -3719,7 +3714,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Rentrée Cté</t>
         </is>
@@ -3733,7 +3728,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="24" t="n"/>
+      <c r="H37" s="23" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3743,7 +3738,7 @@
         <v>12</v>
       </c>
       <c r="K37" s="7" t="n"/>
-      <c r="L37" s="24" t="n"/>
+      <c r="L37" s="23" t="n"/>
       <c r="M37" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -3781,7 +3776,7 @@
         <v>12</v>
       </c>
       <c r="W37" s="7" t="n"/>
-      <c r="X37" s="19" t="n"/>
+      <c r="X37" s="18" t="n"/>
       <c r="Y37" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3791,7 +3786,7 @@
         <v>12</v>
       </c>
       <c r="AA37" s="7" t="n"/>
-      <c r="AB37" s="19" t="n"/>
+      <c r="AB37" s="18" t="n"/>
       <c r="AC37" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3801,7 +3796,7 @@
         <v>12</v>
       </c>
       <c r="AE37" s="7" t="n"/>
-      <c r="AF37" s="19" t="n"/>
+      <c r="AF37" s="18" t="n"/>
       <c r="AG37" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3811,7 +3806,7 @@
         <v>12</v>
       </c>
       <c r="AI37" s="7" t="n"/>
-      <c r="AJ37" s="19" t="n"/>
+      <c r="AJ37" s="18" t="n"/>
       <c r="AK37" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3835,7 +3830,7 @@
         <v>12</v>
       </c>
       <c r="AQ37" s="12" t="n"/>
-      <c r="AR37" s="19" t="n"/>
+      <c r="AR37" s="18" t="n"/>
       <c r="AS37" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3845,105 +3840,105 @@
         <v>12</v>
       </c>
       <c r="AU37" s="12" t="n"/>
-      <c r="AV37" s="19" t="n"/>
+      <c r="AV37" s="18" t="n"/>
     </row>
     <row r="38" ht="20.1" customHeight="1">
-      <c r="A38" s="22" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="G38" s="23" t="n"/>
-      <c r="H38" s="24" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="K38" s="23" t="n"/>
-      <c r="L38" s="24" t="n"/>
-      <c r="M38" s="22" t="n"/>
-      <c r="O38" s="23" t="n"/>
-      <c r="P38" s="18" t="inlineStr">
+      <c r="A38" s="21" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="21" t="n"/>
+      <c r="K38" s="22" t="n"/>
+      <c r="L38" s="23" t="n"/>
+      <c r="M38" s="21" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="17" t="inlineStr">
         <is>
           <t>WE Frat ccn</t>
         </is>
       </c>
-      <c r="Q38" s="22" t="n"/>
-      <c r="S38" s="23" t="n"/>
+      <c r="Q38" s="21" t="n"/>
+      <c r="S38" s="22" t="n"/>
       <c r="T38" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="U38" s="22" t="n"/>
-      <c r="W38" s="23" t="n"/>
-      <c r="X38" s="27" t="n"/>
-      <c r="Y38" s="22" t="n"/>
-      <c r="AA38" s="23" t="n"/>
-      <c r="AB38" s="27" t="n"/>
-      <c r="AC38" s="22" t="n"/>
-      <c r="AE38" s="23" t="n"/>
-      <c r="AF38" s="27" t="n"/>
-      <c r="AG38" s="22" t="n"/>
-      <c r="AI38" s="23" t="n"/>
-      <c r="AJ38" s="27" t="n"/>
-      <c r="AK38" s="22" t="n"/>
-      <c r="AM38" s="23" t="n"/>
+      <c r="U38" s="21" t="n"/>
+      <c r="W38" s="22" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="21" t="n"/>
+      <c r="AA38" s="22" t="n"/>
+      <c r="AB38" s="26" t="n"/>
+      <c r="AC38" s="21" t="n"/>
+      <c r="AE38" s="22" t="n"/>
+      <c r="AF38" s="26" t="n"/>
+      <c r="AG38" s="21" t="n"/>
+      <c r="AI38" s="22" t="n"/>
+      <c r="AJ38" s="26" t="n"/>
+      <c r="AK38" s="21" t="n"/>
+      <c r="AM38" s="22" t="n"/>
       <c r="AN38" s="36" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
-      <c r="AO38" s="22" t="n"/>
-      <c r="AQ38" s="25" t="n"/>
-      <c r="AR38" s="27" t="n"/>
-      <c r="AS38" s="22" t="n"/>
-      <c r="AU38" s="25" t="n"/>
-      <c r="AV38" s="27" t="n"/>
+      <c r="AO38" s="21" t="n"/>
+      <c r="AQ38" s="24" t="n"/>
+      <c r="AR38" s="26" t="n"/>
+      <c r="AS38" s="21" t="n"/>
+      <c r="AU38" s="24" t="n"/>
+      <c r="AV38" s="26" t="n"/>
     </row>
     <row r="39" ht="20.1" customHeight="1">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="31" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="24" t="n"/>
-      <c r="I39" s="29" t="n"/>
-      <c r="J39" s="30" t="n"/>
-      <c r="K39" s="31" t="n"/>
-      <c r="L39" s="24" t="n"/>
-      <c r="M39" s="29" t="n"/>
-      <c r="N39" s="30" t="n"/>
-      <c r="O39" s="31" t="n"/>
-      <c r="P39" s="24" t="n"/>
-      <c r="Q39" s="29" t="n"/>
-      <c r="R39" s="30" t="n"/>
-      <c r="S39" s="31" t="n"/>
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="28" t="n"/>
+      <c r="J39" s="29" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="23" t="n"/>
+      <c r="M39" s="28" t="n"/>
+      <c r="N39" s="29" t="n"/>
+      <c r="O39" s="30" t="n"/>
+      <c r="P39" s="23" t="n"/>
+      <c r="Q39" s="28" t="n"/>
+      <c r="R39" s="29" t="n"/>
+      <c r="S39" s="30" t="n"/>
       <c r="T39" s="33" t="n"/>
-      <c r="U39" s="29" t="n"/>
-      <c r="V39" s="30" t="n"/>
-      <c r="W39" s="31" t="n"/>
+      <c r="U39" s="28" t="n"/>
+      <c r="V39" s="29" t="n"/>
+      <c r="W39" s="30" t="n"/>
       <c r="X39" s="33" t="n"/>
-      <c r="Y39" s="29" t="n"/>
-      <c r="Z39" s="30" t="n"/>
-      <c r="AA39" s="31" t="n"/>
+      <c r="Y39" s="28" t="n"/>
+      <c r="Z39" s="29" t="n"/>
+      <c r="AA39" s="30" t="n"/>
       <c r="AB39" s="33" t="n"/>
-      <c r="AC39" s="29" t="n"/>
-      <c r="AD39" s="30" t="n"/>
-      <c r="AE39" s="31" t="n"/>
+      <c r="AC39" s="28" t="n"/>
+      <c r="AD39" s="29" t="n"/>
+      <c r="AE39" s="30" t="n"/>
       <c r="AF39" s="33" t="n"/>
-      <c r="AG39" s="29" t="n"/>
-      <c r="AH39" s="30" t="n"/>
-      <c r="AI39" s="31" t="n"/>
+      <c r="AG39" s="28" t="n"/>
+      <c r="AH39" s="29" t="n"/>
+      <c r="AI39" s="30" t="n"/>
       <c r="AJ39" s="33" t="n"/>
-      <c r="AK39" s="29" t="n"/>
-      <c r="AL39" s="30" t="n"/>
-      <c r="AM39" s="31" t="n"/>
+      <c r="AK39" s="28" t="n"/>
+      <c r="AL39" s="29" t="n"/>
+      <c r="AM39" s="30" t="n"/>
       <c r="AN39" s="33" t="n"/>
-      <c r="AO39" s="29" t="n"/>
-      <c r="AP39" s="30" t="n"/>
+      <c r="AO39" s="28" t="n"/>
+      <c r="AP39" s="29" t="n"/>
       <c r="AQ39" s="32" t="n"/>
       <c r="AR39" s="33" t="n"/>
-      <c r="AS39" s="29" t="n"/>
-      <c r="AT39" s="30" t="n"/>
+      <c r="AS39" s="28" t="n"/>
+      <c r="AT39" s="29" t="n"/>
       <c r="AU39" s="32" t="n"/>
       <c r="AV39" s="33" t="n"/>
     </row>
@@ -3956,8 +3951,8 @@
       <c r="B40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C40" s="41" t="n"/>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="C40" s="42" t="n"/>
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Rentrée Kion</t>
         </is>
@@ -3971,7 +3966,7 @@
         <v>13</v>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="24" t="n"/>
+      <c r="H40" s="23" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3981,7 +3976,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="7" t="n"/>
-      <c r="L40" s="24" t="n"/>
+      <c r="L40" s="23" t="n"/>
       <c r="M40" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -3990,8 +3985,8 @@
       <c r="N40" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="O40" s="41" t="n"/>
-      <c r="P40" s="26" t="n"/>
+      <c r="O40" s="42" t="n"/>
+      <c r="P40" s="31" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4001,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="7" t="n"/>
-      <c r="T40" s="19" t="n"/>
+      <c r="T40" s="18" t="n"/>
       <c r="U40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -4011,7 +4006,7 @@
         <v>13</v>
       </c>
       <c r="W40" s="7" t="n"/>
-      <c r="X40" s="19" t="n"/>
+      <c r="X40" s="18" t="n"/>
       <c r="Y40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -4021,7 +4016,7 @@
         <v>13</v>
       </c>
       <c r="AA40" s="7" t="n"/>
-      <c r="AB40" s="18" t="inlineStr">
+      <c r="AB40" s="17" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -4062,8 +4057,8 @@
       <c r="AL40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="AM40" s="41" t="n"/>
-      <c r="AN40" s="21" t="n"/>
+      <c r="AM40" s="42" t="n"/>
+      <c r="AN40" s="20" t="n"/>
       <c r="AO40" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4073,7 +4068,7 @@
         <v>13</v>
       </c>
       <c r="AQ40" s="12" t="n"/>
-      <c r="AR40" s="19" t="n"/>
+      <c r="AR40" s="18" t="n"/>
       <c r="AS40" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4083,109 +4078,109 @@
         <v>13</v>
       </c>
       <c r="AU40" s="12" t="n"/>
-      <c r="AV40" s="19" t="n"/>
+      <c r="AV40" s="18" t="n"/>
     </row>
     <row r="41" ht="20.1" customHeight="1">
-      <c r="A41" s="22" t="n"/>
+      <c r="A41" s="21" t="n"/>
       <c r="C41" s="44" t="n"/>
-      <c r="D41" s="24" t="n"/>
-      <c r="E41" s="22" t="n"/>
-      <c r="G41" s="23" t="n"/>
-      <c r="H41" s="26" t="n"/>
-      <c r="I41" s="22" t="n"/>
-      <c r="K41" s="23" t="n"/>
-      <c r="L41" s="24" t="n"/>
-      <c r="M41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="31" t="n"/>
+      <c r="I41" s="21" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="23" t="n"/>
+      <c r="M41" s="21" t="n"/>
       <c r="O41" s="44" t="n"/>
-      <c r="P41" s="49" t="inlineStr">
+      <c r="P41" s="50" t="inlineStr">
         <is>
           <t>3e dim. de l'Avent</t>
         </is>
       </c>
-      <c r="Q41" s="22" t="n"/>
-      <c r="S41" s="23" t="n"/>
-      <c r="T41" s="27" t="n"/>
-      <c r="U41" s="22" t="n"/>
-      <c r="W41" s="23" t="n"/>
-      <c r="X41" s="27" t="n"/>
-      <c r="Y41" s="22" t="n"/>
-      <c r="AA41" s="23" t="n"/>
-      <c r="AB41" s="24" t="n"/>
-      <c r="AC41" s="22" t="n"/>
-      <c r="AE41" s="23" t="n"/>
+      <c r="Q41" s="21" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="21" t="n"/>
+      <c r="W41" s="22" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="21" t="n"/>
+      <c r="AA41" s="22" t="n"/>
+      <c r="AB41" s="23" t="n"/>
+      <c r="AC41" s="21" t="n"/>
+      <c r="AE41" s="22" t="n"/>
       <c r="AF41" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AG41" s="22" t="n"/>
-      <c r="AI41" s="23" t="n"/>
-      <c r="AJ41" s="24" t="n"/>
-      <c r="AK41" s="22" t="n"/>
+      <c r="AG41" s="21" t="n"/>
+      <c r="AI41" s="22" t="n"/>
+      <c r="AJ41" s="23" t="n"/>
+      <c r="AK41" s="21" t="n"/>
       <c r="AM41" s="44" t="n"/>
-      <c r="AN41" s="28" t="n"/>
-      <c r="AO41" s="22" t="n"/>
-      <c r="AQ41" s="25" t="n"/>
-      <c r="AR41" s="27" t="n"/>
-      <c r="AS41" s="22" t="n"/>
-      <c r="AU41" s="25" t="n"/>
-      <c r="AV41" s="27" t="n"/>
+      <c r="AN41" s="27" t="n"/>
+      <c r="AO41" s="21" t="n"/>
+      <c r="AQ41" s="24" t="n"/>
+      <c r="AR41" s="26" t="n"/>
+      <c r="AS41" s="21" t="n"/>
+      <c r="AU41" s="24" t="n"/>
+      <c r="AV41" s="26" t="n"/>
     </row>
     <row r="42" ht="20.1" customHeight="1">
-      <c r="A42" s="29" t="n"/>
-      <c r="B42" s="30" t="n"/>
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="29" t="n"/>
       <c r="C42" s="45" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="29" t="n"/>
+      <c r="G42" s="30" t="n"/>
       <c r="H42" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="I42" s="29" t="n"/>
-      <c r="J42" s="30" t="n"/>
-      <c r="K42" s="31" t="n"/>
-      <c r="L42" s="24" t="n"/>
-      <c r="M42" s="29" t="n"/>
-      <c r="N42" s="30" t="n"/>
+      <c r="I42" s="28" t="n"/>
+      <c r="J42" s="29" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="23" t="n"/>
+      <c r="M42" s="28" t="n"/>
+      <c r="N42" s="29" t="n"/>
       <c r="O42" s="45" t="n"/>
       <c r="P42" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Q42" s="29" t="n"/>
-      <c r="R42" s="30" t="n"/>
-      <c r="S42" s="31" t="n"/>
+      <c r="Q42" s="28" t="n"/>
+      <c r="R42" s="29" t="n"/>
+      <c r="S42" s="30" t="n"/>
       <c r="T42" s="33" t="n"/>
-      <c r="U42" s="29" t="n"/>
-      <c r="V42" s="30" t="n"/>
-      <c r="W42" s="31" t="n"/>
+      <c r="U42" s="28" t="n"/>
+      <c r="V42" s="29" t="n"/>
+      <c r="W42" s="30" t="n"/>
       <c r="X42" s="33" t="n"/>
-      <c r="Y42" s="29" t="n"/>
-      <c r="Z42" s="30" t="n"/>
-      <c r="AA42" s="31" t="n"/>
-      <c r="AB42" s="26" t="n"/>
-      <c r="AC42" s="29" t="n"/>
-      <c r="AD42" s="30" t="n"/>
-      <c r="AE42" s="31" t="n"/>
+      <c r="Y42" s="28" t="n"/>
+      <c r="Z42" s="29" t="n"/>
+      <c r="AA42" s="30" t="n"/>
+      <c r="AB42" s="31" t="n"/>
+      <c r="AC42" s="28" t="n"/>
+      <c r="AD42" s="29" t="n"/>
+      <c r="AE42" s="30" t="n"/>
       <c r="AF42" s="33" t="n"/>
-      <c r="AG42" s="29" t="n"/>
-      <c r="AH42" s="30" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="26" t="n"/>
-      <c r="AK42" s="29" t="n"/>
-      <c r="AL42" s="30" t="n"/>
+      <c r="AG42" s="28" t="n"/>
+      <c r="AH42" s="29" t="n"/>
+      <c r="AI42" s="30" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="28" t="n"/>
+      <c r="AL42" s="29" t="n"/>
       <c r="AM42" s="45" t="n"/>
       <c r="AN42" s="34" t="n"/>
-      <c r="AO42" s="29" t="n"/>
-      <c r="AP42" s="30" t="n"/>
+      <c r="AO42" s="28" t="n"/>
+      <c r="AP42" s="29" t="n"/>
       <c r="AQ42" s="32" t="n"/>
       <c r="AR42" s="33" t="n"/>
-      <c r="AS42" s="29" t="n"/>
-      <c r="AT42" s="30" t="n"/>
+      <c r="AS42" s="28" t="n"/>
+      <c r="AT42" s="29" t="n"/>
       <c r="AU42" s="32" t="n"/>
       <c r="AV42" s="33" t="n"/>
     </row>
@@ -4199,7 +4194,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="19" t="n"/>
+      <c r="D43" s="18" t="n"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4223,7 +4218,7 @@
         <v>14</v>
       </c>
       <c r="K43" s="7" t="n"/>
-      <c r="L43" s="26" t="n"/>
+      <c r="L43" s="31" t="n"/>
       <c r="M43" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4233,7 +4228,7 @@
         <v>14</v>
       </c>
       <c r="O43" s="7" t="n"/>
-      <c r="P43" s="19" t="n"/>
+      <c r="P43" s="18" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4243,7 +4238,7 @@
         <v>14</v>
       </c>
       <c r="S43" s="7" t="n"/>
-      <c r="T43" s="19" t="n"/>
+      <c r="T43" s="18" t="n"/>
       <c r="U43" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -4252,8 +4247,8 @@
       <c r="V43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="W43" s="41" t="n"/>
-      <c r="X43" s="49" t="inlineStr">
+      <c r="W43" s="42" t="n"/>
+      <c r="X43" s="50" t="inlineStr">
         <is>
           <t>1er dim. de Carême</t>
         </is>
@@ -4266,8 +4261,8 @@
       <c r="Z43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="AA43" s="41" t="n"/>
-      <c r="AB43" s="49" t="inlineStr">
+      <c r="AA43" s="42" t="n"/>
+      <c r="AB43" s="50" t="inlineStr">
         <is>
           <t>5e dim. de Carême</t>
         </is>
@@ -4281,7 +4276,7 @@
         <v>14</v>
       </c>
       <c r="AE43" s="7" t="n"/>
-      <c r="AF43" s="19" t="n"/>
+      <c r="AF43" s="18" t="n"/>
       <c r="AG43" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4291,7 +4286,7 @@
         <v>14</v>
       </c>
       <c r="AI43" s="7" t="n"/>
-      <c r="AJ43" s="19" t="n"/>
+      <c r="AJ43" s="18" t="n"/>
       <c r="AK43" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4301,7 +4296,7 @@
         <v>14</v>
       </c>
       <c r="AM43" s="7" t="n"/>
-      <c r="AN43" s="19" t="n"/>
+      <c r="AN43" s="18" t="n"/>
       <c r="AO43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4311,7 +4306,7 @@
         <v>14</v>
       </c>
       <c r="AQ43" s="12" t="n"/>
-      <c r="AR43" s="20" t="inlineStr">
+      <c r="AR43" s="19" t="inlineStr">
         <is>
           <t>Fête nationale</t>
         </is>
@@ -4325,121 +4320,121 @@
         <v>14</v>
       </c>
       <c r="AU43" s="12" t="n"/>
-      <c r="AV43" s="19" t="n"/>
+      <c r="AV43" s="18" t="n"/>
     </row>
     <row r="44" ht="20.1" customHeight="1">
-      <c r="A44" s="22" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="22" t="n"/>
-      <c r="G44" s="23" t="n"/>
+      <c r="A44" s="21" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="26" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="G44" s="22" t="n"/>
       <c r="H44" s="53" t="inlineStr">
         <is>
           <t>Semaine missionnaire</t>
         </is>
       </c>
-      <c r="I44" s="22" t="n"/>
-      <c r="K44" s="23" t="n"/>
+      <c r="I44" s="21" t="n"/>
+      <c r="K44" s="22" t="n"/>
       <c r="L44" s="16" t="inlineStr">
         <is>
           <t>WE Couples Miss.</t>
         </is>
       </c>
-      <c r="M44" s="22" t="n"/>
-      <c r="O44" s="23" t="n"/>
-      <c r="P44" s="27" t="n"/>
-      <c r="Q44" s="22" t="n"/>
-      <c r="S44" s="23" t="n"/>
-      <c r="T44" s="27" t="n"/>
-      <c r="U44" s="22" t="n"/>
+      <c r="M44" s="21" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="26" t="n"/>
+      <c r="Q44" s="21" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="26" t="n"/>
+      <c r="U44" s="21" t="n"/>
       <c r="W44" s="44" t="n"/>
       <c r="X44" s="36" t="inlineStr">
         <is>
           <t>Appel décisif</t>
         </is>
       </c>
-      <c r="Y44" s="22" t="n"/>
+      <c r="Y44" s="21" t="n"/>
       <c r="AA44" s="44" t="n"/>
       <c r="AB44" s="36" t="inlineStr">
         <is>
           <t>3ème scrutin</t>
         </is>
       </c>
-      <c r="AC44" s="22" t="n"/>
-      <c r="AE44" s="23" t="n"/>
-      <c r="AF44" s="27" t="n"/>
-      <c r="AG44" s="22" t="n"/>
-      <c r="AI44" s="23" t="n"/>
-      <c r="AJ44" s="27" t="n"/>
-      <c r="AK44" s="22" t="n"/>
-      <c r="AM44" s="23" t="n"/>
-      <c r="AN44" s="27" t="n"/>
-      <c r="AO44" s="22" t="n"/>
-      <c r="AQ44" s="25" t="n"/>
-      <c r="AR44" s="24" t="n"/>
-      <c r="AS44" s="22" t="n"/>
-      <c r="AU44" s="25" t="n"/>
-      <c r="AV44" s="27" t="n"/>
+      <c r="AC44" s="21" t="n"/>
+      <c r="AE44" s="22" t="n"/>
+      <c r="AF44" s="26" t="n"/>
+      <c r="AG44" s="21" t="n"/>
+      <c r="AI44" s="22" t="n"/>
+      <c r="AJ44" s="26" t="n"/>
+      <c r="AK44" s="21" t="n"/>
+      <c r="AM44" s="22" t="n"/>
+      <c r="AN44" s="26" t="n"/>
+      <c r="AO44" s="21" t="n"/>
+      <c r="AQ44" s="24" t="n"/>
+      <c r="AR44" s="23" t="n"/>
+      <c r="AS44" s="21" t="n"/>
+      <c r="AU44" s="24" t="n"/>
+      <c r="AV44" s="26" t="n"/>
     </row>
     <row r="45" ht="20.1" customHeight="1">
-      <c r="A45" s="29" t="n"/>
-      <c r="B45" s="30" t="n"/>
-      <c r="C45" s="31" t="n"/>
+      <c r="A45" s="28" t="n"/>
+      <c r="B45" s="29" t="n"/>
+      <c r="C45" s="30" t="n"/>
       <c r="D45" s="33" t="n"/>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="30" t="n"/>
-      <c r="G45" s="31" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="29" t="n"/>
-      <c r="J45" s="30" t="n"/>
-      <c r="K45" s="31" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="29" t="n"/>
+      <c r="G45" s="30" t="n"/>
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="28" t="n"/>
+      <c r="J45" s="29" t="n"/>
+      <c r="K45" s="30" t="n"/>
       <c r="L45" s="36" t="inlineStr">
         <is>
           <t>Formation accompagnateurs</t>
         </is>
       </c>
-      <c r="M45" s="29" t="n"/>
-      <c r="N45" s="30" t="n"/>
-      <c r="O45" s="31" t="n"/>
+      <c r="M45" s="28" t="n"/>
+      <c r="N45" s="29" t="n"/>
+      <c r="O45" s="30" t="n"/>
       <c r="P45" s="33" t="n"/>
-      <c r="Q45" s="29" t="n"/>
-      <c r="R45" s="30" t="n"/>
-      <c r="S45" s="31" t="n"/>
+      <c r="Q45" s="28" t="n"/>
+      <c r="R45" s="29" t="n"/>
+      <c r="S45" s="30" t="n"/>
       <c r="T45" s="33" t="n"/>
-      <c r="U45" s="29" t="n"/>
-      <c r="V45" s="30" t="n"/>
+      <c r="U45" s="28" t="n"/>
+      <c r="V45" s="29" t="n"/>
       <c r="W45" s="45" t="n"/>
       <c r="X45" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Y45" s="29" t="n"/>
-      <c r="Z45" s="30" t="n"/>
+      <c r="Y45" s="28" t="n"/>
+      <c r="Z45" s="29" t="n"/>
       <c r="AA45" s="45" t="n"/>
       <c r="AB45" s="16" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="AC45" s="29" t="n"/>
-      <c r="AD45" s="30" t="n"/>
-      <c r="AE45" s="31" t="n"/>
+      <c r="AC45" s="28" t="n"/>
+      <c r="AD45" s="29" t="n"/>
+      <c r="AE45" s="30" t="n"/>
       <c r="AF45" s="33" t="n"/>
-      <c r="AG45" s="29" t="n"/>
-      <c r="AH45" s="30" t="n"/>
-      <c r="AI45" s="31" t="n"/>
+      <c r="AG45" s="28" t="n"/>
+      <c r="AH45" s="29" t="n"/>
+      <c r="AI45" s="30" t="n"/>
       <c r="AJ45" s="33" t="n"/>
-      <c r="AK45" s="29" t="n"/>
-      <c r="AL45" s="30" t="n"/>
-      <c r="AM45" s="31" t="n"/>
+      <c r="AK45" s="28" t="n"/>
+      <c r="AL45" s="29" t="n"/>
+      <c r="AM45" s="30" t="n"/>
       <c r="AN45" s="33" t="n"/>
-      <c r="AO45" s="29" t="n"/>
-      <c r="AP45" s="30" t="n"/>
+      <c r="AO45" s="28" t="n"/>
+      <c r="AP45" s="29" t="n"/>
       <c r="AQ45" s="32" t="n"/>
-      <c r="AR45" s="26" t="n"/>
-      <c r="AS45" s="29" t="n"/>
-      <c r="AT45" s="30" t="n"/>
+      <c r="AR45" s="31" t="n"/>
+      <c r="AS45" s="28" t="n"/>
+      <c r="AT45" s="29" t="n"/>
       <c r="AU45" s="32" t="n"/>
       <c r="AV45" s="33" t="n"/>
     </row>
@@ -4453,7 +4448,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="19" t="n"/>
+      <c r="D46" s="18" t="n"/>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4463,7 +4458,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="24" t="n"/>
+      <c r="H46" s="23" t="n"/>
       <c r="I46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4472,7 +4467,7 @@
       <c r="J46" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="K46" s="41" t="n"/>
+      <c r="K46" s="42" t="n"/>
       <c r="L46" s="16" t="n"/>
       <c r="M46" s="14" t="inlineStr">
         <is>
@@ -4497,7 +4492,7 @@
         <v>15</v>
       </c>
       <c r="S46" s="7" t="n"/>
-      <c r="T46" s="19" t="n"/>
+      <c r="T46" s="18" t="n"/>
       <c r="U46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4507,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="W46" s="7" t="n"/>
-      <c r="X46" s="19" t="n"/>
+      <c r="X46" s="18" t="n"/>
       <c r="Y46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4517,7 +4512,7 @@
         <v>15</v>
       </c>
       <c r="AA46" s="7" t="n"/>
-      <c r="AB46" s="19" t="n"/>
+      <c r="AB46" s="18" t="n"/>
       <c r="AC46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4569,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="AQ46" s="12" t="n"/>
-      <c r="AR46" s="19" t="n"/>
+      <c r="AR46" s="18" t="n"/>
       <c r="AS46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4579,111 +4574,111 @@
         <v>15</v>
       </c>
       <c r="AU46" s="12" t="n"/>
-      <c r="AV46" s="20" t="inlineStr">
+      <c r="AV46" s="19" t="inlineStr">
         <is>
           <t>Assomption</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20.1" customHeight="1">
-      <c r="A47" s="22" t="n"/>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="22" t="n"/>
-      <c r="G47" s="23" t="n"/>
-      <c r="H47" s="24" t="n"/>
-      <c r="I47" s="22" t="n"/>
+      <c r="A47" s="21" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="23" t="n"/>
+      <c r="I47" s="21" t="n"/>
       <c r="K47" s="44" t="n"/>
-      <c r="L47" s="50" t="n"/>
-      <c r="M47" s="22" t="n"/>
-      <c r="O47" s="23" t="n"/>
+      <c r="L47" s="25" t="n"/>
+      <c r="M47" s="21" t="n"/>
+      <c r="O47" s="22" t="n"/>
       <c r="P47" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="Q47" s="22" t="n"/>
-      <c r="S47" s="23" t="n"/>
-      <c r="T47" s="27" t="n"/>
-      <c r="U47" s="22" t="n"/>
-      <c r="W47" s="23" t="n"/>
-      <c r="X47" s="27" t="n"/>
-      <c r="Y47" s="22" t="n"/>
-      <c r="AA47" s="23" t="n"/>
-      <c r="AB47" s="27" t="n"/>
-      <c r="AC47" s="22" t="n"/>
-      <c r="AE47" s="23" t="n"/>
-      <c r="AF47" s="24" t="n"/>
-      <c r="AG47" s="22" t="n"/>
-      <c r="AI47" s="23" t="n"/>
-      <c r="AJ47" s="18" t="inlineStr">
+      <c r="Q47" s="21" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="26" t="n"/>
+      <c r="U47" s="21" t="n"/>
+      <c r="W47" s="22" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="21" t="n"/>
+      <c r="AA47" s="22" t="n"/>
+      <c r="AB47" s="26" t="n"/>
+      <c r="AC47" s="21" t="n"/>
+      <c r="AE47" s="22" t="n"/>
+      <c r="AF47" s="23" t="n"/>
+      <c r="AG47" s="21" t="n"/>
+      <c r="AI47" s="22" t="n"/>
+      <c r="AJ47" s="17" t="inlineStr">
         <is>
           <t>Pentecôte Miss. ccn</t>
         </is>
       </c>
-      <c r="AK47" s="22" t="n"/>
-      <c r="AM47" s="23" t="n"/>
+      <c r="AK47" s="21" t="n"/>
+      <c r="AM47" s="22" t="n"/>
       <c r="AN47" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AO47" s="22" t="n"/>
-      <c r="AQ47" s="25" t="n"/>
-      <c r="AR47" s="27" t="n"/>
-      <c r="AS47" s="22" t="n"/>
-      <c r="AU47" s="25" t="n"/>
-      <c r="AV47" s="24" t="n"/>
+      <c r="AO47" s="21" t="n"/>
+      <c r="AQ47" s="24" t="n"/>
+      <c r="AR47" s="26" t="n"/>
+      <c r="AS47" s="21" t="n"/>
+      <c r="AU47" s="24" t="n"/>
+      <c r="AV47" s="23" t="n"/>
     </row>
     <row r="48" ht="20.1" customHeight="1">
-      <c r="A48" s="29" t="n"/>
-      <c r="B48" s="30" t="n"/>
-      <c r="C48" s="31" t="n"/>
+      <c r="A48" s="28" t="n"/>
+      <c r="B48" s="29" t="n"/>
+      <c r="C48" s="30" t="n"/>
       <c r="D48" s="33" t="n"/>
-      <c r="E48" s="29" t="n"/>
-      <c r="F48" s="30" t="n"/>
-      <c r="G48" s="31" t="n"/>
-      <c r="H48" s="24" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="30" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="29" t="n"/>
+      <c r="G48" s="30" t="n"/>
+      <c r="H48" s="23" t="n"/>
+      <c r="I48" s="28" t="n"/>
+      <c r="J48" s="29" t="n"/>
       <c r="K48" s="45" t="n"/>
-      <c r="L48" s="24" t="n"/>
-      <c r="M48" s="29" t="n"/>
-      <c r="N48" s="30" t="n"/>
-      <c r="O48" s="31" t="n"/>
+      <c r="L48" s="23" t="n"/>
+      <c r="M48" s="28" t="n"/>
+      <c r="N48" s="29" t="n"/>
+      <c r="O48" s="30" t="n"/>
       <c r="P48" s="33" t="n"/>
-      <c r="Q48" s="29" t="n"/>
-      <c r="R48" s="30" t="n"/>
-      <c r="S48" s="31" t="n"/>
+      <c r="Q48" s="28" t="n"/>
+      <c r="R48" s="29" t="n"/>
+      <c r="S48" s="30" t="n"/>
       <c r="T48" s="33" t="n"/>
-      <c r="U48" s="29" t="n"/>
-      <c r="V48" s="30" t="n"/>
-      <c r="W48" s="31" t="n"/>
+      <c r="U48" s="28" t="n"/>
+      <c r="V48" s="29" t="n"/>
+      <c r="W48" s="30" t="n"/>
       <c r="X48" s="33" t="n"/>
-      <c r="Y48" s="29" t="n"/>
-      <c r="Z48" s="30" t="n"/>
-      <c r="AA48" s="31" t="n"/>
+      <c r="Y48" s="28" t="n"/>
+      <c r="Z48" s="29" t="n"/>
+      <c r="AA48" s="30" t="n"/>
       <c r="AB48" s="33" t="n"/>
-      <c r="AC48" s="29" t="n"/>
-      <c r="AD48" s="30" t="n"/>
-      <c r="AE48" s="31" t="n"/>
-      <c r="AF48" s="26" t="n"/>
-      <c r="AG48" s="29" t="n"/>
-      <c r="AH48" s="30" t="n"/>
-      <c r="AI48" s="31" t="n"/>
-      <c r="AJ48" s="24" t="n"/>
-      <c r="AK48" s="29" t="n"/>
-      <c r="AL48" s="30" t="n"/>
-      <c r="AM48" s="31" t="n"/>
+      <c r="AC48" s="28" t="n"/>
+      <c r="AD48" s="29" t="n"/>
+      <c r="AE48" s="30" t="n"/>
+      <c r="AF48" s="31" t="n"/>
+      <c r="AG48" s="28" t="n"/>
+      <c r="AH48" s="29" t="n"/>
+      <c r="AI48" s="30" t="n"/>
+      <c r="AJ48" s="23" t="n"/>
+      <c r="AK48" s="28" t="n"/>
+      <c r="AL48" s="29" t="n"/>
+      <c r="AM48" s="30" t="n"/>
       <c r="AN48" s="33" t="n"/>
-      <c r="AO48" s="29" t="n"/>
-      <c r="AP48" s="30" t="n"/>
+      <c r="AO48" s="28" t="n"/>
+      <c r="AP48" s="29" t="n"/>
       <c r="AQ48" s="32" t="n"/>
       <c r="AR48" s="33" t="n"/>
-      <c r="AS48" s="29" t="n"/>
-      <c r="AT48" s="30" t="n"/>
+      <c r="AS48" s="28" t="n"/>
+      <c r="AT48" s="29" t="n"/>
       <c r="AU48" s="32" t="n"/>
-      <c r="AV48" s="26" t="n"/>
+      <c r="AV48" s="31" t="n"/>
     </row>
     <row r="49" ht="20.1" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -4695,7 +4690,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="19" t="n"/>
+      <c r="D49" s="18" t="n"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4705,7 +4700,7 @@
         <v>16</v>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="24" t="n"/>
+      <c r="H49" s="23" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4715,7 +4710,7 @@
         <v>16</v>
       </c>
       <c r="K49" s="7" t="n"/>
-      <c r="L49" s="24" t="n"/>
+      <c r="L49" s="23" t="n"/>
       <c r="M49" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4725,7 +4720,7 @@
         <v>16</v>
       </c>
       <c r="O49" s="7" t="n"/>
-      <c r="P49" s="19" t="n"/>
+      <c r="P49" s="18" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4735,7 +4730,7 @@
         <v>16</v>
       </c>
       <c r="S49" s="7" t="n"/>
-      <c r="T49" s="19" t="n"/>
+      <c r="T49" s="18" t="n"/>
       <c r="U49" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4773,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="AE49" s="7" t="n"/>
-      <c r="AF49" s="19" t="n"/>
+      <c r="AF49" s="18" t="n"/>
       <c r="AG49" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4782,8 +4777,8 @@
       <c r="AH49" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AI49" s="41" t="n"/>
-      <c r="AJ49" s="24" t="n"/>
+      <c r="AI49" s="42" t="n"/>
+      <c r="AJ49" s="23" t="n"/>
       <c r="AK49" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4793,7 +4788,7 @@
         <v>16</v>
       </c>
       <c r="AM49" s="7" t="n"/>
-      <c r="AN49" s="19" t="n"/>
+      <c r="AN49" s="18" t="n"/>
       <c r="AO49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4803,7 +4798,7 @@
         <v>16</v>
       </c>
       <c r="AQ49" s="12" t="n"/>
-      <c r="AR49" s="19" t="n"/>
+      <c r="AR49" s="18" t="n"/>
       <c r="AS49" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4813,105 +4808,105 @@
         <v>16</v>
       </c>
       <c r="AU49" s="12" t="n"/>
-      <c r="AV49" s="19" t="n"/>
+      <c r="AV49" s="18" t="n"/>
     </row>
     <row r="50" ht="20.1" customHeight="1">
-      <c r="A50" s="22" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="27" t="n"/>
-      <c r="E50" s="22" t="n"/>
-      <c r="G50" s="23" t="n"/>
-      <c r="H50" s="24" t="n"/>
-      <c r="I50" s="22" t="n"/>
-      <c r="K50" s="23" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="22" t="n"/>
-      <c r="O50" s="23" t="n"/>
-      <c r="P50" s="27" t="n"/>
-      <c r="Q50" s="22" t="n"/>
-      <c r="S50" s="23" t="n"/>
-      <c r="T50" s="27" t="n"/>
-      <c r="U50" s="22" t="n"/>
-      <c r="W50" s="23" t="n"/>
+      <c r="A50" s="21" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="26" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="21" t="n"/>
+      <c r="K50" s="22" t="n"/>
+      <c r="L50" s="23" t="n"/>
+      <c r="M50" s="21" t="n"/>
+      <c r="O50" s="22" t="n"/>
+      <c r="P50" s="26" t="n"/>
+      <c r="Q50" s="21" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="26" t="n"/>
+      <c r="U50" s="21" t="n"/>
+      <c r="W50" s="22" t="n"/>
       <c r="X50" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="Y50" s="22" t="n"/>
-      <c r="AA50" s="23" t="n"/>
+      <c r="Y50" s="21" t="n"/>
+      <c r="AA50" s="22" t="n"/>
       <c r="AB50" s="16" t="inlineStr">
         <is>
           <t>Soirée réconciliation</t>
         </is>
       </c>
-      <c r="AC50" s="22" t="n"/>
-      <c r="AE50" s="23" t="n"/>
-      <c r="AF50" s="27" t="n"/>
-      <c r="AG50" s="22" t="n"/>
+      <c r="AC50" s="21" t="n"/>
+      <c r="AE50" s="22" t="n"/>
+      <c r="AF50" s="26" t="n"/>
+      <c r="AG50" s="21" t="n"/>
       <c r="AI50" s="44" t="n"/>
-      <c r="AJ50" s="26" t="n"/>
-      <c r="AK50" s="22" t="n"/>
-      <c r="AM50" s="23" t="n"/>
-      <c r="AN50" s="27" t="n"/>
-      <c r="AO50" s="22" t="n"/>
-      <c r="AQ50" s="25" t="n"/>
-      <c r="AR50" s="27" t="n"/>
-      <c r="AS50" s="22" t="n"/>
-      <c r="AU50" s="25" t="n"/>
-      <c r="AV50" s="27" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="21" t="n"/>
+      <c r="AM50" s="22" t="n"/>
+      <c r="AN50" s="26" t="n"/>
+      <c r="AO50" s="21" t="n"/>
+      <c r="AQ50" s="24" t="n"/>
+      <c r="AR50" s="26" t="n"/>
+      <c r="AS50" s="21" t="n"/>
+      <c r="AU50" s="24" t="n"/>
+      <c r="AV50" s="26" t="n"/>
     </row>
     <row r="51" ht="20.1" customHeight="1">
-      <c r="A51" s="29" t="n"/>
-      <c r="B51" s="30" t="n"/>
-      <c r="C51" s="31" t="n"/>
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="30" t="n"/>
       <c r="D51" s="33" t="n"/>
-      <c r="E51" s="29" t="n"/>
-      <c r="F51" s="30" t="n"/>
-      <c r="G51" s="31" t="n"/>
-      <c r="H51" s="24" t="n"/>
-      <c r="I51" s="29" t="n"/>
-      <c r="J51" s="30" t="n"/>
-      <c r="K51" s="31" t="n"/>
-      <c r="L51" s="26" t="n"/>
-      <c r="M51" s="29" t="n"/>
-      <c r="N51" s="30" t="n"/>
-      <c r="O51" s="31" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="30" t="n"/>
+      <c r="H51" s="23" t="n"/>
+      <c r="I51" s="28" t="n"/>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="30" t="n"/>
+      <c r="L51" s="31" t="n"/>
+      <c r="M51" s="28" t="n"/>
+      <c r="N51" s="29" t="n"/>
+      <c r="O51" s="30" t="n"/>
       <c r="P51" s="33" t="n"/>
-      <c r="Q51" s="29" t="n"/>
-      <c r="R51" s="30" t="n"/>
-      <c r="S51" s="31" t="n"/>
+      <c r="Q51" s="28" t="n"/>
+      <c r="R51" s="29" t="n"/>
+      <c r="S51" s="30" t="n"/>
       <c r="T51" s="33" t="n"/>
-      <c r="U51" s="29" t="n"/>
-      <c r="V51" s="30" t="n"/>
-      <c r="W51" s="31" t="n"/>
+      <c r="U51" s="28" t="n"/>
+      <c r="V51" s="29" t="n"/>
+      <c r="W51" s="30" t="n"/>
       <c r="X51" s="33" t="n"/>
-      <c r="Y51" s="29" t="n"/>
-      <c r="Z51" s="30" t="n"/>
-      <c r="AA51" s="31" t="n"/>
+      <c r="Y51" s="28" t="n"/>
+      <c r="Z51" s="29" t="n"/>
+      <c r="AA51" s="30" t="n"/>
       <c r="AB51" s="33" t="n"/>
-      <c r="AC51" s="29" t="n"/>
-      <c r="AD51" s="30" t="n"/>
-      <c r="AE51" s="31" t="n"/>
+      <c r="AC51" s="28" t="n"/>
+      <c r="AD51" s="29" t="n"/>
+      <c r="AE51" s="30" t="n"/>
       <c r="AF51" s="33" t="n"/>
-      <c r="AG51" s="29" t="n"/>
-      <c r="AH51" s="30" t="n"/>
+      <c r="AG51" s="28" t="n"/>
+      <c r="AH51" s="29" t="n"/>
       <c r="AI51" s="45" t="n"/>
-      <c r="AJ51" s="17" t="inlineStr">
+      <c r="AJ51" s="13" t="inlineStr">
         <is>
           <t>Pentecôte</t>
         </is>
       </c>
-      <c r="AK51" s="29" t="n"/>
-      <c r="AL51" s="30" t="n"/>
-      <c r="AM51" s="31" t="n"/>
+      <c r="AK51" s="28" t="n"/>
+      <c r="AL51" s="29" t="n"/>
+      <c r="AM51" s="30" t="n"/>
       <c r="AN51" s="33" t="n"/>
-      <c r="AO51" s="29" t="n"/>
-      <c r="AP51" s="30" t="n"/>
+      <c r="AO51" s="28" t="n"/>
+      <c r="AP51" s="29" t="n"/>
       <c r="AQ51" s="32" t="n"/>
       <c r="AR51" s="33" t="n"/>
-      <c r="AS51" s="29" t="n"/>
-      <c r="AT51" s="30" t="n"/>
+      <c r="AS51" s="28" t="n"/>
+      <c r="AT51" s="29" t="n"/>
       <c r="AU51" s="32" t="n"/>
       <c r="AV51" s="33" t="n"/>
     </row>
@@ -4925,7 +4920,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="19" t="n"/>
+      <c r="D52" s="18" t="n"/>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4935,7 +4930,7 @@
         <v>17</v>
       </c>
       <c r="G52" s="12" t="n"/>
-      <c r="H52" s="24" t="n"/>
+      <c r="H52" s="23" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4959,7 +4954,7 @@
         <v>17</v>
       </c>
       <c r="O52" s="7" t="n"/>
-      <c r="P52" s="19" t="n"/>
+      <c r="P52" s="18" t="n"/>
       <c r="Q52" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4968,8 +4963,8 @@
       <c r="R52" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="S52" s="41" t="n"/>
-      <c r="T52" s="21" t="n"/>
+      <c r="S52" s="42" t="n"/>
+      <c r="T52" s="20" t="n"/>
       <c r="U52" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4979,7 +4974,7 @@
         <v>17</v>
       </c>
       <c r="W52" s="7" t="n"/>
-      <c r="X52" s="19" t="n"/>
+      <c r="X52" s="18" t="n"/>
       <c r="Y52" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4989,7 +4984,7 @@
         <v>17</v>
       </c>
       <c r="AA52" s="7" t="n"/>
-      <c r="AB52" s="19" t="n"/>
+      <c r="AB52" s="18" t="n"/>
       <c r="AC52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4999,7 +4994,7 @@
         <v>17</v>
       </c>
       <c r="AE52" s="12" t="n"/>
-      <c r="AF52" s="19" t="n"/>
+      <c r="AF52" s="18" t="n"/>
       <c r="AG52" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5019,7 +5014,7 @@
         <v>17</v>
       </c>
       <c r="AM52" s="7" t="n"/>
-      <c r="AN52" s="19" t="n"/>
+      <c r="AN52" s="18" t="n"/>
       <c r="AO52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5029,7 +5024,7 @@
         <v>17</v>
       </c>
       <c r="AQ52" s="12" t="n"/>
-      <c r="AR52" s="19" t="n"/>
+      <c r="AR52" s="18" t="n"/>
       <c r="AS52" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5039,105 +5034,105 @@
         <v>17</v>
       </c>
       <c r="AU52" s="12" t="n"/>
-      <c r="AV52" s="19" t="n"/>
+      <c r="AV52" s="18" t="n"/>
     </row>
     <row r="53" ht="20.1" customHeight="1">
-      <c r="A53" s="22" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="G53" s="25" t="n"/>
-      <c r="H53" s="24" t="n"/>
-      <c r="I53" s="22" t="n"/>
-      <c r="K53" s="23" t="n"/>
+      <c r="A53" s="21" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="26" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="23" t="n"/>
+      <c r="I53" s="21" t="n"/>
+      <c r="K53" s="22" t="n"/>
       <c r="L53" s="16" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
       </c>
-      <c r="M53" s="22" t="n"/>
-      <c r="O53" s="23" t="n"/>
-      <c r="P53" s="27" t="n"/>
-      <c r="Q53" s="22" t="n"/>
+      <c r="M53" s="21" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="26" t="n"/>
+      <c r="Q53" s="21" t="n"/>
       <c r="S53" s="44" t="n"/>
-      <c r="T53" s="28" t="n"/>
-      <c r="U53" s="22" t="n"/>
-      <c r="W53" s="23" t="n"/>
-      <c r="X53" s="27" t="n"/>
-      <c r="Y53" s="22" t="n"/>
-      <c r="AA53" s="23" t="n"/>
-      <c r="AB53" s="27" t="n"/>
-      <c r="AC53" s="22" t="n"/>
-      <c r="AE53" s="25" t="n"/>
-      <c r="AF53" s="27" t="n"/>
-      <c r="AG53" s="22" t="n"/>
-      <c r="AI53" s="23" t="n"/>
-      <c r="AJ53" s="26" t="n"/>
-      <c r="AK53" s="22" t="n"/>
-      <c r="AM53" s="23" t="n"/>
-      <c r="AN53" s="27" t="n"/>
-      <c r="AO53" s="22" t="n"/>
-      <c r="AQ53" s="25" t="n"/>
-      <c r="AR53" s="27" t="n"/>
-      <c r="AS53" s="22" t="n"/>
-      <c r="AU53" s="25" t="n"/>
-      <c r="AV53" s="27" t="n"/>
+      <c r="T53" s="27" t="n"/>
+      <c r="U53" s="21" t="n"/>
+      <c r="W53" s="22" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="21" t="n"/>
+      <c r="AA53" s="22" t="n"/>
+      <c r="AB53" s="26" t="n"/>
+      <c r="AC53" s="21" t="n"/>
+      <c r="AE53" s="24" t="n"/>
+      <c r="AF53" s="26" t="n"/>
+      <c r="AG53" s="21" t="n"/>
+      <c r="AI53" s="22" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="21" t="n"/>
+      <c r="AM53" s="22" t="n"/>
+      <c r="AN53" s="26" t="n"/>
+      <c r="AO53" s="21" t="n"/>
+      <c r="AQ53" s="24" t="n"/>
+      <c r="AR53" s="26" t="n"/>
+      <c r="AS53" s="21" t="n"/>
+      <c r="AU53" s="24" t="n"/>
+      <c r="AV53" s="26" t="n"/>
     </row>
     <row r="54" ht="20.1" customHeight="1">
-      <c r="A54" s="29" t="n"/>
-      <c r="B54" s="30" t="n"/>
-      <c r="C54" s="31" t="n"/>
+      <c r="A54" s="28" t="n"/>
+      <c r="B54" s="29" t="n"/>
+      <c r="C54" s="30" t="n"/>
       <c r="D54" s="33" t="n"/>
-      <c r="E54" s="29" t="n"/>
-      <c r="F54" s="30" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="29" t="n"/>
       <c r="G54" s="32" t="n"/>
-      <c r="H54" s="24" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="30" t="n"/>
-      <c r="K54" s="31" t="n"/>
+      <c r="H54" s="23" t="n"/>
+      <c r="I54" s="28" t="n"/>
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="30" t="n"/>
       <c r="L54" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="M54" s="29" t="n"/>
-      <c r="N54" s="30" t="n"/>
-      <c r="O54" s="31" t="n"/>
+      <c r="M54" s="28" t="n"/>
+      <c r="N54" s="29" t="n"/>
+      <c r="O54" s="30" t="n"/>
       <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="29" t="n"/>
-      <c r="R54" s="30" t="n"/>
+      <c r="Q54" s="28" t="n"/>
+      <c r="R54" s="29" t="n"/>
       <c r="S54" s="45" t="n"/>
       <c r="T54" s="34" t="n"/>
-      <c r="U54" s="29" t="n"/>
-      <c r="V54" s="30" t="n"/>
-      <c r="W54" s="31" t="n"/>
+      <c r="U54" s="28" t="n"/>
+      <c r="V54" s="29" t="n"/>
+      <c r="W54" s="30" t="n"/>
       <c r="X54" s="33" t="n"/>
-      <c r="Y54" s="29" t="n"/>
-      <c r="Z54" s="30" t="n"/>
-      <c r="AA54" s="31" t="n"/>
+      <c r="Y54" s="28" t="n"/>
+      <c r="Z54" s="29" t="n"/>
+      <c r="AA54" s="30" t="n"/>
       <c r="AB54" s="33" t="n"/>
-      <c r="AC54" s="29" t="n"/>
-      <c r="AD54" s="30" t="n"/>
+      <c r="AC54" s="28" t="n"/>
+      <c r="AD54" s="29" t="n"/>
       <c r="AE54" s="32" t="n"/>
       <c r="AF54" s="33" t="n"/>
-      <c r="AG54" s="29" t="n"/>
-      <c r="AH54" s="30" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="17" t="inlineStr">
+      <c r="AG54" s="28" t="n"/>
+      <c r="AH54" s="29" t="n"/>
+      <c r="AI54" s="30" t="n"/>
+      <c r="AJ54" s="13" t="inlineStr">
         <is>
           <t>Lundi de Pentecôte</t>
         </is>
       </c>
-      <c r="AK54" s="29" t="n"/>
-      <c r="AL54" s="30" t="n"/>
-      <c r="AM54" s="31" t="n"/>
+      <c r="AK54" s="28" t="n"/>
+      <c r="AL54" s="29" t="n"/>
+      <c r="AM54" s="30" t="n"/>
       <c r="AN54" s="33" t="n"/>
-      <c r="AO54" s="29" t="n"/>
-      <c r="AP54" s="30" t="n"/>
+      <c r="AO54" s="28" t="n"/>
+      <c r="AP54" s="29" t="n"/>
       <c r="AQ54" s="32" t="n"/>
       <c r="AR54" s="33" t="n"/>
-      <c r="AS54" s="29" t="n"/>
-      <c r="AT54" s="30" t="n"/>
+      <c r="AS54" s="28" t="n"/>
+      <c r="AT54" s="29" t="n"/>
       <c r="AU54" s="32" t="n"/>
       <c r="AV54" s="33" t="n"/>
     </row>
@@ -5165,7 +5160,7 @@
         <v>18</v>
       </c>
       <c r="G55" s="12" t="n"/>
-      <c r="H55" s="24" t="n"/>
+      <c r="H55" s="23" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5175,7 +5170,7 @@
         <v>18</v>
       </c>
       <c r="K55" s="7" t="n"/>
-      <c r="L55" s="50" t="n"/>
+      <c r="L55" s="25" t="n"/>
       <c r="M55" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5185,7 +5180,7 @@
         <v>18</v>
       </c>
       <c r="O55" s="7" t="n"/>
-      <c r="P55" s="19" t="n"/>
+      <c r="P55" s="18" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5195,7 +5190,7 @@
         <v>18</v>
       </c>
       <c r="S55" s="7" t="n"/>
-      <c r="T55" s="19" t="n"/>
+      <c r="T55" s="18" t="n"/>
       <c r="U55" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -5233,7 +5228,7 @@
         <v>18</v>
       </c>
       <c r="AE55" s="12" t="n"/>
-      <c r="AF55" s="21" t="n"/>
+      <c r="AF55" s="20" t="n"/>
       <c r="AG55" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5257,7 +5252,7 @@
         <v>18</v>
       </c>
       <c r="AM55" s="7" t="n"/>
-      <c r="AN55" s="19" t="n"/>
+      <c r="AN55" s="18" t="n"/>
       <c r="AO55" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -5267,7 +5262,7 @@
         <v>18</v>
       </c>
       <c r="AQ55" s="12" t="n"/>
-      <c r="AR55" s="21" t="n"/>
+      <c r="AR55" s="20" t="n"/>
       <c r="AS55" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5277,101 +5272,101 @@
         <v>18</v>
       </c>
       <c r="AU55" s="12" t="n"/>
-      <c r="AV55" s="19" t="n"/>
+      <c r="AV55" s="18" t="n"/>
     </row>
     <row r="56" ht="20.1" customHeight="1">
-      <c r="A56" s="22" t="n"/>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="24" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="G56" s="25" t="n"/>
-      <c r="H56" s="26" t="n"/>
-      <c r="I56" s="22" t="n"/>
-      <c r="K56" s="23" t="n"/>
-      <c r="L56" s="24" t="n"/>
-      <c r="M56" s="22" t="n"/>
-      <c r="O56" s="23" t="n"/>
-      <c r="P56" s="27" t="n"/>
-      <c r="Q56" s="22" t="n"/>
-      <c r="S56" s="23" t="n"/>
-      <c r="T56" s="27" t="n"/>
-      <c r="U56" s="22" t="n"/>
-      <c r="W56" s="23" t="n"/>
-      <c r="X56" s="24" t="n"/>
-      <c r="Y56" s="22" t="n"/>
-      <c r="AA56" s="23" t="n"/>
-      <c r="AB56" s="24" t="n"/>
-      <c r="AC56" s="22" t="n"/>
-      <c r="AE56" s="25" t="n"/>
-      <c r="AF56" s="28" t="n"/>
-      <c r="AG56" s="22" t="n"/>
-      <c r="AI56" s="23" t="n"/>
+      <c r="A56" s="21" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="31" t="n"/>
+      <c r="I56" s="21" t="n"/>
+      <c r="K56" s="22" t="n"/>
+      <c r="L56" s="23" t="n"/>
+      <c r="M56" s="21" t="n"/>
+      <c r="O56" s="22" t="n"/>
+      <c r="P56" s="26" t="n"/>
+      <c r="Q56" s="21" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="26" t="n"/>
+      <c r="U56" s="21" t="n"/>
+      <c r="W56" s="22" t="n"/>
+      <c r="X56" s="23" t="n"/>
+      <c r="Y56" s="21" t="n"/>
+      <c r="AA56" s="22" t="n"/>
+      <c r="AB56" s="23" t="n"/>
+      <c r="AC56" s="21" t="n"/>
+      <c r="AE56" s="24" t="n"/>
+      <c r="AF56" s="27" t="n"/>
+      <c r="AG56" s="21" t="n"/>
+      <c r="AI56" s="22" t="n"/>
       <c r="AJ56" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AK56" s="22" t="n"/>
-      <c r="AM56" s="23" t="n"/>
-      <c r="AN56" s="27" t="n"/>
-      <c r="AO56" s="22" t="n"/>
-      <c r="AQ56" s="25" t="n"/>
-      <c r="AR56" s="28" t="n"/>
-      <c r="AS56" s="22" t="n"/>
-      <c r="AU56" s="25" t="n"/>
-      <c r="AV56" s="27" t="n"/>
+      <c r="AK56" s="21" t="n"/>
+      <c r="AM56" s="22" t="n"/>
+      <c r="AN56" s="26" t="n"/>
+      <c r="AO56" s="21" t="n"/>
+      <c r="AQ56" s="24" t="n"/>
+      <c r="AR56" s="27" t="n"/>
+      <c r="AS56" s="21" t="n"/>
+      <c r="AU56" s="24" t="n"/>
+      <c r="AV56" s="26" t="n"/>
     </row>
     <row r="57" ht="20.1" customHeight="1">
-      <c r="A57" s="29" t="n"/>
-      <c r="B57" s="30" t="n"/>
-      <c r="C57" s="31" t="n"/>
-      <c r="D57" s="26" t="n"/>
-      <c r="E57" s="29" t="n"/>
-      <c r="F57" s="30" t="n"/>
+      <c r="A57" s="28" t="n"/>
+      <c r="B57" s="29" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="29" t="n"/>
       <c r="G57" s="32" t="n"/>
       <c r="H57" s="43" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
       </c>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="30" t="n"/>
-      <c r="K57" s="31" t="n"/>
-      <c r="L57" s="24" t="n"/>
-      <c r="M57" s="29" t="n"/>
-      <c r="N57" s="30" t="n"/>
-      <c r="O57" s="31" t="n"/>
+      <c r="I57" s="28" t="n"/>
+      <c r="J57" s="29" t="n"/>
+      <c r="K57" s="30" t="n"/>
+      <c r="L57" s="23" t="n"/>
+      <c r="M57" s="28" t="n"/>
+      <c r="N57" s="29" t="n"/>
+      <c r="O57" s="30" t="n"/>
       <c r="P57" s="33" t="n"/>
-      <c r="Q57" s="29" t="n"/>
-      <c r="R57" s="30" t="n"/>
-      <c r="S57" s="31" t="n"/>
+      <c r="Q57" s="28" t="n"/>
+      <c r="R57" s="29" t="n"/>
+      <c r="S57" s="30" t="n"/>
       <c r="T57" s="33" t="n"/>
-      <c r="U57" s="29" t="n"/>
-      <c r="V57" s="30" t="n"/>
-      <c r="W57" s="31" t="n"/>
-      <c r="X57" s="26" t="n"/>
-      <c r="Y57" s="29" t="n"/>
-      <c r="Z57" s="30" t="n"/>
-      <c r="AA57" s="31" t="n"/>
-      <c r="AB57" s="26" t="n"/>
-      <c r="AC57" s="29" t="n"/>
-      <c r="AD57" s="30" t="n"/>
+      <c r="U57" s="28" t="n"/>
+      <c r="V57" s="29" t="n"/>
+      <c r="W57" s="30" t="n"/>
+      <c r="X57" s="31" t="n"/>
+      <c r="Y57" s="28" t="n"/>
+      <c r="Z57" s="29" t="n"/>
+      <c r="AA57" s="30" t="n"/>
+      <c r="AB57" s="31" t="n"/>
+      <c r="AC57" s="28" t="n"/>
+      <c r="AD57" s="29" t="n"/>
       <c r="AE57" s="32" t="n"/>
       <c r="AF57" s="34" t="n"/>
-      <c r="AG57" s="29" t="n"/>
-      <c r="AH57" s="30" t="n"/>
-      <c r="AI57" s="31" t="n"/>
+      <c r="AG57" s="28" t="n"/>
+      <c r="AH57" s="29" t="n"/>
+      <c r="AI57" s="30" t="n"/>
       <c r="AJ57" s="33" t="n"/>
-      <c r="AK57" s="29" t="n"/>
-      <c r="AL57" s="30" t="n"/>
-      <c r="AM57" s="31" t="n"/>
+      <c r="AK57" s="28" t="n"/>
+      <c r="AL57" s="29" t="n"/>
+      <c r="AM57" s="30" t="n"/>
       <c r="AN57" s="33" t="n"/>
-      <c r="AO57" s="29" t="n"/>
-      <c r="AP57" s="30" t="n"/>
+      <c r="AO57" s="28" t="n"/>
+      <c r="AP57" s="29" t="n"/>
       <c r="AQ57" s="32" t="n"/>
       <c r="AR57" s="34" t="n"/>
-      <c r="AS57" s="29" t="n"/>
-      <c r="AT57" s="30" t="n"/>
+      <c r="AS57" s="28" t="n"/>
+      <c r="AT57" s="29" t="n"/>
       <c r="AU57" s="32" t="n"/>
       <c r="AV57" s="33" t="n"/>
     </row>
@@ -5399,7 +5394,7 @@
         <v>19</v>
       </c>
       <c r="G58" s="12" t="n"/>
-      <c r="H58" s="19" t="n"/>
+      <c r="H58" s="18" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5409,7 +5404,7 @@
         <v>19</v>
       </c>
       <c r="K58" s="7" t="n"/>
-      <c r="L58" s="24" t="n"/>
+      <c r="L58" s="23" t="n"/>
       <c r="M58" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5419,7 +5414,7 @@
         <v>19</v>
       </c>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="19" t="n"/>
+      <c r="P58" s="18" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5443,7 +5438,7 @@
         <v>19</v>
       </c>
       <c r="W58" s="7" t="n"/>
-      <c r="X58" s="19" t="n"/>
+      <c r="X58" s="18" t="n"/>
       <c r="Y58" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5453,7 +5448,7 @@
         <v>19</v>
       </c>
       <c r="AA58" s="7" t="n"/>
-      <c r="AB58" s="19" t="n"/>
+      <c r="AB58" s="18" t="n"/>
       <c r="AC58" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5463,7 +5458,7 @@
         <v>19</v>
       </c>
       <c r="AE58" s="12" t="n"/>
-      <c r="AF58" s="19" t="n"/>
+      <c r="AF58" s="18" t="n"/>
       <c r="AG58" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5473,7 +5468,7 @@
         <v>19</v>
       </c>
       <c r="AI58" s="7" t="n"/>
-      <c r="AJ58" s="19" t="n"/>
+      <c r="AJ58" s="18" t="n"/>
       <c r="AK58" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5483,7 +5478,7 @@
         <v>19</v>
       </c>
       <c r="AM58" s="7" t="n"/>
-      <c r="AN58" s="20" t="inlineStr">
+      <c r="AN58" s="19" t="inlineStr">
         <is>
           <t>St Antoine (Tamoul)</t>
         </is>
@@ -5497,7 +5492,7 @@
         <v>19</v>
       </c>
       <c r="AQ58" s="12" t="n"/>
-      <c r="AR58" s="19" t="n"/>
+      <c r="AR58" s="18" t="n"/>
       <c r="AS58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5507,105 +5502,105 @@
         <v>19</v>
       </c>
       <c r="AU58" s="12" t="n"/>
-      <c r="AV58" s="19" t="n"/>
+      <c r="AV58" s="18" t="n"/>
     </row>
     <row r="59" ht="20.1" customHeight="1">
-      <c r="A59" s="22" t="n"/>
-      <c r="C59" s="23" t="n"/>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="A59" s="21" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>ND Velankanni (Tamoul)</t>
         </is>
       </c>
-      <c r="E59" s="22" t="n"/>
-      <c r="G59" s="25" t="n"/>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="22" t="n"/>
-      <c r="K59" s="23" t="n"/>
-      <c r="L59" s="26" t="n"/>
-      <c r="M59" s="22" t="n"/>
-      <c r="O59" s="25" t="n"/>
-      <c r="P59" s="27" t="n"/>
-      <c r="Q59" s="22" t="n"/>
-      <c r="S59" s="23" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="26" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="K59" s="22" t="n"/>
+      <c r="L59" s="31" t="n"/>
+      <c r="M59" s="21" t="n"/>
+      <c r="O59" s="24" t="n"/>
+      <c r="P59" s="26" t="n"/>
+      <c r="Q59" s="21" t="n"/>
+      <c r="S59" s="22" t="n"/>
       <c r="T59" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="U59" s="22" t="n"/>
-      <c r="W59" s="23" t="n"/>
-      <c r="X59" s="27" t="n"/>
-      <c r="Y59" s="22" t="n"/>
-      <c r="AA59" s="23" t="n"/>
-      <c r="AB59" s="27" t="n"/>
-      <c r="AC59" s="22" t="n"/>
-      <c r="AE59" s="25" t="n"/>
-      <c r="AF59" s="27" t="n"/>
-      <c r="AG59" s="22" t="n"/>
-      <c r="AI59" s="23" t="n"/>
-      <c r="AJ59" s="27" t="n"/>
-      <c r="AK59" s="22" t="n"/>
-      <c r="AM59" s="23" t="n"/>
-      <c r="AN59" s="24" t="n"/>
-      <c r="AO59" s="22" t="n"/>
-      <c r="AQ59" s="25" t="n"/>
-      <c r="AR59" s="27" t="n"/>
-      <c r="AS59" s="22" t="n"/>
-      <c r="AU59" s="25" t="n"/>
-      <c r="AV59" s="27" t="n"/>
+      <c r="U59" s="21" t="n"/>
+      <c r="W59" s="22" t="n"/>
+      <c r="X59" s="26" t="n"/>
+      <c r="Y59" s="21" t="n"/>
+      <c r="AA59" s="22" t="n"/>
+      <c r="AB59" s="26" t="n"/>
+      <c r="AC59" s="21" t="n"/>
+      <c r="AE59" s="24" t="n"/>
+      <c r="AF59" s="26" t="n"/>
+      <c r="AG59" s="21" t="n"/>
+      <c r="AI59" s="22" t="n"/>
+      <c r="AJ59" s="26" t="n"/>
+      <c r="AK59" s="21" t="n"/>
+      <c r="AM59" s="22" t="n"/>
+      <c r="AN59" s="23" t="n"/>
+      <c r="AO59" s="21" t="n"/>
+      <c r="AQ59" s="24" t="n"/>
+      <c r="AR59" s="26" t="n"/>
+      <c r="AS59" s="21" t="n"/>
+      <c r="AU59" s="24" t="n"/>
+      <c r="AV59" s="26" t="n"/>
     </row>
     <row r="60" ht="20.1" customHeight="1">
-      <c r="A60" s="29" t="n"/>
-      <c r="B60" s="30" t="n"/>
-      <c r="C60" s="31" t="n"/>
+      <c r="A60" s="28" t="n"/>
+      <c r="B60" s="29" t="n"/>
+      <c r="C60" s="30" t="n"/>
       <c r="D60" s="33" t="n"/>
-      <c r="E60" s="29" t="n"/>
-      <c r="F60" s="30" t="n"/>
+      <c r="E60" s="28" t="n"/>
+      <c r="F60" s="29" t="n"/>
       <c r="G60" s="32" t="n"/>
       <c r="H60" s="33" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="30" t="n"/>
-      <c r="K60" s="31" t="n"/>
+      <c r="I60" s="28" t="n"/>
+      <c r="J60" s="29" t="n"/>
+      <c r="K60" s="30" t="n"/>
       <c r="L60" s="39" t="inlineStr">
         <is>
           <t>Conseil presbytéral</t>
         </is>
       </c>
-      <c r="M60" s="29" t="n"/>
-      <c r="N60" s="30" t="n"/>
+      <c r="M60" s="28" t="n"/>
+      <c r="N60" s="29" t="n"/>
       <c r="O60" s="32" t="n"/>
       <c r="P60" s="33" t="n"/>
-      <c r="Q60" s="29" t="n"/>
-      <c r="R60" s="30" t="n"/>
-      <c r="S60" s="31" t="n"/>
+      <c r="Q60" s="28" t="n"/>
+      <c r="R60" s="29" t="n"/>
+      <c r="S60" s="30" t="n"/>
       <c r="T60" s="33" t="n"/>
-      <c r="U60" s="29" t="n"/>
-      <c r="V60" s="30" t="n"/>
-      <c r="W60" s="31" t="n"/>
+      <c r="U60" s="28" t="n"/>
+      <c r="V60" s="29" t="n"/>
+      <c r="W60" s="30" t="n"/>
       <c r="X60" s="33" t="n"/>
-      <c r="Y60" s="29" t="n"/>
-      <c r="Z60" s="30" t="n"/>
-      <c r="AA60" s="31" t="n"/>
+      <c r="Y60" s="28" t="n"/>
+      <c r="Z60" s="29" t="n"/>
+      <c r="AA60" s="30" t="n"/>
       <c r="AB60" s="33" t="n"/>
-      <c r="AC60" s="29" t="n"/>
-      <c r="AD60" s="30" t="n"/>
+      <c r="AC60" s="28" t="n"/>
+      <c r="AD60" s="29" t="n"/>
       <c r="AE60" s="32" t="n"/>
       <c r="AF60" s="33" t="n"/>
-      <c r="AG60" s="29" t="n"/>
-      <c r="AH60" s="30" t="n"/>
-      <c r="AI60" s="31" t="n"/>
+      <c r="AG60" s="28" t="n"/>
+      <c r="AH60" s="29" t="n"/>
+      <c r="AI60" s="30" t="n"/>
       <c r="AJ60" s="33" t="n"/>
-      <c r="AK60" s="29" t="n"/>
-      <c r="AL60" s="30" t="n"/>
-      <c r="AM60" s="31" t="n"/>
-      <c r="AN60" s="26" t="n"/>
-      <c r="AO60" s="29" t="n"/>
-      <c r="AP60" s="30" t="n"/>
+      <c r="AK60" s="28" t="n"/>
+      <c r="AL60" s="29" t="n"/>
+      <c r="AM60" s="30" t="n"/>
+      <c r="AN60" s="31" t="n"/>
+      <c r="AO60" s="28" t="n"/>
+      <c r="AP60" s="29" t="n"/>
       <c r="AQ60" s="32" t="n"/>
       <c r="AR60" s="33" t="n"/>
-      <c r="AS60" s="29" t="n"/>
-      <c r="AT60" s="30" t="n"/>
+      <c r="AS60" s="28" t="n"/>
+      <c r="AT60" s="29" t="n"/>
       <c r="AU60" s="32" t="n"/>
       <c r="AV60" s="33" t="n"/>
     </row>
@@ -5618,8 +5613,8 @@
       <c r="B61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C61" s="41" t="n"/>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="C61" s="42" t="n"/>
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Journée Communautaire</t>
         </is>
@@ -5647,7 +5642,7 @@
         <v>20</v>
       </c>
       <c r="K61" s="7" t="n"/>
-      <c r="L61" s="50" t="n"/>
+      <c r="L61" s="25" t="n"/>
       <c r="M61" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -5671,7 +5666,7 @@
         <v>20</v>
       </c>
       <c r="S61" s="7" t="n"/>
-      <c r="T61" s="19" t="n"/>
+      <c r="T61" s="18" t="n"/>
       <c r="U61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5681,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="W61" s="12" t="n"/>
-      <c r="X61" s="19" t="n"/>
+      <c r="X61" s="18" t="n"/>
       <c r="Y61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5691,7 +5686,7 @@
         <v>20</v>
       </c>
       <c r="AA61" s="7" t="n"/>
-      <c r="AB61" s="18" t="inlineStr">
+      <c r="AB61" s="17" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -5705,7 +5700,7 @@
         <v>20</v>
       </c>
       <c r="AE61" s="12" t="n"/>
-      <c r="AF61" s="18" t="inlineStr">
+      <c r="AF61" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -5732,8 +5727,8 @@
       <c r="AL61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AM61" s="41" t="n"/>
-      <c r="AN61" s="21" t="n"/>
+      <c r="AM61" s="42" t="n"/>
+      <c r="AN61" s="20" t="n"/>
       <c r="AO61" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5743,7 +5738,7 @@
         <v>20</v>
       </c>
       <c r="AQ61" s="12" t="n"/>
-      <c r="AR61" s="19" t="n"/>
+      <c r="AR61" s="18" t="n"/>
       <c r="AS61" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5753,93 +5748,93 @@
         <v>20</v>
       </c>
       <c r="AU61" s="12" t="n"/>
-      <c r="AV61" s="19" t="n"/>
+      <c r="AV61" s="18" t="n"/>
     </row>
     <row r="62" ht="20.1" customHeight="1">
-      <c r="A62" s="22" t="n"/>
+      <c r="A62" s="21" t="n"/>
       <c r="C62" s="44" t="n"/>
-      <c r="D62" s="24" t="n"/>
-      <c r="E62" s="22" t="n"/>
-      <c r="G62" s="25" t="n"/>
-      <c r="H62" s="42" t="n"/>
-      <c r="I62" s="22" t="n"/>
-      <c r="K62" s="23" t="n"/>
-      <c r="L62" s="24" t="n"/>
-      <c r="M62" s="22" t="n"/>
-      <c r="O62" s="25" t="n"/>
-      <c r="P62" s="24" t="n"/>
-      <c r="Q62" s="22" t="n"/>
-      <c r="S62" s="23" t="n"/>
-      <c r="T62" s="27" t="n"/>
-      <c r="U62" s="22" t="n"/>
-      <c r="W62" s="25" t="n"/>
-      <c r="X62" s="27" t="n"/>
-      <c r="Y62" s="22" t="n"/>
-      <c r="AA62" s="23" t="n"/>
-      <c r="AB62" s="24" t="n"/>
-      <c r="AC62" s="22" t="n"/>
-      <c r="AE62" s="25" t="n"/>
-      <c r="AF62" s="24" t="n"/>
-      <c r="AG62" s="22" t="n"/>
-      <c r="AI62" s="23" t="n"/>
-      <c r="AJ62" s="24" t="n"/>
-      <c r="AK62" s="22" t="n"/>
+      <c r="D62" s="23" t="n"/>
+      <c r="E62" s="21" t="n"/>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="41" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="K62" s="22" t="n"/>
+      <c r="L62" s="23" t="n"/>
+      <c r="M62" s="21" t="n"/>
+      <c r="O62" s="24" t="n"/>
+      <c r="P62" s="23" t="n"/>
+      <c r="Q62" s="21" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="26" t="n"/>
+      <c r="U62" s="21" t="n"/>
+      <c r="W62" s="24" t="n"/>
+      <c r="X62" s="26" t="n"/>
+      <c r="Y62" s="21" t="n"/>
+      <c r="AA62" s="22" t="n"/>
+      <c r="AB62" s="23" t="n"/>
+      <c r="AC62" s="21" t="n"/>
+      <c r="AE62" s="24" t="n"/>
+      <c r="AF62" s="23" t="n"/>
+      <c r="AG62" s="21" t="n"/>
+      <c r="AI62" s="22" t="n"/>
+      <c r="AJ62" s="23" t="n"/>
+      <c r="AK62" s="21" t="n"/>
       <c r="AM62" s="44" t="n"/>
-      <c r="AN62" s="28" t="n"/>
-      <c r="AO62" s="22" t="n"/>
-      <c r="AQ62" s="25" t="n"/>
-      <c r="AR62" s="27" t="n"/>
-      <c r="AS62" s="22" t="n"/>
-      <c r="AU62" s="25" t="n"/>
-      <c r="AV62" s="27" t="n"/>
+      <c r="AN62" s="27" t="n"/>
+      <c r="AO62" s="21" t="n"/>
+      <c r="AQ62" s="24" t="n"/>
+      <c r="AR62" s="26" t="n"/>
+      <c r="AS62" s="21" t="n"/>
+      <c r="AU62" s="24" t="n"/>
+      <c r="AV62" s="26" t="n"/>
     </row>
     <row r="63" ht="20.1" customHeight="1">
-      <c r="A63" s="29" t="n"/>
-      <c r="B63" s="30" t="n"/>
+      <c r="A63" s="28" t="n"/>
+      <c r="B63" s="29" t="n"/>
       <c r="C63" s="45" t="n"/>
-      <c r="D63" s="26" t="n"/>
-      <c r="E63" s="29" t="n"/>
-      <c r="F63" s="30" t="n"/>
+      <c r="D63" s="31" t="n"/>
+      <c r="E63" s="28" t="n"/>
+      <c r="F63" s="29" t="n"/>
       <c r="G63" s="32" t="n"/>
-      <c r="H63" s="24" t="n"/>
-      <c r="I63" s="29" t="n"/>
-      <c r="J63" s="30" t="n"/>
-      <c r="K63" s="31" t="n"/>
-      <c r="L63" s="26" t="n"/>
-      <c r="M63" s="29" t="n"/>
-      <c r="N63" s="30" t="n"/>
+      <c r="H63" s="23" t="n"/>
+      <c r="I63" s="28" t="n"/>
+      <c r="J63" s="29" t="n"/>
+      <c r="K63" s="30" t="n"/>
+      <c r="L63" s="31" t="n"/>
+      <c r="M63" s="28" t="n"/>
+      <c r="N63" s="29" t="n"/>
       <c r="O63" s="32" t="n"/>
-      <c r="P63" s="26" t="n"/>
-      <c r="Q63" s="29" t="n"/>
-      <c r="R63" s="30" t="n"/>
-      <c r="S63" s="31" t="n"/>
+      <c r="P63" s="31" t="n"/>
+      <c r="Q63" s="28" t="n"/>
+      <c r="R63" s="29" t="n"/>
+      <c r="S63" s="30" t="n"/>
       <c r="T63" s="33" t="n"/>
-      <c r="U63" s="29" t="n"/>
-      <c r="V63" s="30" t="n"/>
+      <c r="U63" s="28" t="n"/>
+      <c r="V63" s="29" t="n"/>
       <c r="W63" s="32" t="n"/>
       <c r="X63" s="33" t="n"/>
-      <c r="Y63" s="29" t="n"/>
-      <c r="Z63" s="30" t="n"/>
-      <c r="AA63" s="31" t="n"/>
-      <c r="AB63" s="26" t="n"/>
-      <c r="AC63" s="29" t="n"/>
-      <c r="AD63" s="30" t="n"/>
+      <c r="Y63" s="28" t="n"/>
+      <c r="Z63" s="29" t="n"/>
+      <c r="AA63" s="30" t="n"/>
+      <c r="AB63" s="31" t="n"/>
+      <c r="AC63" s="28" t="n"/>
+      <c r="AD63" s="29" t="n"/>
       <c r="AE63" s="32" t="n"/>
-      <c r="AF63" s="26" t="n"/>
-      <c r="AG63" s="29" t="n"/>
-      <c r="AH63" s="30" t="n"/>
-      <c r="AI63" s="31" t="n"/>
-      <c r="AJ63" s="26" t="n"/>
-      <c r="AK63" s="29" t="n"/>
-      <c r="AL63" s="30" t="n"/>
+      <c r="AF63" s="31" t="n"/>
+      <c r="AG63" s="28" t="n"/>
+      <c r="AH63" s="29" t="n"/>
+      <c r="AI63" s="30" t="n"/>
+      <c r="AJ63" s="31" t="n"/>
+      <c r="AK63" s="28" t="n"/>
+      <c r="AL63" s="29" t="n"/>
       <c r="AM63" s="45" t="n"/>
       <c r="AN63" s="34" t="n"/>
-      <c r="AO63" s="29" t="n"/>
-      <c r="AP63" s="30" t="n"/>
+      <c r="AO63" s="28" t="n"/>
+      <c r="AP63" s="29" t="n"/>
       <c r="AQ63" s="32" t="n"/>
       <c r="AR63" s="33" t="n"/>
-      <c r="AS63" s="29" t="n"/>
-      <c r="AT63" s="30" t="n"/>
+      <c r="AS63" s="28" t="n"/>
+      <c r="AT63" s="29" t="n"/>
       <c r="AU63" s="32" t="n"/>
       <c r="AV63" s="33" t="n"/>
     </row>
@@ -5853,7 +5848,7 @@
         <v>21</v>
       </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="19" t="n"/>
+      <c r="D64" s="18" t="n"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5863,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="G64" s="12" t="n"/>
-      <c r="H64" s="24" t="n"/>
+      <c r="H64" s="23" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5873,7 +5868,7 @@
         <v>21</v>
       </c>
       <c r="K64" s="7" t="n"/>
-      <c r="L64" s="19" t="n"/>
+      <c r="L64" s="18" t="n"/>
       <c r="M64" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -5883,7 +5878,7 @@
         <v>21</v>
       </c>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="19" t="n"/>
+      <c r="P64" s="18" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5893,7 +5888,7 @@
         <v>21</v>
       </c>
       <c r="S64" s="7" t="n"/>
-      <c r="T64" s="19" t="n"/>
+      <c r="T64" s="18" t="n"/>
       <c r="U64" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -5903,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="W64" s="12" t="n"/>
-      <c r="X64" s="49" t="inlineStr">
+      <c r="X64" s="50" t="inlineStr">
         <is>
           <t>2e dim. de Carême</t>
         </is>
@@ -5916,8 +5911,8 @@
       <c r="Z64" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="AA64" s="41" t="n"/>
-      <c r="AB64" s="49" t="inlineStr">
+      <c r="AA64" s="42" t="n"/>
+      <c r="AB64" s="50" t="inlineStr">
         <is>
           <t>Rameaux</t>
         </is>
@@ -5931,7 +5926,7 @@
         <v>21</v>
       </c>
       <c r="AE64" s="12" t="n"/>
-      <c r="AF64" s="19" t="n"/>
+      <c r="AF64" s="18" t="n"/>
       <c r="AG64" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5941,7 +5936,7 @@
         <v>21</v>
       </c>
       <c r="AI64" s="7" t="n"/>
-      <c r="AJ64" s="19" t="n"/>
+      <c r="AJ64" s="18" t="n"/>
       <c r="AK64" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5951,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="AM64" s="7" t="n"/>
-      <c r="AN64" s="19" t="n"/>
+      <c r="AN64" s="18" t="n"/>
       <c r="AO64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5961,7 +5956,7 @@
         <v>21</v>
       </c>
       <c r="AQ64" s="12" t="n"/>
-      <c r="AR64" s="19" t="n"/>
+      <c r="AR64" s="18" t="n"/>
       <c r="AS64" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5971,97 +5966,97 @@
         <v>21</v>
       </c>
       <c r="AU64" s="12" t="n"/>
-      <c r="AV64" s="19" t="n"/>
+      <c r="AV64" s="18" t="n"/>
     </row>
     <row r="65" ht="20.1" customHeight="1">
-      <c r="A65" s="22" t="n"/>
-      <c r="C65" s="23" t="n"/>
-      <c r="D65" s="27" t="n"/>
-      <c r="E65" s="22" t="n"/>
-      <c r="G65" s="25" t="n"/>
-      <c r="H65" s="24" t="n"/>
-      <c r="I65" s="22" t="n"/>
-      <c r="K65" s="23" t="n"/>
-      <c r="L65" s="27" t="n"/>
-      <c r="M65" s="22" t="n"/>
-      <c r="O65" s="25" t="n"/>
-      <c r="P65" s="27" t="n"/>
-      <c r="Q65" s="22" t="n"/>
-      <c r="S65" s="23" t="n"/>
-      <c r="T65" s="27" t="n"/>
-      <c r="U65" s="22" t="n"/>
-      <c r="W65" s="25" t="n"/>
+      <c r="A65" s="21" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="26" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="G65" s="24" t="n"/>
+      <c r="H65" s="23" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="K65" s="22" t="n"/>
+      <c r="L65" s="26" t="n"/>
+      <c r="M65" s="21" t="n"/>
+      <c r="O65" s="24" t="n"/>
+      <c r="P65" s="26" t="n"/>
+      <c r="Q65" s="21" t="n"/>
+      <c r="S65" s="22" t="n"/>
+      <c r="T65" s="26" t="n"/>
+      <c r="U65" s="21" t="n"/>
+      <c r="W65" s="24" t="n"/>
       <c r="X65" s="54" t="n"/>
-      <c r="Y65" s="22" t="n"/>
+      <c r="Y65" s="21" t="n"/>
       <c r="AA65" s="44" t="n"/>
       <c r="AB65" s="55" t="inlineStr">
         <is>
           <t>Semaine Sainte</t>
         </is>
       </c>
-      <c r="AC65" s="22" t="n"/>
-      <c r="AE65" s="25" t="n"/>
-      <c r="AF65" s="27" t="n"/>
-      <c r="AG65" s="22" t="n"/>
-      <c r="AI65" s="23" t="n"/>
-      <c r="AJ65" s="27" t="n"/>
-      <c r="AK65" s="22" t="n"/>
-      <c r="AM65" s="23" t="n"/>
-      <c r="AN65" s="27" t="n"/>
-      <c r="AO65" s="22" t="n"/>
-      <c r="AQ65" s="25" t="n"/>
-      <c r="AR65" s="27" t="n"/>
-      <c r="AS65" s="22" t="n"/>
-      <c r="AU65" s="25" t="n"/>
-      <c r="AV65" s="27" t="n"/>
+      <c r="AC65" s="21" t="n"/>
+      <c r="AE65" s="24" t="n"/>
+      <c r="AF65" s="26" t="n"/>
+      <c r="AG65" s="21" t="n"/>
+      <c r="AI65" s="22" t="n"/>
+      <c r="AJ65" s="26" t="n"/>
+      <c r="AK65" s="21" t="n"/>
+      <c r="AM65" s="22" t="n"/>
+      <c r="AN65" s="26" t="n"/>
+      <c r="AO65" s="21" t="n"/>
+      <c r="AQ65" s="24" t="n"/>
+      <c r="AR65" s="26" t="n"/>
+      <c r="AS65" s="21" t="n"/>
+      <c r="AU65" s="24" t="n"/>
+      <c r="AV65" s="26" t="n"/>
     </row>
     <row r="66" ht="20.1" customHeight="1">
-      <c r="A66" s="29" t="n"/>
-      <c r="B66" s="30" t="n"/>
-      <c r="C66" s="31" t="n"/>
+      <c r="A66" s="28" t="n"/>
+      <c r="B66" s="29" t="n"/>
+      <c r="C66" s="30" t="n"/>
       <c r="D66" s="33" t="n"/>
-      <c r="E66" s="29" t="n"/>
-      <c r="F66" s="30" t="n"/>
+      <c r="E66" s="28" t="n"/>
+      <c r="F66" s="29" t="n"/>
       <c r="G66" s="32" t="n"/>
-      <c r="H66" s="24" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="30" t="n"/>
-      <c r="K66" s="31" t="n"/>
+      <c r="H66" s="23" t="n"/>
+      <c r="I66" s="28" t="n"/>
+      <c r="J66" s="29" t="n"/>
+      <c r="K66" s="30" t="n"/>
       <c r="L66" s="33" t="n"/>
-      <c r="M66" s="29" t="n"/>
-      <c r="N66" s="30" t="n"/>
+      <c r="M66" s="28" t="n"/>
+      <c r="N66" s="29" t="n"/>
       <c r="O66" s="32" t="n"/>
       <c r="P66" s="33" t="n"/>
-      <c r="Q66" s="29" t="n"/>
-      <c r="R66" s="30" t="n"/>
-      <c r="S66" s="31" t="n"/>
+      <c r="Q66" s="28" t="n"/>
+      <c r="R66" s="29" t="n"/>
+      <c r="S66" s="30" t="n"/>
       <c r="T66" s="33" t="n"/>
-      <c r="U66" s="29" t="n"/>
-      <c r="V66" s="30" t="n"/>
+      <c r="U66" s="28" t="n"/>
+      <c r="V66" s="29" t="n"/>
       <c r="W66" s="32" t="n"/>
-      <c r="X66" s="24" t="n"/>
-      <c r="Y66" s="29" t="n"/>
-      <c r="Z66" s="30" t="n"/>
+      <c r="X66" s="23" t="n"/>
+      <c r="Y66" s="28" t="n"/>
+      <c r="Z66" s="29" t="n"/>
       <c r="AA66" s="45" t="n"/>
-      <c r="AB66" s="24" t="n"/>
-      <c r="AC66" s="29" t="n"/>
-      <c r="AD66" s="30" t="n"/>
+      <c r="AB66" s="23" t="n"/>
+      <c r="AC66" s="28" t="n"/>
+      <c r="AD66" s="29" t="n"/>
       <c r="AE66" s="32" t="n"/>
       <c r="AF66" s="33" t="n"/>
-      <c r="AG66" s="29" t="n"/>
-      <c r="AH66" s="30" t="n"/>
-      <c r="AI66" s="31" t="n"/>
+      <c r="AG66" s="28" t="n"/>
+      <c r="AH66" s="29" t="n"/>
+      <c r="AI66" s="30" t="n"/>
       <c r="AJ66" s="33" t="n"/>
-      <c r="AK66" s="29" t="n"/>
-      <c r="AL66" s="30" t="n"/>
-      <c r="AM66" s="31" t="n"/>
+      <c r="AK66" s="28" t="n"/>
+      <c r="AL66" s="29" t="n"/>
+      <c r="AM66" s="30" t="n"/>
       <c r="AN66" s="33" t="n"/>
-      <c r="AO66" s="29" t="n"/>
-      <c r="AP66" s="30" t="n"/>
+      <c r="AO66" s="28" t="n"/>
+      <c r="AP66" s="29" t="n"/>
       <c r="AQ66" s="32" t="n"/>
       <c r="AR66" s="33" t="n"/>
-      <c r="AS66" s="29" t="n"/>
-      <c r="AT66" s="30" t="n"/>
+      <c r="AS66" s="28" t="n"/>
+      <c r="AT66" s="29" t="n"/>
       <c r="AU66" s="32" t="n"/>
       <c r="AV66" s="33" t="n"/>
     </row>
@@ -6075,7 +6070,7 @@
         <v>22</v>
       </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Rentrée District CCN + Kion</t>
         </is>
@@ -6089,7 +6084,7 @@
         <v>22</v>
       </c>
       <c r="G67" s="12" t="n"/>
-      <c r="H67" s="24" t="n"/>
+      <c r="H67" s="23" t="n"/>
       <c r="I67" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6098,8 +6093,8 @@
       <c r="J67" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="K67" s="41" t="n"/>
-      <c r="L67" s="20" t="inlineStr">
+      <c r="K67" s="42" t="n"/>
+      <c r="L67" s="19" t="inlineStr">
         <is>
           <t>Christ Roi</t>
         </is>
@@ -6113,7 +6108,7 @@
         <v>22</v>
       </c>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="18" t="inlineStr">
+      <c r="P67" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -6127,7 +6122,7 @@
         <v>22</v>
       </c>
       <c r="S67" s="7" t="n"/>
-      <c r="T67" s="19" t="n"/>
+      <c r="T67" s="18" t="n"/>
       <c r="U67" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -6137,7 +6132,7 @@
         <v>22</v>
       </c>
       <c r="W67" s="12" t="n"/>
-      <c r="X67" s="24" t="n"/>
+      <c r="X67" s="23" t="n"/>
       <c r="Y67" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -6147,7 +6142,7 @@
         <v>22</v>
       </c>
       <c r="AA67" s="7" t="n"/>
-      <c r="AB67" s="24" t="n"/>
+      <c r="AB67" s="23" t="n"/>
       <c r="AC67" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6157,7 +6152,7 @@
         <v>22</v>
       </c>
       <c r="AE67" s="12" t="n"/>
-      <c r="AF67" s="19" t="n"/>
+      <c r="AF67" s="18" t="n"/>
       <c r="AG67" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6167,7 +6162,7 @@
         <v>22</v>
       </c>
       <c r="AI67" s="7" t="n"/>
-      <c r="AJ67" s="18" t="inlineStr">
+      <c r="AJ67" s="17" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -6195,7 +6190,7 @@
         <v>22</v>
       </c>
       <c r="AQ67" s="12" t="n"/>
-      <c r="AR67" s="19" t="n"/>
+      <c r="AR67" s="18" t="n"/>
       <c r="AS67" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6205,97 +6200,97 @@
         <v>22</v>
       </c>
       <c r="AU67" s="12" t="n"/>
-      <c r="AV67" s="21" t="n"/>
+      <c r="AV67" s="20" t="n"/>
     </row>
     <row r="68" ht="20.1" customHeight="1">
-      <c r="A68" s="22" t="n"/>
-      <c r="C68" s="23" t="n"/>
-      <c r="D68" s="24" t="n"/>
-      <c r="E68" s="22" t="n"/>
-      <c r="G68" s="25" t="n"/>
-      <c r="H68" s="24" t="n"/>
-      <c r="I68" s="22" t="n"/>
+      <c r="A68" s="21" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="21" t="n"/>
+      <c r="G68" s="24" t="n"/>
+      <c r="H68" s="23" t="n"/>
+      <c r="I68" s="21" t="n"/>
       <c r="K68" s="44" t="n"/>
-      <c r="L68" s="24" t="n"/>
-      <c r="M68" s="22" t="n"/>
-      <c r="O68" s="25" t="n"/>
-      <c r="P68" s="24" t="n"/>
-      <c r="Q68" s="22" t="n"/>
-      <c r="S68" s="23" t="n"/>
-      <c r="T68" s="27" t="n"/>
-      <c r="U68" s="22" t="n"/>
-      <c r="W68" s="25" t="n"/>
-      <c r="X68" s="24" t="n"/>
-      <c r="Y68" s="22" t="n"/>
-      <c r="AA68" s="23" t="n"/>
-      <c r="AB68" s="24" t="n"/>
-      <c r="AC68" s="22" t="n"/>
-      <c r="AE68" s="25" t="n"/>
-      <c r="AF68" s="27" t="n"/>
-      <c r="AG68" s="22" t="n"/>
-      <c r="AI68" s="23" t="n"/>
-      <c r="AJ68" s="24" t="n"/>
-      <c r="AK68" s="22" t="n"/>
-      <c r="AM68" s="23" t="n"/>
+      <c r="L68" s="23" t="n"/>
+      <c r="M68" s="21" t="n"/>
+      <c r="O68" s="24" t="n"/>
+      <c r="P68" s="23" t="n"/>
+      <c r="Q68" s="21" t="n"/>
+      <c r="S68" s="22" t="n"/>
+      <c r="T68" s="26" t="n"/>
+      <c r="U68" s="21" t="n"/>
+      <c r="W68" s="24" t="n"/>
+      <c r="X68" s="23" t="n"/>
+      <c r="Y68" s="21" t="n"/>
+      <c r="AA68" s="22" t="n"/>
+      <c r="AB68" s="23" t="n"/>
+      <c r="AC68" s="21" t="n"/>
+      <c r="AE68" s="24" t="n"/>
+      <c r="AF68" s="26" t="n"/>
+      <c r="AG68" s="21" t="n"/>
+      <c r="AI68" s="22" t="n"/>
+      <c r="AJ68" s="23" t="n"/>
+      <c r="AK68" s="21" t="n"/>
+      <c r="AM68" s="22" t="n"/>
       <c r="AN68" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AO68" s="22" t="n"/>
-      <c r="AQ68" s="25" t="n"/>
-      <c r="AR68" s="27" t="n"/>
-      <c r="AS68" s="22" t="n"/>
-      <c r="AU68" s="25" t="n"/>
-      <c r="AV68" s="28" t="n"/>
+      <c r="AO68" s="21" t="n"/>
+      <c r="AQ68" s="24" t="n"/>
+      <c r="AR68" s="26" t="n"/>
+      <c r="AS68" s="21" t="n"/>
+      <c r="AU68" s="24" t="n"/>
+      <c r="AV68" s="27" t="n"/>
     </row>
     <row r="69" ht="20.1" customHeight="1">
-      <c r="A69" s="29" t="n"/>
-      <c r="B69" s="30" t="n"/>
-      <c r="C69" s="31" t="n"/>
-      <c r="D69" s="26" t="n"/>
-      <c r="E69" s="29" t="n"/>
-      <c r="F69" s="30" t="n"/>
+      <c r="A69" s="28" t="n"/>
+      <c r="B69" s="29" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="31" t="n"/>
+      <c r="E69" s="28" t="n"/>
+      <c r="F69" s="29" t="n"/>
       <c r="G69" s="32" t="n"/>
-      <c r="H69" s="24" t="n"/>
-      <c r="I69" s="29" t="n"/>
-      <c r="J69" s="30" t="n"/>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="28" t="n"/>
+      <c r="J69" s="29" t="n"/>
       <c r="K69" s="45" t="n"/>
-      <c r="L69" s="26" t="n"/>
-      <c r="M69" s="29" t="n"/>
-      <c r="N69" s="30" t="n"/>
+      <c r="L69" s="31" t="n"/>
+      <c r="M69" s="28" t="n"/>
+      <c r="N69" s="29" t="n"/>
       <c r="O69" s="32" t="n"/>
-      <c r="P69" s="26" t="n"/>
-      <c r="Q69" s="29" t="n"/>
-      <c r="R69" s="30" t="n"/>
-      <c r="S69" s="31" t="n"/>
+      <c r="P69" s="31" t="n"/>
+      <c r="Q69" s="28" t="n"/>
+      <c r="R69" s="29" t="n"/>
+      <c r="S69" s="30" t="n"/>
       <c r="T69" s="33" t="n"/>
-      <c r="U69" s="29" t="n"/>
-      <c r="V69" s="30" t="n"/>
+      <c r="U69" s="28" t="n"/>
+      <c r="V69" s="29" t="n"/>
       <c r="W69" s="32" t="n"/>
-      <c r="X69" s="24" t="n"/>
-      <c r="Y69" s="29" t="n"/>
-      <c r="Z69" s="30" t="n"/>
-      <c r="AA69" s="31" t="n"/>
-      <c r="AB69" s="24" t="n"/>
-      <c r="AC69" s="29" t="n"/>
-      <c r="AD69" s="30" t="n"/>
+      <c r="X69" s="23" t="n"/>
+      <c r="Y69" s="28" t="n"/>
+      <c r="Z69" s="29" t="n"/>
+      <c r="AA69" s="30" t="n"/>
+      <c r="AB69" s="23" t="n"/>
+      <c r="AC69" s="28" t="n"/>
+      <c r="AD69" s="29" t="n"/>
       <c r="AE69" s="32" t="n"/>
       <c r="AF69" s="33" t="n"/>
-      <c r="AG69" s="29" t="n"/>
-      <c r="AH69" s="30" t="n"/>
-      <c r="AI69" s="31" t="n"/>
-      <c r="AJ69" s="26" t="n"/>
-      <c r="AK69" s="29" t="n"/>
-      <c r="AL69" s="30" t="n"/>
-      <c r="AM69" s="31" t="n"/>
+      <c r="AG69" s="28" t="n"/>
+      <c r="AH69" s="29" t="n"/>
+      <c r="AI69" s="30" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="28" t="n"/>
+      <c r="AL69" s="29" t="n"/>
+      <c r="AM69" s="30" t="n"/>
       <c r="AN69" s="33" t="n"/>
-      <c r="AO69" s="29" t="n"/>
-      <c r="AP69" s="30" t="n"/>
+      <c r="AO69" s="28" t="n"/>
+      <c r="AP69" s="29" t="n"/>
       <c r="AQ69" s="32" t="n"/>
       <c r="AR69" s="33" t="n"/>
-      <c r="AS69" s="29" t="n"/>
-      <c r="AT69" s="30" t="n"/>
+      <c r="AS69" s="28" t="n"/>
+      <c r="AT69" s="29" t="n"/>
       <c r="AU69" s="32" t="n"/>
       <c r="AV69" s="34" t="n"/>
     </row>
@@ -6309,7 +6304,7 @@
         <v>23</v>
       </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="19" t="n"/>
+      <c r="D70" s="18" t="n"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6319,7 +6314,7 @@
         <v>23</v>
       </c>
       <c r="G70" s="12" t="n"/>
-      <c r="H70" s="24" t="n"/>
+      <c r="H70" s="23" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6329,7 +6324,7 @@
         <v>23</v>
       </c>
       <c r="K70" s="7" t="n"/>
-      <c r="L70" s="19" t="n"/>
+      <c r="L70" s="18" t="n"/>
       <c r="M70" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6339,7 +6334,7 @@
         <v>23</v>
       </c>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="19" t="n"/>
+      <c r="P70" s="18" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6349,7 +6344,7 @@
         <v>23</v>
       </c>
       <c r="S70" s="7" t="n"/>
-      <c r="T70" s="18" t="inlineStr">
+      <c r="T70" s="17" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -6363,7 +6358,7 @@
         <v>23</v>
       </c>
       <c r="W70" s="12" t="n"/>
-      <c r="X70" s="24" t="n"/>
+      <c r="X70" s="23" t="n"/>
       <c r="Y70" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6373,7 +6368,7 @@
         <v>23</v>
       </c>
       <c r="AA70" s="7" t="n"/>
-      <c r="AB70" s="26" t="n"/>
+      <c r="AB70" s="31" t="n"/>
       <c r="AC70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6383,7 +6378,7 @@
         <v>23</v>
       </c>
       <c r="AE70" s="12" t="n"/>
-      <c r="AF70" s="19" t="n"/>
+      <c r="AF70" s="18" t="n"/>
       <c r="AG70" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6392,8 +6387,8 @@
       <c r="AH70" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="AI70" s="41" t="n"/>
-      <c r="AJ70" s="21" t="n"/>
+      <c r="AI70" s="42" t="n"/>
+      <c r="AJ70" s="20" t="n"/>
       <c r="AK70" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6403,7 +6398,7 @@
         <v>23</v>
       </c>
       <c r="AM70" s="7" t="n"/>
-      <c r="AN70" s="19" t="n"/>
+      <c r="AN70" s="18" t="n"/>
       <c r="AO70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6413,7 +6408,7 @@
         <v>23</v>
       </c>
       <c r="AQ70" s="12" t="n"/>
-      <c r="AR70" s="19" t="n"/>
+      <c r="AR70" s="18" t="n"/>
       <c r="AS70" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6423,109 +6418,109 @@
         <v>23</v>
       </c>
       <c r="AU70" s="12" t="n"/>
-      <c r="AV70" s="19" t="n"/>
+      <c r="AV70" s="18" t="n"/>
     </row>
     <row r="71" ht="20.1" customHeight="1">
-      <c r="A71" s="22" t="n"/>
-      <c r="C71" s="23" t="n"/>
-      <c r="D71" s="27" t="n"/>
-      <c r="E71" s="22" t="n"/>
-      <c r="G71" s="25" t="n"/>
-      <c r="H71" s="26" t="n"/>
-      <c r="I71" s="22" t="n"/>
-      <c r="K71" s="23" t="n"/>
-      <c r="L71" s="27" t="n"/>
-      <c r="M71" s="22" t="n"/>
-      <c r="O71" s="25" t="n"/>
-      <c r="P71" s="27" t="n"/>
-      <c r="Q71" s="22" t="n"/>
-      <c r="S71" s="23" t="n"/>
-      <c r="T71" s="24" t="n"/>
-      <c r="U71" s="22" t="n"/>
-      <c r="W71" s="25" t="n"/>
-      <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="22" t="n"/>
-      <c r="AA71" s="23" t="n"/>
-      <c r="AB71" s="49" t="inlineStr">
+      <c r="A71" s="21" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="26" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="G71" s="24" t="n"/>
+      <c r="H71" s="31" t="n"/>
+      <c r="I71" s="21" t="n"/>
+      <c r="K71" s="22" t="n"/>
+      <c r="L71" s="26" t="n"/>
+      <c r="M71" s="21" t="n"/>
+      <c r="O71" s="24" t="n"/>
+      <c r="P71" s="26" t="n"/>
+      <c r="Q71" s="21" t="n"/>
+      <c r="S71" s="22" t="n"/>
+      <c r="T71" s="23" t="n"/>
+      <c r="U71" s="21" t="n"/>
+      <c r="W71" s="24" t="n"/>
+      <c r="X71" s="31" t="n"/>
+      <c r="Y71" s="21" t="n"/>
+      <c r="AA71" s="22" t="n"/>
+      <c r="AB71" s="50" t="inlineStr">
         <is>
           <t>Messe Chrismale</t>
         </is>
       </c>
-      <c r="AC71" s="22" t="n"/>
-      <c r="AE71" s="25" t="n"/>
-      <c r="AF71" s="27" t="n"/>
-      <c r="AG71" s="22" t="n"/>
+      <c r="AC71" s="21" t="n"/>
+      <c r="AE71" s="24" t="n"/>
+      <c r="AF71" s="26" t="n"/>
+      <c r="AG71" s="21" t="n"/>
       <c r="AI71" s="44" t="n"/>
-      <c r="AJ71" s="28" t="n"/>
-      <c r="AK71" s="22" t="n"/>
-      <c r="AM71" s="23" t="n"/>
-      <c r="AN71" s="27" t="n"/>
-      <c r="AO71" s="22" t="n"/>
-      <c r="AQ71" s="25" t="n"/>
-      <c r="AR71" s="27" t="n"/>
-      <c r="AS71" s="22" t="n"/>
-      <c r="AU71" s="25" t="n"/>
-      <c r="AV71" s="27" t="n"/>
+      <c r="AJ71" s="27" t="n"/>
+      <c r="AK71" s="21" t="n"/>
+      <c r="AM71" s="22" t="n"/>
+      <c r="AN71" s="26" t="n"/>
+      <c r="AO71" s="21" t="n"/>
+      <c r="AQ71" s="24" t="n"/>
+      <c r="AR71" s="26" t="n"/>
+      <c r="AS71" s="21" t="n"/>
+      <c r="AU71" s="24" t="n"/>
+      <c r="AV71" s="26" t="n"/>
     </row>
     <row r="72" ht="20.1" customHeight="1">
-      <c r="A72" s="29" t="n"/>
-      <c r="B72" s="30" t="n"/>
-      <c r="C72" s="31" t="n"/>
+      <c r="A72" s="28" t="n"/>
+      <c r="B72" s="29" t="n"/>
+      <c r="C72" s="30" t="n"/>
       <c r="D72" s="33" t="n"/>
-      <c r="E72" s="29" t="n"/>
-      <c r="F72" s="30" t="n"/>
+      <c r="E72" s="28" t="n"/>
+      <c r="F72" s="29" t="n"/>
       <c r="G72" s="32" t="n"/>
       <c r="H72" s="40" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
       </c>
-      <c r="I72" s="29" t="n"/>
-      <c r="J72" s="30" t="n"/>
-      <c r="K72" s="31" t="n"/>
+      <c r="I72" s="28" t="n"/>
+      <c r="J72" s="29" t="n"/>
+      <c r="K72" s="30" t="n"/>
       <c r="L72" s="33" t="n"/>
-      <c r="M72" s="29" t="n"/>
-      <c r="N72" s="30" t="n"/>
+      <c r="M72" s="28" t="n"/>
+      <c r="N72" s="29" t="n"/>
       <c r="O72" s="32" t="n"/>
       <c r="P72" s="33" t="n"/>
-      <c r="Q72" s="29" t="n"/>
-      <c r="R72" s="30" t="n"/>
-      <c r="S72" s="31" t="n"/>
-      <c r="T72" s="26" t="n"/>
-      <c r="U72" s="29" t="n"/>
-      <c r="V72" s="30" t="n"/>
+      <c r="Q72" s="28" t="n"/>
+      <c r="R72" s="29" t="n"/>
+      <c r="S72" s="30" t="n"/>
+      <c r="T72" s="31" t="n"/>
+      <c r="U72" s="28" t="n"/>
+      <c r="V72" s="29" t="n"/>
       <c r="W72" s="32" t="n"/>
       <c r="X72" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="Y72" s="29" t="n"/>
-      <c r="Z72" s="30" t="n"/>
-      <c r="AA72" s="31" t="n"/>
+      <c r="Y72" s="28" t="n"/>
+      <c r="Z72" s="29" t="n"/>
+      <c r="AA72" s="30" t="n"/>
       <c r="AB72" s="39" t="inlineStr">
         <is>
           <t>Rencontre des prêtres</t>
         </is>
       </c>
-      <c r="AC72" s="29" t="n"/>
-      <c r="AD72" s="30" t="n"/>
+      <c r="AC72" s="28" t="n"/>
+      <c r="AD72" s="29" t="n"/>
       <c r="AE72" s="32" t="n"/>
       <c r="AF72" s="33" t="n"/>
-      <c r="AG72" s="29" t="n"/>
-      <c r="AH72" s="30" t="n"/>
+      <c r="AG72" s="28" t="n"/>
+      <c r="AH72" s="29" t="n"/>
       <c r="AI72" s="45" t="n"/>
       <c r="AJ72" s="34" t="n"/>
-      <c r="AK72" s="29" t="n"/>
-      <c r="AL72" s="30" t="n"/>
-      <c r="AM72" s="31" t="n"/>
+      <c r="AK72" s="28" t="n"/>
+      <c r="AL72" s="29" t="n"/>
+      <c r="AM72" s="30" t="n"/>
       <c r="AN72" s="33" t="n"/>
-      <c r="AO72" s="29" t="n"/>
-      <c r="AP72" s="30" t="n"/>
+      <c r="AO72" s="28" t="n"/>
+      <c r="AP72" s="29" t="n"/>
       <c r="AQ72" s="32" t="n"/>
       <c r="AR72" s="33" t="n"/>
-      <c r="AS72" s="29" t="n"/>
-      <c r="AT72" s="30" t="n"/>
+      <c r="AS72" s="28" t="n"/>
+      <c r="AT72" s="29" t="n"/>
       <c r="AU72" s="32" t="n"/>
       <c r="AV72" s="33" t="n"/>
     </row>
@@ -6539,7 +6534,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="19" t="n"/>
+      <c r="D73" s="18" t="n"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6549,7 +6544,11 @@
         <v>24</v>
       </c>
       <c r="G73" s="12" t="n"/>
-      <c r="H73" s="42" t="n"/>
+      <c r="H73" s="41" t="inlineStr">
+        <is>
+          <t>Père Pascal en Côte d'Ivoire</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6573,7 +6572,7 @@
         <v>24</v>
       </c>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="19" t="n"/>
+      <c r="P73" s="18" t="n"/>
       <c r="Q73" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6582,8 +6581,8 @@
       <c r="R73" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S73" s="41" t="n"/>
-      <c r="T73" s="21" t="n"/>
+      <c r="S73" s="42" t="n"/>
+      <c r="T73" s="20" t="n"/>
       <c r="U73" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6617,7 +6616,11 @@
         <v>24</v>
       </c>
       <c r="AE73" s="12" t="n"/>
-      <c r="AF73" s="19" t="n"/>
+      <c r="AF73" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
       <c r="AG73" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6627,7 +6630,7 @@
         <v>24</v>
       </c>
       <c r="AI73" s="7" t="n"/>
-      <c r="AJ73" s="19" t="n"/>
+      <c r="AJ73" s="18" t="n"/>
       <c r="AK73" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6637,7 +6640,7 @@
         <v>24</v>
       </c>
       <c r="AM73" s="7" t="n"/>
-      <c r="AN73" s="19" t="n"/>
+      <c r="AN73" s="18" t="n"/>
       <c r="AO73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6647,7 +6650,7 @@
         <v>24</v>
       </c>
       <c r="AQ73" s="12" t="n"/>
-      <c r="AR73" s="19" t="n"/>
+      <c r="AR73" s="18" t="n"/>
       <c r="AS73" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6657,97 +6660,97 @@
         <v>24</v>
       </c>
       <c r="AU73" s="12" t="n"/>
-      <c r="AV73" s="19" t="n"/>
+      <c r="AV73" s="18" t="n"/>
     </row>
     <row r="74" ht="20.1" customHeight="1">
-      <c r="A74" s="22" t="n"/>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="27" t="n"/>
-      <c r="E74" s="22" t="n"/>
-      <c r="G74" s="25" t="n"/>
-      <c r="H74" s="24" t="n"/>
-      <c r="I74" s="22" t="n"/>
-      <c r="K74" s="23" t="n"/>
+      <c r="A74" s="21" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="26" t="n"/>
+      <c r="E74" s="21" t="n"/>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="23" t="n"/>
+      <c r="I74" s="21" t="n"/>
+      <c r="K74" s="22" t="n"/>
       <c r="L74" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="M74" s="22" t="n"/>
-      <c r="O74" s="25" t="n"/>
-      <c r="P74" s="27" t="n"/>
-      <c r="Q74" s="22" t="n"/>
+      <c r="M74" s="21" t="n"/>
+      <c r="O74" s="24" t="n"/>
+      <c r="P74" s="26" t="n"/>
+      <c r="Q74" s="21" t="n"/>
       <c r="S74" s="44" t="n"/>
-      <c r="T74" s="28" t="n"/>
-      <c r="U74" s="22" t="n"/>
-      <c r="W74" s="25" t="n"/>
-      <c r="X74" s="24" t="n"/>
-      <c r="Y74" s="22" t="n"/>
-      <c r="AA74" s="23" t="n"/>
-      <c r="AB74" s="24" t="n"/>
-      <c r="AC74" s="22" t="n"/>
-      <c r="AE74" s="25" t="n"/>
-      <c r="AF74" s="27" t="n"/>
-      <c r="AG74" s="22" t="n"/>
-      <c r="AI74" s="23" t="n"/>
-      <c r="AJ74" s="27" t="n"/>
-      <c r="AK74" s="22" t="n"/>
-      <c r="AM74" s="23" t="n"/>
-      <c r="AN74" s="27" t="n"/>
-      <c r="AO74" s="22" t="n"/>
-      <c r="AQ74" s="25" t="n"/>
-      <c r="AR74" s="27" t="n"/>
-      <c r="AS74" s="22" t="n"/>
-      <c r="AU74" s="25" t="n"/>
-      <c r="AV74" s="27" t="n"/>
+      <c r="T74" s="27" t="n"/>
+      <c r="U74" s="21" t="n"/>
+      <c r="W74" s="24" t="n"/>
+      <c r="X74" s="23" t="n"/>
+      <c r="Y74" s="21" t="n"/>
+      <c r="AA74" s="22" t="n"/>
+      <c r="AB74" s="23" t="n"/>
+      <c r="AC74" s="21" t="n"/>
+      <c r="AE74" s="24" t="n"/>
+      <c r="AF74" s="23" t="n"/>
+      <c r="AG74" s="21" t="n"/>
+      <c r="AI74" s="22" t="n"/>
+      <c r="AJ74" s="26" t="n"/>
+      <c r="AK74" s="21" t="n"/>
+      <c r="AM74" s="22" t="n"/>
+      <c r="AN74" s="26" t="n"/>
+      <c r="AO74" s="21" t="n"/>
+      <c r="AQ74" s="24" t="n"/>
+      <c r="AR74" s="26" t="n"/>
+      <c r="AS74" s="21" t="n"/>
+      <c r="AU74" s="24" t="n"/>
+      <c r="AV74" s="26" t="n"/>
     </row>
     <row r="75" ht="20.1" customHeight="1">
-      <c r="A75" s="29" t="n"/>
-      <c r="B75" s="30" t="n"/>
-      <c r="C75" s="31" t="n"/>
+      <c r="A75" s="28" t="n"/>
+      <c r="B75" s="29" t="n"/>
+      <c r="C75" s="30" t="n"/>
       <c r="D75" s="33" t="n"/>
-      <c r="E75" s="29" t="n"/>
-      <c r="F75" s="30" t="n"/>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="29" t="n"/>
       <c r="G75" s="32" t="n"/>
-      <c r="H75" s="24" t="n"/>
-      <c r="I75" s="29" t="n"/>
-      <c r="J75" s="30" t="n"/>
-      <c r="K75" s="31" t="n"/>
+      <c r="H75" s="23" t="n"/>
+      <c r="I75" s="28" t="n"/>
+      <c r="J75" s="29" t="n"/>
+      <c r="K75" s="30" t="n"/>
       <c r="L75" s="33" t="n"/>
-      <c r="M75" s="29" t="n"/>
-      <c r="N75" s="30" t="n"/>
+      <c r="M75" s="28" t="n"/>
+      <c r="N75" s="29" t="n"/>
       <c r="O75" s="32" t="n"/>
       <c r="P75" s="33" t="n"/>
-      <c r="Q75" s="29" t="n"/>
-      <c r="R75" s="30" t="n"/>
+      <c r="Q75" s="28" t="n"/>
+      <c r="R75" s="29" t="n"/>
       <c r="S75" s="45" t="n"/>
       <c r="T75" s="34" t="n"/>
-      <c r="U75" s="29" t="n"/>
-      <c r="V75" s="30" t="n"/>
+      <c r="U75" s="28" t="n"/>
+      <c r="V75" s="29" t="n"/>
       <c r="W75" s="32" t="n"/>
-      <c r="X75" s="24" t="n"/>
-      <c r="Y75" s="29" t="n"/>
-      <c r="Z75" s="30" t="n"/>
-      <c r="AA75" s="31" t="n"/>
-      <c r="AB75" s="24" t="n"/>
-      <c r="AC75" s="29" t="n"/>
-      <c r="AD75" s="30" t="n"/>
+      <c r="X75" s="23" t="n"/>
+      <c r="Y75" s="28" t="n"/>
+      <c r="Z75" s="29" t="n"/>
+      <c r="AA75" s="30" t="n"/>
+      <c r="AB75" s="23" t="n"/>
+      <c r="AC75" s="28" t="n"/>
+      <c r="AD75" s="29" t="n"/>
       <c r="AE75" s="32" t="n"/>
-      <c r="AF75" s="33" t="n"/>
-      <c r="AG75" s="29" t="n"/>
-      <c r="AH75" s="30" t="n"/>
-      <c r="AI75" s="31" t="n"/>
+      <c r="AF75" s="31" t="n"/>
+      <c r="AG75" s="28" t="n"/>
+      <c r="AH75" s="29" t="n"/>
+      <c r="AI75" s="30" t="n"/>
       <c r="AJ75" s="33" t="n"/>
-      <c r="AK75" s="29" t="n"/>
-      <c r="AL75" s="30" t="n"/>
-      <c r="AM75" s="31" t="n"/>
+      <c r="AK75" s="28" t="n"/>
+      <c r="AL75" s="29" t="n"/>
+      <c r="AM75" s="30" t="n"/>
       <c r="AN75" s="33" t="n"/>
-      <c r="AO75" s="29" t="n"/>
-      <c r="AP75" s="30" t="n"/>
+      <c r="AO75" s="28" t="n"/>
+      <c r="AP75" s="29" t="n"/>
       <c r="AQ75" s="32" t="n"/>
       <c r="AR75" s="33" t="n"/>
-      <c r="AS75" s="29" t="n"/>
-      <c r="AT75" s="30" t="n"/>
+      <c r="AS75" s="28" t="n"/>
+      <c r="AT75" s="29" t="n"/>
       <c r="AU75" s="32" t="n"/>
       <c r="AV75" s="33" t="n"/>
     </row>
@@ -6761,11 +6764,7 @@
         <v>25</v>
       </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="50" t="inlineStr">
-        <is>
-          <t>Visite du Pape</t>
-        </is>
-      </c>
+      <c r="D76" s="25" t="n"/>
       <c r="E76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6775,7 +6774,7 @@
         <v>25</v>
       </c>
       <c r="G76" s="12" t="n"/>
-      <c r="H76" s="24" t="n"/>
+      <c r="H76" s="23" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6785,7 +6784,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="7" t="n"/>
-      <c r="L76" s="19" t="n"/>
+      <c r="L76" s="18" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6795,7 +6794,7 @@
         <v>25</v>
       </c>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="20" t="inlineStr">
+      <c r="P76" s="19" t="inlineStr">
         <is>
           <t>Noël</t>
         </is>
@@ -6809,7 +6808,7 @@
         <v>25</v>
       </c>
       <c r="S76" s="7" t="n"/>
-      <c r="T76" s="19" t="n"/>
+      <c r="T76" s="18" t="n"/>
       <c r="U76" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6819,7 +6818,7 @@
         <v>25</v>
       </c>
       <c r="W76" s="12" t="n"/>
-      <c r="X76" s="24" t="n"/>
+      <c r="X76" s="23" t="n"/>
       <c r="Y76" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6829,7 +6828,7 @@
         <v>25</v>
       </c>
       <c r="AA76" s="7" t="n"/>
-      <c r="AB76" s="24" t="n"/>
+      <c r="AB76" s="23" t="n"/>
       <c r="AC76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6839,7 +6838,7 @@
         <v>25</v>
       </c>
       <c r="AE76" s="12" t="n"/>
-      <c r="AF76" s="21" t="n"/>
+      <c r="AF76" s="20" t="n"/>
       <c r="AG76" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6863,7 +6862,7 @@
         <v>25</v>
       </c>
       <c r="AM76" s="7" t="n"/>
-      <c r="AN76" s="19" t="n"/>
+      <c r="AN76" s="18" t="n"/>
       <c r="AO76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6873,7 +6872,7 @@
         <v>25</v>
       </c>
       <c r="AQ76" s="12" t="n"/>
-      <c r="AR76" s="21" t="n"/>
+      <c r="AR76" s="20" t="n"/>
       <c r="AS76" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6883,101 +6882,101 @@
         <v>25</v>
       </c>
       <c r="AU76" s="12" t="n"/>
-      <c r="AV76" s="19" t="n"/>
+      <c r="AV76" s="18" t="n"/>
     </row>
     <row r="77" ht="20.1" customHeight="1">
-      <c r="A77" s="22" t="n"/>
-      <c r="C77" s="23" t="n"/>
-      <c r="D77" s="24" t="n"/>
-      <c r="E77" s="22" t="n"/>
-      <c r="G77" s="25" t="n"/>
-      <c r="H77" s="24" t="n"/>
-      <c r="I77" s="22" t="n"/>
-      <c r="K77" s="23" t="n"/>
-      <c r="L77" s="27" t="n"/>
-      <c r="M77" s="22" t="n"/>
-      <c r="O77" s="25" t="n"/>
-      <c r="P77" s="24" t="n"/>
-      <c r="Q77" s="22" t="n"/>
-      <c r="S77" s="23" t="n"/>
-      <c r="T77" s="27" t="n"/>
-      <c r="U77" s="22" t="n"/>
-      <c r="W77" s="25" t="n"/>
-      <c r="X77" s="24" t="n"/>
-      <c r="Y77" s="22" t="n"/>
-      <c r="AA77" s="23" t="n"/>
-      <c r="AB77" s="26" t="n"/>
-      <c r="AC77" s="22" t="n"/>
-      <c r="AE77" s="25" t="n"/>
-      <c r="AF77" s="28" t="n"/>
-      <c r="AG77" s="22" t="n"/>
-      <c r="AI77" s="23" t="n"/>
+      <c r="A77" s="21" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="21" t="n"/>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="23" t="n"/>
+      <c r="I77" s="21" t="n"/>
+      <c r="K77" s="22" t="n"/>
+      <c r="L77" s="26" t="n"/>
+      <c r="M77" s="21" t="n"/>
+      <c r="O77" s="24" t="n"/>
+      <c r="P77" s="23" t="n"/>
+      <c r="Q77" s="21" t="n"/>
+      <c r="S77" s="22" t="n"/>
+      <c r="T77" s="26" t="n"/>
+      <c r="U77" s="21" t="n"/>
+      <c r="W77" s="24" t="n"/>
+      <c r="X77" s="23" t="n"/>
+      <c r="Y77" s="21" t="n"/>
+      <c r="AA77" s="22" t="n"/>
+      <c r="AB77" s="31" t="n"/>
+      <c r="AC77" s="21" t="n"/>
+      <c r="AE77" s="24" t="n"/>
+      <c r="AF77" s="27" t="n"/>
+      <c r="AG77" s="21" t="n"/>
+      <c r="AI77" s="22" t="n"/>
       <c r="AJ77" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AK77" s="22" t="n"/>
-      <c r="AM77" s="23" t="n"/>
-      <c r="AN77" s="27" t="n"/>
-      <c r="AO77" s="22" t="n"/>
-      <c r="AQ77" s="25" t="n"/>
-      <c r="AR77" s="28" t="n"/>
-      <c r="AS77" s="22" t="n"/>
-      <c r="AU77" s="25" t="n"/>
-      <c r="AV77" s="27" t="n"/>
+      <c r="AK77" s="21" t="n"/>
+      <c r="AM77" s="22" t="n"/>
+      <c r="AN77" s="26" t="n"/>
+      <c r="AO77" s="21" t="n"/>
+      <c r="AQ77" s="24" t="n"/>
+      <c r="AR77" s="27" t="n"/>
+      <c r="AS77" s="21" t="n"/>
+      <c r="AU77" s="24" t="n"/>
+      <c r="AV77" s="26" t="n"/>
     </row>
     <row r="78" ht="20.1" customHeight="1">
-      <c r="A78" s="29" t="n"/>
-      <c r="B78" s="30" t="n"/>
-      <c r="C78" s="31" t="n"/>
-      <c r="D78" s="24" t="n"/>
-      <c r="E78" s="29" t="n"/>
-      <c r="F78" s="30" t="n"/>
+      <c r="A78" s="28" t="n"/>
+      <c r="B78" s="29" t="n"/>
+      <c r="C78" s="30" t="n"/>
+      <c r="D78" s="23" t="n"/>
+      <c r="E78" s="28" t="n"/>
+      <c r="F78" s="29" t="n"/>
       <c r="G78" s="32" t="n"/>
-      <c r="H78" s="24" t="n"/>
-      <c r="I78" s="29" t="n"/>
-      <c r="J78" s="30" t="n"/>
-      <c r="K78" s="31" t="n"/>
+      <c r="H78" s="23" t="n"/>
+      <c r="I78" s="28" t="n"/>
+      <c r="J78" s="29" t="n"/>
+      <c r="K78" s="30" t="n"/>
       <c r="L78" s="33" t="n"/>
-      <c r="M78" s="29" t="n"/>
-      <c r="N78" s="30" t="n"/>
+      <c r="M78" s="28" t="n"/>
+      <c r="N78" s="29" t="n"/>
       <c r="O78" s="32" t="n"/>
-      <c r="P78" s="26" t="n"/>
-      <c r="Q78" s="29" t="n"/>
-      <c r="R78" s="30" t="n"/>
-      <c r="S78" s="31" t="n"/>
+      <c r="P78" s="31" t="n"/>
+      <c r="Q78" s="28" t="n"/>
+      <c r="R78" s="29" t="n"/>
+      <c r="S78" s="30" t="n"/>
       <c r="T78" s="33" t="n"/>
-      <c r="U78" s="29" t="n"/>
-      <c r="V78" s="30" t="n"/>
+      <c r="U78" s="28" t="n"/>
+      <c r="V78" s="29" t="n"/>
       <c r="W78" s="32" t="n"/>
-      <c r="X78" s="24" t="n"/>
-      <c r="Y78" s="29" t="n"/>
-      <c r="Z78" s="30" t="n"/>
-      <c r="AA78" s="31" t="n"/>
-      <c r="AB78" s="49" t="inlineStr">
+      <c r="X78" s="23" t="n"/>
+      <c r="Y78" s="28" t="n"/>
+      <c r="Z78" s="29" t="n"/>
+      <c r="AA78" s="30" t="n"/>
+      <c r="AB78" s="50" t="inlineStr">
         <is>
           <t>Jeudi saint</t>
         </is>
       </c>
-      <c r="AC78" s="29" t="n"/>
-      <c r="AD78" s="30" t="n"/>
+      <c r="AC78" s="28" t="n"/>
+      <c r="AD78" s="29" t="n"/>
       <c r="AE78" s="32" t="n"/>
       <c r="AF78" s="34" t="n"/>
-      <c r="AG78" s="29" t="n"/>
-      <c r="AH78" s="30" t="n"/>
-      <c r="AI78" s="31" t="n"/>
+      <c r="AG78" s="28" t="n"/>
+      <c r="AH78" s="29" t="n"/>
+      <c r="AI78" s="30" t="n"/>
       <c r="AJ78" s="33" t="n"/>
-      <c r="AK78" s="29" t="n"/>
-      <c r="AL78" s="30" t="n"/>
-      <c r="AM78" s="31" t="n"/>
+      <c r="AK78" s="28" t="n"/>
+      <c r="AL78" s="29" t="n"/>
+      <c r="AM78" s="30" t="n"/>
       <c r="AN78" s="33" t="n"/>
-      <c r="AO78" s="29" t="n"/>
-      <c r="AP78" s="30" t="n"/>
+      <c r="AO78" s="28" t="n"/>
+      <c r="AP78" s="29" t="n"/>
       <c r="AQ78" s="32" t="n"/>
       <c r="AR78" s="34" t="n"/>
-      <c r="AS78" s="29" t="n"/>
-      <c r="AT78" s="30" t="n"/>
+      <c r="AS78" s="28" t="n"/>
+      <c r="AT78" s="29" t="n"/>
       <c r="AU78" s="32" t="n"/>
       <c r="AV78" s="33" t="n"/>
     </row>
@@ -6991,7 +6990,7 @@
         <v>26</v>
       </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="24" t="n"/>
+      <c r="D79" s="31" t="n"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7001,7 +7000,7 @@
         <v>26</v>
       </c>
       <c r="G79" s="12" t="n"/>
-      <c r="H79" s="24" t="n"/>
+      <c r="H79" s="23" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7011,7 +7010,7 @@
         <v>26</v>
       </c>
       <c r="K79" s="7" t="n"/>
-      <c r="L79" s="19" t="n"/>
+      <c r="L79" s="18" t="n"/>
       <c r="M79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7021,7 +7020,11 @@
         <v>26</v>
       </c>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="19" t="n"/>
+      <c r="P79" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7045,7 +7048,7 @@
         <v>26</v>
       </c>
       <c r="W79" s="12" t="n"/>
-      <c r="X79" s="24" t="n"/>
+      <c r="X79" s="23" t="n"/>
       <c r="Y79" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -7055,7 +7058,7 @@
         <v>26</v>
       </c>
       <c r="AA79" s="7" t="n"/>
-      <c r="AB79" s="49" t="inlineStr">
+      <c r="AB79" s="50" t="inlineStr">
         <is>
           <t>Vendredi saint</t>
         </is>
@@ -7069,7 +7072,7 @@
         <v>26</v>
       </c>
       <c r="AE79" s="12" t="n"/>
-      <c r="AF79" s="19" t="n"/>
+      <c r="AF79" s="18" t="n"/>
       <c r="AG79" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7079,7 +7082,7 @@
         <v>26</v>
       </c>
       <c r="AI79" s="7" t="n"/>
-      <c r="AJ79" s="19" t="n"/>
+      <c r="AJ79" s="18" t="n"/>
       <c r="AK79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7089,7 +7092,11 @@
         <v>26</v>
       </c>
       <c r="AM79" s="7" t="n"/>
-      <c r="AN79" s="19" t="n"/>
+      <c r="AN79" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
       <c r="AO79" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7099,7 +7106,7 @@
         <v>26</v>
       </c>
       <c r="AQ79" s="12" t="n"/>
-      <c r="AR79" s="19" t="n"/>
+      <c r="AR79" s="18" t="n"/>
       <c r="AS79" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7109,101 +7116,105 @@
         <v>26</v>
       </c>
       <c r="AU79" s="12" t="n"/>
-      <c r="AV79" s="19" t="n"/>
+      <c r="AV79" s="18" t="n"/>
     </row>
     <row r="80" ht="20.1" customHeight="1">
-      <c r="A80" s="22" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="22" t="n"/>
-      <c r="G80" s="25" t="n"/>
-      <c r="H80" s="24" t="n"/>
-      <c r="I80" s="22" t="n"/>
-      <c r="K80" s="23" t="n"/>
-      <c r="L80" s="27" t="n"/>
-      <c r="M80" s="22" t="n"/>
-      <c r="O80" s="25" t="n"/>
-      <c r="P80" s="27" t="n"/>
-      <c r="Q80" s="22" t="n"/>
-      <c r="S80" s="23" t="n"/>
+      <c r="A80" s="21" t="n"/>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="n"/>
+      <c r="G80" s="24" t="n"/>
+      <c r="H80" s="23" t="n"/>
+      <c r="I80" s="21" t="n"/>
+      <c r="K80" s="22" t="n"/>
+      <c r="L80" s="26" t="n"/>
+      <c r="M80" s="21" t="n"/>
+      <c r="O80" s="24" t="n"/>
+      <c r="P80" s="23" t="n"/>
+      <c r="Q80" s="21" t="n"/>
+      <c r="S80" s="22" t="n"/>
       <c r="T80" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="U80" s="22" t="n"/>
-      <c r="W80" s="25" t="n"/>
-      <c r="X80" s="24" t="n"/>
-      <c r="Y80" s="22" t="n"/>
-      <c r="AA80" s="23" t="n"/>
+      <c r="U80" s="21" t="n"/>
+      <c r="W80" s="24" t="n"/>
+      <c r="X80" s="23" t="n"/>
+      <c r="Y80" s="21" t="n"/>
+      <c r="AA80" s="22" t="n"/>
       <c r="AB80" s="47" t="n"/>
-      <c r="AC80" s="22" t="n"/>
-      <c r="AE80" s="25" t="n"/>
-      <c r="AF80" s="27" t="n"/>
-      <c r="AG80" s="22" t="n"/>
-      <c r="AI80" s="23" t="n"/>
-      <c r="AJ80" s="27" t="n"/>
-      <c r="AK80" s="22" t="n"/>
-      <c r="AM80" s="23" t="n"/>
-      <c r="AN80" s="27" t="n"/>
-      <c r="AO80" s="22" t="n"/>
-      <c r="AQ80" s="25" t="n"/>
-      <c r="AR80" s="27" t="n"/>
-      <c r="AS80" s="22" t="n"/>
-      <c r="AU80" s="25" t="n"/>
-      <c r="AV80" s="27" t="n"/>
+      <c r="AC80" s="21" t="n"/>
+      <c r="AE80" s="24" t="n"/>
+      <c r="AF80" s="26" t="n"/>
+      <c r="AG80" s="21" t="n"/>
+      <c r="AI80" s="22" t="n"/>
+      <c r="AJ80" s="26" t="n"/>
+      <c r="AK80" s="21" t="n"/>
+      <c r="AM80" s="22" t="n"/>
+      <c r="AN80" s="23" t="n"/>
+      <c r="AO80" s="21" t="n"/>
+      <c r="AQ80" s="24" t="n"/>
+      <c r="AR80" s="26" t="n"/>
+      <c r="AS80" s="21" t="n"/>
+      <c r="AU80" s="24" t="n"/>
+      <c r="AV80" s="26" t="n"/>
     </row>
     <row r="81" ht="20.1" customHeight="1">
-      <c r="A81" s="29" t="n"/>
-      <c r="B81" s="30" t="n"/>
-      <c r="C81" s="31" t="n"/>
+      <c r="A81" s="28" t="n"/>
+      <c r="B81" s="29" t="n"/>
+      <c r="C81" s="30" t="n"/>
       <c r="D81" s="40" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="E81" s="29" t="n"/>
-      <c r="F81" s="30" t="n"/>
+      <c r="E81" s="28" t="n"/>
+      <c r="F81" s="29" t="n"/>
       <c r="G81" s="32" t="n"/>
-      <c r="H81" s="24" t="n"/>
-      <c r="I81" s="29" t="n"/>
-      <c r="J81" s="30" t="n"/>
-      <c r="K81" s="31" t="n"/>
+      <c r="H81" s="23" t="n"/>
+      <c r="I81" s="28" t="n"/>
+      <c r="J81" s="29" t="n"/>
+      <c r="K81" s="30" t="n"/>
       <c r="L81" s="33" t="n"/>
-      <c r="M81" s="29" t="n"/>
-      <c r="N81" s="30" t="n"/>
+      <c r="M81" s="28" t="n"/>
+      <c r="N81" s="29" t="n"/>
       <c r="O81" s="32" t="n"/>
-      <c r="P81" s="33" t="n"/>
-      <c r="Q81" s="29" t="n"/>
-      <c r="R81" s="30" t="n"/>
-      <c r="S81" s="31" t="n"/>
+      <c r="P81" s="31" t="n"/>
+      <c r="Q81" s="28" t="n"/>
+      <c r="R81" s="29" t="n"/>
+      <c r="S81" s="30" t="n"/>
       <c r="T81" s="33" t="n"/>
-      <c r="U81" s="29" t="n"/>
-      <c r="V81" s="30" t="n"/>
+      <c r="U81" s="28" t="n"/>
+      <c r="V81" s="29" t="n"/>
       <c r="W81" s="32" t="n"/>
-      <c r="X81" s="26" t="n"/>
-      <c r="Y81" s="29" t="n"/>
-      <c r="Z81" s="30" t="n"/>
-      <c r="AA81" s="31" t="n"/>
-      <c r="AB81" s="24" t="n"/>
-      <c r="AC81" s="29" t="n"/>
-      <c r="AD81" s="30" t="n"/>
+      <c r="X81" s="31" t="n"/>
+      <c r="Y81" s="28" t="n"/>
+      <c r="Z81" s="29" t="n"/>
+      <c r="AA81" s="30" t="n"/>
+      <c r="AB81" s="23" t="n"/>
+      <c r="AC81" s="28" t="n"/>
+      <c r="AD81" s="29" t="n"/>
       <c r="AE81" s="32" t="n"/>
       <c r="AF81" s="33" t="n"/>
-      <c r="AG81" s="29" t="n"/>
-      <c r="AH81" s="30" t="n"/>
-      <c r="AI81" s="31" t="n"/>
+      <c r="AG81" s="28" t="n"/>
+      <c r="AH81" s="29" t="n"/>
+      <c r="AI81" s="30" t="n"/>
       <c r="AJ81" s="33" t="n"/>
-      <c r="AK81" s="29" t="n"/>
-      <c r="AL81" s="30" t="n"/>
-      <c r="AM81" s="31" t="n"/>
-      <c r="AN81" s="33" t="n"/>
-      <c r="AO81" s="29" t="n"/>
-      <c r="AP81" s="30" t="n"/>
+      <c r="AK81" s="28" t="n"/>
+      <c r="AL81" s="29" t="n"/>
+      <c r="AM81" s="30" t="n"/>
+      <c r="AN81" s="31" t="n"/>
+      <c r="AO81" s="28" t="n"/>
+      <c r="AP81" s="29" t="n"/>
       <c r="AQ81" s="32" t="n"/>
       <c r="AR81" s="33" t="n"/>
-      <c r="AS81" s="29" t="n"/>
-      <c r="AT81" s="30" t="n"/>
+      <c r="AS81" s="28" t="n"/>
+      <c r="AT81" s="29" t="n"/>
       <c r="AU81" s="32" t="n"/>
       <c r="AV81" s="33" t="n"/>
     </row>
@@ -7216,7 +7227,7 @@
       <c r="B82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C82" s="41" t="n"/>
+      <c r="C82" s="42" t="n"/>
       <c r="D82" s="40" t="inlineStr">
         <is>
           <t>Baptême</t>
@@ -7231,7 +7242,7 @@
         <v>27</v>
       </c>
       <c r="G82" s="12" t="n"/>
-      <c r="H82" s="24" t="n"/>
+      <c r="H82" s="23" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7255,7 +7266,7 @@
         <v>27</v>
       </c>
       <c r="O82" s="12" t="n"/>
-      <c r="P82" s="21" t="n"/>
+      <c r="P82" s="20" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7265,7 +7276,7 @@
         <v>27</v>
       </c>
       <c r="S82" s="7" t="n"/>
-      <c r="T82" s="19" t="n"/>
+      <c r="T82" s="18" t="n"/>
       <c r="U82" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -7275,7 +7286,11 @@
         <v>27</v>
       </c>
       <c r="W82" s="12" t="n"/>
-      <c r="X82" s="19" t="n"/>
+      <c r="X82" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
       <c r="Y82" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -7285,7 +7300,7 @@
         <v>27</v>
       </c>
       <c r="AA82" s="7" t="n"/>
-      <c r="AB82" s="24" t="n"/>
+      <c r="AB82" s="31" t="n"/>
       <c r="AC82" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7295,7 +7310,7 @@
         <v>27</v>
       </c>
       <c r="AE82" s="12" t="n"/>
-      <c r="AF82" s="18" t="inlineStr">
+      <c r="AF82" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -7322,8 +7337,8 @@
       <c r="AL82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="AM82" s="41" t="n"/>
-      <c r="AN82" s="18" t="inlineStr">
+      <c r="AM82" s="42" t="n"/>
+      <c r="AN82" s="17" t="inlineStr">
         <is>
           <t>Fête de départ de la paroisse</t>
         </is>
@@ -7337,7 +7352,7 @@
         <v>27</v>
       </c>
       <c r="AQ82" s="12" t="n"/>
-      <c r="AR82" s="19" t="n"/>
+      <c r="AR82" s="18" t="n"/>
       <c r="AS82" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7347,101 +7362,109 @@
         <v>27</v>
       </c>
       <c r="AU82" s="12" t="n"/>
-      <c r="AV82" s="19" t="n"/>
+      <c r="AV82" s="18" t="n"/>
     </row>
     <row r="83" ht="20.1" customHeight="1">
-      <c r="A83" s="22" t="n"/>
+      <c r="A83" s="21" t="n"/>
       <c r="C83" s="44" t="n"/>
-      <c r="D83" s="50" t="n"/>
-      <c r="E83" s="22" t="n"/>
-      <c r="G83" s="25" t="n"/>
-      <c r="H83" s="26" t="n"/>
-      <c r="I83" s="22" t="n"/>
-      <c r="K83" s="23" t="n"/>
-      <c r="L83" s="24" t="n"/>
-      <c r="M83" s="22" t="n"/>
-      <c r="O83" s="25" t="n"/>
-      <c r="P83" s="28" t="n"/>
-      <c r="Q83" s="22" t="n"/>
-      <c r="S83" s="23" t="n"/>
-      <c r="T83" s="27" t="n"/>
-      <c r="U83" s="22" t="n"/>
-      <c r="W83" s="25" t="n"/>
-      <c r="X83" s="27" t="n"/>
-      <c r="Y83" s="22" t="n"/>
-      <c r="AA83" s="23" t="n"/>
-      <c r="AB83" s="26" t="n"/>
-      <c r="AC83" s="22" t="n"/>
-      <c r="AE83" s="25" t="n"/>
-      <c r="AF83" s="24" t="n"/>
-      <c r="AG83" s="22" t="n"/>
-      <c r="AI83" s="23" t="n"/>
-      <c r="AJ83" s="24" t="n"/>
-      <c r="AK83" s="22" t="n"/>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>Visite du Pape</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="n"/>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="31" t="n"/>
+      <c r="I83" s="21" t="n"/>
+      <c r="K83" s="22" t="n"/>
+      <c r="L83" s="23" t="n"/>
+      <c r="M83" s="21" t="n"/>
+      <c r="O83" s="24" t="n"/>
+      <c r="P83" s="27" t="n"/>
+      <c r="Q83" s="21" t="n"/>
+      <c r="S83" s="22" t="n"/>
+      <c r="T83" s="26" t="n"/>
+      <c r="U83" s="21" t="n"/>
+      <c r="W83" s="24" t="n"/>
+      <c r="X83" s="23" t="n"/>
+      <c r="Y83" s="21" t="n"/>
+      <c r="AA83" s="22" t="n"/>
+      <c r="AB83" s="36" t="inlineStr">
+        <is>
+          <t>Catéchuménat</t>
+        </is>
+      </c>
+      <c r="AC83" s="21" t="n"/>
+      <c r="AE83" s="24" t="n"/>
+      <c r="AF83" s="23" t="n"/>
+      <c r="AG83" s="21" t="n"/>
+      <c r="AI83" s="22" t="n"/>
+      <c r="AJ83" s="23" t="n"/>
+      <c r="AK83" s="21" t="n"/>
       <c r="AM83" s="44" t="n"/>
-      <c r="AN83" s="24" t="n"/>
-      <c r="AO83" s="22" t="n"/>
-      <c r="AQ83" s="25" t="n"/>
-      <c r="AR83" s="27" t="n"/>
-      <c r="AS83" s="22" t="n"/>
-      <c r="AU83" s="25" t="n"/>
-      <c r="AV83" s="27" t="n"/>
+      <c r="AN83" s="23" t="n"/>
+      <c r="AO83" s="21" t="n"/>
+      <c r="AQ83" s="24" t="n"/>
+      <c r="AR83" s="26" t="n"/>
+      <c r="AS83" s="21" t="n"/>
+      <c r="AU83" s="24" t="n"/>
+      <c r="AV83" s="26" t="n"/>
     </row>
     <row r="84" ht="20.1" customHeight="1">
-      <c r="A84" s="29" t="n"/>
-      <c r="B84" s="30" t="n"/>
+      <c r="A84" s="28" t="n"/>
+      <c r="B84" s="29" t="n"/>
       <c r="C84" s="45" t="n"/>
-      <c r="D84" s="24" t="n"/>
-      <c r="E84" s="29" t="n"/>
-      <c r="F84" s="30" t="n"/>
+      <c r="D84" s="23" t="n"/>
+      <c r="E84" s="28" t="n"/>
+      <c r="F84" s="29" t="n"/>
       <c r="G84" s="32" t="n"/>
       <c r="H84" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="I84" s="29" t="n"/>
-      <c r="J84" s="30" t="n"/>
-      <c r="K84" s="31" t="n"/>
-      <c r="L84" s="26" t="n"/>
-      <c r="M84" s="29" t="n"/>
-      <c r="N84" s="30" t="n"/>
+      <c r="I84" s="28" t="n"/>
+      <c r="J84" s="29" t="n"/>
+      <c r="K84" s="30" t="n"/>
+      <c r="L84" s="31" t="n"/>
+      <c r="M84" s="28" t="n"/>
+      <c r="N84" s="29" t="n"/>
       <c r="O84" s="32" t="n"/>
       <c r="P84" s="34" t="n"/>
-      <c r="Q84" s="29" t="n"/>
-      <c r="R84" s="30" t="n"/>
-      <c r="S84" s="31" t="n"/>
+      <c r="Q84" s="28" t="n"/>
+      <c r="R84" s="29" t="n"/>
+      <c r="S84" s="30" t="n"/>
       <c r="T84" s="33" t="n"/>
-      <c r="U84" s="29" t="n"/>
-      <c r="V84" s="30" t="n"/>
+      <c r="U84" s="28" t="n"/>
+      <c r="V84" s="29" t="n"/>
       <c r="W84" s="32" t="n"/>
-      <c r="X84" s="33" t="n"/>
-      <c r="Y84" s="29" t="n"/>
-      <c r="Z84" s="30" t="n"/>
-      <c r="AA84" s="31" t="n"/>
-      <c r="AB84" s="36" t="inlineStr">
-        <is>
-          <t>Catéchuménat</t>
-        </is>
-      </c>
-      <c r="AC84" s="29" t="n"/>
-      <c r="AD84" s="30" t="n"/>
+      <c r="X84" s="31" t="n"/>
+      <c r="Y84" s="28" t="n"/>
+      <c r="Z84" s="29" t="n"/>
+      <c r="AA84" s="30" t="n"/>
+      <c r="AB84" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="AC84" s="28" t="n"/>
+      <c r="AD84" s="29" t="n"/>
       <c r="AE84" s="32" t="n"/>
-      <c r="AF84" s="26" t="n"/>
-      <c r="AG84" s="29" t="n"/>
-      <c r="AH84" s="30" t="n"/>
-      <c r="AI84" s="31" t="n"/>
-      <c r="AJ84" s="26" t="n"/>
-      <c r="AK84" s="29" t="n"/>
-      <c r="AL84" s="30" t="n"/>
+      <c r="AF84" s="31" t="n"/>
+      <c r="AG84" s="28" t="n"/>
+      <c r="AH84" s="29" t="n"/>
+      <c r="AI84" s="30" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="28" t="n"/>
+      <c r="AL84" s="29" t="n"/>
       <c r="AM84" s="45" t="n"/>
-      <c r="AN84" s="26" t="n"/>
-      <c r="AO84" s="29" t="n"/>
-      <c r="AP84" s="30" t="n"/>
+      <c r="AN84" s="31" t="n"/>
+      <c r="AO84" s="28" t="n"/>
+      <c r="AP84" s="29" t="n"/>
       <c r="AQ84" s="32" t="n"/>
       <c r="AR84" s="33" t="n"/>
-      <c r="AS84" s="29" t="n"/>
-      <c r="AT84" s="30" t="n"/>
+      <c r="AS84" s="28" t="n"/>
+      <c r="AT84" s="29" t="n"/>
       <c r="AU84" s="32" t="n"/>
       <c r="AV84" s="33" t="n"/>
     </row>
@@ -7455,7 +7478,7 @@
         <v>28</v>
       </c>
       <c r="C85" s="7" t="n"/>
-      <c r="D85" s="24" t="n"/>
+      <c r="D85" s="23" t="n"/>
       <c r="E85" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7465,11 +7488,7 @@
         <v>28</v>
       </c>
       <c r="G85" s="12" t="n"/>
-      <c r="H85" s="56" t="inlineStr">
-        <is>
-          <t>Père Pascal en Côte d'Ivoire</t>
-        </is>
-      </c>
+      <c r="H85" s="41" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7479,7 +7498,7 @@
         <v>28</v>
       </c>
       <c r="K85" s="7" t="n"/>
-      <c r="L85" s="18" t="inlineStr">
+      <c r="L85" s="16" t="inlineStr">
         <is>
           <t>CMP avec Chartres 2040</t>
         </is>
@@ -7493,7 +7512,7 @@
         <v>28</v>
       </c>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="19" t="n"/>
+      <c r="P85" s="18" t="n"/>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7517,7 +7536,7 @@
         <v>28</v>
       </c>
       <c r="W85" s="12" t="n"/>
-      <c r="X85" s="49" t="inlineStr">
+      <c r="X85" s="50" t="inlineStr">
         <is>
           <t>3e dim. de Carême</t>
         </is>
@@ -7530,8 +7549,8 @@
       <c r="Z85" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AA85" s="41" t="n"/>
-      <c r="AB85" s="20" t="inlineStr">
+      <c r="AA85" s="42" t="n"/>
+      <c r="AB85" s="19" t="inlineStr">
         <is>
           <t>Pâques</t>
         </is>
@@ -7545,7 +7564,7 @@
         <v>28</v>
       </c>
       <c r="AE85" s="12" t="n"/>
-      <c r="AF85" s="19" t="n"/>
+      <c r="AF85" s="18" t="n"/>
       <c r="AG85" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7555,7 +7574,7 @@
         <v>28</v>
       </c>
       <c r="AI85" s="7" t="n"/>
-      <c r="AJ85" s="19" t="n"/>
+      <c r="AJ85" s="18" t="n"/>
       <c r="AK85" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7565,7 +7584,7 @@
         <v>28</v>
       </c>
       <c r="AM85" s="7" t="n"/>
-      <c r="AN85" s="19" t="n"/>
+      <c r="AN85" s="18" t="n"/>
       <c r="AO85" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7575,7 +7594,7 @@
         <v>28</v>
       </c>
       <c r="AQ85" s="12" t="n"/>
-      <c r="AR85" s="19" t="n"/>
+      <c r="AR85" s="18" t="n"/>
       <c r="AS85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7585,99 +7604,107 @@
         <v>28</v>
       </c>
       <c r="AU85" s="12" t="n"/>
-      <c r="AV85" s="19" t="n"/>
+      <c r="AV85" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="20.1" customHeight="1">
-      <c r="A86" s="22" t="n"/>
-      <c r="C86" s="23" t="n"/>
-      <c r="D86" s="24" t="n"/>
-      <c r="E86" s="22" t="n"/>
-      <c r="G86" s="25" t="n"/>
-      <c r="H86" s="24" t="n"/>
-      <c r="I86" s="22" t="n"/>
-      <c r="K86" s="23" t="n"/>
-      <c r="L86" s="24" t="n"/>
-      <c r="M86" s="22" t="n"/>
-      <c r="O86" s="25" t="n"/>
-      <c r="P86" s="27" t="n"/>
-      <c r="Q86" s="22" t="n"/>
-      <c r="S86" s="23" t="n"/>
-      <c r="T86" s="24" t="n"/>
-      <c r="U86" s="22" t="n"/>
-      <c r="W86" s="25" t="n"/>
+      <c r="A86" s="21" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="23" t="n"/>
+      <c r="E86" s="21" t="n"/>
+      <c r="G86" s="24" t="n"/>
+      <c r="H86" s="23" t="n"/>
+      <c r="I86" s="21" t="n"/>
+      <c r="K86" s="22" t="n"/>
+      <c r="L86" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="M86" s="21" t="n"/>
+      <c r="O86" s="24" t="n"/>
+      <c r="P86" s="26" t="n"/>
+      <c r="Q86" s="21" t="n"/>
+      <c r="S86" s="22" t="n"/>
+      <c r="T86" s="23" t="n"/>
+      <c r="U86" s="21" t="n"/>
+      <c r="W86" s="24" t="n"/>
       <c r="X86" s="36" t="inlineStr">
         <is>
           <t>1er scrutin</t>
         </is>
       </c>
-      <c r="Y86" s="22" t="n"/>
+      <c r="Y86" s="21" t="n"/>
       <c r="AA86" s="44" t="n"/>
-      <c r="AB86" s="24" t="n"/>
-      <c r="AC86" s="22" t="n"/>
-      <c r="AE86" s="25" t="n"/>
-      <c r="AF86" s="27" t="n"/>
-      <c r="AG86" s="22" t="n"/>
-      <c r="AI86" s="23" t="n"/>
-      <c r="AJ86" s="27" t="n"/>
-      <c r="AK86" s="22" t="n"/>
-      <c r="AM86" s="23" t="n"/>
-      <c r="AN86" s="27" t="n"/>
-      <c r="AO86" s="22" t="n"/>
-      <c r="AQ86" s="25" t="n"/>
-      <c r="AR86" s="27" t="n"/>
-      <c r="AS86" s="22" t="n"/>
-      <c r="AU86" s="25" t="n"/>
-      <c r="AV86" s="27" t="n"/>
+      <c r="AB86" s="23" t="n"/>
+      <c r="AC86" s="21" t="n"/>
+      <c r="AE86" s="24" t="n"/>
+      <c r="AF86" s="26" t="n"/>
+      <c r="AG86" s="21" t="n"/>
+      <c r="AI86" s="22" t="n"/>
+      <c r="AJ86" s="26" t="n"/>
+      <c r="AK86" s="21" t="n"/>
+      <c r="AM86" s="22" t="n"/>
+      <c r="AN86" s="26" t="n"/>
+      <c r="AO86" s="21" t="n"/>
+      <c r="AQ86" s="24" t="n"/>
+      <c r="AR86" s="26" t="n"/>
+      <c r="AS86" s="21" t="n"/>
+      <c r="AU86" s="24" t="n"/>
+      <c r="AV86" s="23" t="n"/>
     </row>
     <row r="87" ht="20.1" customHeight="1">
-      <c r="A87" s="29" t="n"/>
-      <c r="B87" s="30" t="n"/>
-      <c r="C87" s="31" t="n"/>
-      <c r="D87" s="26" t="n"/>
-      <c r="E87" s="29" t="n"/>
-      <c r="F87" s="30" t="n"/>
+      <c r="A87" s="28" t="n"/>
+      <c r="B87" s="29" t="n"/>
+      <c r="C87" s="30" t="n"/>
+      <c r="D87" s="31" t="n"/>
+      <c r="E87" s="28" t="n"/>
+      <c r="F87" s="29" t="n"/>
       <c r="G87" s="32" t="n"/>
-      <c r="H87" s="24" t="n"/>
-      <c r="I87" s="29" t="n"/>
-      <c r="J87" s="30" t="n"/>
-      <c r="K87" s="31" t="n"/>
-      <c r="L87" s="26" t="n"/>
-      <c r="M87" s="29" t="n"/>
-      <c r="N87" s="30" t="n"/>
+      <c r="H87" s="23" t="n"/>
+      <c r="I87" s="28" t="n"/>
+      <c r="J87" s="29" t="n"/>
+      <c r="K87" s="30" t="n"/>
+      <c r="L87" s="33" t="n"/>
+      <c r="M87" s="28" t="n"/>
+      <c r="N87" s="29" t="n"/>
       <c r="O87" s="32" t="n"/>
       <c r="P87" s="33" t="n"/>
-      <c r="Q87" s="29" t="n"/>
-      <c r="R87" s="30" t="n"/>
-      <c r="S87" s="31" t="n"/>
-      <c r="T87" s="26" t="n"/>
-      <c r="U87" s="29" t="n"/>
-      <c r="V87" s="30" t="n"/>
+      <c r="Q87" s="28" t="n"/>
+      <c r="R87" s="29" t="n"/>
+      <c r="S87" s="30" t="n"/>
+      <c r="T87" s="31" t="n"/>
+      <c r="U87" s="28" t="n"/>
+      <c r="V87" s="29" t="n"/>
       <c r="W87" s="32" t="n"/>
       <c r="X87" s="34" t="n"/>
-      <c r="Y87" s="29" t="n"/>
-      <c r="Z87" s="30" t="n"/>
+      <c r="Y87" s="28" t="n"/>
+      <c r="Z87" s="29" t="n"/>
       <c r="AA87" s="45" t="n"/>
-      <c r="AB87" s="26" t="n"/>
-      <c r="AC87" s="29" t="n"/>
-      <c r="AD87" s="30" t="n"/>
+      <c r="AB87" s="31" t="n"/>
+      <c r="AC87" s="28" t="n"/>
+      <c r="AD87" s="29" t="n"/>
       <c r="AE87" s="32" t="n"/>
       <c r="AF87" s="33" t="n"/>
-      <c r="AG87" s="29" t="n"/>
-      <c r="AH87" s="30" t="n"/>
-      <c r="AI87" s="31" t="n"/>
+      <c r="AG87" s="28" t="n"/>
+      <c r="AH87" s="29" t="n"/>
+      <c r="AI87" s="30" t="n"/>
       <c r="AJ87" s="33" t="n"/>
-      <c r="AK87" s="29" t="n"/>
-      <c r="AL87" s="30" t="n"/>
-      <c r="AM87" s="31" t="n"/>
+      <c r="AK87" s="28" t="n"/>
+      <c r="AL87" s="29" t="n"/>
+      <c r="AM87" s="30" t="n"/>
       <c r="AN87" s="33" t="n"/>
-      <c r="AO87" s="29" t="n"/>
-      <c r="AP87" s="30" t="n"/>
+      <c r="AO87" s="28" t="n"/>
+      <c r="AP87" s="29" t="n"/>
       <c r="AQ87" s="32" t="n"/>
       <c r="AR87" s="33" t="n"/>
-      <c r="AS87" s="29" t="n"/>
-      <c r="AT87" s="30" t="n"/>
+      <c r="AS87" s="28" t="n"/>
+      <c r="AT87" s="29" t="n"/>
       <c r="AU87" s="32" t="n"/>
-      <c r="AV87" s="33" t="n"/>
+      <c r="AV87" s="31" t="n"/>
     </row>
     <row r="88" ht="20.1" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -7689,7 +7716,7 @@
         <v>29</v>
       </c>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="18" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>Groupe de prière</t>
         </is>
@@ -7703,7 +7730,7 @@
         <v>29</v>
       </c>
       <c r="G88" s="12" t="n"/>
-      <c r="H88" s="24" t="n"/>
+      <c r="H88" s="23" t="n"/>
       <c r="I88" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -7712,7 +7739,7 @@
       <c r="J88" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="K88" s="41" t="n"/>
+      <c r="K88" s="42" t="n"/>
       <c r="L88" s="47" t="inlineStr">
         <is>
           <t>1er dim. de l'Avent</t>
@@ -7727,7 +7754,7 @@
         <v>29</v>
       </c>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="18" t="inlineStr">
+      <c r="P88" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -7741,7 +7768,7 @@
         <v>29</v>
       </c>
       <c r="S88" s="7" t="n"/>
-      <c r="T88" s="19" t="n"/>
+      <c r="T88" s="18" t="n"/>
       <c r="Y88" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7751,7 +7778,7 @@
         <v>29</v>
       </c>
       <c r="AA88" s="7" t="n"/>
-      <c r="AB88" s="17" t="inlineStr">
+      <c r="AB88" s="13" t="inlineStr">
         <is>
           <t>Lundi de Pâques</t>
         </is>
@@ -7765,7 +7792,7 @@
         <v>29</v>
       </c>
       <c r="AE88" s="12" t="n"/>
-      <c r="AF88" s="19" t="n"/>
+      <c r="AF88" s="18" t="n"/>
       <c r="AG88" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7775,7 +7802,7 @@
         <v>29</v>
       </c>
       <c r="AI88" s="7" t="n"/>
-      <c r="AJ88" s="8" t="inlineStr">
+      <c r="AJ88" s="43" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
@@ -7789,7 +7816,7 @@
         <v>29</v>
       </c>
       <c r="AM88" s="7" t="n"/>
-      <c r="AN88" s="18" t="inlineStr">
+      <c r="AN88" s="17" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
@@ -7803,7 +7830,7 @@
         <v>29</v>
       </c>
       <c r="AQ88" s="12" t="n"/>
-      <c r="AR88" s="19" t="n"/>
+      <c r="AR88" s="18" t="n"/>
       <c r="AS88" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7813,90 +7840,94 @@
         <v>29</v>
       </c>
       <c r="AU88" s="12" t="n"/>
-      <c r="AV88" s="21" t="n"/>
+      <c r="AV88" s="20" t="n"/>
     </row>
     <row r="89" ht="20.1" customHeight="1">
-      <c r="A89" s="22" t="n"/>
-      <c r="C89" s="23" t="n"/>
-      <c r="D89" s="24" t="n"/>
-      <c r="E89" s="22" t="n"/>
-      <c r="G89" s="25" t="n"/>
-      <c r="H89" s="24" t="n"/>
-      <c r="I89" s="22" t="n"/>
+      <c r="A89" s="21" t="n"/>
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="23" t="n"/>
+      <c r="E89" s="21" t="n"/>
+      <c r="G89" s="24" t="n"/>
+      <c r="H89" s="23" t="n"/>
+      <c r="I89" s="21" t="n"/>
       <c r="K89" s="44" t="n"/>
-      <c r="L89" s="24" t="n"/>
-      <c r="M89" s="22" t="n"/>
-      <c r="O89" s="25" t="n"/>
-      <c r="P89" s="24" t="n"/>
-      <c r="Q89" s="22" t="n"/>
-      <c r="S89" s="23" t="n"/>
-      <c r="T89" s="27" t="n"/>
-      <c r="Y89" s="22" t="n"/>
-      <c r="AA89" s="23" t="n"/>
+      <c r="L89" s="23" t="n"/>
+      <c r="M89" s="21" t="n"/>
+      <c r="O89" s="24" t="n"/>
+      <c r="P89" s="23" t="n"/>
+      <c r="Q89" s="21" t="n"/>
+      <c r="S89" s="22" t="n"/>
+      <c r="T89" s="26" t="n"/>
+      <c r="Y89" s="21" t="n"/>
+      <c r="AA89" s="22" t="n"/>
       <c r="AB89" s="16" t="inlineStr">
         <is>
           <t>Lundi de Pâques CCN + Kion + Cana</t>
         </is>
       </c>
-      <c r="AC89" s="22" t="n"/>
-      <c r="AE89" s="25" t="n"/>
-      <c r="AF89" s="27" t="n"/>
-      <c r="AG89" s="22" t="n"/>
-      <c r="AI89" s="23" t="n"/>
-      <c r="AJ89" s="24" t="n"/>
-      <c r="AK89" s="22" t="n"/>
-      <c r="AM89" s="23" t="n"/>
-      <c r="AN89" s="24" t="n"/>
-      <c r="AO89" s="22" t="n"/>
-      <c r="AQ89" s="25" t="n"/>
-      <c r="AR89" s="27" t="n"/>
-      <c r="AS89" s="22" t="n"/>
-      <c r="AU89" s="25" t="n"/>
-      <c r="AV89" s="28" t="n"/>
+      <c r="AC89" s="21" t="n"/>
+      <c r="AE89" s="24" t="n"/>
+      <c r="AF89" s="26" t="n"/>
+      <c r="AG89" s="21" t="n"/>
+      <c r="AI89" s="22" t="n"/>
+      <c r="AJ89" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="AK89" s="21" t="n"/>
+      <c r="AM89" s="22" t="n"/>
+      <c r="AN89" s="23" t="n"/>
+      <c r="AO89" s="21" t="n"/>
+      <c r="AQ89" s="24" t="n"/>
+      <c r="AR89" s="26" t="n"/>
+      <c r="AS89" s="21" t="n"/>
+      <c r="AU89" s="24" t="n"/>
+      <c r="AV89" s="27" t="n"/>
     </row>
     <row r="90" ht="20.1" customHeight="1">
-      <c r="A90" s="29" t="n"/>
-      <c r="B90" s="30" t="n"/>
-      <c r="C90" s="31" t="n"/>
-      <c r="D90" s="26" t="n"/>
-      <c r="E90" s="29" t="n"/>
-      <c r="F90" s="30" t="n"/>
+      <c r="A90" s="28" t="n"/>
+      <c r="B90" s="29" t="n"/>
+      <c r="C90" s="30" t="n"/>
+      <c r="D90" s="31" t="n"/>
+      <c r="E90" s="28" t="n"/>
+      <c r="F90" s="29" t="n"/>
       <c r="G90" s="32" t="n"/>
-      <c r="H90" s="24" t="n"/>
-      <c r="I90" s="29" t="n"/>
-      <c r="J90" s="30" t="n"/>
+      <c r="H90" s="23" t="n"/>
+      <c r="I90" s="28" t="n"/>
+      <c r="J90" s="29" t="n"/>
       <c r="K90" s="45" t="n"/>
-      <c r="L90" s="26" t="n"/>
-      <c r="M90" s="29" t="n"/>
-      <c r="N90" s="30" t="n"/>
+      <c r="L90" s="31" t="n"/>
+      <c r="M90" s="28" t="n"/>
+      <c r="N90" s="29" t="n"/>
       <c r="O90" s="32" t="n"/>
-      <c r="P90" s="26" t="n"/>
-      <c r="Q90" s="29" t="n"/>
-      <c r="R90" s="30" t="n"/>
-      <c r="S90" s="31" t="n"/>
+      <c r="P90" s="31" t="n"/>
+      <c r="Q90" s="28" t="n"/>
+      <c r="R90" s="29" t="n"/>
+      <c r="S90" s="30" t="n"/>
       <c r="T90" s="33" t="n"/>
-      <c r="Y90" s="29" t="n"/>
-      <c r="Z90" s="30" t="n"/>
-      <c r="AA90" s="31" t="n"/>
+      <c r="Y90" s="28" t="n"/>
+      <c r="Z90" s="29" t="n"/>
+      <c r="AA90" s="30" t="n"/>
       <c r="AB90" s="33" t="n"/>
-      <c r="AC90" s="29" t="n"/>
-      <c r="AD90" s="30" t="n"/>
+      <c r="AC90" s="28" t="n"/>
+      <c r="AD90" s="29" t="n"/>
       <c r="AE90" s="32" t="n"/>
       <c r="AF90" s="33" t="n"/>
-      <c r="AG90" s="29" t="n"/>
-      <c r="AH90" s="30" t="n"/>
-      <c r="AI90" s="31" t="n"/>
-      <c r="AJ90" s="26" t="n"/>
-      <c r="AK90" s="29" t="n"/>
-      <c r="AL90" s="30" t="n"/>
-      <c r="AM90" s="31" t="n"/>
-      <c r="AN90" s="26" t="n"/>
-      <c r="AO90" s="29" t="n"/>
-      <c r="AP90" s="30" t="n"/>
+      <c r="AG90" s="28" t="n"/>
+      <c r="AH90" s="29" t="n"/>
+      <c r="AI90" s="30" t="n"/>
+      <c r="AJ90" s="33" t="n"/>
+      <c r="AK90" s="28" t="n"/>
+      <c r="AL90" s="29" t="n"/>
+      <c r="AM90" s="30" t="n"/>
+      <c r="AN90" s="31" t="n"/>
+      <c r="AO90" s="28" t="n"/>
+      <c r="AP90" s="29" t="n"/>
       <c r="AQ90" s="32" t="n"/>
       <c r="AR90" s="33" t="n"/>
-      <c r="AS90" s="29" t="n"/>
-      <c r="AT90" s="30" t="n"/>
+      <c r="AS90" s="28" t="n"/>
+      <c r="AT90" s="29" t="n"/>
       <c r="AU90" s="32" t="n"/>
       <c r="AV90" s="34" t="n"/>
     </row>
@@ -7910,7 +7941,7 @@
         <v>30</v>
       </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="19" t="n"/>
+      <c r="D91" s="18" t="n"/>
       <c r="E91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7920,7 +7951,7 @@
         <v>30</v>
       </c>
       <c r="G91" s="12" t="n"/>
-      <c r="H91" s="24" t="n"/>
+      <c r="H91" s="23" t="n"/>
       <c r="I91" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -7930,7 +7961,7 @@
         <v>30</v>
       </c>
       <c r="K91" s="7" t="n"/>
-      <c r="L91" s="19" t="n"/>
+      <c r="L91" s="18" t="n"/>
       <c r="M91" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7940,7 +7971,7 @@
         <v>30</v>
       </c>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="19" t="n"/>
+      <c r="P91" s="18" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7978,7 +8009,7 @@
         <v>30</v>
       </c>
       <c r="AE91" s="12" t="n"/>
-      <c r="AF91" s="19" t="n"/>
+      <c r="AF91" s="18" t="n"/>
       <c r="AG91" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7987,8 +8018,8 @@
       <c r="AH91" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AI91" s="41" t="n"/>
-      <c r="AJ91" s="21" t="n"/>
+      <c r="AI91" s="42" t="n"/>
+      <c r="AJ91" s="20" t="n"/>
       <c r="AK91" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7998,7 +8029,7 @@
         <v>30</v>
       </c>
       <c r="AM91" s="7" t="n"/>
-      <c r="AN91" s="19" t="n"/>
+      <c r="AN91" s="18" t="n"/>
       <c r="AO91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -8008,7 +8039,7 @@
         <v>30</v>
       </c>
       <c r="AQ91" s="12" t="n"/>
-      <c r="AR91" s="19" t="n"/>
+      <c r="AR91" s="18" t="n"/>
       <c r="AS91" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -8018,94 +8049,98 @@
         <v>30</v>
       </c>
       <c r="AU91" s="12" t="n"/>
-      <c r="AV91" s="19" t="n"/>
+      <c r="AV91" s="18" t="n"/>
     </row>
     <row r="92" ht="20.1" customHeight="1">
-      <c r="A92" s="22" t="n"/>
-      <c r="C92" s="23" t="n"/>
-      <c r="D92" s="27" t="n"/>
-      <c r="E92" s="22" t="n"/>
-      <c r="G92" s="25" t="n"/>
-      <c r="H92" s="24" t="n"/>
-      <c r="I92" s="22" t="n"/>
-      <c r="K92" s="23" t="n"/>
-      <c r="L92" s="27" t="n"/>
-      <c r="M92" s="22" t="n"/>
-      <c r="O92" s="25" t="n"/>
-      <c r="P92" s="27" t="n"/>
-      <c r="Q92" s="22" t="n"/>
-      <c r="S92" s="23" t="n"/>
-      <c r="T92" s="18" t="inlineStr">
-        <is>
-          <t>WE Engagés ccn</t>
-        </is>
-      </c>
-      <c r="Y92" s="22" t="n"/>
-      <c r="AA92" s="23" t="n"/>
+      <c r="A92" s="21" t="n"/>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="26" t="n"/>
+      <c r="E92" s="21" t="n"/>
+      <c r="G92" s="24" t="n"/>
+      <c r="H92" s="23" t="n"/>
+      <c r="I92" s="21" t="n"/>
+      <c r="K92" s="22" t="n"/>
+      <c r="L92" s="26" t="n"/>
+      <c r="M92" s="21" t="n"/>
+      <c r="O92" s="24" t="n"/>
+      <c r="P92" s="26" t="n"/>
+      <c r="Q92" s="21" t="n"/>
+      <c r="S92" s="22" t="n"/>
+      <c r="T92" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="Y92" s="21" t="n"/>
+      <c r="AA92" s="22" t="n"/>
       <c r="AB92" s="16" t="inlineStr">
         <is>
           <t>Journée d'adoration</t>
         </is>
       </c>
-      <c r="AC92" s="22" t="n"/>
-      <c r="AE92" s="25" t="n"/>
-      <c r="AF92" s="27" t="n"/>
-      <c r="AG92" s="22" t="n"/>
+      <c r="AC92" s="21" t="n"/>
+      <c r="AE92" s="24" t="n"/>
+      <c r="AF92" s="26" t="n"/>
+      <c r="AG92" s="21" t="n"/>
       <c r="AI92" s="44" t="n"/>
-      <c r="AJ92" s="28" t="n"/>
-      <c r="AK92" s="22" t="n"/>
-      <c r="AM92" s="23" t="n"/>
-      <c r="AN92" s="27" t="n"/>
-      <c r="AO92" s="22" t="n"/>
-      <c r="AQ92" s="25" t="n"/>
-      <c r="AR92" s="27" t="n"/>
-      <c r="AS92" s="22" t="n"/>
-      <c r="AU92" s="25" t="n"/>
-      <c r="AV92" s="27" t="n"/>
+      <c r="AJ92" s="27" t="n"/>
+      <c r="AK92" s="21" t="n"/>
+      <c r="AM92" s="22" t="n"/>
+      <c r="AN92" s="26" t="n"/>
+      <c r="AO92" s="21" t="n"/>
+      <c r="AQ92" s="24" t="n"/>
+      <c r="AR92" s="26" t="n"/>
+      <c r="AS92" s="21" t="n"/>
+      <c r="AU92" s="24" t="n"/>
+      <c r="AV92" s="26" t="n"/>
     </row>
     <row r="93" ht="20.1" customHeight="1">
-      <c r="A93" s="29" t="n"/>
-      <c r="B93" s="30" t="n"/>
-      <c r="C93" s="31" t="n"/>
+      <c r="A93" s="28" t="n"/>
+      <c r="B93" s="29" t="n"/>
+      <c r="C93" s="30" t="n"/>
       <c r="D93" s="33" t="n"/>
-      <c r="E93" s="29" t="n"/>
-      <c r="F93" s="30" t="n"/>
+      <c r="E93" s="28" t="n"/>
+      <c r="F93" s="29" t="n"/>
       <c r="G93" s="32" t="n"/>
-      <c r="H93" s="24" t="n"/>
-      <c r="I93" s="29" t="n"/>
-      <c r="J93" s="30" t="n"/>
-      <c r="K93" s="31" t="n"/>
+      <c r="H93" s="23" t="n"/>
+      <c r="I93" s="28" t="n"/>
+      <c r="J93" s="29" t="n"/>
+      <c r="K93" s="30" t="n"/>
       <c r="L93" s="33" t="n"/>
-      <c r="M93" s="29" t="n"/>
-      <c r="N93" s="30" t="n"/>
+      <c r="M93" s="28" t="n"/>
+      <c r="N93" s="29" t="n"/>
       <c r="O93" s="32" t="n"/>
       <c r="P93" s="33" t="n"/>
-      <c r="Q93" s="29" t="n"/>
-      <c r="R93" s="30" t="n"/>
-      <c r="S93" s="31" t="n"/>
-      <c r="T93" s="24" t="n"/>
-      <c r="Y93" s="29" t="n"/>
-      <c r="Z93" s="30" t="n"/>
-      <c r="AA93" s="31" t="n"/>
+      <c r="Q93" s="28" t="n"/>
+      <c r="R93" s="29" t="n"/>
+      <c r="S93" s="30" t="n"/>
+      <c r="T93" s="17" t="inlineStr">
+        <is>
+          <t>WE Engagés ccn</t>
+        </is>
+      </c>
+      <c r="Y93" s="28" t="n"/>
+      <c r="Z93" s="29" t="n"/>
+      <c r="AA93" s="30" t="n"/>
       <c r="AB93" s="33" t="n"/>
-      <c r="AC93" s="29" t="n"/>
-      <c r="AD93" s="30" t="n"/>
+      <c r="AC93" s="28" t="n"/>
+      <c r="AD93" s="29" t="n"/>
       <c r="AE93" s="32" t="n"/>
       <c r="AF93" s="33" t="n"/>
-      <c r="AG93" s="29" t="n"/>
-      <c r="AH93" s="30" t="n"/>
+      <c r="AG93" s="28" t="n"/>
+      <c r="AH93" s="29" t="n"/>
       <c r="AI93" s="45" t="n"/>
       <c r="AJ93" s="34" t="n"/>
-      <c r="AK93" s="29" t="n"/>
-      <c r="AL93" s="30" t="n"/>
-      <c r="AM93" s="31" t="n"/>
+      <c r="AK93" s="28" t="n"/>
+      <c r="AL93" s="29" t="n"/>
+      <c r="AM93" s="30" t="n"/>
       <c r="AN93" s="33" t="n"/>
-      <c r="AO93" s="29" t="n"/>
-      <c r="AP93" s="30" t="n"/>
+      <c r="AO93" s="28" t="n"/>
+      <c r="AP93" s="29" t="n"/>
       <c r="AQ93" s="32" t="n"/>
       <c r="AR93" s="33" t="n"/>
-      <c r="AS93" s="29" t="n"/>
-      <c r="AT93" s="30" t="n"/>
+      <c r="AS93" s="28" t="n"/>
+      <c r="AT93" s="29" t="n"/>
       <c r="AU93" s="32" t="n"/>
       <c r="AV93" s="33" t="n"/>
     </row>
@@ -8119,7 +8154,7 @@
         <v>31</v>
       </c>
       <c r="G94" s="12" t="n"/>
-      <c r="H94" s="24" t="n"/>
+      <c r="H94" s="23" t="n"/>
       <c r="M94" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -8129,7 +8164,7 @@
         <v>31</v>
       </c>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="19" t="n"/>
+      <c r="P94" s="18" t="n"/>
       <c r="Q94" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -8138,8 +8173,8 @@
       <c r="R94" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="S94" s="41" t="n"/>
-      <c r="T94" s="24" t="n"/>
+      <c r="S94" s="42" t="n"/>
+      <c r="T94" s="23" t="n"/>
       <c r="Y94" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -8149,7 +8184,7 @@
         <v>31</v>
       </c>
       <c r="AA94" s="7" t="n"/>
-      <c r="AB94" s="19" t="n"/>
+      <c r="AB94" s="18" t="n"/>
       <c r="AG94" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -8159,7 +8194,7 @@
         <v>31</v>
       </c>
       <c r="AI94" s="7" t="n"/>
-      <c r="AJ94" s="18" t="inlineStr">
+      <c r="AJ94" s="17" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -8173,7 +8208,11 @@
         <v>31</v>
       </c>
       <c r="AQ94" s="12" t="n"/>
-      <c r="AR94" s="19" t="n"/>
+      <c r="AR94" s="17" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
       <c r="AS94" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -8183,63 +8222,67 @@
         <v>31</v>
       </c>
       <c r="AU94" s="12" t="n"/>
-      <c r="AV94" s="19" t="n"/>
+      <c r="AV94" s="18" t="n"/>
     </row>
     <row r="95" ht="20.1" customHeight="1">
-      <c r="E95" s="22" t="n"/>
-      <c r="G95" s="25" t="n"/>
-      <c r="H95" s="24" t="n"/>
-      <c r="M95" s="22" t="n"/>
-      <c r="O95" s="25" t="n"/>
-      <c r="P95" s="27" t="n"/>
-      <c r="Q95" s="22" t="n"/>
+      <c r="E95" s="21" t="n"/>
+      <c r="G95" s="24" t="n"/>
+      <c r="H95" s="31" t="n"/>
+      <c r="M95" s="21" t="n"/>
+      <c r="O95" s="24" t="n"/>
+      <c r="P95" s="26" t="n"/>
+      <c r="Q95" s="21" t="n"/>
       <c r="S95" s="44" t="n"/>
-      <c r="T95" s="26" t="n"/>
-      <c r="Y95" s="22" t="n"/>
-      <c r="AA95" s="23" t="n"/>
-      <c r="AB95" s="27" t="n"/>
-      <c r="AG95" s="22" t="n"/>
-      <c r="AI95" s="23" t="n"/>
-      <c r="AJ95" s="24" t="n"/>
-      <c r="AO95" s="22" t="n"/>
-      <c r="AQ95" s="25" t="n"/>
-      <c r="AR95" s="27" t="n"/>
-      <c r="AS95" s="22" t="n"/>
-      <c r="AU95" s="25" t="n"/>
-      <c r="AV95" s="27" t="n"/>
+      <c r="T95" s="31" t="n"/>
+      <c r="Y95" s="21" t="n"/>
+      <c r="AA95" s="22" t="n"/>
+      <c r="AB95" s="26" t="n"/>
+      <c r="AG95" s="21" t="n"/>
+      <c r="AI95" s="22" t="n"/>
+      <c r="AJ95" s="23" t="n"/>
+      <c r="AO95" s="21" t="n"/>
+      <c r="AQ95" s="24" t="n"/>
+      <c r="AR95" s="23" t="n"/>
+      <c r="AS95" s="21" t="n"/>
+      <c r="AU95" s="24" t="n"/>
+      <c r="AV95" s="26" t="n"/>
     </row>
     <row r="96" ht="20.1" customHeight="1">
-      <c r="E96" s="29" t="n"/>
-      <c r="F96" s="30" t="n"/>
+      <c r="E96" s="28" t="n"/>
+      <c r="F96" s="29" t="n"/>
       <c r="G96" s="32" t="n"/>
-      <c r="H96" s="26" t="n"/>
-      <c r="M96" s="29" t="n"/>
-      <c r="N96" s="30" t="n"/>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>Messe pour les défunts</t>
+        </is>
+      </c>
+      <c r="M96" s="28" t="n"/>
+      <c r="N96" s="29" t="n"/>
       <c r="O96" s="32" t="n"/>
       <c r="P96" s="33" t="n"/>
-      <c r="Q96" s="29" t="n"/>
-      <c r="R96" s="30" t="n"/>
+      <c r="Q96" s="28" t="n"/>
+      <c r="R96" s="29" t="n"/>
       <c r="S96" s="45" t="n"/>
       <c r="T96" s="36" t="n"/>
-      <c r="Y96" s="29" t="n"/>
-      <c r="Z96" s="30" t="n"/>
-      <c r="AA96" s="31" t="n"/>
+      <c r="Y96" s="28" t="n"/>
+      <c r="Z96" s="29" t="n"/>
+      <c r="AA96" s="30" t="n"/>
       <c r="AB96" s="33" t="n"/>
-      <c r="AG96" s="29" t="n"/>
-      <c r="AH96" s="30" t="n"/>
-      <c r="AI96" s="31" t="n"/>
-      <c r="AJ96" s="26" t="n"/>
-      <c r="AO96" s="29" t="n"/>
-      <c r="AP96" s="30" t="n"/>
+      <c r="AG96" s="28" t="n"/>
+      <c r="AH96" s="29" t="n"/>
+      <c r="AI96" s="30" t="n"/>
+      <c r="AJ96" s="31" t="n"/>
+      <c r="AO96" s="28" t="n"/>
+      <c r="AP96" s="29" t="n"/>
       <c r="AQ96" s="32" t="n"/>
-      <c r="AR96" s="33" t="n"/>
-      <c r="AS96" s="29" t="n"/>
-      <c r="AT96" s="30" t="n"/>
+      <c r="AR96" s="31" t="n"/>
+      <c r="AS96" s="28" t="n"/>
+      <c r="AT96" s="29" t="n"/>
       <c r="AU96" s="32" t="n"/>
       <c r="AV96" s="33" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="839">
+  <mergeCells count="842">
     <mergeCell ref="AC22:AC24"/>
     <mergeCell ref="R91:R93"/>
     <mergeCell ref="B34:B36"/>
@@ -8263,6 +8306,7 @@
     <mergeCell ref="AG73:AG75"/>
     <mergeCell ref="M52:M54"/>
     <mergeCell ref="AF34:AF36"/>
+    <mergeCell ref="AV85:AV87"/>
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="AH28:AH30"/>
     <mergeCell ref="N7:N9"/>
@@ -8356,6 +8400,7 @@
     <mergeCell ref="AP70:AP72"/>
     <mergeCell ref="AT46:AT48"/>
     <mergeCell ref="AO25:AO27"/>
+    <mergeCell ref="H85:H95"/>
     <mergeCell ref="U52:U54"/>
     <mergeCell ref="AC49:AC51"/>
     <mergeCell ref="AT61:AT63"/>
@@ -8370,7 +8415,6 @@
     <mergeCell ref="V58:V60"/>
     <mergeCell ref="Q37:Q39"/>
     <mergeCell ref="AG94:AG96"/>
-    <mergeCell ref="L9:L10"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="V73:V75"/>
     <mergeCell ref="B52:B54"/>
@@ -8489,6 +8533,7 @@
     <mergeCell ref="AS76:AS78"/>
     <mergeCell ref="AC76:AC78"/>
     <mergeCell ref="AD31:AD33"/>
+    <mergeCell ref="AN79:AN81"/>
     <mergeCell ref="V31:V33"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="AP79:AP81"/>
@@ -8576,6 +8621,7 @@
     <mergeCell ref="AP16:AP18"/>
     <mergeCell ref="A79:A81"/>
     <mergeCell ref="AK13:AK15"/>
+    <mergeCell ref="D76:D79"/>
     <mergeCell ref="E37:E39"/>
     <mergeCell ref="AS58:AS60"/>
     <mergeCell ref="AK28:AK30"/>
@@ -8604,6 +8650,7 @@
     <mergeCell ref="AF16:AF18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="AT10:AT12"/>
+    <mergeCell ref="L5:L7"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="AC79:AC81"/>
     <mergeCell ref="I58:I60"/>
@@ -8628,11 +8675,13 @@
     <mergeCell ref="U19:U21"/>
     <mergeCell ref="AO76:AO78"/>
     <mergeCell ref="D88:D90"/>
+    <mergeCell ref="AB80:AB82"/>
     <mergeCell ref="F88:F90"/>
     <mergeCell ref="AD58:AD60"/>
     <mergeCell ref="AK3:AN3"/>
     <mergeCell ref="AD73:AD75"/>
     <mergeCell ref="N16:N18"/>
+    <mergeCell ref="AF73:AF75"/>
     <mergeCell ref="AS85:AS87"/>
     <mergeCell ref="AC28:AC30"/>
     <mergeCell ref="AK25:AK27"/>
@@ -8674,7 +8723,6 @@
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="M43:M45"/>
     <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="AB55:AB57"/>
     <mergeCell ref="AF46:AF48"/>
     <mergeCell ref="AD55:AD57"/>
@@ -8692,7 +8740,6 @@
     <mergeCell ref="AD79:AD81"/>
     <mergeCell ref="AL70:AL72"/>
     <mergeCell ref="R49:R51"/>
-    <mergeCell ref="L13:L19"/>
     <mergeCell ref="F79:F81"/>
     <mergeCell ref="AR13:AR15"/>
     <mergeCell ref="E34:E36"/>
@@ -8758,7 +8805,6 @@
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="AO91:AO93"/>
     <mergeCell ref="Y34:Y36"/>
-    <mergeCell ref="L85:L87"/>
     <mergeCell ref="I67:I69"/>
     <mergeCell ref="AL55:AL57"/>
     <mergeCell ref="R70:R72"/>
@@ -8804,16 +8850,17 @@
     <mergeCell ref="AG22:AG24"/>
     <mergeCell ref="AL43:AL45"/>
     <mergeCell ref="AS4:AS6"/>
+    <mergeCell ref="X82:X84"/>
     <mergeCell ref="AF82:AF84"/>
     <mergeCell ref="AT76:AT78"/>
     <mergeCell ref="AD19:AD21"/>
+    <mergeCell ref="T93:T95"/>
     <mergeCell ref="AS31:AS33"/>
     <mergeCell ref="M88:M90"/>
     <mergeCell ref="AP34:AP36"/>
     <mergeCell ref="F94:F96"/>
     <mergeCell ref="AH34:AH36"/>
     <mergeCell ref="AK73:AK75"/>
-    <mergeCell ref="D76:D80"/>
     <mergeCell ref="P13:P15"/>
     <mergeCell ref="AH64:AH66"/>
     <mergeCell ref="AL28:AL30"/>
@@ -8828,6 +8875,7 @@
     <mergeCell ref="J22:J24"/>
     <mergeCell ref="AL67:AL69"/>
     <mergeCell ref="R46:R48"/>
+    <mergeCell ref="AR94:AR96"/>
     <mergeCell ref="AP61:AP63"/>
     <mergeCell ref="Z4:Z6"/>
     <mergeCell ref="AD37:AD39"/>
@@ -8838,6 +8886,7 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="L30:L31"/>
     <mergeCell ref="B64:B66"/>
+    <mergeCell ref="L12:L17"/>
     <mergeCell ref="Q16:Q18"/>
     <mergeCell ref="AR31:AR33"/>
     <mergeCell ref="Q76:Q78"/>
@@ -8845,6 +8894,7 @@
     <mergeCell ref="E52:E54"/>
     <mergeCell ref="AG10:AG12"/>
     <mergeCell ref="N79:N81"/>
+    <mergeCell ref="P79:P81"/>
     <mergeCell ref="M34:M36"/>
     <mergeCell ref="Z70:Z72"/>
     <mergeCell ref="AT13:AT15"/>
@@ -8920,7 +8970,6 @@
     <mergeCell ref="AS52:AS54"/>
     <mergeCell ref="AG76:AG78"/>
     <mergeCell ref="Q19:Q21"/>
-    <mergeCell ref="H85:H96"/>
     <mergeCell ref="AK76:AK78"/>
     <mergeCell ref="I55:I57"/>
     <mergeCell ref="B88:B90"/>
@@ -8932,14 +8981,12 @@
     <mergeCell ref="J16:J18"/>
     <mergeCell ref="Y28:Y30"/>
     <mergeCell ref="AB25:AB28"/>
-    <mergeCell ref="AJ88:AJ90"/>
     <mergeCell ref="J43:J45"/>
     <mergeCell ref="AL88:AL90"/>
     <mergeCell ref="R67:R69"/>
     <mergeCell ref="Y70:Y72"/>
     <mergeCell ref="AO22:AO24"/>
     <mergeCell ref="AS13:AS15"/>
-    <mergeCell ref="T92:T95"/>
     <mergeCell ref="R82:R84"/>
     <mergeCell ref="B25:B27"/>
     <mergeCell ref="AO64:AO66"/>
@@ -8971,7 +9018,6 @@
     <mergeCell ref="AD46:AD48"/>
     <mergeCell ref="AL37:AL39"/>
     <mergeCell ref="J4:J6"/>
-    <mergeCell ref="AB80:AB83"/>
     <mergeCell ref="AB61:AB63"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="E76:E78"/>

--- a/calendrier.xlsx
+++ b/calendrier.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
@@ -81,16 +93,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="15"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -109,47 +115,82 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="006A4C93"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0CECE"/>
+        <fgColor rgb="00C6D9F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B0F0"/>
+        <fgColor rgb="00A8D672"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="007B8F2A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00E85D9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
+        <fgColor rgb="00FFD23F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
+        <fgColor rgb="004F8FD8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BF9000"/>
+        <fgColor rgb="002B2D42"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDB4E8"/>
+        <fgColor rgb="007A4E2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003E8E5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C6A12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C3DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D79A3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A9D8F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009AA0A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1B8"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +200,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
+        <fgColor rgb="00EE7B4D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A61E2E"/>
       </patternFill>
     </fill>
   </fills>
@@ -311,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -333,7 +379,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -343,7 +389,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -352,14 +398,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -367,10 +413,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -379,61 +428,112 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -864,7 +964,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fond rouge des jours : Avent (29/11 → 24/12), Carême (10/02 → 27/03)   ·   Bande bleue : vacances scolaires zone B</t>
+          <t>Fond violet des jours : Avent (29/11 → 24/12), Carême (10/02 → 27/03)   ·   Bande bleue : vacances scolaires zone B</t>
         </is>
       </c>
     </row>
@@ -1018,11 +1118,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="7" t="n"/>
-      <c r="P4" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="P4" s="16" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1032,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="S4" s="12" t="n"/>
-      <c r="T4" s="13" t="inlineStr">
+      <c r="T4" s="17" t="inlineStr">
         <is>
           <t>Jour de l'an</t>
         </is>
@@ -1046,7 +1142,7 @@
         <v>1</v>
       </c>
       <c r="W4" s="7" t="n"/>
-      <c r="X4" s="17" t="inlineStr">
+      <c r="X4" s="18" t="inlineStr">
         <is>
           <t>WE Engagés ccn</t>
         </is>
@@ -1060,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="AA4" s="12" t="n"/>
-      <c r="AB4" s="18" t="n"/>
+      <c r="AB4" s="16" t="n"/>
       <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1070,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="AE4" s="7" t="n"/>
-      <c r="AF4" s="18" t="n"/>
+      <c r="AF4" s="16" t="n"/>
       <c r="AG4" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1094,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="AM4" s="7" t="n"/>
-      <c r="AN4" s="16" t="inlineStr">
+      <c r="AN4" s="18" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -1108,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="18" t="n"/>
+      <c r="AR4" s="16" t="n"/>
       <c r="AS4" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1132,14 +1228,10 @@
       <c r="L5" s="25" t="n"/>
       <c r="M5" s="21" t="n"/>
       <c r="O5" s="22" t="n"/>
-      <c r="P5" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="P5" s="26" t="n"/>
       <c r="Q5" s="21" t="n"/>
       <c r="S5" s="24" t="n"/>
-      <c r="T5" s="16" t="inlineStr">
+      <c r="T5" s="27" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1158,71 +1250,63 @@
       <c r="AJ5" s="23" t="n"/>
       <c r="AK5" s="21" t="n"/>
       <c r="AM5" s="22" t="n"/>
-      <c r="AN5" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AN5" s="23" t="n"/>
       <c r="AO5" s="21" t="n"/>
       <c r="AQ5" s="22" t="n"/>
       <c r="AR5" s="26" t="n"/>
       <c r="AS5" s="21" t="n"/>
       <c r="AU5" s="24" t="n"/>
-      <c r="AV5" s="27" t="n"/>
+      <c r="AV5" s="28" t="n"/>
     </row>
     <row r="6" ht="20.1" customHeight="1">
-      <c r="A6" s="28" t="n"/>
-      <c r="B6" s="29" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="31" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="29" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="31" t="n"/>
-      <c r="I6" s="28" t="n"/>
-      <c r="J6" s="29" t="n"/>
-      <c r="K6" s="32" t="n"/>
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="29" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="31" t="n"/>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="29" t="n"/>
+      <c r="J6" s="30" t="n"/>
+      <c r="K6" s="33" t="n"/>
       <c r="L6" s="23" t="n"/>
-      <c r="M6" s="28" t="n"/>
-      <c r="N6" s="29" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="33" t="n"/>
-      <c r="Q6" s="28" t="n"/>
-      <c r="R6" s="29" t="n"/>
-      <c r="S6" s="32" t="n"/>
-      <c r="T6" s="33" t="n"/>
-      <c r="U6" s="28" t="n"/>
-      <c r="V6" s="29" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="31" t="n"/>
-      <c r="Y6" s="28" t="n"/>
-      <c r="Z6" s="29" t="n"/>
-      <c r="AA6" s="32" t="n"/>
-      <c r="AB6" s="33" t="n"/>
-      <c r="AC6" s="28" t="n"/>
-      <c r="AD6" s="29" t="n"/>
-      <c r="AE6" s="30" t="n"/>
-      <c r="AF6" s="33" t="n"/>
-      <c r="AG6" s="28" t="n"/>
-      <c r="AH6" s="29" t="n"/>
-      <c r="AI6" s="32" t="n"/>
-      <c r="AJ6" s="31" t="n"/>
-      <c r="AK6" s="28" t="n"/>
-      <c r="AL6" s="29" t="n"/>
-      <c r="AM6" s="30" t="n"/>
-      <c r="AN6" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="AO6" s="28" t="n"/>
-      <c r="AP6" s="29" t="n"/>
-      <c r="AQ6" s="30" t="n"/>
-      <c r="AR6" s="33" t="n"/>
-      <c r="AS6" s="28" t="n"/>
-      <c r="AT6" s="29" t="n"/>
-      <c r="AU6" s="32" t="n"/>
-      <c r="AV6" s="34" t="n"/>
+      <c r="M6" s="29" t="n"/>
+      <c r="N6" s="30" t="n"/>
+      <c r="O6" s="31" t="n"/>
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="29" t="n"/>
+      <c r="R6" s="30" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="34" t="n"/>
+      <c r="U6" s="29" t="n"/>
+      <c r="V6" s="30" t="n"/>
+      <c r="W6" s="31" t="n"/>
+      <c r="X6" s="32" t="n"/>
+      <c r="Y6" s="29" t="n"/>
+      <c r="Z6" s="30" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="34" t="n"/>
+      <c r="AC6" s="29" t="n"/>
+      <c r="AD6" s="30" t="n"/>
+      <c r="AE6" s="31" t="n"/>
+      <c r="AF6" s="34" t="n"/>
+      <c r="AG6" s="29" t="n"/>
+      <c r="AH6" s="30" t="n"/>
+      <c r="AI6" s="33" t="n"/>
+      <c r="AJ6" s="32" t="n"/>
+      <c r="AK6" s="29" t="n"/>
+      <c r="AL6" s="30" t="n"/>
+      <c r="AM6" s="31" t="n"/>
+      <c r="AN6" s="32" t="n"/>
+      <c r="AO6" s="29" t="n"/>
+      <c r="AP6" s="30" t="n"/>
+      <c r="AQ6" s="31" t="n"/>
+      <c r="AR6" s="34" t="n"/>
+      <c r="AS6" s="29" t="n"/>
+      <c r="AT6" s="30" t="n"/>
+      <c r="AU6" s="33" t="n"/>
+      <c r="AV6" s="35" t="n"/>
     </row>
     <row r="7" ht="20.1" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1234,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="D7" s="16" t="n"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1244,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -1258,7 +1342,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="7" t="n"/>
-      <c r="L7" s="31" t="n"/>
+      <c r="L7" s="32" t="n"/>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1268,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="O7" s="7" t="n"/>
-      <c r="P7" s="18" t="n"/>
+      <c r="P7" s="16" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1278,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="S7" s="12" t="n"/>
-      <c r="T7" s="18" t="n"/>
+      <c r="T7" s="16" t="n"/>
       <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -1288,11 +1372,7 @@
         <v>2</v>
       </c>
       <c r="W7" s="7" t="n"/>
-      <c r="X7" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="X7" s="16" t="n"/>
       <c r="Y7" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -1302,11 +1382,7 @@
         <v>2</v>
       </c>
       <c r="AA7" s="12" t="n"/>
-      <c r="AB7" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AB7" s="16" t="n"/>
       <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1316,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="AE7" s="7" t="n"/>
-      <c r="AF7" s="17" t="inlineStr">
+      <c r="AF7" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1340,7 +1416,7 @@
         <v>2</v>
       </c>
       <c r="AM7" s="7" t="n"/>
-      <c r="AN7" s="18" t="n"/>
+      <c r="AN7" s="16" t="n"/>
       <c r="AO7" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -1350,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" s="7" t="n"/>
-      <c r="AR7" s="17" t="inlineStr">
+      <c r="AR7" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1364,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="AU7" s="12" t="n"/>
-      <c r="AV7" s="18" t="n"/>
+      <c r="AV7" s="16" t="n"/>
     </row>
     <row r="8" ht="20.1" customHeight="1">
       <c r="A8" s="21" t="n"/>
@@ -1375,7 +1451,7 @@
       <c r="H8" s="23" t="n"/>
       <c r="I8" s="21" t="n"/>
       <c r="K8" s="22" t="n"/>
-      <c r="L8" s="36" t="inlineStr">
+      <c r="L8" s="38" t="inlineStr">
         <is>
           <t>Défunts</t>
         </is>
@@ -1388,20 +1464,16 @@
       <c r="T8" s="26" t="n"/>
       <c r="U8" s="21" t="n"/>
       <c r="W8" s="22" t="n"/>
-      <c r="X8" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="X8" s="26" t="n"/>
       <c r="Y8" s="21" t="n"/>
       <c r="AA8" s="24" t="n"/>
-      <c r="AB8" s="23" t="n"/>
+      <c r="AB8" s="26" t="n"/>
       <c r="AC8" s="21" t="n"/>
       <c r="AE8" s="22" t="n"/>
       <c r="AF8" s="23" t="n"/>
       <c r="AG8" s="21" t="n"/>
       <c r="AI8" s="24" t="n"/>
-      <c r="AJ8" s="27" t="n"/>
+      <c r="AJ8" s="28" t="n"/>
       <c r="AK8" s="21" t="n"/>
       <c r="AM8" s="22" t="n"/>
       <c r="AN8" s="26" t="n"/>
@@ -1413,58 +1485,58 @@
       <c r="AV8" s="26" t="n"/>
     </row>
     <row r="9" ht="20.1" customHeight="1">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="31" t="n"/>
+      <c r="L9" s="27" t="inlineStr">
         <is>
           <t>Messe des défunts</t>
         </is>
       </c>
-      <c r="M9" s="28" t="n"/>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="30" t="n"/>
-      <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="32" t="n"/>
-      <c r="T9" s="33" t="n"/>
-      <c r="U9" s="28" t="n"/>
-      <c r="V9" s="29" t="n"/>
-      <c r="W9" s="30" t="n"/>
-      <c r="X9" s="33" t="n"/>
-      <c r="Y9" s="28" t="n"/>
-      <c r="Z9" s="29" t="n"/>
-      <c r="AA9" s="32" t="n"/>
-      <c r="AB9" s="31" t="n"/>
-      <c r="AC9" s="28" t="n"/>
-      <c r="AD9" s="29" t="n"/>
-      <c r="AE9" s="30" t="n"/>
-      <c r="AF9" s="31" t="n"/>
-      <c r="AG9" s="28" t="n"/>
-      <c r="AH9" s="29" t="n"/>
-      <c r="AI9" s="32" t="n"/>
-      <c r="AJ9" s="34" t="n"/>
-      <c r="AK9" s="28" t="n"/>
-      <c r="AL9" s="29" t="n"/>
-      <c r="AM9" s="30" t="n"/>
-      <c r="AN9" s="33" t="n"/>
-      <c r="AO9" s="28" t="n"/>
-      <c r="AP9" s="29" t="n"/>
-      <c r="AQ9" s="30" t="n"/>
-      <c r="AR9" s="31" t="n"/>
-      <c r="AS9" s="28" t="n"/>
-      <c r="AT9" s="29" t="n"/>
-      <c r="AU9" s="32" t="n"/>
-      <c r="AV9" s="33" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="30" t="n"/>
+      <c r="O9" s="31" t="n"/>
+      <c r="P9" s="34" t="n"/>
+      <c r="Q9" s="29" t="n"/>
+      <c r="R9" s="30" t="n"/>
+      <c r="S9" s="33" t="n"/>
+      <c r="T9" s="34" t="n"/>
+      <c r="U9" s="29" t="n"/>
+      <c r="V9" s="30" t="n"/>
+      <c r="W9" s="31" t="n"/>
+      <c r="X9" s="34" t="n"/>
+      <c r="Y9" s="29" t="n"/>
+      <c r="Z9" s="30" t="n"/>
+      <c r="AA9" s="33" t="n"/>
+      <c r="AB9" s="34" t="n"/>
+      <c r="AC9" s="29" t="n"/>
+      <c r="AD9" s="30" t="n"/>
+      <c r="AE9" s="31" t="n"/>
+      <c r="AF9" s="32" t="n"/>
+      <c r="AG9" s="29" t="n"/>
+      <c r="AH9" s="30" t="n"/>
+      <c r="AI9" s="33" t="n"/>
+      <c r="AJ9" s="35" t="n"/>
+      <c r="AK9" s="29" t="n"/>
+      <c r="AL9" s="30" t="n"/>
+      <c r="AM9" s="31" t="n"/>
+      <c r="AN9" s="34" t="n"/>
+      <c r="AO9" s="29" t="n"/>
+      <c r="AP9" s="30" t="n"/>
+      <c r="AQ9" s="31" t="n"/>
+      <c r="AR9" s="32" t="n"/>
+      <c r="AS9" s="29" t="n"/>
+      <c r="AT9" s="30" t="n"/>
+      <c r="AU9" s="33" t="n"/>
+      <c r="AV9" s="34" t="n"/>
     </row>
     <row r="10" ht="20.1" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1476,7 +1548,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="7" t="n"/>
-      <c r="D10" s="18" t="n"/>
+      <c r="D10" s="16" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1486,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="36" t="inlineStr">
+      <c r="H10" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -1500,9 +1572,9 @@
         <v>3</v>
       </c>
       <c r="K10" s="7" t="n"/>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
+      <c r="L10" s="40" t="inlineStr">
+        <is>
+          <t>Père Pascal en Côte d'Ivoire</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
@@ -1514,7 +1586,7 @@
         <v>3</v>
       </c>
       <c r="O10" s="7" t="n"/>
-      <c r="P10" s="18" t="n"/>
+      <c r="P10" s="16" t="n"/>
       <c r="Q10" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1524,7 +1596,11 @@
         <v>3</v>
       </c>
       <c r="S10" s="12" t="n"/>
-      <c r="T10" s="37" t="n"/>
+      <c r="T10" s="41" t="inlineStr">
+        <is>
+          <t>Semaine Épiphanie</t>
+        </is>
+      </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1534,7 +1610,7 @@
         <v>3</v>
       </c>
       <c r="W10" s="7" t="n"/>
-      <c r="X10" s="18" t="n"/>
+      <c r="X10" s="16" t="n"/>
       <c r="Y10" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -1544,7 +1620,7 @@
         <v>3</v>
       </c>
       <c r="AA10" s="12" t="n"/>
-      <c r="AB10" s="18" t="n"/>
+      <c r="AB10" s="16" t="n"/>
       <c r="AC10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1554,7 +1630,7 @@
         <v>3</v>
       </c>
       <c r="AE10" s="7" t="n"/>
-      <c r="AF10" s="35" t="inlineStr">
+      <c r="AF10" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -1568,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="AI10" s="7" t="n"/>
-      <c r="AJ10" s="18" t="n"/>
+      <c r="AJ10" s="16" t="n"/>
       <c r="AK10" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1578,7 +1654,7 @@
         <v>3</v>
       </c>
       <c r="AM10" s="7" t="n"/>
-      <c r="AN10" s="18" t="n"/>
+      <c r="AN10" s="16" t="n"/>
       <c r="AO10" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -1588,7 +1664,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" s="12" t="n"/>
-      <c r="AR10" s="38" t="inlineStr">
+      <c r="AR10" s="43" t="inlineStr">
         <is>
           <t>Repas catéchuménat</t>
         </is>
@@ -1602,7 +1678,7 @@
         <v>3</v>
       </c>
       <c r="AU10" s="12" t="n"/>
-      <c r="AV10" s="18" t="n"/>
+      <c r="AV10" s="16" t="n"/>
     </row>
     <row r="11" ht="20.1" customHeight="1">
       <c r="A11" s="21" t="n"/>
@@ -1610,18 +1686,14 @@
       <c r="D11" s="26" t="n"/>
       <c r="E11" s="21" t="n"/>
       <c r="G11" s="22" t="n"/>
-      <c r="H11" s="39" t="inlineStr">
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>Rencontre CMP &amp; CPAE</t>
         </is>
       </c>
       <c r="I11" s="21" t="n"/>
       <c r="K11" s="22" t="n"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="L11" s="23" t="n"/>
       <c r="M11" s="21" t="n"/>
       <c r="O11" s="22" t="n"/>
       <c r="P11" s="26" t="n"/>
@@ -1651,58 +1723,58 @@
       <c r="AV11" s="26" t="n"/>
     </row>
     <row r="12" ht="20.1" customHeight="1">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="29" t="n"/>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="33" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="40" t="inlineStr">
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="45" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="41" t="n"/>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="28" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="32" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="30" t="n"/>
+      <c r="S12" s="33" t="n"/>
       <c r="T12" s="23" t="n"/>
-      <c r="U12" s="28" t="n"/>
-      <c r="V12" s="29" t="n"/>
-      <c r="W12" s="30" t="n"/>
-      <c r="X12" s="33" t="n"/>
-      <c r="Y12" s="28" t="n"/>
-      <c r="Z12" s="29" t="n"/>
-      <c r="AA12" s="32" t="n"/>
-      <c r="AB12" s="33" t="n"/>
-      <c r="AC12" s="28" t="n"/>
-      <c r="AD12" s="29" t="n"/>
-      <c r="AE12" s="30" t="n"/>
-      <c r="AF12" s="31" t="n"/>
-      <c r="AG12" s="28" t="n"/>
-      <c r="AH12" s="29" t="n"/>
-      <c r="AI12" s="30" t="n"/>
-      <c r="AJ12" s="33" t="n"/>
-      <c r="AK12" s="28" t="n"/>
-      <c r="AL12" s="29" t="n"/>
-      <c r="AM12" s="30" t="n"/>
-      <c r="AN12" s="33" t="n"/>
-      <c r="AO12" s="28" t="n"/>
-      <c r="AP12" s="29" t="n"/>
-      <c r="AQ12" s="32" t="n"/>
-      <c r="AR12" s="31" t="n"/>
-      <c r="AS12" s="28" t="n"/>
-      <c r="AT12" s="29" t="n"/>
-      <c r="AU12" s="32" t="n"/>
-      <c r="AV12" s="33" t="n"/>
+      <c r="U12" s="29" t="n"/>
+      <c r="V12" s="30" t="n"/>
+      <c r="W12" s="31" t="n"/>
+      <c r="X12" s="34" t="n"/>
+      <c r="Y12" s="29" t="n"/>
+      <c r="Z12" s="30" t="n"/>
+      <c r="AA12" s="33" t="n"/>
+      <c r="AB12" s="34" t="n"/>
+      <c r="AC12" s="29" t="n"/>
+      <c r="AD12" s="30" t="n"/>
+      <c r="AE12" s="31" t="n"/>
+      <c r="AF12" s="32" t="n"/>
+      <c r="AG12" s="29" t="n"/>
+      <c r="AH12" s="30" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="34" t="n"/>
+      <c r="AK12" s="29" t="n"/>
+      <c r="AL12" s="30" t="n"/>
+      <c r="AM12" s="31" t="n"/>
+      <c r="AN12" s="34" t="n"/>
+      <c r="AO12" s="29" t="n"/>
+      <c r="AP12" s="30" t="n"/>
+      <c r="AQ12" s="33" t="n"/>
+      <c r="AR12" s="32" t="n"/>
+      <c r="AS12" s="29" t="n"/>
+      <c r="AT12" s="30" t="n"/>
+      <c r="AU12" s="33" t="n"/>
+      <c r="AV12" s="34" t="n"/>
     </row>
     <row r="13" ht="20.1" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1714,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="D13" s="16" t="n"/>
       <c r="E13" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -1723,7 +1795,7 @@
       <c r="F13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="42" t="n"/>
+      <c r="G13" s="46" t="n"/>
       <c r="H13" s="20" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -1744,7 +1816,7 @@
         <v>4</v>
       </c>
       <c r="O13" s="7" t="n"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="P13" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1768,7 +1840,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="7" t="n"/>
-      <c r="X13" s="18" t="n"/>
+      <c r="X13" s="16" t="n"/>
       <c r="Y13" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -1778,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="AA13" s="12" t="n"/>
-      <c r="AB13" s="35" t="inlineStr">
+      <c r="AB13" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -1791,8 +1863,8 @@
       <c r="AD13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="AE13" s="42" t="n"/>
-      <c r="AF13" s="43" t="inlineStr">
+      <c r="AE13" s="46" t="n"/>
+      <c r="AF13" s="47" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
@@ -1806,7 +1878,7 @@
         <v>4</v>
       </c>
       <c r="AI13" s="7" t="n"/>
-      <c r="AJ13" s="16" t="inlineStr">
+      <c r="AJ13" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -1820,7 +1892,7 @@
         <v>4</v>
       </c>
       <c r="AM13" s="7" t="n"/>
-      <c r="AN13" s="17" t="inlineStr">
+      <c r="AN13" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -1834,7 +1906,7 @@
         <v>4</v>
       </c>
       <c r="AQ13" s="12" t="n"/>
-      <c r="AR13" s="35" t="inlineStr">
+      <c r="AR13" s="49" t="inlineStr">
         <is>
           <t>Profession de foi</t>
         </is>
@@ -1848,15 +1920,15 @@
         <v>4</v>
       </c>
       <c r="AU13" s="12" t="n"/>
-      <c r="AV13" s="18" t="n"/>
+      <c r="AV13" s="16" t="n"/>
     </row>
     <row r="14" ht="20.1" customHeight="1">
       <c r="A14" s="21" t="n"/>
       <c r="C14" s="22" t="n"/>
       <c r="D14" s="26" t="n"/>
       <c r="E14" s="21" t="n"/>
-      <c r="G14" s="44" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="G14" s="50" t="n"/>
+      <c r="H14" s="28" t="n"/>
       <c r="I14" s="21" t="n"/>
       <c r="K14" s="22" t="n"/>
       <c r="L14" s="23" t="n"/>
@@ -1873,7 +1945,7 @@
       <c r="AA14" s="24" t="n"/>
       <c r="AB14" s="23" t="n"/>
       <c r="AC14" s="21" t="n"/>
-      <c r="AE14" s="44" t="n"/>
+      <c r="AE14" s="50" t="n"/>
       <c r="AF14" s="13" t="inlineStr">
         <is>
           <t>Divine Miséricorde</t>
@@ -1881,11 +1953,7 @@
       </c>
       <c r="AG14" s="21" t="n"/>
       <c r="AI14" s="22" t="n"/>
-      <c r="AJ14" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AJ14" s="23" t="n"/>
       <c r="AK14" s="21" t="n"/>
       <c r="AM14" s="22" t="n"/>
       <c r="AN14" s="23" t="n"/>
@@ -1897,62 +1965,58 @@
       <c r="AV14" s="26" t="n"/>
     </row>
     <row r="15" ht="20.1" customHeight="1">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="30" t="n"/>
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="51" t="n"/>
+      <c r="H15" s="35" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="30" t="n"/>
+      <c r="K15" s="31" t="n"/>
       <c r="L15" s="23" t="n"/>
-      <c r="M15" s="28" t="n"/>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="28" t="n"/>
-      <c r="R15" s="29" t="n"/>
-      <c r="S15" s="30" t="n"/>
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="30" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="32" t="n"/>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="30" t="n"/>
+      <c r="S15" s="31" t="n"/>
       <c r="T15" s="23" t="n"/>
-      <c r="U15" s="28" t="n"/>
-      <c r="V15" s="29" t="n"/>
-      <c r="W15" s="30" t="n"/>
-      <c r="X15" s="33" t="n"/>
-      <c r="Y15" s="28" t="n"/>
-      <c r="Z15" s="29" t="n"/>
-      <c r="AA15" s="32" t="n"/>
-      <c r="AB15" s="31" t="n"/>
-      <c r="AC15" s="28" t="n"/>
-      <c r="AD15" s="29" t="n"/>
-      <c r="AE15" s="45" t="n"/>
-      <c r="AF15" s="46" t="inlineStr">
+      <c r="U15" s="29" t="n"/>
+      <c r="V15" s="30" t="n"/>
+      <c r="W15" s="31" t="n"/>
+      <c r="X15" s="34" t="n"/>
+      <c r="Y15" s="29" t="n"/>
+      <c r="Z15" s="30" t="n"/>
+      <c r="AA15" s="33" t="n"/>
+      <c r="AB15" s="32" t="n"/>
+      <c r="AC15" s="29" t="n"/>
+      <c r="AD15" s="30" t="n"/>
+      <c r="AE15" s="51" t="n"/>
+      <c r="AF15" s="52" t="inlineStr">
         <is>
           <t>J. Sexualité</t>
         </is>
       </c>
-      <c r="AG15" s="28" t="n"/>
-      <c r="AH15" s="29" t="n"/>
-      <c r="AI15" s="30" t="n"/>
-      <c r="AJ15" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="AK15" s="28" t="n"/>
-      <c r="AL15" s="29" t="n"/>
-      <c r="AM15" s="30" t="n"/>
-      <c r="AN15" s="31" t="n"/>
-      <c r="AO15" s="28" t="n"/>
-      <c r="AP15" s="29" t="n"/>
-      <c r="AQ15" s="32" t="n"/>
-      <c r="AR15" s="31" t="n"/>
-      <c r="AS15" s="28" t="n"/>
-      <c r="AT15" s="29" t="n"/>
-      <c r="AU15" s="32" t="n"/>
-      <c r="AV15" s="33" t="n"/>
+      <c r="AG15" s="29" t="n"/>
+      <c r="AH15" s="30" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="32" t="n"/>
+      <c r="AK15" s="29" t="n"/>
+      <c r="AL15" s="30" t="n"/>
+      <c r="AM15" s="31" t="n"/>
+      <c r="AN15" s="32" t="n"/>
+      <c r="AO15" s="29" t="n"/>
+      <c r="AP15" s="30" t="n"/>
+      <c r="AQ15" s="33" t="n"/>
+      <c r="AR15" s="32" t="n"/>
+      <c r="AS15" s="29" t="n"/>
+      <c r="AT15" s="30" t="n"/>
+      <c r="AU15" s="33" t="n"/>
+      <c r="AV15" s="34" t="n"/>
     </row>
     <row r="16" ht="20.1" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1964,7 +2028,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="7" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="D16" s="16" t="n"/>
       <c r="E16" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -1974,7 +2038,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="18" t="n"/>
+      <c r="H16" s="16" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -1994,7 +2058,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="7" t="n"/>
-      <c r="P16" s="38" t="inlineStr">
+      <c r="P16" s="43" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -2008,7 +2072,7 @@
         <v>5</v>
       </c>
       <c r="S16" s="7" t="n"/>
-      <c r="T16" s="31" t="n"/>
+      <c r="T16" s="23" t="n"/>
       <c r="U16" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2018,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="W16" s="7" t="n"/>
-      <c r="X16" s="17" t="inlineStr">
+      <c r="X16" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -2032,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="AA16" s="12" t="n"/>
-      <c r="AB16" s="17" t="inlineStr">
+      <c r="AB16" s="37" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
@@ -2046,7 +2110,7 @@
         <v>5</v>
       </c>
       <c r="AE16" s="7" t="n"/>
-      <c r="AF16" s="19" t="inlineStr">
+      <c r="AF16" s="53" t="inlineStr">
         <is>
           <t>Annonciation</t>
         </is>
@@ -2060,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="AI16" s="7" t="n"/>
-      <c r="AJ16" s="18" t="n"/>
+      <c r="AJ16" s="16" t="n"/>
       <c r="AK16" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2070,7 +2134,7 @@
         <v>5</v>
       </c>
       <c r="AM16" s="7" t="n"/>
-      <c r="AN16" s="39" t="inlineStr">
+      <c r="AN16" s="54" t="inlineStr">
         <is>
           <t>Chartres 2040</t>
         </is>
@@ -2084,7 +2148,7 @@
         <v>5</v>
       </c>
       <c r="AQ16" s="12" t="n"/>
-      <c r="AR16" s="18" t="n"/>
+      <c r="AR16" s="16" t="n"/>
       <c r="AS16" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2094,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="AU16" s="12" t="n"/>
-      <c r="AV16" s="18" t="n"/>
+      <c r="AV16" s="16" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1">
       <c r="A17" s="21" t="n"/>
@@ -2105,17 +2169,13 @@
       <c r="H17" s="26" t="n"/>
       <c r="I17" s="21" t="n"/>
       <c r="K17" s="22" t="n"/>
-      <c r="L17" s="31" t="n"/>
+      <c r="L17" s="32" t="n"/>
       <c r="M17" s="21" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="23" t="n"/>
       <c r="Q17" s="21" t="n"/>
       <c r="S17" s="22" t="n"/>
-      <c r="T17" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="T17" s="23" t="n"/>
       <c r="U17" s="21" t="n"/>
       <c r="W17" s="22" t="n"/>
       <c r="X17" s="23" t="n"/>
@@ -2130,7 +2190,7 @@
       <c r="AJ17" s="26" t="n"/>
       <c r="AK17" s="21" t="n"/>
       <c r="AM17" s="22" t="n"/>
-      <c r="AN17" s="40" t="inlineStr">
+      <c r="AN17" s="45" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -2143,62 +2203,58 @@
       <c r="AV17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="29" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="33" t="n"/>
-      <c r="E18" s="28" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="28" t="n"/>
-      <c r="J18" s="29" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="34" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="30" t="n"/>
+      <c r="K18" s="31" t="n"/>
+      <c r="L18" s="27" t="inlineStr">
         <is>
           <t>Reunion Paroissiale Chartres 2040</t>
         </is>
       </c>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="29" t="n"/>
-      <c r="O18" s="30" t="n"/>
-      <c r="P18" s="31" t="n"/>
-      <c r="Q18" s="28" t="n"/>
-      <c r="R18" s="29" t="n"/>
-      <c r="S18" s="30" t="n"/>
-      <c r="T18" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="U18" s="28" t="n"/>
-      <c r="V18" s="29" t="n"/>
-      <c r="W18" s="30" t="n"/>
-      <c r="X18" s="31" t="n"/>
-      <c r="Y18" s="28" t="n"/>
-      <c r="Z18" s="29" t="n"/>
-      <c r="AA18" s="32" t="n"/>
-      <c r="AB18" s="31" t="n"/>
-      <c r="AC18" s="28" t="n"/>
-      <c r="AD18" s="29" t="n"/>
-      <c r="AE18" s="30" t="n"/>
-      <c r="AF18" s="31" t="n"/>
-      <c r="AG18" s="28" t="n"/>
-      <c r="AH18" s="29" t="n"/>
-      <c r="AI18" s="30" t="n"/>
-      <c r="AJ18" s="33" t="n"/>
-      <c r="AK18" s="28" t="n"/>
-      <c r="AL18" s="29" t="n"/>
-      <c r="AM18" s="30" t="n"/>
-      <c r="AN18" s="33" t="n"/>
-      <c r="AO18" s="28" t="n"/>
-      <c r="AP18" s="29" t="n"/>
-      <c r="AQ18" s="32" t="n"/>
-      <c r="AR18" s="33" t="n"/>
-      <c r="AS18" s="28" t="n"/>
-      <c r="AT18" s="29" t="n"/>
-      <c r="AU18" s="32" t="n"/>
-      <c r="AV18" s="33" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="30" t="n"/>
+      <c r="O18" s="31" t="n"/>
+      <c r="P18" s="32" t="n"/>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="30" t="n"/>
+      <c r="S18" s="31" t="n"/>
+      <c r="T18" s="23" t="n"/>
+      <c r="U18" s="29" t="n"/>
+      <c r="V18" s="30" t="n"/>
+      <c r="W18" s="31" t="n"/>
+      <c r="X18" s="32" t="n"/>
+      <c r="Y18" s="29" t="n"/>
+      <c r="Z18" s="30" t="n"/>
+      <c r="AA18" s="33" t="n"/>
+      <c r="AB18" s="32" t="n"/>
+      <c r="AC18" s="29" t="n"/>
+      <c r="AD18" s="30" t="n"/>
+      <c r="AE18" s="31" t="n"/>
+      <c r="AF18" s="32" t="n"/>
+      <c r="AG18" s="29" t="n"/>
+      <c r="AH18" s="30" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="34" t="n"/>
+      <c r="AK18" s="29" t="n"/>
+      <c r="AL18" s="30" t="n"/>
+      <c r="AM18" s="31" t="n"/>
+      <c r="AN18" s="34" t="n"/>
+      <c r="AO18" s="29" t="n"/>
+      <c r="AP18" s="30" t="n"/>
+      <c r="AQ18" s="33" t="n"/>
+      <c r="AR18" s="34" t="n"/>
+      <c r="AS18" s="29" t="n"/>
+      <c r="AT18" s="30" t="n"/>
+      <c r="AU18" s="33" t="n"/>
+      <c r="AV18" s="34" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -2209,7 +2265,7 @@
       <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="42" t="n"/>
+      <c r="C19" s="46" t="n"/>
       <c r="D19" s="20" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -2220,9 +2276,9 @@
         <v>6</v>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>Equipe pilote</t>
+      <c r="H19" s="48" t="inlineStr">
+        <is>
+          <t>Équipe pilote</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -2234,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="K19" s="7" t="n"/>
-      <c r="L19" s="40" t="inlineStr">
+      <c r="L19" s="55" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -2247,8 +2303,8 @@
       <c r="N19" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="O19" s="42" t="n"/>
-      <c r="P19" s="47" t="inlineStr">
+      <c r="O19" s="46" t="n"/>
+      <c r="P19" s="56" t="inlineStr">
         <is>
           <t>2e dim. de l'Avent</t>
         </is>
@@ -2262,11 +2318,7 @@
         <v>6</v>
       </c>
       <c r="S19" s="7" t="n"/>
-      <c r="T19" s="37" t="inlineStr">
-        <is>
-          <t>Semaine Épiphanie</t>
-        </is>
-      </c>
+      <c r="T19" s="23" t="n"/>
       <c r="U19" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2276,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="W19" s="7" t="n"/>
-      <c r="X19" s="16" t="inlineStr">
+      <c r="X19" s="44" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -2290,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="AA19" s="12" t="n"/>
-      <c r="AB19" s="36" t="inlineStr">
+      <c r="AB19" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -2304,11 +2356,7 @@
         <v>6</v>
       </c>
       <c r="AE19" s="7" t="n"/>
-      <c r="AF19" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AF19" s="16" t="n"/>
       <c r="AG19" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2331,8 +2379,8 @@
       <c r="AL19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="AM19" s="42" t="n"/>
-      <c r="AN19" s="35" t="inlineStr">
+      <c r="AM19" s="46" t="n"/>
+      <c r="AN19" s="49" t="inlineStr">
         <is>
           <t>1ère Communion</t>
         </is>
@@ -2346,11 +2394,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" s="12" t="n"/>
-      <c r="AR19" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AR19" s="16" t="n"/>
       <c r="AS19" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2360,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="AU19" s="12" t="n"/>
-      <c r="AV19" s="19" t="inlineStr">
+      <c r="AV19" s="53" t="inlineStr">
         <is>
           <t>Transfiguration</t>
         </is>
@@ -2368,115 +2412,103 @@
     </row>
     <row r="20" ht="20.1" customHeight="1">
       <c r="A20" s="21" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="27" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="28" t="n"/>
       <c r="E20" s="21" t="n"/>
       <c r="G20" s="22" t="n"/>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="H20" s="23" t="n"/>
       <c r="I20" s="21" t="n"/>
       <c r="K20" s="22" t="n"/>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L20" s="27" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
       <c r="M20" s="21" t="n"/>
-      <c r="O20" s="44" t="n"/>
+      <c r="O20" s="50" t="n"/>
       <c r="P20" s="23" t="n"/>
       <c r="Q20" s="21" t="n"/>
       <c r="S20" s="22" t="n"/>
       <c r="T20" s="23" t="n"/>
       <c r="U20" s="21" t="n"/>
       <c r="W20" s="22" t="n"/>
-      <c r="X20" s="36" t="inlineStr">
+      <c r="X20" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
       <c r="Y20" s="21" t="n"/>
       <c r="AA20" s="24" t="n"/>
-      <c r="AB20" s="48" t="inlineStr">
+      <c r="AB20" s="57" t="inlineStr">
         <is>
           <t>WE Prépa Mariage</t>
         </is>
       </c>
       <c r="AC20" s="21" t="n"/>
       <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AF20" s="26" t="n"/>
       <c r="AG20" s="21" t="n"/>
       <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="17" t="n"/>
+      <c r="AJ20" s="37" t="n"/>
       <c r="AK20" s="21" t="n"/>
-      <c r="AM20" s="44" t="n"/>
+      <c r="AM20" s="50" t="n"/>
       <c r="AN20" s="23" t="n"/>
       <c r="AO20" s="21" t="n"/>
       <c r="AQ20" s="24" t="n"/>
-      <c r="AR20" s="23" t="n"/>
+      <c r="AR20" s="26" t="n"/>
       <c r="AS20" s="21" t="n"/>
       <c r="AU20" s="24" t="n"/>
       <c r="AV20" s="23" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="n"/>
-      <c r="J21" s="29" t="n"/>
-      <c r="K21" s="30" t="n"/>
-      <c r="L21" s="49" t="n"/>
-      <c r="M21" s="28" t="n"/>
-      <c r="N21" s="29" t="n"/>
-      <c r="O21" s="45" t="n"/>
-      <c r="P21" s="31" t="n"/>
-      <c r="Q21" s="28" t="n"/>
-      <c r="R21" s="29" t="n"/>
-      <c r="S21" s="30" t="n"/>
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="30" t="n"/>
+      <c r="K21" s="31" t="n"/>
+      <c r="L21" s="58" t="n"/>
+      <c r="M21" s="29" t="n"/>
+      <c r="N21" s="30" t="n"/>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="32" t="n"/>
+      <c r="Q21" s="29" t="n"/>
+      <c r="R21" s="30" t="n"/>
+      <c r="S21" s="31" t="n"/>
       <c r="T21" s="23" t="n"/>
-      <c r="U21" s="28" t="n"/>
-      <c r="V21" s="29" t="n"/>
-      <c r="W21" s="30" t="n"/>
-      <c r="X21" s="33" t="n"/>
-      <c r="Y21" s="28" t="n"/>
-      <c r="Z21" s="29" t="n"/>
-      <c r="AA21" s="32" t="n"/>
+      <c r="U21" s="29" t="n"/>
+      <c r="V21" s="30" t="n"/>
+      <c r="W21" s="31" t="n"/>
+      <c r="X21" s="34" t="n"/>
+      <c r="Y21" s="29" t="n"/>
+      <c r="Z21" s="30" t="n"/>
+      <c r="AA21" s="33" t="n"/>
       <c r="AB21" s="23" t="n"/>
-      <c r="AC21" s="28" t="n"/>
-      <c r="AD21" s="29" t="n"/>
-      <c r="AE21" s="30" t="n"/>
-      <c r="AF21" s="33" t="n"/>
-      <c r="AG21" s="28" t="n"/>
-      <c r="AH21" s="29" t="n"/>
-      <c r="AI21" s="30" t="n"/>
+      <c r="AC21" s="29" t="n"/>
+      <c r="AD21" s="30" t="n"/>
+      <c r="AE21" s="31" t="n"/>
+      <c r="AF21" s="34" t="n"/>
+      <c r="AG21" s="29" t="n"/>
+      <c r="AH21" s="30" t="n"/>
+      <c r="AI21" s="31" t="n"/>
       <c r="AJ21" s="23" t="n"/>
-      <c r="AK21" s="28" t="n"/>
-      <c r="AL21" s="29" t="n"/>
-      <c r="AM21" s="45" t="n"/>
-      <c r="AN21" s="31" t="n"/>
-      <c r="AO21" s="28" t="n"/>
-      <c r="AP21" s="29" t="n"/>
-      <c r="AQ21" s="32" t="n"/>
-      <c r="AR21" s="31" t="n"/>
-      <c r="AS21" s="28" t="n"/>
-      <c r="AT21" s="29" t="n"/>
-      <c r="AU21" s="32" t="n"/>
-      <c r="AV21" s="31" t="n"/>
+      <c r="AK21" s="29" t="n"/>
+      <c r="AL21" s="30" t="n"/>
+      <c r="AM21" s="51" t="n"/>
+      <c r="AN21" s="32" t="n"/>
+      <c r="AO21" s="29" t="n"/>
+      <c r="AP21" s="30" t="n"/>
+      <c r="AQ21" s="33" t="n"/>
+      <c r="AR21" s="34" t="n"/>
+      <c r="AS21" s="29" t="n"/>
+      <c r="AT21" s="30" t="n"/>
+      <c r="AU21" s="33" t="n"/>
+      <c r="AV21" s="32" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2488,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="7" t="n"/>
-      <c r="D22" s="18" t="n"/>
+      <c r="D22" s="16" t="n"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2498,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="18" t="n"/>
+      <c r="H22" s="16" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2508,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="7" t="n"/>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L22" s="44" t="inlineStr">
         <is>
           <t>CMP avec Florence Metayer</t>
         </is>
@@ -2522,7 +2554,7 @@
         <v>7</v>
       </c>
       <c r="O22" s="7" t="n"/>
-      <c r="P22" s="18" t="n"/>
+      <c r="P22" s="16" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2541,7 +2573,7 @@
       <c r="V22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="W22" s="42" t="n"/>
+      <c r="W22" s="46" t="n"/>
       <c r="X22" s="20" t="n"/>
       <c r="Y22" s="14" t="inlineStr">
         <is>
@@ -2552,7 +2584,7 @@
         <v>7</v>
       </c>
       <c r="AA22" s="12" t="n"/>
-      <c r="AB22" s="31" t="n"/>
+      <c r="AB22" s="32" t="n"/>
       <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2562,7 +2594,7 @@
         <v>7</v>
       </c>
       <c r="AE22" s="7" t="n"/>
-      <c r="AF22" s="18" t="n"/>
+      <c r="AF22" s="16" t="n"/>
       <c r="AG22" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2572,7 +2604,7 @@
         <v>7</v>
       </c>
       <c r="AI22" s="7" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
+      <c r="AJ22" s="32" t="n"/>
       <c r="AK22" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -2582,7 +2614,7 @@
         <v>7</v>
       </c>
       <c r="AM22" s="7" t="n"/>
-      <c r="AN22" s="18" t="n"/>
+      <c r="AN22" s="16" t="n"/>
       <c r="AO22" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -2592,7 +2624,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" s="12" t="n"/>
-      <c r="AR22" s="18" t="n"/>
+      <c r="AR22" s="16" t="n"/>
       <c r="AS22" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2602,7 +2634,7 @@
         <v>7</v>
       </c>
       <c r="AU22" s="12" t="n"/>
-      <c r="AV22" s="18" t="n"/>
+      <c r="AV22" s="16" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1">
       <c r="A23" s="21" t="n"/>
@@ -2613,7 +2645,7 @@
       <c r="H23" s="26" t="n"/>
       <c r="I23" s="21" t="n"/>
       <c r="K23" s="22" t="n"/>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="L23" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -2625,11 +2657,11 @@
       <c r="S23" s="22" t="n"/>
       <c r="T23" s="23" t="n"/>
       <c r="U23" s="21" t="n"/>
-      <c r="W23" s="44" t="n"/>
-      <c r="X23" s="27" t="n"/>
+      <c r="W23" s="50" t="n"/>
+      <c r="X23" s="28" t="n"/>
       <c r="Y23" s="21" t="n"/>
       <c r="AA23" s="24" t="n"/>
-      <c r="AB23" s="50" t="inlineStr">
+      <c r="AB23" s="38" t="inlineStr">
         <is>
           <t>4e dim. de Carême</t>
         </is>
@@ -2639,7 +2671,7 @@
       <c r="AF23" s="26" t="n"/>
       <c r="AG23" s="21" t="n"/>
       <c r="AI23" s="22" t="n"/>
-      <c r="AJ23" s="43" t="inlineStr">
+      <c r="AJ23" s="59" t="inlineStr">
         <is>
           <t>Pont de l'Ascension</t>
         </is>
@@ -2655,66 +2687,66 @@
       <c r="AV23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1">
-      <c r="A24" s="28" t="n"/>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="28" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="28" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="30" t="n"/>
-      <c r="L24" s="40" t="inlineStr">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="30" t="n"/>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="30" t="n"/>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="45" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="M24" s="28" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="30" t="n"/>
-      <c r="P24" s="33" t="n"/>
-      <c r="Q24" s="28" t="n"/>
-      <c r="R24" s="29" t="n"/>
-      <c r="S24" s="30" t="n"/>
+      <c r="M24" s="29" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="31" t="n"/>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="29" t="n"/>
+      <c r="R24" s="30" t="n"/>
+      <c r="S24" s="31" t="n"/>
       <c r="T24" s="23" t="n"/>
-      <c r="U24" s="28" t="n"/>
-      <c r="V24" s="29" t="n"/>
-      <c r="W24" s="45" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="28" t="n"/>
-      <c r="Z24" s="29" t="n"/>
-      <c r="AA24" s="32" t="n"/>
-      <c r="AB24" s="36" t="inlineStr">
+      <c r="U24" s="29" t="n"/>
+      <c r="V24" s="30" t="n"/>
+      <c r="W24" s="51" t="n"/>
+      <c r="X24" s="35" t="n"/>
+      <c r="Y24" s="29" t="n"/>
+      <c r="Z24" s="30" t="n"/>
+      <c r="AA24" s="33" t="n"/>
+      <c r="AB24" s="39" t="inlineStr">
         <is>
           <t>2ème scrutin</t>
         </is>
       </c>
-      <c r="AC24" s="28" t="n"/>
-      <c r="AD24" s="29" t="n"/>
-      <c r="AE24" s="30" t="n"/>
-      <c r="AF24" s="33" t="n"/>
-      <c r="AG24" s="28" t="n"/>
-      <c r="AH24" s="29" t="n"/>
-      <c r="AI24" s="30" t="n"/>
-      <c r="AJ24" s="16" t="inlineStr">
+      <c r="AC24" s="29" t="n"/>
+      <c r="AD24" s="30" t="n"/>
+      <c r="AE24" s="31" t="n"/>
+      <c r="AF24" s="34" t="n"/>
+      <c r="AG24" s="29" t="n"/>
+      <c r="AH24" s="30" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="27" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
-      <c r="AK24" s="28" t="n"/>
-      <c r="AL24" s="29" t="n"/>
-      <c r="AM24" s="30" t="n"/>
-      <c r="AN24" s="33" t="n"/>
-      <c r="AO24" s="28" t="n"/>
-      <c r="AP24" s="29" t="n"/>
-      <c r="AQ24" s="32" t="n"/>
-      <c r="AR24" s="33" t="n"/>
-      <c r="AS24" s="28" t="n"/>
-      <c r="AT24" s="29" t="n"/>
-      <c r="AU24" s="32" t="n"/>
-      <c r="AV24" s="33" t="n"/>
+      <c r="AK24" s="29" t="n"/>
+      <c r="AL24" s="30" t="n"/>
+      <c r="AM24" s="31" t="n"/>
+      <c r="AN24" s="34" t="n"/>
+      <c r="AO24" s="29" t="n"/>
+      <c r="AP24" s="30" t="n"/>
+      <c r="AQ24" s="33" t="n"/>
+      <c r="AR24" s="34" t="n"/>
+      <c r="AS24" s="29" t="n"/>
+      <c r="AT24" s="30" t="n"/>
+      <c r="AU24" s="33" t="n"/>
+      <c r="AV24" s="34" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2726,9 +2758,9 @@
         <v>8</v>
       </c>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Equipe pilote</t>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>Équipe pilote</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2740,7 +2772,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="18" t="n"/>
+      <c r="H25" s="16" t="n"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2749,7 +2781,7 @@
       <c r="J25" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="K25" s="42" t="n"/>
+      <c r="K25" s="46" t="n"/>
       <c r="L25" s="25" t="n"/>
       <c r="M25" s="14" t="inlineStr">
         <is>
@@ -2760,9 +2792,9 @@
         <v>8</v>
       </c>
       <c r="O25" s="7" t="n"/>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
+      <c r="P25" s="37" t="inlineStr">
+        <is>
+          <t>Soirée réconciliation</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
@@ -2784,7 +2816,7 @@
         <v>8</v>
       </c>
       <c r="W25" s="7" t="n"/>
-      <c r="X25" s="18" t="n"/>
+      <c r="X25" s="16" t="n"/>
       <c r="Y25" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -2794,7 +2826,7 @@
         <v>8</v>
       </c>
       <c r="AA25" s="7" t="n"/>
-      <c r="AB25" s="17" t="inlineStr">
+      <c r="AB25" s="60" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -2808,7 +2840,7 @@
         <v>8</v>
       </c>
       <c r="AE25" s="7" t="n"/>
-      <c r="AF25" s="18" t="n"/>
+      <c r="AF25" s="16" t="n"/>
       <c r="AG25" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -2818,7 +2850,7 @@
         <v>8</v>
       </c>
       <c r="AI25" s="7" t="n"/>
-      <c r="AJ25" s="13" t="inlineStr">
+      <c r="AJ25" s="17" t="inlineStr">
         <is>
           <t>Victoire 1945</t>
         </is>
@@ -2832,11 +2864,7 @@
         <v>8</v>
       </c>
       <c r="AM25" s="7" t="n"/>
-      <c r="AN25" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AN25" s="16" t="n"/>
       <c r="AO25" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -2846,7 +2874,7 @@
         <v>8</v>
       </c>
       <c r="AQ25" s="12" t="n"/>
-      <c r="AR25" s="18" t="n"/>
+      <c r="AR25" s="16" t="n"/>
       <c r="AS25" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -2866,18 +2894,14 @@
       <c r="G26" s="22" t="n"/>
       <c r="H26" s="26" t="n"/>
       <c r="I26" s="21" t="n"/>
-      <c r="K26" s="44" t="n"/>
+      <c r="K26" s="50" t="n"/>
       <c r="L26" s="23" t="n"/>
       <c r="M26" s="21" t="n"/>
       <c r="O26" s="22" t="n"/>
-      <c r="P26" s="16" t="inlineStr">
-        <is>
-          <t>Soirée réconciliation</t>
-        </is>
-      </c>
+      <c r="P26" s="23" t="n"/>
       <c r="Q26" s="21" t="n"/>
       <c r="S26" s="22" t="n"/>
-      <c r="T26" s="31" t="n"/>
+      <c r="T26" s="32" t="n"/>
       <c r="U26" s="21" t="n"/>
       <c r="W26" s="22" t="n"/>
       <c r="X26" s="26" t="n"/>
@@ -2889,82 +2913,78 @@
       <c r="AF26" s="26" t="n"/>
       <c r="AG26" s="21" t="n"/>
       <c r="AI26" s="22" t="n"/>
-      <c r="AJ26" s="16" t="inlineStr">
+      <c r="AJ26" s="27" t="inlineStr">
         <is>
           <t>Nuit d'adoration</t>
         </is>
       </c>
       <c r="AK26" s="21" t="n"/>
       <c r="AM26" s="22" t="n"/>
-      <c r="AN26" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AN26" s="26" t="n"/>
       <c r="AO26" s="21" t="n"/>
       <c r="AQ26" s="24" t="n"/>
       <c r="AR26" s="26" t="n"/>
       <c r="AS26" s="21" t="n"/>
       <c r="AU26" s="24" t="n"/>
-      <c r="AV26" s="27" t="n"/>
+      <c r="AV26" s="28" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="28" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="28" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="45" t="n"/>
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="51" t="n"/>
       <c r="L27" s="23" t="n"/>
-      <c r="M27" s="28" t="n"/>
-      <c r="N27" s="29" t="n"/>
-      <c r="O27" s="30" t="n"/>
-      <c r="P27" s="33" t="n"/>
-      <c r="Q27" s="28" t="n"/>
-      <c r="R27" s="29" t="n"/>
-      <c r="S27" s="30" t="n"/>
-      <c r="T27" s="16" t="inlineStr">
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="30" t="n"/>
+      <c r="O27" s="31" t="n"/>
+      <c r="P27" s="32" t="n"/>
+      <c r="Q27" s="29" t="n"/>
+      <c r="R27" s="30" t="n"/>
+      <c r="S27" s="31" t="n"/>
+      <c r="T27" s="61" t="inlineStr">
         <is>
           <t>Rencontre CCN + Kion</t>
         </is>
       </c>
-      <c r="U27" s="28" t="n"/>
-      <c r="V27" s="29" t="n"/>
-      <c r="W27" s="30" t="n"/>
-      <c r="X27" s="33" t="n"/>
-      <c r="Y27" s="28" t="n"/>
-      <c r="Z27" s="29" t="n"/>
-      <c r="AA27" s="30" t="n"/>
+      <c r="U27" s="29" t="n"/>
+      <c r="V27" s="30" t="n"/>
+      <c r="W27" s="31" t="n"/>
+      <c r="X27" s="34" t="n"/>
+      <c r="Y27" s="29" t="n"/>
+      <c r="Z27" s="30" t="n"/>
+      <c r="AA27" s="31" t="n"/>
       <c r="AB27" s="23" t="n"/>
-      <c r="AC27" s="28" t="n"/>
-      <c r="AD27" s="29" t="n"/>
-      <c r="AE27" s="30" t="n"/>
-      <c r="AF27" s="33" t="n"/>
-      <c r="AG27" s="28" t="n"/>
-      <c r="AH27" s="29" t="n"/>
-      <c r="AI27" s="30" t="n"/>
-      <c r="AJ27" s="17" t="inlineStr">
+      <c r="AC27" s="29" t="n"/>
+      <c r="AD27" s="30" t="n"/>
+      <c r="AE27" s="31" t="n"/>
+      <c r="AF27" s="34" t="n"/>
+      <c r="AG27" s="29" t="n"/>
+      <c r="AH27" s="30" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="37" t="inlineStr">
         <is>
           <t>WE Ascension</t>
         </is>
       </c>
-      <c r="AK27" s="28" t="n"/>
-      <c r="AL27" s="29" t="n"/>
-      <c r="AM27" s="30" t="n"/>
-      <c r="AN27" s="33" t="n"/>
-      <c r="AO27" s="28" t="n"/>
-      <c r="AP27" s="29" t="n"/>
-      <c r="AQ27" s="32" t="n"/>
-      <c r="AR27" s="33" t="n"/>
-      <c r="AS27" s="28" t="n"/>
-      <c r="AT27" s="29" t="n"/>
-      <c r="AU27" s="32" t="n"/>
-      <c r="AV27" s="34" t="n"/>
+      <c r="AK27" s="29" t="n"/>
+      <c r="AL27" s="30" t="n"/>
+      <c r="AM27" s="31" t="n"/>
+      <c r="AN27" s="34" t="n"/>
+      <c r="AO27" s="29" t="n"/>
+      <c r="AP27" s="30" t="n"/>
+      <c r="AQ27" s="33" t="n"/>
+      <c r="AR27" s="34" t="n"/>
+      <c r="AS27" s="29" t="n"/>
+      <c r="AT27" s="30" t="n"/>
+      <c r="AU27" s="33" t="n"/>
+      <c r="AV27" s="35" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2976,7 +2996,7 @@
         <v>9</v>
       </c>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="18" t="n"/>
+      <c r="D28" s="16" t="n"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -2986,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="18" t="n"/>
+      <c r="H28" s="16" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3006,7 +3026,7 @@
         <v>9</v>
       </c>
       <c r="O28" s="7" t="n"/>
-      <c r="P28" s="18" t="n"/>
+      <c r="P28" s="16" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3016,7 +3036,7 @@
         <v>9</v>
       </c>
       <c r="S28" s="7" t="n"/>
-      <c r="T28" s="16" t="inlineStr">
+      <c r="T28" s="44" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3030,11 +3050,7 @@
         <v>9</v>
       </c>
       <c r="W28" s="7" t="n"/>
-      <c r="X28" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="X28" s="16" t="n"/>
       <c r="Y28" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -3044,7 +3060,7 @@
         <v>9</v>
       </c>
       <c r="AA28" s="7" t="n"/>
-      <c r="AB28" s="31" t="n"/>
+      <c r="AB28" s="23" t="n"/>
       <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3054,7 +3070,7 @@
         <v>9</v>
       </c>
       <c r="AE28" s="7" t="n"/>
-      <c r="AF28" s="18" t="n"/>
+      <c r="AF28" s="16" t="n"/>
       <c r="AG28" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3063,7 +3079,7 @@
       <c r="AH28" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="AI28" s="42" t="n"/>
+      <c r="AI28" s="46" t="n"/>
       <c r="AJ28" s="23" t="n"/>
       <c r="AK28" s="5" t="inlineStr">
         <is>
@@ -3074,7 +3090,7 @@
         <v>9</v>
       </c>
       <c r="AM28" s="7" t="n"/>
-      <c r="AN28" s="18" t="n"/>
+      <c r="AN28" s="16" t="n"/>
       <c r="AO28" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3084,7 +3100,7 @@
         <v>9</v>
       </c>
       <c r="AQ28" s="12" t="n"/>
-      <c r="AR28" s="18" t="n"/>
+      <c r="AR28" s="16" t="n"/>
       <c r="AS28" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3094,7 +3110,7 @@
         <v>9</v>
       </c>
       <c r="AU28" s="12" t="n"/>
-      <c r="AV28" s="18" t="n"/>
+      <c r="AV28" s="16" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1">
       <c r="A29" s="21" t="n"/>
@@ -3105,36 +3121,28 @@
       <c r="H29" s="26" t="n"/>
       <c r="I29" s="21" t="n"/>
       <c r="K29" s="22" t="n"/>
-      <c r="L29" s="31" t="n"/>
+      <c r="L29" s="32" t="n"/>
       <c r="M29" s="21" t="n"/>
       <c r="O29" s="22" t="n"/>
       <c r="P29" s="26" t="n"/>
       <c r="Q29" s="21" t="n"/>
       <c r="S29" s="22" t="n"/>
-      <c r="T29" s="36" t="inlineStr">
+      <c r="T29" s="39" t="inlineStr">
         <is>
           <t>Prépa Appel décisif</t>
         </is>
       </c>
       <c r="U29" s="21" t="n"/>
       <c r="W29" s="22" t="n"/>
-      <c r="X29" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="X29" s="26" t="n"/>
       <c r="Y29" s="21" t="n"/>
       <c r="AA29" s="22" t="n"/>
-      <c r="AB29" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AB29" s="23" t="n"/>
       <c r="AC29" s="21" t="n"/>
       <c r="AE29" s="22" t="n"/>
       <c r="AF29" s="26" t="n"/>
       <c r="AG29" s="21" t="n"/>
-      <c r="AI29" s="44" t="n"/>
+      <c r="AI29" s="50" t="n"/>
       <c r="AJ29" s="23" t="n"/>
       <c r="AK29" s="21" t="n"/>
       <c r="AM29" s="22" t="n"/>
@@ -3147,62 +3155,58 @@
       <c r="AV29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1">
-      <c r="A30" s="28" t="n"/>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="29" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="28" t="n"/>
-      <c r="J30" s="29" t="n"/>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="51" t="inlineStr">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="62" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
       </c>
-      <c r="M30" s="28" t="n"/>
-      <c r="N30" s="29" t="n"/>
-      <c r="O30" s="30" t="n"/>
-      <c r="P30" s="33" t="n"/>
-      <c r="Q30" s="28" t="n"/>
-      <c r="R30" s="29" t="n"/>
-      <c r="S30" s="30" t="n"/>
-      <c r="T30" s="33" t="n"/>
-      <c r="U30" s="28" t="n"/>
-      <c r="V30" s="29" t="n"/>
-      <c r="W30" s="30" t="n"/>
-      <c r="X30" s="33" t="n"/>
-      <c r="Y30" s="28" t="n"/>
-      <c r="Z30" s="29" t="n"/>
-      <c r="AA30" s="30" t="n"/>
-      <c r="AB30" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="AC30" s="28" t="n"/>
-      <c r="AD30" s="29" t="n"/>
-      <c r="AE30" s="30" t="n"/>
-      <c r="AF30" s="33" t="n"/>
-      <c r="AG30" s="28" t="n"/>
-      <c r="AH30" s="29" t="n"/>
-      <c r="AI30" s="45" t="n"/>
-      <c r="AJ30" s="31" t="n"/>
-      <c r="AK30" s="28" t="n"/>
-      <c r="AL30" s="29" t="n"/>
-      <c r="AM30" s="30" t="n"/>
-      <c r="AN30" s="33" t="n"/>
-      <c r="AO30" s="28" t="n"/>
-      <c r="AP30" s="29" t="n"/>
-      <c r="AQ30" s="32" t="n"/>
-      <c r="AR30" s="33" t="n"/>
-      <c r="AS30" s="28" t="n"/>
-      <c r="AT30" s="29" t="n"/>
-      <c r="AU30" s="32" t="n"/>
-      <c r="AV30" s="33" t="n"/>
+      <c r="M30" s="29" t="n"/>
+      <c r="N30" s="30" t="n"/>
+      <c r="O30" s="31" t="n"/>
+      <c r="P30" s="34" t="n"/>
+      <c r="Q30" s="29" t="n"/>
+      <c r="R30" s="30" t="n"/>
+      <c r="S30" s="31" t="n"/>
+      <c r="T30" s="34" t="n"/>
+      <c r="U30" s="29" t="n"/>
+      <c r="V30" s="30" t="n"/>
+      <c r="W30" s="31" t="n"/>
+      <c r="X30" s="34" t="n"/>
+      <c r="Y30" s="29" t="n"/>
+      <c r="Z30" s="30" t="n"/>
+      <c r="AA30" s="31" t="n"/>
+      <c r="AB30" s="32" t="n"/>
+      <c r="AC30" s="29" t="n"/>
+      <c r="AD30" s="30" t="n"/>
+      <c r="AE30" s="31" t="n"/>
+      <c r="AF30" s="34" t="n"/>
+      <c r="AG30" s="29" t="n"/>
+      <c r="AH30" s="30" t="n"/>
+      <c r="AI30" s="51" t="n"/>
+      <c r="AJ30" s="32" t="n"/>
+      <c r="AK30" s="29" t="n"/>
+      <c r="AL30" s="30" t="n"/>
+      <c r="AM30" s="31" t="n"/>
+      <c r="AN30" s="34" t="n"/>
+      <c r="AO30" s="29" t="n"/>
+      <c r="AP30" s="30" t="n"/>
+      <c r="AQ30" s="33" t="n"/>
+      <c r="AR30" s="34" t="n"/>
+      <c r="AS30" s="29" t="n"/>
+      <c r="AT30" s="30" t="n"/>
+      <c r="AU30" s="33" t="n"/>
+      <c r="AV30" s="34" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -3214,7 +3218,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="18" t="n"/>
+      <c r="D31" s="16" t="n"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3224,9 +3228,9 @@
         <v>10</v>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="40" t="inlineStr">
-        <is>
-          <t>Baptême</t>
+      <c r="H31" s="44" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -3238,7 +3242,7 @@
         <v>10</v>
       </c>
       <c r="K31" s="7" t="n"/>
-      <c r="L31" s="31" t="n"/>
+      <c r="L31" s="32" t="n"/>
       <c r="M31" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3248,7 +3252,7 @@
         <v>10</v>
       </c>
       <c r="O31" s="7" t="n"/>
-      <c r="P31" s="18" t="n"/>
+      <c r="P31" s="16" t="n"/>
       <c r="Q31" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3257,8 +3261,8 @@
       <c r="R31" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="S31" s="42" t="n"/>
-      <c r="T31" s="17" t="inlineStr">
+      <c r="S31" s="46" t="n"/>
+      <c r="T31" s="63" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3272,7 +3276,7 @@
         <v>10</v>
       </c>
       <c r="W31" s="7" t="n"/>
-      <c r="X31" s="47" t="inlineStr">
+      <c r="X31" s="56" t="inlineStr">
         <is>
           <t>Cendres</t>
         </is>
@@ -3286,7 +3290,7 @@
         <v>10</v>
       </c>
       <c r="AA31" s="7" t="n"/>
-      <c r="AB31" s="18" t="n"/>
+      <c r="AB31" s="16" t="n"/>
       <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3296,7 +3300,7 @@
         <v>10</v>
       </c>
       <c r="AE31" s="7" t="n"/>
-      <c r="AF31" s="16" t="inlineStr">
+      <c r="AF31" s="44" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3310,7 +3314,7 @@
         <v>10</v>
       </c>
       <c r="AI31" s="7" t="n"/>
-      <c r="AJ31" s="18" t="n"/>
+      <c r="AJ31" s="16" t="n"/>
       <c r="AK31" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3320,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="AM31" s="7" t="n"/>
-      <c r="AN31" s="18" t="n"/>
+      <c r="AN31" s="16" t="n"/>
       <c r="AO31" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3330,7 +3334,7 @@
         <v>10</v>
       </c>
       <c r="AQ31" s="12" t="n"/>
-      <c r="AR31" s="17" t="inlineStr">
+      <c r="AR31" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3344,7 +3348,7 @@
         <v>10</v>
       </c>
       <c r="AU31" s="12" t="n"/>
-      <c r="AV31" s="18" t="n"/>
+      <c r="AV31" s="16" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1">
       <c r="A32" s="21" t="n"/>
@@ -3352,23 +3356,19 @@
       <c r="D32" s="26" t="n"/>
       <c r="E32" s="21" t="n"/>
       <c r="G32" s="22" t="n"/>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>CMP</t>
+      <c r="H32" s="45" t="inlineStr">
+        <is>
+          <t>V &amp; V</t>
         </is>
       </c>
       <c r="I32" s="21" t="n"/>
       <c r="K32" s="22" t="n"/>
-      <c r="L32" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="L32" s="25" t="n"/>
       <c r="M32" s="21" t="n"/>
       <c r="O32" s="22" t="n"/>
       <c r="P32" s="26" t="n"/>
       <c r="Q32" s="21" t="n"/>
-      <c r="S32" s="44" t="n"/>
+      <c r="S32" s="50" t="n"/>
       <c r="T32" s="23" t="n"/>
       <c r="U32" s="21" t="n"/>
       <c r="W32" s="22" t="n"/>
@@ -3378,7 +3378,7 @@
       <c r="AB32" s="26" t="n"/>
       <c r="AC32" s="21" t="n"/>
       <c r="AE32" s="22" t="n"/>
-      <c r="AF32" s="36" t="inlineStr">
+      <c r="AF32" s="39" t="inlineStr">
         <is>
           <t>Formation Eucharistie</t>
         </is>
@@ -3397,62 +3397,54 @@
       <c r="AV32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="28" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="40" t="inlineStr">
-        <is>
-          <t>V &amp; V</t>
-        </is>
-      </c>
-      <c r="I33" s="28" t="n"/>
-      <c r="J33" s="29" t="n"/>
-      <c r="K33" s="30" t="n"/>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="M33" s="28" t="n"/>
-      <c r="N33" s="29" t="n"/>
-      <c r="O33" s="30" t="n"/>
-      <c r="P33" s="33" t="n"/>
-      <c r="Q33" s="28" t="n"/>
-      <c r="R33" s="29" t="n"/>
-      <c r="S33" s="45" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="28" t="n"/>
-      <c r="V33" s="29" t="n"/>
-      <c r="W33" s="30" t="n"/>
-      <c r="X33" s="31" t="n"/>
-      <c r="Y33" s="28" t="n"/>
-      <c r="Z33" s="29" t="n"/>
-      <c r="AA33" s="30" t="n"/>
-      <c r="AB33" s="33" t="n"/>
-      <c r="AC33" s="28" t="n"/>
-      <c r="AD33" s="29" t="n"/>
-      <c r="AE33" s="30" t="n"/>
-      <c r="AF33" s="33" t="n"/>
-      <c r="AG33" s="28" t="n"/>
-      <c r="AH33" s="29" t="n"/>
-      <c r="AI33" s="30" t="n"/>
-      <c r="AJ33" s="33" t="n"/>
-      <c r="AK33" s="28" t="n"/>
-      <c r="AL33" s="29" t="n"/>
-      <c r="AM33" s="30" t="n"/>
-      <c r="AN33" s="33" t="n"/>
-      <c r="AO33" s="28" t="n"/>
-      <c r="AP33" s="29" t="n"/>
-      <c r="AQ33" s="32" t="n"/>
-      <c r="AR33" s="31" t="n"/>
-      <c r="AS33" s="28" t="n"/>
-      <c r="AT33" s="29" t="n"/>
-      <c r="AU33" s="32" t="n"/>
-      <c r="AV33" s="33" t="n"/>
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="34" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="29" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="31" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="29" t="n"/>
+      <c r="N33" s="30" t="n"/>
+      <c r="O33" s="31" t="n"/>
+      <c r="P33" s="34" t="n"/>
+      <c r="Q33" s="29" t="n"/>
+      <c r="R33" s="30" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="32" t="n"/>
+      <c r="U33" s="29" t="n"/>
+      <c r="V33" s="30" t="n"/>
+      <c r="W33" s="31" t="n"/>
+      <c r="X33" s="32" t="n"/>
+      <c r="Y33" s="29" t="n"/>
+      <c r="Z33" s="30" t="n"/>
+      <c r="AA33" s="31" t="n"/>
+      <c r="AB33" s="34" t="n"/>
+      <c r="AC33" s="29" t="n"/>
+      <c r="AD33" s="30" t="n"/>
+      <c r="AE33" s="31" t="n"/>
+      <c r="AF33" s="34" t="n"/>
+      <c r="AG33" s="29" t="n"/>
+      <c r="AH33" s="30" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="34" t="n"/>
+      <c r="AK33" s="29" t="n"/>
+      <c r="AL33" s="30" t="n"/>
+      <c r="AM33" s="31" t="n"/>
+      <c r="AN33" s="34" t="n"/>
+      <c r="AO33" s="29" t="n"/>
+      <c r="AP33" s="30" t="n"/>
+      <c r="AQ33" s="33" t="n"/>
+      <c r="AR33" s="32" t="n"/>
+      <c r="AS33" s="29" t="n"/>
+      <c r="AT33" s="30" t="n"/>
+      <c r="AU33" s="33" t="n"/>
+      <c r="AV33" s="34" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -3464,7 +3456,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="7" t="n"/>
-      <c r="D34" s="18" t="n"/>
+      <c r="D34" s="16" t="n"/>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3473,10 +3465,10 @@
       <c r="F34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="42" t="n"/>
-      <c r="H34" s="40" t="inlineStr">
-        <is>
-          <t>Baptême</t>
+      <c r="G34" s="46" t="n"/>
+      <c r="H34" s="64" t="inlineStr">
+        <is>
+          <t>Éveil à la Foi</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -3488,11 +3480,7 @@
         <v>11</v>
       </c>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="13" t="inlineStr">
-        <is>
-          <t>Armistice 1918</t>
-        </is>
-      </c>
+      <c r="L34" s="32" t="n"/>
       <c r="M34" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3502,7 +3490,7 @@
         <v>11</v>
       </c>
       <c r="O34" s="7" t="n"/>
-      <c r="P34" s="35" t="inlineStr">
+      <c r="P34" s="36" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -3516,7 +3504,7 @@
         <v>11</v>
       </c>
       <c r="S34" s="7" t="n"/>
-      <c r="T34" s="18" t="n"/>
+      <c r="T34" s="16" t="n"/>
       <c r="U34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3526,7 +3514,7 @@
         <v>11</v>
       </c>
       <c r="W34" s="7" t="n"/>
-      <c r="X34" s="18" t="n"/>
+      <c r="X34" s="16" t="n"/>
       <c r="Y34" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -3536,7 +3524,7 @@
         <v>11</v>
       </c>
       <c r="AA34" s="7" t="n"/>
-      <c r="AB34" s="35" t="inlineStr">
+      <c r="AB34" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -3549,8 +3537,8 @@
       <c r="AD34" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="AE34" s="42" t="n"/>
-      <c r="AF34" s="17" t="inlineStr">
+      <c r="AE34" s="46" t="n"/>
+      <c r="AF34" s="63" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
@@ -3564,11 +3552,7 @@
         <v>11</v>
       </c>
       <c r="AI34" s="7" t="n"/>
-      <c r="AJ34" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AJ34" s="16" t="n"/>
       <c r="AK34" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -3578,7 +3562,7 @@
         <v>11</v>
       </c>
       <c r="AM34" s="7" t="n"/>
-      <c r="AN34" s="18" t="n"/>
+      <c r="AN34" s="16" t="n"/>
       <c r="AO34" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -3598,24 +3582,20 @@
         <v>11</v>
       </c>
       <c r="AU34" s="12" t="n"/>
-      <c r="AV34" s="18" t="n"/>
+      <c r="AV34" s="16" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1">
       <c r="A35" s="21" t="n"/>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="26" t="n"/>
       <c r="E35" s="21" t="n"/>
-      <c r="G35" s="44" t="n"/>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>Éveil à la Foi</t>
-        </is>
-      </c>
+      <c r="G35" s="50" t="n"/>
+      <c r="H35" s="65" t="n"/>
       <c r="I35" s="21" t="n"/>
       <c r="K35" s="22" t="n"/>
-      <c r="L35" s="16" t="inlineStr">
-        <is>
-          <t>Éveil à la Foi</t>
+      <c r="L35" s="17" t="inlineStr">
+        <is>
+          <t>Armistice 1918</t>
         </is>
       </c>
       <c r="M35" s="21" t="n"/>
@@ -3631,78 +3611,74 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="23" t="n"/>
       <c r="AC35" s="21" t="n"/>
-      <c r="AE35" s="44" t="n"/>
+      <c r="AE35" s="50" t="n"/>
       <c r="AF35" s="23" t="n"/>
       <c r="AG35" s="21" t="n"/>
       <c r="AI35" s="22" t="n"/>
-      <c r="AJ35" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AJ35" s="26" t="n"/>
       <c r="AK35" s="21" t="n"/>
       <c r="AM35" s="22" t="n"/>
       <c r="AN35" s="26" t="n"/>
       <c r="AO35" s="21" t="n"/>
       <c r="AQ35" s="24" t="n"/>
-      <c r="AR35" s="27" t="n"/>
+      <c r="AR35" s="28" t="n"/>
       <c r="AS35" s="21" t="n"/>
       <c r="AU35" s="24" t="n"/>
       <c r="AV35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1">
-      <c r="A36" s="28" t="n"/>
-      <c r="B36" s="29" t="n"/>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="28" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="45" t="n"/>
-      <c r="H36" s="52" t="n"/>
-      <c r="I36" s="28" t="n"/>
-      <c r="J36" s="29" t="n"/>
-      <c r="K36" s="30" t="n"/>
-      <c r="L36" s="41" t="inlineStr">
-        <is>
-          <t>Père Pascal en Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="M36" s="28" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="30" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="28" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="30" t="n"/>
-      <c r="T36" s="33" t="n"/>
-      <c r="U36" s="28" t="n"/>
-      <c r="V36" s="29" t="n"/>
-      <c r="W36" s="30" t="n"/>
-      <c r="X36" s="33" t="n"/>
-      <c r="Y36" s="28" t="n"/>
-      <c r="Z36" s="29" t="n"/>
-      <c r="AA36" s="30" t="n"/>
-      <c r="AB36" s="31" t="n"/>
-      <c r="AC36" s="28" t="n"/>
-      <c r="AD36" s="29" t="n"/>
-      <c r="AE36" s="45" t="n"/>
-      <c r="AF36" s="31" t="n"/>
-      <c r="AG36" s="28" t="n"/>
-      <c r="AH36" s="29" t="n"/>
-      <c r="AI36" s="30" t="n"/>
-      <c r="AJ36" s="33" t="n"/>
-      <c r="AK36" s="28" t="n"/>
-      <c r="AL36" s="29" t="n"/>
-      <c r="AM36" s="30" t="n"/>
-      <c r="AN36" s="33" t="n"/>
-      <c r="AO36" s="28" t="n"/>
-      <c r="AP36" s="29" t="n"/>
-      <c r="AQ36" s="32" t="n"/>
-      <c r="AR36" s="34" t="n"/>
-      <c r="AS36" s="28" t="n"/>
-      <c r="AT36" s="29" t="n"/>
-      <c r="AU36" s="32" t="n"/>
-      <c r="AV36" s="33" t="n"/>
+      <c r="A36" s="29" t="n"/>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="51" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="64" t="inlineStr">
+        <is>
+          <t>Éveil à la Foi</t>
+        </is>
+      </c>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="30" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="32" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="30" t="n"/>
+      <c r="S36" s="31" t="n"/>
+      <c r="T36" s="34" t="n"/>
+      <c r="U36" s="29" t="n"/>
+      <c r="V36" s="30" t="n"/>
+      <c r="W36" s="31" t="n"/>
+      <c r="X36" s="34" t="n"/>
+      <c r="Y36" s="29" t="n"/>
+      <c r="Z36" s="30" t="n"/>
+      <c r="AA36" s="31" t="n"/>
+      <c r="AB36" s="32" t="n"/>
+      <c r="AC36" s="29" t="n"/>
+      <c r="AD36" s="30" t="n"/>
+      <c r="AE36" s="51" t="n"/>
+      <c r="AF36" s="32" t="n"/>
+      <c r="AG36" s="29" t="n"/>
+      <c r="AH36" s="30" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="34" t="n"/>
+      <c r="AK36" s="29" t="n"/>
+      <c r="AL36" s="30" t="n"/>
+      <c r="AM36" s="31" t="n"/>
+      <c r="AN36" s="34" t="n"/>
+      <c r="AO36" s="29" t="n"/>
+      <c r="AP36" s="30" t="n"/>
+      <c r="AQ36" s="33" t="n"/>
+      <c r="AR36" s="35" t="n"/>
+      <c r="AS36" s="29" t="n"/>
+      <c r="AT36" s="30" t="n"/>
+      <c r="AU36" s="33" t="n"/>
+      <c r="AV36" s="34" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -3714,7 +3690,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="7" t="n"/>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Rentrée Cté</t>
         </is>
@@ -3738,7 +3714,7 @@
         <v>12</v>
       </c>
       <c r="K37" s="7" t="n"/>
-      <c r="L37" s="23" t="n"/>
+      <c r="L37" s="40" t="n"/>
       <c r="M37" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -3748,7 +3724,7 @@
         <v>12</v>
       </c>
       <c r="O37" s="7" t="n"/>
-      <c r="P37" s="16" t="inlineStr">
+      <c r="P37" s="44" t="inlineStr">
         <is>
           <t>CMP avec Ecole des témoins</t>
         </is>
@@ -3762,11 +3738,7 @@
         <v>12</v>
       </c>
       <c r="S37" s="7" t="n"/>
-      <c r="T37" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="T37" s="16" t="n"/>
       <c r="U37" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3776,7 +3748,7 @@
         <v>12</v>
       </c>
       <c r="W37" s="7" t="n"/>
-      <c r="X37" s="18" t="n"/>
+      <c r="X37" s="16" t="n"/>
       <c r="Y37" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -3786,7 +3758,7 @@
         <v>12</v>
       </c>
       <c r="AA37" s="7" t="n"/>
-      <c r="AB37" s="18" t="n"/>
+      <c r="AB37" s="16" t="n"/>
       <c r="AC37" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -3796,7 +3768,7 @@
         <v>12</v>
       </c>
       <c r="AE37" s="7" t="n"/>
-      <c r="AF37" s="18" t="n"/>
+      <c r="AF37" s="16" t="n"/>
       <c r="AG37" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3806,7 +3778,7 @@
         <v>12</v>
       </c>
       <c r="AI37" s="7" t="n"/>
-      <c r="AJ37" s="18" t="n"/>
+      <c r="AJ37" s="16" t="n"/>
       <c r="AK37" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -3816,7 +3788,7 @@
         <v>12</v>
       </c>
       <c r="AM37" s="7" t="n"/>
-      <c r="AN37" s="16" t="inlineStr">
+      <c r="AN37" s="44" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -3830,7 +3802,7 @@
         <v>12</v>
       </c>
       <c r="AQ37" s="12" t="n"/>
-      <c r="AR37" s="18" t="n"/>
+      <c r="AR37" s="16" t="n"/>
       <c r="AS37" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -3840,7 +3812,7 @@
         <v>12</v>
       </c>
       <c r="AU37" s="12" t="n"/>
-      <c r="AV37" s="18" t="n"/>
+      <c r="AV37" s="16" t="n"/>
     </row>
     <row r="38" ht="20.1" customHeight="1">
       <c r="A38" s="21" t="n"/>
@@ -3854,18 +3826,14 @@
       <c r="L38" s="23" t="n"/>
       <c r="M38" s="21" t="n"/>
       <c r="O38" s="22" t="n"/>
-      <c r="P38" s="17" t="inlineStr">
+      <c r="P38" s="18" t="inlineStr">
         <is>
           <t>WE Frat ccn</t>
         </is>
       </c>
       <c r="Q38" s="21" t="n"/>
       <c r="S38" s="22" t="n"/>
-      <c r="T38" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="T38" s="26" t="n"/>
       <c r="U38" s="21" t="n"/>
       <c r="W38" s="22" t="n"/>
       <c r="X38" s="26" t="n"/>
@@ -3880,7 +3848,7 @@
       <c r="AJ38" s="26" t="n"/>
       <c r="AK38" s="21" t="n"/>
       <c r="AM38" s="22" t="n"/>
-      <c r="AN38" s="36" t="inlineStr">
+      <c r="AN38" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -3893,54 +3861,54 @@
       <c r="AV38" s="26" t="n"/>
     </row>
     <row r="39" ht="20.1" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="28" t="n"/>
-      <c r="F39" s="29" t="n"/>
-      <c r="G39" s="30" t="n"/>
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="32" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="31" t="n"/>
       <c r="H39" s="23" t="n"/>
-      <c r="I39" s="28" t="n"/>
-      <c r="J39" s="29" t="n"/>
-      <c r="K39" s="30" t="n"/>
+      <c r="I39" s="29" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="31" t="n"/>
       <c r="L39" s="23" t="n"/>
-      <c r="M39" s="28" t="n"/>
-      <c r="N39" s="29" t="n"/>
-      <c r="O39" s="30" t="n"/>
+      <c r="M39" s="29" t="n"/>
+      <c r="N39" s="30" t="n"/>
+      <c r="O39" s="31" t="n"/>
       <c r="P39" s="23" t="n"/>
-      <c r="Q39" s="28" t="n"/>
-      <c r="R39" s="29" t="n"/>
-      <c r="S39" s="30" t="n"/>
-      <c r="T39" s="33" t="n"/>
-      <c r="U39" s="28" t="n"/>
-      <c r="V39" s="29" t="n"/>
-      <c r="W39" s="30" t="n"/>
-      <c r="X39" s="33" t="n"/>
-      <c r="Y39" s="28" t="n"/>
-      <c r="Z39" s="29" t="n"/>
-      <c r="AA39" s="30" t="n"/>
-      <c r="AB39" s="33" t="n"/>
-      <c r="AC39" s="28" t="n"/>
-      <c r="AD39" s="29" t="n"/>
-      <c r="AE39" s="30" t="n"/>
-      <c r="AF39" s="33" t="n"/>
-      <c r="AG39" s="28" t="n"/>
-      <c r="AH39" s="29" t="n"/>
-      <c r="AI39" s="30" t="n"/>
-      <c r="AJ39" s="33" t="n"/>
-      <c r="AK39" s="28" t="n"/>
-      <c r="AL39" s="29" t="n"/>
-      <c r="AM39" s="30" t="n"/>
-      <c r="AN39" s="33" t="n"/>
-      <c r="AO39" s="28" t="n"/>
-      <c r="AP39" s="29" t="n"/>
-      <c r="AQ39" s="32" t="n"/>
-      <c r="AR39" s="33" t="n"/>
-      <c r="AS39" s="28" t="n"/>
-      <c r="AT39" s="29" t="n"/>
-      <c r="AU39" s="32" t="n"/>
-      <c r="AV39" s="33" t="n"/>
+      <c r="Q39" s="29" t="n"/>
+      <c r="R39" s="30" t="n"/>
+      <c r="S39" s="31" t="n"/>
+      <c r="T39" s="34" t="n"/>
+      <c r="U39" s="29" t="n"/>
+      <c r="V39" s="30" t="n"/>
+      <c r="W39" s="31" t="n"/>
+      <c r="X39" s="34" t="n"/>
+      <c r="Y39" s="29" t="n"/>
+      <c r="Z39" s="30" t="n"/>
+      <c r="AA39" s="31" t="n"/>
+      <c r="AB39" s="34" t="n"/>
+      <c r="AC39" s="29" t="n"/>
+      <c r="AD39" s="30" t="n"/>
+      <c r="AE39" s="31" t="n"/>
+      <c r="AF39" s="34" t="n"/>
+      <c r="AG39" s="29" t="n"/>
+      <c r="AH39" s="30" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="34" t="n"/>
+      <c r="AK39" s="29" t="n"/>
+      <c r="AL39" s="30" t="n"/>
+      <c r="AM39" s="31" t="n"/>
+      <c r="AN39" s="34" t="n"/>
+      <c r="AO39" s="29" t="n"/>
+      <c r="AP39" s="30" t="n"/>
+      <c r="AQ39" s="33" t="n"/>
+      <c r="AR39" s="34" t="n"/>
+      <c r="AS39" s="29" t="n"/>
+      <c r="AT39" s="30" t="n"/>
+      <c r="AU39" s="33" t="n"/>
+      <c r="AV39" s="34" t="n"/>
     </row>
     <row r="40" ht="20.1" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -3951,8 +3919,8 @@
       <c r="B40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C40" s="42" t="n"/>
-      <c r="D40" s="17" t="inlineStr">
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>Rentrée Kion</t>
         </is>
@@ -3985,8 +3953,8 @@
       <c r="N40" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="O40" s="42" t="n"/>
-      <c r="P40" s="31" t="n"/>
+      <c r="O40" s="46" t="n"/>
+      <c r="P40" s="32" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -3996,7 +3964,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="7" t="n"/>
-      <c r="T40" s="18" t="n"/>
+      <c r="T40" s="16" t="n"/>
       <c r="U40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -4006,7 +3974,7 @@
         <v>13</v>
       </c>
       <c r="W40" s="7" t="n"/>
-      <c r="X40" s="18" t="n"/>
+      <c r="X40" s="16" t="n"/>
       <c r="Y40" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -4016,7 +3984,7 @@
         <v>13</v>
       </c>
       <c r="AA40" s="7" t="n"/>
-      <c r="AB40" s="17" t="inlineStr">
+      <c r="AB40" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -4030,11 +3998,7 @@
         <v>13</v>
       </c>
       <c r="AE40" s="7" t="n"/>
-      <c r="AF40" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AF40" s="16" t="n"/>
       <c r="AG40" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4044,7 +4008,7 @@
         <v>13</v>
       </c>
       <c r="AI40" s="7" t="n"/>
-      <c r="AJ40" s="35" t="inlineStr">
+      <c r="AJ40" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -4057,7 +4021,7 @@
       <c r="AL40" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="AM40" s="42" t="n"/>
+      <c r="AM40" s="46" t="n"/>
       <c r="AN40" s="20" t="n"/>
       <c r="AO40" s="5" t="inlineStr">
         <is>
@@ -4068,7 +4032,7 @@
         <v>13</v>
       </c>
       <c r="AQ40" s="12" t="n"/>
-      <c r="AR40" s="18" t="n"/>
+      <c r="AR40" s="16" t="n"/>
       <c r="AS40" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4078,21 +4042,21 @@
         <v>13</v>
       </c>
       <c r="AU40" s="12" t="n"/>
-      <c r="AV40" s="18" t="n"/>
+      <c r="AV40" s="16" t="n"/>
     </row>
     <row r="41" ht="20.1" customHeight="1">
       <c r="A41" s="21" t="n"/>
-      <c r="C41" s="44" t="n"/>
+      <c r="C41" s="50" t="n"/>
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="21" t="n"/>
       <c r="G41" s="22" t="n"/>
-      <c r="H41" s="31" t="n"/>
+      <c r="H41" s="23" t="n"/>
       <c r="I41" s="21" t="n"/>
       <c r="K41" s="22" t="n"/>
       <c r="L41" s="23" t="n"/>
       <c r="M41" s="21" t="n"/>
-      <c r="O41" s="44" t="n"/>
-      <c r="P41" s="50" t="inlineStr">
+      <c r="O41" s="50" t="n"/>
+      <c r="P41" s="38" t="inlineStr">
         <is>
           <t>3e dim. de l'Avent</t>
         </is>
@@ -4108,17 +4072,13 @@
       <c r="AB41" s="23" t="n"/>
       <c r="AC41" s="21" t="n"/>
       <c r="AE41" s="22" t="n"/>
-      <c r="AF41" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AF41" s="26" t="n"/>
       <c r="AG41" s="21" t="n"/>
       <c r="AI41" s="22" t="n"/>
       <c r="AJ41" s="23" t="n"/>
       <c r="AK41" s="21" t="n"/>
-      <c r="AM41" s="44" t="n"/>
-      <c r="AN41" s="27" t="n"/>
+      <c r="AM41" s="50" t="n"/>
+      <c r="AN41" s="28" t="n"/>
       <c r="AO41" s="21" t="n"/>
       <c r="AQ41" s="24" t="n"/>
       <c r="AR41" s="26" t="n"/>
@@ -4127,62 +4087,58 @@
       <c r="AV41" s="26" t="n"/>
     </row>
     <row r="42" ht="20.1" customHeight="1">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="31" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="29" t="n"/>
-      <c r="K42" s="30" t="n"/>
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="51" t="n"/>
+      <c r="D42" s="32" t="n"/>
+      <c r="E42" s="29" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="23" t="n"/>
+      <c r="I42" s="29" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="31" t="n"/>
       <c r="L42" s="23" t="n"/>
-      <c r="M42" s="28" t="n"/>
-      <c r="N42" s="29" t="n"/>
-      <c r="O42" s="45" t="n"/>
-      <c r="P42" s="16" t="inlineStr">
+      <c r="M42" s="29" t="n"/>
+      <c r="N42" s="30" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="64" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Q42" s="28" t="n"/>
-      <c r="R42" s="29" t="n"/>
-      <c r="S42" s="30" t="n"/>
-      <c r="T42" s="33" t="n"/>
-      <c r="U42" s="28" t="n"/>
-      <c r="V42" s="29" t="n"/>
-      <c r="W42" s="30" t="n"/>
-      <c r="X42" s="33" t="n"/>
-      <c r="Y42" s="28" t="n"/>
-      <c r="Z42" s="29" t="n"/>
-      <c r="AA42" s="30" t="n"/>
-      <c r="AB42" s="31" t="n"/>
-      <c r="AC42" s="28" t="n"/>
-      <c r="AD42" s="29" t="n"/>
-      <c r="AE42" s="30" t="n"/>
-      <c r="AF42" s="33" t="n"/>
-      <c r="AG42" s="28" t="n"/>
-      <c r="AH42" s="29" t="n"/>
-      <c r="AI42" s="30" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="28" t="n"/>
-      <c r="AL42" s="29" t="n"/>
-      <c r="AM42" s="45" t="n"/>
-      <c r="AN42" s="34" t="n"/>
-      <c r="AO42" s="28" t="n"/>
-      <c r="AP42" s="29" t="n"/>
-      <c r="AQ42" s="32" t="n"/>
-      <c r="AR42" s="33" t="n"/>
-      <c r="AS42" s="28" t="n"/>
-      <c r="AT42" s="29" t="n"/>
-      <c r="AU42" s="32" t="n"/>
-      <c r="AV42" s="33" t="n"/>
+      <c r="Q42" s="29" t="n"/>
+      <c r="R42" s="30" t="n"/>
+      <c r="S42" s="31" t="n"/>
+      <c r="T42" s="34" t="n"/>
+      <c r="U42" s="29" t="n"/>
+      <c r="V42" s="30" t="n"/>
+      <c r="W42" s="31" t="n"/>
+      <c r="X42" s="34" t="n"/>
+      <c r="Y42" s="29" t="n"/>
+      <c r="Z42" s="30" t="n"/>
+      <c r="AA42" s="31" t="n"/>
+      <c r="AB42" s="32" t="n"/>
+      <c r="AC42" s="29" t="n"/>
+      <c r="AD42" s="30" t="n"/>
+      <c r="AE42" s="31" t="n"/>
+      <c r="AF42" s="34" t="n"/>
+      <c r="AG42" s="29" t="n"/>
+      <c r="AH42" s="30" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="32" t="n"/>
+      <c r="AK42" s="29" t="n"/>
+      <c r="AL42" s="30" t="n"/>
+      <c r="AM42" s="51" t="n"/>
+      <c r="AN42" s="35" t="n"/>
+      <c r="AO42" s="29" t="n"/>
+      <c r="AP42" s="30" t="n"/>
+      <c r="AQ42" s="33" t="n"/>
+      <c r="AR42" s="34" t="n"/>
+      <c r="AS42" s="29" t="n"/>
+      <c r="AT42" s="30" t="n"/>
+      <c r="AU42" s="33" t="n"/>
+      <c r="AV42" s="34" t="n"/>
     </row>
     <row r="43" ht="20.1" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -4194,7 +4150,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="7" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="D43" s="16" t="n"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4204,11 +4160,7 @@
         <v>14</v>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="40" t="inlineStr">
-        <is>
-          <t>Catéchisme</t>
-        </is>
-      </c>
+      <c r="H43" s="23" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4218,7 +4170,7 @@
         <v>14</v>
       </c>
       <c r="K43" s="7" t="n"/>
-      <c r="L43" s="31" t="n"/>
+      <c r="L43" s="32" t="n"/>
       <c r="M43" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4228,7 +4180,7 @@
         <v>14</v>
       </c>
       <c r="O43" s="7" t="n"/>
-      <c r="P43" s="18" t="n"/>
+      <c r="P43" s="16" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4238,7 +4190,7 @@
         <v>14</v>
       </c>
       <c r="S43" s="7" t="n"/>
-      <c r="T43" s="18" t="n"/>
+      <c r="T43" s="16" t="n"/>
       <c r="U43" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -4247,8 +4199,8 @@
       <c r="V43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="W43" s="42" t="n"/>
-      <c r="X43" s="50" t="inlineStr">
+      <c r="W43" s="46" t="n"/>
+      <c r="X43" s="38" t="inlineStr">
         <is>
           <t>1er dim. de Carême</t>
         </is>
@@ -4261,8 +4213,8 @@
       <c r="Z43" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="AA43" s="42" t="n"/>
-      <c r="AB43" s="50" t="inlineStr">
+      <c r="AA43" s="46" t="n"/>
+      <c r="AB43" s="38" t="inlineStr">
         <is>
           <t>5e dim. de Carême</t>
         </is>
@@ -4276,7 +4228,7 @@
         <v>14</v>
       </c>
       <c r="AE43" s="7" t="n"/>
-      <c r="AF43" s="18" t="n"/>
+      <c r="AF43" s="16" t="n"/>
       <c r="AG43" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4286,7 +4238,7 @@
         <v>14</v>
       </c>
       <c r="AI43" s="7" t="n"/>
-      <c r="AJ43" s="18" t="n"/>
+      <c r="AJ43" s="16" t="n"/>
       <c r="AK43" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4296,7 +4248,7 @@
         <v>14</v>
       </c>
       <c r="AM43" s="7" t="n"/>
-      <c r="AN43" s="18" t="n"/>
+      <c r="AN43" s="16" t="n"/>
       <c r="AO43" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4320,7 +4272,7 @@
         <v>14</v>
       </c>
       <c r="AU43" s="12" t="n"/>
-      <c r="AV43" s="18" t="n"/>
+      <c r="AV43" s="16" t="n"/>
     </row>
     <row r="44" ht="20.1" customHeight="1">
       <c r="A44" s="21" t="n"/>
@@ -4328,14 +4280,10 @@
       <c r="D44" s="26" t="n"/>
       <c r="E44" s="21" t="n"/>
       <c r="G44" s="22" t="n"/>
-      <c r="H44" s="53" t="inlineStr">
-        <is>
-          <t>Semaine missionnaire</t>
-        </is>
-      </c>
+      <c r="H44" s="32" t="n"/>
       <c r="I44" s="21" t="n"/>
       <c r="K44" s="22" t="n"/>
-      <c r="L44" s="16" t="inlineStr">
+      <c r="L44" s="27" t="inlineStr">
         <is>
           <t>WE Couples Miss.</t>
         </is>
@@ -4347,15 +4295,15 @@
       <c r="S44" s="22" t="n"/>
       <c r="T44" s="26" t="n"/>
       <c r="U44" s="21" t="n"/>
-      <c r="W44" s="44" t="n"/>
-      <c r="X44" s="36" t="inlineStr">
+      <c r="W44" s="50" t="n"/>
+      <c r="X44" s="39" t="inlineStr">
         <is>
           <t>Appel décisif</t>
         </is>
       </c>
       <c r="Y44" s="21" t="n"/>
-      <c r="AA44" s="44" t="n"/>
-      <c r="AB44" s="36" t="inlineStr">
+      <c r="AA44" s="50" t="n"/>
+      <c r="AB44" s="39" t="inlineStr">
         <is>
           <t>3ème scrutin</t>
         </is>
@@ -4377,66 +4325,70 @@
       <c r="AV44" s="26" t="n"/>
     </row>
     <row r="45" ht="20.1" customHeight="1">
-      <c r="A45" s="28" t="n"/>
-      <c r="B45" s="29" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="28" t="n"/>
-      <c r="F45" s="29" t="n"/>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="23" t="n"/>
-      <c r="I45" s="28" t="n"/>
-      <c r="J45" s="29" t="n"/>
-      <c r="K45" s="30" t="n"/>
-      <c r="L45" s="36" t="inlineStr">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="30" t="n"/>
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="34" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="30" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="66" t="inlineStr">
+        <is>
+          <t>Catéchisme</t>
+        </is>
+      </c>
+      <c r="I45" s="29" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="31" t="n"/>
+      <c r="L45" s="39" t="inlineStr">
         <is>
           <t>Formation accompagnateurs</t>
         </is>
       </c>
-      <c r="M45" s="28" t="n"/>
-      <c r="N45" s="29" t="n"/>
-      <c r="O45" s="30" t="n"/>
-      <c r="P45" s="33" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="29" t="n"/>
-      <c r="S45" s="30" t="n"/>
-      <c r="T45" s="33" t="n"/>
-      <c r="U45" s="28" t="n"/>
-      <c r="V45" s="29" t="n"/>
-      <c r="W45" s="45" t="n"/>
-      <c r="X45" s="16" t="inlineStr">
+      <c r="M45" s="29" t="n"/>
+      <c r="N45" s="30" t="n"/>
+      <c r="O45" s="31" t="n"/>
+      <c r="P45" s="34" t="n"/>
+      <c r="Q45" s="29" t="n"/>
+      <c r="R45" s="30" t="n"/>
+      <c r="S45" s="31" t="n"/>
+      <c r="T45" s="34" t="n"/>
+      <c r="U45" s="29" t="n"/>
+      <c r="V45" s="30" t="n"/>
+      <c r="W45" s="51" t="n"/>
+      <c r="X45" s="64" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="Y45" s="28" t="n"/>
-      <c r="Z45" s="29" t="n"/>
-      <c r="AA45" s="45" t="n"/>
-      <c r="AB45" s="16" t="inlineStr">
+      <c r="Y45" s="29" t="n"/>
+      <c r="Z45" s="30" t="n"/>
+      <c r="AA45" s="51" t="n"/>
+      <c r="AB45" s="64" t="inlineStr">
         <is>
           <t>Éveil à la Foi</t>
         </is>
       </c>
-      <c r="AC45" s="28" t="n"/>
-      <c r="AD45" s="29" t="n"/>
-      <c r="AE45" s="30" t="n"/>
-      <c r="AF45" s="33" t="n"/>
-      <c r="AG45" s="28" t="n"/>
-      <c r="AH45" s="29" t="n"/>
-      <c r="AI45" s="30" t="n"/>
-      <c r="AJ45" s="33" t="n"/>
-      <c r="AK45" s="28" t="n"/>
-      <c r="AL45" s="29" t="n"/>
-      <c r="AM45" s="30" t="n"/>
-      <c r="AN45" s="33" t="n"/>
-      <c r="AO45" s="28" t="n"/>
-      <c r="AP45" s="29" t="n"/>
-      <c r="AQ45" s="32" t="n"/>
-      <c r="AR45" s="31" t="n"/>
-      <c r="AS45" s="28" t="n"/>
-      <c r="AT45" s="29" t="n"/>
-      <c r="AU45" s="32" t="n"/>
-      <c r="AV45" s="33" t="n"/>
+      <c r="AC45" s="29" t="n"/>
+      <c r="AD45" s="30" t="n"/>
+      <c r="AE45" s="31" t="n"/>
+      <c r="AF45" s="34" t="n"/>
+      <c r="AG45" s="29" t="n"/>
+      <c r="AH45" s="30" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="34" t="n"/>
+      <c r="AK45" s="29" t="n"/>
+      <c r="AL45" s="30" t="n"/>
+      <c r="AM45" s="31" t="n"/>
+      <c r="AN45" s="34" t="n"/>
+      <c r="AO45" s="29" t="n"/>
+      <c r="AP45" s="30" t="n"/>
+      <c r="AQ45" s="33" t="n"/>
+      <c r="AR45" s="32" t="n"/>
+      <c r="AS45" s="29" t="n"/>
+      <c r="AT45" s="30" t="n"/>
+      <c r="AU45" s="33" t="n"/>
+      <c r="AV45" s="34" t="n"/>
     </row>
     <row r="46" ht="20.1" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -4448,7 +4400,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="7" t="n"/>
-      <c r="D46" s="18" t="n"/>
+      <c r="D46" s="16" t="n"/>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4458,7 +4410,11 @@
         <v>15</v>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="23" t="n"/>
+      <c r="H46" s="65" t="inlineStr">
+        <is>
+          <t>Semaine missionnaire</t>
+        </is>
+      </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4467,8 +4423,8 @@
       <c r="J46" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="K46" s="42" t="n"/>
-      <c r="L46" s="16" t="n"/>
+      <c r="K46" s="46" t="n"/>
+      <c r="L46" s="27" t="n"/>
       <c r="M46" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4478,11 +4434,7 @@
         <v>15</v>
       </c>
       <c r="O46" s="7" t="n"/>
-      <c r="P46" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="P46" s="16" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4492,7 +4444,7 @@
         <v>15</v>
       </c>
       <c r="S46" s="7" t="n"/>
-      <c r="T46" s="18" t="n"/>
+      <c r="T46" s="16" t="n"/>
       <c r="U46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4502,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="W46" s="7" t="n"/>
-      <c r="X46" s="18" t="n"/>
+      <c r="X46" s="16" t="n"/>
       <c r="Y46" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -4512,7 +4464,7 @@
         <v>15</v>
       </c>
       <c r="AA46" s="7" t="n"/>
-      <c r="AB46" s="18" t="n"/>
+      <c r="AB46" s="16" t="n"/>
       <c r="AC46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4522,7 +4474,7 @@
         <v>15</v>
       </c>
       <c r="AE46" s="7" t="n"/>
-      <c r="AF46" s="48" t="inlineStr">
+      <c r="AF46" s="57" t="inlineStr">
         <is>
           <t>Prépa Mariage 3</t>
         </is>
@@ -4536,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="AI46" s="7" t="n"/>
-      <c r="AJ46" s="36" t="inlineStr">
+      <c r="AJ46" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
@@ -4550,11 +4502,7 @@
         <v>15</v>
       </c>
       <c r="AM46" s="7" t="n"/>
-      <c r="AN46" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AN46" s="16" t="n"/>
       <c r="AO46" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -4564,7 +4512,7 @@
         <v>15</v>
       </c>
       <c r="AQ46" s="12" t="n"/>
-      <c r="AR46" s="18" t="n"/>
+      <c r="AR46" s="16" t="n"/>
       <c r="AS46" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4574,7 +4522,7 @@
         <v>15</v>
       </c>
       <c r="AU46" s="12" t="n"/>
-      <c r="AV46" s="19" t="inlineStr">
+      <c r="AV46" s="53" t="inlineStr">
         <is>
           <t>Assomption</t>
         </is>
@@ -4588,15 +4536,11 @@
       <c r="G47" s="22" t="n"/>
       <c r="H47" s="23" t="n"/>
       <c r="I47" s="21" t="n"/>
-      <c r="K47" s="44" t="n"/>
-      <c r="L47" s="25" t="n"/>
+      <c r="K47" s="50" t="n"/>
+      <c r="L47" s="40" t="n"/>
       <c r="M47" s="21" t="n"/>
       <c r="O47" s="22" t="n"/>
-      <c r="P47" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="P47" s="26" t="n"/>
       <c r="Q47" s="21" t="n"/>
       <c r="S47" s="22" t="n"/>
       <c r="T47" s="26" t="n"/>
@@ -4611,18 +4555,14 @@
       <c r="AF47" s="23" t="n"/>
       <c r="AG47" s="21" t="n"/>
       <c r="AI47" s="22" t="n"/>
-      <c r="AJ47" s="17" t="inlineStr">
+      <c r="AJ47" s="18" t="inlineStr">
         <is>
           <t>Pentecôte Miss. ccn</t>
         </is>
       </c>
       <c r="AK47" s="21" t="n"/>
       <c r="AM47" s="22" t="n"/>
-      <c r="AN47" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AN47" s="26" t="n"/>
       <c r="AO47" s="21" t="n"/>
       <c r="AQ47" s="24" t="n"/>
       <c r="AR47" s="26" t="n"/>
@@ -4631,54 +4571,54 @@
       <c r="AV47" s="23" t="n"/>
     </row>
     <row r="48" ht="20.1" customHeight="1">
-      <c r="A48" s="28" t="n"/>
-      <c r="B48" s="29" t="n"/>
-      <c r="C48" s="30" t="n"/>
-      <c r="D48" s="33" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="30" t="n"/>
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="29" t="n"/>
+      <c r="F48" s="30" t="n"/>
+      <c r="G48" s="31" t="n"/>
       <c r="H48" s="23" t="n"/>
-      <c r="I48" s="28" t="n"/>
-      <c r="J48" s="29" t="n"/>
-      <c r="K48" s="45" t="n"/>
+      <c r="I48" s="29" t="n"/>
+      <c r="J48" s="30" t="n"/>
+      <c r="K48" s="51" t="n"/>
       <c r="L48" s="23" t="n"/>
-      <c r="M48" s="28" t="n"/>
-      <c r="N48" s="29" t="n"/>
-      <c r="O48" s="30" t="n"/>
-      <c r="P48" s="33" t="n"/>
-      <c r="Q48" s="28" t="n"/>
-      <c r="R48" s="29" t="n"/>
-      <c r="S48" s="30" t="n"/>
-      <c r="T48" s="33" t="n"/>
-      <c r="U48" s="28" t="n"/>
-      <c r="V48" s="29" t="n"/>
-      <c r="W48" s="30" t="n"/>
-      <c r="X48" s="33" t="n"/>
-      <c r="Y48" s="28" t="n"/>
-      <c r="Z48" s="29" t="n"/>
-      <c r="AA48" s="30" t="n"/>
-      <c r="AB48" s="33" t="n"/>
-      <c r="AC48" s="28" t="n"/>
-      <c r="AD48" s="29" t="n"/>
-      <c r="AE48" s="30" t="n"/>
-      <c r="AF48" s="31" t="n"/>
-      <c r="AG48" s="28" t="n"/>
-      <c r="AH48" s="29" t="n"/>
-      <c r="AI48" s="30" t="n"/>
+      <c r="M48" s="29" t="n"/>
+      <c r="N48" s="30" t="n"/>
+      <c r="O48" s="31" t="n"/>
+      <c r="P48" s="34" t="n"/>
+      <c r="Q48" s="29" t="n"/>
+      <c r="R48" s="30" t="n"/>
+      <c r="S48" s="31" t="n"/>
+      <c r="T48" s="34" t="n"/>
+      <c r="U48" s="29" t="n"/>
+      <c r="V48" s="30" t="n"/>
+      <c r="W48" s="31" t="n"/>
+      <c r="X48" s="34" t="n"/>
+      <c r="Y48" s="29" t="n"/>
+      <c r="Z48" s="30" t="n"/>
+      <c r="AA48" s="31" t="n"/>
+      <c r="AB48" s="34" t="n"/>
+      <c r="AC48" s="29" t="n"/>
+      <c r="AD48" s="30" t="n"/>
+      <c r="AE48" s="31" t="n"/>
+      <c r="AF48" s="32" t="n"/>
+      <c r="AG48" s="29" t="n"/>
+      <c r="AH48" s="30" t="n"/>
+      <c r="AI48" s="31" t="n"/>
       <c r="AJ48" s="23" t="n"/>
-      <c r="AK48" s="28" t="n"/>
-      <c r="AL48" s="29" t="n"/>
-      <c r="AM48" s="30" t="n"/>
-      <c r="AN48" s="33" t="n"/>
-      <c r="AO48" s="28" t="n"/>
-      <c r="AP48" s="29" t="n"/>
-      <c r="AQ48" s="32" t="n"/>
-      <c r="AR48" s="33" t="n"/>
-      <c r="AS48" s="28" t="n"/>
-      <c r="AT48" s="29" t="n"/>
-      <c r="AU48" s="32" t="n"/>
-      <c r="AV48" s="31" t="n"/>
+      <c r="AK48" s="29" t="n"/>
+      <c r="AL48" s="30" t="n"/>
+      <c r="AM48" s="31" t="n"/>
+      <c r="AN48" s="34" t="n"/>
+      <c r="AO48" s="29" t="n"/>
+      <c r="AP48" s="30" t="n"/>
+      <c r="AQ48" s="33" t="n"/>
+      <c r="AR48" s="34" t="n"/>
+      <c r="AS48" s="29" t="n"/>
+      <c r="AT48" s="30" t="n"/>
+      <c r="AU48" s="33" t="n"/>
+      <c r="AV48" s="32" t="n"/>
     </row>
     <row r="49" ht="20.1" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -4690,7 +4630,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="7" t="n"/>
-      <c r="D49" s="18" t="n"/>
+      <c r="D49" s="16" t="n"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4720,7 +4660,7 @@
         <v>16</v>
       </c>
       <c r="O49" s="7" t="n"/>
-      <c r="P49" s="18" t="n"/>
+      <c r="P49" s="16" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4730,7 +4670,7 @@
         <v>16</v>
       </c>
       <c r="S49" s="7" t="n"/>
-      <c r="T49" s="18" t="n"/>
+      <c r="T49" s="16" t="n"/>
       <c r="U49" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4740,11 +4680,7 @@
         <v>16</v>
       </c>
       <c r="W49" s="7" t="n"/>
-      <c r="X49" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="X49" s="16" t="n"/>
       <c r="Y49" s="14" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -4754,9 +4690,9 @@
         <v>16</v>
       </c>
       <c r="AA49" s="7" t="n"/>
-      <c r="AB49" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
+      <c r="AB49" s="37" t="inlineStr">
+        <is>
+          <t>Soirée réconciliation</t>
         </is>
       </c>
       <c r="AC49" s="5" t="inlineStr">
@@ -4768,7 +4704,7 @@
         <v>16</v>
       </c>
       <c r="AE49" s="7" t="n"/>
-      <c r="AF49" s="18" t="n"/>
+      <c r="AF49" s="16" t="n"/>
       <c r="AG49" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4777,7 +4713,7 @@
       <c r="AH49" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="AI49" s="42" t="n"/>
+      <c r="AI49" s="46" t="n"/>
       <c r="AJ49" s="23" t="n"/>
       <c r="AK49" s="5" t="inlineStr">
         <is>
@@ -4788,7 +4724,7 @@
         <v>16</v>
       </c>
       <c r="AM49" s="7" t="n"/>
-      <c r="AN49" s="18" t="n"/>
+      <c r="AN49" s="16" t="n"/>
       <c r="AO49" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -4798,7 +4734,7 @@
         <v>16</v>
       </c>
       <c r="AQ49" s="12" t="n"/>
-      <c r="AR49" s="18" t="n"/>
+      <c r="AR49" s="16" t="n"/>
       <c r="AS49" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -4808,7 +4744,7 @@
         <v>16</v>
       </c>
       <c r="AU49" s="12" t="n"/>
-      <c r="AV49" s="18" t="n"/>
+      <c r="AV49" s="16" t="n"/>
     </row>
     <row r="50" ht="20.1" customHeight="1">
       <c r="A50" s="21" t="n"/>
@@ -4828,24 +4764,16 @@
       <c r="T50" s="26" t="n"/>
       <c r="U50" s="21" t="n"/>
       <c r="W50" s="22" t="n"/>
-      <c r="X50" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="X50" s="26" t="n"/>
       <c r="Y50" s="21" t="n"/>
       <c r="AA50" s="22" t="n"/>
-      <c r="AB50" s="16" t="inlineStr">
-        <is>
-          <t>Soirée réconciliation</t>
-        </is>
-      </c>
+      <c r="AB50" s="23" t="n"/>
       <c r="AC50" s="21" t="n"/>
       <c r="AE50" s="22" t="n"/>
       <c r="AF50" s="26" t="n"/>
       <c r="AG50" s="21" t="n"/>
-      <c r="AI50" s="44" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
+      <c r="AI50" s="50" t="n"/>
+      <c r="AJ50" s="32" t="n"/>
       <c r="AK50" s="21" t="n"/>
       <c r="AM50" s="22" t="n"/>
       <c r="AN50" s="26" t="n"/>
@@ -4857,58 +4785,58 @@
       <c r="AV50" s="26" t="n"/>
     </row>
     <row r="51" ht="20.1" customHeight="1">
-      <c r="A51" s="28" t="n"/>
-      <c r="B51" s="29" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="29" t="n"/>
-      <c r="G51" s="30" t="n"/>
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="31" t="n"/>
+      <c r="D51" s="34" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="30" t="n"/>
+      <c r="G51" s="31" t="n"/>
       <c r="H51" s="23" t="n"/>
-      <c r="I51" s="28" t="n"/>
-      <c r="J51" s="29" t="n"/>
-      <c r="K51" s="30" t="n"/>
-      <c r="L51" s="31" t="n"/>
-      <c r="M51" s="28" t="n"/>
-      <c r="N51" s="29" t="n"/>
-      <c r="O51" s="30" t="n"/>
-      <c r="P51" s="33" t="n"/>
-      <c r="Q51" s="28" t="n"/>
-      <c r="R51" s="29" t="n"/>
-      <c r="S51" s="30" t="n"/>
-      <c r="T51" s="33" t="n"/>
-      <c r="U51" s="28" t="n"/>
-      <c r="V51" s="29" t="n"/>
-      <c r="W51" s="30" t="n"/>
-      <c r="X51" s="33" t="n"/>
-      <c r="Y51" s="28" t="n"/>
-      <c r="Z51" s="29" t="n"/>
-      <c r="AA51" s="30" t="n"/>
-      <c r="AB51" s="33" t="n"/>
-      <c r="AC51" s="28" t="n"/>
-      <c r="AD51" s="29" t="n"/>
-      <c r="AE51" s="30" t="n"/>
-      <c r="AF51" s="33" t="n"/>
-      <c r="AG51" s="28" t="n"/>
-      <c r="AH51" s="29" t="n"/>
-      <c r="AI51" s="45" t="n"/>
+      <c r="I51" s="29" t="n"/>
+      <c r="J51" s="30" t="n"/>
+      <c r="K51" s="31" t="n"/>
+      <c r="L51" s="23" t="n"/>
+      <c r="M51" s="29" t="n"/>
+      <c r="N51" s="30" t="n"/>
+      <c r="O51" s="31" t="n"/>
+      <c r="P51" s="34" t="n"/>
+      <c r="Q51" s="29" t="n"/>
+      <c r="R51" s="30" t="n"/>
+      <c r="S51" s="31" t="n"/>
+      <c r="T51" s="34" t="n"/>
+      <c r="U51" s="29" t="n"/>
+      <c r="V51" s="30" t="n"/>
+      <c r="W51" s="31" t="n"/>
+      <c r="X51" s="34" t="n"/>
+      <c r="Y51" s="29" t="n"/>
+      <c r="Z51" s="30" t="n"/>
+      <c r="AA51" s="31" t="n"/>
+      <c r="AB51" s="32" t="n"/>
+      <c r="AC51" s="29" t="n"/>
+      <c r="AD51" s="30" t="n"/>
+      <c r="AE51" s="31" t="n"/>
+      <c r="AF51" s="34" t="n"/>
+      <c r="AG51" s="29" t="n"/>
+      <c r="AH51" s="30" t="n"/>
+      <c r="AI51" s="51" t="n"/>
       <c r="AJ51" s="13" t="inlineStr">
         <is>
           <t>Pentecôte</t>
         </is>
       </c>
-      <c r="AK51" s="28" t="n"/>
-      <c r="AL51" s="29" t="n"/>
-      <c r="AM51" s="30" t="n"/>
-      <c r="AN51" s="33" t="n"/>
-      <c r="AO51" s="28" t="n"/>
-      <c r="AP51" s="29" t="n"/>
-      <c r="AQ51" s="32" t="n"/>
-      <c r="AR51" s="33" t="n"/>
-      <c r="AS51" s="28" t="n"/>
-      <c r="AT51" s="29" t="n"/>
-      <c r="AU51" s="32" t="n"/>
-      <c r="AV51" s="33" t="n"/>
+      <c r="AK51" s="29" t="n"/>
+      <c r="AL51" s="30" t="n"/>
+      <c r="AM51" s="31" t="n"/>
+      <c r="AN51" s="34" t="n"/>
+      <c r="AO51" s="29" t="n"/>
+      <c r="AP51" s="30" t="n"/>
+      <c r="AQ51" s="33" t="n"/>
+      <c r="AR51" s="34" t="n"/>
+      <c r="AS51" s="29" t="n"/>
+      <c r="AT51" s="30" t="n"/>
+      <c r="AU51" s="33" t="n"/>
+      <c r="AV51" s="34" t="n"/>
     </row>
     <row r="52" ht="20.1" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -4920,7 +4848,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="7" t="n"/>
-      <c r="D52" s="18" t="n"/>
+      <c r="D52" s="16" t="n"/>
       <c r="E52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4940,11 +4868,7 @@
         <v>17</v>
       </c>
       <c r="K52" s="7" t="n"/>
-      <c r="L52" s="16" t="inlineStr">
-        <is>
-          <t>Equipe Pilote</t>
-        </is>
-      </c>
+      <c r="L52" s="23" t="n"/>
       <c r="M52" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -4954,7 +4878,7 @@
         <v>17</v>
       </c>
       <c r="O52" s="7" t="n"/>
-      <c r="P52" s="18" t="n"/>
+      <c r="P52" s="16" t="n"/>
       <c r="Q52" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -4963,7 +4887,7 @@
       <c r="R52" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="S52" s="42" t="n"/>
+      <c r="S52" s="46" t="n"/>
       <c r="T52" s="20" t="n"/>
       <c r="U52" s="14" t="inlineStr">
         <is>
@@ -4974,7 +4898,7 @@
         <v>17</v>
       </c>
       <c r="W52" s="7" t="n"/>
-      <c r="X52" s="18" t="n"/>
+      <c r="X52" s="16" t="n"/>
       <c r="Y52" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -4984,7 +4908,7 @@
         <v>17</v>
       </c>
       <c r="AA52" s="7" t="n"/>
-      <c r="AB52" s="18" t="n"/>
+      <c r="AB52" s="16" t="n"/>
       <c r="AC52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -4994,7 +4918,7 @@
         <v>17</v>
       </c>
       <c r="AE52" s="12" t="n"/>
-      <c r="AF52" s="18" t="n"/>
+      <c r="AF52" s="16" t="n"/>
       <c r="AG52" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5004,7 +4928,7 @@
         <v>17</v>
       </c>
       <c r="AI52" s="7" t="n"/>
-      <c r="AJ52" s="51" t="n"/>
+      <c r="AJ52" s="62" t="n"/>
       <c r="AK52" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5014,7 +4938,7 @@
         <v>17</v>
       </c>
       <c r="AM52" s="7" t="n"/>
-      <c r="AN52" s="18" t="n"/>
+      <c r="AN52" s="16" t="n"/>
       <c r="AO52" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5024,7 +4948,7 @@
         <v>17</v>
       </c>
       <c r="AQ52" s="12" t="n"/>
-      <c r="AR52" s="18" t="n"/>
+      <c r="AR52" s="16" t="n"/>
       <c r="AS52" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5034,7 +4958,7 @@
         <v>17</v>
       </c>
       <c r="AU52" s="12" t="n"/>
-      <c r="AV52" s="18" t="n"/>
+      <c r="AV52" s="16" t="n"/>
     </row>
     <row r="53" ht="20.1" customHeight="1">
       <c r="A53" s="21" t="n"/>
@@ -5045,17 +4969,13 @@
       <c r="H53" s="23" t="n"/>
       <c r="I53" s="21" t="n"/>
       <c r="K53" s="22" t="n"/>
-      <c r="L53" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="L53" s="32" t="n"/>
       <c r="M53" s="21" t="n"/>
       <c r="O53" s="22" t="n"/>
       <c r="P53" s="26" t="n"/>
       <c r="Q53" s="21" t="n"/>
-      <c r="S53" s="44" t="n"/>
-      <c r="T53" s="27" t="n"/>
+      <c r="S53" s="50" t="n"/>
+      <c r="T53" s="28" t="n"/>
       <c r="U53" s="21" t="n"/>
       <c r="W53" s="22" t="n"/>
       <c r="X53" s="26" t="n"/>
@@ -5067,7 +4987,7 @@
       <c r="AF53" s="26" t="n"/>
       <c r="AG53" s="21" t="n"/>
       <c r="AI53" s="22" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
+      <c r="AJ53" s="32" t="n"/>
       <c r="AK53" s="21" t="n"/>
       <c r="AM53" s="22" t="n"/>
       <c r="AN53" s="26" t="n"/>
@@ -5079,62 +4999,62 @@
       <c r="AV53" s="26" t="n"/>
     </row>
     <row r="54" ht="20.1" customHeight="1">
-      <c r="A54" s="28" t="n"/>
-      <c r="B54" s="29" t="n"/>
-      <c r="C54" s="30" t="n"/>
-      <c r="D54" s="33" t="n"/>
-      <c r="E54" s="28" t="n"/>
-      <c r="F54" s="29" t="n"/>
-      <c r="G54" s="32" t="n"/>
+      <c r="A54" s="29" t="n"/>
+      <c r="B54" s="30" t="n"/>
+      <c r="C54" s="31" t="n"/>
+      <c r="D54" s="34" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="30" t="n"/>
+      <c r="G54" s="33" t="n"/>
       <c r="H54" s="23" t="n"/>
-      <c r="I54" s="28" t="n"/>
-      <c r="J54" s="29" t="n"/>
-      <c r="K54" s="30" t="n"/>
-      <c r="L54" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="M54" s="28" t="n"/>
-      <c r="N54" s="29" t="n"/>
-      <c r="O54" s="30" t="n"/>
-      <c r="P54" s="33" t="n"/>
-      <c r="Q54" s="28" t="n"/>
-      <c r="R54" s="29" t="n"/>
-      <c r="S54" s="45" t="n"/>
-      <c r="T54" s="34" t="n"/>
-      <c r="U54" s="28" t="n"/>
-      <c r="V54" s="29" t="n"/>
-      <c r="W54" s="30" t="n"/>
-      <c r="X54" s="33" t="n"/>
-      <c r="Y54" s="28" t="n"/>
-      <c r="Z54" s="29" t="n"/>
-      <c r="AA54" s="30" t="n"/>
-      <c r="AB54" s="33" t="n"/>
-      <c r="AC54" s="28" t="n"/>
-      <c r="AD54" s="29" t="n"/>
-      <c r="AE54" s="32" t="n"/>
-      <c r="AF54" s="33" t="n"/>
-      <c r="AG54" s="28" t="n"/>
-      <c r="AH54" s="29" t="n"/>
-      <c r="AI54" s="30" t="n"/>
-      <c r="AJ54" s="13" t="inlineStr">
+      <c r="I54" s="29" t="n"/>
+      <c r="J54" s="30" t="n"/>
+      <c r="K54" s="31" t="n"/>
+      <c r="L54" s="44" t="inlineStr">
+        <is>
+          <t>Équipe pilote</t>
+        </is>
+      </c>
+      <c r="M54" s="29" t="n"/>
+      <c r="N54" s="30" t="n"/>
+      <c r="O54" s="31" t="n"/>
+      <c r="P54" s="34" t="n"/>
+      <c r="Q54" s="29" t="n"/>
+      <c r="R54" s="30" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="35" t="n"/>
+      <c r="U54" s="29" t="n"/>
+      <c r="V54" s="30" t="n"/>
+      <c r="W54" s="31" t="n"/>
+      <c r="X54" s="34" t="n"/>
+      <c r="Y54" s="29" t="n"/>
+      <c r="Z54" s="30" t="n"/>
+      <c r="AA54" s="31" t="n"/>
+      <c r="AB54" s="34" t="n"/>
+      <c r="AC54" s="29" t="n"/>
+      <c r="AD54" s="30" t="n"/>
+      <c r="AE54" s="33" t="n"/>
+      <c r="AF54" s="34" t="n"/>
+      <c r="AG54" s="29" t="n"/>
+      <c r="AH54" s="30" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="17" t="inlineStr">
         <is>
           <t>Lundi de Pentecôte</t>
         </is>
       </c>
-      <c r="AK54" s="28" t="n"/>
-      <c r="AL54" s="29" t="n"/>
-      <c r="AM54" s="30" t="n"/>
-      <c r="AN54" s="33" t="n"/>
-      <c r="AO54" s="28" t="n"/>
-      <c r="AP54" s="29" t="n"/>
-      <c r="AQ54" s="32" t="n"/>
-      <c r="AR54" s="33" t="n"/>
-      <c r="AS54" s="28" t="n"/>
-      <c r="AT54" s="29" t="n"/>
-      <c r="AU54" s="32" t="n"/>
-      <c r="AV54" s="33" t="n"/>
+      <c r="AK54" s="29" t="n"/>
+      <c r="AL54" s="30" t="n"/>
+      <c r="AM54" s="31" t="n"/>
+      <c r="AN54" s="34" t="n"/>
+      <c r="AO54" s="29" t="n"/>
+      <c r="AP54" s="30" t="n"/>
+      <c r="AQ54" s="33" t="n"/>
+      <c r="AR54" s="34" t="n"/>
+      <c r="AS54" s="29" t="n"/>
+      <c r="AT54" s="30" t="n"/>
+      <c r="AU54" s="33" t="n"/>
+      <c r="AV54" s="34" t="n"/>
     </row>
     <row r="55" ht="20.1" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -5146,7 +5066,7 @@
         <v>18</v>
       </c>
       <c r="C55" s="7" t="n"/>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="36" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -5180,7 +5100,7 @@
         <v>18</v>
       </c>
       <c r="O55" s="7" t="n"/>
-      <c r="P55" s="18" t="n"/>
+      <c r="P55" s="16" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5190,7 +5110,7 @@
         <v>18</v>
       </c>
       <c r="S55" s="7" t="n"/>
-      <c r="T55" s="18" t="n"/>
+      <c r="T55" s="16" t="n"/>
       <c r="U55" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -5200,7 +5120,7 @@
         <v>18</v>
       </c>
       <c r="W55" s="7" t="n"/>
-      <c r="X55" s="48" t="inlineStr">
+      <c r="X55" s="57" t="inlineStr">
         <is>
           <t>Prépa Mariage 2</t>
         </is>
@@ -5214,7 +5134,7 @@
         <v>18</v>
       </c>
       <c r="AA55" s="7" t="n"/>
-      <c r="AB55" s="35" t="inlineStr">
+      <c r="AB55" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -5238,11 +5158,7 @@
         <v>18</v>
       </c>
       <c r="AI55" s="7" t="n"/>
-      <c r="AJ55" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AJ55" s="16" t="n"/>
       <c r="AK55" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5252,7 +5168,7 @@
         <v>18</v>
       </c>
       <c r="AM55" s="7" t="n"/>
-      <c r="AN55" s="18" t="n"/>
+      <c r="AN55" s="16" t="n"/>
       <c r="AO55" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -5272,7 +5188,7 @@
         <v>18</v>
       </c>
       <c r="AU55" s="12" t="n"/>
-      <c r="AV55" s="18" t="n"/>
+      <c r="AV55" s="16" t="n"/>
     </row>
     <row r="56" ht="20.1" customHeight="1">
       <c r="A56" s="21" t="n"/>
@@ -5280,7 +5196,7 @@
       <c r="D56" s="23" t="n"/>
       <c r="E56" s="21" t="n"/>
       <c r="G56" s="24" t="n"/>
-      <c r="H56" s="31" t="n"/>
+      <c r="H56" s="32" t="n"/>
       <c r="I56" s="21" t="n"/>
       <c r="K56" s="22" t="n"/>
       <c r="L56" s="23" t="n"/>
@@ -5298,77 +5214,73 @@
       <c r="AB56" s="23" t="n"/>
       <c r="AC56" s="21" t="n"/>
       <c r="AE56" s="24" t="n"/>
-      <c r="AF56" s="27" t="n"/>
+      <c r="AF56" s="28" t="n"/>
       <c r="AG56" s="21" t="n"/>
       <c r="AI56" s="22" t="n"/>
-      <c r="AJ56" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AJ56" s="26" t="n"/>
       <c r="AK56" s="21" t="n"/>
       <c r="AM56" s="22" t="n"/>
       <c r="AN56" s="26" t="n"/>
       <c r="AO56" s="21" t="n"/>
       <c r="AQ56" s="24" t="n"/>
-      <c r="AR56" s="27" t="n"/>
+      <c r="AR56" s="28" t="n"/>
       <c r="AS56" s="21" t="n"/>
       <c r="AU56" s="24" t="n"/>
       <c r="AV56" s="26" t="n"/>
     </row>
     <row r="57" ht="20.1" customHeight="1">
-      <c r="A57" s="28" t="n"/>
-      <c r="B57" s="29" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="28" t="n"/>
-      <c r="F57" s="29" t="n"/>
-      <c r="G57" s="32" t="n"/>
-      <c r="H57" s="43" t="inlineStr">
+      <c r="A57" s="29" t="n"/>
+      <c r="B57" s="30" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="29" t="n"/>
+      <c r="F57" s="30" t="n"/>
+      <c r="G57" s="33" t="n"/>
+      <c r="H57" s="47" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
       </c>
-      <c r="I57" s="28" t="n"/>
-      <c r="J57" s="29" t="n"/>
-      <c r="K57" s="30" t="n"/>
+      <c r="I57" s="29" t="n"/>
+      <c r="J57" s="30" t="n"/>
+      <c r="K57" s="31" t="n"/>
       <c r="L57" s="23" t="n"/>
-      <c r="M57" s="28" t="n"/>
-      <c r="N57" s="29" t="n"/>
-      <c r="O57" s="30" t="n"/>
-      <c r="P57" s="33" t="n"/>
-      <c r="Q57" s="28" t="n"/>
-      <c r="R57" s="29" t="n"/>
-      <c r="S57" s="30" t="n"/>
-      <c r="T57" s="33" t="n"/>
-      <c r="U57" s="28" t="n"/>
-      <c r="V57" s="29" t="n"/>
-      <c r="W57" s="30" t="n"/>
-      <c r="X57" s="31" t="n"/>
-      <c r="Y57" s="28" t="n"/>
-      <c r="Z57" s="29" t="n"/>
-      <c r="AA57" s="30" t="n"/>
-      <c r="AB57" s="31" t="n"/>
-      <c r="AC57" s="28" t="n"/>
-      <c r="AD57" s="29" t="n"/>
-      <c r="AE57" s="32" t="n"/>
-      <c r="AF57" s="34" t="n"/>
-      <c r="AG57" s="28" t="n"/>
-      <c r="AH57" s="29" t="n"/>
-      <c r="AI57" s="30" t="n"/>
-      <c r="AJ57" s="33" t="n"/>
-      <c r="AK57" s="28" t="n"/>
-      <c r="AL57" s="29" t="n"/>
-      <c r="AM57" s="30" t="n"/>
-      <c r="AN57" s="33" t="n"/>
-      <c r="AO57" s="28" t="n"/>
-      <c r="AP57" s="29" t="n"/>
-      <c r="AQ57" s="32" t="n"/>
-      <c r="AR57" s="34" t="n"/>
-      <c r="AS57" s="28" t="n"/>
-      <c r="AT57" s="29" t="n"/>
-      <c r="AU57" s="32" t="n"/>
-      <c r="AV57" s="33" t="n"/>
+      <c r="M57" s="29" t="n"/>
+      <c r="N57" s="30" t="n"/>
+      <c r="O57" s="31" t="n"/>
+      <c r="P57" s="34" t="n"/>
+      <c r="Q57" s="29" t="n"/>
+      <c r="R57" s="30" t="n"/>
+      <c r="S57" s="31" t="n"/>
+      <c r="T57" s="34" t="n"/>
+      <c r="U57" s="29" t="n"/>
+      <c r="V57" s="30" t="n"/>
+      <c r="W57" s="31" t="n"/>
+      <c r="X57" s="32" t="n"/>
+      <c r="Y57" s="29" t="n"/>
+      <c r="Z57" s="30" t="n"/>
+      <c r="AA57" s="31" t="n"/>
+      <c r="AB57" s="32" t="n"/>
+      <c r="AC57" s="29" t="n"/>
+      <c r="AD57" s="30" t="n"/>
+      <c r="AE57" s="33" t="n"/>
+      <c r="AF57" s="35" t="n"/>
+      <c r="AG57" s="29" t="n"/>
+      <c r="AH57" s="30" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="34" t="n"/>
+      <c r="AK57" s="29" t="n"/>
+      <c r="AL57" s="30" t="n"/>
+      <c r="AM57" s="31" t="n"/>
+      <c r="AN57" s="34" t="n"/>
+      <c r="AO57" s="29" t="n"/>
+      <c r="AP57" s="30" t="n"/>
+      <c r="AQ57" s="33" t="n"/>
+      <c r="AR57" s="35" t="n"/>
+      <c r="AS57" s="29" t="n"/>
+      <c r="AT57" s="30" t="n"/>
+      <c r="AU57" s="33" t="n"/>
+      <c r="AV57" s="34" t="n"/>
     </row>
     <row r="58" ht="20.1" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -5380,9 +5292,9 @@
         <v>19</v>
       </c>
       <c r="C58" s="7" t="n"/>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>Baptême</t>
+      <c r="D58" s="53" t="inlineStr">
+        <is>
+          <t>ND Velankanni (Tamoul)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -5394,7 +5306,7 @@
         <v>19</v>
       </c>
       <c r="G58" s="12" t="n"/>
-      <c r="H58" s="18" t="n"/>
+      <c r="H58" s="16" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5414,7 +5326,7 @@
         <v>19</v>
       </c>
       <c r="O58" s="12" t="n"/>
-      <c r="P58" s="18" t="n"/>
+      <c r="P58" s="16" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -5424,11 +5336,7 @@
         <v>19</v>
       </c>
       <c r="S58" s="7" t="n"/>
-      <c r="T58" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="T58" s="16" t="n"/>
       <c r="U58" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5438,7 +5346,7 @@
         <v>19</v>
       </c>
       <c r="W58" s="7" t="n"/>
-      <c r="X58" s="18" t="n"/>
+      <c r="X58" s="16" t="n"/>
       <c r="Y58" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -5448,7 +5356,7 @@
         <v>19</v>
       </c>
       <c r="AA58" s="7" t="n"/>
-      <c r="AB58" s="18" t="n"/>
+      <c r="AB58" s="16" t="n"/>
       <c r="AC58" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5458,7 +5366,7 @@
         <v>19</v>
       </c>
       <c r="AE58" s="12" t="n"/>
-      <c r="AF58" s="18" t="n"/>
+      <c r="AF58" s="16" t="n"/>
       <c r="AG58" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5468,7 +5376,7 @@
         <v>19</v>
       </c>
       <c r="AI58" s="7" t="n"/>
-      <c r="AJ58" s="18" t="n"/>
+      <c r="AJ58" s="16" t="n"/>
       <c r="AK58" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5478,7 +5386,7 @@
         <v>19</v>
       </c>
       <c r="AM58" s="7" t="n"/>
-      <c r="AN58" s="19" t="inlineStr">
+      <c r="AN58" s="53" t="inlineStr">
         <is>
           <t>St Antoine (Tamoul)</t>
         </is>
@@ -5492,7 +5400,7 @@
         <v>19</v>
       </c>
       <c r="AQ58" s="12" t="n"/>
-      <c r="AR58" s="18" t="n"/>
+      <c r="AR58" s="16" t="n"/>
       <c r="AS58" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5502,32 +5410,24 @@
         <v>19</v>
       </c>
       <c r="AU58" s="12" t="n"/>
-      <c r="AV58" s="18" t="n"/>
+      <c r="AV58" s="16" t="n"/>
     </row>
     <row r="59" ht="20.1" customHeight="1">
       <c r="A59" s="21" t="n"/>
       <c r="C59" s="22" t="n"/>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>ND Velankanni (Tamoul)</t>
-        </is>
-      </c>
+      <c r="D59" s="23" t="n"/>
       <c r="E59" s="21" t="n"/>
       <c r="G59" s="24" t="n"/>
       <c r="H59" s="26" t="n"/>
       <c r="I59" s="21" t="n"/>
       <c r="K59" s="22" t="n"/>
-      <c r="L59" s="31" t="n"/>
+      <c r="L59" s="32" t="n"/>
       <c r="M59" s="21" t="n"/>
       <c r="O59" s="24" t="n"/>
       <c r="P59" s="26" t="n"/>
       <c r="Q59" s="21" t="n"/>
       <c r="S59" s="22" t="n"/>
-      <c r="T59" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="T59" s="26" t="n"/>
       <c r="U59" s="21" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="26" t="n"/>
@@ -5551,58 +5451,58 @@
       <c r="AV59" s="26" t="n"/>
     </row>
     <row r="60" ht="20.1" customHeight="1">
-      <c r="A60" s="28" t="n"/>
-      <c r="B60" s="29" t="n"/>
-      <c r="C60" s="30" t="n"/>
-      <c r="D60" s="33" t="n"/>
-      <c r="E60" s="28" t="n"/>
-      <c r="F60" s="29" t="n"/>
-      <c r="G60" s="32" t="n"/>
-      <c r="H60" s="33" t="n"/>
-      <c r="I60" s="28" t="n"/>
-      <c r="J60" s="29" t="n"/>
-      <c r="K60" s="30" t="n"/>
-      <c r="L60" s="39" t="inlineStr">
+      <c r="A60" s="29" t="n"/>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="31" t="n"/>
+      <c r="D60" s="32" t="n"/>
+      <c r="E60" s="29" t="n"/>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="33" t="n"/>
+      <c r="H60" s="34" t="n"/>
+      <c r="I60" s="29" t="n"/>
+      <c r="J60" s="30" t="n"/>
+      <c r="K60" s="31" t="n"/>
+      <c r="L60" s="54" t="inlineStr">
         <is>
           <t>Conseil presbytéral</t>
         </is>
       </c>
-      <c r="M60" s="28" t="n"/>
-      <c r="N60" s="29" t="n"/>
-      <c r="O60" s="32" t="n"/>
-      <c r="P60" s="33" t="n"/>
-      <c r="Q60" s="28" t="n"/>
-      <c r="R60" s="29" t="n"/>
-      <c r="S60" s="30" t="n"/>
-      <c r="T60" s="33" t="n"/>
-      <c r="U60" s="28" t="n"/>
-      <c r="V60" s="29" t="n"/>
-      <c r="W60" s="30" t="n"/>
-      <c r="X60" s="33" t="n"/>
-      <c r="Y60" s="28" t="n"/>
-      <c r="Z60" s="29" t="n"/>
-      <c r="AA60" s="30" t="n"/>
-      <c r="AB60" s="33" t="n"/>
-      <c r="AC60" s="28" t="n"/>
-      <c r="AD60" s="29" t="n"/>
-      <c r="AE60" s="32" t="n"/>
-      <c r="AF60" s="33" t="n"/>
-      <c r="AG60" s="28" t="n"/>
-      <c r="AH60" s="29" t="n"/>
-      <c r="AI60" s="30" t="n"/>
-      <c r="AJ60" s="33" t="n"/>
-      <c r="AK60" s="28" t="n"/>
-      <c r="AL60" s="29" t="n"/>
-      <c r="AM60" s="30" t="n"/>
-      <c r="AN60" s="31" t="n"/>
-      <c r="AO60" s="28" t="n"/>
-      <c r="AP60" s="29" t="n"/>
-      <c r="AQ60" s="32" t="n"/>
-      <c r="AR60" s="33" t="n"/>
-      <c r="AS60" s="28" t="n"/>
-      <c r="AT60" s="29" t="n"/>
-      <c r="AU60" s="32" t="n"/>
-      <c r="AV60" s="33" t="n"/>
+      <c r="M60" s="29" t="n"/>
+      <c r="N60" s="30" t="n"/>
+      <c r="O60" s="33" t="n"/>
+      <c r="P60" s="34" t="n"/>
+      <c r="Q60" s="29" t="n"/>
+      <c r="R60" s="30" t="n"/>
+      <c r="S60" s="31" t="n"/>
+      <c r="T60" s="34" t="n"/>
+      <c r="U60" s="29" t="n"/>
+      <c r="V60" s="30" t="n"/>
+      <c r="W60" s="31" t="n"/>
+      <c r="X60" s="34" t="n"/>
+      <c r="Y60" s="29" t="n"/>
+      <c r="Z60" s="30" t="n"/>
+      <c r="AA60" s="31" t="n"/>
+      <c r="AB60" s="34" t="n"/>
+      <c r="AC60" s="29" t="n"/>
+      <c r="AD60" s="30" t="n"/>
+      <c r="AE60" s="33" t="n"/>
+      <c r="AF60" s="34" t="n"/>
+      <c r="AG60" s="29" t="n"/>
+      <c r="AH60" s="30" t="n"/>
+      <c r="AI60" s="31" t="n"/>
+      <c r="AJ60" s="34" t="n"/>
+      <c r="AK60" s="29" t="n"/>
+      <c r="AL60" s="30" t="n"/>
+      <c r="AM60" s="31" t="n"/>
+      <c r="AN60" s="32" t="n"/>
+      <c r="AO60" s="29" t="n"/>
+      <c r="AP60" s="30" t="n"/>
+      <c r="AQ60" s="33" t="n"/>
+      <c r="AR60" s="34" t="n"/>
+      <c r="AS60" s="29" t="n"/>
+      <c r="AT60" s="30" t="n"/>
+      <c r="AU60" s="33" t="n"/>
+      <c r="AV60" s="34" t="n"/>
     </row>
     <row r="61" ht="20.1" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -5613,8 +5513,8 @@
       <c r="B61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C61" s="42" t="n"/>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="37" t="inlineStr">
         <is>
           <t>Journée Communautaire</t>
         </is>
@@ -5628,11 +5528,7 @@
         <v>20</v>
       </c>
       <c r="G61" s="12" t="n"/>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="H61" s="40" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5652,7 +5548,7 @@
         <v>20</v>
       </c>
       <c r="O61" s="12" t="n"/>
-      <c r="P61" s="47" t="inlineStr">
+      <c r="P61" s="56" t="inlineStr">
         <is>
           <t>4e dim. de l'Avent</t>
         </is>
@@ -5666,7 +5562,7 @@
         <v>20</v>
       </c>
       <c r="S61" s="7" t="n"/>
-      <c r="T61" s="18" t="n"/>
+      <c r="T61" s="16" t="n"/>
       <c r="U61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5676,7 +5572,7 @@
         <v>20</v>
       </c>
       <c r="W61" s="12" t="n"/>
-      <c r="X61" s="18" t="n"/>
+      <c r="X61" s="16" t="n"/>
       <c r="Y61" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -5686,7 +5582,7 @@
         <v>20</v>
       </c>
       <c r="AA61" s="7" t="n"/>
-      <c r="AB61" s="17" t="inlineStr">
+      <c r="AB61" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -5700,11 +5596,7 @@
         <v>20</v>
       </c>
       <c r="AE61" s="12" t="n"/>
-      <c r="AF61" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AF61" s="16" t="n"/>
       <c r="AG61" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5714,7 +5606,7 @@
         <v>20</v>
       </c>
       <c r="AI61" s="7" t="n"/>
-      <c r="AJ61" s="35" t="inlineStr">
+      <c r="AJ61" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -5727,7 +5619,7 @@
       <c r="AL61" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AM61" s="42" t="n"/>
+      <c r="AM61" s="46" t="n"/>
       <c r="AN61" s="20" t="n"/>
       <c r="AO61" s="5" t="inlineStr">
         <is>
@@ -5738,7 +5630,7 @@
         <v>20</v>
       </c>
       <c r="AQ61" s="12" t="n"/>
-      <c r="AR61" s="18" t="n"/>
+      <c r="AR61" s="16" t="n"/>
       <c r="AS61" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5748,15 +5640,15 @@
         <v>20</v>
       </c>
       <c r="AU61" s="12" t="n"/>
-      <c r="AV61" s="18" t="n"/>
+      <c r="AV61" s="16" t="n"/>
     </row>
     <row r="62" ht="20.1" customHeight="1">
       <c r="A62" s="21" t="n"/>
-      <c r="C62" s="44" t="n"/>
+      <c r="C62" s="50" t="n"/>
       <c r="D62" s="23" t="n"/>
       <c r="E62" s="21" t="n"/>
       <c r="G62" s="24" t="n"/>
-      <c r="H62" s="41" t="n"/>
+      <c r="H62" s="23" t="n"/>
       <c r="I62" s="21" t="n"/>
       <c r="K62" s="22" t="n"/>
       <c r="L62" s="23" t="n"/>
@@ -5774,13 +5666,13 @@
       <c r="AB62" s="23" t="n"/>
       <c r="AC62" s="21" t="n"/>
       <c r="AE62" s="24" t="n"/>
-      <c r="AF62" s="23" t="n"/>
+      <c r="AF62" s="26" t="n"/>
       <c r="AG62" s="21" t="n"/>
       <c r="AI62" s="22" t="n"/>
       <c r="AJ62" s="23" t="n"/>
       <c r="AK62" s="21" t="n"/>
-      <c r="AM62" s="44" t="n"/>
-      <c r="AN62" s="27" t="n"/>
+      <c r="AM62" s="50" t="n"/>
+      <c r="AN62" s="28" t="n"/>
       <c r="AO62" s="21" t="n"/>
       <c r="AQ62" s="24" t="n"/>
       <c r="AR62" s="26" t="n"/>
@@ -5789,54 +5681,54 @@
       <c r="AV62" s="26" t="n"/>
     </row>
     <row r="63" ht="20.1" customHeight="1">
-      <c r="A63" s="28" t="n"/>
-      <c r="B63" s="29" t="n"/>
-      <c r="C63" s="45" t="n"/>
-      <c r="D63" s="31" t="n"/>
-      <c r="E63" s="28" t="n"/>
-      <c r="F63" s="29" t="n"/>
-      <c r="G63" s="32" t="n"/>
+      <c r="A63" s="29" t="n"/>
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="51" t="n"/>
+      <c r="D63" s="32" t="n"/>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="30" t="n"/>
+      <c r="G63" s="33" t="n"/>
       <c r="H63" s="23" t="n"/>
-      <c r="I63" s="28" t="n"/>
-      <c r="J63" s="29" t="n"/>
-      <c r="K63" s="30" t="n"/>
-      <c r="L63" s="31" t="n"/>
-      <c r="M63" s="28" t="n"/>
-      <c r="N63" s="29" t="n"/>
-      <c r="O63" s="32" t="n"/>
-      <c r="P63" s="31" t="n"/>
-      <c r="Q63" s="28" t="n"/>
-      <c r="R63" s="29" t="n"/>
-      <c r="S63" s="30" t="n"/>
-      <c r="T63" s="33" t="n"/>
-      <c r="U63" s="28" t="n"/>
-      <c r="V63" s="29" t="n"/>
-      <c r="W63" s="32" t="n"/>
-      <c r="X63" s="33" t="n"/>
-      <c r="Y63" s="28" t="n"/>
-      <c r="Z63" s="29" t="n"/>
-      <c r="AA63" s="30" t="n"/>
-      <c r="AB63" s="31" t="n"/>
-      <c r="AC63" s="28" t="n"/>
-      <c r="AD63" s="29" t="n"/>
-      <c r="AE63" s="32" t="n"/>
-      <c r="AF63" s="31" t="n"/>
-      <c r="AG63" s="28" t="n"/>
-      <c r="AH63" s="29" t="n"/>
-      <c r="AI63" s="30" t="n"/>
-      <c r="AJ63" s="31" t="n"/>
-      <c r="AK63" s="28" t="n"/>
-      <c r="AL63" s="29" t="n"/>
-      <c r="AM63" s="45" t="n"/>
-      <c r="AN63" s="34" t="n"/>
-      <c r="AO63" s="28" t="n"/>
-      <c r="AP63" s="29" t="n"/>
-      <c r="AQ63" s="32" t="n"/>
-      <c r="AR63" s="33" t="n"/>
-      <c r="AS63" s="28" t="n"/>
-      <c r="AT63" s="29" t="n"/>
-      <c r="AU63" s="32" t="n"/>
-      <c r="AV63" s="33" t="n"/>
+      <c r="I63" s="29" t="n"/>
+      <c r="J63" s="30" t="n"/>
+      <c r="K63" s="31" t="n"/>
+      <c r="L63" s="32" t="n"/>
+      <c r="M63" s="29" t="n"/>
+      <c r="N63" s="30" t="n"/>
+      <c r="O63" s="33" t="n"/>
+      <c r="P63" s="32" t="n"/>
+      <c r="Q63" s="29" t="n"/>
+      <c r="R63" s="30" t="n"/>
+      <c r="S63" s="31" t="n"/>
+      <c r="T63" s="34" t="n"/>
+      <c r="U63" s="29" t="n"/>
+      <c r="V63" s="30" t="n"/>
+      <c r="W63" s="33" t="n"/>
+      <c r="X63" s="34" t="n"/>
+      <c r="Y63" s="29" t="n"/>
+      <c r="Z63" s="30" t="n"/>
+      <c r="AA63" s="31" t="n"/>
+      <c r="AB63" s="32" t="n"/>
+      <c r="AC63" s="29" t="n"/>
+      <c r="AD63" s="30" t="n"/>
+      <c r="AE63" s="33" t="n"/>
+      <c r="AF63" s="34" t="n"/>
+      <c r="AG63" s="29" t="n"/>
+      <c r="AH63" s="30" t="n"/>
+      <c r="AI63" s="31" t="n"/>
+      <c r="AJ63" s="32" t="n"/>
+      <c r="AK63" s="29" t="n"/>
+      <c r="AL63" s="30" t="n"/>
+      <c r="AM63" s="51" t="n"/>
+      <c r="AN63" s="35" t="n"/>
+      <c r="AO63" s="29" t="n"/>
+      <c r="AP63" s="30" t="n"/>
+      <c r="AQ63" s="33" t="n"/>
+      <c r="AR63" s="34" t="n"/>
+      <c r="AS63" s="29" t="n"/>
+      <c r="AT63" s="30" t="n"/>
+      <c r="AU63" s="33" t="n"/>
+      <c r="AV63" s="34" t="n"/>
     </row>
     <row r="64" ht="20.1" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -5848,7 +5740,7 @@
         <v>21</v>
       </c>
       <c r="C64" s="7" t="n"/>
-      <c r="D64" s="18" t="n"/>
+      <c r="D64" s="16" t="n"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5868,7 +5760,7 @@
         <v>21</v>
       </c>
       <c r="K64" s="7" t="n"/>
-      <c r="L64" s="18" t="n"/>
+      <c r="L64" s="16" t="n"/>
       <c r="M64" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -5878,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="O64" s="12" t="n"/>
-      <c r="P64" s="18" t="n"/>
+      <c r="P64" s="16" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -5888,7 +5780,7 @@
         <v>21</v>
       </c>
       <c r="S64" s="7" t="n"/>
-      <c r="T64" s="18" t="n"/>
+      <c r="T64" s="16" t="n"/>
       <c r="U64" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -5898,7 +5790,7 @@
         <v>21</v>
       </c>
       <c r="W64" s="12" t="n"/>
-      <c r="X64" s="50" t="inlineStr">
+      <c r="X64" s="38" t="inlineStr">
         <is>
           <t>2e dim. de Carême</t>
         </is>
@@ -5911,8 +5803,8 @@
       <c r="Z64" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="AA64" s="42" t="n"/>
-      <c r="AB64" s="50" t="inlineStr">
+      <c r="AA64" s="46" t="n"/>
+      <c r="AB64" s="67" t="inlineStr">
         <is>
           <t>Rameaux</t>
         </is>
@@ -5926,7 +5818,7 @@
         <v>21</v>
       </c>
       <c r="AE64" s="12" t="n"/>
-      <c r="AF64" s="18" t="n"/>
+      <c r="AF64" s="16" t="n"/>
       <c r="AG64" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -5936,7 +5828,7 @@
         <v>21</v>
       </c>
       <c r="AI64" s="7" t="n"/>
-      <c r="AJ64" s="18" t="n"/>
+      <c r="AJ64" s="16" t="n"/>
       <c r="AK64" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -5946,7 +5838,7 @@
         <v>21</v>
       </c>
       <c r="AM64" s="7" t="n"/>
-      <c r="AN64" s="18" t="n"/>
+      <c r="AN64" s="16" t="n"/>
       <c r="AO64" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -5956,7 +5848,7 @@
         <v>21</v>
       </c>
       <c r="AQ64" s="12" t="n"/>
-      <c r="AR64" s="18" t="n"/>
+      <c r="AR64" s="16" t="n"/>
       <c r="AS64" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -5966,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="AU64" s="12" t="n"/>
-      <c r="AV64" s="18" t="n"/>
+      <c r="AV64" s="16" t="n"/>
     </row>
     <row r="65" ht="20.1" customHeight="1">
       <c r="A65" s="21" t="n"/>
@@ -5986,10 +5878,14 @@
       <c r="T65" s="26" t="n"/>
       <c r="U65" s="21" t="n"/>
       <c r="W65" s="24" t="n"/>
-      <c r="X65" s="54" t="n"/>
+      <c r="X65" s="68" t="inlineStr">
+        <is>
+          <t>Retraite des prêtres</t>
+        </is>
+      </c>
       <c r="Y65" s="21" t="n"/>
-      <c r="AA65" s="44" t="n"/>
-      <c r="AB65" s="55" t="inlineStr">
+      <c r="AA65" s="50" t="n"/>
+      <c r="AB65" s="69" t="inlineStr">
         <is>
           <t>Semaine Sainte</t>
         </is>
@@ -6011,54 +5907,54 @@
       <c r="AV65" s="26" t="n"/>
     </row>
     <row r="66" ht="20.1" customHeight="1">
-      <c r="A66" s="28" t="n"/>
-      <c r="B66" s="29" t="n"/>
-      <c r="C66" s="30" t="n"/>
-      <c r="D66" s="33" t="n"/>
-      <c r="E66" s="28" t="n"/>
-      <c r="F66" s="29" t="n"/>
-      <c r="G66" s="32" t="n"/>
+      <c r="A66" s="29" t="n"/>
+      <c r="B66" s="30" t="n"/>
+      <c r="C66" s="31" t="n"/>
+      <c r="D66" s="34" t="n"/>
+      <c r="E66" s="29" t="n"/>
+      <c r="F66" s="30" t="n"/>
+      <c r="G66" s="33" t="n"/>
       <c r="H66" s="23" t="n"/>
-      <c r="I66" s="28" t="n"/>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="30" t="n"/>
-      <c r="L66" s="33" t="n"/>
-      <c r="M66" s="28" t="n"/>
-      <c r="N66" s="29" t="n"/>
-      <c r="O66" s="32" t="n"/>
-      <c r="P66" s="33" t="n"/>
-      <c r="Q66" s="28" t="n"/>
-      <c r="R66" s="29" t="n"/>
-      <c r="S66" s="30" t="n"/>
-      <c r="T66" s="33" t="n"/>
-      <c r="U66" s="28" t="n"/>
-      <c r="V66" s="29" t="n"/>
-      <c r="W66" s="32" t="n"/>
+      <c r="I66" s="29" t="n"/>
+      <c r="J66" s="30" t="n"/>
+      <c r="K66" s="31" t="n"/>
+      <c r="L66" s="34" t="n"/>
+      <c r="M66" s="29" t="n"/>
+      <c r="N66" s="30" t="n"/>
+      <c r="O66" s="33" t="n"/>
+      <c r="P66" s="34" t="n"/>
+      <c r="Q66" s="29" t="n"/>
+      <c r="R66" s="30" t="n"/>
+      <c r="S66" s="31" t="n"/>
+      <c r="T66" s="34" t="n"/>
+      <c r="U66" s="29" t="n"/>
+      <c r="V66" s="30" t="n"/>
+      <c r="W66" s="33" t="n"/>
       <c r="X66" s="23" t="n"/>
-      <c r="Y66" s="28" t="n"/>
-      <c r="Z66" s="29" t="n"/>
-      <c r="AA66" s="45" t="n"/>
+      <c r="Y66" s="29" t="n"/>
+      <c r="Z66" s="30" t="n"/>
+      <c r="AA66" s="51" t="n"/>
       <c r="AB66" s="23" t="n"/>
-      <c r="AC66" s="28" t="n"/>
-      <c r="AD66" s="29" t="n"/>
-      <c r="AE66" s="32" t="n"/>
-      <c r="AF66" s="33" t="n"/>
-      <c r="AG66" s="28" t="n"/>
-      <c r="AH66" s="29" t="n"/>
-      <c r="AI66" s="30" t="n"/>
-      <c r="AJ66" s="33" t="n"/>
-      <c r="AK66" s="28" t="n"/>
-      <c r="AL66" s="29" t="n"/>
-      <c r="AM66" s="30" t="n"/>
-      <c r="AN66" s="33" t="n"/>
-      <c r="AO66" s="28" t="n"/>
-      <c r="AP66" s="29" t="n"/>
-      <c r="AQ66" s="32" t="n"/>
-      <c r="AR66" s="33" t="n"/>
-      <c r="AS66" s="28" t="n"/>
-      <c r="AT66" s="29" t="n"/>
-      <c r="AU66" s="32" t="n"/>
-      <c r="AV66" s="33" t="n"/>
+      <c r="AC66" s="29" t="n"/>
+      <c r="AD66" s="30" t="n"/>
+      <c r="AE66" s="33" t="n"/>
+      <c r="AF66" s="34" t="n"/>
+      <c r="AG66" s="29" t="n"/>
+      <c r="AH66" s="30" t="n"/>
+      <c r="AI66" s="31" t="n"/>
+      <c r="AJ66" s="34" t="n"/>
+      <c r="AK66" s="29" t="n"/>
+      <c r="AL66" s="30" t="n"/>
+      <c r="AM66" s="31" t="n"/>
+      <c r="AN66" s="34" t="n"/>
+      <c r="AO66" s="29" t="n"/>
+      <c r="AP66" s="30" t="n"/>
+      <c r="AQ66" s="33" t="n"/>
+      <c r="AR66" s="34" t="n"/>
+      <c r="AS66" s="29" t="n"/>
+      <c r="AT66" s="30" t="n"/>
+      <c r="AU66" s="33" t="n"/>
+      <c r="AV66" s="34" t="n"/>
     </row>
     <row r="67" ht="20.1" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -6070,7 +5966,7 @@
         <v>22</v>
       </c>
       <c r="C67" s="7" t="n"/>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Rentrée District CCN + Kion</t>
         </is>
@@ -6093,8 +5989,8 @@
       <c r="J67" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="K67" s="42" t="n"/>
-      <c r="L67" s="19" t="inlineStr">
+      <c r="K67" s="46" t="n"/>
+      <c r="L67" s="53" t="inlineStr">
         <is>
           <t>Christ Roi</t>
         </is>
@@ -6108,11 +6004,7 @@
         <v>22</v>
       </c>
       <c r="O67" s="12" t="n"/>
-      <c r="P67" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="P67" s="16" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6122,7 +6014,7 @@
         <v>22</v>
       </c>
       <c r="S67" s="7" t="n"/>
-      <c r="T67" s="18" t="n"/>
+      <c r="T67" s="16" t="n"/>
       <c r="U67" s="14" t="inlineStr">
         <is>
           <t>L</t>
@@ -6152,7 +6044,7 @@
         <v>22</v>
       </c>
       <c r="AE67" s="12" t="n"/>
-      <c r="AF67" s="18" t="n"/>
+      <c r="AF67" s="16" t="n"/>
       <c r="AG67" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6162,7 +6054,7 @@
         <v>22</v>
       </c>
       <c r="AI67" s="7" t="n"/>
-      <c r="AJ67" s="17" t="inlineStr">
+      <c r="AJ67" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -6176,11 +6068,7 @@
         <v>22</v>
       </c>
       <c r="AM67" s="7" t="n"/>
-      <c r="AN67" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AN67" s="16" t="n"/>
       <c r="AO67" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6190,7 +6078,7 @@
         <v>22</v>
       </c>
       <c r="AQ67" s="12" t="n"/>
-      <c r="AR67" s="18" t="n"/>
+      <c r="AR67" s="16" t="n"/>
       <c r="AS67" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6210,11 +6098,11 @@
       <c r="G68" s="24" t="n"/>
       <c r="H68" s="23" t="n"/>
       <c r="I68" s="21" t="n"/>
-      <c r="K68" s="44" t="n"/>
+      <c r="K68" s="50" t="n"/>
       <c r="L68" s="23" t="n"/>
       <c r="M68" s="21" t="n"/>
       <c r="O68" s="24" t="n"/>
-      <c r="P68" s="23" t="n"/>
+      <c r="P68" s="26" t="n"/>
       <c r="Q68" s="21" t="n"/>
       <c r="S68" s="22" t="n"/>
       <c r="T68" s="26" t="n"/>
@@ -6232,67 +6120,63 @@
       <c r="AJ68" s="23" t="n"/>
       <c r="AK68" s="21" t="n"/>
       <c r="AM68" s="22" t="n"/>
-      <c r="AN68" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AN68" s="26" t="n"/>
       <c r="AO68" s="21" t="n"/>
       <c r="AQ68" s="24" t="n"/>
       <c r="AR68" s="26" t="n"/>
       <c r="AS68" s="21" t="n"/>
       <c r="AU68" s="24" t="n"/>
-      <c r="AV68" s="27" t="n"/>
+      <c r="AV68" s="28" t="n"/>
     </row>
     <row r="69" ht="20.1" customHeight="1">
-      <c r="A69" s="28" t="n"/>
-      <c r="B69" s="29" t="n"/>
-      <c r="C69" s="30" t="n"/>
-      <c r="D69" s="31" t="n"/>
-      <c r="E69" s="28" t="n"/>
-      <c r="F69" s="29" t="n"/>
-      <c r="G69" s="32" t="n"/>
+      <c r="A69" s="29" t="n"/>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="31" t="n"/>
+      <c r="D69" s="32" t="n"/>
+      <c r="E69" s="29" t="n"/>
+      <c r="F69" s="30" t="n"/>
+      <c r="G69" s="33" t="n"/>
       <c r="H69" s="23" t="n"/>
-      <c r="I69" s="28" t="n"/>
-      <c r="J69" s="29" t="n"/>
-      <c r="K69" s="45" t="n"/>
-      <c r="L69" s="31" t="n"/>
-      <c r="M69" s="28" t="n"/>
-      <c r="N69" s="29" t="n"/>
-      <c r="O69" s="32" t="n"/>
-      <c r="P69" s="31" t="n"/>
-      <c r="Q69" s="28" t="n"/>
-      <c r="R69" s="29" t="n"/>
-      <c r="S69" s="30" t="n"/>
-      <c r="T69" s="33" t="n"/>
-      <c r="U69" s="28" t="n"/>
-      <c r="V69" s="29" t="n"/>
-      <c r="W69" s="32" t="n"/>
+      <c r="I69" s="29" t="n"/>
+      <c r="J69" s="30" t="n"/>
+      <c r="K69" s="51" t="n"/>
+      <c r="L69" s="32" t="n"/>
+      <c r="M69" s="29" t="n"/>
+      <c r="N69" s="30" t="n"/>
+      <c r="O69" s="33" t="n"/>
+      <c r="P69" s="34" t="n"/>
+      <c r="Q69" s="29" t="n"/>
+      <c r="R69" s="30" t="n"/>
+      <c r="S69" s="31" t="n"/>
+      <c r="T69" s="34" t="n"/>
+      <c r="U69" s="29" t="n"/>
+      <c r="V69" s="30" t="n"/>
+      <c r="W69" s="33" t="n"/>
       <c r="X69" s="23" t="n"/>
-      <c r="Y69" s="28" t="n"/>
-      <c r="Z69" s="29" t="n"/>
-      <c r="AA69" s="30" t="n"/>
+      <c r="Y69" s="29" t="n"/>
+      <c r="Z69" s="30" t="n"/>
+      <c r="AA69" s="31" t="n"/>
       <c r="AB69" s="23" t="n"/>
-      <c r="AC69" s="28" t="n"/>
-      <c r="AD69" s="29" t="n"/>
-      <c r="AE69" s="32" t="n"/>
-      <c r="AF69" s="33" t="n"/>
-      <c r="AG69" s="28" t="n"/>
-      <c r="AH69" s="29" t="n"/>
-      <c r="AI69" s="30" t="n"/>
-      <c r="AJ69" s="31" t="n"/>
-      <c r="AK69" s="28" t="n"/>
-      <c r="AL69" s="29" t="n"/>
-      <c r="AM69" s="30" t="n"/>
-      <c r="AN69" s="33" t="n"/>
-      <c r="AO69" s="28" t="n"/>
-      <c r="AP69" s="29" t="n"/>
-      <c r="AQ69" s="32" t="n"/>
-      <c r="AR69" s="33" t="n"/>
-      <c r="AS69" s="28" t="n"/>
-      <c r="AT69" s="29" t="n"/>
-      <c r="AU69" s="32" t="n"/>
-      <c r="AV69" s="34" t="n"/>
+      <c r="AC69" s="29" t="n"/>
+      <c r="AD69" s="30" t="n"/>
+      <c r="AE69" s="33" t="n"/>
+      <c r="AF69" s="34" t="n"/>
+      <c r="AG69" s="29" t="n"/>
+      <c r="AH69" s="30" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="32" t="n"/>
+      <c r="AK69" s="29" t="n"/>
+      <c r="AL69" s="30" t="n"/>
+      <c r="AM69" s="31" t="n"/>
+      <c r="AN69" s="34" t="n"/>
+      <c r="AO69" s="29" t="n"/>
+      <c r="AP69" s="30" t="n"/>
+      <c r="AQ69" s="33" t="n"/>
+      <c r="AR69" s="34" t="n"/>
+      <c r="AS69" s="29" t="n"/>
+      <c r="AT69" s="30" t="n"/>
+      <c r="AU69" s="33" t="n"/>
+      <c r="AV69" s="35" t="n"/>
     </row>
     <row r="70" ht="20.1" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -6304,7 +6188,7 @@
         <v>23</v>
       </c>
       <c r="C70" s="7" t="n"/>
-      <c r="D70" s="18" t="n"/>
+      <c r="D70" s="16" t="n"/>
       <c r="E70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6324,7 +6208,7 @@
         <v>23</v>
       </c>
       <c r="K70" s="7" t="n"/>
-      <c r="L70" s="18" t="n"/>
+      <c r="L70" s="16" t="n"/>
       <c r="M70" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6334,7 +6218,7 @@
         <v>23</v>
       </c>
       <c r="O70" s="12" t="n"/>
-      <c r="P70" s="18" t="n"/>
+      <c r="P70" s="16" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6344,7 +6228,7 @@
         <v>23</v>
       </c>
       <c r="S70" s="7" t="n"/>
-      <c r="T70" s="17" t="inlineStr">
+      <c r="T70" s="48" t="inlineStr">
         <is>
           <t>CMP</t>
         </is>
@@ -6368,7 +6252,7 @@
         <v>23</v>
       </c>
       <c r="AA70" s="7" t="n"/>
-      <c r="AB70" s="31" t="n"/>
+      <c r="AB70" s="32" t="n"/>
       <c r="AC70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6378,7 +6262,7 @@
         <v>23</v>
       </c>
       <c r="AE70" s="12" t="n"/>
-      <c r="AF70" s="18" t="n"/>
+      <c r="AF70" s="16" t="n"/>
       <c r="AG70" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6387,7 +6271,7 @@
       <c r="AH70" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="AI70" s="42" t="n"/>
+      <c r="AI70" s="46" t="n"/>
       <c r="AJ70" s="20" t="n"/>
       <c r="AK70" s="5" t="inlineStr">
         <is>
@@ -6398,7 +6282,7 @@
         <v>23</v>
       </c>
       <c r="AM70" s="7" t="n"/>
-      <c r="AN70" s="18" t="n"/>
+      <c r="AN70" s="16" t="n"/>
       <c r="AO70" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6408,7 +6292,7 @@
         <v>23</v>
       </c>
       <c r="AQ70" s="12" t="n"/>
-      <c r="AR70" s="18" t="n"/>
+      <c r="AR70" s="16" t="n"/>
       <c r="AS70" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -6418,7 +6302,7 @@
         <v>23</v>
       </c>
       <c r="AU70" s="12" t="n"/>
-      <c r="AV70" s="18" t="n"/>
+      <c r="AV70" s="16" t="n"/>
     </row>
     <row r="71" ht="20.1" customHeight="1">
       <c r="A71" s="21" t="n"/>
@@ -6426,7 +6310,7 @@
       <c r="D71" s="26" t="n"/>
       <c r="E71" s="21" t="n"/>
       <c r="G71" s="24" t="n"/>
-      <c r="H71" s="31" t="n"/>
+      <c r="H71" s="32" t="n"/>
       <c r="I71" s="21" t="n"/>
       <c r="K71" s="22" t="n"/>
       <c r="L71" s="26" t="n"/>
@@ -6438,10 +6322,10 @@
       <c r="T71" s="23" t="n"/>
       <c r="U71" s="21" t="n"/>
       <c r="W71" s="24" t="n"/>
-      <c r="X71" s="31" t="n"/>
+      <c r="X71" s="23" t="n"/>
       <c r="Y71" s="21" t="n"/>
       <c r="AA71" s="22" t="n"/>
-      <c r="AB71" s="50" t="inlineStr">
+      <c r="AB71" s="67" t="inlineStr">
         <is>
           <t>Messe Chrismale</t>
         </is>
@@ -6450,8 +6334,8 @@
       <c r="AE71" s="24" t="n"/>
       <c r="AF71" s="26" t="n"/>
       <c r="AG71" s="21" t="n"/>
-      <c r="AI71" s="44" t="n"/>
-      <c r="AJ71" s="27" t="n"/>
+      <c r="AI71" s="50" t="n"/>
+      <c r="AJ71" s="28" t="n"/>
       <c r="AK71" s="21" t="n"/>
       <c r="AM71" s="22" t="n"/>
       <c r="AN71" s="26" t="n"/>
@@ -6463,66 +6347,62 @@
       <c r="AV71" s="26" t="n"/>
     </row>
     <row r="72" ht="20.1" customHeight="1">
-      <c r="A72" s="28" t="n"/>
-      <c r="B72" s="29" t="n"/>
-      <c r="C72" s="30" t="n"/>
-      <c r="D72" s="33" t="n"/>
-      <c r="E72" s="28" t="n"/>
-      <c r="F72" s="29" t="n"/>
-      <c r="G72" s="32" t="n"/>
-      <c r="H72" s="40" t="inlineStr">
+      <c r="A72" s="29" t="n"/>
+      <c r="B72" s="30" t="n"/>
+      <c r="C72" s="31" t="n"/>
+      <c r="D72" s="34" t="n"/>
+      <c r="E72" s="29" t="n"/>
+      <c r="F72" s="30" t="n"/>
+      <c r="G72" s="33" t="n"/>
+      <c r="H72" s="55" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
       </c>
-      <c r="I72" s="28" t="n"/>
-      <c r="J72" s="29" t="n"/>
-      <c r="K72" s="30" t="n"/>
-      <c r="L72" s="33" t="n"/>
-      <c r="M72" s="28" t="n"/>
-      <c r="N72" s="29" t="n"/>
-      <c r="O72" s="32" t="n"/>
-      <c r="P72" s="33" t="n"/>
-      <c r="Q72" s="28" t="n"/>
-      <c r="R72" s="29" t="n"/>
-      <c r="S72" s="30" t="n"/>
-      <c r="T72" s="31" t="n"/>
-      <c r="U72" s="28" t="n"/>
-      <c r="V72" s="29" t="n"/>
-      <c r="W72" s="32" t="n"/>
-      <c r="X72" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="Y72" s="28" t="n"/>
-      <c r="Z72" s="29" t="n"/>
-      <c r="AA72" s="30" t="n"/>
-      <c r="AB72" s="39" t="inlineStr">
+      <c r="I72" s="29" t="n"/>
+      <c r="J72" s="30" t="n"/>
+      <c r="K72" s="31" t="n"/>
+      <c r="L72" s="34" t="n"/>
+      <c r="M72" s="29" t="n"/>
+      <c r="N72" s="30" t="n"/>
+      <c r="O72" s="33" t="n"/>
+      <c r="P72" s="34" t="n"/>
+      <c r="Q72" s="29" t="n"/>
+      <c r="R72" s="30" t="n"/>
+      <c r="S72" s="31" t="n"/>
+      <c r="T72" s="32" t="n"/>
+      <c r="U72" s="29" t="n"/>
+      <c r="V72" s="30" t="n"/>
+      <c r="W72" s="33" t="n"/>
+      <c r="X72" s="23" t="n"/>
+      <c r="Y72" s="29" t="n"/>
+      <c r="Z72" s="30" t="n"/>
+      <c r="AA72" s="31" t="n"/>
+      <c r="AB72" s="54" t="inlineStr">
         <is>
           <t>Rencontre des prêtres</t>
         </is>
       </c>
-      <c r="AC72" s="28" t="n"/>
-      <c r="AD72" s="29" t="n"/>
-      <c r="AE72" s="32" t="n"/>
-      <c r="AF72" s="33" t="n"/>
-      <c r="AG72" s="28" t="n"/>
-      <c r="AH72" s="29" t="n"/>
-      <c r="AI72" s="45" t="n"/>
-      <c r="AJ72" s="34" t="n"/>
-      <c r="AK72" s="28" t="n"/>
-      <c r="AL72" s="29" t="n"/>
-      <c r="AM72" s="30" t="n"/>
-      <c r="AN72" s="33" t="n"/>
-      <c r="AO72" s="28" t="n"/>
-      <c r="AP72" s="29" t="n"/>
-      <c r="AQ72" s="32" t="n"/>
-      <c r="AR72" s="33" t="n"/>
-      <c r="AS72" s="28" t="n"/>
-      <c r="AT72" s="29" t="n"/>
-      <c r="AU72" s="32" t="n"/>
-      <c r="AV72" s="33" t="n"/>
+      <c r="AC72" s="29" t="n"/>
+      <c r="AD72" s="30" t="n"/>
+      <c r="AE72" s="33" t="n"/>
+      <c r="AF72" s="34" t="n"/>
+      <c r="AG72" s="29" t="n"/>
+      <c r="AH72" s="30" t="n"/>
+      <c r="AI72" s="51" t="n"/>
+      <c r="AJ72" s="35" t="n"/>
+      <c r="AK72" s="29" t="n"/>
+      <c r="AL72" s="30" t="n"/>
+      <c r="AM72" s="31" t="n"/>
+      <c r="AN72" s="34" t="n"/>
+      <c r="AO72" s="29" t="n"/>
+      <c r="AP72" s="30" t="n"/>
+      <c r="AQ72" s="33" t="n"/>
+      <c r="AR72" s="34" t="n"/>
+      <c r="AS72" s="29" t="n"/>
+      <c r="AT72" s="30" t="n"/>
+      <c r="AU72" s="33" t="n"/>
+      <c r="AV72" s="34" t="n"/>
     </row>
     <row r="73" ht="20.1" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -6534,7 +6414,7 @@
         <v>24</v>
       </c>
       <c r="C73" s="7" t="n"/>
-      <c r="D73" s="18" t="n"/>
+      <c r="D73" s="16" t="n"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6544,7 +6424,7 @@
         <v>24</v>
       </c>
       <c r="G73" s="12" t="n"/>
-      <c r="H73" s="41" t="inlineStr">
+      <c r="H73" s="70" t="inlineStr">
         <is>
           <t>Père Pascal en Côte d'Ivoire</t>
         </is>
@@ -6558,11 +6438,7 @@
         <v>24</v>
       </c>
       <c r="K73" s="7" t="n"/>
-      <c r="L73" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="L73" s="16" t="n"/>
       <c r="M73" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6572,7 +6448,7 @@
         <v>24</v>
       </c>
       <c r="O73" s="12" t="n"/>
-      <c r="P73" s="18" t="n"/>
+      <c r="P73" s="16" t="n"/>
       <c r="Q73" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6581,7 +6457,7 @@
       <c r="R73" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S73" s="42" t="n"/>
+      <c r="S73" s="46" t="n"/>
       <c r="T73" s="20" t="n"/>
       <c r="U73" s="14" t="inlineStr">
         <is>
@@ -6592,11 +6468,7 @@
         <v>24</v>
       </c>
       <c r="W73" s="12" t="n"/>
-      <c r="X73" s="54" t="inlineStr">
-        <is>
-          <t>Retraite des prêtres</t>
-        </is>
-      </c>
+      <c r="X73" s="23" t="n"/>
       <c r="Y73" s="14" t="inlineStr">
         <is>
           <t>Me</t>
@@ -6606,7 +6478,7 @@
         <v>24</v>
       </c>
       <c r="AA73" s="7" t="n"/>
-      <c r="AB73" s="47" t="n"/>
+      <c r="AB73" s="71" t="n"/>
       <c r="AC73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6616,7 +6488,7 @@
         <v>24</v>
       </c>
       <c r="AE73" s="12" t="n"/>
-      <c r="AF73" s="17" t="inlineStr">
+      <c r="AF73" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -6630,7 +6502,7 @@
         <v>24</v>
       </c>
       <c r="AI73" s="7" t="n"/>
-      <c r="AJ73" s="18" t="n"/>
+      <c r="AJ73" s="16" t="n"/>
       <c r="AK73" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -6640,7 +6512,7 @@
         <v>24</v>
       </c>
       <c r="AM73" s="7" t="n"/>
-      <c r="AN73" s="18" t="n"/>
+      <c r="AN73" s="16" t="n"/>
       <c r="AO73" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -6650,7 +6522,7 @@
         <v>24</v>
       </c>
       <c r="AQ73" s="12" t="n"/>
-      <c r="AR73" s="18" t="n"/>
+      <c r="AR73" s="16" t="n"/>
       <c r="AS73" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -6660,7 +6532,7 @@
         <v>24</v>
       </c>
       <c r="AU73" s="12" t="n"/>
-      <c r="AV73" s="18" t="n"/>
+      <c r="AV73" s="16" t="n"/>
     </row>
     <row r="74" ht="20.1" customHeight="1">
       <c r="A74" s="21" t="n"/>
@@ -6671,17 +6543,13 @@
       <c r="H74" s="23" t="n"/>
       <c r="I74" s="21" t="n"/>
       <c r="K74" s="22" t="n"/>
-      <c r="L74" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="L74" s="26" t="n"/>
       <c r="M74" s="21" t="n"/>
       <c r="O74" s="24" t="n"/>
       <c r="P74" s="26" t="n"/>
       <c r="Q74" s="21" t="n"/>
-      <c r="S74" s="44" t="n"/>
-      <c r="T74" s="27" t="n"/>
+      <c r="S74" s="50" t="n"/>
+      <c r="T74" s="28" t="n"/>
       <c r="U74" s="21" t="n"/>
       <c r="W74" s="24" t="n"/>
       <c r="X74" s="23" t="n"/>
@@ -6705,54 +6573,54 @@
       <c r="AV74" s="26" t="n"/>
     </row>
     <row r="75" ht="20.1" customHeight="1">
-      <c r="A75" s="28" t="n"/>
-      <c r="B75" s="29" t="n"/>
-      <c r="C75" s="30" t="n"/>
-      <c r="D75" s="33" t="n"/>
-      <c r="E75" s="28" t="n"/>
-      <c r="F75" s="29" t="n"/>
-      <c r="G75" s="32" t="n"/>
+      <c r="A75" s="29" t="n"/>
+      <c r="B75" s="30" t="n"/>
+      <c r="C75" s="31" t="n"/>
+      <c r="D75" s="34" t="n"/>
+      <c r="E75" s="29" t="n"/>
+      <c r="F75" s="30" t="n"/>
+      <c r="G75" s="33" t="n"/>
       <c r="H75" s="23" t="n"/>
-      <c r="I75" s="28" t="n"/>
-      <c r="J75" s="29" t="n"/>
-      <c r="K75" s="30" t="n"/>
-      <c r="L75" s="33" t="n"/>
-      <c r="M75" s="28" t="n"/>
-      <c r="N75" s="29" t="n"/>
-      <c r="O75" s="32" t="n"/>
-      <c r="P75" s="33" t="n"/>
-      <c r="Q75" s="28" t="n"/>
-      <c r="R75" s="29" t="n"/>
-      <c r="S75" s="45" t="n"/>
-      <c r="T75" s="34" t="n"/>
-      <c r="U75" s="28" t="n"/>
-      <c r="V75" s="29" t="n"/>
-      <c r="W75" s="32" t="n"/>
+      <c r="I75" s="29" t="n"/>
+      <c r="J75" s="30" t="n"/>
+      <c r="K75" s="31" t="n"/>
+      <c r="L75" s="34" t="n"/>
+      <c r="M75" s="29" t="n"/>
+      <c r="N75" s="30" t="n"/>
+      <c r="O75" s="33" t="n"/>
+      <c r="P75" s="34" t="n"/>
+      <c r="Q75" s="29" t="n"/>
+      <c r="R75" s="30" t="n"/>
+      <c r="S75" s="51" t="n"/>
+      <c r="T75" s="35" t="n"/>
+      <c r="U75" s="29" t="n"/>
+      <c r="V75" s="30" t="n"/>
+      <c r="W75" s="33" t="n"/>
       <c r="X75" s="23" t="n"/>
-      <c r="Y75" s="28" t="n"/>
-      <c r="Z75" s="29" t="n"/>
-      <c r="AA75" s="30" t="n"/>
+      <c r="Y75" s="29" t="n"/>
+      <c r="Z75" s="30" t="n"/>
+      <c r="AA75" s="31" t="n"/>
       <c r="AB75" s="23" t="n"/>
-      <c r="AC75" s="28" t="n"/>
-      <c r="AD75" s="29" t="n"/>
-      <c r="AE75" s="32" t="n"/>
-      <c r="AF75" s="31" t="n"/>
-      <c r="AG75" s="28" t="n"/>
-      <c r="AH75" s="29" t="n"/>
-      <c r="AI75" s="30" t="n"/>
-      <c r="AJ75" s="33" t="n"/>
-      <c r="AK75" s="28" t="n"/>
-      <c r="AL75" s="29" t="n"/>
-      <c r="AM75" s="30" t="n"/>
-      <c r="AN75" s="33" t="n"/>
-      <c r="AO75" s="28" t="n"/>
-      <c r="AP75" s="29" t="n"/>
-      <c r="AQ75" s="32" t="n"/>
-      <c r="AR75" s="33" t="n"/>
-      <c r="AS75" s="28" t="n"/>
-      <c r="AT75" s="29" t="n"/>
-      <c r="AU75" s="32" t="n"/>
-      <c r="AV75" s="33" t="n"/>
+      <c r="AC75" s="29" t="n"/>
+      <c r="AD75" s="30" t="n"/>
+      <c r="AE75" s="33" t="n"/>
+      <c r="AF75" s="32" t="n"/>
+      <c r="AG75" s="29" t="n"/>
+      <c r="AH75" s="30" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="34" t="n"/>
+      <c r="AK75" s="29" t="n"/>
+      <c r="AL75" s="30" t="n"/>
+      <c r="AM75" s="31" t="n"/>
+      <c r="AN75" s="34" t="n"/>
+      <c r="AO75" s="29" t="n"/>
+      <c r="AP75" s="30" t="n"/>
+      <c r="AQ75" s="33" t="n"/>
+      <c r="AR75" s="34" t="n"/>
+      <c r="AS75" s="29" t="n"/>
+      <c r="AT75" s="30" t="n"/>
+      <c r="AU75" s="33" t="n"/>
+      <c r="AV75" s="34" t="n"/>
     </row>
     <row r="76" ht="20.1" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -6764,7 +6632,7 @@
         <v>25</v>
       </c>
       <c r="C76" s="7" t="n"/>
-      <c r="D76" s="25" t="n"/>
+      <c r="D76" s="72" t="n"/>
       <c r="E76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6784,7 +6652,7 @@
         <v>25</v>
       </c>
       <c r="K76" s="7" t="n"/>
-      <c r="L76" s="18" t="n"/>
+      <c r="L76" s="16" t="n"/>
       <c r="M76" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6794,7 +6662,7 @@
         <v>25</v>
       </c>
       <c r="O76" s="12" t="n"/>
-      <c r="P76" s="19" t="inlineStr">
+      <c r="P76" s="53" t="inlineStr">
         <is>
           <t>Noël</t>
         </is>
@@ -6808,7 +6676,7 @@
         <v>25</v>
       </c>
       <c r="S76" s="7" t="n"/>
-      <c r="T76" s="18" t="n"/>
+      <c r="T76" s="16" t="n"/>
       <c r="U76" s="14" t="inlineStr">
         <is>
           <t>J</t>
@@ -6848,11 +6716,7 @@
         <v>25</v>
       </c>
       <c r="AI76" s="7" t="n"/>
-      <c r="AJ76" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AJ76" s="16" t="n"/>
       <c r="AK76" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -6862,7 +6726,7 @@
         <v>25</v>
       </c>
       <c r="AM76" s="7" t="n"/>
-      <c r="AN76" s="18" t="n"/>
+      <c r="AN76" s="16" t="n"/>
       <c r="AO76" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -6882,7 +6746,7 @@
         <v>25</v>
       </c>
       <c r="AU76" s="12" t="n"/>
-      <c r="AV76" s="18" t="n"/>
+      <c r="AV76" s="16" t="n"/>
     </row>
     <row r="77" ht="20.1" customHeight="1">
       <c r="A77" s="21" t="n"/>
@@ -6905,80 +6769,76 @@
       <c r="X77" s="23" t="n"/>
       <c r="Y77" s="21" t="n"/>
       <c r="AA77" s="22" t="n"/>
-      <c r="AB77" s="31" t="n"/>
+      <c r="AB77" s="32" t="n"/>
       <c r="AC77" s="21" t="n"/>
       <c r="AE77" s="24" t="n"/>
-      <c r="AF77" s="27" t="n"/>
+      <c r="AF77" s="28" t="n"/>
       <c r="AG77" s="21" t="n"/>
       <c r="AI77" s="22" t="n"/>
-      <c r="AJ77" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AJ77" s="26" t="n"/>
       <c r="AK77" s="21" t="n"/>
       <c r="AM77" s="22" t="n"/>
       <c r="AN77" s="26" t="n"/>
       <c r="AO77" s="21" t="n"/>
       <c r="AQ77" s="24" t="n"/>
-      <c r="AR77" s="27" t="n"/>
+      <c r="AR77" s="28" t="n"/>
       <c r="AS77" s="21" t="n"/>
       <c r="AU77" s="24" t="n"/>
       <c r="AV77" s="26" t="n"/>
     </row>
     <row r="78" ht="20.1" customHeight="1">
-      <c r="A78" s="28" t="n"/>
-      <c r="B78" s="29" t="n"/>
-      <c r="C78" s="30" t="n"/>
+      <c r="A78" s="29" t="n"/>
+      <c r="B78" s="30" t="n"/>
+      <c r="C78" s="31" t="n"/>
       <c r="D78" s="23" t="n"/>
-      <c r="E78" s="28" t="n"/>
-      <c r="F78" s="29" t="n"/>
-      <c r="G78" s="32" t="n"/>
+      <c r="E78" s="29" t="n"/>
+      <c r="F78" s="30" t="n"/>
+      <c r="G78" s="33" t="n"/>
       <c r="H78" s="23" t="n"/>
-      <c r="I78" s="28" t="n"/>
-      <c r="J78" s="29" t="n"/>
-      <c r="K78" s="30" t="n"/>
-      <c r="L78" s="33" t="n"/>
-      <c r="M78" s="28" t="n"/>
-      <c r="N78" s="29" t="n"/>
-      <c r="O78" s="32" t="n"/>
-      <c r="P78" s="31" t="n"/>
-      <c r="Q78" s="28" t="n"/>
-      <c r="R78" s="29" t="n"/>
-      <c r="S78" s="30" t="n"/>
-      <c r="T78" s="33" t="n"/>
-      <c r="U78" s="28" t="n"/>
-      <c r="V78" s="29" t="n"/>
-      <c r="W78" s="32" t="n"/>
+      <c r="I78" s="29" t="n"/>
+      <c r="J78" s="30" t="n"/>
+      <c r="K78" s="31" t="n"/>
+      <c r="L78" s="34" t="n"/>
+      <c r="M78" s="29" t="n"/>
+      <c r="N78" s="30" t="n"/>
+      <c r="O78" s="33" t="n"/>
+      <c r="P78" s="32" t="n"/>
+      <c r="Q78" s="29" t="n"/>
+      <c r="R78" s="30" t="n"/>
+      <c r="S78" s="31" t="n"/>
+      <c r="T78" s="34" t="n"/>
+      <c r="U78" s="29" t="n"/>
+      <c r="V78" s="30" t="n"/>
+      <c r="W78" s="33" t="n"/>
       <c r="X78" s="23" t="n"/>
-      <c r="Y78" s="28" t="n"/>
-      <c r="Z78" s="29" t="n"/>
-      <c r="AA78" s="30" t="n"/>
-      <c r="AB78" s="50" t="inlineStr">
+      <c r="Y78" s="29" t="n"/>
+      <c r="Z78" s="30" t="n"/>
+      <c r="AA78" s="31" t="n"/>
+      <c r="AB78" s="67" t="inlineStr">
         <is>
           <t>Jeudi saint</t>
         </is>
       </c>
-      <c r="AC78" s="28" t="n"/>
-      <c r="AD78" s="29" t="n"/>
-      <c r="AE78" s="32" t="n"/>
-      <c r="AF78" s="34" t="n"/>
-      <c r="AG78" s="28" t="n"/>
-      <c r="AH78" s="29" t="n"/>
-      <c r="AI78" s="30" t="n"/>
-      <c r="AJ78" s="33" t="n"/>
-      <c r="AK78" s="28" t="n"/>
-      <c r="AL78" s="29" t="n"/>
-      <c r="AM78" s="30" t="n"/>
-      <c r="AN78" s="33" t="n"/>
-      <c r="AO78" s="28" t="n"/>
-      <c r="AP78" s="29" t="n"/>
-      <c r="AQ78" s="32" t="n"/>
-      <c r="AR78" s="34" t="n"/>
-      <c r="AS78" s="28" t="n"/>
-      <c r="AT78" s="29" t="n"/>
-      <c r="AU78" s="32" t="n"/>
-      <c r="AV78" s="33" t="n"/>
+      <c r="AC78" s="29" t="n"/>
+      <c r="AD78" s="30" t="n"/>
+      <c r="AE78" s="33" t="n"/>
+      <c r="AF78" s="35" t="n"/>
+      <c r="AG78" s="29" t="n"/>
+      <c r="AH78" s="30" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="34" t="n"/>
+      <c r="AK78" s="29" t="n"/>
+      <c r="AL78" s="30" t="n"/>
+      <c r="AM78" s="31" t="n"/>
+      <c r="AN78" s="34" t="n"/>
+      <c r="AO78" s="29" t="n"/>
+      <c r="AP78" s="30" t="n"/>
+      <c r="AQ78" s="33" t="n"/>
+      <c r="AR78" s="35" t="n"/>
+      <c r="AS78" s="29" t="n"/>
+      <c r="AT78" s="30" t="n"/>
+      <c r="AU78" s="33" t="n"/>
+      <c r="AV78" s="34" t="n"/>
     </row>
     <row r="79" ht="20.1" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -6990,7 +6850,7 @@
         <v>26</v>
       </c>
       <c r="C79" s="7" t="n"/>
-      <c r="D79" s="31" t="n"/>
+      <c r="D79" s="32" t="n"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7010,7 +6870,7 @@
         <v>26</v>
       </c>
       <c r="K79" s="7" t="n"/>
-      <c r="L79" s="18" t="n"/>
+      <c r="L79" s="16" t="n"/>
       <c r="M79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7020,7 +6880,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="12" t="n"/>
-      <c r="P79" s="17" t="inlineStr">
+      <c r="P79" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7034,11 +6894,7 @@
         <v>26</v>
       </c>
       <c r="S79" s="7" t="n"/>
-      <c r="T79" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="T79" s="16" t="n"/>
       <c r="U79" s="14" t="inlineStr">
         <is>
           <t>V</t>
@@ -7058,7 +6914,7 @@
         <v>26</v>
       </c>
       <c r="AA79" s="7" t="n"/>
-      <c r="AB79" s="50" t="inlineStr">
+      <c r="AB79" s="67" t="inlineStr">
         <is>
           <t>Vendredi saint</t>
         </is>
@@ -7072,7 +6928,7 @@
         <v>26</v>
       </c>
       <c r="AE79" s="12" t="n"/>
-      <c r="AF79" s="18" t="n"/>
+      <c r="AF79" s="16" t="n"/>
       <c r="AG79" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7082,7 +6938,7 @@
         <v>26</v>
       </c>
       <c r="AI79" s="7" t="n"/>
-      <c r="AJ79" s="18" t="n"/>
+      <c r="AJ79" s="16" t="n"/>
       <c r="AK79" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7092,7 +6948,7 @@
         <v>26</v>
       </c>
       <c r="AM79" s="7" t="n"/>
-      <c r="AN79" s="17" t="inlineStr">
+      <c r="AN79" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7106,7 +6962,7 @@
         <v>26</v>
       </c>
       <c r="AQ79" s="12" t="n"/>
-      <c r="AR79" s="18" t="n"/>
+      <c r="AR79" s="16" t="n"/>
       <c r="AS79" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7116,12 +6972,12 @@
         <v>26</v>
       </c>
       <c r="AU79" s="12" t="n"/>
-      <c r="AV79" s="18" t="n"/>
+      <c r="AV79" s="16" t="n"/>
     </row>
     <row r="80" ht="20.1" customHeight="1">
       <c r="A80" s="21" t="n"/>
       <c r="C80" s="22" t="n"/>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7137,17 +6993,13 @@
       <c r="P80" s="23" t="n"/>
       <c r="Q80" s="21" t="n"/>
       <c r="S80" s="22" t="n"/>
-      <c r="T80" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="T80" s="26" t="n"/>
       <c r="U80" s="21" t="n"/>
       <c r="W80" s="24" t="n"/>
       <c r="X80" s="23" t="n"/>
       <c r="Y80" s="21" t="n"/>
       <c r="AA80" s="22" t="n"/>
-      <c r="AB80" s="47" t="n"/>
+      <c r="AB80" s="71" t="n"/>
       <c r="AC80" s="21" t="n"/>
       <c r="AE80" s="24" t="n"/>
       <c r="AF80" s="26" t="n"/>
@@ -7165,58 +7017,58 @@
       <c r="AV80" s="26" t="n"/>
     </row>
     <row r="81" ht="20.1" customHeight="1">
-      <c r="A81" s="28" t="n"/>
-      <c r="B81" s="29" t="n"/>
-      <c r="C81" s="30" t="n"/>
-      <c r="D81" s="40" t="inlineStr">
+      <c r="A81" s="29" t="n"/>
+      <c r="B81" s="30" t="n"/>
+      <c r="C81" s="31" t="n"/>
+      <c r="D81" s="45" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
       </c>
-      <c r="E81" s="28" t="n"/>
-      <c r="F81" s="29" t="n"/>
-      <c r="G81" s="32" t="n"/>
+      <c r="E81" s="29" t="n"/>
+      <c r="F81" s="30" t="n"/>
+      <c r="G81" s="33" t="n"/>
       <c r="H81" s="23" t="n"/>
-      <c r="I81" s="28" t="n"/>
-      <c r="J81" s="29" t="n"/>
-      <c r="K81" s="30" t="n"/>
-      <c r="L81" s="33" t="n"/>
-      <c r="M81" s="28" t="n"/>
-      <c r="N81" s="29" t="n"/>
-      <c r="O81" s="32" t="n"/>
-      <c r="P81" s="31" t="n"/>
-      <c r="Q81" s="28" t="n"/>
-      <c r="R81" s="29" t="n"/>
-      <c r="S81" s="30" t="n"/>
-      <c r="T81" s="33" t="n"/>
-      <c r="U81" s="28" t="n"/>
-      <c r="V81" s="29" t="n"/>
-      <c r="W81" s="32" t="n"/>
-      <c r="X81" s="31" t="n"/>
-      <c r="Y81" s="28" t="n"/>
-      <c r="Z81" s="29" t="n"/>
-      <c r="AA81" s="30" t="n"/>
+      <c r="I81" s="29" t="n"/>
+      <c r="J81" s="30" t="n"/>
+      <c r="K81" s="31" t="n"/>
+      <c r="L81" s="34" t="n"/>
+      <c r="M81" s="29" t="n"/>
+      <c r="N81" s="30" t="n"/>
+      <c r="O81" s="33" t="n"/>
+      <c r="P81" s="32" t="n"/>
+      <c r="Q81" s="29" t="n"/>
+      <c r="R81" s="30" t="n"/>
+      <c r="S81" s="31" t="n"/>
+      <c r="T81" s="34" t="n"/>
+      <c r="U81" s="29" t="n"/>
+      <c r="V81" s="30" t="n"/>
+      <c r="W81" s="33" t="n"/>
+      <c r="X81" s="32" t="n"/>
+      <c r="Y81" s="29" t="n"/>
+      <c r="Z81" s="30" t="n"/>
+      <c r="AA81" s="31" t="n"/>
       <c r="AB81" s="23" t="n"/>
-      <c r="AC81" s="28" t="n"/>
-      <c r="AD81" s="29" t="n"/>
-      <c r="AE81" s="32" t="n"/>
-      <c r="AF81" s="33" t="n"/>
-      <c r="AG81" s="28" t="n"/>
-      <c r="AH81" s="29" t="n"/>
-      <c r="AI81" s="30" t="n"/>
-      <c r="AJ81" s="33" t="n"/>
-      <c r="AK81" s="28" t="n"/>
-      <c r="AL81" s="29" t="n"/>
-      <c r="AM81" s="30" t="n"/>
-      <c r="AN81" s="31" t="n"/>
-      <c r="AO81" s="28" t="n"/>
-      <c r="AP81" s="29" t="n"/>
-      <c r="AQ81" s="32" t="n"/>
-      <c r="AR81" s="33" t="n"/>
-      <c r="AS81" s="28" t="n"/>
-      <c r="AT81" s="29" t="n"/>
-      <c r="AU81" s="32" t="n"/>
-      <c r="AV81" s="33" t="n"/>
+      <c r="AC81" s="29" t="n"/>
+      <c r="AD81" s="30" t="n"/>
+      <c r="AE81" s="33" t="n"/>
+      <c r="AF81" s="34" t="n"/>
+      <c r="AG81" s="29" t="n"/>
+      <c r="AH81" s="30" t="n"/>
+      <c r="AI81" s="31" t="n"/>
+      <c r="AJ81" s="34" t="n"/>
+      <c r="AK81" s="29" t="n"/>
+      <c r="AL81" s="30" t="n"/>
+      <c r="AM81" s="31" t="n"/>
+      <c r="AN81" s="32" t="n"/>
+      <c r="AO81" s="29" t="n"/>
+      <c r="AP81" s="30" t="n"/>
+      <c r="AQ81" s="33" t="n"/>
+      <c r="AR81" s="34" t="n"/>
+      <c r="AS81" s="29" t="n"/>
+      <c r="AT81" s="30" t="n"/>
+      <c r="AU81" s="33" t="n"/>
+      <c r="AV81" s="34" t="n"/>
     </row>
     <row r="82" ht="20.1" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
@@ -7227,10 +7079,10 @@
       <c r="B82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C82" s="42" t="n"/>
-      <c r="D82" s="40" t="inlineStr">
-        <is>
-          <t>Baptême</t>
+      <c r="C82" s="46" t="n"/>
+      <c r="D82" s="73" t="inlineStr">
+        <is>
+          <t>Visite du Pape</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -7252,7 +7104,7 @@
         <v>27</v>
       </c>
       <c r="K82" s="7" t="n"/>
-      <c r="L82" s="35" t="inlineStr">
+      <c r="L82" s="36" t="inlineStr">
         <is>
           <t>Casa</t>
         </is>
@@ -7276,7 +7128,7 @@
         <v>27</v>
       </c>
       <c r="S82" s="7" t="n"/>
-      <c r="T82" s="18" t="n"/>
+      <c r="T82" s="16" t="n"/>
       <c r="U82" s="14" t="inlineStr">
         <is>
           <t>S</t>
@@ -7286,7 +7138,7 @@
         <v>27</v>
       </c>
       <c r="W82" s="12" t="n"/>
-      <c r="X82" s="17" t="inlineStr">
+      <c r="X82" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7300,7 +7152,7 @@
         <v>27</v>
       </c>
       <c r="AA82" s="7" t="n"/>
-      <c r="AB82" s="31" t="n"/>
+      <c r="AB82" s="32" t="n"/>
       <c r="AC82" s="5" t="inlineStr">
         <is>
           <t>Ma</t>
@@ -7310,11 +7162,7 @@
         <v>27</v>
       </c>
       <c r="AE82" s="12" t="n"/>
-      <c r="AF82" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AF82" s="16" t="n"/>
       <c r="AG82" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7324,7 +7172,7 @@
         <v>27</v>
       </c>
       <c r="AI82" s="7" t="n"/>
-      <c r="AJ82" s="35" t="inlineStr">
+      <c r="AJ82" s="42" t="inlineStr">
         <is>
           <t>V &amp; V</t>
         </is>
@@ -7337,8 +7185,8 @@
       <c r="AL82" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="AM82" s="42" t="n"/>
-      <c r="AN82" s="17" t="inlineStr">
+      <c r="AM82" s="46" t="n"/>
+      <c r="AN82" s="37" t="inlineStr">
         <is>
           <t>Fête de départ de la paroisse</t>
         </is>
@@ -7352,7 +7200,7 @@
         <v>27</v>
       </c>
       <c r="AQ82" s="12" t="n"/>
-      <c r="AR82" s="18" t="n"/>
+      <c r="AR82" s="16" t="n"/>
       <c r="AS82" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7362,25 +7210,21 @@
         <v>27</v>
       </c>
       <c r="AU82" s="12" t="n"/>
-      <c r="AV82" s="18" t="n"/>
+      <c r="AV82" s="16" t="n"/>
     </row>
     <row r="83" ht="20.1" customHeight="1">
       <c r="A83" s="21" t="n"/>
-      <c r="C83" s="44" t="n"/>
-      <c r="D83" s="25" t="inlineStr">
-        <is>
-          <t>Visite du Pape</t>
-        </is>
-      </c>
+      <c r="C83" s="50" t="n"/>
+      <c r="D83" s="23" t="n"/>
       <c r="E83" s="21" t="n"/>
       <c r="G83" s="24" t="n"/>
-      <c r="H83" s="31" t="n"/>
+      <c r="H83" s="23" t="n"/>
       <c r="I83" s="21" t="n"/>
       <c r="K83" s="22" t="n"/>
       <c r="L83" s="23" t="n"/>
       <c r="M83" s="21" t="n"/>
       <c r="O83" s="24" t="n"/>
-      <c r="P83" s="27" t="n"/>
+      <c r="P83" s="28" t="n"/>
       <c r="Q83" s="21" t="n"/>
       <c r="S83" s="22" t="n"/>
       <c r="T83" s="26" t="n"/>
@@ -7389,19 +7233,19 @@
       <c r="X83" s="23" t="n"/>
       <c r="Y83" s="21" t="n"/>
       <c r="AA83" s="22" t="n"/>
-      <c r="AB83" s="36" t="inlineStr">
+      <c r="AB83" s="39" t="inlineStr">
         <is>
           <t>Catéchuménat</t>
         </is>
       </c>
       <c r="AC83" s="21" t="n"/>
       <c r="AE83" s="24" t="n"/>
-      <c r="AF83" s="23" t="n"/>
+      <c r="AF83" s="26" t="n"/>
       <c r="AG83" s="21" t="n"/>
       <c r="AI83" s="22" t="n"/>
       <c r="AJ83" s="23" t="n"/>
       <c r="AK83" s="21" t="n"/>
-      <c r="AM83" s="44" t="n"/>
+      <c r="AM83" s="50" t="n"/>
       <c r="AN83" s="23" t="n"/>
       <c r="AO83" s="21" t="n"/>
       <c r="AQ83" s="24" t="n"/>
@@ -7411,62 +7255,58 @@
       <c r="AV83" s="26" t="n"/>
     </row>
     <row r="84" ht="20.1" customHeight="1">
-      <c r="A84" s="28" t="n"/>
-      <c r="B84" s="29" t="n"/>
-      <c r="C84" s="45" t="n"/>
+      <c r="A84" s="29" t="n"/>
+      <c r="B84" s="30" t="n"/>
+      <c r="C84" s="51" t="n"/>
       <c r="D84" s="23" t="n"/>
-      <c r="E84" s="28" t="n"/>
-      <c r="F84" s="29" t="n"/>
-      <c r="G84" s="32" t="n"/>
-      <c r="H84" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
-      <c r="I84" s="28" t="n"/>
-      <c r="J84" s="29" t="n"/>
-      <c r="K84" s="30" t="n"/>
-      <c r="L84" s="31" t="n"/>
-      <c r="M84" s="28" t="n"/>
-      <c r="N84" s="29" t="n"/>
-      <c r="O84" s="32" t="n"/>
-      <c r="P84" s="34" t="n"/>
-      <c r="Q84" s="28" t="n"/>
-      <c r="R84" s="29" t="n"/>
-      <c r="S84" s="30" t="n"/>
-      <c r="T84" s="33" t="n"/>
-      <c r="U84" s="28" t="n"/>
-      <c r="V84" s="29" t="n"/>
-      <c r="W84" s="32" t="n"/>
-      <c r="X84" s="31" t="n"/>
-      <c r="Y84" s="28" t="n"/>
-      <c r="Z84" s="29" t="n"/>
-      <c r="AA84" s="30" t="n"/>
-      <c r="AB84" s="16" t="inlineStr">
+      <c r="E84" s="29" t="n"/>
+      <c r="F84" s="30" t="n"/>
+      <c r="G84" s="33" t="n"/>
+      <c r="H84" s="23" t="n"/>
+      <c r="I84" s="29" t="n"/>
+      <c r="J84" s="30" t="n"/>
+      <c r="K84" s="31" t="n"/>
+      <c r="L84" s="32" t="n"/>
+      <c r="M84" s="29" t="n"/>
+      <c r="N84" s="30" t="n"/>
+      <c r="O84" s="33" t="n"/>
+      <c r="P84" s="35" t="n"/>
+      <c r="Q84" s="29" t="n"/>
+      <c r="R84" s="30" t="n"/>
+      <c r="S84" s="31" t="n"/>
+      <c r="T84" s="34" t="n"/>
+      <c r="U84" s="29" t="n"/>
+      <c r="V84" s="30" t="n"/>
+      <c r="W84" s="33" t="n"/>
+      <c r="X84" s="32" t="n"/>
+      <c r="Y84" s="29" t="n"/>
+      <c r="Z84" s="30" t="n"/>
+      <c r="AA84" s="31" t="n"/>
+      <c r="AB84" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
       </c>
-      <c r="AC84" s="28" t="n"/>
-      <c r="AD84" s="29" t="n"/>
-      <c r="AE84" s="32" t="n"/>
-      <c r="AF84" s="31" t="n"/>
-      <c r="AG84" s="28" t="n"/>
-      <c r="AH84" s="29" t="n"/>
-      <c r="AI84" s="30" t="n"/>
-      <c r="AJ84" s="31" t="n"/>
-      <c r="AK84" s="28" t="n"/>
-      <c r="AL84" s="29" t="n"/>
-      <c r="AM84" s="45" t="n"/>
-      <c r="AN84" s="31" t="n"/>
-      <c r="AO84" s="28" t="n"/>
-      <c r="AP84" s="29" t="n"/>
-      <c r="AQ84" s="32" t="n"/>
-      <c r="AR84" s="33" t="n"/>
-      <c r="AS84" s="28" t="n"/>
-      <c r="AT84" s="29" t="n"/>
-      <c r="AU84" s="32" t="n"/>
-      <c r="AV84" s="33" t="n"/>
+      <c r="AC84" s="29" t="n"/>
+      <c r="AD84" s="30" t="n"/>
+      <c r="AE84" s="33" t="n"/>
+      <c r="AF84" s="34" t="n"/>
+      <c r="AG84" s="29" t="n"/>
+      <c r="AH84" s="30" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="32" t="n"/>
+      <c r="AK84" s="29" t="n"/>
+      <c r="AL84" s="30" t="n"/>
+      <c r="AM84" s="51" t="n"/>
+      <c r="AN84" s="32" t="n"/>
+      <c r="AO84" s="29" t="n"/>
+      <c r="AP84" s="30" t="n"/>
+      <c r="AQ84" s="33" t="n"/>
+      <c r="AR84" s="34" t="n"/>
+      <c r="AS84" s="29" t="n"/>
+      <c r="AT84" s="30" t="n"/>
+      <c r="AU84" s="33" t="n"/>
+      <c r="AV84" s="34" t="n"/>
     </row>
     <row r="85" ht="20.1" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -7488,7 +7328,7 @@
         <v>28</v>
       </c>
       <c r="G85" s="12" t="n"/>
-      <c r="H85" s="41" t="n"/>
+      <c r="H85" s="23" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7498,7 +7338,7 @@
         <v>28</v>
       </c>
       <c r="K85" s="7" t="n"/>
-      <c r="L85" s="16" t="inlineStr">
+      <c r="L85" s="44" t="inlineStr">
         <is>
           <t>CMP avec Chartres 2040</t>
         </is>
@@ -7512,7 +7352,7 @@
         <v>28</v>
       </c>
       <c r="O85" s="12" t="n"/>
-      <c r="P85" s="18" t="n"/>
+      <c r="P85" s="16" t="n"/>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7522,7 +7362,7 @@
         <v>28</v>
       </c>
       <c r="S85" s="7" t="n"/>
-      <c r="T85" s="48" t="inlineStr">
+      <c r="T85" s="57" t="inlineStr">
         <is>
           <t>Prépa Mariage 1</t>
         </is>
@@ -7536,7 +7376,7 @@
         <v>28</v>
       </c>
       <c r="W85" s="12" t="n"/>
-      <c r="X85" s="50" t="inlineStr">
+      <c r="X85" s="38" t="inlineStr">
         <is>
           <t>3e dim. de Carême</t>
         </is>
@@ -7549,8 +7389,8 @@
       <c r="Z85" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="AA85" s="42" t="n"/>
-      <c r="AB85" s="19" t="inlineStr">
+      <c r="AA85" s="46" t="n"/>
+      <c r="AB85" s="53" t="inlineStr">
         <is>
           <t>Pâques</t>
         </is>
@@ -7564,7 +7404,7 @@
         <v>28</v>
       </c>
       <c r="AE85" s="12" t="n"/>
-      <c r="AF85" s="18" t="n"/>
+      <c r="AF85" s="16" t="n"/>
       <c r="AG85" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7574,7 +7414,7 @@
         <v>28</v>
       </c>
       <c r="AI85" s="7" t="n"/>
-      <c r="AJ85" s="18" t="n"/>
+      <c r="AJ85" s="16" t="n"/>
       <c r="AK85" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7584,7 +7424,7 @@
         <v>28</v>
       </c>
       <c r="AM85" s="7" t="n"/>
-      <c r="AN85" s="18" t="n"/>
+      <c r="AN85" s="16" t="n"/>
       <c r="AO85" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7594,7 +7434,7 @@
         <v>28</v>
       </c>
       <c r="AQ85" s="12" t="n"/>
-      <c r="AR85" s="18" t="n"/>
+      <c r="AR85" s="16" t="n"/>
       <c r="AS85" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7604,7 +7444,7 @@
         <v>28</v>
       </c>
       <c r="AU85" s="12" t="n"/>
-      <c r="AV85" s="17" t="inlineStr">
+      <c r="AV85" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7619,7 +7459,7 @@
       <c r="H86" s="23" t="n"/>
       <c r="I86" s="21" t="n"/>
       <c r="K86" s="22" t="n"/>
-      <c r="L86" s="16" t="inlineStr">
+      <c r="L86" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -7632,13 +7472,13 @@
       <c r="T86" s="23" t="n"/>
       <c r="U86" s="21" t="n"/>
       <c r="W86" s="24" t="n"/>
-      <c r="X86" s="36" t="inlineStr">
+      <c r="X86" s="39" t="inlineStr">
         <is>
           <t>1er scrutin</t>
         </is>
       </c>
       <c r="Y86" s="21" t="n"/>
-      <c r="AA86" s="44" t="n"/>
+      <c r="AA86" s="50" t="n"/>
       <c r="AB86" s="23" t="n"/>
       <c r="AC86" s="21" t="n"/>
       <c r="AE86" s="24" t="n"/>
@@ -7657,54 +7497,54 @@
       <c r="AV86" s="23" t="n"/>
     </row>
     <row r="87" ht="20.1" customHeight="1">
-      <c r="A87" s="28" t="n"/>
-      <c r="B87" s="29" t="n"/>
-      <c r="C87" s="30" t="n"/>
-      <c r="D87" s="31" t="n"/>
-      <c r="E87" s="28" t="n"/>
-      <c r="F87" s="29" t="n"/>
-      <c r="G87" s="32" t="n"/>
+      <c r="A87" s="29" t="n"/>
+      <c r="B87" s="30" t="n"/>
+      <c r="C87" s="31" t="n"/>
+      <c r="D87" s="32" t="n"/>
+      <c r="E87" s="29" t="n"/>
+      <c r="F87" s="30" t="n"/>
+      <c r="G87" s="33" t="n"/>
       <c r="H87" s="23" t="n"/>
-      <c r="I87" s="28" t="n"/>
-      <c r="J87" s="29" t="n"/>
-      <c r="K87" s="30" t="n"/>
-      <c r="L87" s="33" t="n"/>
-      <c r="M87" s="28" t="n"/>
-      <c r="N87" s="29" t="n"/>
-      <c r="O87" s="32" t="n"/>
-      <c r="P87" s="33" t="n"/>
-      <c r="Q87" s="28" t="n"/>
-      <c r="R87" s="29" t="n"/>
-      <c r="S87" s="30" t="n"/>
-      <c r="T87" s="31" t="n"/>
-      <c r="U87" s="28" t="n"/>
-      <c r="V87" s="29" t="n"/>
-      <c r="W87" s="32" t="n"/>
-      <c r="X87" s="34" t="n"/>
-      <c r="Y87" s="28" t="n"/>
-      <c r="Z87" s="29" t="n"/>
-      <c r="AA87" s="45" t="n"/>
-      <c r="AB87" s="31" t="n"/>
-      <c r="AC87" s="28" t="n"/>
-      <c r="AD87" s="29" t="n"/>
-      <c r="AE87" s="32" t="n"/>
-      <c r="AF87" s="33" t="n"/>
-      <c r="AG87" s="28" t="n"/>
-      <c r="AH87" s="29" t="n"/>
-      <c r="AI87" s="30" t="n"/>
-      <c r="AJ87" s="33" t="n"/>
-      <c r="AK87" s="28" t="n"/>
-      <c r="AL87" s="29" t="n"/>
-      <c r="AM87" s="30" t="n"/>
-      <c r="AN87" s="33" t="n"/>
-      <c r="AO87" s="28" t="n"/>
-      <c r="AP87" s="29" t="n"/>
-      <c r="AQ87" s="32" t="n"/>
-      <c r="AR87" s="33" t="n"/>
-      <c r="AS87" s="28" t="n"/>
-      <c r="AT87" s="29" t="n"/>
-      <c r="AU87" s="32" t="n"/>
-      <c r="AV87" s="31" t="n"/>
+      <c r="I87" s="29" t="n"/>
+      <c r="J87" s="30" t="n"/>
+      <c r="K87" s="31" t="n"/>
+      <c r="L87" s="34" t="n"/>
+      <c r="M87" s="29" t="n"/>
+      <c r="N87" s="30" t="n"/>
+      <c r="O87" s="33" t="n"/>
+      <c r="P87" s="34" t="n"/>
+      <c r="Q87" s="29" t="n"/>
+      <c r="R87" s="30" t="n"/>
+      <c r="S87" s="31" t="n"/>
+      <c r="T87" s="32" t="n"/>
+      <c r="U87" s="29" t="n"/>
+      <c r="V87" s="30" t="n"/>
+      <c r="W87" s="33" t="n"/>
+      <c r="X87" s="35" t="n"/>
+      <c r="Y87" s="29" t="n"/>
+      <c r="Z87" s="30" t="n"/>
+      <c r="AA87" s="51" t="n"/>
+      <c r="AB87" s="32" t="n"/>
+      <c r="AC87" s="29" t="n"/>
+      <c r="AD87" s="30" t="n"/>
+      <c r="AE87" s="33" t="n"/>
+      <c r="AF87" s="34" t="n"/>
+      <c r="AG87" s="29" t="n"/>
+      <c r="AH87" s="30" t="n"/>
+      <c r="AI87" s="31" t="n"/>
+      <c r="AJ87" s="34" t="n"/>
+      <c r="AK87" s="29" t="n"/>
+      <c r="AL87" s="30" t="n"/>
+      <c r="AM87" s="31" t="n"/>
+      <c r="AN87" s="34" t="n"/>
+      <c r="AO87" s="29" t="n"/>
+      <c r="AP87" s="30" t="n"/>
+      <c r="AQ87" s="33" t="n"/>
+      <c r="AR87" s="34" t="n"/>
+      <c r="AS87" s="29" t="n"/>
+      <c r="AT87" s="30" t="n"/>
+      <c r="AU87" s="33" t="n"/>
+      <c r="AV87" s="32" t="n"/>
     </row>
     <row r="88" ht="20.1" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -7716,11 +7556,7 @@
         <v>29</v>
       </c>
       <c r="C88" s="7" t="n"/>
-      <c r="D88" s="17" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="D88" s="16" t="n"/>
       <c r="E88" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7739,8 +7575,8 @@
       <c r="J88" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="K88" s="42" t="n"/>
-      <c r="L88" s="47" t="inlineStr">
+      <c r="K88" s="46" t="n"/>
+      <c r="L88" s="56" t="inlineStr">
         <is>
           <t>1er dim. de l'Avent</t>
         </is>
@@ -7754,11 +7590,7 @@
         <v>29</v>
       </c>
       <c r="O88" s="12" t="n"/>
-      <c r="P88" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="P88" s="16" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7768,7 +7600,7 @@
         <v>29</v>
       </c>
       <c r="S88" s="7" t="n"/>
-      <c r="T88" s="18" t="n"/>
+      <c r="T88" s="16" t="n"/>
       <c r="Y88" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -7778,7 +7610,7 @@
         <v>29</v>
       </c>
       <c r="AA88" s="7" t="n"/>
-      <c r="AB88" s="13" t="inlineStr">
+      <c r="AB88" s="17" t="inlineStr">
         <is>
           <t>Lundi de Pâques</t>
         </is>
@@ -7792,7 +7624,7 @@
         <v>29</v>
       </c>
       <c r="AE88" s="12" t="n"/>
-      <c r="AF88" s="18" t="n"/>
+      <c r="AF88" s="16" t="n"/>
       <c r="AG88" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7802,7 +7634,7 @@
         <v>29</v>
       </c>
       <c r="AI88" s="7" t="n"/>
-      <c r="AJ88" s="43" t="inlineStr">
+      <c r="AJ88" s="47" t="inlineStr">
         <is>
           <t>Concert</t>
         </is>
@@ -7816,11 +7648,7 @@
         <v>29</v>
       </c>
       <c r="AM88" s="7" t="n"/>
-      <c r="AN88" s="17" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AN88" s="16" t="n"/>
       <c r="AO88" s="5" t="inlineStr">
         <is>
           <t>J</t>
@@ -7830,7 +7658,7 @@
         <v>29</v>
       </c>
       <c r="AQ88" s="12" t="n"/>
-      <c r="AR88" s="18" t="n"/>
+      <c r="AR88" s="16" t="n"/>
       <c r="AS88" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -7845,22 +7673,22 @@
     <row r="89" ht="20.1" customHeight="1">
       <c r="A89" s="21" t="n"/>
       <c r="C89" s="22" t="n"/>
-      <c r="D89" s="23" t="n"/>
+      <c r="D89" s="26" t="n"/>
       <c r="E89" s="21" t="n"/>
       <c r="G89" s="24" t="n"/>
       <c r="H89" s="23" t="n"/>
       <c r="I89" s="21" t="n"/>
-      <c r="K89" s="44" t="n"/>
+      <c r="K89" s="50" t="n"/>
       <c r="L89" s="23" t="n"/>
       <c r="M89" s="21" t="n"/>
       <c r="O89" s="24" t="n"/>
-      <c r="P89" s="23" t="n"/>
+      <c r="P89" s="26" t="n"/>
       <c r="Q89" s="21" t="n"/>
       <c r="S89" s="22" t="n"/>
       <c r="T89" s="26" t="n"/>
       <c r="Y89" s="21" t="n"/>
       <c r="AA89" s="22" t="n"/>
-      <c r="AB89" s="16" t="inlineStr">
+      <c r="AB89" s="61" t="inlineStr">
         <is>
           <t>Lundi de Pâques CCN + Kion + Cana</t>
         </is>
@@ -7870,66 +7698,66 @@
       <c r="AF89" s="26" t="n"/>
       <c r="AG89" s="21" t="n"/>
       <c r="AI89" s="22" t="n"/>
-      <c r="AJ89" s="16" t="inlineStr">
+      <c r="AJ89" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
       </c>
       <c r="AK89" s="21" t="n"/>
       <c r="AM89" s="22" t="n"/>
-      <c r="AN89" s="23" t="n"/>
+      <c r="AN89" s="26" t="n"/>
       <c r="AO89" s="21" t="n"/>
       <c r="AQ89" s="24" t="n"/>
       <c r="AR89" s="26" t="n"/>
       <c r="AS89" s="21" t="n"/>
       <c r="AU89" s="24" t="n"/>
-      <c r="AV89" s="27" t="n"/>
+      <c r="AV89" s="28" t="n"/>
     </row>
     <row r="90" ht="20.1" customHeight="1">
-      <c r="A90" s="28" t="n"/>
-      <c r="B90" s="29" t="n"/>
-      <c r="C90" s="30" t="n"/>
-      <c r="D90" s="31" t="n"/>
-      <c r="E90" s="28" t="n"/>
-      <c r="F90" s="29" t="n"/>
-      <c r="G90" s="32" t="n"/>
+      <c r="A90" s="29" t="n"/>
+      <c r="B90" s="30" t="n"/>
+      <c r="C90" s="31" t="n"/>
+      <c r="D90" s="34" t="n"/>
+      <c r="E90" s="29" t="n"/>
+      <c r="F90" s="30" t="n"/>
+      <c r="G90" s="33" t="n"/>
       <c r="H90" s="23" t="n"/>
-      <c r="I90" s="28" t="n"/>
-      <c r="J90" s="29" t="n"/>
-      <c r="K90" s="45" t="n"/>
-      <c r="L90" s="31" t="n"/>
-      <c r="M90" s="28" t="n"/>
-      <c r="N90" s="29" t="n"/>
-      <c r="O90" s="32" t="n"/>
-      <c r="P90" s="31" t="n"/>
-      <c r="Q90" s="28" t="n"/>
-      <c r="R90" s="29" t="n"/>
-      <c r="S90" s="30" t="n"/>
-      <c r="T90" s="33" t="n"/>
-      <c r="Y90" s="28" t="n"/>
-      <c r="Z90" s="29" t="n"/>
-      <c r="AA90" s="30" t="n"/>
-      <c r="AB90" s="33" t="n"/>
-      <c r="AC90" s="28" t="n"/>
-      <c r="AD90" s="29" t="n"/>
-      <c r="AE90" s="32" t="n"/>
-      <c r="AF90" s="33" t="n"/>
-      <c r="AG90" s="28" t="n"/>
-      <c r="AH90" s="29" t="n"/>
-      <c r="AI90" s="30" t="n"/>
-      <c r="AJ90" s="33" t="n"/>
-      <c r="AK90" s="28" t="n"/>
-      <c r="AL90" s="29" t="n"/>
-      <c r="AM90" s="30" t="n"/>
-      <c r="AN90" s="31" t="n"/>
-      <c r="AO90" s="28" t="n"/>
-      <c r="AP90" s="29" t="n"/>
-      <c r="AQ90" s="32" t="n"/>
-      <c r="AR90" s="33" t="n"/>
-      <c r="AS90" s="28" t="n"/>
-      <c r="AT90" s="29" t="n"/>
-      <c r="AU90" s="32" t="n"/>
-      <c r="AV90" s="34" t="n"/>
+      <c r="I90" s="29" t="n"/>
+      <c r="J90" s="30" t="n"/>
+      <c r="K90" s="51" t="n"/>
+      <c r="L90" s="32" t="n"/>
+      <c r="M90" s="29" t="n"/>
+      <c r="N90" s="30" t="n"/>
+      <c r="O90" s="33" t="n"/>
+      <c r="P90" s="34" t="n"/>
+      <c r="Q90" s="29" t="n"/>
+      <c r="R90" s="30" t="n"/>
+      <c r="S90" s="31" t="n"/>
+      <c r="T90" s="34" t="n"/>
+      <c r="Y90" s="29" t="n"/>
+      <c r="Z90" s="30" t="n"/>
+      <c r="AA90" s="31" t="n"/>
+      <c r="AB90" s="34" t="n"/>
+      <c r="AC90" s="29" t="n"/>
+      <c r="AD90" s="30" t="n"/>
+      <c r="AE90" s="33" t="n"/>
+      <c r="AF90" s="34" t="n"/>
+      <c r="AG90" s="29" t="n"/>
+      <c r="AH90" s="30" t="n"/>
+      <c r="AI90" s="31" t="n"/>
+      <c r="AJ90" s="34" t="n"/>
+      <c r="AK90" s="29" t="n"/>
+      <c r="AL90" s="30" t="n"/>
+      <c r="AM90" s="31" t="n"/>
+      <c r="AN90" s="34" t="n"/>
+      <c r="AO90" s="29" t="n"/>
+      <c r="AP90" s="30" t="n"/>
+      <c r="AQ90" s="33" t="n"/>
+      <c r="AR90" s="34" t="n"/>
+      <c r="AS90" s="29" t="n"/>
+      <c r="AT90" s="30" t="n"/>
+      <c r="AU90" s="33" t="n"/>
+      <c r="AV90" s="35" t="n"/>
     </row>
     <row r="91" ht="20.1" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -7941,7 +7769,7 @@
         <v>30</v>
       </c>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="18" t="n"/>
+      <c r="D91" s="16" t="n"/>
       <c r="E91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -7961,7 +7789,7 @@
         <v>30</v>
       </c>
       <c r="K91" s="7" t="n"/>
-      <c r="L91" s="18" t="n"/>
+      <c r="L91" s="16" t="n"/>
       <c r="M91" s="5" t="inlineStr">
         <is>
           <t>Me</t>
@@ -7971,7 +7799,7 @@
         <v>30</v>
       </c>
       <c r="O91" s="12" t="n"/>
-      <c r="P91" s="18" t="n"/>
+      <c r="P91" s="16" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>S</t>
@@ -7981,7 +7809,7 @@
         <v>30</v>
       </c>
       <c r="S91" s="7" t="n"/>
-      <c r="T91" s="36" t="inlineStr">
+      <c r="T91" s="39" t="inlineStr">
         <is>
           <t>WE catéchumènes</t>
         </is>
@@ -7995,11 +7823,7 @@
         <v>30</v>
       </c>
       <c r="AA91" s="7" t="n"/>
-      <c r="AB91" s="16" t="inlineStr">
-        <is>
-          <t>Groupe de prière</t>
-        </is>
-      </c>
+      <c r="AB91" s="16" t="n"/>
       <c r="AC91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -8009,7 +7833,7 @@
         <v>30</v>
       </c>
       <c r="AE91" s="12" t="n"/>
-      <c r="AF91" s="18" t="n"/>
+      <c r="AF91" s="16" t="n"/>
       <c r="AG91" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -8018,7 +7842,7 @@
       <c r="AH91" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AI91" s="42" t="n"/>
+      <c r="AI91" s="46" t="n"/>
       <c r="AJ91" s="20" t="n"/>
       <c r="AK91" s="5" t="inlineStr">
         <is>
@@ -8029,7 +7853,7 @@
         <v>30</v>
       </c>
       <c r="AM91" s="7" t="n"/>
-      <c r="AN91" s="18" t="n"/>
+      <c r="AN91" s="16" t="n"/>
       <c r="AO91" s="5" t="inlineStr">
         <is>
           <t>V</t>
@@ -8039,7 +7863,7 @@
         <v>30</v>
       </c>
       <c r="AQ91" s="12" t="n"/>
-      <c r="AR91" s="18" t="n"/>
+      <c r="AR91" s="16" t="n"/>
       <c r="AS91" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -8049,7 +7873,7 @@
         <v>30</v>
       </c>
       <c r="AU91" s="12" t="n"/>
-      <c r="AV91" s="18" t="n"/>
+      <c r="AV91" s="16" t="n"/>
     </row>
     <row r="92" ht="20.1" customHeight="1">
       <c r="A92" s="21" t="n"/>
@@ -8066,24 +7890,20 @@
       <c r="P92" s="26" t="n"/>
       <c r="Q92" s="21" t="n"/>
       <c r="S92" s="22" t="n"/>
-      <c r="T92" s="16" t="inlineStr">
+      <c r="T92" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
       </c>
       <c r="Y92" s="21" t="n"/>
       <c r="AA92" s="22" t="n"/>
-      <c r="AB92" s="16" t="inlineStr">
-        <is>
-          <t>Journée d'adoration</t>
-        </is>
-      </c>
+      <c r="AB92" s="26" t="n"/>
       <c r="AC92" s="21" t="n"/>
       <c r="AE92" s="24" t="n"/>
       <c r="AF92" s="26" t="n"/>
       <c r="AG92" s="21" t="n"/>
-      <c r="AI92" s="44" t="n"/>
-      <c r="AJ92" s="27" t="n"/>
+      <c r="AI92" s="50" t="n"/>
+      <c r="AJ92" s="28" t="n"/>
       <c r="AK92" s="21" t="n"/>
       <c r="AM92" s="22" t="n"/>
       <c r="AN92" s="26" t="n"/>
@@ -8095,54 +7915,54 @@
       <c r="AV92" s="26" t="n"/>
     </row>
     <row r="93" ht="20.1" customHeight="1">
-      <c r="A93" s="28" t="n"/>
-      <c r="B93" s="29" t="n"/>
-      <c r="C93" s="30" t="n"/>
-      <c r="D93" s="33" t="n"/>
-      <c r="E93" s="28" t="n"/>
-      <c r="F93" s="29" t="n"/>
-      <c r="G93" s="32" t="n"/>
+      <c r="A93" s="29" t="n"/>
+      <c r="B93" s="30" t="n"/>
+      <c r="C93" s="31" t="n"/>
+      <c r="D93" s="34" t="n"/>
+      <c r="E93" s="29" t="n"/>
+      <c r="F93" s="30" t="n"/>
+      <c r="G93" s="33" t="n"/>
       <c r="H93" s="23" t="n"/>
-      <c r="I93" s="28" t="n"/>
-      <c r="J93" s="29" t="n"/>
-      <c r="K93" s="30" t="n"/>
-      <c r="L93" s="33" t="n"/>
-      <c r="M93" s="28" t="n"/>
-      <c r="N93" s="29" t="n"/>
-      <c r="O93" s="32" t="n"/>
-      <c r="P93" s="33" t="n"/>
-      <c r="Q93" s="28" t="n"/>
-      <c r="R93" s="29" t="n"/>
-      <c r="S93" s="30" t="n"/>
-      <c r="T93" s="17" t="inlineStr">
+      <c r="I93" s="29" t="n"/>
+      <c r="J93" s="30" t="n"/>
+      <c r="K93" s="31" t="n"/>
+      <c r="L93" s="34" t="n"/>
+      <c r="M93" s="29" t="n"/>
+      <c r="N93" s="30" t="n"/>
+      <c r="O93" s="33" t="n"/>
+      <c r="P93" s="34" t="n"/>
+      <c r="Q93" s="29" t="n"/>
+      <c r="R93" s="30" t="n"/>
+      <c r="S93" s="31" t="n"/>
+      <c r="T93" s="18" t="inlineStr">
         <is>
           <t>WE Engagés ccn</t>
         </is>
       </c>
-      <c r="Y93" s="28" t="n"/>
-      <c r="Z93" s="29" t="n"/>
-      <c r="AA93" s="30" t="n"/>
-      <c r="AB93" s="33" t="n"/>
-      <c r="AC93" s="28" t="n"/>
-      <c r="AD93" s="29" t="n"/>
-      <c r="AE93" s="32" t="n"/>
-      <c r="AF93" s="33" t="n"/>
-      <c r="AG93" s="28" t="n"/>
-      <c r="AH93" s="29" t="n"/>
-      <c r="AI93" s="45" t="n"/>
-      <c r="AJ93" s="34" t="n"/>
-      <c r="AK93" s="28" t="n"/>
-      <c r="AL93" s="29" t="n"/>
-      <c r="AM93" s="30" t="n"/>
-      <c r="AN93" s="33" t="n"/>
-      <c r="AO93" s="28" t="n"/>
-      <c r="AP93" s="29" t="n"/>
-      <c r="AQ93" s="32" t="n"/>
-      <c r="AR93" s="33" t="n"/>
-      <c r="AS93" s="28" t="n"/>
-      <c r="AT93" s="29" t="n"/>
-      <c r="AU93" s="32" t="n"/>
-      <c r="AV93" s="33" t="n"/>
+      <c r="Y93" s="29" t="n"/>
+      <c r="Z93" s="30" t="n"/>
+      <c r="AA93" s="31" t="n"/>
+      <c r="AB93" s="34" t="n"/>
+      <c r="AC93" s="29" t="n"/>
+      <c r="AD93" s="30" t="n"/>
+      <c r="AE93" s="33" t="n"/>
+      <c r="AF93" s="34" t="n"/>
+      <c r="AG93" s="29" t="n"/>
+      <c r="AH93" s="30" t="n"/>
+      <c r="AI93" s="51" t="n"/>
+      <c r="AJ93" s="35" t="n"/>
+      <c r="AK93" s="29" t="n"/>
+      <c r="AL93" s="30" t="n"/>
+      <c r="AM93" s="31" t="n"/>
+      <c r="AN93" s="34" t="n"/>
+      <c r="AO93" s="29" t="n"/>
+      <c r="AP93" s="30" t="n"/>
+      <c r="AQ93" s="33" t="n"/>
+      <c r="AR93" s="34" t="n"/>
+      <c r="AS93" s="29" t="n"/>
+      <c r="AT93" s="30" t="n"/>
+      <c r="AU93" s="33" t="n"/>
+      <c r="AV93" s="34" t="n"/>
     </row>
     <row r="94" ht="20.1" customHeight="1">
       <c r="E94" s="5" t="inlineStr">
@@ -8164,7 +7984,7 @@
         <v>31</v>
       </c>
       <c r="O94" s="12" t="n"/>
-      <c r="P94" s="18" t="n"/>
+      <c r="P94" s="16" t="n"/>
       <c r="Q94" s="10" t="inlineStr">
         <is>
           <t>D</t>
@@ -8173,7 +7993,7 @@
       <c r="R94" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="S94" s="42" t="n"/>
+      <c r="S94" s="46" t="n"/>
       <c r="T94" s="23" t="n"/>
       <c r="Y94" s="5" t="inlineStr">
         <is>
@@ -8184,7 +8004,7 @@
         <v>31</v>
       </c>
       <c r="AA94" s="7" t="n"/>
-      <c r="AB94" s="18" t="n"/>
+      <c r="AB94" s="16" t="n"/>
       <c r="AG94" s="5" t="inlineStr">
         <is>
           <t>L</t>
@@ -8194,7 +8014,7 @@
         <v>31</v>
       </c>
       <c r="AI94" s="7" t="n"/>
-      <c r="AJ94" s="17" t="inlineStr">
+      <c r="AJ94" s="18" t="inlineStr">
         <is>
           <t>Journée Paroisse</t>
         </is>
@@ -8208,7 +8028,7 @@
         <v>31</v>
       </c>
       <c r="AQ94" s="12" t="n"/>
-      <c r="AR94" s="17" t="inlineStr">
+      <c r="AR94" s="37" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
@@ -8222,18 +8042,18 @@
         <v>31</v>
       </c>
       <c r="AU94" s="12" t="n"/>
-      <c r="AV94" s="18" t="n"/>
+      <c r="AV94" s="16" t="n"/>
     </row>
     <row r="95" ht="20.1" customHeight="1">
       <c r="E95" s="21" t="n"/>
       <c r="G95" s="24" t="n"/>
-      <c r="H95" s="31" t="n"/>
+      <c r="H95" s="32" t="n"/>
       <c r="M95" s="21" t="n"/>
       <c r="O95" s="24" t="n"/>
       <c r="P95" s="26" t="n"/>
       <c r="Q95" s="21" t="n"/>
-      <c r="S95" s="44" t="n"/>
-      <c r="T95" s="31" t="n"/>
+      <c r="S95" s="50" t="n"/>
+      <c r="T95" s="32" t="n"/>
       <c r="Y95" s="21" t="n"/>
       <c r="AA95" s="22" t="n"/>
       <c r="AB95" s="26" t="n"/>
@@ -8248,41 +8068,41 @@
       <c r="AV95" s="26" t="n"/>
     </row>
     <row r="96" ht="20.1" customHeight="1">
-      <c r="E96" s="28" t="n"/>
-      <c r="F96" s="29" t="n"/>
-      <c r="G96" s="32" t="n"/>
-      <c r="H96" s="16" t="inlineStr">
+      <c r="E96" s="29" t="n"/>
+      <c r="F96" s="30" t="n"/>
+      <c r="G96" s="33" t="n"/>
+      <c r="H96" s="27" t="inlineStr">
         <is>
           <t>Messe pour les défunts</t>
         </is>
       </c>
-      <c r="M96" s="28" t="n"/>
-      <c r="N96" s="29" t="n"/>
-      <c r="O96" s="32" t="n"/>
-      <c r="P96" s="33" t="n"/>
-      <c r="Q96" s="28" t="n"/>
-      <c r="R96" s="29" t="n"/>
-      <c r="S96" s="45" t="n"/>
-      <c r="T96" s="36" t="n"/>
-      <c r="Y96" s="28" t="n"/>
-      <c r="Z96" s="29" t="n"/>
-      <c r="AA96" s="30" t="n"/>
-      <c r="AB96" s="33" t="n"/>
-      <c r="AG96" s="28" t="n"/>
-      <c r="AH96" s="29" t="n"/>
-      <c r="AI96" s="30" t="n"/>
-      <c r="AJ96" s="31" t="n"/>
-      <c r="AO96" s="28" t="n"/>
-      <c r="AP96" s="29" t="n"/>
-      <c r="AQ96" s="32" t="n"/>
-      <c r="AR96" s="31" t="n"/>
-      <c r="AS96" s="28" t="n"/>
-      <c r="AT96" s="29" t="n"/>
-      <c r="AU96" s="32" t="n"/>
-      <c r="AV96" s="33" t="n"/>
+      <c r="M96" s="29" t="n"/>
+      <c r="N96" s="30" t="n"/>
+      <c r="O96" s="33" t="n"/>
+      <c r="P96" s="34" t="n"/>
+      <c r="Q96" s="29" t="n"/>
+      <c r="R96" s="30" t="n"/>
+      <c r="S96" s="51" t="n"/>
+      <c r="T96" s="39" t="n"/>
+      <c r="Y96" s="29" t="n"/>
+      <c r="Z96" s="30" t="n"/>
+      <c r="AA96" s="31" t="n"/>
+      <c r="AB96" s="34" t="n"/>
+      <c r="AG96" s="29" t="n"/>
+      <c r="AH96" s="30" t="n"/>
+      <c r="AI96" s="31" t="n"/>
+      <c r="AJ96" s="32" t="n"/>
+      <c r="AO96" s="29" t="n"/>
+      <c r="AP96" s="30" t="n"/>
+      <c r="AQ96" s="33" t="n"/>
+      <c r="AR96" s="32" t="n"/>
+      <c r="AS96" s="29" t="n"/>
+      <c r="AT96" s="30" t="n"/>
+      <c r="AU96" s="33" t="n"/>
+      <c r="AV96" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="842">
+  <mergeCells count="838">
     <mergeCell ref="AC22:AC24"/>
     <mergeCell ref="R91:R93"/>
     <mergeCell ref="B34:B36"/>
@@ -8298,7 +8118,6 @@
     <mergeCell ref="V55:V57"/>
     <mergeCell ref="Z19:Z21"/>
     <mergeCell ref="AT67:AT69"/>
-    <mergeCell ref="X73:X81"/>
     <mergeCell ref="AO31:AO33"/>
     <mergeCell ref="I88:I90"/>
     <mergeCell ref="AG58:AG60"/>
@@ -8316,7 +8135,6 @@
     <mergeCell ref="Q43:Q45"/>
     <mergeCell ref="AS88:AS90"/>
     <mergeCell ref="AG25:AG27"/>
-    <mergeCell ref="L47:L51"/>
     <mergeCell ref="AH67:AH69"/>
     <mergeCell ref="N46:N48"/>
     <mergeCell ref="AJ67:AJ69"/>
@@ -8328,6 +8146,7 @@
     <mergeCell ref="R37:R39"/>
     <mergeCell ref="N61:N63"/>
     <mergeCell ref="AP94:AP96"/>
+    <mergeCell ref="L37:L43"/>
     <mergeCell ref="Y94:Y96"/>
     <mergeCell ref="I37:I39"/>
     <mergeCell ref="AC10:AC12"/>
@@ -8352,6 +8171,7 @@
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="I13:I15"/>
     <mergeCell ref="I64:I66"/>
+    <mergeCell ref="H61:H71"/>
     <mergeCell ref="AK61:AK63"/>
     <mergeCell ref="U4:U6"/>
     <mergeCell ref="AD52:AD54"/>
@@ -8387,6 +8207,7 @@
     <mergeCell ref="Q82:Q84"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="Y82:Y84"/>
+    <mergeCell ref="AN4:AN6"/>
     <mergeCell ref="L55:L59"/>
     <mergeCell ref="Y19:Y21"/>
     <mergeCell ref="AG16:AG18"/>
@@ -8400,7 +8221,6 @@
     <mergeCell ref="AP70:AP72"/>
     <mergeCell ref="AT46:AT48"/>
     <mergeCell ref="AO25:AO27"/>
-    <mergeCell ref="H85:H95"/>
     <mergeCell ref="U52:U54"/>
     <mergeCell ref="AC49:AC51"/>
     <mergeCell ref="AT61:AT63"/>
@@ -8429,7 +8249,6 @@
     <mergeCell ref="AO13:AO15"/>
     <mergeCell ref="AS40:AS42"/>
     <mergeCell ref="AS46:AS48"/>
-    <mergeCell ref="P67:P69"/>
     <mergeCell ref="F91:F93"/>
     <mergeCell ref="N82:N84"/>
     <mergeCell ref="U7:U9"/>
@@ -8437,7 +8256,6 @@
     <mergeCell ref="AH19:AH21"/>
     <mergeCell ref="AH55:AH57"/>
     <mergeCell ref="F22:F24"/>
-    <mergeCell ref="H44:H56"/>
     <mergeCell ref="AC31:AC33"/>
     <mergeCell ref="AO79:AO81"/>
     <mergeCell ref="U58:U60"/>
@@ -8463,12 +8281,12 @@
     <mergeCell ref="AH37:AH39"/>
     <mergeCell ref="A2:AV2"/>
     <mergeCell ref="F4:F6"/>
+    <mergeCell ref="L32:L34"/>
     <mergeCell ref="D40:D42"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="F40:F42"/>
     <mergeCell ref="AK19:AK21"/>
     <mergeCell ref="J64:J66"/>
-    <mergeCell ref="P88:P90"/>
     <mergeCell ref="R88:R90"/>
     <mergeCell ref="AF10:AF12"/>
     <mergeCell ref="M79:M81"/>
@@ -8496,7 +8314,6 @@
     <mergeCell ref="AS61:AS63"/>
     <mergeCell ref="AJ27:AJ30"/>
     <mergeCell ref="AN58:AN60"/>
-    <mergeCell ref="X65:X71"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="R52:R54"/>
     <mergeCell ref="V16:V18"/>
@@ -8504,6 +8321,7 @@
     <mergeCell ref="Z67:Z69"/>
     <mergeCell ref="P19:P21"/>
     <mergeCell ref="D55:D57"/>
+    <mergeCell ref="H19:H21"/>
     <mergeCell ref="AH94:AH96"/>
     <mergeCell ref="F61:F63"/>
     <mergeCell ref="U79:U81"/>
@@ -8520,7 +8338,6 @@
     <mergeCell ref="N85:N87"/>
     <mergeCell ref="U10:U12"/>
     <mergeCell ref="AH22:AH24"/>
-    <mergeCell ref="H36:H41"/>
     <mergeCell ref="AG88:AG90"/>
     <mergeCell ref="M67:M69"/>
     <mergeCell ref="AL22:AL24"/>
@@ -8565,6 +8382,7 @@
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="AL10:AL12"/>
     <mergeCell ref="AT7:AT9"/>
+    <mergeCell ref="T10:T26"/>
     <mergeCell ref="AL34:AL36"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="AT25:AT27"/>
@@ -8606,7 +8424,6 @@
     <mergeCell ref="AC25:AC27"/>
     <mergeCell ref="J46:J48"/>
     <mergeCell ref="M85:M87"/>
-    <mergeCell ref="AB7:AB9"/>
     <mergeCell ref="E85:E87"/>
     <mergeCell ref="AD7:AD9"/>
     <mergeCell ref="AT64:AT66"/>
@@ -8674,7 +8491,6 @@
     <mergeCell ref="AO52:AO54"/>
     <mergeCell ref="U19:U21"/>
     <mergeCell ref="AO76:AO78"/>
-    <mergeCell ref="D88:D90"/>
     <mergeCell ref="AB80:AB82"/>
     <mergeCell ref="F88:F90"/>
     <mergeCell ref="AD58:AD60"/>
@@ -8687,26 +8503,24 @@
     <mergeCell ref="AK25:AK27"/>
     <mergeCell ref="Q52:Q54"/>
     <mergeCell ref="E28:E30"/>
-    <mergeCell ref="AN88:AN90"/>
     <mergeCell ref="N43:N45"/>
     <mergeCell ref="V40:V42"/>
     <mergeCell ref="AP88:AP90"/>
     <mergeCell ref="AS22:AS24"/>
     <mergeCell ref="AC67:AC69"/>
     <mergeCell ref="A46:A48"/>
+    <mergeCell ref="D82:D87"/>
     <mergeCell ref="M46:M48"/>
     <mergeCell ref="F85:F87"/>
     <mergeCell ref="AP19:AP21"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="U37:U39"/>
-    <mergeCell ref="AR19:AR21"/>
     <mergeCell ref="M37:M39"/>
     <mergeCell ref="E40:E42"/>
     <mergeCell ref="AK31:AK33"/>
     <mergeCell ref="AB65:AB70"/>
     <mergeCell ref="AJ52:AJ53"/>
     <mergeCell ref="AT34:AT36"/>
-    <mergeCell ref="H73:H83"/>
     <mergeCell ref="AB13:AB15"/>
     <mergeCell ref="Z10:Z12"/>
     <mergeCell ref="I79:I81"/>
@@ -8718,7 +8532,6 @@
     <mergeCell ref="AO40:AO42"/>
     <mergeCell ref="AT85:AT87"/>
     <mergeCell ref="L67:L69"/>
-    <mergeCell ref="D83:D87"/>
     <mergeCell ref="AG64:AG66"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="M43:M45"/>
@@ -8732,7 +8545,6 @@
     <mergeCell ref="N4:N6"/>
     <mergeCell ref="V61:V63"/>
     <mergeCell ref="Y58:Y60"/>
-    <mergeCell ref="AF61:AF63"/>
     <mergeCell ref="Q58:Q60"/>
     <mergeCell ref="AC16:AC18"/>
     <mergeCell ref="I76:I78"/>
@@ -8743,6 +8555,7 @@
     <mergeCell ref="F79:F81"/>
     <mergeCell ref="AR13:AR15"/>
     <mergeCell ref="E34:E36"/>
+    <mergeCell ref="AJ13:AJ15"/>
     <mergeCell ref="AC82:AC84"/>
     <mergeCell ref="M25:M27"/>
     <mergeCell ref="AH43:AH45"/>
@@ -8753,7 +8566,6 @@
     <mergeCell ref="Q85:Q87"/>
     <mergeCell ref="E61:E63"/>
     <mergeCell ref="AT4:AT6"/>
-    <mergeCell ref="T19:T26"/>
     <mergeCell ref="AO43:AO45"/>
     <mergeCell ref="AC19:AC21"/>
     <mergeCell ref="D4:D6"/>
@@ -8778,6 +8590,7 @@
     <mergeCell ref="AK70:AK72"/>
     <mergeCell ref="AH25:AH27"/>
     <mergeCell ref="AB34:AB36"/>
+    <mergeCell ref="AB25:AB30"/>
     <mergeCell ref="V85:V87"/>
     <mergeCell ref="AO67:AO69"/>
     <mergeCell ref="AO61:AO63"/>
@@ -8800,7 +8613,6 @@
     <mergeCell ref="N64:N66"/>
     <mergeCell ref="AS43:AS45"/>
     <mergeCell ref="Y10:Y12"/>
-    <mergeCell ref="T10:T16"/>
     <mergeCell ref="J85:J87"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="AO91:AO93"/>
@@ -8809,7 +8621,6 @@
     <mergeCell ref="AL55:AL57"/>
     <mergeCell ref="R70:R72"/>
     <mergeCell ref="AP46:AP48"/>
-    <mergeCell ref="L36:L43"/>
     <mergeCell ref="AP40:AP42"/>
     <mergeCell ref="N13:N15"/>
     <mergeCell ref="AJ47:AJ50"/>
@@ -8823,11 +8634,13 @@
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="AT79:AT81"/>
+    <mergeCell ref="H35:H44"/>
     <mergeCell ref="AL79:AL81"/>
     <mergeCell ref="R58:R60"/>
     <mergeCell ref="AT70:AT72"/>
     <mergeCell ref="Z49:Z51"/>
     <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="AB49:AB51"/>
     <mergeCell ref="Y3:AB3"/>
     <mergeCell ref="J76:J78"/>
     <mergeCell ref="B16:B18"/>
@@ -8850,8 +8663,8 @@
     <mergeCell ref="AG22:AG24"/>
     <mergeCell ref="AL43:AL45"/>
     <mergeCell ref="AS4:AS6"/>
+    <mergeCell ref="P25:P27"/>
     <mergeCell ref="X82:X84"/>
-    <mergeCell ref="AF82:AF84"/>
     <mergeCell ref="AT76:AT78"/>
     <mergeCell ref="AD19:AD21"/>
     <mergeCell ref="T93:T95"/>
@@ -8862,6 +8675,7 @@
     <mergeCell ref="AH34:AH36"/>
     <mergeCell ref="AK73:AK75"/>
     <mergeCell ref="P13:P15"/>
+    <mergeCell ref="H46:H56"/>
     <mergeCell ref="AH64:AH66"/>
     <mergeCell ref="AL28:AL30"/>
     <mergeCell ref="Z52:Z54"/>
@@ -8886,7 +8700,6 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="L30:L31"/>
     <mergeCell ref="B64:B66"/>
-    <mergeCell ref="L12:L17"/>
     <mergeCell ref="Q16:Q18"/>
     <mergeCell ref="AR31:AR33"/>
     <mergeCell ref="Q76:Q78"/>
@@ -8925,7 +8738,6 @@
     <mergeCell ref="Y49:Y51"/>
     <mergeCell ref="AD91:AD93"/>
     <mergeCell ref="N34:N36"/>
-    <mergeCell ref="H62:H71"/>
     <mergeCell ref="AD85:AD87"/>
     <mergeCell ref="N28:N30"/>
     <mergeCell ref="V25:V27"/>
@@ -8967,6 +8779,7 @@
     <mergeCell ref="AB40:AB42"/>
     <mergeCell ref="AD40:AD42"/>
     <mergeCell ref="AH4:AH6"/>
+    <mergeCell ref="L47:L53"/>
     <mergeCell ref="AS52:AS54"/>
     <mergeCell ref="AG76:AG78"/>
     <mergeCell ref="Q19:Q21"/>
@@ -8980,7 +8793,6 @@
     <mergeCell ref="F52:F54"/>
     <mergeCell ref="J16:J18"/>
     <mergeCell ref="Y28:Y30"/>
-    <mergeCell ref="AB25:AB28"/>
     <mergeCell ref="J43:J45"/>
     <mergeCell ref="AL88:AL90"/>
     <mergeCell ref="R67:R69"/>
@@ -9023,6 +8835,7 @@
     <mergeCell ref="E76:E78"/>
     <mergeCell ref="AO10:AO12"/>
     <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="D58:D60"/>
     <mergeCell ref="Z79:Z81"/>
     <mergeCell ref="F58:F60"/>
     <mergeCell ref="AH70:AH72"/>
@@ -9040,6 +8853,7 @@
     <mergeCell ref="I61:I63"/>
     <mergeCell ref="AP4:AP6"/>
     <mergeCell ref="AP25:AP27"/>
+    <mergeCell ref="X65:X81"/>
     <mergeCell ref="U22:U24"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="J88:J90"/>
@@ -9060,6 +8874,7 @@
     <mergeCell ref="AH73:AH75"/>
     <mergeCell ref="AO3:AR3"/>
     <mergeCell ref="AP73:AP75"/>
+    <mergeCell ref="H73:H95"/>
     <mergeCell ref="AB16:AB18"/>
     <mergeCell ref="Y79:Y81"/>
     <mergeCell ref="AL91:AL93"/>
@@ -9069,6 +8884,7 @@
     <mergeCell ref="Y73:Y75"/>
     <mergeCell ref="AD25:AD27"/>
     <mergeCell ref="AG70:AG72"/>
+    <mergeCell ref="L10:L17"/>
     <mergeCell ref="AD61:AD63"/>
     <mergeCell ref="R85:R87"/>
     <mergeCell ref="B28:B30"/>
